--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4009E25-4EA4-4B4D-9298-3641F1E95990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="AHL" sheetId="1" r:id="rId1"/>
-    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
-    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
-    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
+    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="269">
   <si>
     <t>sl</t>
   </si>
@@ -294,24 +280,24 @@
     <t>2024-10-23</t>
   </si>
   <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>2024-10-24</t>
+  </si>
+  <si>
+    <t>2024-11-14</t>
+  </si>
+  <si>
     <t>2024-10-27</t>
   </si>
   <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-10-24</t>
-  </si>
-  <si>
-    <t>2024-11-14</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
     <t>2024-10-16</t>
   </si>
   <si>
@@ -348,27 +334,27 @@
     <t>2024-11-02</t>
   </si>
   <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
     <t>2024-12-04</t>
   </si>
   <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
-    <t>2024-11-12</t>
-  </si>
-  <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
     <t>2024-11-26</t>
   </si>
   <si>
@@ -465,10 +451,10 @@
     <t>Eishalle Celje;HlavatyAl;WidmannFl;LegatKo;WuchererGe</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;RuetzMa;SpiegelSe;JägerRi;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;LazzeriAl;RivisFe;EislCh;RinkerDa</t>
+    <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;LazzeriAl;RivisFe;RinkerDa;StrimitzerDa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;HolzerTo;RuetzMa;JägerRi;SeewaldJe</t>
@@ -492,7 +478,7 @@
     <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;MoschenAn;SoraperraSi;CristeliMa;FormaioniTh</t>
+    <t>Eishalle Sterzing;MoschenAn;SoraperraSi;CusinFe;FormaioniTh</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
@@ -528,7 +514,7 @@
     <t>Eishalle Sissek Zibel;SnojTa;WidmannFl;ArlicMa;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Cortina;EggerTh;HolzerTo;CusinFe;JägerRi</t>
+    <t>Eishalle Ritten;EggerTh;HolzerTo;CusinFe;JägerRi</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;HuberRe;MoschenAn;IlmerNo;StrimitzerDa</t>
@@ -549,10 +535,10 @@
     <t>Eishalle Ritten;EggerTh;PinieOm;FleischmannLu;PaceJa</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CristeliMa</t>
-  </si>
-  <si>
-    <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;GrisentiLu</t>
+    <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CusinFe</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;RuetzMa;SpiegelSe;EislCh;JägerRi</t>
   </si>
   <si>
     <t>Eisarena Salzburg;MeixnerSe;MoschenAn;CristeliMa;MoidlMa</t>
@@ -675,7 +661,7 @@
     <t>Eisarena Salzburg;HolzerTo;HuberRe;MattheyPh;RinkerDa</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;GiacomozziFe;StefenelliFe;BrondiPa;GrisentiLu</t>
+    <t>Würtharena Neumarkt;MoschenAn;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;BrockAd;OrelSt;WendnerMa;WuchererGe</t>
@@ -687,7 +673,7 @@
     <t>Eishalle Meran;LesniakBo;OrelSt;MarkizetiGr;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Ritten;LazzeriAl;PirasAn;GrisentiLu;ScalzeriAl</t>
+    <t>Eishalle Ritten;EggerTh;LazzeriAl;GrisentiLu;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Ritten;MoschenAn;SpiegelSe;FecchioFe;JägerRi</t>
@@ -726,7 +712,7 @@
     <t>Eishalle Gröden;LazzeriAl;SoraperraSi;CusinFe;FormaioniTh</t>
   </si>
   <si>
-    <t>Eishalle Cortina;EggerTh;LebenJa;AbeltinoSi;IlmerNo</t>
+    <t>Eishalle Cortina;LebenJa;PirasAn;AbeltinoSi;IlmerNo</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;EggerTh;RuetzMa;DivisDo;IlmerNo</t>
@@ -738,13 +724,13 @@
     <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;DivisDo;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;BenvegnuAn;RivisFe;FecchioFe;RivisAn</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;StefenelliFe;VirtaTu;CusinFe;FleischmannLu</t>
-  </si>
-  <si>
-    <t>Eishalle Cortina;LegaSi;VirtaTu;CusinFe;IlmerNo</t>
+    <t>Eishalle Sterzing;HuberRe;RivisFe;FecchioFe;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;StefenelliFe;VirtaTu;CristeliMa;FleischmannLu</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;LegaSi;VirtaTu;CristeliMa;IlmerNo</t>
   </si>
   <si>
     <t>Eishalle Gröden;GiacomozziFe;MoidlDa;MattheyPh;MoidlMa</t>
@@ -780,7 +766,7 @@
     <t>vse delegacije</t>
   </si>
   <si>
-    <t>procenti delegacij</t>
+    <t>Procenti delegacij</t>
   </si>
   <si>
     <t>slo</t>
@@ -789,45 +775,102 @@
     <t>-</t>
   </si>
   <si>
-    <t>klubi</t>
-  </si>
-  <si>
-    <t>predviden procent</t>
-  </si>
-  <si>
-    <t>dejanski</t>
-  </si>
-  <si>
-    <t>slo+hr</t>
-  </si>
-  <si>
-    <t>aut</t>
+    <t>No. Teams</t>
+  </si>
+  <si>
+    <t>% per team</t>
+  </si>
+  <si>
+    <t>Actual %</t>
+  </si>
+  <si>
+    <t>Expected assignments</t>
+  </si>
+  <si>
+    <t>Actual assignments</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Difference in games</t>
+  </si>
+  <si>
+    <t>Slo</t>
+  </si>
+  <si>
+    <t>It</t>
   </si>
   <si>
     <t>kotrola</t>
+  </si>
+  <si>
+    <t>Aut</t>
+  </si>
+  <si>
+    <t>kontrola</t>
+  </si>
+  <si>
+    <t>till 7.12.2024</t>
+  </si>
+  <si>
+    <t>% games per team</t>
+  </si>
+  <si>
+    <t>Data untill 7.12.2024</t>
+  </si>
+  <si>
+    <t>Expected assignmnets per country based on team %</t>
+  </si>
+  <si>
+    <t>Actual assigned games per country</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="238"/>
+      <color rgb="FF9C0006"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="238"/>
+      <color rgb="FF006100"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -836,25 +879,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -866,23 +909,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.3999755851924192"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="22">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1037,19 +1111,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1080,9 +1141,7 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1095,9 +1154,57 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -1108,7 +1215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1116,53 +1223,135 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1442,9 +1631,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BP73"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BQ73"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -1515,7 +1704,7 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
         <v>9</v>
@@ -1569,8 +1758,8 @@
         <v>1</v>
       </c>
       <c r="N1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>COUNTIF(N4:N69,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="O1">
         <f>COUNTIF(O4:O69,"&lt;&gt;")</f>
@@ -1598,7 +1787,7 @@
       </c>
       <c r="U1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V68,"&lt;&gt;")</f>
@@ -1625,15 +1814,15 @@
         <v>8</v>
       </c>
       <c r="AB1">
-        <f>COUNTIF(AB4:AB69,"&lt;&gt;")</f>
-        <v>8</v>
+        <f>COUNTIF(AB4:AB68,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="AC1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="AD1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(AD4:AD69,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AE1">
@@ -1641,7 +1830,7 @@
         <v>8</v>
       </c>
       <c r="AF1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(AF4:AF66,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AG1">
@@ -1657,11 +1846,11 @@
         <v>3</v>
       </c>
       <c r="AJ1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(AJ4:AJ68,"&lt;&gt;")</f>
         <v>7</v>
       </c>
       <c r="AK1">
-        <f t="shared" ref="AK1" si="2">COUNTIF(AK4:AK69,"&lt;&gt;")</f>
+        <f>COUNTIF(AK4:AK67,"&lt;&gt;")</f>
         <v>7</v>
       </c>
       <c r="AL1">
@@ -1678,10 +1867,10 @@
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO69,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(AP4:AP68,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AQ1">
@@ -1697,7 +1886,7 @@
         <v>8</v>
       </c>
       <c r="AT1">
-        <f>COUNTIF(AT4:AT69,"&lt;&gt;")</f>
+        <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="AU1">
@@ -1721,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AZ1">
-        <f>COUNTIF(AZ4:AZ69,"&lt;&gt;")</f>
+        <f>COUNTIF(AZ4:AZ66,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="BA1">
@@ -1753,43 +1942,43 @@
         <v>4</v>
       </c>
       <c r="BH1">
-        <f t="shared" ref="BH1:BP1" si="3">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
+        <f t="shared" ref="BH1:BP1" si="2">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
         <v>4</v>
       </c>
       <c r="BI1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="BJ1">
-        <f t="shared" ref="BJ1" si="4">COUNTIF(BJ4:BJ69,"&lt;&gt;")</f>
+        <f t="shared" ref="BJ1" si="3">COUNTIF(BJ4:BJ69,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="BK1">
-        <f>COUNTIF(BK4:BK69,"&lt;&gt;")</f>
+        <f>COUNTIF(BK4:BK66,"&lt;&gt;")</f>
         <v>7</v>
       </c>
       <c r="BL1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="BM1">
-        <f t="shared" ref="BM1" si="5">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
+        <f t="shared" ref="BM1" si="4">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="BN1">
-        <f t="shared" si="3"/>
+        <f>COUNTIF(BN4:BN69,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="BO1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="BP1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1995,7 +2184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2197,11 +2386,11 @@
       <c r="BO3" t="s">
         <v>70</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BP3" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -2407,7 +2596,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -2444,7 +2633,7 @@
       <c r="L5" t="s">
         <v>79</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="7"/>
       <c r="N5" t="s">
         <v>74</v>
       </c>
@@ -2475,7 +2664,7 @@
       <c r="W5" t="s">
         <v>75</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="X5" s="7" t="s">
         <v>89</v>
       </c>
       <c r="Y5" t="s">
@@ -2508,7 +2697,7 @@
       <c r="AH5" t="s">
         <v>90</v>
       </c>
-      <c r="AI5" s="6" t="s">
+      <c r="AI5" s="7" t="s">
         <v>91</v>
       </c>
       <c r="AJ5" t="s">
@@ -2575,29 +2764,29 @@
         <v>96</v>
       </c>
       <c r="BE5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="BF5" t="s">
         <v>76</v>
       </c>
-      <c r="BG5" s="6" t="s">
+      <c r="BG5" s="7" t="s">
         <v>97</v>
       </c>
       <c r="BH5" t="s">
         <v>98</v>
       </c>
-      <c r="BI5" s="6"/>
+      <c r="BI5" s="7"/>
       <c r="BJ5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="BK5" t="s">
-        <v>92</v>
-      </c>
-      <c r="BL5" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="BL5" s="7"/>
       <c r="BM5" t="s">
         <v>80</v>
       </c>
-      <c r="BN5" s="6" t="s">
+      <c r="BN5" s="7" t="s">
         <v>89</v>
       </c>
       <c r="BO5" t="s">
@@ -2607,7 +2796,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -2635,7 +2824,7 @@
       <c r="I6" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>97</v>
       </c>
       <c r="K6" t="s">
@@ -2687,7 +2876,7 @@
         <v>93</v>
       </c>
       <c r="AB6" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AC6" t="s">
         <v>79</v>
@@ -2710,8 +2899,8 @@
       <c r="AI6" t="s">
         <v>102</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>87</v>
+      <c r="AJ6" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="AK6" t="s">
         <v>78</v>
@@ -2773,10 +2962,10 @@
       <c r="BD6" t="s">
         <v>95</v>
       </c>
-      <c r="BE6" s="6" t="s">
+      <c r="BE6" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="BF6" s="6" t="s">
+      <c r="BF6" s="7" t="s">
         <v>89</v>
       </c>
       <c r="BG6" t="s">
@@ -2785,26 +2974,26 @@
       <c r="BH6" t="s">
         <v>104</v>
       </c>
-      <c r="BJ6" s="6" t="s">
+      <c r="BJ6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="BK6" t="s">
-        <v>96</v>
-      </c>
-      <c r="BM6" s="6" t="s">
+      <c r="BK6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BM6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="BN6" t="s">
+        <v>102</v>
+      </c>
+      <c r="BO6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP6" t="s">
         <v>105</v>
       </c>
-      <c r="BO6" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>106</v>
-      </c>
     </row>
-    <row r="7" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>95</v>
       </c>
@@ -2821,7 +3010,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G7" t="s">
         <v>90</v>
@@ -2830,7 +3019,7 @@
         <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J7" t="s">
         <v>89</v>
@@ -2872,7 +3061,7 @@
         <v>83</v>
       </c>
       <c r="X7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y7" t="s">
         <v>79</v>
@@ -2883,8 +3072,8 @@
       <c r="AA7" t="s">
         <v>101</v>
       </c>
-      <c r="AB7" t="s">
-        <v>101</v>
+      <c r="AB7" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="AC7" t="s">
         <v>94</v>
@@ -2896,19 +3085,19 @@
         <v>95</v>
       </c>
       <c r="AF7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AG7" t="s">
         <v>78</v>
       </c>
-      <c r="AH7" s="6" t="s">
+      <c r="AH7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AJ7" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK7" s="6" t="s">
-        <v>107</v>
+      <c r="AJ7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK7" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="AL7" t="s">
         <v>80</v>
@@ -2976,26 +3165,26 @@
       <c r="BG7" t="s">
         <v>99</v>
       </c>
-      <c r="BH7" s="6" t="s">
+      <c r="BH7" s="7" t="s">
         <v>100</v>
       </c>
       <c r="BJ7" t="s">
         <v>99</v>
       </c>
-      <c r="BK7" s="6" t="s">
-        <v>109</v>
+      <c r="BK7" t="s">
+        <v>107</v>
       </c>
       <c r="BM7" t="s">
         <v>100</v>
       </c>
       <c r="BN7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="BO7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -3012,25 +3201,25 @@
         <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>108</v>
       </c>
       <c r="H8" t="s">
         <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K8" t="s">
         <v>76</v>
       </c>
-      <c r="L8" s="6" t="s">
-        <v>107</v>
+      <c r="L8" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="N8" t="s">
         <v>81</v>
@@ -3071,13 +3260,13 @@
       <c r="AA8" t="s">
         <v>78</v>
       </c>
-      <c r="AB8" s="6" t="s">
-        <v>99</v>
+      <c r="AB8" t="s">
+        <v>91</v>
       </c>
       <c r="AC8" t="s">
         <v>78</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AD8" s="6" t="s">
         <v>101</v>
       </c>
       <c r="AE8" t="s">
@@ -3093,13 +3282,13 @@
         <v>89</v>
       </c>
       <c r="AJ8" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="AK8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="AL8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AM8" t="s">
         <v>76</v>
@@ -3108,7 +3297,7 @@
         <v>76</v>
       </c>
       <c r="AO8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AP8" t="s">
         <v>90</v>
@@ -3153,7 +3342,7 @@
         <v>104</v>
       </c>
       <c r="BD8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="BE8" t="s">
         <v>102</v>
@@ -3162,7 +3351,7 @@
         <v>91</v>
       </c>
       <c r="BJ8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BK8" t="s">
         <v>110</v>
@@ -3171,18 +3360,18 @@
         <v>108</v>
       </c>
       <c r="BN8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
         <v>95</v>
@@ -3190,22 +3379,22 @@
       <c r="E9" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>107</v>
+      <c r="K9" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="L9" t="s">
         <v>102</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="6" t="s">
         <v>98</v>
       </c>
       <c r="O9" t="s">
@@ -3218,7 +3407,7 @@
         <v>95</v>
       </c>
       <c r="R9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="S9" t="s">
         <v>98</v>
@@ -3229,7 +3418,7 @@
       <c r="U9" t="s">
         <v>80</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="V9" s="7" t="s">
         <v>89</v>
       </c>
       <c r="W9" t="s">
@@ -3241,37 +3430,37 @@
       <c r="Z9" t="s">
         <v>90</v>
       </c>
-      <c r="AA9" s="6" t="s">
+      <c r="AA9" s="7" t="s">
         <v>91</v>
       </c>
       <c r="AB9" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AC9" t="s">
         <v>80</v>
       </c>
-      <c r="AD9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE9" s="6" t="s">
+      <c r="AD9" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="7" t="s">
         <v>89</v>
       </c>
       <c r="AF9" t="s">
         <v>90</v>
       </c>
       <c r="AG9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH9" t="s">
         <v>108</v>
       </c>
       <c r="AJ9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL9" s="7" t="s">
         <v>99</v>
       </c>
       <c r="AM9" t="s">
@@ -3283,22 +3472,22 @@
       <c r="AO9" t="s">
         <v>86</v>
       </c>
-      <c r="AP9" s="6" t="s">
+      <c r="AP9" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AQ9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AR9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AS9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT9" t="s">
         <v>78</v>
       </c>
-      <c r="AU9" s="6" t="s">
+      <c r="AU9" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AV9" t="s">
@@ -3317,38 +3506,38 @@
         <v>86</v>
       </c>
       <c r="BA9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BB9" t="s">
         <v>87</v>
       </c>
-      <c r="BB9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BC9" s="6" t="s">
+      <c r="BC9" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="BD9" s="6" t="s">
+      <c r="BD9" s="7" t="s">
         <v>99</v>
       </c>
       <c r="BE9" t="s">
         <v>108</v>
       </c>
       <c r="BF9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BK9" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B10" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>89</v>
       </c>
       <c r="E10" t="s">
@@ -3366,13 +3555,13 @@
       <c r="L10" t="s">
         <v>108</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>91</v>
+      <c r="N10" t="s">
+        <v>110</v>
       </c>
       <c r="O10" t="s">
         <v>90</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="7" t="s">
         <v>91</v>
       </c>
       <c r="Q10" t="s">
@@ -3385,72 +3574,72 @@
         <v>76</v>
       </c>
       <c r="T10" t="s">
-        <v>87</v>
-      </c>
-      <c r="U10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="U10" s="7" t="s">
         <v>99</v>
       </c>
       <c r="V10" t="s">
         <v>91</v>
       </c>
       <c r="W10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Y10" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>107</v>
+        <v>87</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="AA10" t="s">
         <v>100</v>
       </c>
       <c r="AB10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AC10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AD10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AE10" t="s">
-        <v>105</v>
-      </c>
-      <c r="AF10" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AG10" s="6" t="s">
+      <c r="AG10" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AJ10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK10" t="s">
         <v>102</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>106</v>
       </c>
       <c r="AL10" t="s">
         <v>91</v>
       </c>
-      <c r="AM10" s="6" t="s">
+      <c r="AM10" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AN10" s="6" t="s">
+      <c r="AN10" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AO10" s="6" t="s">
+      <c r="AO10" s="7" t="s">
         <v>89</v>
       </c>
       <c r="AP10" t="s">
         <v>89</v>
       </c>
-      <c r="AQ10" s="6" t="s">
+      <c r="AQ10" s="7" t="s">
         <v>91</v>
       </c>
       <c r="AR10" t="s">
         <v>76</v>
       </c>
-      <c r="AS10" s="6" t="s">
+      <c r="AS10" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AT10" t="s">
@@ -3462,20 +3651,20 @@
       <c r="AV10" t="s">
         <v>98</v>
       </c>
-      <c r="AW10" s="6" t="s">
+      <c r="AW10" s="7" t="s">
         <v>99</v>
       </c>
       <c r="AX10" t="s">
-        <v>92</v>
-      </c>
-      <c r="AY10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY10" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AZ10" t="s">
         <v>80</v>
       </c>
       <c r="BA10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="BB10" t="s">
         <v>90</v>
@@ -3484,13 +3673,13 @@
         <v>102</v>
       </c>
       <c r="BD10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BK10" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -3503,19 +3692,19 @@
       <c r="D11" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>99</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K11" t="s">
         <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>111</v>
-      </c>
-      <c r="O11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="O11" s="7" t="s">
         <v>99</v>
       </c>
       <c r="P11" t="s">
@@ -3530,7 +3719,7 @@
       <c r="S11" t="s">
         <v>90</v>
       </c>
-      <c r="T11" s="6" t="s">
+      <c r="T11" s="7" t="s">
         <v>91</v>
       </c>
       <c r="U11" t="s">
@@ -3539,7 +3728,7 @@
       <c r="W11" t="s">
         <v>90</v>
       </c>
-      <c r="Y11" s="6" t="s">
+      <c r="Y11" s="7" t="s">
         <v>86</v>
       </c>
       <c r="Z11" t="s">
@@ -3548,26 +3737,23 @@
       <c r="AA11" t="s">
         <v>102</v>
       </c>
-      <c r="AB11" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC11" s="6" t="s">
+      <c r="AC11" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AD11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AE11" t="s">
         <v>91</v>
       </c>
       <c r="AF11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG11" t="s">
         <v>89</v>
       </c>
       <c r="AL11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AM11" t="s">
         <v>89</v>
@@ -3575,25 +3761,28 @@
       <c r="AN11" t="s">
         <v>89</v>
       </c>
+      <c r="AO11" t="s">
+        <v>91</v>
+      </c>
       <c r="AP11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AQ11" t="s">
         <v>102</v>
       </c>
-      <c r="AR11" s="6" t="s">
+      <c r="AR11" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AS11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AT11" t="s">
         <v>80</v>
       </c>
       <c r="AU11" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AV11" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AW11" t="s">
@@ -3605,37 +3794,37 @@
       <c r="AY11" t="s">
         <v>89</v>
       </c>
-      <c r="AZ11" s="6" t="s">
+      <c r="AZ11" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="BA11" s="6" t="s">
+      <c r="BA11" s="7" t="s">
         <v>89</v>
       </c>
       <c r="BB11" t="s">
         <v>86</v>
       </c>
       <c r="BC11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BD11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
       </c>
       <c r="N12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="O12" t="s">
         <v>91</v>
@@ -3643,13 +3832,13 @@
       <c r="P12" t="s">
         <v>102</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="Q12" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="R12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="S12" s="6" t="s">
+      <c r="R12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="S12" s="7" t="s">
         <v>109</v>
       </c>
       <c r="T12" t="s">
@@ -3658,7 +3847,7 @@
       <c r="U12" t="s">
         <v>100</v>
       </c>
-      <c r="W12" s="6" t="s">
+      <c r="W12" s="7" t="s">
         <v>97</v>
       </c>
       <c r="Y12" t="s">
@@ -3671,10 +3860,10 @@
         <v>99</v>
       </c>
       <c r="AD12" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="AF12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AG12" t="s">
         <v>99</v>
@@ -3686,7 +3875,7 @@
         <v>99</v>
       </c>
       <c r="AP12" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="AQ12" t="s">
         <v>108</v>
@@ -3694,7 +3883,7 @@
       <c r="AR12" t="s">
         <v>89</v>
       </c>
-      <c r="AT12" s="6" t="s">
+      <c r="AT12" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AV12" t="s">
@@ -3703,7 +3892,7 @@
       <c r="AW12" t="s">
         <v>108</v>
       </c>
-      <c r="AX12" s="6" t="s">
+      <c r="AX12" s="7" t="s">
         <v>97</v>
       </c>
       <c r="AY12" t="s">
@@ -3715,17 +3904,14 @@
       <c r="BA12" t="s">
         <v>99</v>
       </c>
-      <c r="BB12" s="6" t="s">
+      <c r="BB12" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>102</v>
       </c>
-      <c r="N13" t="s">
-        <v>108</v>
-      </c>
       <c r="O13" t="s">
         <v>100</v>
       </c>
@@ -3742,10 +3928,10 @@
         <v>91</v>
       </c>
       <c r="T13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W13" t="s">
         <v>100</v>
@@ -3760,46 +3946,49 @@
         <v>102</v>
       </c>
       <c r="AN13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AR13" t="s">
         <v>99</v>
       </c>
       <c r="AT13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AV13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AX13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY13" t="s">
         <v>105</v>
       </c>
-      <c r="AY13" t="s">
-        <v>106</v>
-      </c>
       <c r="AZ13" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="BA13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BB13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
       <c r="O14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q14" t="s">
         <v>100</v>
       </c>
       <c r="R14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S14" t="s">
         <v>100</v>
       </c>
+      <c r="U14" t="s">
+        <v>90</v>
+      </c>
       <c r="W14" t="s">
         <v>102</v>
       </c>
@@ -3807,21 +3996,21 @@
         <v>102</v>
       </c>
       <c r="AT14" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AX14" t="s">
         <v>112</v>
       </c>
       <c r="AZ14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="BB14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="15:54" x14ac:dyDescent="0.25">
       <c r="Q15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R15" t="s">
         <v>112</v>
@@ -3833,10 +4022,10 @@
         <v>108</v>
       </c>
       <c r="AT15" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3896,14 +4085,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:AO42"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -3948,7 +4137,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -4010,7 +4199,7 @@
         <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -4022,7 +4211,7 @@
         <v>104</v>
       </c>
       <c r="Y3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Z3" t="s">
         <v>90</v>
@@ -4034,7 +4223,7 @@
         <v>97</v>
       </c>
       <c r="AC3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="s">
         <v>89</v>
@@ -4046,16 +4235,16 @@
         <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AI3" t="s">
         <v>91</v>
       </c>
       <c r="AJ3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="s">
         <v>100</v>
@@ -4070,10 +4259,10 @@
         <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4168,7 +4357,7 @@
         <v>68</v>
       </c>
       <c r="AF4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="AG4" t="s">
         <v>21</v>
@@ -4198,7 +4387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4293,7 +4482,7 @@
         <v>54</v>
       </c>
       <c r="AF5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="s">
         <v>34</v>
@@ -4323,7 +4512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4418,10 +4607,10 @@
         <v>51</v>
       </c>
       <c r="AF6" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="AH6" t="s">
         <v>66</v>
@@ -4445,10 +4634,10 @@
         <v>52</v>
       </c>
       <c r="AO6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4543,10 +4732,10 @@
         <v>43</v>
       </c>
       <c r="AF7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG7" t="s">
         <v>55</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>53</v>
       </c>
       <c r="AH7" t="s">
         <v>59</v>
@@ -4573,7 +4762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4632,7 +4821,7 @@
         <v>31</v>
       </c>
       <c r="AF8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="AI8" t="s">
         <v>46</v>
@@ -4650,7 +4839,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -4709,7 +4898,7 @@
         <v>18</v>
       </c>
       <c r="AF9" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="AI9" t="s">
         <v>24</v>
@@ -4727,7 +4916,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -4786,7 +4975,7 @@
         <v>32</v>
       </c>
       <c r="AF10" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="AI10" t="s">
         <v>40</v>
@@ -4804,7 +4993,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -4860,10 +5049,10 @@
         <v>37</v>
       </c>
       <c r="AE11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AF11" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="AI11" t="s">
         <v>61</v>
@@ -4881,7 +5070,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -4949,7 +5138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -5017,7 +5206,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -5085,7 +5274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -5153,7 +5342,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -5194,7 +5383,7 @@
         <v>56</v>
       </c>
       <c r="Z16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AB16" t="s">
         <v>58</v>
@@ -5206,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="AI16" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="AK16" t="s">
         <v>24</v>
@@ -5218,7 +5407,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -5271,7 +5460,7 @@
         <v>47</v>
       </c>
       <c r="AI17" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="s">
         <v>45</v>
@@ -5283,7 +5472,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -5348,7 +5537,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5413,7 +5602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -5442,7 +5631,7 @@
         <v>21</v>
       </c>
       <c r="Y20" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="AB20" t="s">
         <v>39</v>
@@ -5454,7 +5643,7 @@
         <v>56</v>
       </c>
       <c r="AI20" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="AK20" t="s">
         <v>29</v>
@@ -5466,7 +5655,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -5495,7 +5684,7 @@
         <v>18</v>
       </c>
       <c r="Y21" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AB21" t="s">
         <v>49</v>
@@ -5519,7 +5708,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -5563,16 +5752,16 @@
         <v>19</v>
       </c>
       <c r="AK22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AO22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -5625,7 +5814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -5651,7 +5840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -5677,7 +5866,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -5703,7 +5892,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -5729,11 +5918,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="28:41" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5749,10 +5938,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:AO14"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -5834,7 +6023,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -5896,7 +6085,7 @@
         <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -5908,7 +6097,7 @@
         <v>104</v>
       </c>
       <c r="Y3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Z3" t="s">
         <v>90</v>
@@ -5920,7 +6109,7 @@
         <v>97</v>
       </c>
       <c r="AC3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="s">
         <v>89</v>
@@ -5932,16 +6121,16 @@
         <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AI3" t="s">
         <v>91</v>
       </c>
       <c r="AJ3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="s">
         <v>100</v>
@@ -5956,10 +6145,10 @@
         <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>113</v>
       </c>
@@ -6084,7 +6273,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -6161,7 +6350,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>179</v>
       </c>
@@ -6229,7 +6418,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>201</v>
       </c>
@@ -6294,7 +6483,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>222</v>
       </c>
@@ -6347,7 +6536,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
         <v>239</v>
       </c>
@@ -6373,69 +6562,77 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="28:41" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" customWidth="1"/>
+    <col min="18" max="18" width="11.5703125" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="7">
+      <c r="B1" s="9"/>
+      <c r="C1" s="10">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="8">
+      <c r="B2" s="12"/>
+      <c r="C2" s="13">
         <f>C1*4</f>
         <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="15">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>536</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="18">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>76</v>
       </c>
@@ -6451,120 +6648,425 @@
       <c r="H4" t="s">
         <v>254</v>
       </c>
+      <c r="I4" t="s">
+        <v>255</v>
+      </c>
+      <c r="J4" t="s">
+        <v>256</v>
+      </c>
+      <c r="K4" t="s">
+        <v>257</v>
+      </c>
+      <c r="L4" t="s">
+        <v>258</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="18">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>16</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="20">
         <v>2</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="21">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="22">
         <f>B4/B3</f>
         <v>0.1417910447761194</v>
       </c>
+      <c r="I5" s="23">
+        <f>C2*G5</f>
+        <v>82.46153846153847</v>
+      </c>
+      <c r="J5">
+        <f>B4</f>
+        <v>76</v>
+      </c>
+      <c r="K5" s="24">
+        <f>J5-I5</f>
+        <v>-6.461538461538467</v>
+      </c>
+      <c r="L5" s="25">
+        <f>K5/4</f>
+        <v>-1.6153846153846168</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="18">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>213</v>
-      </c>
-      <c r="E6" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="20">
         <v>1</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="21">
         <f>F6/13</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="H6" s="16">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H6" s="22">
         <f>B5/B3</f>
-        <v>2.9850746268656716E-2</v>
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="I6" s="23">
+        <f>C2*G6</f>
+        <v>41.23076923076923</v>
+      </c>
+      <c r="J6">
+        <f>B5</f>
+        <v>16</v>
+      </c>
+      <c r="K6" s="24">
+        <f>J6-I6</f>
+        <v>-25.230769230769234</v>
+      </c>
+      <c r="L6" s="25">
+        <f t="shared" ref="L6" si="0">K6/4</f>
+        <v>-6.307692307692308</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="27">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>231</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="F7" s="20">
+        <v>232</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="F7" s="29">
         <v>3</v>
       </c>
-      <c r="G7" s="21">
-        <f t="shared" ref="G7:G9" si="0">F7/13</f>
+      <c r="G7" s="30">
+        <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="31">
         <f>(B5+B4)/B3</f>
         <v>0.17164179104477612</v>
       </c>
+      <c r="I7" s="23">
+        <f>C2*G7</f>
+        <v>123.6923076923077</v>
+      </c>
+      <c r="J7">
+        <f>B4+B5</f>
+        <v>92</v>
+      </c>
+      <c r="K7" s="24">
+        <f>J7-I7</f>
+        <v>-31.692307692307693</v>
+      </c>
+      <c r="L7" s="25">
+        <f>K7/4</f>
+        <v>-7.923076923076923</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="24">
+    <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E8" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="33">
         <v>6</v>
       </c>
-      <c r="G8" s="25">
-        <f t="shared" si="0"/>
+      <c r="G8" s="34">
+        <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="35">
         <f>B6/B3</f>
-        <v>0.39738805970149255</v>
+        <v>0.39552238805970147</v>
+      </c>
+      <c r="I8" s="23">
+        <f>C2*G8</f>
+        <v>247.3846153846154</v>
+      </c>
+      <c r="J8">
+        <f>B6</f>
+        <v>212</v>
+      </c>
+      <c r="K8" s="24">
+        <f>J8-I8</f>
+        <v>-35.38461538461539</v>
+      </c>
+      <c r="L8" s="25">
+        <f>K8/4</f>
+        <v>-8.846153846153847</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>536</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" s="33">
+        <v>4</v>
+      </c>
+      <c r="G9" s="34">
+        <f t="shared" si="1"/>
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H9" s="35">
+        <f>B7/B3</f>
+        <v>0.43283582089552236</v>
+      </c>
+      <c r="I9" s="23">
+        <f>C2*G9</f>
+        <v>164.92307692307693</v>
+      </c>
+      <c r="J9">
+        <f>B7</f>
+        <v>232</v>
+      </c>
+      <c r="K9" s="36">
+        <f>J9-I9</f>
+        <v>67.07692307692307</v>
+      </c>
+      <c r="L9" s="25">
+        <f>K9/4</f>
+        <v>16.769230769230766</v>
+      </c>
+    </row>
+    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="I11" s="38">
+        <f>SUM(I7:I9)</f>
+        <v>536</v>
+      </c>
+      <c r="J11" s="32">
+        <f>SUM(J7:J9)</f>
+        <v>536</v>
+      </c>
+      <c r="K11" s="39">
+        <f>SUM(K7:K9)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="40">
+        <f>SUM(L7:L9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>264</v>
+      </c>
+      <c r="F16" t="s">
+        <v>252</v>
+      </c>
+      <c r="G16" t="s">
+        <v>265</v>
+      </c>
+      <c r="H16" t="s">
+        <v>254</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="J16" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="F9" s="24">
+      <c r="K16" t="s">
+        <v>257</v>
+      </c>
+      <c r="L16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F17" s="43">
+        <v>3</v>
+      </c>
+      <c r="G17" s="44">
+        <f t="shared" ref="G17:G19" si="2">F17/13</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="H17" s="45">
+        <f>(B5+B4)/B3</f>
+        <v>0.17164179104477612</v>
+      </c>
+      <c r="I17" s="46">
+        <f>B3*G17</f>
+        <v>123.6923076923077</v>
+      </c>
+      <c r="J17" s="47">
+        <f>B5+B4</f>
+        <v>92</v>
+      </c>
+      <c r="K17" s="48">
+        <f>J17-I17</f>
+        <v>-31.692307692307693</v>
+      </c>
+      <c r="L17" s="25">
+        <f>K17/4</f>
+        <v>-7.923076923076923</v>
+      </c>
+    </row>
+    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E18" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" s="50">
+        <v>6</v>
+      </c>
+      <c r="G18" s="51">
+        <f t="shared" si="2"/>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H18" s="52">
+        <f>B6/B3</f>
+        <v>0.39552238805970147</v>
+      </c>
+      <c r="I18" s="53">
+        <f>B3*G18</f>
+        <v>247.3846153846154</v>
+      </c>
+      <c r="J18" s="54">
+        <f>B6</f>
+        <v>212</v>
+      </c>
+      <c r="K18" s="55">
+        <f>J18-I18</f>
+        <v>-35.38461538461539</v>
+      </c>
+      <c r="L18" s="25">
+        <f>K18/4</f>
+        <v>-8.846153846153847</v>
+      </c>
+      <c r="Q18" s="56"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" s="58">
         <v>4</v>
       </c>
-      <c r="G9" s="25">
-        <f t="shared" si="0"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H9" s="26">
+      <c r="G19" s="59">
+        <f t="shared" si="2"/>
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H19" s="60">
         <f>B7/B3</f>
-        <v>0.43097014925373134</v>
+        <v>0.43283582089552236</v>
+      </c>
+      <c r="I19" s="61">
+        <f>B3*G19</f>
+        <v>164.92307692307693</v>
+      </c>
+      <c r="J19" s="62">
+        <f>B7</f>
+        <v>232</v>
+      </c>
+      <c r="K19" s="63">
+        <f>J19-I19</f>
+        <v>67.07692307692307</v>
+      </c>
+      <c r="L19" s="25">
+        <f>K19/4</f>
+        <v>16.769230769230766</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="P24" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="64"/>
+      <c r="S24" s="64"/>
+    </row>
+    <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P25" s="65"/>
+      <c r="Q25" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="R25" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="S25" s="68" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P26" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q26" s="32">
+        <v>247</v>
+      </c>
+      <c r="R26" s="32">
+        <v>212</v>
+      </c>
+      <c r="S26" s="18">
+        <f>R26-Q26</f>
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="27" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P27" s="69" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q27" s="32">
+        <v>124</v>
+      </c>
+      <c r="R27" s="32">
+        <v>92</v>
+      </c>
+      <c r="S27" s="18">
+        <f t="shared" ref="S27:S28" si="3">R27-Q27</f>
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P28" s="70" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q28" s="71">
+        <v>165</v>
+      </c>
+      <c r="R28" s="71">
+        <v>232</v>
+      </c>
+      <c r="S28" s="27">
+        <f t="shared" si="3"/>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="P24:S24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="273">
   <si>
     <t>sl</t>
   </si>
@@ -151,213 +151,222 @@
     <t>WuchererGe</t>
   </si>
   <si>
+    <t>Huber rRe</t>
+  </si>
+  <si>
+    <t>SpiegelSe</t>
+  </si>
+  <si>
+    <t>MeixnerSe</t>
+  </si>
+  <si>
+    <t>OrelSt</t>
+  </si>
+  <si>
+    <t>WendnerMa</t>
+  </si>
+  <si>
+    <t>RuetzMa</t>
+  </si>
+  <si>
+    <t>VoicanCh</t>
+  </si>
+  <si>
+    <t>LegatKo</t>
+  </si>
+  <si>
+    <t>PreiserJu</t>
+  </si>
+  <si>
+    <t>RinkerDa</t>
+  </si>
+  <si>
+    <t>WidmannFl</t>
+  </si>
+  <si>
+    <t>StrimitzerDa</t>
+  </si>
+  <si>
+    <t>HolzerTo</t>
+  </si>
+  <si>
+    <t>DivisDo</t>
+  </si>
+  <si>
+    <t>BrockAd</t>
+  </si>
+  <si>
+    <t>SeewaldJe</t>
+  </si>
+  <si>
+    <t>ZacherlPa</t>
+  </si>
+  <si>
+    <t>MoidlMa</t>
+  </si>
+  <si>
+    <t>WeissAl</t>
+  </si>
+  <si>
+    <t>WenuschHe</t>
+  </si>
+  <si>
+    <t>PuffWo</t>
+  </si>
+  <si>
+    <t>MattheyPh</t>
+  </si>
+  <si>
+    <t>JägerRi</t>
+  </si>
+  <si>
+    <t>SternatCh</t>
+  </si>
+  <si>
+    <t>HlavatyAl</t>
+  </si>
+  <si>
+    <t>EislCh</t>
+  </si>
+  <si>
+    <t>MoidlDa</t>
+  </si>
+  <si>
+    <t>LehnerMo</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>2024-09-26</t>
+  </si>
+  <si>
+    <t>2024-10-05</t>
+  </si>
+  <si>
+    <t>2024-09-28</t>
+  </si>
+  <si>
+    <t>2024-11-01</t>
+  </si>
+  <si>
+    <t>2024-09-22</t>
+  </si>
+  <si>
+    <t>2024-10-19</t>
+  </si>
+  <si>
+    <t>2024-10-12</t>
+  </si>
+  <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
+    <t>2024-09-24</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>2024-09-29</t>
+  </si>
+  <si>
+    <t>2024-10-03</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-10-29</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>2024-10-24</t>
+  </si>
+  <si>
+    <t>2024-11-14</t>
+  </si>
+  <si>
+    <t>2024-10-27</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>2024-10-17</t>
+  </si>
+  <si>
+    <t>2024-10-09</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+  </si>
+  <si>
+    <t>2024-11-30</t>
+  </si>
+  <si>
+    <t>2024-11-21</t>
+  </si>
+  <si>
+    <t>2024-10-31</t>
+  </si>
+  <si>
+    <t>2024-11-28</t>
+  </si>
+  <si>
+    <t>2024-10-06</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-26</t>
+  </si>
+  <si>
     <t>HuberRe</t>
   </si>
   <si>
-    <t>SpiegelSe</t>
-  </si>
-  <si>
-    <t>MeixnerSe</t>
-  </si>
-  <si>
-    <t>OrelSt</t>
-  </si>
-  <si>
-    <t>WendnerMa</t>
-  </si>
-  <si>
-    <t>RuetzMa</t>
-  </si>
-  <si>
-    <t>VoicanCh</t>
-  </si>
-  <si>
-    <t>LegatKo</t>
-  </si>
-  <si>
-    <t>PreiserJu</t>
-  </si>
-  <si>
-    <t>RinkerDa</t>
-  </si>
-  <si>
-    <t>WidmannFl</t>
-  </si>
-  <si>
-    <t>StrimitzerDa</t>
-  </si>
-  <si>
-    <t>HolzerTo</t>
-  </si>
-  <si>
-    <t>DivisDo</t>
-  </si>
-  <si>
-    <t>BrockAd</t>
-  </si>
-  <si>
-    <t>SeewaldJe</t>
-  </si>
-  <si>
-    <t>ZacherlPa</t>
-  </si>
-  <si>
-    <t>MoidlMa</t>
-  </si>
-  <si>
-    <t>WeissAl</t>
-  </si>
-  <si>
-    <t>WenuschHe</t>
-  </si>
-  <si>
-    <t>PuffWo</t>
-  </si>
-  <si>
-    <t>MattheyPh</t>
-  </si>
-  <si>
-    <t>JägerRi</t>
-  </si>
-  <si>
-    <t>SternatCh</t>
-  </si>
-  <si>
-    <t>HlavatyAl</t>
-  </si>
-  <si>
-    <t>EislCh</t>
-  </si>
-  <si>
-    <t>MoidlDa</t>
-  </si>
-  <si>
-    <t>LehnerMo</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>2024-09-26</t>
-  </si>
-  <si>
-    <t>2024-10-05</t>
-  </si>
-  <si>
-    <t>2024-09-28</t>
-  </si>
-  <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>2024-09-22</t>
-  </si>
-  <si>
-    <t>2024-10-19</t>
-  </si>
-  <si>
-    <t>2024-10-12</t>
-  </si>
-  <si>
-    <t>2024-10-29</t>
-  </si>
-  <si>
-    <t>2024-10-20</t>
-  </si>
-  <si>
-    <t>2024-09-24</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>2024-09-29</t>
-  </si>
-  <si>
-    <t>2024-10-03</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-10-24</t>
-  </si>
-  <si>
-    <t>2024-11-14</t>
-  </si>
-  <si>
-    <t>2024-10-27</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>2024-10-17</t>
-  </si>
-  <si>
-    <t>2024-10-09</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-10-25</t>
-  </si>
-  <si>
-    <t>2024-11-30</t>
-  </si>
-  <si>
-    <t>2024-11-21</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2024-11-28</t>
-  </si>
-  <si>
-    <t>2024-10-06</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-11-12</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-11-26</t>
-  </si>
-  <si>
     <t>Eishalle Sterzing;BenvegnuAn;SoraperraSi;FecchioFe;GrisentiLu</t>
   </si>
   <si>
@@ -445,7 +454,7 @@
     <t>Eishalle Ritten;MetzingerFi;StefenelliFe;CristeliMa;KnezRo</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;OrelSt;SnojTa;ArlicMa;TelesklavFa</t>
+    <t>Eishalle Jesenice;BrockAd;SnojTa;ArlicMa;TelesklavFa</t>
   </si>
   <si>
     <t>Eishalle Celje;HlavatyAl;WidmannFl;LegatKo;WuchererGe</t>
@@ -460,19 +469,19 @@
     <t>Eisarena Salzburg;HolzerTo;RuetzMa;JägerRi;SeewaldJe</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;KainbergerJu;LegaSi;CusinFe;ZacherlPa</t>
+    <t>Sportpark Kitzbühel;KainbergerJu;LegaSi;CristeliMa;ZacherlPa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;BenvegnuAn;LazzeriAl;DivisDo;JägerRi</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;HlavatyAl;WenuschHe;PreiserJu;ZacherlPa</t>
+    <t>KELIT Arena Zell am See;HlavatyAl;WenuschHe;EislCh;ZacherlPa</t>
   </si>
   <si>
     <t>Kitzbühel Sportpark;BenvegnuAn;LazzeriAl;RinkerDa;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;BrockAd;MeixnerSe;EislCh;ZacherlPa</t>
+    <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
@@ -517,7 +526,7 @@
     <t>Eishalle Ritten;EggerTh;HolzerTo;CusinFe;JägerRi</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;HuberRe;MoschenAn;IlmerNo;StrimitzerDa</t>
+    <t>Sportpark Kitzbühel;Huber rRe;MoschenAn;IlmerNo;StrimitzerDa</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;StefenelliFe;VirtaTu;BrondiPa;PaceJa</t>
@@ -541,7 +550,7 @@
     <t>Eishalle Ritten;RuetzMa;SpiegelSe;EislCh;JägerRi</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;MeixnerSe;MoschenAn;CristeliMa;MoidlMa</t>
+    <t>Eisarena Salzburg;MeixnerSe;MoschenAn;IlmerNo;MoidlMa</t>
   </si>
   <si>
     <t>Eishalle Sterzing;GiacomozziFe;RuetzMa;BrondiPa;StrimitzerDa</t>
@@ -550,10 +559,10 @@
     <t>Eishalle Sissek Zibel;LebenJa;OrelSt;MarkizetiGr;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Celje;BajtMi;MetzingerFi;KnezRo;MiklicGr</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;BrockAd;VoicanCh;LegatKo;WendnerMa</t>
+    <t>ZBRISANO</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;WeissAl</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
@@ -604,7 +613,7 @@
     <t>Eishalle Celje;VoicanCh;WidmannFl;WeissAl;WuchererGe</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WeissAl</t>
+    <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WendnerMa</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;BulovecMi;SnojTa;ArlicMa;MarkizetiGr</t>
@@ -658,7 +667,7 @@
     <t>Eishalle Sissek Zibel;LesniakBo;MetzingerFi;JavornikBl;KnezRo</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;HolzerTo;HuberRe;MattheyPh;RinkerDa</t>
+    <t>Eisarena Salzburg;HolzerTo;Huber rRe;MattheyPh;RinkerDa</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;MoschenAn;StefenelliFe;BrondiPa;GrisentiLu</t>
@@ -682,6 +691,9 @@
     <t>Eishalle Meran;MetzingerFi;PirasAn;FecchioFe;KnezRo</t>
   </si>
   <si>
+    <t>Eishalle Celje;BajtMi;MetzingerFi;KnezRo;MarkizetiGr</t>
+  </si>
+  <si>
     <t>Eishalle Meran;KainbergerJu;LehnerMo;EislCh;FleischmannLu</t>
   </si>
   <si>
@@ -706,25 +718,25 @@
     <t>Eishalle Dornbirn;GiacomozziFe;RivisFe;AbeltinoSi;DivisDo</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;EggerTh;RivisFe;AbeltinoSi;CristeliMa</t>
-  </si>
-  <si>
-    <t>Eishalle Gröden;LazzeriAl;SoraperraSi;CusinFe;FormaioniTh</t>
-  </si>
-  <si>
-    <t>Eishalle Cortina;LebenJa;PirasAn;AbeltinoSi;IlmerNo</t>
+    <t>Würtharena Neumarkt;RivisFe;SoraperraSi;AbeltinoSi;CristeliMa</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;EggerTh;LazzeriAl;CusinFe;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;LebenJa;PirasAn;AbeltinoSi;CristeliMa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;EggerTh;RuetzMa;DivisDo;IlmerNo</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;HuberRe;LehnerMo;EislCh;StrimitzerDa</t>
+    <t>Eisarena Salzburg;Huber rRe;LehnerMo;EislCh;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;DivisDo;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;HuberRe;RivisFe;FecchioFe;RivisAn</t>
+    <t>Eishalle Sterzing;Huber rRe;RivisFe;FecchioFe;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Meran;StefenelliFe;VirtaTu;CristeliMa;FleischmannLu</t>
@@ -742,7 +754,7 @@
     <t>Würtharena Neumarkt;LegaSi;RuetzMa;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Meran;LesniakBo;SnojTa;RinkerDa;StrimitzerDa</t>
+    <t>Eishalle Meran;LesniakBo;SnojTa;JeramFi;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;HolzerTo;SpiegelSe;MattheyPh;MoidlMa</t>
@@ -1701,6 +1713,7 @@
     <col min="65" max="65" width="12" customWidth="1"/>
     <col min="66" max="66" width="11.85546875" customWidth="1"/>
     <col min="67" max="67" width="11.28515625" customWidth="1"/>
+    <col min="69" max="69" width="11.140625" customWidth="1"/>
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1898,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="AW1">
-        <f>COUNTIF(AW4:AW69,"&lt;&gt;")</f>
+        <f>COUNTIF(AW4:AW68,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AX1">
@@ -1966,7 +1979,7 @@
         <v>5</v>
       </c>
       <c r="BN1">
-        <f>COUNTIF(BN4:BN69,"&lt;&gt;")</f>
+        <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="BO1">
@@ -2587,13 +2600,13 @@
         <v>88</v>
       </c>
       <c r="BN4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="BO4" t="s">
         <v>76</v>
       </c>
       <c r="BP4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -2625,7 +2638,7 @@
         <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s">
         <v>75</v>
@@ -2665,7 +2678,7 @@
         <v>75</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="s">
         <v>75</v>
@@ -2695,16 +2708,16 @@
         <v>85</v>
       </c>
       <c r="AH5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AJ5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AL5" t="s">
         <v>83</v>
@@ -2725,7 +2738,7 @@
         <v>83</v>
       </c>
       <c r="AR5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AS5" t="s">
         <v>74</v>
@@ -2743,7 +2756,7 @@
         <v>84</v>
       </c>
       <c r="AX5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AY5" t="s">
         <v>75</v>
@@ -2758,10 +2771,10 @@
         <v>85</v>
       </c>
       <c r="BC5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BD5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BE5" t="s">
         <v>87</v>
@@ -2770,30 +2783,30 @@
         <v>76</v>
       </c>
       <c r="BG5" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BH5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BI5" s="7"/>
       <c r="BJ5" t="s">
         <v>87</v>
       </c>
       <c r="BK5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BL5" s="7"/>
       <c r="BM5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="BN5" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BO5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BP5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -2822,10 +2835,10 @@
         <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K6" t="s">
         <v>79</v>
@@ -2864,19 +2877,19 @@
         <v>85</v>
       </c>
       <c r="X6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y6" t="s">
         <v>85</v>
       </c>
       <c r="Z6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA6" t="s">
         <v>94</v>
       </c>
-      <c r="AA6" t="s">
-        <v>93</v>
-      </c>
       <c r="AB6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AC6" t="s">
         <v>79</v>
@@ -2894,43 +2907,43 @@
         <v>83</v>
       </c>
       <c r="AH6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AI6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s">
         <v>78</v>
       </c>
       <c r="AL6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AM6" t="s">
         <v>73</v>
       </c>
       <c r="AN6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO6" t="s">
         <v>78</v>
       </c>
       <c r="AP6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AQ6" t="s">
         <v>73</v>
       </c>
       <c r="AR6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS6" t="s">
         <v>75</v>
       </c>
       <c r="AT6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AU6" t="s">
         <v>83</v>
@@ -2942,7 +2955,7 @@
         <v>79</v>
       </c>
       <c r="AX6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AY6" t="s">
         <v>72</v>
@@ -2960,48 +2973,48 @@
         <v>74</v>
       </c>
       <c r="BD6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BE6" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BF6" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BG6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BH6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BJ6" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BK6" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BM6" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BN6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="BO6" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BP6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
         <v>79</v>
@@ -3010,19 +3023,19 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
         <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K7" t="s">
         <v>88</v>
@@ -3037,7 +3050,7 @@
         <v>83</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="s">
         <v>75</v>
@@ -3061,61 +3074,61 @@
         <v>83</v>
       </c>
       <c r="X7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y7" t="s">
         <v>79</v>
       </c>
       <c r="Z7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AC7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="s">
         <v>78</v>
       </c>
       <c r="AE7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG7" t="s">
         <v>78</v>
       </c>
       <c r="AH7" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL7" t="s">
         <v>89</v>
-      </c>
-      <c r="AK7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>80</v>
       </c>
       <c r="AM7" t="s">
         <v>78</v>
       </c>
       <c r="AN7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AO7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AP7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AQ7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AR7" t="s">
         <v>75</v>
@@ -3133,7 +3146,7 @@
         <v>74</v>
       </c>
       <c r="AW7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AX7" t="s">
         <v>79</v>
@@ -3142,13 +3155,13 @@
         <v>78</v>
       </c>
       <c r="AZ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA7" t="s">
+        <v>97</v>
+      </c>
+      <c r="BB7" t="s">
         <v>96</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>95</v>
       </c>
       <c r="BC7" t="s">
         <v>88</v>
@@ -3157,31 +3170,31 @@
         <v>75</v>
       </c>
       <c r="BE7" t="s">
+        <v>101</v>
+      </c>
+      <c r="BF7" t="s">
         <v>100</v>
       </c>
-      <c r="BF7" t="s">
-        <v>99</v>
-      </c>
       <c r="BG7" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="BH7" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="BJ7" t="s">
         <v>100</v>
       </c>
-      <c r="BJ7" t="s">
-        <v>99</v>
-      </c>
       <c r="BK7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BM7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BN7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BO7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:67" x14ac:dyDescent="0.25">
@@ -3204,28 +3217,28 @@
         <v>87</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
         <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K8" t="s">
         <v>76</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N8" t="s">
         <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
         <v>74</v>
@@ -3240,7 +3253,7 @@
         <v>79</v>
       </c>
       <c r="T8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U8" t="s">
         <v>78</v>
@@ -3249,7 +3262,7 @@
         <v>88</v>
       </c>
       <c r="W8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y8" t="s">
         <v>78</v>
@@ -3261,16 +3274,16 @@
         <v>78</v>
       </c>
       <c r="AB8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC8" t="s">
         <v>78</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AF8" t="s">
         <v>76</v>
@@ -3279,13 +3292,13 @@
         <v>88</v>
       </c>
       <c r="AH8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="s">
         <v>109</v>
       </c>
       <c r="AK8" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AL8" t="s">
         <v>87</v>
@@ -3300,13 +3313,13 @@
         <v>87</v>
       </c>
       <c r="AP8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AQ8" t="s">
         <v>86</v>
       </c>
       <c r="AR8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AS8" t="s">
         <v>88</v>
@@ -3315,13 +3328,13 @@
         <v>74</v>
       </c>
       <c r="AU8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AV8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AW8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AX8" t="s">
         <v>78</v>
@@ -3333,147 +3346,150 @@
         <v>78</v>
       </c>
       <c r="BA8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BB8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="BC8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BD8" t="s">
         <v>87</v>
       </c>
       <c r="BE8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BF8" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>106</v>
       </c>
       <c r="BJ8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BK8" t="s">
         <v>110</v>
       </c>
       <c r="BM8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BN8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>81</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="P9" t="s">
         <v>78</v>
       </c>
       <c r="Q9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="S9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T9" t="s">
         <v>76</v>
       </c>
       <c r="U9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="W9" t="s">
         <v>76</v>
       </c>
       <c r="Y9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Z9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AA9" s="7" t="s">
+      <c r="AF9" t="s">
         <v>91</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>90</v>
       </c>
       <c r="AG9" t="s">
         <v>87</v>
       </c>
       <c r="AH9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AJ9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK9" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL9" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="AL9" s="7" t="s">
-        <v>99</v>
       </c>
       <c r="AM9" t="s">
         <v>88</v>
       </c>
       <c r="AN9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AO9" t="s">
         <v>86</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AQ9" t="s">
         <v>87</v>
@@ -3488,16 +3504,16 @@
         <v>78</v>
       </c>
       <c r="AU9" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AV9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AW9" t="s">
         <v>88</v>
       </c>
       <c r="AX9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AY9" t="s">
         <v>76</v>
@@ -3506,63 +3522,66 @@
         <v>86</v>
       </c>
       <c r="BA9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BB9" t="s">
         <v>87</v>
       </c>
       <c r="BC9" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BD9" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BE9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BF9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BK9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H10" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="I10" t="s">
+        <v>98</v>
       </c>
       <c r="K10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="N10" t="s">
         <v>110</v>
       </c>
       <c r="O10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q10" t="s">
         <v>88</v>
@@ -3574,106 +3593,106 @@
         <v>76</v>
       </c>
       <c r="T10" t="s">
+        <v>93</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="V10" t="s">
         <v>92</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="V10" t="s">
-        <v>91</v>
       </c>
       <c r="W10" t="s">
         <v>87</v>
       </c>
       <c r="Y10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="Z10" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB10" t="s">
         <v>106</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>105</v>
       </c>
       <c r="AC10" t="s">
         <v>87</v>
       </c>
       <c r="AD10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AE10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF10" s="7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AG10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AJ10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AK10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AL10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AN10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AO10" s="7" t="s">
-        <v>89</v>
+        <v>98</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>90</v>
       </c>
       <c r="AP10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AQ10" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AR10" t="s">
         <v>76</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AT10" t="s">
         <v>86</v>
       </c>
       <c r="AU10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AV10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AW10" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AX10" t="s">
         <v>87</v>
       </c>
       <c r="AY10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AZ10" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="BA10" t="s">
         <v>87</v>
       </c>
       <c r="BB10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BC10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BD10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BK10" t="s">
         <v>109</v>
@@ -3681,52 +3700,55 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" t="s">
+        <v>111</v>
+      </c>
+      <c r="L11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" t="s">
+        <v>114</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="P11" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q11" t="s">
         <v>91</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" t="s">
-        <v>108</v>
-      </c>
-      <c r="N11" t="s">
-        <v>112</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="P11" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>90</v>
       </c>
       <c r="R11" t="s">
         <v>86</v>
       </c>
       <c r="S11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="U11" t="s">
+        <v>92</v>
+      </c>
+      <c r="W11" t="s">
         <v>91</v>
-      </c>
-      <c r="U11" t="s">
-        <v>91</v>
-      </c>
-      <c r="W11" t="s">
-        <v>90</v>
       </c>
       <c r="Y11" s="7" t="s">
         <v>86</v>
@@ -3735,297 +3757,333 @@
         <v>109</v>
       </c>
       <c r="AA11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AD11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AE11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AV11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>111</v>
+      </c>
+      <c r="AX11" t="s">
         <v>91</v>
       </c>
-      <c r="AF11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>80</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AV11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX11" t="s">
+      <c r="AY11" t="s">
         <v>90</v>
       </c>
-      <c r="AY11" t="s">
-        <v>89</v>
-      </c>
       <c r="AZ11" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BA11" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="BB11" t="s">
         <v>86</v>
       </c>
       <c r="BC11" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="BD11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="K12" t="s">
+        <v>113</v>
       </c>
       <c r="N12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>109</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S12" s="7" t="s">
         <v>109</v>
       </c>
       <c r="T12" t="s">
+        <v>101</v>
+      </c>
+      <c r="U12" t="s">
+        <v>101</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC12" t="s">
         <v>100</v>
-      </c>
-      <c r="U12" t="s">
-        <v>100</v>
-      </c>
-      <c r="W12" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>99</v>
       </c>
       <c r="AD12" t="s">
         <v>87</v>
       </c>
       <c r="AF12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG12" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>87</v>
       </c>
       <c r="AM12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AP12" t="s">
         <v>109</v>
       </c>
       <c r="AQ12" t="s">
+        <v>111</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>90</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" t="s">
+        <v>101</v>
+      </c>
+      <c r="P13" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>92</v>
+      </c>
+      <c r="R13" t="s">
+        <v>92</v>
+      </c>
+      <c r="S13" t="s">
+        <v>92</v>
+      </c>
+      <c r="T13" t="s">
+        <v>106</v>
+      </c>
+      <c r="U13" t="s">
+        <v>106</v>
+      </c>
+      <c r="W13" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT13" t="s">
         <v>108</v>
       </c>
-      <c r="AR12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT12" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AW12" t="s">
+      <c r="AV13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA13" t="s">
         <v>108</v>
       </c>
-      <c r="AX12" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>89</v>
-      </c>
-      <c r="BA12" t="s">
-        <v>99</v>
-      </c>
-      <c r="BB12" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="E13" t="s">
-        <v>102</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="BB13" t="s">
         <v>100</v>
-      </c>
-      <c r="P13" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>91</v>
-      </c>
-      <c r="R13" t="s">
-        <v>91</v>
-      </c>
-      <c r="S13" t="s">
-        <v>91</v>
-      </c>
-      <c r="T13" t="s">
-        <v>105</v>
-      </c>
-      <c r="U13" t="s">
-        <v>105</v>
-      </c>
-      <c r="W13" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>105</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>111</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>105</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>100</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>111</v>
+      </c>
       <c r="O14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R14" t="s">
         <v>110</v>
       </c>
       <c r="S14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W14" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>113</v>
       </c>
       <c r="AR14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AT14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AX14" t="s">
+        <v>114</v>
+      </c>
+      <c r="AZ14" t="s">
         <v>112</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>111</v>
       </c>
       <c r="BB14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="15:54" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+      <c r="O15" t="s">
+        <v>89</v>
+      </c>
       <c r="Q15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W15" t="s">
-        <v>108</v>
+        <v>111</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>106</v>
       </c>
       <c r="AT15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15" customHeight="1" spans="15:46" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4091,7 +4149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AO42"/>
+  <dimension ref="A3:AP42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -4137,7 +4195,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -4163,10 +4221,10 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K3" t="s">
         <v>83</v>
@@ -4175,13 +4233,13 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P3" t="s">
         <v>78</v>
@@ -4193,76 +4251,79 @@
         <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T3" t="s">
         <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="W3" t="s">
         <v>76</v>
       </c>
       <c r="X3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y3" t="s">
         <v>87</v>
       </c>
       <c r="Z3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD3" t="s">
         <v>90</v>
       </c>
-      <c r="AA3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>89</v>
-      </c>
       <c r="AE3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="s">
         <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AH3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AJ3" t="s">
         <v>110</v>
       </c>
       <c r="AK3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AL3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AN3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AO3" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4351,7 +4412,7 @@
         <v>14</v>
       </c>
       <c r="AD4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="AE4" t="s">
         <v>68</v>
@@ -4386,8 +4447,11 @@
       <c r="AO4" t="s">
         <v>24</v>
       </c>
+      <c r="AP4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4511,8 +4575,11 @@
       <c r="AO5" t="s">
         <v>18</v>
       </c>
+      <c r="AP5" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4616,19 +4683,19 @@
         <v>66</v>
       </c>
       <c r="AI6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="s">
         <v>57</v>
       </c>
       <c r="AK6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="AL6" t="s">
         <v>53</v>
       </c>
       <c r="AM6" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="AN6" t="s">
         <v>52</v>
@@ -4636,8 +4703,11 @@
       <c r="AO6" t="s">
         <v>35</v>
       </c>
+      <c r="AP6" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4761,13 +4831,16 @@
       <c r="AO7" t="s">
         <v>23</v>
       </c>
+      <c r="AP7" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -4791,7 +4864,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -4833,10 +4906,10 @@
         <v>9</v>
       </c>
       <c r="AN8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -4853,7 +4926,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -4910,7 +4983,7 @@
         <v>47</v>
       </c>
       <c r="AN9" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="s">
         <v>50</v>
@@ -4978,7 +5051,7 @@
         <v>69</v>
       </c>
       <c r="AI10" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AK10" t="s">
         <v>22</v>
@@ -4987,7 +5060,7 @@
         <v>8</v>
       </c>
       <c r="AN10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="s">
         <v>51</v>
@@ -5064,10 +5137,10 @@
         <v>42</v>
       </c>
       <c r="AN11" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="AO11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
@@ -5096,7 +5169,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -5132,7 +5205,7 @@
         <v>39</v>
       </c>
       <c r="AN12" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AO12" t="s">
         <v>6</v>
@@ -5200,7 +5273,7 @@
         <v>29</v>
       </c>
       <c r="AN13" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="s">
         <v>54</v>
@@ -5268,7 +5341,7 @@
         <v>22</v>
       </c>
       <c r="AN14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="s">
         <v>7</v>
@@ -5324,7 +5397,7 @@
         <v>43</v>
       </c>
       <c r="AE15" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="AI15" t="s">
         <v>8</v>
@@ -5336,7 +5409,7 @@
         <v>30</v>
       </c>
       <c r="AN15" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="s">
         <v>43</v>
@@ -5625,10 +5698,10 @@
         <v>31</v>
       </c>
       <c r="V20" t="s">
+        <v>34</v>
+      </c>
+      <c r="W20" t="s">
         <v>39</v>
-      </c>
-      <c r="W20" t="s">
-        <v>21</v>
       </c>
       <c r="Y20" t="s">
         <v>9</v>
@@ -5678,10 +5751,10 @@
         <v>34</v>
       </c>
       <c r="V21" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="W21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="s">
         <v>33</v>
@@ -5790,7 +5863,7 @@
         <v>23</v>
       </c>
       <c r="Y23" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AB23" t="s">
         <v>28</v>
@@ -5874,7 +5947,7 @@
         <v>22</v>
       </c>
       <c r="AB26" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="s">
         <v>65</v>
@@ -5940,7 +6013,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AO14"/>
+  <dimension ref="A3:AP14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -6023,7 +6096,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -6049,10 +6122,10 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K3" t="s">
         <v>83</v>
@@ -6061,13 +6134,13 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P3" t="s">
         <v>78</v>
@@ -6079,487 +6152,496 @@
         <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T3" t="s">
         <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="W3" t="s">
         <v>76</v>
       </c>
       <c r="X3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y3" t="s">
         <v>87</v>
       </c>
       <c r="Z3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD3" t="s">
         <v>90</v>
       </c>
-      <c r="AA3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>89</v>
-      </c>
       <c r="AE3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="s">
         <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AH3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AJ3" t="s">
         <v>110</v>
       </c>
       <c r="AK3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AL3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AM3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AN3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AO3" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="P4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="R4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="S4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="T4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="U4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="V4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="W4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="X4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Y4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Z4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AA4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AB4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AC4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AD4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AE4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AF4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AP4" t="s">
         <v>144</v>
       </c>
-      <c r="AG4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>153</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="R5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="T5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="U5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="V5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="W5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Y5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Z5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AB5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AD5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AE5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AF5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AI5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AK5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AM5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AN5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AO5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="V6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="W6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Y6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Z6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AB6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AD6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AE6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AI6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AK6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AM6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AN6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AO6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="V7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="W7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Y7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Z7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AB7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AD7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AE7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AI7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AK7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AM7" t="s">
-        <v>220</v>
+        <v>223</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>224</v>
       </c>
       <c r="AO7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G8" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H8" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="V8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="W8" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Y8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AB8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AD8" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AE8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AI8" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AK8" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AM8" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AO8" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="L9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AB9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AD9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AE9" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AI9" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AK9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AO9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="28:41" x14ac:dyDescent="0.25"/>
@@ -6595,7 +6677,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="10">
@@ -6605,7 +6687,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="13">
@@ -6615,14 +6697,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B3" s="15">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>536</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
@@ -6630,35 +6712,35 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B4" s="18">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6670,7 +6752,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F5" s="20">
         <v>2</v>
@@ -6748,7 +6830,7 @@
         <v>232</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F7" s="29">
         <v>3</v>
@@ -6780,7 +6862,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E8" s="32" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F8" s="33">
         <v>6</v>
@@ -6812,14 +6894,14 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>536</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F9" s="33">
         <v>4</v>
@@ -6851,7 +6933,7 @@
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="37" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I11" s="38">
         <f>SUM(I7:I9)</f>
@@ -6872,33 +6954,33 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F16" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G16" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H16" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L16" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="42" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F17" s="43">
         <v>3</v>
@@ -6930,7 +7012,7 @@
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="49" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F18" s="50">
         <v>6</v>
@@ -6963,7 +7045,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="57" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F19" s="58">
         <v>4</v>
@@ -6997,7 +7079,7 @@
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="P24" s="64" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q24" s="64"/>
       <c r="R24" s="64"/>
@@ -7006,18 +7088,18 @@
     <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P25" s="65"/>
       <c r="Q25" s="66" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="R25" s="67" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="S25" s="68" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P26" s="69" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q26" s="32">
         <v>247</v>
@@ -7032,7 +7114,7 @@
     </row>
     <row r="27" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P27" s="69" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q27" s="32">
         <v>124</v>
@@ -7047,7 +7129,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P28" s="70" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q28" s="71">
         <v>165</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="275">
   <si>
     <t>sl</t>
   </si>
@@ -259,48 +259,51 @@
     <t>2024-10-12</t>
   </si>
   <si>
+    <t>2024-10-27</t>
+  </si>
+  <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
+    <t>2024-09-24</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>2024-09-29</t>
+  </si>
+  <si>
+    <t>2024-10-03</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>2024-11-03</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>2024-10-29</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>2024-10-24</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2024-11-14</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-10-20</t>
-  </si>
-  <si>
-    <t>2024-09-24</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>2024-09-29</t>
-  </si>
-  <si>
-    <t>2024-10-03</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>2024-11-03</t>
-  </si>
-  <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>2024-10-29</t>
-  </si>
-  <si>
-    <t>2024-11-23</t>
-  </si>
-  <si>
-    <t>2024-10-24</t>
-  </si>
-  <si>
-    <t>2024-11-14</t>
-  </si>
-  <si>
-    <t>2024-10-27</t>
-  </si>
-  <si>
     <t>2024-10-16</t>
   </si>
   <si>
@@ -322,46 +325,46 @@
     <t>2024-11-30</t>
   </si>
   <si>
+    <t>2024-10-31</t>
+  </si>
+  <si>
+    <t>2024-11-28</t>
+  </si>
+  <si>
+    <t>2024-10-06</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
     <t>2024-11-21</t>
   </si>
   <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2024-11-28</t>
-  </si>
-  <si>
-    <t>2024-10-06</t>
-  </si>
-  <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
     <t>2024-11-12</t>
   </si>
   <si>
-    <t>2024-12-03</t>
+    <t>2024-11-26</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
   </si>
   <si>
     <t>2024-11-19</t>
   </si>
   <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
     <t>2024-12-04</t>
   </si>
   <si>
     <t>2024-12-01</t>
   </si>
   <si>
-    <t>2024-11-26</t>
+    <t>2024-11-24</t>
   </si>
   <si>
     <t>HuberRe</t>
@@ -448,184 +451,193 @@
     <t>Eishalle Sterzing;GiacomozziFe;PirasAn;PaceJa;ScalzeriAl</t>
   </si>
   <si>
+    <t>Eishalle Jesenice;VirtaTu;WidmannFl;AbeltinoSi;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;MetzingerFi;StefenelliFe;CristeliMa;KnezRo</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;BrockAd;SnojTa;ArlicMa;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;HlavatyAl;WidmannFl;LegatKo;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;LazzeriAl;RivisFe;RinkerDa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HolzerTo;RuetzMa;JägerRi;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;KainbergerJu;LegaSi;CristeliMa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;BenvegnuAn;LazzeriAl;DivisDo;JägerRi</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;HlavatyAl;WenuschHe;EislCh;WuchererGe</t>
+  </si>
+  <si>
+    <t>Kitzbühel Sportpark;BenvegnuAn;LazzeriAl;RinkerDa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;MoschenAn;SoraperraSi;CusinFe;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;LesniakBo;RivisFe;ArlicMa;RivisAn</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HuberRe;MeixnerSe;StrimitzerDa;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;LebenJa;WidmannFl;LegatKo;MiklicGr</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LesniakBo;SnojTa;JeramFi;RinkerDa</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;HolzerTo;HuberRe;DivisDo;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;KainbergerJu;VoicanCh;LegatKo;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;MetzingerFi;VoicanCh;KnezRo;WendnerMa</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;BrockAd;MeixnerSe;RinkerDa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;PiragicTr;PirasAn;CristeliMa;FecchioFe</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;HuberRe;LazzeriAl;DivisDo;IlmerNo</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;SnojTa;WidmannFl;ArlicMa;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;EggerTh;HolzerTo;CusinFe;JägerRi</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;Huber rRe;MoschenAn;IlmerNo;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;StefenelliFe;VirtaTu;BrondiPa;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;MeixnerSe;OrelSt;JeramFi;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;SoraperraSi;VirtaTu;CusinFe;PaceJa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;SpiegelSe;VoicanCh;LegatKo;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;EggerTh;PinieOm;IlmerNo;PaceJa</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CusinFe</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;RuetzMa;SpiegelSe;EislCh;JägerRi</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;MeixnerSe;MoschenAn;IlmerNo;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;GiacomozziFe;RuetzMa;BrondiPa;StrimitzerDa</t>
+  </si>
+  <si>
     <t>Würtharena Neumarkt;BajtMi;PinieOm;JavornikBl;PaceJa</t>
   </si>
   <si>
-    <t>Eishalle Ritten;MetzingerFi;StefenelliFe;CristeliMa;KnezRo</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;BrockAd;SnojTa;ArlicMa;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;HlavatyAl;WidmannFl;LegatKo;WuchererGe</t>
-  </si>
-  <si>
-    <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;GrisentiLu</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;LazzeriAl;RivisFe;RinkerDa;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;HolzerTo;RuetzMa;JägerRi;SeewaldJe</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;KainbergerJu;LegaSi;CristeliMa;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;BenvegnuAn;LazzeriAl;DivisDo;JägerRi</t>
-  </si>
-  <si>
-    <t>KELIT Arena Zell am See;HlavatyAl;WenuschHe;EislCh;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Kitzbühel Sportpark;BenvegnuAn;LazzeriAl;RinkerDa;SeewaldJe</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;MoschenAn;SoraperraSi;CusinFe;FormaioniTh</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;HuberRe;MeixnerSe;StrimitzerDa;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;LebenJa;WidmannFl;LegatKo;MiklicGr</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;LesniakBo;SnojTa;JeramFi;RinkerDa</t>
-  </si>
-  <si>
-    <t>KELIT Arena Zell am See;HolzerTo;HuberRe;DivisDo;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>KELIT Arena Zell am See;KainbergerJu;VoicanCh;LegatKo;MoidlMa</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;MetzingerFi;VoicanCh;KnezRo;WendnerMa</t>
-  </si>
-  <si>
-    <t>KELIT Arena Zell am See;BrockAd;MeixnerSe;RinkerDa;SeewaldJe</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;PiragicTr;PirasAn;CristeliMa;FecchioFe</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;HuberRe;LazzeriAl;DivisDo;IlmerNo</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;SnojTa;WidmannFl;ArlicMa;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;EggerTh;HolzerTo;CusinFe;JägerRi</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;Huber rRe;MoschenAn;IlmerNo;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>Würtharena Neumarkt;StefenelliFe;VirtaTu;BrondiPa;PaceJa</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;MeixnerSe;OrelSt;JeramFi;WendnerMa</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;SoraperraSi;VirtaTu;CusinFe;PaceJa</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;VirtaTu;WidmannFl;AbeltinoSi;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;EggerTh;PinieOm;FleischmannLu;PaceJa</t>
-  </si>
-  <si>
-    <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CusinFe</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;RuetzMa;SpiegelSe;EislCh;JägerRi</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;MeixnerSe;MoschenAn;IlmerNo;MoidlMa</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;GiacomozziFe;RuetzMa;BrondiPa;StrimitzerDa</t>
-  </si>
-  <si>
     <t>Eishalle Sissek Zibel;LebenJa;OrelSt;MarkizetiGr;TelesklavFa</t>
   </si>
   <si>
+    <t>Würtharena Neumarkt;BenvegnuAn;VirtaTu;FecchioFe;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;WeissAl</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;PirasAn;RivisFe;BrondiPa;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BajtMi;LesniakBo;ArlicMa;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;MetzingerFi;WidmannFl;KnezRo;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;PinieOm;PirasAn;CusinFe;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;PirasAn;SoraperraSi;BrondiPa;CusinFe</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;BenvegnuAn;MoschenAn;IlmerNo;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;RivisFe;SoraperraSi;FormaioniTh;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;HuberRe;MoschenAn;AbeltinoSi;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;MetzingerFi;PinieOm;GrisentiLu;KnezRo</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;OrelSt;VoicanCh;LegatKo;WuchererGe</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;BajtMi;MoidlDa;MiklicGr;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;BulovecMi;KainbergerJu;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;MoidlDa;SpiegelSe;DivisDo;RinkerDa</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;BrockAd;OrelSt;WendnerMa;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;VoicanCh;WidmannFl;WeissAl;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BulovecMi;SnojTa;JeramFi;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;BulovecMi;LebenJa;GrisentiLu;JeramFi</t>
+  </si>
+  <si>
     <t>ZBRISANO</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;WeissAl</t>
-  </si>
-  <si>
-    <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
-  </si>
-  <si>
-    <t>Würtharena Neumarkt;PirasAn;RivisFe;BrondiPa;GrisentiLu</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;BajtMi;LesniakBo;ArlicMa;MarkizetiGr</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;MetzingerFi;WidmannFl;KnezRo;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;PinieOm;PirasAn;CusinFe;FormaioniTh</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;PirasAn;SoraperraSi;BrondiPa;CusinFe</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;BenvegnuAn;MoschenAn;IlmerNo;RivisAn</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;RivisFe;SoraperraSi;FormaioniTh;GrisentiLu</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;HuberRe;MoschenAn;AbeltinoSi;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;MetzingerFi;PinieOm;GrisentiLu;KnezRo</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;OrelSt;VoicanCh;LegatKo;WuchererGe</t>
-  </si>
-  <si>
-    <t>KELIT Arena Zell am See;BajtMi;MoidlDa;MiklicGr;MoidlMa</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;BulovecMi;KainbergerJu;SeewaldJe;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;MoidlDa;SpiegelSe;DivisDo;RinkerDa</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;SpiegelSe;VoicanCh;LegatKo;WeissAl</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;VoicanCh;WidmannFl;WeissAl;WuchererGe</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WendnerMa</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;BulovecMi;SnojTa;ArlicMa;MarkizetiGr</t>
-  </si>
-  <si>
-    <t>Würtharena Neumarkt;BulovecMi;LebenJa;GrisentiLu;JeramFi</t>
-  </si>
-  <si>
     <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;ScalzeriAl</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;BenvegnuAn;VirtaTu;FecchioFe;PaceJa</t>
+    <t>Eishalle Celje;BajtMi;MetzingerFi;KnezRo;MarkizetiGr</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;BulovecMi;WidmannFl;ArlicMa;WuchererGe</t>
@@ -673,7 +685,7 @@
     <t>Würtharena Neumarkt;MoschenAn;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;BrockAd;OrelSt;WendnerMa;WuchererGe</t>
+    <t>Eishalle Dornbirn;MoschenAn;RuetzMa;DivisDo;IlmerNo</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;BajtMi;RivisFe;JavornikBl;RivisAn</t>
@@ -682,18 +694,18 @@
     <t>Eishalle Meran;LesniakBo;OrelSt;MarkizetiGr;TelesklavFa</t>
   </si>
   <si>
+    <t>Eishalle Sterzing;Huber rRe;RivisFe;FecchioFe;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;MoschenAn;SpiegelSe;FecchioFe;JägerRi</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;MetzingerFi;PirasAn;FecchioFe;KnezRo</t>
+  </si>
+  <si>
     <t>Eishalle Ritten;EggerTh;LazzeriAl;GrisentiLu;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Ritten;MoschenAn;SpiegelSe;FecchioFe;JägerRi</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;MetzingerFi;PirasAn;FecchioFe;KnezRo</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;BajtMi;MetzingerFi;KnezRo;MarkizetiGr</t>
-  </si>
-  <si>
     <t>Eishalle Meran;KainbergerJu;LehnerMo;EislCh;FleischmannLu</t>
   </si>
   <si>
@@ -727,7 +739,7 @@
     <t>Eishalle Cortina;LebenJa;PirasAn;AbeltinoSi;CristeliMa</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;EggerTh;RuetzMa;DivisDo;IlmerNo</t>
+    <t>Eishalle Meran;LesniakBo;SnojTa;ArlicMa;StrimitzerDa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;Huber rRe;LehnerMo;EislCh;StrimitzerDa</t>
@@ -736,10 +748,10 @@
     <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;DivisDo;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;Huber rRe;RivisFe;FecchioFe;RivisAn</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;StefenelliFe;VirtaTu;CristeliMa;FleischmannLu</t>
+    <t>Eishalle Cortina;GiacomozziFe;SoraperraSi;BrondiPa;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;StefenelliFe;VirtaTu;CristeliMa;PaceJa</t>
   </si>
   <si>
     <t>Eishalle Cortina;LegaSi;VirtaTu;CristeliMa;IlmerNo</t>
@@ -754,16 +766,10 @@
     <t>Würtharena Neumarkt;LegaSi;RuetzMa;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Meran;LesniakBo;SnojTa;JeramFi;StrimitzerDa</t>
-  </si>
-  <si>
     <t>Eishalle Dornbirn;HolzerTo;SpiegelSe;MattheyPh;MoidlMa</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
-  </si>
-  <si>
-    <t>Eishalle Cortina;GiacomozziFe;SoraperraSi;BrondiPa;FormaioniTh</t>
   </si>
   <si>
     <t>Eishalle Gröden;PirasAn;SoraperraSi;FormaioniTh;ScalzeriAl</t>
@@ -1723,7 +1729,7 @@
         <v>9</v>
       </c>
       <c r="B1">
-        <f>COUNTIF(B4:B69,"&lt;&gt;")</f>
+        <f>COUNTIF(B4:B68,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="C1">
@@ -1731,40 +1737,40 @@
         <v>9</v>
       </c>
       <c r="D1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>COUNTIF(D4:D69,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F69,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="G1">
-        <f>COUNTIF(G4:G69,"&lt;&gt;")</f>
-        <v>5</v>
+        <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
+        <v>4</v>
       </c>
       <c r="H1">
         <f>COUNTIF(H4:H69,"&lt;&gt;")</f>
+        <v>8</v>
+      </c>
+      <c r="I1">
+        <f>COUNTIF(I4:I69,"&lt;&gt;")</f>
         <v>7</v>
       </c>
-      <c r="I1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
       <c r="J1">
-        <f>COUNTIF(J4:J69,"&lt;&gt;")</f>
+        <f>COUNTIF(J4:J68,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M1">
         <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
@@ -1775,7 +1781,7 @@
         <v>9</v>
       </c>
       <c r="O1">
-        <f>COUNTIF(O4:O69,"&lt;&gt;")</f>
+        <f>COUNTIF(O4:O68,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="P1">
@@ -1783,11 +1789,11 @@
         <v>10</v>
       </c>
       <c r="Q1">
-        <f>COUNTIF(Q4:Q69,"&lt;&gt;")</f>
+        <f>COUNTIF(Q4:Q68,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R68,"&lt;&gt;")</f>
+        <f>COUNTIF(R4:R67,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="S1">
@@ -1804,26 +1810,26 @@
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V68,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W1">
         <f>COUNTIF(W4:W69,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="X1">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
+        <v>2</v>
       </c>
       <c r="Y1">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>COUNTIF(Y4:Y69,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA1">
-        <f>COUNTIF(AA4:AA67,"&lt;&gt;")</f>
+        <f>COUNTIF(AA4:AA66,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="AB1">
@@ -1840,31 +1846,31 @@
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE69,"&lt;&gt;")</f>
+        <v>9</v>
+      </c>
+      <c r="AF1">
+        <f>COUNTIF(AF4:AF65,"&lt;&gt;")</f>
         <v>8</v>
       </c>
-      <c r="AF1">
-        <f>COUNTIF(AF4:AF66,"&lt;&gt;")</f>
+      <c r="AG1">
+        <f>COUNTIF(AG4:AG69,"&lt;&gt;")</f>
         <v>9</v>
       </c>
-      <c r="AG1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
       <c r="AH1">
-        <f t="shared" ref="AH1" si="1">COUNTIF(AH4:AH69,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI69,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ68,"&lt;&gt;")</f>
+        <f>COUNTIF(AJ4:AJ66,"&lt;&gt;")</f>
         <v>7</v>
       </c>
       <c r="AK1">
-        <f>COUNTIF(AK4:AK67,"&lt;&gt;")</f>
-        <v>7</v>
+        <f>COUNTIF(AK4:AK66,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL68,"&lt;&gt;")</f>
@@ -1876,7 +1882,7 @@
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN66,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO69,"&lt;&gt;")</f>
@@ -1891,11 +1897,11 @@
         <v>9</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR65,"&lt;&gt;")</f>
+        <f>COUNTIF(AR4:AR64,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AS1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(AS4:AS69,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="AT1">
@@ -1915,8 +1921,8 @@
         <v>9</v>
       </c>
       <c r="AX1">
-        <f>COUNTIF(AX4:AX68,"&lt;&gt;")</f>
-        <v>11</v>
+        <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY68,"&lt;&gt;")</f>
@@ -1935,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="BC1">
-        <f>COUNTIF(BC4:BC69,"&lt;&gt;")</f>
+        <f>COUNTIF(BC4:BC68,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="BD1">
@@ -1943,27 +1949,27 @@
         <v>8</v>
       </c>
       <c r="BE1">
-        <f>COUNTIF(BE4:BE69,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(BE4:BE68,"&lt;&gt;")</f>
+        <v>5</v>
       </c>
       <c r="BF1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="BG1">
-        <f>COUNTIF(BG4:BG69,"&lt;&gt;")</f>
+        <f>COUNTIF(BG4:BG68,"&lt;&gt;")</f>
         <v>4</v>
       </c>
       <c r="BH1">
-        <f t="shared" ref="BH1:BP1" si="2">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
+        <f t="shared" ref="BH1:BP1" si="1">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
         <v>4</v>
       </c>
       <c r="BI1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BJ1">
-        <f t="shared" ref="BJ1" si="3">COUNTIF(BJ4:BJ69,"&lt;&gt;")</f>
+        <f t="shared" ref="BJ1" si="2">COUNTIF(BJ4:BJ69,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="BK1">
@@ -1971,11 +1977,11 @@
         <v>7</v>
       </c>
       <c r="BL1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BM1">
-        <f t="shared" ref="BM1" si="4">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
+        <f t="shared" ref="BM1" si="3">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
         <v>5</v>
       </c>
       <c r="BN1">
@@ -1983,11 +1989,11 @@
         <v>5</v>
       </c>
       <c r="BO1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="BP1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2637,7 +2643,7 @@
       <c r="I5" t="s">
         <v>83</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="6" t="s">
         <v>91</v>
       </c>
       <c r="K5" t="s">
@@ -2677,8 +2683,8 @@
       <c r="W5" t="s">
         <v>75</v>
       </c>
-      <c r="X5" s="7" t="s">
-        <v>90</v>
+      <c r="X5" t="s">
+        <v>92</v>
       </c>
       <c r="Y5" t="s">
         <v>75</v>
@@ -2711,10 +2717,10 @@
         <v>91</v>
       </c>
       <c r="AI5" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ5" t="s">
         <v>93</v>
+      </c>
+      <c r="AJ5" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="AK5" t="s">
         <v>89</v>
@@ -2738,7 +2744,7 @@
         <v>83</v>
       </c>
       <c r="AR5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AS5" t="s">
         <v>74</v>
@@ -2756,7 +2762,7 @@
         <v>84</v>
       </c>
       <c r="AX5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AY5" t="s">
         <v>75</v>
@@ -2771,10 +2777,10 @@
         <v>85</v>
       </c>
       <c r="BC5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BD5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BE5" t="s">
         <v>87</v>
@@ -2783,17 +2789,17 @@
         <v>76</v>
       </c>
       <c r="BG5" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BH5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BI5" s="7"/>
       <c r="BJ5" t="s">
         <v>87</v>
       </c>
       <c r="BK5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BL5" s="7"/>
       <c r="BM5" t="s">
@@ -2806,7 +2812,7 @@
         <v>91</v>
       </c>
       <c r="BP5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -2835,10 +2841,10 @@
         <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="J6" t="s">
+        <v>90</v>
       </c>
       <c r="K6" t="s">
         <v>79</v>
@@ -2876,17 +2882,14 @@
       <c r="W6" t="s">
         <v>85</v>
       </c>
-      <c r="X6" t="s">
-        <v>101</v>
-      </c>
       <c r="Y6" t="s">
         <v>85</v>
       </c>
       <c r="Z6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA6" t="s">
         <v>95</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>94</v>
       </c>
       <c r="AB6" t="s">
         <v>102</v>
@@ -2906,20 +2909,20 @@
       <c r="AG6" t="s">
         <v>83</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AH6" s="6" t="s">
         <v>102</v>
       </c>
       <c r="AI6" t="s">
         <v>103</v>
       </c>
-      <c r="AJ6" s="7" t="s">
-        <v>98</v>
+      <c r="AJ6" t="s">
+        <v>90</v>
       </c>
       <c r="AK6" t="s">
         <v>78</v>
       </c>
       <c r="AL6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AM6" t="s">
         <v>73</v>
@@ -2931,7 +2934,7 @@
         <v>78</v>
       </c>
       <c r="AP6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AQ6" t="s">
         <v>73</v>
@@ -2943,7 +2946,7 @@
         <v>75</v>
       </c>
       <c r="AT6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AU6" t="s">
         <v>83</v>
@@ -2955,7 +2958,7 @@
         <v>79</v>
       </c>
       <c r="AX6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AY6" t="s">
         <v>72</v>
@@ -2973,10 +2976,10 @@
         <v>74</v>
       </c>
       <c r="BD6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BE6" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BF6" s="7" t="s">
         <v>90</v>
@@ -2991,30 +2994,30 @@
         <v>90</v>
       </c>
       <c r="BK6" s="6" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="BM6" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BN6" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="BO6" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BP6" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>79</v>
@@ -3023,7 +3026,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -3032,10 +3035,10 @@
         <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s">
         <v>88</v>
@@ -3050,7 +3053,7 @@
         <v>83</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q7" t="s">
         <v>75</v>
@@ -3073,41 +3076,38 @@
       <c r="W7" t="s">
         <v>83</v>
       </c>
-      <c r="X7" t="s">
-        <v>106</v>
-      </c>
       <c r="Y7" t="s">
         <v>79</v>
       </c>
       <c r="Z7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="s">
         <v>102</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AC7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s">
         <v>78</v>
       </c>
       <c r="AE7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AG7" t="s">
         <v>78</v>
       </c>
-      <c r="AH7" s="7" t="s">
-        <v>98</v>
+      <c r="AH7" t="s">
+        <v>90</v>
       </c>
       <c r="AJ7" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AK7" s="7" t="s">
         <v>107</v>
@@ -3119,7 +3119,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO7" t="s">
         <v>89</v>
@@ -3128,7 +3128,7 @@
         <v>89</v>
       </c>
       <c r="AQ7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AR7" t="s">
         <v>75</v>
@@ -3158,10 +3158,10 @@
         <v>104</v>
       </c>
       <c r="BA7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB7" t="s">
         <v>97</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>96</v>
       </c>
       <c r="BC7" t="s">
         <v>88</v>
@@ -3170,38 +3170,38 @@
         <v>75</v>
       </c>
       <c r="BE7" t="s">
+        <v>103</v>
+      </c>
+      <c r="BF7" t="s">
         <v>101</v>
       </c>
-      <c r="BF7" t="s">
-        <v>100</v>
-      </c>
       <c r="BG7" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="BH7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BJ7" t="s">
         <v>101</v>
       </c>
-      <c r="BJ7" t="s">
-        <v>100</v>
-      </c>
       <c r="BK7" t="s">
+        <v>109</v>
+      </c>
+      <c r="BM7" t="s">
         <v>108</v>
       </c>
-      <c r="BM7" t="s">
-        <v>101</v>
-      </c>
       <c r="BN7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="BO7" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C8" t="s">
@@ -3216,9 +3216,6 @@
       <c r="F8" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>80</v>
-      </c>
       <c r="H8" t="s">
         <v>91</v>
       </c>
@@ -3226,7 +3223,7 @@
         <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K8" t="s">
         <v>76</v>
@@ -3238,7 +3235,7 @@
         <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P8" t="s">
         <v>74</v>
@@ -3253,7 +3250,7 @@
         <v>79</v>
       </c>
       <c r="T8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U8" t="s">
         <v>78</v>
@@ -3270,11 +3267,11 @@
       <c r="Z8" t="s">
         <v>76</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AA8" s="6" t="s">
         <v>78</v>
       </c>
       <c r="AB8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC8" t="s">
         <v>78</v>
@@ -3292,13 +3289,13 @@
         <v>88</v>
       </c>
       <c r="AH8" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="AJ8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AK8" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
         <v>87</v>
@@ -3346,7 +3343,7 @@
         <v>78</v>
       </c>
       <c r="BA8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BB8" t="s">
         <v>89</v>
@@ -3358,51 +3355,48 @@
         <v>87</v>
       </c>
       <c r="BE8" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="BF8" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ8" t="s">
         <v>92</v>
       </c>
-      <c r="BG8" t="s">
-        <v>106</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>106</v>
-      </c>
       <c r="BK8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BM8" t="s">
         <v>111</v>
       </c>
       <c r="BN8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>98</v>
+      <c r="B9" t="s">
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>81</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>107</v>
@@ -3411,22 +3405,22 @@
         <v>103</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="P9" t="s">
         <v>78</v>
       </c>
       <c r="Q9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R9" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T9" t="s">
         <v>76</v>
@@ -3446,17 +3440,17 @@
       <c r="Z9" t="s">
         <v>91</v>
       </c>
-      <c r="AA9" s="7" t="s">
-        <v>92</v>
+      <c r="AA9" t="s">
+        <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
         <v>89</v>
       </c>
       <c r="AD9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AE9" s="7" t="s">
         <v>90</v>
@@ -3464,20 +3458,20 @@
       <c r="AF9" t="s">
         <v>91</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="AG9" s="6" t="s">
         <v>87</v>
       </c>
       <c r="AH9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK9" t="s">
         <v>103</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AL9" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="AL9" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AM9" t="s">
         <v>88</v>
@@ -3489,7 +3483,7 @@
         <v>86</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AQ9" t="s">
         <v>87</v>
@@ -3504,7 +3498,7 @@
         <v>78</v>
       </c>
       <c r="AU9" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AV9" t="s">
         <v>105</v>
@@ -3522,36 +3516,33 @@
         <v>86</v>
       </c>
       <c r="BA9" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="BB9" t="s">
         <v>87</v>
       </c>
       <c r="BC9" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BD9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="BF9" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="BK9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>90</v>
@@ -3563,10 +3554,10 @@
         <v>103</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K10" t="s">
         <v>103</v>
@@ -3575,13 +3566,13 @@
         <v>111</v>
       </c>
       <c r="N10" t="s">
-        <v>110</v>
-      </c>
-      <c r="O10" t="s">
-        <v>91</v>
+        <v>112</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="s">
         <v>88</v>
@@ -3593,28 +3584,28 @@
         <v>76</v>
       </c>
       <c r="T10" t="s">
+        <v>80</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="V10" t="s">
         <v>93</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="V10" t="s">
-        <v>92</v>
       </c>
       <c r="W10" t="s">
         <v>87</v>
       </c>
-      <c r="Y10" t="s">
-        <v>80</v>
+      <c r="Y10" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="Z10" s="7" t="s">
         <v>107</v>
       </c>
       <c r="AA10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AB10" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AC10" t="s">
         <v>87</v>
@@ -3623,28 +3614,31 @@
         <v>103</v>
       </c>
       <c r="AE10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AF10" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG10" s="7" t="s">
-        <v>98</v>
+        <v>113</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="AL10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AM10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AN10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AO10" t="s">
         <v>90</v>
@@ -3653,13 +3647,13 @@
         <v>90</v>
       </c>
       <c r="AQ10" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AR10" t="s">
         <v>76</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AT10" t="s">
         <v>86</v>
@@ -3668,16 +3662,16 @@
         <v>90</v>
       </c>
       <c r="AV10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AW10" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AX10" t="s">
         <v>87</v>
       </c>
       <c r="AY10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AZ10" t="s">
         <v>89</v>
@@ -3692,10 +3686,10 @@
         <v>103</v>
       </c>
       <c r="BD10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
@@ -3703,34 +3697,37 @@
         <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>92</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
       </c>
       <c r="K11" t="s">
         <v>111</v>
       </c>
       <c r="L11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s">
-        <v>114</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>100</v>
+        <v>110</v>
+      </c>
+      <c r="O11" t="s">
+        <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="s">
         <v>91</v>
@@ -3742,46 +3739,46 @@
         <v>91</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U11" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="V11" t="s">
+        <v>94</v>
       </c>
       <c r="W11" t="s">
         <v>91</v>
       </c>
-      <c r="Y11" s="7" t="s">
-        <v>86</v>
+      <c r="Y11" t="s">
+        <v>99</v>
       </c>
       <c r="Z11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AA11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AD11" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AE11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF11" t="s">
         <v>92</v>
       </c>
-      <c r="AF11" t="s">
-        <v>100</v>
-      </c>
       <c r="AG11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="AL11" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AM11" t="s">
         <v>90</v>
@@ -3790,28 +3787,28 @@
         <v>90</v>
       </c>
       <c r="AO11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AP11" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="AQ11" t="s">
         <v>103</v>
       </c>
       <c r="AR11" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AS11" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AT11" t="s">
         <v>89</v>
       </c>
       <c r="AU11" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AV11" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AW11" t="s">
         <v>111</v>
@@ -3823,7 +3820,7 @@
         <v>90</v>
       </c>
       <c r="AZ11" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BA11" s="7" t="s">
         <v>90</v>
@@ -3832,205 +3829,211 @@
         <v>86</v>
       </c>
       <c r="BC11" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BD11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
         <v>92</v>
       </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="H12" t="s">
+        <v>115</v>
       </c>
       <c r="K12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N12" t="s">
         <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="P12" t="s">
         <v>103</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T12" t="s">
+        <v>108</v>
+      </c>
+      <c r="U12" t="s">
+        <v>108</v>
+      </c>
+      <c r="V12" t="s">
+        <v>115</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC12" t="s">
         <v>101</v>
-      </c>
-      <c r="U12" t="s">
-        <v>101</v>
-      </c>
-      <c r="W12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>100</v>
       </c>
       <c r="AD12" t="s">
         <v>87</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AE12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP12" t="s">
         <v>106</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>109</v>
       </c>
       <c r="AQ12" t="s">
         <v>111</v>
       </c>
       <c r="AR12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AT12" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AV12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AW12" t="s">
         <v>103</v>
       </c>
-      <c r="AX12" s="7" t="s">
-        <v>80</v>
+      <c r="AX12" t="s">
+        <v>113</v>
       </c>
       <c r="AY12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AZ12" t="s">
         <v>90</v>
       </c>
       <c r="BA12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BB12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
       <c r="E13" t="s">
         <v>103</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="P13" t="s">
         <v>111</v>
       </c>
       <c r="Q13" t="s">
+        <v>108</v>
+      </c>
+      <c r="R13" t="s">
+        <v>112</v>
+      </c>
+      <c r="S13" t="s">
+        <v>93</v>
+      </c>
+      <c r="T13" t="s">
         <v>92</v>
       </c>
-      <c r="R13" t="s">
+      <c r="U13" t="s">
         <v>92</v>
       </c>
-      <c r="S13" t="s">
-        <v>92</v>
-      </c>
-      <c r="T13" t="s">
-        <v>106</v>
-      </c>
-      <c r="U13" t="s">
-        <v>106</v>
-      </c>
       <c r="W13" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="Z13" t="s">
         <v>103</v>
       </c>
-      <c r="AK13" t="s">
-        <v>92</v>
+      <c r="AE13" t="s">
+        <v>115</v>
       </c>
       <c r="AM13" t="s">
         <v>103</v>
       </c>
       <c r="AN13" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AR13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AT13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AZ13" t="s">
         <v>108</v>
       </c>
-      <c r="AV13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>112</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AZ13" t="s">
+      <c r="BA13" t="s">
+        <v>109</v>
+      </c>
+      <c r="BB13" t="s">
         <v>101</v>
       </c>
-      <c r="BA13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>100</v>
-      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>115</v>
+      </c>
       <c r="E14" t="s">
         <v>111</v>
       </c>
       <c r="O14" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="Q14" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="R14" t="s">
         <v>110</v>
       </c>
       <c r="S14" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="U14" t="s">
         <v>91</v>
@@ -4039,51 +4042,48 @@
         <v>103</v>
       </c>
       <c r="Y14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>114</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR14" t="s">
         <v>92</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AT14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ14" t="s">
         <v>113</v>
       </c>
-      <c r="AR14" t="s">
-        <v>103</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>101</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>114</v>
-      </c>
-      <c r="AZ14" t="s">
+      <c r="BB14" t="s">
         <v>112</v>
       </c>
-      <c r="BB14" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
-      <c r="O15" t="s">
-        <v>89</v>
-      </c>
+    <row r="15" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
       <c r="Q15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="R15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S15" t="s">
         <v>103</v>
       </c>
+      <c r="U15" t="s">
+        <v>99</v>
+      </c>
       <c r="W15" t="s">
         <v>111</v>
       </c>
-      <c r="AR15" t="s">
+      <c r="AT15" t="s">
         <v>106</v>
       </c>
-      <c r="AT15" t="s">
-        <v>109</v>
-      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="15:46" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4149,7 +4149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AP42"/>
+  <dimension ref="A3:AQ42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -4195,7 +4195,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -4221,10 +4221,10 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K3" t="s">
         <v>83</v>
@@ -4233,10 +4233,10 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
         <v>104</v>
@@ -4251,13 +4251,13 @@
         <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T3" t="s">
         <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="V3" t="s">
         <v>89</v>
@@ -4278,7 +4278,7 @@
         <v>102</v>
       </c>
       <c r="AB3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="s">
         <v>107</v>
@@ -4287,28 +4287,28 @@
         <v>90</v>
       </c>
       <c r="AE3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH3" t="s">
         <v>109</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>112</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AK3" t="s">
         <v>108</v>
       </c>
-      <c r="AI3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AL3" t="s">
         <v>110</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>114</v>
       </c>
       <c r="AM3" t="s">
         <v>103</v>
@@ -4317,13 +4317,16 @@
         <v>111</v>
       </c>
       <c r="AO3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AP3" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4406,7 +4409,7 @@
         <v>31</v>
       </c>
       <c r="AB4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AC4" t="s">
         <v>14</v>
@@ -4450,8 +4453,11 @@
       <c r="AP4" t="s">
         <v>14</v>
       </c>
+      <c r="AQ4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4534,7 +4540,7 @@
         <v>33</v>
       </c>
       <c r="AB5" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="AC5" t="s">
         <v>29</v>
@@ -4578,8 +4584,11 @@
       <c r="AP5" t="s">
         <v>29</v>
       </c>
+      <c r="AQ5" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4662,7 +4671,7 @@
         <v>37</v>
       </c>
       <c r="AB6" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AC6" t="s">
         <v>40</v>
@@ -4706,8 +4715,11 @@
       <c r="AP6" t="s">
         <v>40</v>
       </c>
+      <c r="AQ6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4790,7 +4802,7 @@
         <v>30</v>
       </c>
       <c r="AB7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AC7" t="s">
         <v>15</v>
@@ -4817,7 +4829,7 @@
         <v>66</v>
       </c>
       <c r="AK7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="AL7" t="s">
         <v>59</v>
@@ -4834,13 +4846,16 @@
       <c r="AP7" t="s">
         <v>15</v>
       </c>
+      <c r="AQ7" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -4864,7 +4879,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -4885,7 +4900,7 @@
         <v>18</v>
       </c>
       <c r="AB8" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="AD8" t="s">
         <v>39</v>
@@ -4901,6 +4916,9 @@
       </c>
       <c r="AK8" t="s">
         <v>31</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>5</v>
       </c>
       <c r="AM8" t="s">
         <v>9</v>
@@ -4926,7 +4944,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -4962,7 +4980,7 @@
         <v>26</v>
       </c>
       <c r="AB9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AD9" t="s">
         <v>36</v>
@@ -4978,6 +4996,9 @@
       </c>
       <c r="AK9" t="s">
         <v>49</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>36</v>
       </c>
       <c r="AM9" t="s">
         <v>47</v>
@@ -5039,10 +5060,10 @@
         <v>35</v>
       </c>
       <c r="AB10" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="AD10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="s">
         <v>32</v>
@@ -5055,6 +5076,9 @@
       </c>
       <c r="AK10" t="s">
         <v>22</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>13</v>
       </c>
       <c r="AM10" t="s">
         <v>8</v>
@@ -5116,7 +5140,7 @@
         <v>37</v>
       </c>
       <c r="AB11" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="AD11" t="s">
         <v>37</v>
@@ -5132,6 +5156,9 @@
       </c>
       <c r="AK11" t="s">
         <v>55</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>37</v>
       </c>
       <c r="AM11" t="s">
         <v>42</v>
@@ -5169,7 +5196,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -5187,7 +5214,7 @@
         <v>70</v>
       </c>
       <c r="AB12" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AD12" t="s">
         <v>50</v>
@@ -5255,7 +5282,7 @@
         <v>45</v>
       </c>
       <c r="AB13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AD13" t="s">
         <v>54</v>
@@ -5323,7 +5350,7 @@
         <v>57</v>
       </c>
       <c r="AB14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AD14" t="s">
         <v>62</v>
@@ -5332,7 +5359,7 @@
         <v>52</v>
       </c>
       <c r="AI14" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AK14" t="s">
         <v>20</v>
@@ -5391,7 +5418,7 @@
         <v>53</v>
       </c>
       <c r="AB15" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AD15" t="s">
         <v>43</v>
@@ -5459,7 +5486,7 @@
         <v>24</v>
       </c>
       <c r="AB16" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="AD16" t="s">
         <v>5</v>
@@ -5468,13 +5495,16 @@
         <v>11</v>
       </c>
       <c r="AI16" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="s">
         <v>24</v>
       </c>
       <c r="AM16" t="s">
         <v>14</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>39</v>
       </c>
       <c r="AO16" t="s">
         <v>41</v>
@@ -5524,7 +5554,7 @@
         <v>29</v>
       </c>
       <c r="AB17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AD17" t="s">
         <v>34</v>
@@ -5533,13 +5563,16 @@
         <v>47</v>
       </c>
       <c r="AI17" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="s">
         <v>45</v>
       </c>
       <c r="AM17" t="s">
         <v>33</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>21</v>
       </c>
       <c r="AO17" t="s">
         <v>71</v>
@@ -5589,7 +5622,7 @@
         <v>22</v>
       </c>
       <c r="AB18" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AD18" t="s">
         <v>13</v>
@@ -5598,13 +5631,16 @@
         <v>8</v>
       </c>
       <c r="AI18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="s">
         <v>19</v>
       </c>
       <c r="AM18" t="s">
         <v>19</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>20</v>
       </c>
       <c r="AO18" t="s">
         <v>69</v>
@@ -5654,7 +5690,7 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="AD19" t="s">
         <v>25</v>
@@ -5663,13 +5699,16 @@
         <v>42</v>
       </c>
       <c r="AI19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="s">
         <v>66</v>
       </c>
       <c r="AM19" t="s">
         <v>15</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>30</v>
       </c>
       <c r="AO19" t="s">
         <v>27</v>
@@ -5707,7 +5746,7 @@
         <v>9</v>
       </c>
       <c r="AB20" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="s">
         <v>44</v>
@@ -5716,7 +5755,7 @@
         <v>56</v>
       </c>
       <c r="AI20" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="AK20" t="s">
         <v>29</v>
@@ -5760,7 +5799,7 @@
         <v>33</v>
       </c>
       <c r="AB21" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="s">
         <v>71</v>
@@ -5769,7 +5808,7 @@
         <v>41</v>
       </c>
       <c r="AI21" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AK21" t="s">
         <v>26</v>
@@ -5813,7 +5852,7 @@
         <v>32</v>
       </c>
       <c r="AB22" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="s">
         <v>69</v>
@@ -5822,7 +5861,7 @@
         <v>57</v>
       </c>
       <c r="AI22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="s">
         <v>40</v>
@@ -5866,7 +5905,7 @@
         <v>40</v>
       </c>
       <c r="AB23" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AD23" t="s">
         <v>55</v>
@@ -5875,10 +5914,10 @@
         <v>59</v>
       </c>
       <c r="AI23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AM23" t="s">
         <v>28</v>
@@ -5894,17 +5933,11 @@
       <c r="L24" t="s">
         <v>38</v>
       </c>
-      <c r="AB24" t="s">
-        <v>11</v>
-      </c>
       <c r="AD24" t="s">
         <v>56</v>
       </c>
       <c r="AE24" t="s">
         <v>71</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>31</v>
       </c>
       <c r="AK24" t="s">
         <v>33</v>
@@ -5920,17 +5953,11 @@
       <c r="L25" t="s">
         <v>49</v>
       </c>
-      <c r="AB25" t="s">
-        <v>4</v>
-      </c>
       <c r="AD25" t="s">
         <v>45</v>
       </c>
       <c r="AE25" t="s">
         <v>70</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>18</v>
       </c>
       <c r="AK25" t="s">
         <v>18</v>
@@ -5946,17 +5973,11 @@
       <c r="L26" t="s">
         <v>22</v>
       </c>
-      <c r="AB26" t="s">
-        <v>12</v>
-      </c>
       <c r="AD26" t="s">
         <v>65</v>
       </c>
       <c r="AE26" t="s">
         <v>65</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>22</v>
       </c>
       <c r="AK26" t="s">
         <v>23</v>
@@ -5972,18 +5993,12 @@
       <c r="L27" t="s">
         <v>20</v>
       </c>
-      <c r="AB27" t="s">
-        <v>55</v>
-      </c>
       <c r="AD27" t="s">
         <v>61</v>
       </c>
       <c r="AE27" t="s">
         <v>61</v>
       </c>
-      <c r="AI27" t="s">
-        <v>23</v>
-      </c>
       <c r="AK27" t="s">
         <v>30</v>
       </c>
@@ -5991,7 +6006,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="28:41" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6013,7 +6028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AP14"/>
+  <dimension ref="A3:AQ14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -6096,7 +6111,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -6122,10 +6137,10 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K3" t="s">
         <v>83</v>
@@ -6134,10 +6149,10 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
         <v>104</v>
@@ -6152,13 +6167,13 @@
         <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T3" t="s">
         <v>88</v>
       </c>
       <c r="U3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="V3" t="s">
         <v>89</v>
@@ -6179,7 +6194,7 @@
         <v>102</v>
       </c>
       <c r="AB3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="s">
         <v>107</v>
@@ -6188,28 +6203,28 @@
         <v>90</v>
       </c>
       <c r="AE3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH3" t="s">
         <v>109</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>112</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AK3" t="s">
         <v>108</v>
       </c>
-      <c r="AI3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AL3" t="s">
         <v>110</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>114</v>
       </c>
       <c r="AM3" t="s">
         <v>103</v>
@@ -6218,433 +6233,439 @@
         <v>111</v>
       </c>
       <c r="AO3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AP3" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="V4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="X4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Y4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Z4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AC4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AP4" t="s">
         <v>145</v>
       </c>
-      <c r="AE4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>144</v>
+      <c r="AQ4" t="s">
+        <v>158</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="T5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="U5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="V5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="W5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Z5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AB5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AD5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AE5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AF5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AI5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AK5" t="s">
-        <v>178</v>
+        <v>180</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>181</v>
       </c>
       <c r="AM5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AN5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AO5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="T6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="V6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="W6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Y6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Z6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AB6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AD6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AE6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AI6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AK6" t="s">
-        <v>200</v>
+        <v>203</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>204</v>
       </c>
       <c r="AM6" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AN6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AO6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="T7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="V7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="W7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Y7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Z7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AB7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AD7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AE7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AI7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AK7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AM7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AN7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AO7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H8" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="V8" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="W8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Y8" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AB8" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AD8" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AE8" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AI8" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AK8" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AM8" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AO8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L9" t="s">
-        <v>244</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AD9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AE9" t="s">
-        <v>247</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AK9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AO9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="28:41" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6677,34 +6698,34 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="10">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="13">
         <f>C1*4</f>
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B3" s="15">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
@@ -6712,35 +6733,35 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B4" s="18">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6749,10 +6770,10 @@
       </c>
       <c r="B5" s="18">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F5" s="20">
         <v>2</v>
@@ -6763,23 +6784,23 @@
       </c>
       <c r="H5" s="22">
         <f>B4/B3</f>
-        <v>0.1417910447761194</v>
+        <v>0.14522058823529413</v>
       </c>
       <c r="I5" s="23">
         <f>C2*G5</f>
-        <v>82.46153846153847</v>
+        <v>83.6923076923077</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K5" s="24">
         <f>J5-I5</f>
-        <v>-6.461538461538467</v>
+        <v>-4.692307692307693</v>
       </c>
       <c r="L5" s="25">
         <f>K5/4</f>
-        <v>-1.6153846153846168</v>
+        <v>-1.1730769230769234</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6788,7 +6809,7 @@
       </c>
       <c r="B6" s="18">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>1</v>
@@ -6802,23 +6823,23 @@
       </c>
       <c r="H6" s="22">
         <f>B5/B3</f>
-        <v>0.029850746268656716</v>
+        <v>0.03308823529411765</v>
       </c>
       <c r="I6" s="23">
         <f>C2*G6</f>
-        <v>41.23076923076923</v>
+        <v>41.84615384615385</v>
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K6" s="24">
         <f>J6-I6</f>
-        <v>-25.230769230769234</v>
+        <v>-23.846153846153847</v>
       </c>
       <c r="L6" s="25">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-6.307692307692308</v>
+        <v>-5.961538461538462</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6827,10 +6848,10 @@
       </c>
       <c r="B7" s="27">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F7" s="29">
         <v>3</v>
@@ -6841,28 +6862,28 @@
       </c>
       <c r="H7" s="31">
         <f>(B5+B4)/B3</f>
-        <v>0.17164179104477612</v>
+        <v>0.17830882352941177</v>
       </c>
       <c r="I7" s="23">
         <f>C2*G7</f>
-        <v>123.6923076923077</v>
+        <v>125.53846153846155</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K7" s="24">
         <f>J7-I7</f>
-        <v>-31.692307692307693</v>
+        <v>-28.538461538461547</v>
       </c>
       <c r="L7" s="25">
         <f>K7/4</f>
-        <v>-7.923076923076923</v>
+        <v>-7.134615384615387</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E8" s="32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F8" s="33">
         <v>6</v>
@@ -6873,35 +6894,35 @@
       </c>
       <c r="H8" s="35">
         <f>B6/B3</f>
-        <v>0.39552238805970147</v>
+        <v>0.39705882352941174</v>
       </c>
       <c r="I8" s="23">
         <f>C2*G8</f>
-        <v>247.3846153846154</v>
+        <v>251.0769230769231</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K8" s="24">
         <f>J8-I8</f>
-        <v>-35.38461538461539</v>
+        <v>-35.076923076923094</v>
       </c>
       <c r="L8" s="25">
         <f>K8/4</f>
-        <v>-8.846153846153847</v>
+        <v>-8.769230769230774</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F9" s="33">
         <v>4</v>
@@ -6912,36 +6933,36 @@
       </c>
       <c r="H9" s="35">
         <f>B7/B3</f>
-        <v>0.43283582089552236</v>
+        <v>0.42463235294117646</v>
       </c>
       <c r="I9" s="23">
         <f>C2*G9</f>
-        <v>164.92307692307693</v>
+        <v>167.3846153846154</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K9" s="36">
         <f>J9-I9</f>
-        <v>67.07692307692307</v>
+        <v>63.61538461538461</v>
       </c>
       <c r="L9" s="25">
         <f>K9/4</f>
-        <v>16.769230769230766</v>
+        <v>15.903846153846153</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="37" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I11" s="38">
         <f>SUM(I7:I9)</f>
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="J11" s="32">
         <f>SUM(J7:J9)</f>
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="K11" s="39">
         <f>SUM(K7:K9)</f>
@@ -6954,33 +6975,33 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G16" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H16" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K16" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="42" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F17" s="43">
         <v>3</v>
@@ -6991,28 +7012,28 @@
       </c>
       <c r="H17" s="45">
         <f>(B5+B4)/B3</f>
-        <v>0.17164179104477612</v>
+        <v>0.17830882352941177</v>
       </c>
       <c r="I17" s="46">
         <f>B3*G17</f>
-        <v>123.6923076923077</v>
+        <v>125.53846153846155</v>
       </c>
       <c r="J17" s="47">
         <f>B5+B4</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K17" s="48">
         <f>J17-I17</f>
-        <v>-31.692307692307693</v>
+        <v>-28.538461538461547</v>
       </c>
       <c r="L17" s="25">
         <f>K17/4</f>
-        <v>-7.923076923076923</v>
+        <v>-7.134615384615387</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="49" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F18" s="50">
         <v>6</v>
@@ -7023,29 +7044,29 @@
       </c>
       <c r="H18" s="52">
         <f>B6/B3</f>
-        <v>0.39552238805970147</v>
+        <v>0.39705882352941174</v>
       </c>
       <c r="I18" s="53">
         <f>B3*G18</f>
-        <v>247.3846153846154</v>
+        <v>251.0769230769231</v>
       </c>
       <c r="J18" s="54">
         <f>B6</f>
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K18" s="55">
         <f>J18-I18</f>
-        <v>-35.38461538461539</v>
+        <v>-35.076923076923094</v>
       </c>
       <c r="L18" s="25">
         <f>K18/4</f>
-        <v>-8.846153846153847</v>
+        <v>-8.769230769230774</v>
       </c>
       <c r="Q18" s="56"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="57" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F19" s="58">
         <v>4</v>
@@ -7056,30 +7077,30 @@
       </c>
       <c r="H19" s="60">
         <f>B7/B3</f>
-        <v>0.43283582089552236</v>
+        <v>0.42463235294117646</v>
       </c>
       <c r="I19" s="61">
         <f>B3*G19</f>
-        <v>164.92307692307693</v>
+        <v>167.3846153846154</v>
       </c>
       <c r="J19" s="62">
         <f>B7</f>
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K19" s="63">
         <f>J19-I19</f>
-        <v>67.07692307692307</v>
+        <v>63.61538461538461</v>
       </c>
       <c r="L19" s="25">
         <f>K19/4</f>
-        <v>16.769230769230766</v>
+        <v>15.903846153846153</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="P24" s="64" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q24" s="64"/>
       <c r="R24" s="64"/>
@@ -7088,18 +7109,18 @@
     <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P25" s="65"/>
       <c r="Q25" s="66" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R25" s="67" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="S25" s="68" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P26" s="69" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q26" s="32">
         <v>247</v>
@@ -7114,7 +7135,7 @@
     </row>
     <row r="27" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P27" s="69" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q27" s="32">
         <v>124</v>
@@ -7129,7 +7150,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P28" s="70" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q28" s="71">
         <v>165</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF563A9-4B9F-41EE-9CBE-624B129874BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
+    <sheet name="AHL" sheetId="1" r:id="rId1"/>
+    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
+    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="273">
   <si>
     <t>sl</t>
   </si>
@@ -301,9 +315,6 @@
     <t>2024-11-14</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2024-10-16</t>
   </si>
   <si>
@@ -629,9 +640,6 @@
   </si>
   <si>
     <t>Würtharena Neumarkt;BulovecMi;LebenJa;GrisentiLu;JeramFi</t>
-  </si>
-  <si>
-    <t>ZBRISANO</t>
   </si>
   <si>
     <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;ScalzeriAl</t>
@@ -847,45 +855,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF9C0006"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF006100"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -897,25 +905,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -927,7 +935,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,7 +952,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -955,7 +963,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1242,25 +1250,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1354,9 +1347,6 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1370,6 +1360,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1649,9 +1657,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BQ73"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BP73"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -1723,7 +1731,7 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
         <v>9</v>
@@ -1737,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="D1">
-        <f>COUNTIF(D4:D69,"&lt;&gt;")</f>
+        <f>COUNTIF(D4:D68,"&lt;&gt;")</f>
         <v>10</v>
       </c>
       <c r="E1">
@@ -1753,7 +1761,7 @@
         <v>4</v>
       </c>
       <c r="H1">
-        <f>COUNTIF(H4:H69,"&lt;&gt;")</f>
+        <f>COUNTIF(H4:H68,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="I1">
@@ -1806,10 +1814,10 @@
       </c>
       <c r="U1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V1">
-        <f>COUNTIF(V4:V68,"&lt;&gt;")</f>
+        <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="W1">
@@ -1845,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="AE1">
-        <f>COUNTIF(AE4:AE69,"&lt;&gt;")</f>
+        <f>COUNTIF(AE4:AE68,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AF1">
@@ -1865,8 +1873,8 @@
         <v>3</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ66,"&lt;&gt;")</f>
-        <v>7</v>
+        <f>COUNTIF(AJ4:AJ65,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="AK1">
         <f>COUNTIF(AK4:AK66,"&lt;&gt;")</f>
@@ -1997,7 +2005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2203,7 +2211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2409,7 +2417,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -2615,7 +2623,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -2719,8 +2727,8 @@
       <c r="AI5" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="AJ5" s="7" t="s">
-        <v>94</v>
+      <c r="AJ5" t="s">
+        <v>90</v>
       </c>
       <c r="AK5" t="s">
         <v>89</v>
@@ -2744,7 +2752,7 @@
         <v>83</v>
       </c>
       <c r="AR5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AS5" t="s">
         <v>74</v>
@@ -2762,7 +2770,7 @@
         <v>84</v>
       </c>
       <c r="AX5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AY5" t="s">
         <v>75</v>
@@ -2777,10 +2785,10 @@
         <v>85</v>
       </c>
       <c r="BC5" t="s">
+        <v>96</v>
+      </c>
+      <c r="BD5" t="s">
         <v>97</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>98</v>
       </c>
       <c r="BE5" t="s">
         <v>87</v>
@@ -2789,17 +2797,17 @@
         <v>76</v>
       </c>
       <c r="BG5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH5" t="s">
         <v>99</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>100</v>
       </c>
       <c r="BI5" s="7"/>
       <c r="BJ5" t="s">
         <v>87</v>
       </c>
       <c r="BK5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BL5" s="7"/>
       <c r="BM5" t="s">
@@ -2812,10 +2820,10 @@
         <v>91</v>
       </c>
       <c r="BP5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -2841,7 +2849,7 @@
         <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" t="s">
         <v>90</v>
@@ -2886,13 +2894,13 @@
         <v>85</v>
       </c>
       <c r="Z6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AA6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AB6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AC6" t="s">
         <v>79</v>
@@ -2910,43 +2918,43 @@
         <v>83</v>
       </c>
       <c r="AH6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI6" t="s">
         <v>102</v>
       </c>
-      <c r="AI6" t="s">
-        <v>103</v>
-      </c>
       <c r="AJ6" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s">
         <v>78</v>
       </c>
       <c r="AL6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AM6" t="s">
         <v>73</v>
       </c>
       <c r="AN6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AO6" t="s">
         <v>78</v>
       </c>
       <c r="AP6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AQ6" t="s">
         <v>73</v>
       </c>
       <c r="AR6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AS6" t="s">
         <v>75</v>
       </c>
       <c r="AT6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AU6" t="s">
         <v>83</v>
@@ -2958,7 +2966,7 @@
         <v>79</v>
       </c>
       <c r="AX6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AY6" t="s">
         <v>72</v>
@@ -2976,7 +2984,7 @@
         <v>74</v>
       </c>
       <c r="BD6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BE6" s="7" t="s">
         <v>93</v>
@@ -2988,7 +2996,7 @@
         <v>90</v>
       </c>
       <c r="BH6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="BJ6" s="7" t="s">
         <v>90</v>
@@ -2997,27 +3005,27 @@
         <v>80</v>
       </c>
       <c r="BM6" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BN6" t="s">
         <v>92</v>
       </c>
       <c r="BO6" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BP6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
         <v>79</v>
@@ -3053,7 +3061,7 @@
         <v>83</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="s">
         <v>75</v>
@@ -3080,22 +3088,22 @@
         <v>79</v>
       </c>
       <c r="Z7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB7" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC7" t="s">
         <v>95</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB7" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>96</v>
       </c>
       <c r="AD7" t="s">
         <v>78</v>
       </c>
       <c r="AE7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF7" t="s">
         <v>80</v>
@@ -3107,10 +3115,10 @@
         <v>90</v>
       </c>
       <c r="AJ7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK7" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="AK7" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="AL7" t="s">
         <v>89</v>
@@ -3119,7 +3127,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AO7" t="s">
         <v>89</v>
@@ -3128,7 +3136,7 @@
         <v>89</v>
       </c>
       <c r="AQ7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AR7" t="s">
         <v>75</v>
@@ -3155,13 +3163,13 @@
         <v>78</v>
       </c>
       <c r="AZ7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="BA7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BB7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BC7" t="s">
         <v>88</v>
@@ -3170,34 +3178,34 @@
         <v>75</v>
       </c>
       <c r="BE7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BF7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BG7" t="s">
         <v>92</v>
       </c>
       <c r="BH7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BK7" t="s">
         <v>108</v>
       </c>
-      <c r="BJ7" t="s">
-        <v>101</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>109</v>
-      </c>
       <c r="BM7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="BN7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BO7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -3223,19 +3231,19 @@
         <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K8" t="s">
         <v>76</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N8" t="s">
         <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
         <v>74</v>
@@ -3250,7 +3258,7 @@
         <v>79</v>
       </c>
       <c r="T8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U8" t="s">
         <v>78</v>
@@ -3259,7 +3267,7 @@
         <v>88</v>
       </c>
       <c r="W8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y8" t="s">
         <v>78</v>
@@ -3277,7 +3285,7 @@
         <v>78</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AE8" t="s">
         <v>89</v>
@@ -3289,13 +3297,13 @@
         <v>88</v>
       </c>
       <c r="AH8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="AK8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AL8" t="s">
         <v>87</v>
@@ -3331,7 +3339,7 @@
         <v>89</v>
       </c>
       <c r="AW8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AX8" t="s">
         <v>78</v>
@@ -3343,19 +3351,19 @@
         <v>78</v>
       </c>
       <c r="BA8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BB8" t="s">
         <v>89</v>
       </c>
       <c r="BC8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="BD8" t="s">
         <v>87</v>
       </c>
       <c r="BE8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BF8" t="s">
         <v>93</v>
@@ -3364,16 +3372,16 @@
         <v>92</v>
       </c>
       <c r="BK8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BM8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BN8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>91</v>
       </c>
@@ -3384,28 +3392,28 @@
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>81</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L9" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="L9" t="s">
-        <v>103</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="O9" t="s">
         <v>91</v>
@@ -3414,13 +3422,13 @@
         <v>78</v>
       </c>
       <c r="Q9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R9" t="s">
         <v>80</v>
       </c>
       <c r="S9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T9" t="s">
         <v>76</v>
@@ -3441,16 +3449,16 @@
         <v>91</v>
       </c>
       <c r="AA9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AB9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AC9" t="s">
         <v>89</v>
       </c>
       <c r="AD9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AE9" s="7" t="s">
         <v>90</v>
@@ -3462,16 +3470,16 @@
         <v>87</v>
       </c>
       <c r="AH9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>110</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>76</v>
-      </c>
       <c r="AK9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AL9" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="s">
         <v>88</v>
@@ -3483,7 +3491,7 @@
         <v>86</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AQ9" t="s">
         <v>87</v>
@@ -3498,10 +3506,10 @@
         <v>78</v>
       </c>
       <c r="AU9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AV9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AW9" t="s">
         <v>88</v>
@@ -3522,24 +3530,24 @@
         <v>87</v>
       </c>
       <c r="BC9" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BD9" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BF9" t="s">
         <v>92</v>
       </c>
       <c r="BK9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>93</v>
@@ -3551,25 +3559,25 @@
         <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s">
+        <v>110</v>
+      </c>
+      <c r="N10" t="s">
         <v>111</v>
       </c>
-      <c r="N10" t="s">
-        <v>112</v>
-      </c>
       <c r="O10" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P10" s="7" t="s">
         <v>93</v>
@@ -3587,7 +3595,7 @@
         <v>80</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -3599,10 +3607,10 @@
         <v>86</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AB10" t="s">
         <v>92</v>
@@ -3611,34 +3619,31 @@
         <v>87</v>
       </c>
       <c r="AD10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AE10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s">
         <v>90</v>
       </c>
       <c r="AH10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AK10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AL10" t="s">
         <v>93</v>
       </c>
       <c r="AM10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AN10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AO10" t="s">
         <v>90</v>
@@ -3653,7 +3658,7 @@
         <v>76</v>
       </c>
       <c r="AS10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AT10" t="s">
         <v>86</v>
@@ -3662,16 +3667,16 @@
         <v>90</v>
       </c>
       <c r="AV10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW10" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="AW10" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="AX10" t="s">
         <v>87</v>
       </c>
       <c r="AY10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AZ10" t="s">
         <v>89</v>
@@ -3683,51 +3688,51 @@
         <v>91</v>
       </c>
       <c r="BC10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BD10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>92</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
         <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="K11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O11" t="s">
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="s">
         <v>91</v>
@@ -3745,22 +3750,22 @@
         <v>93</v>
       </c>
       <c r="V11" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="W11" t="s">
         <v>91</v>
       </c>
       <c r="Y11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AA11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AD11" t="s">
         <v>92</v>
@@ -3772,7 +3777,7 @@
         <v>92</v>
       </c>
       <c r="AG11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s">
         <v>87</v>
@@ -3790,16 +3795,16 @@
         <v>93</v>
       </c>
       <c r="AP11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AQ11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AR11" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AS11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AT11" t="s">
         <v>89</v>
@@ -3808,10 +3813,10 @@
         <v>92</v>
       </c>
       <c r="AV11" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AW11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AX11" t="s">
         <v>91</v>
@@ -3820,7 +3825,7 @@
         <v>90</v>
       </c>
       <c r="AZ11" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="BA11" s="7" t="s">
         <v>90</v>
@@ -3832,10 +3837,10 @@
         <v>90</v>
       </c>
       <c r="BD11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -3843,126 +3848,120 @@
         <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>93</v>
       </c>
-      <c r="H12" t="s">
-        <v>115</v>
-      </c>
       <c r="K12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U12" t="s">
-        <v>108</v>
-      </c>
-      <c r="V12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AC12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AD12" t="s">
         <v>87</v>
       </c>
       <c r="AE12" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK12" t="s">
         <v>93</v>
       </c>
       <c r="AM12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AP12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AQ12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AR12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AT12" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AV12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AW12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AX12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AY12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AZ12" t="s">
         <v>90</v>
       </c>
       <c r="BA12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BB12" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O13" t="s">
         <v>92</v>
       </c>
       <c r="P13" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>107</v>
+      </c>
+      <c r="R13" t="s">
         <v>111</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>108</v>
-      </c>
-      <c r="R13" t="s">
-        <v>112</v>
       </c>
       <c r="S13" t="s">
         <v>93</v>
@@ -3974,54 +3973,48 @@
         <v>92</v>
       </c>
       <c r="W13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y13" t="s">
         <v>93</v>
       </c>
       <c r="Z13" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="AM13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AN13" t="s">
         <v>92</v>
       </c>
       <c r="AR13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AT13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV13" t="s">
         <v>92</v>
       </c>
       <c r="AX13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AY13" t="s">
         <v>92</v>
       </c>
       <c r="AZ13" t="s">
+        <v>107</v>
+      </c>
+      <c r="BA13" t="s">
         <v>108</v>
       </c>
-      <c r="BA13" t="s">
-        <v>109</v>
-      </c>
       <c r="BB13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
+    <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O14" t="s">
         <v>89</v>
@@ -4030,60 +4023,60 @@
         <v>92</v>
       </c>
       <c r="R14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="U14" t="s">
         <v>91</v>
       </c>
       <c r="W14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y14" t="s">
         <v>90</v>
       </c>
       <c r="Z14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AN14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AR14" t="s">
         <v>92</v>
       </c>
       <c r="AT14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AZ14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BB14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AT15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4143,14 +4136,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:AQ42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -4195,7 +4188,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -4221,10 +4214,10 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K3" t="s">
         <v>83</v>
@@ -4233,13 +4226,13 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P3" t="s">
         <v>78</v>
@@ -4251,7 +4244,7 @@
         <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T3" t="s">
         <v>88</v>
@@ -4266,7 +4259,7 @@
         <v>76</v>
       </c>
       <c r="X3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y3" t="s">
         <v>87</v>
@@ -4275,58 +4268,58 @@
         <v>91</v>
       </c>
       <c r="AA3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AB3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="s">
         <v>90</v>
       </c>
       <c r="AE3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
         <v>93</v>
       </c>
       <c r="AJ3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AL3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN3" t="s">
         <v>110</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>111</v>
       </c>
       <c r="AO3" t="s">
         <v>92</v>
       </c>
       <c r="AP3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>114</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>115</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4457,7 +4450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4588,7 +4581,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4719,7 +4712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4850,12 +4843,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -4879,7 +4872,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -4930,7 +4923,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -4944,7 +4937,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -5010,7 +5003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -5090,7 +5083,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -5170,7 +5163,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -5196,7 +5189,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -5238,7 +5231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -5306,7 +5299,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -5374,7 +5367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -5442,7 +5435,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -5510,7 +5503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -5578,7 +5571,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -5646,7 +5639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5714,7 +5707,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -5767,7 +5760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -5820,7 +5813,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -5873,7 +5866,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -5926,7 +5919,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -5946,7 +5939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -5966,7 +5959,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -5986,7 +5979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -6006,11 +5999,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6026,10 +6019,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:AQ14"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -6111,7 +6104,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -6137,10 +6130,10 @@
         <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K3" t="s">
         <v>83</v>
@@ -6149,13 +6142,13 @@
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P3" t="s">
         <v>78</v>
@@ -6167,7 +6160,7 @@
         <v>86</v>
       </c>
       <c r="S3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T3" t="s">
         <v>88</v>
@@ -6182,7 +6175,7 @@
         <v>76</v>
       </c>
       <c r="X3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y3" t="s">
         <v>87</v>
@@ -6191,495 +6184,492 @@
         <v>91</v>
       </c>
       <c r="AA3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AB3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AD3" t="s">
         <v>90</v>
       </c>
       <c r="AE3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AH3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
         <v>93</v>
       </c>
       <c r="AJ3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AL3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN3" t="s">
         <v>110</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>111</v>
       </c>
       <c r="AO3" t="s">
         <v>92</v>
       </c>
       <c r="AP3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>114</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>115</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" t="s">
         <v>117</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>118</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>119</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>120</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>121</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>122</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>123</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>124</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>125</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>126</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>127</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>128</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>129</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>130</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>131</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>132</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>133</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>134</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>135</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>136</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>137</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>138</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>139</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>140</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>141</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>142</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>143</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>144</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>145</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>146</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>147</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>148</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>149</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>150</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>151</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>152</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>153</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>154</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>155</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>156</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>157</v>
       </c>
-      <c r="AP4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AQ4" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>158</v>
       </c>
+      <c r="D5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K5" t="s">
+        <v>163</v>
+      </c>
+      <c r="L5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N5" t="s">
+        <v>165</v>
+      </c>
+      <c r="P5" t="s">
+        <v>166</v>
+      </c>
+      <c r="R5" t="s">
+        <v>167</v>
+      </c>
+      <c r="T5" t="s">
+        <v>168</v>
+      </c>
+      <c r="U5" t="s">
+        <v>169</v>
+      </c>
+      <c r="V5" t="s">
+        <v>170</v>
+      </c>
+      <c r="W5" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>179</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>180</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>181</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>183</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" t="s">
-        <v>162</v>
-      </c>
-      <c r="H5" t="s">
-        <v>163</v>
-      </c>
-      <c r="K5" t="s">
-        <v>164</v>
-      </c>
-      <c r="L5" t="s">
-        <v>165</v>
-      </c>
-      <c r="N5" t="s">
-        <v>166</v>
-      </c>
-      <c r="P5" t="s">
-        <v>167</v>
-      </c>
-      <c r="R5" t="s">
-        <v>168</v>
-      </c>
-      <c r="T5" t="s">
-        <v>169</v>
-      </c>
-      <c r="U5" t="s">
-        <v>170</v>
-      </c>
-      <c r="V5" t="s">
-        <v>171</v>
-      </c>
-      <c r="W5" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>175</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>178</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>180</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>181</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>182</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>183</v>
-      </c>
-      <c r="AO5" t="s">
+    <row r="6" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>184</v>
       </c>
+      <c r="D6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K6" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" t="s">
+        <v>190</v>
+      </c>
+      <c r="N6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P6" t="s">
+        <v>192</v>
+      </c>
+      <c r="T6" t="s">
+        <v>193</v>
+      </c>
+      <c r="V6" t="s">
+        <v>194</v>
+      </c>
+      <c r="W6" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>205</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" t="s">
-        <v>187</v>
-      </c>
-      <c r="G6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H6" t="s">
-        <v>189</v>
-      </c>
-      <c r="K6" t="s">
-        <v>190</v>
-      </c>
-      <c r="L6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N6" t="s">
-        <v>192</v>
-      </c>
-      <c r="P6" t="s">
-        <v>193</v>
-      </c>
-      <c r="T6" t="s">
-        <v>194</v>
-      </c>
-      <c r="V6" t="s">
-        <v>195</v>
-      </c>
-      <c r="W6" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>198</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>199</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>200</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>202</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>203</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>204</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>205</v>
-      </c>
-      <c r="AN6" t="s">
+    <row r="7" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>206</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="D7" t="s">
         <v>207</v>
       </c>
+      <c r="F7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" t="s">
+        <v>210</v>
+      </c>
+      <c r="K7" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" t="s">
+        <v>213</v>
+      </c>
+      <c r="P7" t="s">
+        <v>214</v>
+      </c>
+      <c r="T7" t="s">
+        <v>215</v>
+      </c>
+      <c r="V7" t="s">
+        <v>216</v>
+      </c>
+      <c r="W7" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>220</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>222</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>223</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>224</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>225</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>226</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>227</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" t="s">
-        <v>212</v>
-      </c>
-      <c r="K7" t="s">
-        <v>213</v>
-      </c>
-      <c r="L7" t="s">
-        <v>214</v>
-      </c>
-      <c r="N7" t="s">
-        <v>215</v>
-      </c>
-      <c r="P7" t="s">
-        <v>216</v>
-      </c>
-      <c r="T7" t="s">
-        <v>217</v>
-      </c>
-      <c r="V7" t="s">
-        <v>218</v>
-      </c>
-      <c r="W7" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>222</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>223</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>224</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>225</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>226</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>227</v>
-      </c>
-      <c r="AN7" t="s">
+    <row r="8" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>228</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="D8" t="s">
         <v>229</v>
       </c>
+      <c r="F8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" t="s">
+        <v>232</v>
+      </c>
+      <c r="K8" t="s">
+        <v>233</v>
+      </c>
+      <c r="L8" t="s">
+        <v>234</v>
+      </c>
+      <c r="V8" t="s">
+        <v>235</v>
+      </c>
+      <c r="W8" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>237</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>238</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>239</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>243</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>244</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" t="s">
-        <v>231</v>
-      </c>
-      <c r="F8" t="s">
-        <v>232</v>
-      </c>
-      <c r="G8" t="s">
-        <v>233</v>
-      </c>
-      <c r="H8" t="s">
-        <v>234</v>
-      </c>
-      <c r="K8" t="s">
-        <v>235</v>
-      </c>
-      <c r="L8" t="s">
-        <v>236</v>
-      </c>
-      <c r="V8" t="s">
-        <v>237</v>
-      </c>
-      <c r="W8" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>239</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>240</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>241</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>242</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>243</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>244</v>
-      </c>
-      <c r="AM8" t="s">
+    <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
         <v>245</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="L9" t="s">
         <v>246</v>
       </c>
+      <c r="AD9" t="s">
+        <v>247</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>249</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>250</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>247</v>
-      </c>
-      <c r="L9" t="s">
-        <v>248</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>249</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>250</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>251</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.140625" customWidth="1"/>
@@ -6696,175 +6686,175 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="8">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>136</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="9">
         <f>C1*4</f>
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B3" s="15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="11">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>544</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
+      <c r="E3" s="70" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="B4" s="18">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="13">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>79</v>
       </c>
       <c r="E4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" t="s">
         <v>257</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>258</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>259</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>260</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>261</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>262</v>
       </c>
-      <c r="K4" t="s">
-        <v>263</v>
-      </c>
-      <c r="L4" t="s">
-        <v>264</v>
-      </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="13">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>18</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="F5" s="20">
+      <c r="E5" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="15">
         <v>2</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="16">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="17">
         <f>B4/B3</f>
         <v>0.14522058823529413</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="18">
         <f>C2*G5</f>
-        <v>83.6923076923077</v>
+        <v>83.692307692307693</v>
       </c>
       <c r="J5">
         <f>B4</f>
         <v>79</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="19">
         <f>J5-I5</f>
-        <v>-4.692307692307693</v>
-      </c>
-      <c r="L5" s="25">
+        <v>-4.6923076923076934</v>
+      </c>
+      <c r="L5" s="20">
         <f>K5/4</f>
         <v>-1.1730769230769234</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="13">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
         <v>216</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="15">
         <v>1</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="16">
         <f>F6/13</f>
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="H6" s="22">
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="H6" s="17">
         <f>B5/B3</f>
-        <v>0.03308823529411765</v>
-      </c>
-      <c r="I6" s="23">
+        <v>3.3088235294117647E-2</v>
+      </c>
+      <c r="I6" s="18">
         <f>C2*G6</f>
-        <v>41.84615384615385</v>
+        <v>41.846153846153847</v>
       </c>
       <c r="J6">
         <f>B5</f>
         <v>18</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="19">
         <f>J6-I6</f>
         <v>-23.846153846153847</v>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="20">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-5.961538461538462</v>
+        <v>-5.9615384615384617</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>231</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="29">
+      <c r="E7" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="24">
         <v>3</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="25">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="26">
         <f>(B5+B4)/B3</f>
         <v>0.17830882352941177</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="18">
         <f>C2*G7</f>
         <v>125.53846153846155</v>
       </c>
@@ -6872,293 +6862,293 @@
         <f>B4+B5</f>
         <v>97</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="19">
         <f>J7-I7</f>
         <v>-28.538461538461547</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="20">
         <f>K7/4</f>
-        <v>-7.134615384615387</v>
+        <v>-7.1346153846153868</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E8" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="33">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" s="28">
         <v>6</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="29">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="30">
         <f>B6/B3</f>
         <v>0.39705882352941174</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="18">
         <f>C2*G8</f>
-        <v>251.0769230769231</v>
+        <v>251.07692307692309</v>
       </c>
       <c r="J8">
         <f>B6</f>
         <v>216</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="19">
         <f>J8-I8</f>
         <v>-35.076923076923094</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="20">
         <f>K8/4</f>
-        <v>-8.769230769230774</v>
+        <v>-8.7692307692307736</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>544</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="F9" s="33">
+      <c r="E9" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="28">
         <v>4</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="29">
         <f t="shared" si="1"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H9" s="35">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H9" s="30">
         <f>B7/B3</f>
         <v>0.42463235294117646</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="18">
         <f>C2*G9</f>
-        <v>167.3846153846154</v>
+        <v>167.38461538461539</v>
       </c>
       <c r="J9">
         <f>B7</f>
         <v>231</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="31">
         <f>J9-I9</f>
-        <v>63.61538461538461</v>
-      </c>
-      <c r="L9" s="25">
+        <v>63.615384615384613</v>
+      </c>
+      <c r="L9" s="20">
         <f>K9/4</f>
         <v>15.903846153846153</v>
       </c>
     </row>
-    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="I11" s="38">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="I11" s="33">
         <f>SUM(I7:I9)</f>
         <v>544</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="27">
         <f>SUM(J7:J9)</f>
         <v>544</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="34">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="35">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F16" t="s">
+        <v>256</v>
+      </c>
+      <c r="G16" t="s">
+        <v>269</v>
+      </c>
+      <c r="H16" t="s">
         <v>258</v>
       </c>
-      <c r="G16" t="s">
-        <v>271</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="I16" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="J16" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="I16" s="41" t="s">
+      <c r="K16" t="s">
         <v>261</v>
       </c>
-      <c r="J16" s="41" t="s">
+      <c r="L16" t="s">
         <v>262</v>
       </c>
-      <c r="K16" t="s">
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E17" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="L16" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="F17" s="43">
+      <c r="F17" s="38">
         <v>3</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="39">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="40">
         <f>(B5+B4)/B3</f>
         <v>0.17830882352941177</v>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="41">
         <f>B3*G17</f>
         <v>125.53846153846155</v>
       </c>
-      <c r="J17" s="47">
+      <c r="J17" s="42">
         <f>B5+B4</f>
         <v>97</v>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="43">
         <f>J17-I17</f>
         <v>-28.538461538461547</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="20">
         <f>K17/4</f>
-        <v>-7.134615384615387</v>
+        <v>-7.1346153846153868</v>
       </c>
     </row>
-    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="49" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="50">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E18" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="F18" s="45">
         <v>6</v>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="46">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="47">
         <f>B6/B3</f>
         <v>0.39705882352941174</v>
       </c>
-      <c r="I18" s="53">
+      <c r="I18" s="48">
         <f>B3*G18</f>
-        <v>251.0769230769231</v>
-      </c>
-      <c r="J18" s="54">
+        <v>251.07692307692309</v>
+      </c>
+      <c r="J18" s="49">
         <f>B6</f>
         <v>216</v>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="50">
         <f>J18-I18</f>
         <v>-35.076923076923094</v>
       </c>
-      <c r="L18" s="25">
+      <c r="L18" s="20">
         <f>K18/4</f>
-        <v>-8.769230769230774</v>
-      </c>
-      <c r="Q18" s="56"/>
+        <v>-8.7692307692307736</v>
+      </c>
+      <c r="Q18" s="51"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="57" t="s">
-        <v>268</v>
-      </c>
-      <c r="F19" s="58">
+    <row r="19" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="52" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" s="53">
         <v>4</v>
       </c>
-      <c r="G19" s="59">
+      <c r="G19" s="54">
         <f t="shared" si="2"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H19" s="60">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H19" s="55">
         <f>B7/B3</f>
         <v>0.42463235294117646</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="56">
         <f>B3*G19</f>
-        <v>167.3846153846154</v>
-      </c>
-      <c r="J19" s="62">
+        <v>167.38461538461539</v>
+      </c>
+      <c r="J19" s="57">
         <f>B7</f>
         <v>231</v>
       </c>
-      <c r="K19" s="63">
+      <c r="K19" s="58">
         <f>J19-I19</f>
-        <v>63.61538461538461</v>
-      </c>
-      <c r="L19" s="25">
+        <v>63.615384615384613</v>
+      </c>
+      <c r="L19" s="20">
         <f>K19/4</f>
         <v>15.903846153846153</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="P24" s="64" t="s">
+    <row r="24" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="P24" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="71"/>
+    </row>
+    <row r="25" spans="5:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="59"/>
+      <c r="Q25" s="60" t="s">
+        <v>271</v>
+      </c>
+      <c r="R25" s="61" t="s">
         <v>272</v>
       </c>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64"/>
+      <c r="S25" s="62" t="s">
+        <v>261</v>
+      </c>
     </row>
-    <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P25" s="65"/>
-      <c r="Q25" s="66" t="s">
-        <v>273</v>
-      </c>
-      <c r="R25" s="67" t="s">
-        <v>274</v>
-      </c>
-      <c r="S25" s="68" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="26" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P26" s="69" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q26" s="32">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="P26" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q26" s="27">
         <v>247</v>
       </c>
-      <c r="R26" s="32">
+      <c r="R26" s="27">
         <v>212</v>
       </c>
-      <c r="S26" s="18">
+      <c r="S26" s="13">
         <f>R26-Q26</f>
         <v>-35</v>
       </c>
     </row>
-    <row r="27" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P27" s="69" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q27" s="32">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="P27" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q27" s="27">
         <v>124</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="27">
         <v>92</v>
       </c>
-      <c r="S27" s="18">
+      <c r="S27" s="13">
         <f t="shared" ref="S27:S28" si="3">R27-Q27</f>
         <v>-32</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P28" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q28" s="71">
+    <row r="28" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q28" s="65">
         <v>165</v>
       </c>
-      <c r="R28" s="71">
+      <c r="R28" s="65">
         <v>232</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="22">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF563A9-4B9F-41EE-9CBE-624B129874BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="AHL" sheetId="1" r:id="rId1"/>
-    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
-    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
-    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
+    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="274">
   <si>
     <t>sl</t>
   </si>
@@ -342,15 +328,15 @@
     <t>2024-11-28</t>
   </si>
   <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
     <t>2024-10-06</t>
   </si>
   <si>
     <t>2024-11-02</t>
   </si>
   <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
     <t>2024-11-17</t>
   </si>
   <si>
@@ -378,6 +364,9 @@
     <t>2024-11-24</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>HuberRe</t>
   </si>
   <si>
@@ -462,7 +451,7 @@
     <t>Eishalle Sterzing;GiacomozziFe;PirasAn;PaceJa;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;VirtaTu;WidmannFl;AbeltinoSi;TelesklavFa</t>
+    <t>Sportpark Kitzbühel;SpiegelSe;VoicanCh;PreiserJu;WeissAl</t>
   </si>
   <si>
     <t>Eishalle Ritten;MetzingerFi;StefenelliFe;CristeliMa;KnezRo</t>
@@ -495,7 +484,7 @@
     <t>Kitzbühel Sportpark;BenvegnuAn;LazzeriAl;RinkerDa;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
+    <t>Eishalle Jesenice;BrockAd;MeixnerSe;LegatKo;ZacherlPa</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
@@ -555,10 +544,10 @@
     <t>Eishalle Ritten;SoraperraSi;VirtaTu;CusinFe;PaceJa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;SpiegelSe;VoicanCh;LegatKo;WeissAl</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;EggerTh;PinieOm;IlmerNo;PaceJa</t>
+    <t>KELIT Arena Zell am See;BrockAd;OrelSt;WendnerMa;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;EggerTh;PinieOm;PaceJa;ScalzeriAl</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CusinFe</t>
@@ -627,7 +616,7 @@
     <t>Eishalle Sterzing;MoidlDa;SpiegelSe;DivisDo;RinkerDa</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;BrockAd;OrelSt;WendnerMa;WuchererGe</t>
+    <t>Eishalle Dornbirn;MoschenAn;RuetzMa;DivisDo;IlmerNo</t>
   </si>
   <si>
     <t>Eishalle Celje;VoicanCh;WidmannFl;WeissAl;WuchererGe</t>
@@ -693,7 +682,7 @@
     <t>Würtharena Neumarkt;MoschenAn;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;MoschenAn;RuetzMa;DivisDo;IlmerNo</t>
+    <t>Eishalle Meran;LesniakBo;SnojTa;ArlicMa;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;BajtMi;RivisFe;JavornikBl;RivisAn</t>
@@ -747,7 +736,7 @@
     <t>Eishalle Cortina;LebenJa;PirasAn;AbeltinoSi;CristeliMa</t>
   </si>
   <si>
-    <t>Eishalle Meran;LesniakBo;SnojTa;ArlicMa;StrimitzerDa</t>
+    <t>Eishalle Jesenice;VirtaTu;WidmannFl;PaceJa;TelesklavFa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;Huber rRe;LehnerMo;EislCh;StrimitzerDa</t>
@@ -762,7 +751,7 @@
     <t>Eishalle Meran;StefenelliFe;VirtaTu;CristeliMa;PaceJa</t>
   </si>
   <si>
-    <t>Eishalle Cortina;LegaSi;VirtaTu;CristeliMa;IlmerNo</t>
+    <t>Eishalle Cortina;LegaSi;VirtaTu;CristeliMa;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Gröden;GiacomozziFe;MoidlDa;MattheyPh;MoidlMa</t>
@@ -855,45 +844,45 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF9C0006"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF006100"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -905,25 +894,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -935,7 +924,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -952,7 +941,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -963,12 +952,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -983,6 +972,13 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1241,7 +1237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1250,134 +1246,135 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1657,9 +1654,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BP73"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BQ73"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -1731,7 +1728,7 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
         <v>9</v>
@@ -1845,8 +1842,8 @@
         <v>7</v>
       </c>
       <c r="AC1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
+        <v>8</v>
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD69,"&lt;&gt;")</f>
@@ -1866,7 +1863,7 @@
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI69,"&lt;&gt;")</f>
@@ -1921,11 +1918,11 @@
         <v>8</v>
       </c>
       <c r="AV1">
-        <f>COUNTIF(AV4:AV68,"&lt;&gt;")</f>
+        <f>COUNTIF(AV4:AV67,"&lt;&gt;")</f>
         <v>10</v>
       </c>
       <c r="AW1">
-        <f>COUNTIF(AW4:AW68,"&lt;&gt;")</f>
+        <f>COUNTIF(AW4:AW67,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AX1">
@@ -2005,7 +2002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:68" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2211,7 +2208,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2417,7 +2414,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -2623,7 +2620,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -2724,7 +2721,7 @@
       <c r="AH5" t="s">
         <v>91</v>
       </c>
-      <c r="AI5" s="7" t="s">
+      <c r="AI5" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AJ5" t="s">
@@ -2796,7 +2793,7 @@
       <c r="BF5" t="s">
         <v>76</v>
       </c>
-      <c r="BG5" s="7" t="s">
+      <c r="BG5" s="8" t="s">
         <v>98</v>
       </c>
       <c r="BH5" t="s">
@@ -2813,7 +2810,7 @@
       <c r="BM5" t="s">
         <v>89</v>
       </c>
-      <c r="BN5" s="7" t="s">
+      <c r="BN5" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BO5" t="s">
@@ -2823,7 +2820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -2890,6 +2887,7 @@
       <c r="W6" t="s">
         <v>85</v>
       </c>
+      <c r="X6" s="7"/>
       <c r="Y6" t="s">
         <v>85</v>
       </c>
@@ -2924,7 +2922,7 @@
         <v>102</v>
       </c>
       <c r="AJ6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s">
         <v>78</v>
@@ -2936,7 +2934,7 @@
         <v>73</v>
       </c>
       <c r="AN6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO6" t="s">
         <v>78</v>
@@ -2948,7 +2946,7 @@
         <v>73</v>
       </c>
       <c r="AR6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AS6" t="s">
         <v>75</v>
@@ -2986,38 +2984,38 @@
       <c r="BD6" t="s">
         <v>96</v>
       </c>
-      <c r="BE6" s="7" t="s">
+      <c r="BE6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="BF6" s="7" t="s">
+      <c r="BF6" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BG6" t="s">
         <v>90</v>
       </c>
       <c r="BH6" t="s">
-        <v>104</v>
-      </c>
-      <c r="BJ6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="BJ6" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BK6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="BM6" s="7" t="s">
+      <c r="BM6" s="8" t="s">
         <v>100</v>
       </c>
       <c r="BN6" t="s">
         <v>92</v>
       </c>
-      <c r="BO6" s="7" t="s">
+      <c r="BO6" s="8" t="s">
         <v>100</v>
       </c>
       <c r="BP6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -3093,7 +3091,7 @@
       <c r="AA7" t="s">
         <v>101</v>
       </c>
-      <c r="AB7" s="7" t="s">
+      <c r="AB7" s="8" t="s">
         <v>100</v>
       </c>
       <c r="AC7" t="s">
@@ -3114,10 +3112,11 @@
       <c r="AH7" t="s">
         <v>90</v>
       </c>
+      <c r="AI7" s="7"/>
       <c r="AJ7" t="s">
         <v>102</v>
       </c>
-      <c r="AK7" s="7" t="s">
+      <c r="AK7" s="8" t="s">
         <v>106</v>
       </c>
       <c r="AL7" t="s">
@@ -3163,7 +3162,7 @@
         <v>78</v>
       </c>
       <c r="AZ7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA7" t="s">
         <v>97</v>
@@ -3186,7 +3185,7 @@
       <c r="BG7" t="s">
         <v>92</v>
       </c>
-      <c r="BH7" s="7" t="s">
+      <c r="BH7" s="8" t="s">
         <v>107</v>
       </c>
       <c r="BJ7" t="s">
@@ -3199,13 +3198,14 @@
         <v>107</v>
       </c>
       <c r="BN7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BO7" t="s">
         <v>92</v>
       </c>
+      <c r="BP7" s="7"/>
     </row>
-    <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -3224,6 +3224,7 @@
       <c r="F8" t="s">
         <v>87</v>
       </c>
+      <c r="G8" s="7"/>
       <c r="H8" t="s">
         <v>91</v>
       </c>
@@ -3236,7 +3237,7 @@
       <c r="K8" t="s">
         <v>76</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="8" t="s">
         <v>106</v>
       </c>
       <c r="N8" t="s">
@@ -3267,7 +3268,7 @@
         <v>88</v>
       </c>
       <c r="W8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Y8" t="s">
         <v>78</v>
@@ -3339,7 +3340,7 @@
         <v>89</v>
       </c>
       <c r="AW8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AX8" t="s">
         <v>78</v>
@@ -3357,7 +3358,7 @@
         <v>89</v>
       </c>
       <c r="BC8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BD8" t="s">
         <v>87</v>
@@ -3368,6 +3369,8 @@
       <c r="BF8" t="s">
         <v>93</v>
       </c>
+      <c r="BG8" s="7"/>
+      <c r="BH8" s="7"/>
       <c r="BJ8" t="s">
         <v>92</v>
       </c>
@@ -3380,8 +3383,9 @@
       <c r="BN8" t="s">
         <v>107</v>
       </c>
+      <c r="BO8" s="7"/>
     </row>
-    <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>91</v>
       </c>
@@ -3397,16 +3401,17 @@
       <c r="E9" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="J9" s="7"/>
+      <c r="K9" s="8" t="s">
         <v>106</v>
       </c>
       <c r="L9" t="s">
@@ -3436,7 +3441,7 @@
       <c r="U9" t="s">
         <v>89</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="V9" s="8" t="s">
         <v>90</v>
       </c>
       <c r="W9" t="s">
@@ -3460,7 +3465,7 @@
       <c r="AD9" t="s">
         <v>107</v>
       </c>
-      <c r="AE9" s="7" t="s">
+      <c r="AE9" s="8" t="s">
         <v>90</v>
       </c>
       <c r="AF9" t="s">
@@ -3478,7 +3483,7 @@
       <c r="AK9" t="s">
         <v>102</v>
       </c>
-      <c r="AL9" s="7" t="s">
+      <c r="AL9" s="8" t="s">
         <v>100</v>
       </c>
       <c r="AM9" t="s">
@@ -3490,7 +3495,7 @@
       <c r="AO9" t="s">
         <v>86</v>
       </c>
-      <c r="AP9" s="7" t="s">
+      <c r="AP9" s="8" t="s">
         <v>98</v>
       </c>
       <c r="AQ9" t="s">
@@ -3505,11 +3510,11 @@
       <c r="AT9" t="s">
         <v>78</v>
       </c>
-      <c r="AU9" s="7" t="s">
+      <c r="AU9" s="8" t="s">
         <v>98</v>
       </c>
       <c r="AV9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AW9" t="s">
         <v>88</v>
@@ -3529,30 +3534,34 @@
       <c r="BB9" t="s">
         <v>87</v>
       </c>
-      <c r="BC9" s="7" t="s">
+      <c r="BC9" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="BD9" s="7" t="s">
+      <c r="BD9" s="8" t="s">
         <v>100</v>
       </c>
+      <c r="BE9" s="7"/>
       <c r="BF9" t="s">
         <v>92</v>
       </c>
+      <c r="BJ9" s="7"/>
       <c r="BK9" t="s">
         <v>107</v>
       </c>
+      <c r="BM9" s="7"/>
+      <c r="BN9" s="7"/>
     </row>
-    <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>98</v>
       </c>
       <c r="B10" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>90</v>
       </c>
       <c r="E10" t="s">
@@ -3576,10 +3585,10 @@
       <c r="N10" t="s">
         <v>111</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="8" t="s">
         <v>93</v>
       </c>
       <c r="Q10" t="s">
@@ -3594,7 +3603,7 @@
       <c r="T10" t="s">
         <v>80</v>
       </c>
-      <c r="U10" s="7" t="s">
+      <c r="U10" s="8" t="s">
         <v>100</v>
       </c>
       <c r="V10" t="s">
@@ -3603,10 +3612,10 @@
       <c r="W10" t="s">
         <v>87</v>
       </c>
-      <c r="Y10" s="7" t="s">
+      <c r="Y10" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="Z10" s="7" t="s">
+      <c r="Z10" s="8" t="s">
         <v>106</v>
       </c>
       <c r="AA10" t="s">
@@ -3615,7 +3624,7 @@
       <c r="AB10" t="s">
         <v>92</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AC10" s="6" t="s">
         <v>87</v>
       </c>
       <c r="AD10" t="s">
@@ -3633,16 +3642,17 @@
       <c r="AH10" t="s">
         <v>107</v>
       </c>
+      <c r="AJ10" s="7"/>
       <c r="AK10" t="s">
         <v>113</v>
       </c>
       <c r="AL10" t="s">
         <v>93</v>
       </c>
-      <c r="AM10" s="7" t="s">
+      <c r="AM10" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AN10" s="7" t="s">
+      <c r="AN10" s="8" t="s">
         <v>98</v>
       </c>
       <c r="AO10" t="s">
@@ -3651,13 +3661,13 @@
       <c r="AP10" t="s">
         <v>90</v>
       </c>
-      <c r="AQ10" s="7" t="s">
+      <c r="AQ10" s="8" t="s">
         <v>93</v>
       </c>
       <c r="AR10" t="s">
         <v>76</v>
       </c>
-      <c r="AS10" s="7" t="s">
+      <c r="AS10" s="8" t="s">
         <v>98</v>
       </c>
       <c r="AT10" t="s">
@@ -3666,16 +3676,16 @@
       <c r="AU10" t="s">
         <v>90</v>
       </c>
-      <c r="AV10" t="s">
+      <c r="AV10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AW10" s="7" t="s">
+      <c r="AW10" s="8" t="s">
         <v>100</v>
       </c>
       <c r="AX10" t="s">
         <v>87</v>
       </c>
-      <c r="AY10" s="7" t="s">
+      <c r="AY10" s="8" t="s">
         <v>98</v>
       </c>
       <c r="AZ10" t="s">
@@ -3693,11 +3703,12 @@
       <c r="BD10" t="s">
         <v>108</v>
       </c>
+      <c r="BF10" s="7"/>
       <c r="BK10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -3710,7 +3721,7 @@
       <c r="D11" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>100</v>
       </c>
       <c r="F11" t="s">
@@ -3719,6 +3730,7 @@
       <c r="H11" t="s">
         <v>114</v>
       </c>
+      <c r="I11" s="7"/>
       <c r="K11" t="s">
         <v>110</v>
       </c>
@@ -3743,7 +3755,7 @@
       <c r="S11" t="s">
         <v>91</v>
       </c>
-      <c r="T11" s="7" t="s">
+      <c r="T11" s="8" t="s">
         <v>93</v>
       </c>
       <c r="U11" t="s">
@@ -3759,13 +3771,14 @@
         <v>98</v>
       </c>
       <c r="Z11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AA11" t="s">
         <v>110</v>
       </c>
-      <c r="AC11" s="7" t="s">
-        <v>98</v>
+      <c r="AB11" s="7"/>
+      <c r="AC11" t="s">
+        <v>100</v>
       </c>
       <c r="AD11" t="s">
         <v>92</v>
@@ -3779,6 +3792,9 @@
       <c r="AG11" t="s">
         <v>100</v>
       </c>
+      <c r="AH11" t="s">
+        <v>98</v>
+      </c>
       <c r="AK11" t="s">
         <v>87</v>
       </c>
@@ -3800,7 +3816,7 @@
       <c r="AQ11" t="s">
         <v>102</v>
       </c>
-      <c r="AR11" s="7" t="s">
+      <c r="AR11" s="8" t="s">
         <v>98</v>
       </c>
       <c r="AS11" t="s">
@@ -3812,8 +3828,8 @@
       <c r="AU11" t="s">
         <v>92</v>
       </c>
-      <c r="AV11" s="7" t="s">
-        <v>98</v>
+      <c r="AV11" t="s">
+        <v>100</v>
       </c>
       <c r="AW11" t="s">
         <v>110</v>
@@ -3824,10 +3840,10 @@
       <c r="AY11" t="s">
         <v>90</v>
       </c>
-      <c r="AZ11" s="7" t="s">
+      <c r="AZ11" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="BA11" s="7" t="s">
+      <c r="BA11" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BB11" t="s">
@@ -3839,11 +3855,13 @@
       <c r="BD11" t="s">
         <v>109</v>
       </c>
+      <c r="BK11" s="7"/>
     </row>
-    <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>93</v>
       </c>
+      <c r="B12" s="7"/>
       <c r="C12" t="s">
         <v>92</v>
       </c>
@@ -3853,9 +3871,12 @@
       <c r="E12" t="s">
         <v>93</v>
       </c>
+      <c r="F12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="K12" t="s">
         <v>113</v>
       </c>
+      <c r="L12" s="7"/>
       <c r="N12" t="s">
         <v>110</v>
       </c>
@@ -3865,14 +3886,14 @@
       <c r="P12" t="s">
         <v>102</v>
       </c>
-      <c r="Q12" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="R12" s="7" t="s">
+      <c r="Q12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>105</v>
+      <c r="S12" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="T12" t="s">
         <v>107</v>
@@ -3880,38 +3901,46 @@
       <c r="U12" t="s">
         <v>107</v>
       </c>
-      <c r="W12" s="7" t="s">
+      <c r="V12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="W12" s="8" t="s">
         <v>98</v>
       </c>
       <c r="Y12" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="Z12" t="s">
         <v>107</v>
       </c>
-      <c r="AC12" t="s">
-        <v>100</v>
-      </c>
+      <c r="AA12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC12" s="7"/>
       <c r="AD12" t="s">
         <v>87</v>
       </c>
       <c r="AE12" t="s">
         <v>114</v>
       </c>
+      <c r="AF12" s="7"/>
       <c r="AG12" t="s">
         <v>109</v>
       </c>
+      <c r="AH12" s="7"/>
       <c r="AK12" t="s">
         <v>93</v>
       </c>
+      <c r="AL12" s="7"/>
       <c r="AM12" t="s">
         <v>100</v>
       </c>
       <c r="AN12" t="s">
         <v>100</v>
       </c>
+      <c r="AO12" s="7"/>
       <c r="AP12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AQ12" t="s">
         <v>110</v>
@@ -3919,14 +3948,16 @@
       <c r="AR12" t="s">
         <v>100</v>
       </c>
-      <c r="AT12" s="7" t="s">
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="8" t="s">
         <v>98</v>
       </c>
+      <c r="AU12" s="7"/>
       <c r="AV12" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AW12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AX12" t="s">
         <v>112</v>
@@ -3940,17 +3971,23 @@
       <c r="BA12" t="s">
         <v>100</v>
       </c>
-      <c r="BB12" s="7" t="s">
+      <c r="BB12" s="8" t="s">
         <v>98</v>
       </c>
+      <c r="BC12" s="7"/>
+      <c r="BD12" s="7"/>
     </row>
-    <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="C13" s="7"/>
       <c r="D13" t="s">
         <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>102</v>
       </c>
+      <c r="K13" s="7"/>
+      <c r="N13" s="7"/>
       <c r="O13" t="s">
         <v>92</v>
       </c>
@@ -3981,12 +4018,18 @@
       <c r="Z13" t="s">
         <v>102</v>
       </c>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AK13" s="7"/>
       <c r="AM13" t="s">
         <v>102</v>
       </c>
       <c r="AN13" t="s">
         <v>92</v>
       </c>
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
       <c r="AR13" t="s">
         <v>102</v>
       </c>
@@ -3994,8 +4037,9 @@
         <v>108</v>
       </c>
       <c r="AV13" t="s">
-        <v>92</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="AW13" s="7"/>
       <c r="AX13" t="s">
         <v>109</v>
       </c>
@@ -4012,13 +4056,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+      <c r="D14" s="7"/>
       <c r="E14" t="s">
         <v>110</v>
       </c>
       <c r="O14" t="s">
         <v>89</v>
       </c>
+      <c r="P14" s="7"/>
       <c r="Q14" t="s">
         <v>92</v>
       </c>
@@ -4028,6 +4074,7 @@
       <c r="S14" t="s">
         <v>107</v>
       </c>
+      <c r="T14" s="7"/>
       <c r="U14" t="s">
         <v>91</v>
       </c>
@@ -4035,11 +4082,12 @@
         <v>102</v>
       </c>
       <c r="Y14" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="Z14" t="s">
         <v>113</v>
       </c>
+      <c r="AM14" s="7"/>
       <c r="AN14" t="s">
         <v>107</v>
       </c>
@@ -4049,14 +4097,20 @@
       <c r="AT14" t="s">
         <v>107</v>
       </c>
+      <c r="AV14" s="7"/>
+      <c r="AX14" s="7"/>
+      <c r="AY14" s="7"/>
       <c r="AZ14" t="s">
         <v>112</v>
       </c>
+      <c r="BA14" s="7"/>
       <c r="BB14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+      <c r="E15" s="7"/>
+      <c r="O15" s="7"/>
       <c r="Q15" t="s">
         <v>110</v>
       </c>
@@ -4072,11 +4126,24 @@
       <c r="W15" t="s">
         <v>110</v>
       </c>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AR15" s="7"/>
       <c r="AT15" t="s">
-        <v>105</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="AZ15" s="7"/>
+      <c r="BB15" s="7"/>
     </row>
-    <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25">
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="AT16" s="7"/>
+    </row>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4136,14 +4203,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:AQ42"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -4188,7 +4255,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -4232,7 +4299,7 @@
         <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P3" t="s">
         <v>78</v>
@@ -4259,7 +4326,7 @@
         <v>76</v>
       </c>
       <c r="X3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y3" t="s">
         <v>87</v>
@@ -4283,7 +4350,7 @@
         <v>100</v>
       </c>
       <c r="AF3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AG3" t="s">
         <v>112</v>
@@ -4319,7 +4386,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4402,7 +4469,7 @@
         <v>31</v>
       </c>
       <c r="AB4" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="AC4" t="s">
         <v>14</v>
@@ -4450,7 +4517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4533,7 +4600,7 @@
         <v>33</v>
       </c>
       <c r="AB5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AC5" t="s">
         <v>29</v>
@@ -4581,7 +4648,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4664,7 +4731,7 @@
         <v>37</v>
       </c>
       <c r="AB6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AC6" t="s">
         <v>40</v>
@@ -4697,7 +4764,7 @@
         <v>53</v>
       </c>
       <c r="AM6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AN6" t="s">
         <v>52</v>
@@ -4712,7 +4779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4795,7 +4862,7 @@
         <v>30</v>
       </c>
       <c r="AB7" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="AC7" t="s">
         <v>15</v>
@@ -4843,12 +4910,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -4872,7 +4939,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -4893,7 +4960,7 @@
         <v>18</v>
       </c>
       <c r="AB8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="AD8" t="s">
         <v>39</v>
@@ -4923,7 +4990,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -4937,7 +5004,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -4973,7 +5040,7 @@
         <v>26</v>
       </c>
       <c r="AB9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AD9" t="s">
         <v>36</v>
@@ -5003,7 +5070,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -5053,10 +5120,10 @@
         <v>35</v>
       </c>
       <c r="AB10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AD10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AE10" t="s">
         <v>32</v>
@@ -5083,7 +5150,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -5133,10 +5200,10 @@
         <v>37</v>
       </c>
       <c r="AB11" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="AD11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="s">
         <v>35</v>
@@ -5163,7 +5230,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -5189,7 +5256,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -5207,7 +5274,7 @@
         <v>70</v>
       </c>
       <c r="AB12" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="AD12" t="s">
         <v>50</v>
@@ -5231,7 +5298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -5275,7 +5342,7 @@
         <v>45</v>
       </c>
       <c r="AB13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AD13" t="s">
         <v>54</v>
@@ -5299,7 +5366,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -5343,7 +5410,7 @@
         <v>57</v>
       </c>
       <c r="AB14" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AD14" t="s">
         <v>62</v>
@@ -5367,7 +5434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -5411,7 +5478,7 @@
         <v>53</v>
       </c>
       <c r="AB15" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="AD15" t="s">
         <v>43</v>
@@ -5435,7 +5502,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -5479,7 +5546,7 @@
         <v>24</v>
       </c>
       <c r="AB16" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="s">
         <v>5</v>
@@ -5503,7 +5570,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -5547,7 +5614,7 @@
         <v>29</v>
       </c>
       <c r="AB17" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="s">
         <v>34</v>
@@ -5571,7 +5638,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -5615,7 +5682,7 @@
         <v>22</v>
       </c>
       <c r="AB18" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="AD18" t="s">
         <v>13</v>
@@ -5639,7 +5706,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5683,7 +5750,7 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AD19" t="s">
         <v>25</v>
@@ -5707,7 +5774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -5739,7 +5806,7 @@
         <v>9</v>
       </c>
       <c r="AB20" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AD20" t="s">
         <v>44</v>
@@ -5760,7 +5827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -5792,7 +5859,7 @@
         <v>33</v>
       </c>
       <c r="AB21" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="AD21" t="s">
         <v>71</v>
@@ -5813,7 +5880,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -5845,7 +5912,7 @@
         <v>32</v>
       </c>
       <c r="AB22" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="AD22" t="s">
         <v>69</v>
@@ -5866,7 +5933,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -5898,7 +5965,7 @@
         <v>40</v>
       </c>
       <c r="AB23" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AD23" t="s">
         <v>55</v>
@@ -5913,13 +5980,13 @@
         <v>37</v>
       </c>
       <c r="AM23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -5939,7 +6006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -5959,7 +6026,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -5979,7 +6046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -5999,11 +6066,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6019,10 +6086,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:AQ14"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -6104,7 +6171,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -6148,7 +6215,7 @@
         <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P3" t="s">
         <v>78</v>
@@ -6175,7 +6242,7 @@
         <v>76</v>
       </c>
       <c r="X3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y3" t="s">
         <v>87</v>
@@ -6199,7 +6266,7 @@
         <v>100</v>
       </c>
       <c r="AF3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AG3" t="s">
         <v>112</v>
@@ -6235,441 +6302,441 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="V4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="X4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Y4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Z4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AC4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AP4" t="s">
         <v>145</v>
       </c>
-      <c r="AE4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>144</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="R5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AE5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AI5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AK5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AM5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="W6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AB6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AD6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AE6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AI6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AK6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="W7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Y7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AB7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AE7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AI7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="V8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="W8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Y8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AB8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AD8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AE8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AI8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AK8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AO8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AD9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AK9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.140625" customWidth="1"/>
@@ -6686,175 +6753,175 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
-        <v>251</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="8">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="11">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="9">
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="14">
         <f>C1*4</f>
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="11">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="16">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>544</v>
       </c>
-      <c r="E3" s="70" t="s">
-        <v>253</v>
-      </c>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
+      <c r="E3" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="13">
+    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="19">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="19">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>18</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="F5" s="15">
+      <c r="E5" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="F5" s="21">
         <v>2</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="22">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="23">
         <f>B4/B3</f>
         <v>0.14522058823529413</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="24">
         <f>C2*G5</f>
-        <v>83.692307692307693</v>
+        <v>83.6923076923077</v>
       </c>
       <c r="J5">
         <f>B4</f>
         <v>79</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="25">
         <f>J5-I5</f>
-        <v>-4.6923076923076934</v>
-      </c>
-      <c r="L5" s="20">
+        <v>-4.692307692307693</v>
+      </c>
+      <c r="L5" s="26">
         <f>K5/4</f>
         <v>-1.1730769230769234</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="19">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
         <v>216</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="21">
         <v>1</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="22">
         <f>F6/13</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="H6" s="17">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H6" s="23">
         <f>B5/B3</f>
-        <v>3.3088235294117647E-2</v>
-      </c>
-      <c r="I6" s="18">
+        <v>0.03308823529411765</v>
+      </c>
+      <c r="I6" s="24">
         <f>C2*G6</f>
-        <v>41.846153846153847</v>
+        <v>41.84615384615385</v>
       </c>
       <c r="J6">
         <f>B5</f>
         <v>18</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="25">
         <f>J6-I6</f>
         <v>-23.846153846153847</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="26">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-5.9615384615384617</v>
+        <v>-5.961538461538462</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="28">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>231</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="24">
+      <c r="E7" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="F7" s="30">
         <v>3</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="31">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="32">
         <f>(B5+B4)/B3</f>
         <v>0.17830882352941177</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="24">
         <f>C2*G7</f>
         <v>125.53846153846155</v>
       </c>
@@ -6862,293 +6929,293 @@
         <f>B4+B5</f>
         <v>97</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="25">
         <f>J7-I7</f>
         <v>-28.538461538461547</v>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="26">
         <f>K7/4</f>
-        <v>-7.1346153846153868</v>
+        <v>-7.134615384615387</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="F8" s="28">
+    <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E8" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="34">
         <v>6</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="35">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="36">
         <f>B6/B3</f>
         <v>0.39705882352941174</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="24">
         <f>C2*G8</f>
-        <v>251.07692307692309</v>
+        <v>251.0769230769231</v>
       </c>
       <c r="J8">
         <f>B6</f>
         <v>216</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="25">
         <f>J8-I8</f>
         <v>-35.076923076923094</v>
       </c>
-      <c r="L8" s="20">
+      <c r="L8" s="26">
         <f>K8/4</f>
-        <v>-8.7692307692307736</v>
+        <v>-8.769230769230774</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>544</v>
       </c>
-      <c r="E9" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="28">
+      <c r="E9" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="F9" s="34">
         <v>4</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="35">
         <f t="shared" si="1"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H9" s="30">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H9" s="36">
         <f>B7/B3</f>
         <v>0.42463235294117646</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="24">
         <f>C2*G9</f>
-        <v>167.38461538461539</v>
+        <v>167.3846153846154</v>
       </c>
       <c r="J9">
         <f>B7</f>
         <v>231</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="37">
         <f>J9-I9</f>
-        <v>63.615384615384613</v>
-      </c>
-      <c r="L9" s="20">
+        <v>63.61538461538461</v>
+      </c>
+      <c r="L9" s="26">
         <f>K9/4</f>
         <v>15.903846153846153</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="I11" s="33">
+    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="I11" s="39">
         <f>SUM(I7:I9)</f>
         <v>544</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="33">
         <f>SUM(J7:J9)</f>
         <v>544</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="40">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="41">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H16" t="s">
-        <v>258</v>
-      </c>
-      <c r="I16" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="J16" s="36" t="s">
+      <c r="I16" s="42" t="s">
         <v>260</v>
       </c>
+      <c r="J16" s="42" t="s">
+        <v>261</v>
+      </c>
       <c r="K16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E17" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="F17" s="38">
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="F17" s="44">
         <v>3</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="45">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="46">
         <f>(B5+B4)/B3</f>
         <v>0.17830882352941177</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="47">
         <f>B3*G17</f>
         <v>125.53846153846155</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="48">
         <f>B5+B4</f>
         <v>97</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="49">
         <f>J17-I17</f>
         <v>-28.538461538461547</v>
       </c>
-      <c r="L17" s="20">
+      <c r="L17" s="26">
         <f>K17/4</f>
-        <v>-7.1346153846153868</v>
+        <v>-7.134615384615387</v>
       </c>
     </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E18" s="44" t="s">
-        <v>264</v>
-      </c>
-      <c r="F18" s="45">
+    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E18" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" s="51">
         <v>6</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="52">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="47">
+      <c r="H18" s="53">
         <f>B6/B3</f>
         <v>0.39705882352941174</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="54">
         <f>B3*G18</f>
-        <v>251.07692307692309</v>
-      </c>
-      <c r="J18" s="49">
+        <v>251.0769230769231</v>
+      </c>
+      <c r="J18" s="55">
         <f>B6</f>
         <v>216</v>
       </c>
-      <c r="K18" s="50">
+      <c r="K18" s="56">
         <f>J18-I18</f>
         <v>-35.076923076923094</v>
       </c>
-      <c r="L18" s="20">
+      <c r="L18" s="26">
         <f>K18/4</f>
-        <v>-8.7692307692307736</v>
-      </c>
-      <c r="Q18" s="51"/>
+        <v>-8.769230769230774</v>
+      </c>
+      <c r="Q18" s="57"/>
     </row>
-    <row r="19" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" s="53">
+    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="F19" s="59">
         <v>4</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="60">
         <f t="shared" si="2"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H19" s="55">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H19" s="61">
         <f>B7/B3</f>
         <v>0.42463235294117646</v>
       </c>
-      <c r="I19" s="56">
+      <c r="I19" s="62">
         <f>B3*G19</f>
-        <v>167.38461538461539</v>
-      </c>
-      <c r="J19" s="57">
+        <v>167.3846153846154</v>
+      </c>
+      <c r="J19" s="63">
         <f>B7</f>
         <v>231</v>
       </c>
-      <c r="K19" s="58">
+      <c r="K19" s="64">
         <f>J19-I19</f>
-        <v>63.615384615384613</v>
-      </c>
-      <c r="L19" s="20">
+        <v>63.61538461538461</v>
+      </c>
+      <c r="L19" s="26">
         <f>K19/4</f>
         <v>15.903846153846153</v>
       </c>
     </row>
-    <row r="24" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="69"/>
-      <c r="F24" s="69"/>
-      <c r="P24" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
+    <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="P24" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
     </row>
-    <row r="25" spans="5:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P25" s="59"/>
-      <c r="Q25" s="60" t="s">
-        <v>271</v>
-      </c>
-      <c r="R25" s="61" t="s">
+    <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P25" s="66"/>
+      <c r="Q25" s="67" t="s">
         <v>272</v>
       </c>
-      <c r="S25" s="62" t="s">
-        <v>261</v>
+      <c r="R25" s="68" t="s">
+        <v>273</v>
+      </c>
+      <c r="S25" s="69" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="P26" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q26" s="27">
+    <row r="26" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P26" s="70" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q26" s="33">
         <v>247</v>
       </c>
-      <c r="R26" s="27">
+      <c r="R26" s="33">
         <v>212</v>
       </c>
-      <c r="S26" s="13">
+      <c r="S26" s="19">
         <f>R26-Q26</f>
         <v>-35</v>
       </c>
     </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="P27" s="63" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q27" s="27">
+    <row r="27" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P27" s="70" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q27" s="33">
         <v>124</v>
       </c>
-      <c r="R27" s="27">
+      <c r="R27" s="33">
         <v>92</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="19">
         <f t="shared" ref="S27:S28" si="3">R27-Q27</f>
         <v>-32</v>
       </c>
     </row>
-    <row r="28" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P28" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q28" s="65">
+    <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P28" s="71" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q28" s="72">
         <v>165</v>
       </c>
-      <c r="R28" s="65">
+      <c r="R28" s="72">
         <v>232</v>
       </c>
-      <c r="S28" s="22">
+      <c r="S28" s="28">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3DCC08-2B22-4850-ABF0-3EA12A67EB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
+    <sheet name="AHL" sheetId="1" r:id="rId1"/>
+    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
+    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="335">
   <si>
     <t>sl</t>
   </si>
@@ -235,6 +249,9 @@
     <t>LehnerMo</t>
   </si>
   <si>
+    <t>UnterwegerDo</t>
+  </si>
+  <si>
     <t>2024-09-21</t>
   </si>
   <si>
@@ -292,6 +309,9 @@
     <t>2024-11-23</t>
   </si>
   <si>
+    <t>2024-12-26</t>
+  </si>
+  <si>
     <t>2024-10-24</t>
   </si>
   <si>
@@ -322,6 +342,12 @@
     <t>2024-11-30</t>
   </si>
   <si>
+    <t>2024-12-17</t>
+  </si>
+  <si>
+    <t>2024-12-28</t>
+  </si>
+  <si>
     <t>2024-10-31</t>
   </si>
   <si>
@@ -337,6 +363,12 @@
     <t>2024-11-02</t>
   </si>
   <si>
+    <t>2024-12-19</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
     <t>2024-11-17</t>
   </si>
   <si>
@@ -346,15 +378,30 @@
     <t>2024-11-12</t>
   </si>
   <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
     <t>2024-11-26</t>
   </si>
   <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
     <t>2024-12-05</t>
   </si>
   <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
     <t>2024-11-19</t>
   </si>
   <si>
+    <t>2025-01-06</t>
+  </si>
+  <si>
+    <t>2025-01-02</t>
+  </si>
+  <si>
     <t>2024-12-04</t>
   </si>
   <si>
@@ -367,6 +414,12 @@
     <t>zbrisano</t>
   </si>
   <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
+    <t>2024-12-27</t>
+  </si>
+  <si>
     <t>HuberRe</t>
   </si>
   <si>
@@ -496,6 +549,42 @@
     <t>Eishalle Celje;LesniakBo;RivisFe;ArlicMa;RivisAn</t>
   </si>
   <si>
+    <t>Eishalle Celje;LehnerMo;MeixnerSe;MattheyPh;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;KainbergerJu;LehnerMo;MarkizetiGr;MattheyPh</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;BrockAd;MoidlDa;FecchioFe;MattheyPh</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;BenvegnuAn;SoraperraSi;BrondiPa;WeissAl</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;LazzeriAl;PinieOm;AbeltinoSi;BrondiPa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LesniakBo;UnterwegerDo;ArlicMa;JavornikBl</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;OrelSt;WidmannFl;EislCh;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;OrelSt;WidmannFl;StrimitzerDa;WuchererGe</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;HlavatyAl;WenuschHe;EislCh;RinkerDa</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;HolzerTo;KainbergerJu;TelesklavFa;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;OrelSt;SnojTa;FleischmannLu;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;ArlicMa;TelesklavFa</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -574,6 +663,39 @@
     <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;WeissAl</t>
   </si>
   <si>
+    <t>Eishalle Gröden;BulovecMi;LazzeriAl;AbeltinoSi;ArlicMa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;LesniakBo;UnterwegerDo;JeramFi;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;OrelSt;WidmannFl;EislCh;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BulovecMi;HlavatyAl;LegatKo;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Zell am See;HlavatyAl;UnterwegerDo;PreiserJu;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;EggerTh;StefenelliFe;FecchioFe;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;MoschenAn;SnojTa;BrondiPa;JeramFi</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;LehnerMo;MoidlDa;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;BulovecMi;LazzeriAl;MarkizetiGr;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BajtMi;BenvegnuAn;CristeliMa;JavornikBl</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
+  </si>
+  <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
   </si>
   <si>
@@ -640,6 +762,36 @@
     <t>Eishalle Sissek Zibel;BulovecMi;WidmannFl;ArlicMa;WuchererGe</t>
   </si>
   <si>
+    <t>KELIT Arena Zell am See;SnojTa;WenuschHe;PreiserJu;RinkerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;GiacomozziFe;LegaSi;PaceJa;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;LazzeriAl;StefenelliFe;AbeltinoSi;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;HolzerTo;LegaSi;CusinFe;DivisDo</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;Huber rRe;VirtaTu;FormaioniTh;RinkerDa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;MetzingerFi;VoicanCh;KnezRo;LegatKo</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;Huber rRe;RuetzMa;IlmerNo;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;EggerTh;MoschenAn;AbeltinoSi;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;MeixnerSe;MetzingerFi;KnezRo;LegatKo</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;SoraperraSi;StefenelliFe;FecchioFe;GrisentiLu</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -706,6 +858,30 @@
     <t>Eishalle Meran;KainbergerJu;LehnerMo;EislCh;FleischmannLu</t>
   </si>
   <si>
+    <t>Eishalle Sterzing;Huber rRe;SpiegelSe;GrisentiLu;IlmerNo</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;EggerTh;RuetzMa;DivisDo;JägerRi</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;GiacomozziFe;PinieOm;CristeliMa;CusinFe</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;BajtMi;MoschenAn;CristeliMa;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;BenvegnuAn;RuetzMa;JägerRi;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;GiacomozziFe;PirasAn;CristeliMa;FleischmannLu</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BrockAd;LebenJa;JeramFi;KnezRo</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;RuetzMa;SpiegelSe;JägerRi;StrimitzerDa</t>
+  </si>
+  <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
   </si>
   <si>
@@ -757,6 +933,21 @@
     <t>Eishalle Gröden;GiacomozziFe;MoidlDa;MattheyPh;MoidlMa</t>
   </si>
   <si>
+    <t>KELIT Arena Zell am See;BajtMi;HolzerTo;JavornikBl;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;PirasAn;VirtaTu;FecchioFe;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;RivisFe;SoraperraSi;GrisentiLu;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;RivisFe;SpiegelSe;BrondiPa;DivisDo</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;HlavatyAl;PirasAn;PreiserJu;ScalzeriAl</t>
+  </si>
+  <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
   </si>
   <si>
@@ -775,6 +966,12 @@
     <t>Eishalle Cortina;LebenJa;PirasAn;GrisentiLu;JavornikBl</t>
   </si>
   <si>
+    <t>Eishalle Gröden;MoschenAn;VirtaTu;FleischmannLu;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;LebenJa;PinieOm;IlmerNo;JeramFi</t>
+  </si>
+  <si>
     <t>vse delegirane tekme</t>
   </si>
   <si>
@@ -826,9 +1023,6 @@
     <t>kontrola</t>
   </si>
   <si>
-    <t>till 7.12.2024</t>
-  </si>
-  <si>
     <t>% games per team</t>
   </si>
   <si>
@@ -839,50 +1033,53 @@
   </si>
   <si>
     <t>Actual assigned games per country</t>
+  </si>
+  <si>
+    <t>till 6.1.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF9C0006"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF006100"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -894,25 +1091,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,7 +1121,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -941,7 +1138,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -952,7 +1149,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -977,7 +1174,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thick"/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1247,25 +1446,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1359,9 +1543,6 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1375,6 +1556,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1654,9 +1853,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BQ73"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -1728,30 +1927,30 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C1">
         <f t="shared" ref="C1:BF1" si="0">COUNTIF(C4:C70,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F69,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1">
         <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
@@ -1759,23 +1958,23 @@
       </c>
       <c r="H1">
         <f>COUNTIF(H4:H68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I69,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J68,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M1">
         <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
@@ -1783,179 +1982,179 @@
       </c>
       <c r="N1">
         <f>COUNTIF(N4:N69,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O1">
         <f>COUNTIF(O4:O68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q68,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R1">
         <f>COUNTIF(R4:R67,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W1">
         <f>COUNTIF(W4:W69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X1">
         <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y1">
         <f>COUNTIF(Y4:Y69,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA1">
         <f>COUNTIF(AA4:AA66,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB68,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD69,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF65,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG69,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI69,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ1">
         <f>COUNTIF(AJ4:AJ65,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AK1">
         <f>COUNTIF(AK4:AK66,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM67,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN66,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO69,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AP1">
         <f>COUNTIF(AP4:AP68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ1">
         <f>COUNTIF(AQ4:AQ68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR1">
         <f>COUNTIF(AR4:AR64,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS69,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT1">
         <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AU1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV67,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW1">
         <f>COUNTIF(AW4:AW67,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ66,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB69,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BE1">
         <f>COUNTIF(BE4:BE68,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF1">
         <f t="shared" si="0"/>
@@ -1963,11 +2162,11 @@
       </c>
       <c r="BG1">
         <f>COUNTIF(BG4:BG68,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BH1">
-        <f t="shared" ref="BH1:BP1" si="1">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
-        <v>4</v>
+        <f t="shared" ref="BH1:BQ1" si="1">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="BI1">
         <f t="shared" si="1"/>
@@ -1975,11 +2174,11 @@
       </c>
       <c r="BJ1">
         <f t="shared" ref="BJ1" si="2">COUNTIF(BJ4:BJ69,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK66,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BL1">
         <f t="shared" si="1"/>
@@ -1987,22 +2186,26 @@
       </c>
       <c r="BM1">
         <f t="shared" ref="BM1" si="3">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BO1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BP1">
         <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="BQ1">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="14.45" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2207,8 +2410,11 @@
       <c r="BP2" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="BQ2" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2413,1753 +2619,2274 @@
       <c r="BP3" s="6" t="s">
         <v>71</v>
       </c>
+      <c r="BQ3" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" t="s">
         <v>73</v>
       </c>
-      <c r="C4" t="s">
+      <c r="O4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" t="s">
+      <c r="P4" t="s">
         <v>73</v>
       </c>
-      <c r="E4" t="s">
+      <c r="Q4" t="s">
         <v>73</v>
       </c>
-      <c r="F4" t="s">
+      <c r="R4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S4" t="s">
+        <v>73</v>
+      </c>
+      <c r="T4" t="s">
+        <v>73</v>
+      </c>
+      <c r="U4" t="s">
+        <v>73</v>
+      </c>
+      <c r="V4" t="s">
+        <v>73</v>
+      </c>
+      <c r="W4" t="s">
+        <v>73</v>
+      </c>
+      <c r="X4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD4" t="s">
         <v>74</v>
       </c>
-      <c r="G4" t="s">
+      <c r="AE4" t="s">
         <v>74</v>
       </c>
-      <c r="H4" t="s">
+      <c r="AF4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY4" t="s">
         <v>75</v>
       </c>
-      <c r="I4" t="s">
+      <c r="AZ4" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>74</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>74</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>76</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>84</v>
+      </c>
+      <c r="BG4" t="s">
         <v>75</v>
       </c>
-      <c r="J4" t="s">
+      <c r="BH4" t="s">
+        <v>80</v>
+      </c>
+      <c r="BI4" t="s">
         <v>76</v>
       </c>
-      <c r="K4" t="s">
+      <c r="BJ4" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>89</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>89</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO4" t="s">
         <v>77</v>
       </c>
-      <c r="L4" t="s">
+      <c r="BP4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
         <v>75</v>
       </c>
-      <c r="M4" t="s">
-        <v>78</v>
-      </c>
-      <c r="N4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" t="s">
-        <v>72</v>
-      </c>
-      <c r="P4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S4" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" t="s">
-        <v>72</v>
-      </c>
-      <c r="U4" t="s">
-        <v>72</v>
-      </c>
-      <c r="V4" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" t="s">
-        <v>72</v>
-      </c>
-      <c r="X4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
         <v>73</v>
       </c>
-      <c r="AE4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AH4" t="s">
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" t="s">
         <v>76</v>
       </c>
-      <c r="AI4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="L5" t="s">
         <v>80</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>73</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>73</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>73</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>85</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>85</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>83</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>74</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>79</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>75</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>86</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>88</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>88</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>89</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>76</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="K5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" t="s">
-        <v>79</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" t="s">
         <v>74</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>75</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>75</v>
+      </c>
+      <c r="S5" t="s">
+        <v>74</v>
+      </c>
+      <c r="T5" t="s">
+        <v>74</v>
+      </c>
+      <c r="U5" t="s">
+        <v>75</v>
+      </c>
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s">
+        <v>76</v>
+      </c>
+      <c r="X5" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI5" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AN5" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" t="s">
-        <v>74</v>
-      </c>
-      <c r="R5" t="s">
-        <v>74</v>
-      </c>
-      <c r="S5" t="s">
-        <v>73</v>
-      </c>
-      <c r="T5" t="s">
-        <v>73</v>
-      </c>
-      <c r="U5" t="s">
-        <v>74</v>
-      </c>
-      <c r="V5" t="s">
-        <v>74</v>
-      </c>
-      <c r="W5" t="s">
+      <c r="AO5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS5" t="s">
         <v>75</v>
       </c>
-      <c r="X5" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA5" t="s">
+      <c r="AT5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU5" t="s">
         <v>85</v>
       </c>
-      <c r="AB5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC5" t="s">
+      <c r="AV5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>76</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>76</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>88</v>
+      </c>
+      <c r="BF5" t="s">
         <v>77</v>
       </c>
-      <c r="AD5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>85</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>96</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>97</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>87</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>76</v>
-      </c>
       <c r="BG5" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BH5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BI5" s="7"/>
       <c r="BJ5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BK5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BL5" s="7"/>
       <c r="BM5" t="s">
+        <v>90</v>
+      </c>
+      <c r="BN5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>93</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>102</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" t="s">
         <v>89</v>
       </c>
-      <c r="BN5" s="8" t="s">
+      <c r="N6" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>74</v>
+      </c>
+      <c r="R6" t="s">
+        <v>74</v>
+      </c>
+      <c r="S6" t="s">
+        <v>86</v>
+      </c>
+      <c r="T6" t="s">
+        <v>86</v>
+      </c>
+      <c r="U6" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" t="s">
+        <v>76</v>
+      </c>
+      <c r="W6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>86</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>86</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>80</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>98</v>
+      </c>
+      <c r="BE6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>109</v>
+      </c>
+      <c r="BJ6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BK6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="BM6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>94</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" t="s">
+        <v>84</v>
+      </c>
+      <c r="P7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7" t="s">
+        <v>84</v>
+      </c>
+      <c r="S7" t="s">
+        <v>84</v>
+      </c>
+      <c r="T7" t="s">
+        <v>84</v>
+      </c>
+      <c r="U7" t="s">
+        <v>80</v>
+      </c>
+      <c r="V7" t="s">
+        <v>80</v>
+      </c>
+      <c r="W7" t="s">
+        <v>84</v>
+      </c>
+      <c r="X7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI7" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK7" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AL7" t="s">
         <v>90</v>
       </c>
-      <c r="BO5" t="s">
-        <v>91</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>100</v>
+      <c r="AM7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>76</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>106</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>102</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>94</v>
+      </c>
+      <c r="BH7" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>102</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>114</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>113</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP7" s="7" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" t="s">
+    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" t="s">
         <v>76</v>
       </c>
-      <c r="H6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" t="s">
-        <v>96</v>
-      </c>
-      <c r="J6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K6" t="s">
-        <v>79</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="F8" t="s">
         <v>88</v>
-      </c>
-      <c r="N6" t="s">
-        <v>73</v>
-      </c>
-      <c r="O6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P6" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R6" t="s">
-        <v>73</v>
-      </c>
-      <c r="S6" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" t="s">
-        <v>85</v>
-      </c>
-      <c r="U6" t="s">
-        <v>75</v>
-      </c>
-      <c r="V6" t="s">
-        <v>75</v>
-      </c>
-      <c r="W6" t="s">
-        <v>85</v>
-      </c>
-      <c r="X6" s="7"/>
-      <c r="Y6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH6" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>103</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>97</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>104</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>95</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>96</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>85</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>85</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>74</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>96</v>
-      </c>
-      <c r="BE6" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="BF6" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>90</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>105</v>
-      </c>
-      <c r="BJ6" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="BK6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="BM6" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>92</v>
-      </c>
-      <c r="BO6" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7" t="s">
-        <v>92</v>
-      </c>
-      <c r="K7" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" t="s">
-        <v>79</v>
-      </c>
-      <c r="O7" t="s">
-        <v>83</v>
-      </c>
-      <c r="P7" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R7" t="s">
-        <v>83</v>
-      </c>
-      <c r="S7" t="s">
-        <v>83</v>
-      </c>
-      <c r="T7" t="s">
-        <v>83</v>
-      </c>
-      <c r="U7" t="s">
-        <v>79</v>
-      </c>
-      <c r="V7" t="s">
-        <v>79</v>
-      </c>
-      <c r="W7" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB7" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI7" s="7"/>
-      <c r="AJ7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK7" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>97</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>96</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>88</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>102</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>100</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH7" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>100</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>107</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>103</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>92</v>
-      </c>
-      <c r="BP7" s="7"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" t="s">
-        <v>87</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="N8" t="s">
+        <v>82</v>
+      </c>
+      <c r="O8" t="s">
+        <v>98</v>
+      </c>
+      <c r="P8" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>80</v>
+      </c>
+      <c r="R8" t="s">
+        <v>79</v>
+      </c>
+      <c r="S8" t="s">
+        <v>80</v>
+      </c>
+      <c r="T8" t="s">
+        <v>98</v>
+      </c>
+      <c r="U8" t="s">
+        <v>79</v>
+      </c>
+      <c r="V8" t="s">
+        <v>89</v>
+      </c>
+      <c r="W8" t="s">
+        <v>108</v>
+      </c>
+      <c r="X8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>98</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>90</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>109</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>95</v>
+      </c>
+      <c r="BG8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BH8" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>94</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>120</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>118</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO8" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
         <v>91</v>
       </c>
-      <c r="I8" t="s">
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L9" t="s">
+        <v>106</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="O9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P9" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>98</v>
+      </c>
+      <c r="R9" t="s">
+        <v>81</v>
+      </c>
+      <c r="S9" t="s">
+        <v>101</v>
+      </c>
+      <c r="T9" t="s">
+        <v>77</v>
+      </c>
+      <c r="U9" t="s">
+        <v>90</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="W9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE9" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO9" t="s">
         <v>87</v>
       </c>
-      <c r="J8" t="s">
+      <c r="AP9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV9" t="s">
         <v>109</v>
       </c>
-      <c r="K8" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="AW9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>81</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>88</v>
+      </c>
+      <c r="BC9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="BE9" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>94</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ9" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN9" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>122</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" t="s">
         <v>106</v>
       </c>
-      <c r="N8" t="s">
+      <c r="H10" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" t="s">
+        <v>110</v>
+      </c>
+      <c r="K10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L10" t="s">
+        <v>118</v>
+      </c>
+      <c r="N10" t="s">
+        <v>120</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>89</v>
+      </c>
+      <c r="R10" t="s">
+        <v>77</v>
+      </c>
+      <c r="S10" t="s">
+        <v>77</v>
+      </c>
+      <c r="T10" t="s">
         <v>81</v>
       </c>
-      <c r="O8" t="s">
-        <v>96</v>
-      </c>
-      <c r="P8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>79</v>
-      </c>
-      <c r="R8" t="s">
-        <v>78</v>
-      </c>
-      <c r="S8" t="s">
-        <v>79</v>
-      </c>
-      <c r="T8" t="s">
-        <v>96</v>
-      </c>
-      <c r="U8" t="s">
-        <v>78</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="U10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="V10" t="s">
+        <v>95</v>
+      </c>
+      <c r="W10" t="s">
         <v>88</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ10" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Y8" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB8" t="s">
+      <c r="AK10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV10" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AW10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AY10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>90</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>88</v>
+      </c>
+      <c r="BB10" t="s">
         <v>93</v>
       </c>
-      <c r="AC8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG8" t="s">
+      <c r="BC10" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>114</v>
+      </c>
+      <c r="BF10" s="7"/>
+      <c r="BJ10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" t="s">
+        <v>117</v>
+      </c>
+      <c r="K11" t="s">
+        <v>118</v>
+      </c>
+      <c r="L11" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" t="s">
+        <v>116</v>
+      </c>
+      <c r="O11" t="s">
+        <v>95</v>
+      </c>
+      <c r="P11" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" t="s">
+        <v>87</v>
+      </c>
+      <c r="S11" t="s">
+        <v>93</v>
+      </c>
+      <c r="T11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="U11" t="s">
+        <v>95</v>
+      </c>
+      <c r="V11" t="s">
+        <v>125</v>
+      </c>
+      <c r="W11" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK11" t="s">
         <v>88</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AL11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>102</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA11" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>116</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>122</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K12" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N12" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12" t="s">
+        <v>113</v>
+      </c>
+      <c r="P12" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="T12" t="s">
+        <v>113</v>
+      </c>
+      <c r="U12" t="s">
+        <v>113</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="W12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA12" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AL12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AO12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AT12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>102</v>
+      </c>
+      <c r="BB12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="BC12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BD12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="BK12" t="s">
         <v>110</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK8" t="s">
+      <c r="BM12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" t="s">
+        <v>122</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" t="s">
+        <v>122</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="O13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P13" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>113</v>
+      </c>
+      <c r="R13" t="s">
+        <v>120</v>
+      </c>
+      <c r="S13" t="s">
+        <v>95</v>
+      </c>
+      <c r="T13" t="s">
+        <v>94</v>
+      </c>
+      <c r="U13" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" t="s">
+        <v>119</v>
+      </c>
+      <c r="W13" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>127</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AQ13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>114</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>122</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" t="s">
+        <v>117</v>
+      </c>
+      <c r="N14" t="s">
+        <v>110</v>
+      </c>
+      <c r="O14" t="s">
+        <v>90</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>94</v>
+      </c>
+      <c r="R14" t="s">
+        <v>116</v>
+      </c>
+      <c r="S14" t="s">
+        <v>113</v>
+      </c>
+      <c r="T14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="U14" t="s">
+        <v>93</v>
+      </c>
+      <c r="V14" t="s">
+        <v>110</v>
+      </c>
+      <c r="W14" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>122</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>117</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="N15" t="s">
+        <v>117</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="P15" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>118</v>
+      </c>
+      <c r="R15" t="s">
+        <v>118</v>
+      </c>
+      <c r="S15" t="s">
+        <v>106</v>
+      </c>
+      <c r="T15" t="s">
+        <v>110</v>
+      </c>
+      <c r="U15" t="s">
+        <v>100</v>
+      </c>
+      <c r="V15" t="s">
+        <v>117</v>
+      </c>
+      <c r="W15" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>111</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN15" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR15" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AT15" t="s">
         <v>107</v>
       </c>
-      <c r="AL8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>91</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AY8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>96</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>89</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>105</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>87</v>
-      </c>
-      <c r="BE8" t="s">
+      <c r="AV15" t="s">
+        <v>111</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX15" t="s">
         <v>110</v>
       </c>
-      <c r="BF8" t="s">
-        <v>93</v>
-      </c>
-      <c r="BG8" s="7"/>
-      <c r="BH8" s="7"/>
-      <c r="BJ8" t="s">
+      <c r="AY15" t="s">
+        <v>111</v>
+      </c>
+      <c r="AZ15" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>103</v>
+      </c>
+      <c r="BB15" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" t="s">
+        <v>103</v>
+      </c>
+      <c r="O16" t="s">
+        <v>110</v>
+      </c>
+      <c r="P16" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="BK8" t="s">
+      <c r="R16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="T16" t="s">
+        <v>127</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR16" t="s">
         <v>111</v>
       </c>
-      <c r="BM8" t="s">
+      <c r="AT16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>122</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>111</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>127</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>127</v>
+      </c>
+      <c r="O17" t="s">
+        <v>121</v>
+      </c>
+      <c r="P17" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>119</v>
+      </c>
+      <c r="R17" t="s">
+        <v>119</v>
+      </c>
+      <c r="S17" t="s">
+        <v>103</v>
+      </c>
+      <c r="U17" t="s">
+        <v>103</v>
+      </c>
+      <c r="W17" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT17" t="s">
         <v>110</v>
       </c>
-      <c r="BN8" t="s">
-        <v>107</v>
-      </c>
-      <c r="BO8" s="7"/>
+      <c r="AX17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L9" t="s">
-        <v>102</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="O9" t="s">
-        <v>91</v>
-      </c>
-      <c r="P9" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>96</v>
-      </c>
-      <c r="R9" t="s">
-        <v>80</v>
-      </c>
-      <c r="S9" t="s">
-        <v>99</v>
-      </c>
-      <c r="T9" t="s">
-        <v>76</v>
-      </c>
-      <c r="U9" t="s">
-        <v>89</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="W9" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE9" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG9" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ9" t="s">
+    <row r="18" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
         <v>110</v>
       </c>
-      <c r="AK9" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AP9" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AU9" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>105</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>86</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>80</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC9" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="BE9" s="7"/>
-      <c r="BF9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BJ9" s="7"/>
-      <c r="BK9" t="s">
-        <v>107</v>
-      </c>
-      <c r="BM9" s="7"/>
-      <c r="BN9" s="7"/>
+      <c r="R18" t="s">
+        <v>103</v>
+      </c>
+      <c r="S18" t="s">
+        <v>111</v>
+      </c>
+      <c r="U18" t="s">
+        <v>111</v>
+      </c>
+      <c r="W18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>117</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" t="s">
-        <v>110</v>
-      </c>
-      <c r="N10" t="s">
-        <v>111</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>88</v>
-      </c>
-      <c r="R10" t="s">
-        <v>76</v>
-      </c>
-      <c r="S10" t="s">
-        <v>76</v>
-      </c>
-      <c r="T10" t="s">
-        <v>80</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="V10" t="s">
-        <v>93</v>
-      </c>
-      <c r="W10" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y10" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z10" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ10" s="7"/>
-      <c r="AK10" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AN10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ10" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>90</v>
-      </c>
-      <c r="AV10" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AW10" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>89</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>87</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>91</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>102</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>108</v>
-      </c>
-      <c r="BF10" s="7"/>
-      <c r="BK10" t="s">
-        <v>103</v>
+    <row r="19" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>121</v>
+      </c>
+      <c r="R19" t="s">
+        <v>127</v>
+      </c>
+      <c r="S19" t="s">
+        <v>122</v>
+      </c>
+      <c r="U19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="K11" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" t="s">
-        <v>113</v>
-      </c>
-      <c r="N11" t="s">
-        <v>109</v>
-      </c>
-      <c r="O11" t="s">
-        <v>93</v>
-      </c>
-      <c r="P11" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>91</v>
-      </c>
-      <c r="R11" t="s">
-        <v>86</v>
-      </c>
-      <c r="S11" t="s">
-        <v>91</v>
-      </c>
-      <c r="T11" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="U11" t="s">
-        <v>93</v>
-      </c>
-      <c r="V11" t="s">
-        <v>114</v>
-      </c>
-      <c r="W11" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB11" s="7"/>
-      <c r="AC11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>107</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AZ11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA11" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>86</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>109</v>
-      </c>
-      <c r="BK11" s="7"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="K12" t="s">
-        <v>113</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="N12" t="s">
-        <v>110</v>
-      </c>
-      <c r="O12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P12" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="T12" t="s">
-        <v>107</v>
-      </c>
-      <c r="U12" t="s">
-        <v>107</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="W12" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC12" s="7"/>
-      <c r="AD12" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF12" s="7"/>
-      <c r="AG12" t="s">
-        <v>109</v>
-      </c>
-      <c r="AH12" s="7"/>
-      <c r="AK12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL12" s="7"/>
-      <c r="AM12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO12" s="7"/>
-      <c r="AP12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AS12" s="7"/>
-      <c r="AT12" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU12" s="7"/>
-      <c r="AV12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>98</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>90</v>
-      </c>
-      <c r="BA12" t="s">
-        <v>100</v>
-      </c>
-      <c r="BB12" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="BC12" s="7"/>
-      <c r="BD12" s="7"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" t="s">
-        <v>102</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" t="s">
-        <v>92</v>
-      </c>
-      <c r="P13" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" t="s">
-        <v>111</v>
-      </c>
-      <c r="S13" t="s">
-        <v>93</v>
-      </c>
-      <c r="T13" t="s">
-        <v>92</v>
-      </c>
-      <c r="U13" t="s">
-        <v>92</v>
-      </c>
-      <c r="W13" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="7"/>
-      <c r="AG13" s="7"/>
-      <c r="AK13" s="7"/>
-      <c r="AM13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP13" s="7"/>
-      <c r="AQ13" s="7"/>
-      <c r="AR13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AW13" s="7"/>
-      <c r="AX13" t="s">
-        <v>109</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>92</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>107</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="D14" s="7"/>
-      <c r="E14" t="s">
-        <v>110</v>
-      </c>
-      <c r="O14" t="s">
-        <v>89</v>
-      </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" t="s">
-        <v>92</v>
-      </c>
-      <c r="R14" t="s">
-        <v>109</v>
-      </c>
-      <c r="S14" t="s">
-        <v>107</v>
-      </c>
-      <c r="T14" s="7"/>
-      <c r="U14" t="s">
-        <v>91</v>
-      </c>
-      <c r="W14" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>113</v>
-      </c>
-      <c r="AM14" s="7"/>
-      <c r="AN14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AV14" s="7"/>
-      <c r="AX14" s="7"/>
-      <c r="AY14" s="7"/>
-      <c r="AZ14" t="s">
-        <v>112</v>
-      </c>
-      <c r="BA14" s="7"/>
-      <c r="BB14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
-      <c r="E15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="Q15" t="s">
-        <v>110</v>
-      </c>
-      <c r="R15" t="s">
-        <v>110</v>
-      </c>
-      <c r="S15" t="s">
-        <v>102</v>
-      </c>
-      <c r="U15" t="s">
-        <v>98</v>
-      </c>
-      <c r="W15" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AN15" s="7"/>
-      <c r="AR15" s="7"/>
-      <c r="AT15" t="s">
-        <v>103</v>
-      </c>
-      <c r="AZ15" s="7"/>
-      <c r="BB15" s="7"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25">
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="AT16" s="7"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="5:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4203,14 +4930,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AQ42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A3:BC42"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -4255,138 +4982,174 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N3" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="X3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI3" t="s">
         <v>95</v>
       </c>
-      <c r="J3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="AJ3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" t="s">
         <v>94</v>
       </c>
-      <c r="N3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="AP3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT3" t="s">
         <v>104</v>
       </c>
-      <c r="P3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>81</v>
-      </c>
-      <c r="R3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U3" t="s">
-        <v>80</v>
-      </c>
-      <c r="V3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W3" t="s">
-        <v>76</v>
-      </c>
-      <c r="X3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AU3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AV3" t="s">
         <v>103</v>
       </c>
-      <c r="AG3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AW3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="s">
         <v>111</v>
       </c>
-      <c r="AK3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>114</v>
+      <c r="AY3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4516,8 +5279,44 @@
       <c r="AQ4" t="s">
         <v>11</v>
       </c>
+      <c r="AR4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>68</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>47</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4647,8 +5446,44 @@
       <c r="AQ5" t="s">
         <v>34</v>
       </c>
+      <c r="AR5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>41</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>4</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4778,8 +5613,44 @@
       <c r="AQ6" t="s">
         <v>7</v>
       </c>
+      <c r="AR6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -4909,13 +5780,49 @@
       <c r="AQ7" t="s">
         <v>25</v>
       </c>
+      <c r="AR7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>48</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>25</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -4939,7 +5846,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -4989,8 +5896,41 @@
       <c r="AO8" t="s">
         <v>47</v>
       </c>
+      <c r="AR8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>6</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -5004,7 +5944,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -5069,8 +6009,41 @@
       <c r="AO9" t="s">
         <v>50</v>
       </c>
+      <c r="AR9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -5149,8 +6122,41 @@
       <c r="AO10" t="s">
         <v>51</v>
       </c>
+      <c r="AR10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>40</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -5229,8 +6235,41 @@
       <c r="AO11" t="s">
         <v>62</v>
       </c>
+      <c r="AR11" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>59</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>60</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>13</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -5256,7 +6295,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -5297,8 +6336,38 @@
       <c r="AO12" t="s">
         <v>6</v>
       </c>
+      <c r="AS12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>44</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>39</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>46</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -5365,8 +6434,38 @@
       <c r="AO13" t="s">
         <v>54</v>
       </c>
+      <c r="AS13" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>49</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -5433,8 +6532,38 @@
       <c r="AO14" t="s">
         <v>7</v>
       </c>
+      <c r="AS14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>15</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>32</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -5501,8 +6630,38 @@
       <c r="AO15" t="s">
         <v>43</v>
       </c>
+      <c r="AS15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>30</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>25</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>30</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -5569,8 +6728,32 @@
       <c r="AO16" t="s">
         <v>41</v>
       </c>
+      <c r="AS16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>58</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -5637,8 +6820,32 @@
       <c r="AO17" t="s">
         <v>71</v>
       </c>
+      <c r="AS17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>24</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>33</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -5705,8 +6912,32 @@
       <c r="AO18" t="s">
         <v>69</v>
       </c>
+      <c r="AS18" t="s">
+        <v>20</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>12</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5773,8 +7004,32 @@
       <c r="AO19" t="s">
         <v>27</v>
       </c>
+      <c r="AS19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -5826,8 +7081,23 @@
       <c r="AO20" t="s">
         <v>31</v>
       </c>
+      <c r="AT20" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -5879,8 +7149,23 @@
       <c r="AO21" t="s">
         <v>70</v>
       </c>
+      <c r="AT21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>18</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -5932,8 +7217,23 @@
       <c r="AO22" t="s">
         <v>65</v>
       </c>
+      <c r="AT22" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>20</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>22</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -5985,8 +7285,23 @@
       <c r="AO23" t="s">
         <v>61</v>
       </c>
+      <c r="AT23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>20</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>57</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -6005,8 +7320,14 @@
       <c r="AO24" t="s">
         <v>9</v>
       </c>
+      <c r="AT24" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -6025,8 +7346,14 @@
       <c r="AO25" t="s">
         <v>33</v>
       </c>
+      <c r="AT25" t="s">
+        <v>26</v>
+      </c>
+      <c r="BC25" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -6045,8 +7372,14 @@
       <c r="AO26" t="s">
         <v>20</v>
       </c>
+      <c r="AT26" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC26" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -6065,12 +7398,18 @@
       <c r="AO27" t="s">
         <v>13</v>
       </c>
+      <c r="AT27" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC27" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6086,10 +7425,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:AQ14"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A3:BC14"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -6171,572 +7510,752 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N3" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S3" t="s">
+        <v>101</v>
+      </c>
+      <c r="T3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="X3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI3" t="s">
         <v>95</v>
       </c>
-      <c r="J3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="AJ3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO3" t="s">
         <v>94</v>
       </c>
-      <c r="N3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="AP3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT3" t="s">
         <v>104</v>
       </c>
-      <c r="P3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>81</v>
-      </c>
-      <c r="R3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U3" t="s">
-        <v>80</v>
-      </c>
-      <c r="V3" t="s">
-        <v>89</v>
-      </c>
-      <c r="W3" t="s">
-        <v>76</v>
-      </c>
-      <c r="X3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AU3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AV3" t="s">
         <v>103</v>
       </c>
-      <c r="AG3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ3" t="s">
+      <c r="AW3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="s">
         <v>111</v>
       </c>
-      <c r="AK3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>110</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>114</v>
+      <c r="AY3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J4" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K4" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="M4" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="N4" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="O4" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="P4" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="Q4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="R4" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="S4" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="T4" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="U4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="V4" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="W4" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="X4" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="Y4" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="Z4" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="AA4" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="AB4" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="AC4" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="AD4" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="AE4" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="AG4" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="AH4" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="AI4" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="AJ4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="AK4" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="AL4" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="AM4" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="AN4" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="AO4" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="AP4" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="AQ4" t="s">
-        <v>158</v>
+        <v>171</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>173</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>176</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>181</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>182</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>183</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="G5" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="H5" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="K5" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="L5" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="N5" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="P5" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="R5" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="T5" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="U5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="V5" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="W5" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="Y5" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="Z5" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="AB5" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="AD5" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="AE5" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="AF5" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="AI5" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="AK5" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="AL5" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="AM5" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="AN5" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="AO5" t="s">
-        <v>184</v>
+        <v>209</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>215</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>216</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>217</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>218</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>219</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>220</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F6" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="G6" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="H6" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="K6" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="L6" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="N6" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="T6" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="V6" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="W6" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="Y6" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="Z6" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="AB6" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="AD6" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="AE6" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="AI6" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="AK6" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="AM6" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="AO6" t="s">
-        <v>206</v>
+        <v>242</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>243</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>244</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>245</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>246</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>247</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>248</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>249</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>250</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>251</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>252</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="H7" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="K7" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="L7" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="N7" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="T7" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="V7" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="W7" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="Y7" t="s">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="Z7" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="AB7" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="AD7" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="AE7" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="AI7" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="AK7" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="AM7" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="AN7" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="AO7" t="s">
-        <v>228</v>
+        <v>274</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>275</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>276</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>277</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>278</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>280</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>281</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>282</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>284</v>
       </c>
       <c r="F8" t="s">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>286</v>
       </c>
       <c r="H8" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="K8" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="L8" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="V8" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="W8" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="Y8" t="s">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="AB8" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="AD8" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="AE8" t="s">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="AI8" t="s">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="AK8" t="s">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="AM8" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="AO8" t="s">
-        <v>245</v>
+        <v>299</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>300</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>301</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>302</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>303</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>304</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="AD9" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="AE9" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="AK9" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="AO9" t="s">
-        <v>251</v>
+        <v>310</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>311</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>312</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="30:41" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.140625" customWidth="1"/>
@@ -6753,469 +8272,469 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="9">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>136</v>
+        <v>184</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
+        <v>314</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="10">
         <f>C1*4</f>
-        <v>544</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B3" s="16">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="12">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>544</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+        <v>738</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="B4" s="19">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="14">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="G4" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="H4" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="I4" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="J4" t="s">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="K4" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="L4" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="14">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>18</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="F5" s="21">
+        <v>23</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="F5" s="16">
         <v>2</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="17">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="18">
         <f>B4/B3</f>
-        <v>0.14522058823529413</v>
-      </c>
-      <c r="I5" s="24">
+        <v>0.14363143631436315</v>
+      </c>
+      <c r="I5" s="19">
         <f>C2*G5</f>
-        <v>83.6923076923077</v>
+        <v>113.23076923076924</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>79</v>
-      </c>
-      <c r="K5" s="25">
+        <v>106</v>
+      </c>
+      <c r="K5" s="20">
         <f>J5-I5</f>
-        <v>-4.692307692307693</v>
-      </c>
-      <c r="L5" s="26">
+        <v>-7.2307692307692406</v>
+      </c>
+      <c r="L5" s="21">
         <f>K5/4</f>
-        <v>-1.1730769230769234</v>
+        <v>-1.8076923076923102</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="14">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>216</v>
-      </c>
-      <c r="E6" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="16">
         <v>1</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="17">
         <f>F6/13</f>
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="H6" s="23">
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="H6" s="18">
         <f>B5/B3</f>
-        <v>0.03308823529411765</v>
-      </c>
-      <c r="I6" s="24">
+        <v>3.1165311653116531E-2</v>
+      </c>
+      <c r="I6" s="19">
         <f>C2*G6</f>
-        <v>41.84615384615385</v>
+        <v>56.61538461538462</v>
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>18</v>
-      </c>
-      <c r="K6" s="25">
+        <v>23</v>
+      </c>
+      <c r="K6" s="20">
         <f>J6-I6</f>
-        <v>-23.846153846153847</v>
-      </c>
-      <c r="L6" s="26">
+        <v>-33.61538461538462</v>
+      </c>
+      <c r="L6" s="21">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-5.961538461538462</v>
+        <v>-8.4038461538461551</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="23">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>231</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="F7" s="30">
+        <v>312</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="F7" s="25">
         <v>3</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="26">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="27">
         <f>(B5+B4)/B3</f>
-        <v>0.17830882352941177</v>
-      </c>
-      <c r="I7" s="24">
+        <v>0.17479674796747968</v>
+      </c>
+      <c r="I7" s="19">
         <f>C2*G7</f>
-        <v>125.53846153846155</v>
+        <v>169.84615384615387</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>97</v>
-      </c>
-      <c r="K7" s="25">
+        <v>129</v>
+      </c>
+      <c r="K7" s="20">
         <f>J7-I7</f>
-        <v>-28.538461538461547</v>
-      </c>
-      <c r="L7" s="26">
+        <v>-40.846153846153868</v>
+      </c>
+      <c r="L7" s="21">
         <f>K7/4</f>
-        <v>-7.134615384615387</v>
+        <v>-10.211538461538467</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E8" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="F8" s="34">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="29">
         <v>6</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="30">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="31">
         <f>B6/B3</f>
-        <v>0.39705882352941174</v>
-      </c>
-      <c r="I8" s="24">
+        <v>0.40243902439024393</v>
+      </c>
+      <c r="I8" s="19">
         <f>C2*G8</f>
-        <v>251.0769230769231</v>
+        <v>339.69230769230774</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>216</v>
-      </c>
-      <c r="K8" s="25">
+        <v>297</v>
+      </c>
+      <c r="K8" s="20">
         <f>J8-I8</f>
-        <v>-35.076923076923094</v>
-      </c>
-      <c r="L8" s="26">
+        <v>-42.692307692307736</v>
+      </c>
+      <c r="L8" s="21">
         <f>K8/4</f>
-        <v>-8.769230769230774</v>
+        <v>-10.673076923076934</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>544</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="F9" s="34">
+        <v>738</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="F9" s="29">
         <v>4</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="30">
         <f t="shared" si="1"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H9" s="36">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H9" s="31">
         <f>B7/B3</f>
-        <v>0.42463235294117646</v>
-      </c>
-      <c r="I9" s="24">
+        <v>0.42276422764227645</v>
+      </c>
+      <c r="I9" s="19">
         <f>C2*G9</f>
-        <v>167.3846153846154</v>
+        <v>226.46153846153848</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>231</v>
-      </c>
-      <c r="K9" s="37">
+        <v>312</v>
+      </c>
+      <c r="K9" s="32">
         <f>J9-I9</f>
-        <v>63.61538461538461</v>
-      </c>
-      <c r="L9" s="26">
+        <v>85.538461538461519</v>
+      </c>
+      <c r="L9" s="21">
         <f>K9/4</f>
-        <v>15.903846153846153</v>
+        <v>21.38461538461538</v>
       </c>
     </row>
-    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="I11" s="39">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="I11" s="34">
         <f>SUM(I7:I9)</f>
-        <v>544</v>
-      </c>
-      <c r="J11" s="33">
+        <v>736.00000000000011</v>
+      </c>
+      <c r="J11" s="28">
         <f>SUM(J7:J9)</f>
-        <v>544</v>
-      </c>
-      <c r="K11" s="40">
+        <v>738</v>
+      </c>
+      <c r="K11" s="35">
         <f>SUM(K7:K9)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="41">
+        <v>1.9999999999999147</v>
+      </c>
+      <c r="L11" s="36">
         <f>SUM(L7:L9)</f>
-        <v>0</v>
+        <v>0.49999999999997868</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>269</v>
+        <v>334</v>
       </c>
       <c r="F16" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="G16" t="s">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="H16" t="s">
-        <v>259</v>
-      </c>
-      <c r="I16" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>261</v>
+        <v>320</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>322</v>
       </c>
       <c r="K16" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="L16" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="43" t="s">
-        <v>264</v>
-      </c>
-      <c r="F17" s="44">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E17" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="F17" s="39">
         <v>3</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="40">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="46">
+      <c r="H17" s="41">
         <f>(B5+B4)/B3</f>
-        <v>0.17830882352941177</v>
-      </c>
-      <c r="I17" s="47">
+        <v>0.17479674796747968</v>
+      </c>
+      <c r="I17" s="42">
         <f>B3*G17</f>
-        <v>125.53846153846155</v>
-      </c>
-      <c r="J17" s="48">
+        <v>170.30769230769232</v>
+      </c>
+      <c r="J17" s="43">
         <f>B5+B4</f>
-        <v>97</v>
-      </c>
-      <c r="K17" s="49">
+        <v>129</v>
+      </c>
+      <c r="K17" s="44">
         <f>J17-I17</f>
-        <v>-28.538461538461547</v>
-      </c>
-      <c r="L17" s="26">
+        <v>-41.307692307692321</v>
+      </c>
+      <c r="L17" s="21">
         <f>K17/4</f>
-        <v>-7.134615384615387</v>
+        <v>-10.32692307692308</v>
       </c>
     </row>
-    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="F18" s="51">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E18" s="45" t="s">
+        <v>326</v>
+      </c>
+      <c r="F18" s="46">
         <v>6</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="47">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="48">
         <f>B6/B3</f>
-        <v>0.39705882352941174</v>
-      </c>
-      <c r="I18" s="54">
+        <v>0.40243902439024393</v>
+      </c>
+      <c r="I18" s="49">
         <f>B3*G18</f>
-        <v>251.0769230769231</v>
-      </c>
-      <c r="J18" s="55">
+        <v>340.61538461538464</v>
+      </c>
+      <c r="J18" s="50">
         <f>B6</f>
-        <v>216</v>
-      </c>
-      <c r="K18" s="56">
+        <v>297</v>
+      </c>
+      <c r="K18" s="51">
         <f>J18-I18</f>
-        <v>-35.076923076923094</v>
-      </c>
-      <c r="L18" s="26">
+        <v>-43.615384615384642</v>
+      </c>
+      <c r="L18" s="21">
         <f>K18/4</f>
-        <v>-8.769230769230774</v>
-      </c>
-      <c r="Q18" s="57"/>
+        <v>-10.90384615384616</v>
+      </c>
+      <c r="Q18" s="52"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="58" t="s">
-        <v>267</v>
-      </c>
-      <c r="F19" s="59">
+    <row r="19" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="53" t="s">
+        <v>328</v>
+      </c>
+      <c r="F19" s="54">
         <v>4</v>
       </c>
-      <c r="G19" s="60">
+      <c r="G19" s="55">
         <f t="shared" si="2"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H19" s="61">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H19" s="56">
         <f>B7/B3</f>
-        <v>0.42463235294117646</v>
-      </c>
-      <c r="I19" s="62">
+        <v>0.42276422764227645</v>
+      </c>
+      <c r="I19" s="57">
         <f>B3*G19</f>
-        <v>167.3846153846154</v>
-      </c>
-      <c r="J19" s="63">
+        <v>227.07692307692309</v>
+      </c>
+      <c r="J19" s="58">
         <f>B7</f>
-        <v>231</v>
-      </c>
-      <c r="K19" s="64">
+        <v>312</v>
+      </c>
+      <c r="K19" s="59">
         <f>J19-I19</f>
-        <v>63.61538461538461</v>
-      </c>
-      <c r="L19" s="26">
+        <v>84.923076923076906</v>
+      </c>
+      <c r="L19" s="21">
         <f>K19/4</f>
-        <v>15.903846153846153</v>
+        <v>21.230769230769226</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="P24" s="65" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65"/>
+    <row r="24" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="P24" s="72" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
     </row>
-    <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P25" s="66"/>
-      <c r="Q25" s="67" t="s">
-        <v>272</v>
-      </c>
-      <c r="R25" s="68" t="s">
-        <v>273</v>
-      </c>
-      <c r="S25" s="69" t="s">
-        <v>262</v>
+    <row r="25" spans="5:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="60"/>
+      <c r="Q25" s="61" t="s">
+        <v>332</v>
+      </c>
+      <c r="R25" s="62" t="s">
+        <v>333</v>
+      </c>
+      <c r="S25" s="63" t="s">
+        <v>323</v>
       </c>
     </row>
-    <row r="26" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P26" s="70" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q26" s="33">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="P26" s="64" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q26" s="28">
         <v>247</v>
       </c>
-      <c r="R26" s="33">
+      <c r="R26" s="28">
         <v>212</v>
       </c>
-      <c r="S26" s="19">
+      <c r="S26" s="14">
         <f>R26-Q26</f>
         <v>-35</v>
       </c>
     </row>
-    <row r="27" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P27" s="70" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q27" s="33">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="P27" s="64" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q27" s="28">
         <v>124</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="28">
         <v>92</v>
       </c>
-      <c r="S27" s="19">
+      <c r="S27" s="14">
         <f t="shared" ref="S27:S28" si="3">R27-Q27</f>
         <v>-32</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P28" s="71" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q28" s="72">
+    <row r="28" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q28" s="66">
         <v>165</v>
       </c>
-      <c r="R28" s="72">
+      <c r="R28" s="66">
         <v>232</v>
       </c>
-      <c r="S28" s="28">
+      <c r="S28" s="23">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,32 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3DCC08-2B22-4850-ABF0-3EA12A67EB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
   </bookViews>
   <sheets>
-    <sheet name="AHL" sheetId="1" r:id="rId1"/>
-    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
-    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
-    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
+    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -1023,6 +1009,9 @@
     <t>kontrola</t>
   </si>
   <si>
+    <t>till 6.1.2025</t>
+  </si>
+  <si>
     <t>% games per team</t>
   </si>
   <si>
@@ -1033,53 +1022,50 @@
   </si>
   <si>
     <t>Actual assigned games per country</t>
-  </si>
-  <si>
-    <t>till 6.1.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF9C0006"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF006100"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1091,25 +1077,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1121,7 +1107,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1138,7 +1124,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1149,7 +1135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1174,9 +1160,7 @@
     <border>
       <left/>
       <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
+      <top style="thick"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1446,10 +1430,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1543,6 +1542,9 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1556,24 +1558,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1853,9 +1837,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BQ73"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BR73"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -1927,7 +1911,7 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
         <v>12</v>
@@ -2205,7 +2189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2414,7 +2398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2623,7 +2607,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -2832,7 +2816,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3035,7 +3019,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3235,7 +3219,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -3432,7 +3416,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3627,7 +3611,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -3815,7 +3799,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>100</v>
       </c>
@@ -3986,7 +3970,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -4156,7 +4140,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -4317,7 +4301,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>92</v>
       </c>
@@ -4469,7 +4453,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>111</v>
       </c>
@@ -4600,7 +4584,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>117</v>
       </c>
@@ -4704,7 +4688,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>121</v>
       </c>
@@ -4778,7 +4762,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>127</v>
       </c>
@@ -4831,7 +4815,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
       <c r="Q18" t="s">
         <v>110</v>
       </c>
@@ -4857,7 +4841,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="17:52" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
         <v>121</v>
       </c>
@@ -4874,19 +4858,19 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="5:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="5:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4930,14 +4914,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:BC42"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -4982,7 +4966,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -5149,7 +5133,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -5316,7 +5300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5483,7 +5467,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5650,7 +5634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -5817,7 +5801,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -5930,7 +5914,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -6043,7 +6027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -6156,7 +6140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -6269,7 +6253,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -6367,7 +6351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -6465,7 +6449,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -6563,7 +6547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -6661,7 +6645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -6753,7 +6737,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -6845,7 +6829,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -6937,7 +6921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -7029,7 +7013,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -7097,7 +7081,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -7165,7 +7149,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -7233,7 +7217,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -7301,7 +7285,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -7327,7 +7311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -7353,7 +7337,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -7379,7 +7363,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -7405,11 +7389,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="30:55" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7425,10 +7409,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:BC14"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -7510,7 +7494,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -7677,7 +7661,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7844,7 +7828,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>184</v>
       </c>
@@ -7957,7 +7941,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>221</v>
       </c>
@@ -8055,7 +8039,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="7" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>253</v>
       </c>
@@ -8147,7 +8131,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="8" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>283</v>
       </c>
@@ -8215,7 +8199,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
         <v>305</v>
       </c>
@@ -8241,21 +8225,21 @@
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="30:55" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.140625" customWidth="1"/>
@@ -8272,46 +8256,46 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="9">
+      <c r="B1" s="10"/>
+      <c r="C1" s="11">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="10">
+      <c r="B2" s="13"/>
+      <c r="C2" s="14">
         <f>C1*4</f>
         <v>736</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="16">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>738</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="19">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>106</v>
       </c>
@@ -8340,29 +8324,29 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="19">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>23</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="21">
         <v>2</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="22">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="23">
         <f>B4/B3</f>
         <v>0.14363143631436315</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="24">
         <f>C2*G5</f>
         <v>113.23076923076924</v>
       </c>
@@ -8370,38 +8354,38 @@
         <f>B4</f>
         <v>106</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="25">
         <f>J5-I5</f>
-        <v>-7.2307692307692406</v>
-      </c>
-      <c r="L5" s="21">
+        <v>-7.230769230769241</v>
+      </c>
+      <c r="L5" s="26">
         <f>K5/4</f>
         <v>-1.8076923076923102</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="19">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
         <v>297</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="21">
         <v>1</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="22">
         <f>F6/13</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="H6" s="18">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H6" s="23">
         <f>B5/B3</f>
-        <v>3.1165311653116531E-2</v>
-      </c>
-      <c r="I6" s="19">
+        <v>0.03116531165311653</v>
+      </c>
+      <c r="I6" s="24">
         <f>C2*G6</f>
         <v>56.61538461538462</v>
       </c>
@@ -8409,38 +8393,38 @@
         <f>B5</f>
         <v>23</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="25">
         <f>J6-I6</f>
         <v>-33.61538461538462</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="26">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-8.4038461538461551</v>
+        <v>-8.403846153846155</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="28">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>312</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="30">
         <v>3</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="31">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="32">
         <f>(B5+B4)/B3</f>
         <v>0.17479674796747968</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="24">
         <f>C2*G7</f>
         <v>169.84615384615387</v>
       </c>
@@ -8448,31 +8432,31 @@
         <f>B4+B5</f>
         <v>129</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="25">
         <f>J7-I7</f>
-        <v>-40.846153846153868</v>
-      </c>
-      <c r="L7" s="21">
+        <v>-40.84615384615387</v>
+      </c>
+      <c r="L7" s="26">
         <f>K7/4</f>
         <v>-10.211538461538467</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="28" t="s">
+    <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E8" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="34">
         <v>6</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="35">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="36">
         <f>B6/B3</f>
-        <v>0.40243902439024393</v>
-      </c>
-      <c r="I8" s="19">
+        <v>0.4024390243902439</v>
+      </c>
+      <c r="I8" s="24">
         <f>C2*G8</f>
         <v>339.69230769230774</v>
       </c>
@@ -8480,16 +8464,16 @@
         <f>B6</f>
         <v>297</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="25">
         <f>J8-I8</f>
         <v>-42.692307692307736</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="26">
         <f>K8/4</f>
         <v>-10.673076923076934</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>327</v>
       </c>
@@ -8497,21 +8481,21 @@
         <f>SUM(B4:B7)</f>
         <v>738</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="34">
         <v>4</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="35">
         <f t="shared" si="1"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H9" s="31">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H9" s="36">
         <f>B7/B3</f>
         <v>0.42276422764227645</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="24">
         <f>C2*G9</f>
         <v>226.46153846153848</v>
       </c>
@@ -8519,53 +8503,53 @@
         <f>B7</f>
         <v>312</v>
       </c>
-      <c r="K9" s="32">
+      <c r="K9" s="37">
         <f>J9-I9</f>
-        <v>85.538461538461519</v>
-      </c>
-      <c r="L9" s="21">
+        <v>85.53846153846152</v>
+      </c>
+      <c r="L9" s="26">
         <f>K9/4</f>
         <v>21.38461538461538</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="33" t="s">
+    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="39">
         <f>SUM(I7:I9)</f>
-        <v>736.00000000000011</v>
-      </c>
-      <c r="J11" s="28">
+        <v>736.0000000000001</v>
+      </c>
+      <c r="J11" s="33">
         <f>SUM(J7:J9)</f>
         <v>738</v>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="40">
         <f>SUM(K7:K9)</f>
         <v>1.9999999999999147</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="41">
         <f>SUM(L7:L9)</f>
-        <v>0.49999999999997868</v>
+        <v>0.4999999999999787</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F16" t="s">
         <v>318</v>
       </c>
       <c r="G16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H16" t="s">
         <v>320</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I16" s="42" t="s">
         <v>321</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J16" s="42" t="s">
         <v>322</v>
       </c>
       <c r="K16" t="s">
@@ -8575,166 +8559,166 @@
         <v>324</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E17" s="38" t="s">
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="44">
         <v>3</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="45">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="46">
         <f>(B5+B4)/B3</f>
         <v>0.17479674796747968</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="47">
         <f>B3*G17</f>
         <v>170.30769230769232</v>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="48">
         <f>B5+B4</f>
         <v>129</v>
       </c>
-      <c r="K17" s="44">
+      <c r="K17" s="49">
         <f>J17-I17</f>
-        <v>-41.307692307692321</v>
-      </c>
-      <c r="L17" s="21">
+        <v>-41.30769230769232</v>
+      </c>
+      <c r="L17" s="26">
         <f>K17/4</f>
         <v>-10.32692307692308</v>
       </c>
     </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E18" s="45" t="s">
+    <row r="18" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E18" s="50" t="s">
         <v>326</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="51">
         <v>6</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="52">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="53">
         <f>B6/B3</f>
-        <v>0.40243902439024393</v>
-      </c>
-      <c r="I18" s="49">
+        <v>0.4024390243902439</v>
+      </c>
+      <c r="I18" s="54">
         <f>B3*G18</f>
         <v>340.61538461538464</v>
       </c>
-      <c r="J18" s="50">
+      <c r="J18" s="55">
         <f>B6</f>
         <v>297</v>
       </c>
-      <c r="K18" s="51">
+      <c r="K18" s="56">
         <f>J18-I18</f>
-        <v>-43.615384615384642</v>
-      </c>
-      <c r="L18" s="21">
+        <v>-43.61538461538464</v>
+      </c>
+      <c r="L18" s="26">
         <f>K18/4</f>
         <v>-10.90384615384616</v>
       </c>
-      <c r="Q18" s="52"/>
+      <c r="Q18" s="57"/>
     </row>
-    <row r="19" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="53" t="s">
+    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="58" t="s">
         <v>328</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="59">
         <v>4</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="60">
         <f t="shared" si="2"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H19" s="56">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H19" s="61">
         <f>B7/B3</f>
         <v>0.42276422764227645</v>
       </c>
-      <c r="I19" s="57">
+      <c r="I19" s="62">
         <f>B3*G19</f>
-        <v>227.07692307692309</v>
-      </c>
-      <c r="J19" s="58">
+        <v>227.0769230769231</v>
+      </c>
+      <c r="J19" s="63">
         <f>B7</f>
         <v>312</v>
       </c>
-      <c r="K19" s="59">
+      <c r="K19" s="64">
         <f>J19-I19</f>
-        <v>84.923076923076906</v>
-      </c>
-      <c r="L19" s="21">
+        <v>84.9230769230769</v>
+      </c>
+      <c r="L19" s="26">
         <f>K19/4</f>
         <v>21.230769230769226</v>
       </c>
     </row>
-    <row r="24" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="P24" s="72" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
+    <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="P24" s="65" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
     </row>
-    <row r="25" spans="5:19" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P25" s="60"/>
-      <c r="Q25" s="61" t="s">
-        <v>332</v>
-      </c>
-      <c r="R25" s="62" t="s">
+    <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P25" s="66"/>
+      <c r="Q25" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="S25" s="63" t="s">
+      <c r="R25" s="68" t="s">
+        <v>334</v>
+      </c>
+      <c r="S25" s="69" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="P26" s="64" t="s">
+    <row r="26" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P26" s="70" t="s">
         <v>326</v>
       </c>
-      <c r="Q26" s="28">
+      <c r="Q26" s="33">
         <v>247</v>
       </c>
-      <c r="R26" s="28">
+      <c r="R26" s="33">
         <v>212</v>
       </c>
-      <c r="S26" s="14">
+      <c r="S26" s="19">
         <f>R26-Q26</f>
         <v>-35</v>
       </c>
     </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="P27" s="64" t="s">
+    <row r="27" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P27" s="70" t="s">
         <v>325</v>
       </c>
-      <c r="Q27" s="28">
+      <c r="Q27" s="33">
         <v>124</v>
       </c>
-      <c r="R27" s="28">
+      <c r="R27" s="33">
         <v>92</v>
       </c>
-      <c r="S27" s="14">
+      <c r="S27" s="19">
         <f t="shared" ref="S27:S28" si="3">R27-Q27</f>
         <v>-32</v>
       </c>
     </row>
-    <row r="28" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P28" s="65" t="s">
+    <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
+      <c r="P28" s="71" t="s">
         <v>328</v>
       </c>
-      <c r="Q28" s="66">
+      <c r="Q28" s="72">
         <v>165</v>
       </c>
-      <c r="R28" s="66">
+      <c r="R28" s="72">
         <v>232</v>
       </c>
-      <c r="S28" s="23">
+      <c r="S28" s="28">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="336">
   <si>
     <t>sl</t>
   </si>
@@ -346,6 +346,9 @@
     <t>2024-10-06</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2024-11-02</t>
   </si>
   <si>
@@ -397,9 +400,6 @@
     <t>2024-11-24</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2025-01-04</t>
   </si>
   <si>
@@ -565,7 +565,7 @@
     <t>KELIT Arena Zell am See;HolzerTo;KainbergerJu;TelesklavFa;WendnerMa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;OrelSt;SnojTa;FleischmannLu;RivisAn</t>
+    <t>Eishalle Sterzing;Huber rRe;SnojTa;FleischmannLu;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;ArlicMa;TelesklavFa</t>
@@ -637,7 +637,7 @@
     <t>Eishalle Sterzing;GiacomozziFe;RuetzMa;BrondiPa;StrimitzerDa</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;BajtMi;PinieOm;JavornikBl;PaceJa</t>
+    <t>Würtharena Neumarkt;BajtMi;GiacomozziFe;JavornikBl;PaceJa</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;LebenJa;OrelSt;MarkizetiGr;TelesklavFa</t>
@@ -727,7 +727,7 @@
     <t>Eishalle Dornbirn;MoschenAn;RuetzMa;DivisDo;IlmerNo</t>
   </si>
   <si>
-    <t>Eishalle Celje;VoicanCh;WidmannFl;WeissAl;WuchererGe</t>
+    <t>Eishalle Celje;VoicanCh;WidmannFl;PreiserJu;WuchererGe</t>
   </si>
   <si>
     <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WendnerMa</t>
@@ -757,7 +757,7 @@
     <t>Eishalle Meran;LazzeriAl;StefenelliFe;AbeltinoSi;RivisAn</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;HolzerTo;LegaSi;CusinFe;DivisDo</t>
+    <t>Eishalle Dornbirn;HolzerTo;LegaSi;DivisDo;JägerRi</t>
   </si>
   <si>
     <t>Eishalle Sterzing;Huber rRe;VirtaTu;FormaioniTh;RinkerDa</t>
@@ -766,7 +766,7 @@
     <t>Sportpark Kitzbühel;MetzingerFi;VoicanCh;KnezRo;LegatKo</t>
   </si>
   <si>
-    <t>Eishalle Meran;Huber rRe;RuetzMa;IlmerNo;ScalzeriAl</t>
+    <t>Eishalle Meran;Huber rRe;RuetzMa;FecchioFe;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Cortina;EggerTh;MoschenAn;AbeltinoSi;FormaioniTh</t>
@@ -844,7 +844,7 @@
     <t>Eishalle Meran;KainbergerJu;LehnerMo;EislCh;FleischmannLu</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;Huber rRe;SpiegelSe;GrisentiLu;IlmerNo</t>
+    <t>Eishalle Sterzing;Huber rRe;SpiegelSe;AbeltinoSi;GrisentiLu</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;EggerTh;RuetzMa;DivisDo;JägerRi</t>
@@ -856,7 +856,7 @@
     <t>Eishalle Cortina;BajtMi;MoschenAn;CristeliMa;MarkizetiGr</t>
   </si>
   <si>
-    <t>Eishalle Meran;BenvegnuAn;RuetzMa;JägerRi;RivisAn</t>
+    <t>ZBRISANO</t>
   </si>
   <si>
     <t>Eishalle Cortina;GiacomozziFe;PirasAn;CristeliMa;FleischmannLu</t>
@@ -901,7 +901,7 @@
     <t>Eishalle Jesenice;VirtaTu;WidmannFl;PaceJa;TelesklavFa</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;Huber rRe;LehnerMo;EislCh;StrimitzerDa</t>
+    <t>Eisarena Salzburg;LehnerMo;OrelSt;EislCh;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;DivisDo;SeewaldJe</t>
@@ -955,7 +955,10 @@
     <t>Eishalle Gröden;MoschenAn;VirtaTu;FleischmannLu;FormaioniTh</t>
   </si>
   <si>
-    <t>Eishalle Cortina;LebenJa;PinieOm;IlmerNo;JeramFi</t>
+    <t>Eishalle Meran;BenvegnuAn;RuetzMa;CusinFe;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;LebenJa;PinieOm;CristeliMa;JeramFi</t>
   </si>
   <si>
     <t>vse delegirane tekme</t>
@@ -3192,10 +3195,10 @@
         <v>91</v>
       </c>
       <c r="BG6" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="BH6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BJ6" s="8" t="s">
         <v>91</v>
@@ -3216,7 +3219,7 @@
         <v>94</v>
       </c>
       <c r="BQ6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
@@ -3287,7 +3290,7 @@
         <v>84</v>
       </c>
       <c r="X7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y7" t="s">
         <v>80</v>
@@ -3326,7 +3329,7 @@
         <v>106</v>
       </c>
       <c r="AK7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AL7" t="s">
         <v>90</v>
@@ -3395,16 +3398,16 @@
         <v>94</v>
       </c>
       <c r="BH7" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BJ7" t="s">
         <v>102</v>
       </c>
       <c r="BK7" t="s">
+        <v>115</v>
+      </c>
+      <c r="BM7" t="s">
         <v>114</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>113</v>
       </c>
       <c r="BN7" t="s">
         <v>107</v>
@@ -3413,7 +3416,7 @@
         <v>94</v>
       </c>
       <c r="BP7" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -3443,13 +3446,13 @@
         <v>88</v>
       </c>
       <c r="J8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K8" t="s">
         <v>77</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s">
         <v>82</v>
@@ -3482,7 +3485,7 @@
         <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y8" t="s">
         <v>79</v>
@@ -3512,7 +3515,7 @@
         <v>89</v>
       </c>
       <c r="AH8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AI8" t="s">
         <v>103</v>
@@ -3521,7 +3524,7 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL8" t="s">
         <v>88</v>
@@ -3557,7 +3560,7 @@
         <v>90</v>
       </c>
       <c r="AW8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AX8" t="s">
         <v>79</v>
@@ -3575,19 +3578,19 @@
         <v>90</v>
       </c>
       <c r="BC8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BD8" t="s">
         <v>88</v>
       </c>
       <c r="BE8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BF8" t="s">
         <v>95</v>
       </c>
       <c r="BG8" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BH8" s="7" t="s">
         <v>92</v>
@@ -3596,13 +3599,13 @@
         <v>94</v>
       </c>
       <c r="BK8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BM8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BN8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BO8" s="7" t="s">
         <v>104</v>
@@ -3628,19 +3631,19 @@
         <v>82</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>100</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>104</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L9" t="s">
         <v>106</v>
@@ -3682,16 +3685,16 @@
         <v>93</v>
       </c>
       <c r="AA9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC9" t="s">
         <v>90</v>
       </c>
       <c r="AD9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AE9" s="8" t="s">
         <v>91</v>
@@ -3703,13 +3706,13 @@
         <v>88</v>
       </c>
       <c r="AH9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AI9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK9" t="s">
         <v>106</v>
@@ -3745,7 +3748,7 @@
         <v>100</v>
       </c>
       <c r="AV9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW9" t="s">
         <v>89</v>
@@ -3772,31 +3775,31 @@
         <v>102</v>
       </c>
       <c r="BE9" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BF9" t="s">
         <v>94</v>
       </c>
       <c r="BH9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BJ9" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BK9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BM9" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BN9" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BO9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BP9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -3804,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>95</v>
@@ -3825,16 +3828,16 @@
         <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K10" t="s">
         <v>106</v>
       </c>
       <c r="L10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>102</v>
@@ -3867,7 +3870,7 @@
         <v>87</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA10" t="s">
         <v>106</v>
@@ -3882,7 +3885,7 @@
         <v>106</v>
       </c>
       <c r="AE10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF10" t="s">
         <v>102</v>
@@ -3891,13 +3894,13 @@
         <v>91</v>
       </c>
       <c r="AH10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AJ10" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AK10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -3909,7 +3912,7 @@
         <v>100</v>
       </c>
       <c r="AO10" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="AP10" t="s">
         <v>91</v>
@@ -3954,7 +3957,7 @@
         <v>106</v>
       </c>
       <c r="BD10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BF10" s="7"/>
       <c r="BJ10" t="s">
@@ -3967,7 +3970,7 @@
         <v>103</v>
       </c>
       <c r="BN10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -3975,10 +3978,10 @@
         <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
         <v>94</v>
@@ -3990,28 +3993,28 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>92</v>
       </c>
       <c r="J11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" t="s">
         <v>117</v>
-      </c>
-      <c r="K11" t="s">
-        <v>118</v>
-      </c>
-      <c r="L11" t="s">
-        <v>124</v>
-      </c>
-      <c r="N11" t="s">
-        <v>116</v>
       </c>
       <c r="O11" t="s">
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q11" t="s">
         <v>93</v>
@@ -4029,7 +4032,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4041,7 +4044,7 @@
         <v>107</v>
       </c>
       <c r="AA11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AB11" s="7" t="s">
         <v>104</v>
@@ -4065,7 +4068,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4083,7 +4086,7 @@
         <v>95</v>
       </c>
       <c r="AP11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AQ11" t="s">
         <v>106</v>
@@ -4104,7 +4107,7 @@
         <v>102</v>
       </c>
       <c r="AW11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AX11" t="s">
         <v>93</v>
@@ -4125,7 +4128,7 @@
         <v>91</v>
       </c>
       <c r="BD11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BJ11" t="s">
         <v>104</v>
@@ -4134,10 +4137,10 @@
         <v>104</v>
       </c>
       <c r="BM11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BN11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4157,25 +4160,25 @@
         <v>95</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P12" t="s">
         <v>106</v>
@@ -4184,16 +4187,16 @@
         <v>107</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" s="8" t="s">
         <v>107</v>
       </c>
       <c r="T12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>106</v>
@@ -4202,31 +4205,31 @@
         <v>100</v>
       </c>
       <c r="Y12" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="Z12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA12" s="7" t="s">
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AC12" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD12" t="s">
         <v>88</v>
       </c>
       <c r="AE12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG12" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>104</v>
@@ -4253,19 +4256,19 @@
         <v>107</v>
       </c>
       <c r="AQ12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AR12" t="s">
         <v>102</v>
       </c>
       <c r="AS12" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AT12" s="8" t="s">
         <v>100</v>
       </c>
       <c r="AU12" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AV12" t="s">
         <v>94</v>
@@ -4274,7 +4277,7 @@
         <v>100</v>
       </c>
       <c r="AX12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4295,10 +4298,10 @@
         <v>103</v>
       </c>
       <c r="BK12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BM12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -4309,43 +4312,43 @@
         <v>103</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
         <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O13" t="s">
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S13" t="s">
         <v>95</v>
@@ -4357,10 +4360,10 @@
         <v>94</v>
       </c>
       <c r="V13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y13" t="s">
         <v>95</v>
@@ -4372,28 +4375,28 @@
         <v>104</v>
       </c>
       <c r="AB13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AC13" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="AF13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AG13" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK13" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL13" t="s">
         <v>127</v>
@@ -4405,13 +4408,13 @@
         <v>94</v>
       </c>
       <c r="AO13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP13" s="7" t="s">
         <v>92</v>
       </c>
       <c r="AQ13" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AR13" t="s">
         <v>106</v>
@@ -4420,7 +4423,7 @@
         <v>127</v>
       </c>
       <c r="AT13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AV13" t="s">
         <v>106</v>
@@ -4429,60 +4432,60 @@
         <v>92</v>
       </c>
       <c r="AX13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AY13" t="s">
         <v>94</v>
       </c>
       <c r="AZ13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BA13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BB13" t="s">
         <v>102</v>
       </c>
       <c r="BC13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK13" t="s">
         <v>122</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>122</v>
-      </c>
-      <c r="BK13" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N14" t="s">
         <v>111</v>
-      </c>
-      <c r="B14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" t="s">
-        <v>117</v>
-      </c>
-      <c r="N14" t="s">
-        <v>110</v>
       </c>
       <c r="O14" t="s">
         <v>90</v>
@@ -4494,10 +4497,10 @@
         <v>94</v>
       </c>
       <c r="R14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T14" s="7" t="s">
         <v>104</v>
@@ -4506,31 +4509,34 @@
         <v>93</v>
       </c>
       <c r="V14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W14" t="s">
         <v>106</v>
       </c>
       <c r="Y14" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="Z14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>117</v>
       </c>
       <c r="AC14" t="s">
         <v>103</v>
       </c>
       <c r="AD14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF14" t="s">
         <v>122</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>121</v>
       </c>
       <c r="AG14" t="s">
         <v>103</v>
@@ -4545,25 +4551,25 @@
         <v>92</v>
       </c>
       <c r="AN14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AO14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AP14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AQ14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
       </c>
       <c r="AT14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AV14" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AW14" t="s">
         <v>103</v>
@@ -4575,90 +4581,96 @@
         <v>104</v>
       </c>
       <c r="AZ14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BA14" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BB14" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
         <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P15" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q15" t="s">
         <v>119</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" t="s">
         <v>119</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>118</v>
-      </c>
-      <c r="R15" t="s">
-        <v>118</v>
       </c>
       <c r="S15" t="s">
         <v>106</v>
       </c>
       <c r="T15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U15" t="s">
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AC15" t="s">
         <v>127</v>
       </c>
       <c r="AD15" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>111</v>
       </c>
       <c r="AG15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AN15" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AO15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AP15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AR15" s="7" t="s">
         <v>104</v>
@@ -4667,16 +4679,16 @@
         <v>107</v>
       </c>
       <c r="AV15" t="s">
+        <v>112</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX15" t="s">
         <v>111</v>
       </c>
-      <c r="AW15" t="s">
-        <v>121</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>110</v>
-      </c>
       <c r="AY15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AZ15" s="7" t="s">
         <v>104</v>
@@ -4690,25 +4702,25 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>103</v>
       </c>
       <c r="O16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>92</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T16" t="s">
         <v>127</v>
@@ -4720,16 +4732,19 @@
         <v>104</v>
       </c>
       <c r="Y16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA16" t="s">
         <v>122</v>
       </c>
-      <c r="Z16" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>121</v>
+      <c r="AC16" t="s">
+        <v>92</v>
       </c>
       <c r="AK16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AM16" t="s">
         <v>127</v>
@@ -4737,23 +4752,29 @@
       <c r="AN16" t="s">
         <v>128</v>
       </c>
+      <c r="AO16" t="s">
+        <v>118</v>
+      </c>
       <c r="AR16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AT16" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AV16" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>91</v>
       </c>
       <c r="AX16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AY16" t="s">
         <v>128</v>
       </c>
       <c r="AZ16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BA16" t="s">
         <v>127</v>
@@ -4767,16 +4788,16 @@
         <v>127</v>
       </c>
       <c r="O17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
@@ -4785,77 +4806,86 @@
         <v>103</v>
       </c>
       <c r="W17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Y17" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Z17" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>122</v>
       </c>
       <c r="AM17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AR17" t="s">
         <v>128</v>
       </c>
       <c r="AT17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AY17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AZ17" t="s">
         <v>128</v>
       </c>
       <c r="BB17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>123</v>
+      </c>
       <c r="Q18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R18" t="s">
         <v>103</v>
       </c>
       <c r="S18" t="s">
+        <v>112</v>
+      </c>
+      <c r="U18" t="s">
+        <v>112</v>
+      </c>
+      <c r="W18" t="s">
         <v>111</v>
       </c>
-      <c r="U18" t="s">
-        <v>111</v>
-      </c>
-      <c r="W18" t="s">
-        <v>110</v>
-      </c>
       <c r="AR18" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="AT18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AZ18" t="s">
         <v>122</v>
       </c>
-      <c r="AZ18" t="s">
-        <v>121</v>
-      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="17:52" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="16:52" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R19" t="s">
         <v>127</v>
       </c>
       <c r="S19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U19" t="s">
         <v>127</v>
       </c>
+      <c r="AR19" t="s">
+        <v>91</v>
+      </c>
       <c r="AT19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
@@ -5037,7 +5067,7 @@
         <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y3" t="s">
         <v>88</v>
@@ -5052,7 +5082,7 @@
         <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD3" t="s">
         <v>91</v>
@@ -5064,40 +5094,40 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AI3" t="s">
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AM3" t="s">
         <v>106</v>
       </c>
       <c r="AN3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AO3" t="s">
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AQ3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AR3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AS3" t="s">
         <v>92</v>
@@ -5106,31 +5136,31 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
       </c>
       <c r="AW3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
         <v>128</v>
       </c>
       <c r="AZ3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BA3" t="s">
         <v>127</v>
       </c>
       <c r="BB3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BC3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
@@ -5294,7 +5324,7 @@
         <v>56</v>
       </c>
       <c r="BB4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="BC4" t="s">
         <v>11</v>
@@ -5982,7 +6012,7 @@
         <v>49</v>
       </c>
       <c r="AL9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AM9" t="s">
         <v>47</v>
@@ -6496,7 +6526,7 @@
         <v>57</v>
       </c>
       <c r="AD14" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AE14" t="s">
         <v>52</v>
@@ -6526,7 +6556,7 @@
         <v>32</v>
       </c>
       <c r="AV14" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="AW14" t="s">
         <v>23</v>
@@ -6535,7 +6565,7 @@
         <v>15</v>
       </c>
       <c r="AZ14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="s">
         <v>32</v>
@@ -6624,7 +6654,7 @@
         <v>25</v>
       </c>
       <c r="AV15" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="AW15" t="s">
         <v>53</v>
@@ -6725,7 +6755,7 @@
         <v>5</v>
       </c>
       <c r="AW16" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AX16" t="s">
         <v>31</v>
@@ -6817,7 +6847,7 @@
         <v>24</v>
       </c>
       <c r="AW17" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="s">
         <v>33</v>
@@ -6897,7 +6927,7 @@
         <v>69</v>
       </c>
       <c r="AS18" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AT18" t="s">
         <v>57</v>
@@ -6909,7 +6939,7 @@
         <v>40</v>
       </c>
       <c r="AW18" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="AX18" t="s">
         <v>40</v>
@@ -6989,7 +7019,7 @@
         <v>27</v>
       </c>
       <c r="AS19" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="s">
         <v>66</v>
@@ -7001,7 +7031,7 @@
         <v>8</v>
       </c>
       <c r="AW19" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX19" t="s">
         <v>27</v>
@@ -7048,7 +7078,7 @@
         <v>26</v>
       </c>
       <c r="AD20" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="AE20" t="s">
         <v>56</v>
@@ -7072,7 +7102,7 @@
         <v>33</v>
       </c>
       <c r="AW20" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="AZ20" t="s">
         <v>34</v>
@@ -7116,7 +7146,7 @@
         <v>54</v>
       </c>
       <c r="AD21" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="AE21" t="s">
         <v>41</v>
@@ -7140,7 +7170,7 @@
         <v>26</v>
       </c>
       <c r="AW21" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="AZ21" t="s">
         <v>45</v>
@@ -7208,7 +7238,7 @@
         <v>19</v>
       </c>
       <c r="AW22" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AZ22" t="s">
         <v>22</v>
@@ -7276,7 +7306,7 @@
         <v>20</v>
       </c>
       <c r="AW23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="s">
         <v>57</v>
@@ -7360,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="BC26" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
@@ -7389,7 +7419,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="30:55" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="31:55" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7565,7 +7595,7 @@
         <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y3" t="s">
         <v>88</v>
@@ -7580,7 +7610,7 @@
         <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD3" t="s">
         <v>91</v>
@@ -7592,40 +7622,40 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AI3" t="s">
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AM3" t="s">
         <v>106</v>
       </c>
       <c r="AN3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AO3" t="s">
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AQ3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AR3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AS3" t="s">
         <v>92</v>
@@ -7634,31 +7664,31 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
       </c>
       <c r="AW3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
         <v>128</v>
       </c>
       <c r="AZ3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BA3" t="s">
         <v>127</v>
       </c>
       <c r="BB3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BC3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
@@ -8221,11 +8251,14 @@
       <c r="AT9" t="s">
         <v>311</v>
       </c>
+      <c r="AW9" t="s">
+        <v>312</v>
+      </c>
       <c r="BC9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="30:55" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="31:55" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8258,7 +8291,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11">
@@ -8268,7 +8301,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14">
@@ -8278,14 +8311,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B3" s="16">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>738</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -8293,35 +8326,35 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B4" s="19">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8333,7 +8366,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F5" s="21">
         <v>2</v>
@@ -8411,7 +8444,7 @@
         <v>312</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F7" s="30">
         <v>3</v>
@@ -8443,7 +8476,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E8" s="33" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F8" s="34">
         <v>6</v>
@@ -8475,14 +8508,14 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>738</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F9" s="34">
         <v>4</v>
@@ -8514,7 +8547,7 @@
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="38" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I11" s="39">
         <f>SUM(I7:I9)</f>
@@ -8535,33 +8568,33 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I16" s="42" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F17" s="44">
         <v>3</v>
@@ -8593,7 +8626,7 @@
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="50" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F18" s="51">
         <v>6</v>
@@ -8626,7 +8659,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="58" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F19" s="59">
         <v>4</v>
@@ -8660,7 +8693,7 @@
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="P24" s="65" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q24" s="65"/>
       <c r="R24" s="65"/>
@@ -8669,18 +8702,18 @@
     <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P25" s="66"/>
       <c r="Q25" s="67" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R25" s="68" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S25" s="69" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P26" s="70" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q26" s="33">
         <v>247</v>
@@ -8695,7 +8728,7 @@
     </row>
     <row r="27" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P27" s="70" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q27" s="33">
         <v>124</v>
@@ -8710,7 +8743,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P28" s="71" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q28" s="72">
         <v>165</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="334">
   <si>
     <t>sl</t>
   </si>
@@ -346,9 +346,6 @@
     <t>2024-10-06</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2024-11-02</t>
   </si>
   <si>
@@ -361,6 +358,9 @@
     <t>2024-11-17</t>
   </si>
   <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
     <t>2024-11-21</t>
   </si>
   <si>
@@ -379,9 +379,6 @@
     <t>2024-12-05</t>
   </si>
   <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
     <t>2024-11-19</t>
   </si>
   <si>
@@ -499,13 +496,13 @@
     <t>Eishalle Jesenice;BrockAd;SnojTa;ArlicMa;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Celje;HlavatyAl;WidmannFl;LegatKo;WuchererGe</t>
+    <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CusinFe</t>
   </si>
   <si>
     <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;LazzeriAl;RivisFe;RinkerDa;StrimitzerDa</t>
+    <t>Eishalle Dornbirn;Huber rRe;RivisFe;RinkerDa;StrimitzerDa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;HolzerTo;RuetzMa;JägerRi;SeewaldJe</t>
@@ -523,7 +520,7 @@
     <t>Kitzbühel Sportpark;BenvegnuAn;LazzeriAl;RinkerDa;SeewaldJe</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;BrockAd;MeixnerSe;LegatKo;ZacherlPa</t>
+    <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
@@ -625,7 +622,7 @@
     <t>Eishalle Ritten;EggerTh;PinieOm;PaceJa;ScalzeriAl</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;GiacomozziFe;SoraperraSi;AbeltinoSi;CusinFe</t>
+    <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WendnerMa</t>
   </si>
   <si>
     <t>Eishalle Ritten;RuetzMa;SpiegelSe;EislCh;JägerRi</t>
@@ -661,7 +658,7 @@
     <t>Eishalle Celje;BulovecMi;HlavatyAl;LegatKo;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Zell am See;HlavatyAl;UnterwegerDo;PreiserJu;SeewaldJe</t>
+    <t>Eishalle Dornbirn;HolzerTo;LegaSi;DivisDo;JägerRi</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;EggerTh;StefenelliFe;FecchioFe;PaceJa</t>
@@ -673,10 +670,10 @@
     <t>KELIT Arena Zell am See;LehnerMo;MoidlDa;SeewaldJe;ZacherlPa</t>
   </si>
   <si>
-    <t>Eishalle Gröden;BulovecMi;LazzeriAl;MarkizetiGr;PaceJa</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;BajtMi;BenvegnuAn;CristeliMa;JavornikBl</t>
+    <t>Eishalle Gröden;BenvegnuAn;LazzeriAl;CristeliMa;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BajtMi;BulovecMi;JavornikBl;MarkizetiGr</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
@@ -730,7 +727,7 @@
     <t>Eishalle Celje;VoicanCh;WidmannFl;PreiserJu;WuchererGe</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;MoschenAn;PinieOm;PreiserJu;WendnerMa</t>
+    <t>Eishalle Meran;LesniakBo;OrelSt;MarkizetiGr;TelesklavFa</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;BulovecMi;SnojTa;JeramFi;MarkizetiGr</t>
@@ -757,10 +754,10 @@
     <t>Eishalle Meran;LazzeriAl;StefenelliFe;AbeltinoSi;RivisAn</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;HolzerTo;LegaSi;DivisDo;JägerRi</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;Huber rRe;VirtaTu;FormaioniTh;RinkerDa</t>
+    <t>Eishalle Cortina;BajtMi;MoschenAn;CristeliMa;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;LazzeriAl;VirtaTu;FormaioniTh;RinkerDa</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;MetzingerFi;VoicanCh;KnezRo;LegatKo</t>
@@ -826,7 +823,7 @@
     <t>Eishalle Sissek Zibel;BajtMi;RivisFe;JavornikBl;RivisAn</t>
   </si>
   <si>
-    <t>Eishalle Meran;LesniakBo;OrelSt;MarkizetiGr;TelesklavFa</t>
+    <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;DivisDo;SeewaldJe</t>
   </si>
   <si>
     <t>Eishalle Sterzing;Huber rRe;RivisFe;FecchioFe;RivisAn</t>
@@ -841,7 +838,7 @@
     <t>Eishalle Ritten;EggerTh;LazzeriAl;GrisentiLu;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Meran;KainbergerJu;LehnerMo;EislCh;FleischmannLu</t>
+    <t>Eishalle Meran;GiacomozziFe;KainbergerJu;EislCh;FleischmannLu</t>
   </si>
   <si>
     <t>Eishalle Sterzing;Huber rRe;SpiegelSe;AbeltinoSi;GrisentiLu</t>
@@ -853,10 +850,10 @@
     <t>Eishalle Cortina;GiacomozziFe;PinieOm;CristeliMa;CusinFe</t>
   </si>
   <si>
-    <t>Eishalle Cortina;BajtMi;MoschenAn;CristeliMa;MarkizetiGr</t>
-  </si>
-  <si>
-    <t>ZBRISANO</t>
+    <t>Eishalle Zell am See;HlavatyAl;UnterwegerDo;LegatKo;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;RivisFe;SoraperraSi;GrisentiLu;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Cortina;GiacomozziFe;PirasAn;CristeliMa;FleischmannLu</t>
@@ -904,7 +901,7 @@
     <t>Eisarena Salzburg;LehnerMo;OrelSt;EislCh;StrimitzerDa</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;DivisDo;SeewaldJe</t>
+    <t>KELIT Arena Zell am See;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
   </si>
   <si>
     <t>Eishalle Cortina;GiacomozziFe;SoraperraSi;BrondiPa;FormaioniTh</t>
@@ -916,7 +913,7 @@
     <t>Eishalle Cortina;LegaSi;VirtaTu;CristeliMa;RivisAn</t>
   </si>
   <si>
-    <t>Eishalle Gröden;GiacomozziFe;MoidlDa;MattheyPh;MoidlMa</t>
+    <t>Eishalle Gröden;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;BajtMi;HolzerTo;JavornikBl;StrimitzerDa</t>
@@ -925,7 +922,7 @@
     <t>Eishalle Gröden;PirasAn;VirtaTu;FecchioFe;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Cortina;RivisFe;SoraperraSi;GrisentiLu;ScalzeriAl</t>
+    <t>Eishalle Meran;BenvegnuAn;RuetzMa;CusinFe;RivisAn</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;RivisFe;SpiegelSe;BrondiPa;DivisDo</t>
@@ -943,7 +940,7 @@
     <t>Eishalle Dornbirn;HolzerTo;SpiegelSe;MattheyPh;MoidlMa</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
+    <t>Eishalle Celje;HlavatyAl;WidmannFl;ArlicMa;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Gröden;PirasAn;SoraperraSi;FormaioniTh;ScalzeriAl</t>
@@ -953,9 +950,6 @@
   </si>
   <si>
     <t>Eishalle Gröden;MoschenAn;VirtaTu;FleischmannLu;FormaioniTh</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;BenvegnuAn;RuetzMa;CusinFe;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Cortina;LebenJa;PinieOm;CristeliMa;JeramFi</t>
@@ -1924,15 +1918,15 @@
         <v>11</v>
       </c>
       <c r="C1">
-        <f t="shared" ref="C1:BF1" si="0">COUNTIF(C4:C70,"&lt;&gt;")</f>
+        <f>COUNTIF(C4:C69,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1">
-        <f>COUNTIF(E4:E68,"&lt;&gt;")</f>
+        <f>COUNTIF(E4:E67,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="F1">
@@ -1968,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="N1">
-        <f>COUNTIF(N4:N69,"&lt;&gt;")</f>
+        <f>COUNTIF(N4:N68,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="O1">
@@ -1976,15 +1970,15 @@
         <v>14</v>
       </c>
       <c r="P1">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f t="shared" ref="P1:BF1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q68,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R67,"&lt;&gt;")</f>
+        <f>COUNTIF(R4:R66,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="S1">
@@ -2012,8 +2006,8 @@
         <v>5</v>
       </c>
       <c r="Y1">
-        <f>COUNTIF(Y4:Y69,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(Y4:Y68,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
@@ -2025,11 +2019,11 @@
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD69,"&lt;&gt;")</f>
@@ -2040,12 +2034,12 @@
         <v>11</v>
       </c>
       <c r="AF1">
-        <f>COUNTIF(AF4:AF65,"&lt;&gt;")</f>
+        <f>COUNTIF(AF4:AF64,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AG1">
-        <f>COUNTIF(AG4:AG69,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AG4:AG68,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
@@ -2060,8 +2054,8 @@
         <v>9</v>
       </c>
       <c r="AK1">
-        <f>COUNTIF(AK4:AK66,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(AK4:AK65,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL68,"&lt;&gt;")</f>
@@ -2076,7 +2070,7 @@
         <v>13</v>
       </c>
       <c r="AO1">
-        <f>COUNTIF(AO4:AO69,"&lt;&gt;")</f>
+        <f>COUNTIF(AO4:AO67,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="AP1">
@@ -2088,7 +2082,7 @@
         <v>11</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR64,"&lt;&gt;")</f>
+        <f>COUNTIF(AR4:AR63,"&lt;&gt;")</f>
         <v>15</v>
       </c>
       <c r="AS1">
@@ -2104,12 +2098,12 @@
         <v>9</v>
       </c>
       <c r="AV1">
-        <f>COUNTIF(AV4:AV67,"&lt;&gt;")</f>
+        <f>COUNTIF(AV4:AV65,"&lt;&gt;")</f>
+        <v>12</v>
+      </c>
+      <c r="AW1">
+        <f>COUNTIF(AW4:AW66,"&lt;&gt;")</f>
         <v>13</v>
-      </c>
-      <c r="AW1">
-        <f>COUNTIF(AW4:AW67,"&lt;&gt;")</f>
-        <v>12</v>
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
@@ -2148,8 +2142,8 @@
         <v>6</v>
       </c>
       <c r="BG1">
-        <f>COUNTIF(BG4:BG68,"&lt;&gt;")</f>
-        <v>5</v>
+        <f>COUNTIF(BG4:BG67,"&lt;&gt;")</f>
+        <v>4</v>
       </c>
       <c r="BH1">
         <f t="shared" ref="BH1:BQ1" si="1">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
@@ -2164,7 +2158,7 @@
         <v>8</v>
       </c>
       <c r="BK1">
-        <f>COUNTIF(BK4:BK66,"&lt;&gt;")</f>
+        <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
         <v>10</v>
       </c>
       <c r="BL1">
@@ -3195,10 +3189,10 @@
         <v>91</v>
       </c>
       <c r="BG6" t="s">
+        <v>94</v>
+      </c>
+      <c r="BH6" t="s">
         <v>109</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>110</v>
       </c>
       <c r="BJ6" s="8" t="s">
         <v>91</v>
@@ -3219,7 +3213,7 @@
         <v>94</v>
       </c>
       <c r="BQ6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
@@ -3290,7 +3284,7 @@
         <v>84</v>
       </c>
       <c r="X7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Y7" t="s">
         <v>80</v>
@@ -3329,7 +3323,7 @@
         <v>106</v>
       </c>
       <c r="AK7" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AL7" t="s">
         <v>90</v>
@@ -3394,8 +3388,8 @@
       <c r="BF7" t="s">
         <v>102</v>
       </c>
-      <c r="BG7" t="s">
-        <v>94</v>
+      <c r="BG7" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="BH7" s="8" t="s">
         <v>114</v>
@@ -3452,7 +3446,7 @@
         <v>77</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s">
         <v>82</v>
@@ -3560,7 +3554,7 @@
         <v>90</v>
       </c>
       <c r="AW8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AX8" t="s">
         <v>79</v>
@@ -3578,7 +3572,7 @@
         <v>90</v>
       </c>
       <c r="BC8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BD8" t="s">
         <v>88</v>
@@ -3589,9 +3583,6 @@
       <c r="BF8" t="s">
         <v>95</v>
       </c>
-      <c r="BG8" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="BH8" s="7" t="s">
         <v>92</v>
       </c>
@@ -3599,7 +3590,7 @@
         <v>94</v>
       </c>
       <c r="BK8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM8" t="s">
         <v>119</v>
@@ -3643,7 +3634,7 @@
         <v>104</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s">
         <v>106</v>
@@ -3709,7 +3700,7 @@
         <v>117</v>
       </c>
       <c r="AI9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AJ9" t="s">
         <v>119</v>
@@ -3748,7 +3739,7 @@
         <v>100</v>
       </c>
       <c r="AV9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AW9" t="s">
         <v>89</v>
@@ -3775,13 +3766,13 @@
         <v>102</v>
       </c>
       <c r="BE9" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BF9" t="s">
         <v>94</v>
       </c>
       <c r="BH9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BJ9" s="7" t="s">
         <v>116</v>
@@ -3790,16 +3781,16 @@
         <v>114</v>
       </c>
       <c r="BM9" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="BN9" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BO9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BP9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -3828,7 +3819,7 @@
         <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K10" t="s">
         <v>106</v>
@@ -3837,7 +3828,7 @@
         <v>119</v>
       </c>
       <c r="N10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>102</v>
@@ -3870,7 +3861,7 @@
         <v>87</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AA10" t="s">
         <v>106</v>
@@ -3885,7 +3876,7 @@
         <v>106</v>
       </c>
       <c r="AE10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AF10" t="s">
         <v>102</v>
@@ -3900,7 +3891,7 @@
         <v>104</v>
       </c>
       <c r="AK10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -3912,7 +3903,7 @@
         <v>100</v>
       </c>
       <c r="AO10" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AP10" t="s">
         <v>91</v>
@@ -3970,7 +3961,7 @@
         <v>103</v>
       </c>
       <c r="BN10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -3993,7 +3984,7 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>92</v>
@@ -4005,7 +3996,7 @@
         <v>119</v>
       </c>
       <c r="L11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N11" t="s">
         <v>117</v>
@@ -4032,7 +4023,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4068,7 +4059,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4082,8 +4073,8 @@
       <c r="AN11" t="s">
         <v>91</v>
       </c>
-      <c r="AO11" t="s">
-        <v>95</v>
+      <c r="AO11" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="AP11" t="s">
         <v>114</v>
@@ -4104,7 +4095,7 @@
         <v>94</v>
       </c>
       <c r="AV11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AW11" t="s">
         <v>119</v>
@@ -4137,10 +4128,10 @@
         <v>104</v>
       </c>
       <c r="BM11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BN11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4160,19 +4151,19 @@
         <v>95</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N12" t="s">
         <v>119</v>
@@ -4186,8 +4177,8 @@
       <c r="Q12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="R12" s="8" t="s">
-        <v>124</v>
+      <c r="R12" t="s">
+        <v>120</v>
       </c>
       <c r="S12" s="8" t="s">
         <v>107</v>
@@ -4205,7 +4196,7 @@
         <v>100</v>
       </c>
       <c r="Y12" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="Z12" t="s">
         <v>114</v>
@@ -4214,7 +4205,7 @@
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AC12" s="7" t="s">
         <v>116</v>
@@ -4223,19 +4214,19 @@
         <v>88</v>
       </c>
       <c r="AE12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>109</v>
+        <v>113</v>
+      </c>
+      <c r="AG12" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AJ12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AK12" t="s">
         <v>95</v>
@@ -4249,8 +4240,8 @@
       <c r="AN12" t="s">
         <v>102</v>
       </c>
-      <c r="AO12" s="7" t="s">
-        <v>92</v>
+      <c r="AO12" t="s">
+        <v>122</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4268,16 +4259,16 @@
         <v>100</v>
       </c>
       <c r="AU12" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>94</v>
+        <v>111</v>
+      </c>
+      <c r="AV12" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="AW12" t="s">
         <v>100</v>
       </c>
       <c r="AX12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4298,10 +4289,10 @@
         <v>103</v>
       </c>
       <c r="BK12" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="BM12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -4315,28 +4306,28 @@
         <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>106</v>
       </c>
       <c r="F13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I13" t="s">
         <v>122</v>
       </c>
-      <c r="H13" t="s">
+      <c r="K13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I13" t="s">
-        <v>123</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="L13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="O13" t="s">
         <v>94</v>
@@ -4348,7 +4339,7 @@
         <v>114</v>
       </c>
       <c r="R13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="S13" t="s">
         <v>95</v>
@@ -4360,14 +4351,11 @@
         <v>94</v>
       </c>
       <c r="V13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="W13" t="s">
         <v>114</v>
       </c>
-      <c r="Y13" t="s">
-        <v>95</v>
-      </c>
       <c r="Z13" t="s">
         <v>106</v>
       </c>
@@ -4375,31 +4363,31 @@
         <v>104</v>
       </c>
       <c r="AB13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AC13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AD13" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AE13" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG13" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>103</v>
       </c>
       <c r="AH13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK13" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AL13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4408,7 +4396,7 @@
         <v>94</v>
       </c>
       <c r="AO13" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="AP13" s="7" t="s">
         <v>92</v>
@@ -4420,13 +4408,13 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AT13" t="s">
         <v>115</v>
       </c>
       <c r="AV13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="AW13" s="7" t="s">
         <v>92</v>
@@ -4447,36 +4435,36 @@
         <v>102</v>
       </c>
       <c r="BC13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BD13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BK13" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
         <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>119</v>
       </c>
       <c r="H14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K14" t="s">
         <v>118</v>
@@ -4485,7 +4473,7 @@
         <v>118</v>
       </c>
       <c r="N14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O14" t="s">
         <v>90</v>
@@ -4497,7 +4485,7 @@
         <v>94</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S14" t="s">
         <v>114</v>
@@ -4509,19 +4497,16 @@
         <v>93</v>
       </c>
       <c r="V14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W14" t="s">
         <v>106</v>
       </c>
-      <c r="Y14" t="s">
-        <v>109</v>
-      </c>
       <c r="Z14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AB14" t="s">
         <v>117</v>
@@ -4530,19 +4515,19 @@
         <v>103</v>
       </c>
       <c r="AD14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AE14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AF14" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="AG14" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="AH14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
@@ -4554,10 +4539,10 @@
         <v>114</v>
       </c>
       <c r="AO14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AP14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AQ14" t="s">
         <v>118</v>
@@ -4568,11 +4553,11 @@
       <c r="AT14" t="s">
         <v>114</v>
       </c>
-      <c r="AV14" s="7" t="s">
-        <v>120</v>
+      <c r="AV14" t="s">
+        <v>118</v>
       </c>
       <c r="AW14" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="AX14" s="7" t="s">
         <v>92</v>
@@ -4581,51 +4566,48 @@
         <v>104</v>
       </c>
       <c r="AZ14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BA14" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BB14" t="s">
-        <v>121</v>
-      </c>
-      <c r="BK14" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" t="s">
-        <v>111</v>
+        <v>118</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="P15" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="s">
         <v>119</v>
       </c>
-      <c r="R15" t="s">
-        <v>119</v>
+      <c r="R15" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="S15" t="s">
         <v>106</v>
       </c>
       <c r="T15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U15" t="s">
         <v>100</v>
@@ -4636,41 +4618,32 @@
       <c r="W15" t="s">
         <v>119</v>
       </c>
-      <c r="Y15" s="7" t="s">
-        <v>109</v>
-      </c>
       <c r="Z15" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AA15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AD15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK15" t="s">
         <v>111</v>
       </c>
-      <c r="AG15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>112</v>
-      </c>
       <c r="AM15" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AN15" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AO15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AP15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AR15" s="7" t="s">
         <v>104</v>
@@ -4679,16 +4652,16 @@
         <v>107</v>
       </c>
       <c r="AV15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="AW15" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="AX15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY15" t="s">
         <v>111</v>
-      </c>
-      <c r="AY15" t="s">
-        <v>112</v>
       </c>
       <c r="AZ15" s="7" t="s">
         <v>104</v>
@@ -4702,28 +4675,28 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>103</v>
       </c>
       <c r="O16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="R16" s="7" t="s">
-        <v>116</v>
+      <c r="R16" t="s">
+        <v>113</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="T16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U16" s="7" t="s">
         <v>104</v>
@@ -4731,73 +4704,67 @@
       <c r="W16" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="Y16" t="s">
-        <v>109</v>
-      </c>
       <c r="Z16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AA16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AC16" t="s">
         <v>92</v>
       </c>
       <c r="AK16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM16" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN16" t="s">
         <v>127</v>
       </c>
-      <c r="AN16" t="s">
-        <v>128</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>118</v>
-      </c>
       <c r="AR16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AT16" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AV16" t="s">
-        <v>118</v>
-      </c>
       <c r="AW16" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AX16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AY16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AZ16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BA16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>121</v>
+      </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="O17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q17" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="R17" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
@@ -4806,86 +4773,80 @@
         <v>103</v>
       </c>
       <c r="W17" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="Z17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>127</v>
+      </c>
+      <c r="BB17" t="s">
         <v>122</v>
       </c>
-      <c r="AK17" t="s">
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
         <v>122</v>
       </c>
-      <c r="AM17" t="s">
+      <c r="Q18" t="s">
+        <v>110</v>
+      </c>
+      <c r="R18" t="s">
+        <v>126</v>
+      </c>
+      <c r="S18" t="s">
+        <v>111</v>
+      </c>
+      <c r="U18" t="s">
+        <v>111</v>
+      </c>
+      <c r="W18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>91</v>
+      </c>
+      <c r="AT18" t="s">
         <v>122</v>
       </c>
-      <c r="AR17" t="s">
-        <v>128</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>111</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>122</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>128</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
-      <c r="P18" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>111</v>
-      </c>
-      <c r="R18" t="s">
-        <v>103</v>
-      </c>
-      <c r="S18" t="s">
-        <v>112</v>
-      </c>
-      <c r="U18" t="s">
-        <v>112</v>
-      </c>
-      <c r="W18" t="s">
-        <v>111</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>109</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>123</v>
-      </c>
       <c r="AZ18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="16:52" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
+        <v>121</v>
+      </c>
+      <c r="R19" t="s">
+        <v>110</v>
+      </c>
+      <c r="S19" t="s">
         <v>122</v>
       </c>
-      <c r="R19" t="s">
-        <v>127</v>
-      </c>
-      <c r="S19" t="s">
-        <v>123</v>
-      </c>
       <c r="U19" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="AT19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
@@ -5067,7 +5028,7 @@
         <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
         <v>88</v>
@@ -5082,7 +5043,7 @@
         <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AD3" t="s">
         <v>91</v>
@@ -5094,7 +5055,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AH3" t="s">
         <v>115</v>
@@ -5103,7 +5064,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="s">
         <v>114</v>
@@ -5121,10 +5082,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>125</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>126</v>
       </c>
       <c r="AR3" t="s">
         <v>116</v>
@@ -5136,31 +5097,31 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
       </c>
       <c r="AW3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="s">
         <v>111</v>
       </c>
-      <c r="AX3" t="s">
-        <v>112</v>
-      </c>
       <c r="AY3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AZ3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
@@ -5255,13 +5216,13 @@
         <v>58</v>
       </c>
       <c r="AE4" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="AF4" t="s">
         <v>39</v>
       </c>
       <c r="AG4" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -5422,7 +5383,7 @@
         <v>4</v>
       </c>
       <c r="AE5" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="s">
         <v>29</v>
@@ -5589,7 +5550,7 @@
         <v>7</v>
       </c>
       <c r="AE6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="s">
         <v>22</v>
@@ -5613,7 +5574,7 @@
         <v>53</v>
       </c>
       <c r="AM6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AN6" t="s">
         <v>52</v>
@@ -5756,7 +5717,7 @@
         <v>42</v>
       </c>
       <c r="AE7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="AF7" t="s">
         <v>20</v>
@@ -5836,7 +5797,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -5860,7 +5821,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -5887,7 +5848,7 @@
         <v>39</v>
       </c>
       <c r="AE8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="s">
         <v>49</v>
@@ -5923,7 +5884,7 @@
         <v>6</v>
       </c>
       <c r="AV8" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AW8" t="s">
         <v>39</v>
@@ -5935,7 +5896,7 @@
         <v>71</v>
       </c>
       <c r="BA8" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BB8" t="s">
         <v>5</v>
@@ -5958,7 +5919,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6000,7 +5961,7 @@
         <v>36</v>
       </c>
       <c r="AE9" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AF9" t="s">
         <v>45</v>
@@ -6036,7 +5997,7 @@
         <v>68</v>
       </c>
       <c r="AV9" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="AW9" t="s">
         <v>29</v>
@@ -6051,7 +6012,7 @@
         <v>21</v>
       </c>
       <c r="BB9" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="s">
         <v>38</v>
@@ -6113,7 +6074,7 @@
         <v>37</v>
       </c>
       <c r="AE10" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AF10" t="s">
         <v>69</v>
@@ -6149,7 +6110,7 @@
         <v>51</v>
       </c>
       <c r="AV10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AW10" t="s">
         <v>19</v>
@@ -6161,10 +6122,10 @@
         <v>59</v>
       </c>
       <c r="BA10" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="s">
         <v>35</v>
@@ -6226,7 +6187,7 @@
         <v>30</v>
       </c>
       <c r="AE11" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="s">
         <v>66</v>
@@ -6262,7 +6223,7 @@
         <v>42</v>
       </c>
       <c r="AV11" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AW11" t="s">
         <v>37</v>
@@ -6277,7 +6238,7 @@
         <v>37</v>
       </c>
       <c r="BB11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="s">
         <v>53</v>
@@ -6309,7 +6270,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -6333,7 +6294,7 @@
         <v>50</v>
       </c>
       <c r="AE12" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="s">
         <v>6</v>
@@ -6360,10 +6321,10 @@
         <v>21</v>
       </c>
       <c r="AV12" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="AW12" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="s">
         <v>14</v>
@@ -6431,7 +6392,7 @@
         <v>54</v>
       </c>
       <c r="AE13" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s">
         <v>4</v>
@@ -6458,7 +6419,7 @@
         <v>29</v>
       </c>
       <c r="AV13" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="s">
         <v>26</v>
@@ -6529,7 +6490,7 @@
         <v>52</v>
       </c>
       <c r="AE14" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="AI14" t="s">
         <v>12</v>
@@ -6556,7 +6517,7 @@
         <v>32</v>
       </c>
       <c r="AV14" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="AW14" t="s">
         <v>23</v>
@@ -6627,7 +6588,7 @@
         <v>43</v>
       </c>
       <c r="AE15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI15" t="s">
         <v>8</v>
@@ -6654,7 +6615,7 @@
         <v>25</v>
       </c>
       <c r="AV15" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="AW15" t="s">
         <v>53</v>
@@ -6725,7 +6686,7 @@
         <v>5</v>
       </c>
       <c r="AE16" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="AI16" t="s">
         <v>44</v>
@@ -6740,7 +6701,7 @@
         <v>39</v>
       </c>
       <c r="AO16" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AS16" t="s">
         <v>44</v>
@@ -6752,7 +6713,7 @@
         <v>31</v>
       </c>
       <c r="AV16" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="AW16" t="s">
         <v>34</v>
@@ -6817,7 +6778,7 @@
         <v>34</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="AI17" t="s">
         <v>34</v>
@@ -6832,7 +6793,7 @@
         <v>21</v>
       </c>
       <c r="AO17" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="AS17" t="s">
         <v>45</v>
@@ -6844,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="AV17" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="AW17" t="s">
         <v>18</v>
@@ -6909,7 +6870,7 @@
         <v>13</v>
       </c>
       <c r="AE18" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="AI18" t="s">
         <v>19</v>
@@ -6936,7 +6897,7 @@
         <v>40</v>
       </c>
       <c r="AV18" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AW18" t="s">
         <v>20</v>
@@ -7001,7 +6962,7 @@
         <v>25</v>
       </c>
       <c r="AE19" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="AI19" t="s">
         <v>25</v>
@@ -7028,7 +6989,7 @@
         <v>35</v>
       </c>
       <c r="AV19" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="AW19" t="s">
         <v>30</v>
@@ -7081,7 +7042,7 @@
         <v>71</v>
       </c>
       <c r="AE20" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AI20" t="s">
         <v>31</v>
@@ -7093,7 +7054,7 @@
         <v>38</v>
       </c>
       <c r="AO20" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="AT20" t="s">
         <v>5</v>
@@ -7149,7 +7110,7 @@
         <v>47</v>
       </c>
       <c r="AE21" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="AI21" t="s">
         <v>18</v>
@@ -7217,7 +7178,7 @@
         <v>69</v>
       </c>
       <c r="AE22" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AI22" t="s">
         <v>22</v>
@@ -7285,7 +7246,7 @@
         <v>55</v>
       </c>
       <c r="AE23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AI23" t="s">
         <v>23</v>
@@ -7326,7 +7287,7 @@
         <v>56</v>
       </c>
       <c r="AE24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AK24" t="s">
         <v>33</v>
@@ -7352,7 +7313,7 @@
         <v>45</v>
       </c>
       <c r="AE25" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="AK25" t="s">
         <v>18</v>
@@ -7378,7 +7339,7 @@
         <v>65</v>
       </c>
       <c r="AE26" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="AK26" t="s">
         <v>23</v>
@@ -7404,7 +7365,7 @@
         <v>61</v>
       </c>
       <c r="AE27" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AK27" t="s">
         <v>30</v>
@@ -7595,7 +7556,7 @@
         <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
         <v>88</v>
@@ -7610,7 +7571,7 @@
         <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AD3" t="s">
         <v>91</v>
@@ -7622,7 +7583,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AH3" t="s">
         <v>115</v>
@@ -7631,7 +7592,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="s">
         <v>114</v>
@@ -7649,10 +7610,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>125</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>126</v>
       </c>
       <c r="AR3" t="s">
         <v>116</v>
@@ -7664,598 +7625,595 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
       </c>
       <c r="AW3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="s">
         <v>111</v>
       </c>
-      <c r="AX3" t="s">
-        <v>112</v>
-      </c>
       <c r="AY3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AZ3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BA3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB3" t="s">
         <v>118</v>
       </c>
       <c r="BC3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
         <v>130</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>131</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>132</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>133</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>134</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>135</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>136</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>137</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>138</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>139</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>140</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>141</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>142</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>143</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>144</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>145</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>146</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>147</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>148</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>149</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>150</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>151</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>152</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>153</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>154</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>155</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>156</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>157</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>158</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>159</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>160</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>161</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>162</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>163</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>164</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>165</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>166</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>167</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>168</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>169</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>170</v>
       </c>
-      <c r="AP4" t="s">
-        <v>158</v>
-      </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>171</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>172</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>173</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>174</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>175</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>176</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>177</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>178</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>179</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>180</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>181</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>182</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" t="s">
         <v>184</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>185</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>186</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>187</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>188</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>189</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>190</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
         <v>191</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
         <v>192</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>193</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>194</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>195</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>196</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>197</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>198</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AB5" t="s">
         <v>199</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AD5" t="s">
         <v>200</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>201</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>202</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AI5" t="s">
         <v>203</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AK5" t="s">
         <v>204</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>205</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>206</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AN5" t="s">
         <v>207</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
         <v>208</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AR5" t="s">
         <v>209</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>210</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>211</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AU5" t="s">
         <v>212</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AV5" t="s">
         <v>213</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AW5" t="s">
         <v>214</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>215</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AZ5" t="s">
         <v>216</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>217</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BB5" t="s">
         <v>218</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BC5" t="s">
         <v>219</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" t="s">
         <v>221</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>222</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>223</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>224</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>225</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>226</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>227</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
         <v>228</v>
       </c>
-      <c r="P6" t="s">
+      <c r="T6" t="s">
         <v>229</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" t="s">
         <v>230</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>231</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Y6" t="s">
         <v>232</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>233</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
         <v>234</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AD6" t="s">
         <v>235</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>236</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AI6" t="s">
         <v>237</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AK6" t="s">
         <v>238</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AM6" t="s">
         <v>239</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AN6" t="s">
         <v>240</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>241</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AS6" t="s">
         <v>242</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
         <v>243</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU6" t="s">
         <v>244</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AV6" t="s">
         <v>245</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AW6" t="s">
         <v>246</v>
       </c>
-      <c r="AW6" t="s">
+      <c r="AX6" t="s">
         <v>247</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AZ6" t="s">
         <v>248</v>
       </c>
-      <c r="AZ6" t="s">
+      <c r="BA6" t="s">
         <v>249</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="BB6" t="s">
         <v>250</v>
       </c>
-      <c r="BB6" t="s">
+      <c r="BC6" t="s">
         <v>251</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D7" t="s">
         <v>253</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>254</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>255</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>256</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>257</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>258</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>259</v>
       </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>260</v>
       </c>
-      <c r="P7" t="s">
+      <c r="T7" t="s">
         <v>261</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>262</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>263</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>264</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>265</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AB7" t="s">
         <v>266</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>267</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>268</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AI7" t="s">
         <v>269</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AK7" t="s">
         <v>270</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AM7" t="s">
         <v>271</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AN7" t="s">
         <v>272</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>273</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AS7" t="s">
         <v>274</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AT7" t="s">
         <v>275</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AU7" t="s">
         <v>276</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>277</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>278</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>279</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AZ7" t="s">
         <v>280</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BC7" t="s">
         <v>281</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" t="s">
         <v>283</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>284</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>285</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>286</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>287</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>288</v>
       </c>
-      <c r="L8" t="s">
+      <c r="V8" t="s">
         <v>289</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>290</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y8" t="s">
         <v>291</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AB8" t="s">
         <v>292</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
         <v>293</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>294</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AI8" t="s">
         <v>295</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AK8" t="s">
         <v>296</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AM8" t="s">
         <v>297</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AO8" t="s">
         <v>298</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AT8" t="s">
         <v>299</v>
       </c>
-      <c r="AT8" t="s">
+      <c r="AU8" t="s">
         <v>300</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AW8" t="s">
         <v>301</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AZ8" t="s">
         <v>302</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BC8" t="s">
         <v>303</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
+        <v>304</v>
+      </c>
+      <c r="L9" t="s">
         <v>305</v>
       </c>
-      <c r="L9" t="s">
+      <c r="AD9" t="s">
         <v>306</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>307</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AK9" t="s">
         <v>308</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AO9" t="s">
         <v>309</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AT9" t="s">
         <v>310</v>
       </c>
-      <c r="AT9" t="s">
+      <c r="BC9" t="s">
         <v>311</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>312</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="31:55" x14ac:dyDescent="0.25"/>
@@ -8291,7 +8249,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11">
@@ -8301,7 +8259,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14">
@@ -8311,14 +8269,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B3" s="16">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -8326,35 +8284,35 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B4" s="19">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" t="s">
+        <v>317</v>
+      </c>
+      <c r="G4" t="s">
         <v>318</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>319</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>320</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>321</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>322</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4" t="s">
         <v>323</v>
-      </c>
-      <c r="K4" t="s">
-        <v>324</v>
-      </c>
-      <c r="L4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8366,7 +8324,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F5" s="21">
         <v>2</v>
@@ -8377,7 +8335,7 @@
       </c>
       <c r="H5" s="23">
         <f>B4/B3</f>
-        <v>0.14363143631436315</v>
+        <v>0.1453804347826087</v>
       </c>
       <c r="I5" s="24">
         <f>C2*G5</f>
@@ -8385,15 +8343,15 @@
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K5" s="25">
         <f>J5-I5</f>
-        <v>-7.230769230769241</v>
+        <v>-6.230769230769241</v>
       </c>
       <c r="L5" s="26">
         <f>K5/4</f>
-        <v>-1.8076923076923102</v>
+        <v>-1.5576923076923102</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8402,7 +8360,7 @@
       </c>
       <c r="B6" s="19">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>1</v>
@@ -8416,7 +8374,7 @@
       </c>
       <c r="H6" s="23">
         <f>B5/B3</f>
-        <v>0.03116531165311653</v>
+        <v>0.03125</v>
       </c>
       <c r="I6" s="24">
         <f>C2*G6</f>
@@ -8441,10 +8399,10 @@
       </c>
       <c r="B7" s="28">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F7" s="30">
         <v>3</v>
@@ -8455,7 +8413,7 @@
       </c>
       <c r="H7" s="32">
         <f>(B5+B4)/B3</f>
-        <v>0.17479674796747968</v>
+        <v>0.1766304347826087</v>
       </c>
       <c r="I7" s="24">
         <f>C2*G7</f>
@@ -8463,20 +8421,20 @@
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K7" s="25">
         <f>J7-I7</f>
-        <v>-40.84615384615387</v>
+        <v>-39.84615384615387</v>
       </c>
       <c r="L7" s="26">
         <f>K7/4</f>
-        <v>-10.211538461538467</v>
+        <v>-9.961538461538467</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E8" s="33" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F8" s="34">
         <v>6</v>
@@ -8487,7 +8445,7 @@
       </c>
       <c r="H8" s="36">
         <f>B6/B3</f>
-        <v>0.4024390243902439</v>
+        <v>0.4008152173913043</v>
       </c>
       <c r="I8" s="24">
         <f>C2*G8</f>
@@ -8495,27 +8453,27 @@
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K8" s="25">
         <f>J8-I8</f>
-        <v>-42.692307692307736</v>
+        <v>-44.692307692307736</v>
       </c>
       <c r="L8" s="26">
         <f>K8/4</f>
-        <v>-10.673076923076934</v>
+        <v>-11.173076923076934</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F9" s="34">
         <v>4</v>
@@ -8526,7 +8484,7 @@
       </c>
       <c r="H9" s="36">
         <f>B7/B3</f>
-        <v>0.42276422764227645</v>
+        <v>0.422554347826087</v>
       </c>
       <c r="I9" s="24">
         <f>C2*G9</f>
@@ -8534,20 +8492,20 @@
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K9" s="37">
         <f>J9-I9</f>
-        <v>85.53846153846152</v>
+        <v>84.53846153846152</v>
       </c>
       <c r="L9" s="26">
         <f>K9/4</f>
-        <v>21.38461538461538</v>
+        <v>21.13461538461538</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="38" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I11" s="39">
         <f>SUM(I7:I9)</f>
@@ -8555,46 +8513,46 @@
       </c>
       <c r="J11" s="33">
         <f>SUM(J7:J9)</f>
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="K11" s="40">
         <f>SUM(K7:K9)</f>
-        <v>1.9999999999999147</v>
+        <v>0</v>
       </c>
       <c r="L11" s="41">
         <f>SUM(L7:L9)</f>
-        <v>0.4999999999999787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F16" t="s">
+        <v>317</v>
+      </c>
+      <c r="G16" t="s">
+        <v>330</v>
+      </c>
+      <c r="H16" t="s">
         <v>319</v>
       </c>
-      <c r="G16" t="s">
-        <v>332</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="I16" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="J16" s="42" t="s">
         <v>321</v>
       </c>
-      <c r="I16" s="42" t="s">
+      <c r="K16" t="s">
         <v>322</v>
       </c>
-      <c r="J16" s="42" t="s">
+      <c r="L16" t="s">
         <v>323</v>
-      </c>
-      <c r="K16" t="s">
-        <v>324</v>
-      </c>
-      <c r="L16" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="43" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F17" s="44">
         <v>3</v>
@@ -8605,28 +8563,28 @@
       </c>
       <c r="H17" s="46">
         <f>(B5+B4)/B3</f>
-        <v>0.17479674796747968</v>
+        <v>0.1766304347826087</v>
       </c>
       <c r="I17" s="47">
         <f>B3*G17</f>
-        <v>170.30769230769232</v>
+        <v>169.84615384615387</v>
       </c>
       <c r="J17" s="48">
         <f>B5+B4</f>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K17" s="49">
         <f>J17-I17</f>
-        <v>-41.30769230769232</v>
+        <v>-39.84615384615387</v>
       </c>
       <c r="L17" s="26">
         <f>K17/4</f>
-        <v>-10.32692307692308</v>
+        <v>-9.961538461538467</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="50" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F18" s="51">
         <v>6</v>
@@ -8637,29 +8595,29 @@
       </c>
       <c r="H18" s="53">
         <f>B6/B3</f>
-        <v>0.4024390243902439</v>
+        <v>0.4008152173913043</v>
       </c>
       <c r="I18" s="54">
         <f>B3*G18</f>
-        <v>340.61538461538464</v>
+        <v>339.69230769230774</v>
       </c>
       <c r="J18" s="55">
         <f>B6</f>
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K18" s="56">
         <f>J18-I18</f>
-        <v>-43.61538461538464</v>
+        <v>-44.692307692307736</v>
       </c>
       <c r="L18" s="26">
         <f>K18/4</f>
-        <v>-10.90384615384616</v>
+        <v>-11.173076923076934</v>
       </c>
       <c r="Q18" s="57"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="58" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F19" s="59">
         <v>4</v>
@@ -8670,30 +8628,30 @@
       </c>
       <c r="H19" s="61">
         <f>B7/B3</f>
-        <v>0.42276422764227645</v>
+        <v>0.422554347826087</v>
       </c>
       <c r="I19" s="62">
         <f>B3*G19</f>
-        <v>227.0769230769231</v>
+        <v>226.46153846153848</v>
       </c>
       <c r="J19" s="63">
         <f>B7</f>
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K19" s="64">
         <f>J19-I19</f>
-        <v>84.9230769230769</v>
+        <v>84.53846153846152</v>
       </c>
       <c r="L19" s="26">
         <f>K19/4</f>
-        <v>21.230769230769226</v>
+        <v>21.13461538461538</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="P24" s="65" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="Q24" s="65"/>
       <c r="R24" s="65"/>
@@ -8702,18 +8660,18 @@
     <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P25" s="66"/>
       <c r="Q25" s="67" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="R25" s="68" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S25" s="69" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P26" s="70" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Q26" s="33">
         <v>247</v>
@@ -8728,7 +8686,7 @@
     </row>
     <row r="27" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P27" s="70" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Q27" s="33">
         <v>124</v>
@@ -8743,7 +8701,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P28" s="71" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Q28" s="72">
         <v>165</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="336">
   <si>
     <t>sl</t>
   </si>
@@ -346,6 +346,9 @@
     <t>2024-10-06</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2024-11-02</t>
   </si>
   <si>
@@ -400,6 +403,9 @@
     <t>2025-01-04</t>
   </si>
   <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
     <t>2024-12-27</t>
   </si>
   <si>
@@ -523,7 +529,7 @@
     <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;PreiserJu;ZacherlPa</t>
+    <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;WeissAl;ZacherlPa</t>
   </si>
   <si>
     <t>Eishalle Sterzing;MoschenAn;SoraperraSi;CusinFe;FormaioniTh</t>
@@ -568,6 +574,9 @@
     <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;ArlicMa;TelesklavFa</t>
   </si>
   <si>
+    <t>Eishalle Jesenice;OrelSt;VoicanCh;PreiserJu;WuchererGe</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -643,7 +652,7 @@
     <t>Würtharena Neumarkt;BenvegnuAn;VirtaTu;FecchioFe;PaceJa</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;WeissAl</t>
+    <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;PreiserJu</t>
   </si>
   <si>
     <t>Eishalle Gröden;BulovecMi;LazzeriAl;AbeltinoSi;ArlicMa</t>
@@ -742,7 +751,7 @@
     <t>Eishalle Celje;BajtMi;MetzingerFi;KnezRo;MarkizetiGr</t>
   </si>
   <si>
-    <t>Eishalle Sissek Zibel;BulovecMi;WidmannFl;ArlicMa;WuchererGe</t>
+    <t>Eishalle Meran;GiacomozziFe;KainbergerJu;EislCh;FleischmannLu</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;SnojTa;WenuschHe;PreiserJu;RinkerDa</t>
@@ -838,13 +847,13 @@
     <t>Eishalle Ritten;EggerTh;LazzeriAl;GrisentiLu;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Meran;GiacomozziFe;KainbergerJu;EislCh;FleischmannLu</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;Huber rRe;SpiegelSe;AbeltinoSi;GrisentiLu</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;EggerTh;RuetzMa;DivisDo;JägerRi</t>
+    <t>Eishalle Gröden;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;EggerTh;Huber rRe;AbeltinoSi;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;RuetzMa;SpiegelSe;DivisDo;JägerRi</t>
   </si>
   <si>
     <t>Eishalle Cortina;GiacomozziFe;PinieOm;CristeliMa;CusinFe</t>
@@ -913,7 +922,7 @@
     <t>Eishalle Cortina;LegaSi;VirtaTu;CristeliMa;RivisAn</t>
   </si>
   <si>
-    <t>Eishalle Gröden;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
+    <t>Eishalle Cortina;LebenJa;PirasAn;GrisentiLu;JavornikBl</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;BajtMi;HolzerTo;JavornikBl;StrimitzerDa</t>
@@ -944,9 +953,6 @@
   </si>
   <si>
     <t>Eishalle Gröden;PirasAn;SoraperraSi;FormaioniTh;ScalzeriAl</t>
-  </si>
-  <si>
-    <t>Eishalle Cortina;LebenJa;PirasAn;GrisentiLu;JavornikBl</t>
   </si>
   <si>
     <t>Eishalle Gröden;MoschenAn;VirtaTu;FleischmannLu;FormaioniTh</t>
@@ -1918,12 +1924,12 @@
         <v>11</v>
       </c>
       <c r="C1">
-        <f>COUNTIF(C4:C69,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(C4:C68,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="D1">
-        <f>COUNTIF(D4:D68,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E67,"&lt;&gt;")</f>
@@ -2066,7 +2072,7 @@
         <v>14</v>
       </c>
       <c r="AN1">
-        <f>COUNTIF(AN4:AN66,"&lt;&gt;")</f>
+        <f>COUNTIF(AN4:AN65,"&lt;&gt;")</f>
         <v>13</v>
       </c>
       <c r="AO1">
@@ -2083,7 +2089,7 @@
       </c>
       <c r="AR1">
         <f>COUNTIF(AR4:AR63,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS69,"&lt;&gt;")</f>
@@ -2095,7 +2101,7 @@
       </c>
       <c r="AU1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV65,"&lt;&gt;")</f>
@@ -2103,15 +2109,15 @@
       </c>
       <c r="AW1">
         <f>COUNTIF(AW4:AW66,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="AY1">
-        <f>COUNTIF(AY4:AY68,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(AY4:AY67,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ66,"&lt;&gt;")</f>
@@ -3189,10 +3195,10 @@
         <v>91</v>
       </c>
       <c r="BG6" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="BH6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BJ6" s="8" t="s">
         <v>91</v>
@@ -3213,7 +3219,7 @@
         <v>94</v>
       </c>
       <c r="BQ6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
@@ -3284,7 +3290,7 @@
         <v>84</v>
       </c>
       <c r="X7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y7" t="s">
         <v>80</v>
@@ -3323,7 +3329,7 @@
         <v>106</v>
       </c>
       <c r="AK7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AL7" t="s">
         <v>90</v>
@@ -3389,19 +3395,19 @@
         <v>102</v>
       </c>
       <c r="BG7" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BH7" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BJ7" t="s">
         <v>102</v>
       </c>
       <c r="BK7" t="s">
+        <v>116</v>
+      </c>
+      <c r="BM7" t="s">
         <v>115</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>114</v>
       </c>
       <c r="BN7" t="s">
         <v>107</v>
@@ -3410,7 +3416,7 @@
         <v>94</v>
       </c>
       <c r="BP7" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -3440,13 +3446,13 @@
         <v>88</v>
       </c>
       <c r="J8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K8" t="s">
         <v>77</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s">
         <v>82</v>
@@ -3479,7 +3485,7 @@
         <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y8" t="s">
         <v>79</v>
@@ -3509,7 +3515,7 @@
         <v>89</v>
       </c>
       <c r="AH8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AI8" t="s">
         <v>103</v>
@@ -3518,7 +3524,7 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL8" t="s">
         <v>88</v>
@@ -3554,7 +3560,7 @@
         <v>90</v>
       </c>
       <c r="AW8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AX8" t="s">
         <v>79</v>
@@ -3572,17 +3578,20 @@
         <v>90</v>
       </c>
       <c r="BC8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BD8" t="s">
         <v>88</v>
       </c>
       <c r="BE8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BF8" t="s">
         <v>95</v>
       </c>
+      <c r="BG8" t="s">
+        <v>120</v>
+      </c>
       <c r="BH8" s="7" t="s">
         <v>92</v>
       </c>
@@ -3590,13 +3599,13 @@
         <v>94</v>
       </c>
       <c r="BK8" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM8" t="s">
         <v>120</v>
       </c>
-      <c r="BM8" t="s">
-        <v>119</v>
-      </c>
       <c r="BN8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BO8" s="7" t="s">
         <v>104</v>
@@ -3622,19 +3631,19 @@
         <v>82</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>100</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>104</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L9" t="s">
         <v>106</v>
@@ -3676,16 +3685,16 @@
         <v>93</v>
       </c>
       <c r="AA9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AB9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC9" t="s">
         <v>90</v>
       </c>
       <c r="AD9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AE9" s="8" t="s">
         <v>91</v>
@@ -3697,13 +3706,13 @@
         <v>88</v>
       </c>
       <c r="AH9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AI9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="s">
         <v>106</v>
@@ -3739,7 +3748,7 @@
         <v>100</v>
       </c>
       <c r="AV9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW9" t="s">
         <v>89</v>
@@ -3766,31 +3775,31 @@
         <v>102</v>
       </c>
       <c r="BE9" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BF9" t="s">
         <v>94</v>
       </c>
       <c r="BH9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BJ9" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BK9" t="s">
+        <v>115</v>
+      </c>
+      <c r="BM9" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="BM9" s="7" t="s">
-        <v>113</v>
       </c>
       <c r="BN9" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BO9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BP9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -3798,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>95</v>
@@ -3819,16 +3828,16 @@
         <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K10" t="s">
         <v>106</v>
       </c>
       <c r="L10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>102</v>
@@ -3861,7 +3870,7 @@
         <v>87</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA10" t="s">
         <v>106</v>
@@ -3876,7 +3885,7 @@
         <v>106</v>
       </c>
       <c r="AE10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF10" t="s">
         <v>102</v>
@@ -3885,13 +3894,13 @@
         <v>91</v>
       </c>
       <c r="AH10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AJ10" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="AK10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -3948,7 +3957,7 @@
         <v>106</v>
       </c>
       <c r="BD10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BF10" s="7"/>
       <c r="BJ10" t="s">
@@ -3961,7 +3970,7 @@
         <v>103</v>
       </c>
       <c r="BN10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -3969,13 +3978,13 @@
         <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>102</v>
@@ -3984,28 +3993,28 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>92</v>
       </c>
       <c r="J11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" t="s">
         <v>118</v>
-      </c>
-      <c r="K11" t="s">
-        <v>119</v>
-      </c>
-      <c r="L11" t="s">
-        <v>124</v>
-      </c>
-      <c r="N11" t="s">
-        <v>117</v>
       </c>
       <c r="O11" t="s">
         <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q11" t="s">
         <v>93</v>
@@ -4023,7 +4032,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4035,7 +4044,7 @@
         <v>107</v>
       </c>
       <c r="AA11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AB11" s="7" t="s">
         <v>104</v>
@@ -4059,7 +4068,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4077,7 +4086,7 @@
         <v>92</v>
       </c>
       <c r="AP11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AQ11" t="s">
         <v>106</v>
@@ -4098,7 +4107,7 @@
         <v>94</v>
       </c>
       <c r="AW11" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AX11" t="s">
         <v>93</v>
@@ -4119,7 +4128,7 @@
         <v>91</v>
       </c>
       <c r="BD11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BJ11" t="s">
         <v>104</v>
@@ -4128,10 +4137,10 @@
         <v>104</v>
       </c>
       <c r="BM11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BN11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4141,35 +4150,35 @@
       <c r="B12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C12" t="s">
-        <v>94</v>
+      <c r="C12" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P12" t="s">
         <v>106</v>
@@ -4178,16 +4187,16 @@
         <v>107</v>
       </c>
       <c r="R12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S12" s="8" t="s">
         <v>107</v>
       </c>
       <c r="T12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>106</v>
@@ -4199,34 +4208,34 @@
         <v>95</v>
       </c>
       <c r="Z12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA12" s="7" t="s">
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC12" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD12" t="s">
         <v>88</v>
       </c>
       <c r="AE12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG12" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AJ12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK12" t="s">
         <v>95</v>
@@ -4241,34 +4250,34 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
       </c>
       <c r="AQ12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AR12" t="s">
         <v>102</v>
       </c>
       <c r="AS12" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AT12" s="8" t="s">
         <v>100</v>
       </c>
       <c r="AU12" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AV12" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AW12" t="s">
         <v>100</v>
       </c>
       <c r="AX12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4289,10 +4298,10 @@
         <v>103</v>
       </c>
       <c r="BK12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BM12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -4302,44 +4311,44 @@
       <c r="B13" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>116</v>
+      <c r="C13" t="s">
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>106</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" t="s">
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S13" t="s">
         <v>95</v>
@@ -4351,10 +4360,10 @@
         <v>94</v>
       </c>
       <c r="V13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z13" t="s">
         <v>106</v>
@@ -4363,82 +4372,88 @@
         <v>104</v>
       </c>
       <c r="AB13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD13" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AC13" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="AF13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG13" t="s">
         <v>103</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>92</v>
       </c>
       <c r="AK13" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AL13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
       </c>
       <c r="AN13" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="AO13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AP13" s="7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AQ13" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AR13" t="s">
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT13" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>128</v>
       </c>
       <c r="AV13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AW13" s="7" t="s">
         <v>92</v>
       </c>
       <c r="AX13" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>94</v>
+        <v>118</v>
+      </c>
+      <c r="AY13" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="AZ13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BA13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BB13" t="s">
         <v>102</v>
       </c>
       <c r="BC13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BD13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BK13" t="s">
         <v>103</v>
@@ -4446,34 +4461,34 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L14" t="s">
+        <v>119</v>
+      </c>
+      <c r="N14" t="s">
         <v>111</v>
-      </c>
-      <c r="B14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" t="s">
-        <v>118</v>
-      </c>
-      <c r="L14" t="s">
-        <v>118</v>
-      </c>
-      <c r="N14" t="s">
-        <v>110</v>
       </c>
       <c r="O14" t="s">
         <v>90</v>
@@ -4485,10 +4500,10 @@
         <v>94</v>
       </c>
       <c r="R14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T14" s="7" t="s">
         <v>104</v>
@@ -4497,37 +4512,37 @@
         <v>93</v>
       </c>
       <c r="V14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W14" t="s">
         <v>106</v>
       </c>
       <c r="Z14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AC14" t="s">
         <v>103</v>
       </c>
       <c r="AD14" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF14" t="s">
         <v>111</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AG14" t="s">
         <v>122</v>
       </c>
-      <c r="AF14" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>121</v>
-      </c>
       <c r="AH14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
@@ -4535,115 +4550,112 @@
       <c r="AM14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AN14" t="s">
-        <v>114</v>
+      <c r="AN14" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AP14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AQ14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
       </c>
       <c r="AT14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AV14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AW14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AX14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AY14" s="7" t="s">
-        <v>104</v>
+      <c r="AY14" t="s">
+        <v>112</v>
       </c>
       <c r="AZ14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BA14" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BB14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
+      </c>
+      <c r="D15" t="s">
+        <v>111</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S15" t="s">
         <v>106</v>
       </c>
       <c r="T15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U15" t="s">
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="W15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD15" t="s">
         <v>122</v>
       </c>
-      <c r="AC15" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>121</v>
-      </c>
       <c r="AK15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM15" t="s">
-        <v>113</v>
-      </c>
-      <c r="AN15" s="7" t="s">
-        <v>104</v>
+        <v>114</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>129</v>
       </c>
       <c r="AO15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AP15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AR15" s="7" t="s">
         <v>104</v>
@@ -4658,10 +4670,10 @@
         <v>91</v>
       </c>
       <c r="AX15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="AZ15" s="7" t="s">
         <v>104</v>
@@ -4675,28 +4687,28 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>103</v>
       </c>
       <c r="O16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>92</v>
       </c>
       <c r="R16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U16" s="7" t="s">
         <v>104</v>
@@ -4705,25 +4717,28 @@
         <v>104</v>
       </c>
       <c r="Z16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC16" t="s">
         <v>92</v>
       </c>
       <c r="AK16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AN16" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>104</v>
       </c>
       <c r="AR16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AT16" s="7" t="s">
         <v>104</v>
@@ -4732,36 +4747,33 @@
         <v>106</v>
       </c>
       <c r="AX16" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY16" t="s">
         <v>122</v>
       </c>
-      <c r="AY16" t="s">
+      <c r="AZ16" t="s">
+        <v>112</v>
+      </c>
+      <c r="BA16" t="s">
         <v>127</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>111</v>
-      </c>
-      <c r="BA16" t="s">
-        <v>126</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>121</v>
-      </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R17" t="s">
         <v>103</v>
@@ -4773,80 +4785,86 @@
         <v>103</v>
       </c>
       <c r="W17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AM17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AR17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>129</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>111</v>
+      </c>
+      <c r="R18" t="s">
         <v>127</v>
       </c>
-      <c r="AT17" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>121</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>121</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>127</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="P18" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>110</v>
-      </c>
-      <c r="R18" t="s">
-        <v>126</v>
-      </c>
       <c r="S18" t="s">
+        <v>112</v>
+      </c>
+      <c r="U18" t="s">
+        <v>112</v>
+      </c>
+      <c r="W18" t="s">
         <v>111</v>
-      </c>
-      <c r="U18" t="s">
-        <v>111</v>
-      </c>
-      <c r="W18" t="s">
-        <v>110</v>
       </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
       <c r="AT18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ18" t="s">
         <v>122</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="16:52" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S19" t="s">
+        <v>123</v>
+      </c>
+      <c r="U19" t="s">
+        <v>127</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT19" t="s">
         <v>122</v>
-      </c>
-      <c r="U19" t="s">
-        <v>126</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
@@ -4911,7 +4929,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BC42"/>
+  <dimension ref="A3:BD42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -4957,7 +4975,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -5028,7 +5046,7 @@
         <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y3" t="s">
         <v>88</v>
@@ -5043,7 +5061,7 @@
         <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD3" t="s">
         <v>91</v>
@@ -5055,40 +5073,40 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AI3" t="s">
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AM3" t="s">
         <v>106</v>
       </c>
       <c r="AN3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="s">
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AQ3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AR3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AS3" t="s">
         <v>92</v>
@@ -5097,34 +5115,37 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
       </c>
       <c r="AW3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" t="s">
         <v>127</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BB3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" t="s">
         <v>122</v>
       </c>
-      <c r="BA3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>121</v>
+      <c r="BD3" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -5290,8 +5311,11 @@
       <c r="BC4" t="s">
         <v>11</v>
       </c>
+      <c r="BD4" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5457,8 +5481,11 @@
       <c r="BC5" t="s">
         <v>54</v>
       </c>
+      <c r="BD5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5577,7 +5604,7 @@
         <v>52</v>
       </c>
       <c r="AN6" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AO6" t="s">
         <v>35</v>
@@ -5624,8 +5651,11 @@
       <c r="BC6" t="s">
         <v>7</v>
       </c>
+      <c r="BD6" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -5791,13 +5821,16 @@
       <c r="BC7" t="s">
         <v>42</v>
       </c>
+      <c r="BD7" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -5821,7 +5854,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -5919,7 +5952,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6208,7 +6241,7 @@
         <v>37</v>
       </c>
       <c r="AO11" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AR11" t="s">
         <v>7</v>
@@ -6270,7 +6303,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -6309,7 +6342,7 @@
         <v>5</v>
       </c>
       <c r="AO12" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AS12" t="s">
         <v>4</v>
@@ -6407,7 +6440,7 @@
         <v>14</v>
       </c>
       <c r="AO13" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="AS13" t="s">
         <v>63</v>
@@ -6505,7 +6538,7 @@
         <v>15</v>
       </c>
       <c r="AO14" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="AS14" t="s">
         <v>52</v>
@@ -6603,7 +6636,7 @@
         <v>8</v>
       </c>
       <c r="AO15" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="s">
         <v>53</v>
@@ -6701,13 +6734,13 @@
         <v>39</v>
       </c>
       <c r="AO16" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="AS16" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AT16" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="AU16" t="s">
         <v>31</v>
@@ -6793,13 +6826,13 @@
         <v>21</v>
       </c>
       <c r="AO17" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="AS17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT17" t="s">
         <v>45</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>49</v>
       </c>
       <c r="AU17" t="s">
         <v>36</v>
@@ -6885,7 +6918,7 @@
         <v>20</v>
       </c>
       <c r="AO18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AS18" t="s">
         <v>32</v>
@@ -6977,7 +7010,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="AS19" t="s">
         <v>20</v>
@@ -7054,7 +7087,7 @@
         <v>38</v>
       </c>
       <c r="AO20" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="AT20" t="s">
         <v>5</v>
@@ -7122,7 +7155,7 @@
         <v>26</v>
       </c>
       <c r="AO21" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="AT21" t="s">
         <v>56</v>
@@ -7190,7 +7223,7 @@
         <v>40</v>
       </c>
       <c r="AO22" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="s">
         <v>13</v>
@@ -7258,7 +7291,7 @@
         <v>25</v>
       </c>
       <c r="AO23" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="AT23" t="s">
         <v>55</v>
@@ -7292,9 +7325,6 @@
       <c r="AK24" t="s">
         <v>33</v>
       </c>
-      <c r="AO24" t="s">
-        <v>9</v>
-      </c>
       <c r="AT24" t="s">
         <v>24</v>
       </c>
@@ -7318,9 +7348,6 @@
       <c r="AK25" t="s">
         <v>18</v>
       </c>
-      <c r="AO25" t="s">
-        <v>33</v>
-      </c>
       <c r="AT25" t="s">
         <v>26</v>
       </c>
@@ -7344,9 +7371,6 @@
       <c r="AK26" t="s">
         <v>23</v>
       </c>
-      <c r="AO26" t="s">
-        <v>20</v>
-      </c>
       <c r="AT26" t="s">
         <v>27</v>
       </c>
@@ -7370,9 +7394,6 @@
       <c r="AK27" t="s">
         <v>30</v>
       </c>
-      <c r="AO27" t="s">
-        <v>13</v>
-      </c>
       <c r="AT27" t="s">
         <v>23</v>
       </c>
@@ -7380,7 +7401,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="31:55" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="46:55" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7402,7 +7423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BC14"/>
+  <dimension ref="A3:BD14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -7485,7 +7506,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -7556,7 +7577,7 @@
         <v>77</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y3" t="s">
         <v>88</v>
@@ -7571,7 +7592,7 @@
         <v>100</v>
       </c>
       <c r="AC3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD3" t="s">
         <v>91</v>
@@ -7583,40 +7604,40 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AI3" t="s">
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AM3" t="s">
         <v>106</v>
       </c>
       <c r="AN3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="s">
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AQ3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AR3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AS3" t="s">
         <v>92</v>
@@ -7625,598 +7646,601 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
       </c>
       <c r="AW3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AX3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AY3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA3" t="s">
         <v>127</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BB3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC3" t="s">
         <v>122</v>
       </c>
-      <c r="BA3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>121</v>
+      <c r="BD3" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="R4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="T4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="U4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="V4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="W4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="X4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Y4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Z4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AA4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AB4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AC4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AD4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AE4" t="s">
+        <v>161</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>163</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>167</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AP4" t="s">
         <v>159</v>
       </c>
-      <c r="AF4" t="s">
-        <v>160</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>163</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>164</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>166</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>168</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>157</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AR4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AS4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AT4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AU4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AV4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AW4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AX4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AY4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AZ4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="BA4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="BB4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="BC4" t="s">
-        <v>182</v>
+        <v>184</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>185</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="P5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="R5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="T5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="U5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="V5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="W5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Y5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Z5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AB5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AD5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AE5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AF5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AI5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AK5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AL5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AM5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AN5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AO5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AR5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AS5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AT5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AU5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AV5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AW5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AX5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AZ5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="BA5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="BB5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="BC5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="N6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="T6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="W6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Y6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Z6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AB6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AD6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AE6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AI6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AK6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AM6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AN6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AO6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AS6" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AT6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AU6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AV6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AW6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AX6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AZ6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="BA6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="BB6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="BC6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="L7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="T7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="V7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="W7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Y7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Z7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AB7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AD7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AE7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AI7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AK7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AM7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AN7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AS7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AT7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AU7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AV7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AW7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AX7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AZ7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="BC7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="V8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="W8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Y8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AB8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AD8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AE8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AI8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AK8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AM8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AO8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AT8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AU8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AW8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AZ8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="BC8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AD9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AE9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AK9" t="s">
-        <v>308</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AT9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="BC9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="31:55" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="46:55" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8249,7 +8273,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11">
@@ -8259,7 +8283,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="14">
@@ -8269,14 +8293,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B3" s="16">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>736</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -8284,35 +8308,35 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B4" s="19">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8324,7 +8348,7 @@
         <v>23</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F5" s="21">
         <v>2</v>
@@ -8335,7 +8359,7 @@
       </c>
       <c r="H5" s="23">
         <f>B4/B3</f>
-        <v>0.1453804347826087</v>
+        <v>0.14266304347826086</v>
       </c>
       <c r="I5" s="24">
         <f>C2*G5</f>
@@ -8343,15 +8367,15 @@
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K5" s="25">
         <f>J5-I5</f>
-        <v>-6.230769230769241</v>
+        <v>-8.23076923076924</v>
       </c>
       <c r="L5" s="26">
         <f>K5/4</f>
-        <v>-1.5576923076923102</v>
+        <v>-2.05769230769231</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8399,10 +8423,10 @@
       </c>
       <c r="B7" s="28">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F7" s="30">
         <v>3</v>
@@ -8413,7 +8437,7 @@
       </c>
       <c r="H7" s="32">
         <f>(B5+B4)/B3</f>
-        <v>0.1766304347826087</v>
+        <v>0.17391304347826086</v>
       </c>
       <c r="I7" s="24">
         <f>C2*G7</f>
@@ -8421,20 +8445,20 @@
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K7" s="25">
         <f>J7-I7</f>
-        <v>-39.84615384615387</v>
+        <v>-41.84615384615387</v>
       </c>
       <c r="L7" s="26">
         <f>K7/4</f>
-        <v>-9.961538461538467</v>
+        <v>-10.461538461538467</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E8" s="33" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F8" s="34">
         <v>6</v>
@@ -8466,14 +8490,14 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>736</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F9" s="34">
         <v>4</v>
@@ -8484,7 +8508,7 @@
       </c>
       <c r="H9" s="36">
         <f>B7/B3</f>
-        <v>0.422554347826087</v>
+        <v>0.42527173913043476</v>
       </c>
       <c r="I9" s="24">
         <f>C2*G9</f>
@@ -8492,20 +8516,20 @@
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K9" s="37">
         <f>J9-I9</f>
-        <v>84.53846153846152</v>
+        <v>86.53846153846152</v>
       </c>
       <c r="L9" s="26">
         <f>K9/4</f>
-        <v>21.13461538461538</v>
+        <v>21.63461538461538</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="38" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I11" s="39">
         <f>SUM(I7:I9)</f>
@@ -8526,33 +8550,33 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F16" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I16" s="42" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J16" s="42" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F17" s="44">
         <v>3</v>
@@ -8563,7 +8587,7 @@
       </c>
       <c r="H17" s="46">
         <f>(B5+B4)/B3</f>
-        <v>0.1766304347826087</v>
+        <v>0.17391304347826086</v>
       </c>
       <c r="I17" s="47">
         <f>B3*G17</f>
@@ -8571,20 +8595,20 @@
       </c>
       <c r="J17" s="48">
         <f>B5+B4</f>
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K17" s="49">
         <f>J17-I17</f>
-        <v>-39.84615384615387</v>
+        <v>-41.84615384615387</v>
       </c>
       <c r="L17" s="26">
         <f>K17/4</f>
-        <v>-9.961538461538467</v>
+        <v>-10.461538461538467</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="50" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F18" s="51">
         <v>6</v>
@@ -8617,7 +8641,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="58" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F19" s="59">
         <v>4</v>
@@ -8628,7 +8652,7 @@
       </c>
       <c r="H19" s="61">
         <f>B7/B3</f>
-        <v>0.422554347826087</v>
+        <v>0.42527173913043476</v>
       </c>
       <c r="I19" s="62">
         <f>B3*G19</f>
@@ -8636,22 +8660,22 @@
       </c>
       <c r="J19" s="63">
         <f>B7</f>
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K19" s="64">
         <f>J19-I19</f>
-        <v>84.53846153846152</v>
+        <v>86.53846153846152</v>
       </c>
       <c r="L19" s="26">
         <f>K19/4</f>
-        <v>21.13461538461538</v>
+        <v>21.63461538461538</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="P24" s="65" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q24" s="65"/>
       <c r="R24" s="65"/>
@@ -8660,18 +8684,18 @@
     <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P25" s="66"/>
       <c r="Q25" s="67" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R25" s="68" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S25" s="69" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P26" s="70" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q26" s="33">
         <v>247</v>
@@ -8686,7 +8710,7 @@
     </row>
     <row r="27" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P27" s="70" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q27" s="33">
         <v>124</v>
@@ -8701,7 +8725,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
       <c r="P28" s="71" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q28" s="72">
         <v>165</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="336">
   <si>
     <t>sl</t>
   </si>
@@ -391,18 +391,18 @@
     <t>2025-01-02</t>
   </si>
   <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
     <t>2024-12-04</t>
   </si>
   <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
     <t>2025-01-03</t>
   </si>
   <si>
@@ -508,7 +508,7 @@
     <t>Eishalle Gröden;EggerTh;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;Huber rRe;RivisFe;RinkerDa;StrimitzerDa</t>
+    <t>Eishalle Dornbirn;HolzerTo;Huber rRe;DivisDo;RinkerDa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;HolzerTo;RuetzMa;JägerRi;SeewaldJe</t>
@@ -529,7 +529,7 @@
     <t>Eishalle Jesenice;BrockAd;MeixnerSe;PreiserJu;ZacherlPa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;WeissAl;ZacherlPa</t>
+    <t>Sportpark Kitzbühel;HlavatyAl;MeixnerSe;EislCh;WeissAl</t>
   </si>
   <si>
     <t>Eishalle Sterzing;MoschenAn;SoraperraSi;CusinFe;FormaioniTh</t>
@@ -775,7 +775,7 @@
     <t>Eishalle Meran;Huber rRe;RuetzMa;FecchioFe;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Cortina;EggerTh;MoschenAn;AbeltinoSi;FormaioniTh</t>
+    <t>Eishalle Cortina;EggerTh;PinieOm;AbeltinoSi;FormaioniTh</t>
   </si>
   <si>
     <t>Eishalle Jesenice;MeixnerSe;MetzingerFi;KnezRo;LegatKo</t>
@@ -958,7 +958,7 @@
     <t>Eishalle Gröden;MoschenAn;VirtaTu;FleischmannLu;FormaioniTh</t>
   </si>
   <si>
-    <t>Eishalle Cortina;LebenJa;PinieOm;CristeliMa;JeramFi</t>
+    <t>Eishalle Cortina;LebenJa;MoschenAn;CristeliMa;JeramFi</t>
   </si>
   <si>
     <t>vse delegirane tekme</t>
@@ -3584,7 +3584,7 @@
         <v>88</v>
       </c>
       <c r="BE8" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BF8" t="s">
         <v>95</v>
@@ -3885,7 +3885,7 @@
         <v>106</v>
       </c>
       <c r="AE10" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="AF10" t="s">
         <v>102</v>
@@ -3900,7 +3900,7 @@
         <v>109</v>
       </c>
       <c r="AK10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -3993,7 +3993,7 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>92</v>
@@ -4005,7 +4005,7 @@
         <v>120</v>
       </c>
       <c r="L11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4032,7 +4032,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4154,7 +4154,7 @@
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
@@ -4169,7 +4169,7 @@
         <v>112</v>
       </c>
       <c r="K12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>112</v>
@@ -4223,7 +4223,7 @@
         <v>88</v>
       </c>
       <c r="AE12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AF12" s="7" t="s">
         <v>114</v>
@@ -4235,7 +4235,7 @@
         <v>104</v>
       </c>
       <c r="AJ12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AK12" t="s">
         <v>95</v>
@@ -4277,7 +4277,7 @@
         <v>100</v>
       </c>
       <c r="AX12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4303,8 +4303,11 @@
       <c r="BM12" t="s">
         <v>122</v>
       </c>
+      <c r="BN12" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>92</v>
       </c>
@@ -4399,7 +4402,7 @@
         <v>114</v>
       </c>
       <c r="AL13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4420,7 +4423,7 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
@@ -4518,7 +4521,7 @@
         <v>106</v>
       </c>
       <c r="Z14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
@@ -4539,10 +4542,10 @@
         <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="AH14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
@@ -4581,7 +4584,7 @@
         <v>112</v>
       </c>
       <c r="AZ14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BA14" s="7" t="s">
         <v>104</v>
@@ -4601,7 +4604,7 @@
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>114</v>
@@ -4637,11 +4640,14 @@
         <v>123</v>
       </c>
       <c r="AC15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AD15" t="s">
         <v>122</v>
       </c>
+      <c r="AG15" t="s">
+        <v>126</v>
+      </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
@@ -4652,7 +4658,7 @@
         <v>129</v>
       </c>
       <c r="AO15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AP15" t="s">
         <v>122</v>
@@ -4708,7 +4714,7 @@
         <v>114</v>
       </c>
       <c r="T16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U16" s="7" t="s">
         <v>104</v>
@@ -4729,7 +4735,7 @@
         <v>122</v>
       </c>
       <c r="AM16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AN16" t="s">
         <v>128</v>
@@ -4756,7 +4762,7 @@
         <v>112</v>
       </c>
       <c r="BA16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
@@ -4791,7 +4797,7 @@
         <v>122</v>
       </c>
       <c r="AK17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM17" t="s">
         <v>122</v>
@@ -4810,6 +4816,9 @@
       </c>
       <c r="AZ17" t="s">
         <v>129</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>127</v>
       </c>
       <c r="BB17" t="s">
         <v>123</v>
@@ -4823,7 +4832,7 @@
         <v>111</v>
       </c>
       <c r="R18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S18" t="s">
         <v>112</v>
@@ -4846,8 +4855,11 @@
       <c r="AZ18" t="s">
         <v>122</v>
       </c>
+      <c r="BB18" t="s">
+        <v>127</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="16:52" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
       <c r="Q19" t="s">
         <v>122</v>
       </c>
@@ -4858,7 +4870,7 @@
         <v>123</v>
       </c>
       <c r="U19" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="AR19" t="s">
         <v>128</v>
@@ -4867,8 +4879,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25">
+      <c r="U20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="21:21" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5073,7 +5089,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5100,10 +5116,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>125</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>126</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -5133,7 +5149,7 @@
         <v>123</v>
       </c>
       <c r="BA3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB3" t="s">
         <v>119</v>
@@ -5243,7 +5259,7 @@
         <v>39</v>
       </c>
       <c r="AG4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -5413,7 +5429,7 @@
         <v>29</v>
       </c>
       <c r="AG5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AH5" t="s">
         <v>49</v>
@@ -5583,7 +5599,7 @@
         <v>22</v>
       </c>
       <c r="AG6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AH6" t="s">
         <v>66</v>
@@ -5604,7 +5620,7 @@
         <v>52</v>
       </c>
       <c r="AN6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AO6" t="s">
         <v>35</v>
@@ -5753,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="AG7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AH7" t="s">
         <v>59</v>
@@ -5774,7 +5790,7 @@
         <v>60</v>
       </c>
       <c r="AN7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AO7" t="s">
         <v>23</v>
@@ -6464,7 +6480,7 @@
         <v>49</v>
       </c>
       <c r="BA13" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="s">
         <v>14</v>
@@ -7352,7 +7368,7 @@
         <v>26</v>
       </c>
       <c r="BC25" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
@@ -7604,7 +7620,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7631,10 +7647,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>125</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>126</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -7664,7 +7680,7 @@
         <v>123</v>
       </c>
       <c r="BA3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BB3" t="s">
         <v>119</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="336">
   <si>
     <t>sl</t>
   </si>
@@ -346,51 +346,51 @@
     <t>2024-10-06</t>
   </si>
   <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-12-19</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>2024-11-21</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
+    <t>2024-11-26</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>2025-01-02</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2025-01-06</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-11-02</t>
-  </si>
-  <si>
-    <t>2024-12-19</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>2024-11-21</t>
-  </si>
-  <si>
-    <t>2024-11-12</t>
-  </si>
-  <si>
-    <t>2024-12-22</t>
-  </si>
-  <si>
-    <t>2024-11-26</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2025-01-06</t>
-  </si>
-  <si>
-    <t>2025-01-02</t>
-  </si>
-  <si>
     <t>2024-12-01</t>
   </si>
   <si>
@@ -562,7 +562,7 @@
     <t>Eishalle Dornbirn;OrelSt;WidmannFl;StrimitzerDa;WuchererGe</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;HlavatyAl;WenuschHe;EislCh;RinkerDa</t>
+    <t>Sportpark Kitzbühel;HlavatyAl;VoicanCh;EislCh;RinkerDa</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;HolzerTo;KainbergerJu;TelesklavFa;WendnerMa</t>
@@ -769,7 +769,7 @@
     <t>Eishalle Sterzing;LazzeriAl;VirtaTu;FormaioniTh;RinkerDa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;MetzingerFi;VoicanCh;KnezRo;LegatKo</t>
+    <t>Sportpark Kitzbühel;MetzingerFi;WenuschHe;KnezRo;LegatKo</t>
   </si>
   <si>
     <t>Eishalle Meran;Huber rRe;RuetzMa;FecchioFe;ScalzeriAl</t>
@@ -847,7 +847,7 @@
     <t>Eishalle Ritten;EggerTh;LazzeriAl;GrisentiLu;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Gröden;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
+    <t>Eishalle Gröden;LehnerMo;MoidlDa;BrondiPa;MoidlMa</t>
   </si>
   <si>
     <t>Eishalle Sterzing;EggerTh;Huber rRe;AbeltinoSi;GrisentiLu</t>
@@ -1989,14 +1989,14 @@
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
         <v>13</v>
       </c>
       <c r="U1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="V1">
@@ -2036,15 +2036,15 @@
         <v>12</v>
       </c>
       <c r="AE1">
-        <f>COUNTIF(AE4:AE68,"&lt;&gt;")</f>
-        <v>11</v>
+        <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
+        <v>10</v>
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF64,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AG1">
-        <f>COUNTIF(AG4:AG68,"&lt;&gt;")</f>
+        <f>COUNTIF(AG4:AG67,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AH1">
@@ -2056,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ65,"&lt;&gt;")</f>
+        <f>COUNTIF(AJ4:AJ64,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AK1">
@@ -2080,7 +2080,7 @@
         <v>12</v>
       </c>
       <c r="AP1">
-        <f>COUNTIF(AP4:AP68,"&lt;&gt;")</f>
+        <f>COUNTIF(AP4:AP67,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="AQ1">
@@ -2108,7 +2108,7 @@
         <v>12</v>
       </c>
       <c r="AW1">
-        <f>COUNTIF(AW4:AW66,"&lt;&gt;")</f>
+        <f>COUNTIF(AW4:AW65,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="AX1">
@@ -2120,16 +2120,16 @@
         <v>13</v>
       </c>
       <c r="AZ1">
-        <f>COUNTIF(AZ4:AZ66,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(AZ4:AZ65,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="BA1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB69,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC68,"&lt;&gt;")</f>
@@ -2140,15 +2140,15 @@
         <v>10</v>
       </c>
       <c r="BE1">
-        <f>COUNTIF(BE4:BE68,"&lt;&gt;")</f>
-        <v>6</v>
+        <f>COUNTIF(BE4:BE67,"&lt;&gt;")</f>
+        <v>5</v>
       </c>
       <c r="BF1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="BG1">
-        <f>COUNTIF(BG4:BG67,"&lt;&gt;")</f>
+        <f>COUNTIF(BG4:BG66,"&lt;&gt;")</f>
         <v>4</v>
       </c>
       <c r="BH1">
@@ -2160,8 +2160,8 @@
         <v>1</v>
       </c>
       <c r="BJ1">
-        <f t="shared" ref="BJ1" si="2">COUNTIF(BJ4:BJ69,"&lt;&gt;")</f>
-        <v>8</v>
+        <f>COUNTIF(BJ4:BJ68,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
@@ -2172,12 +2172,12 @@
         <v>1</v>
       </c>
       <c r="BM1">
-        <f t="shared" ref="BM1" si="3">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
+        <f t="shared" ref="BM1" si="2">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BO1">
         <f t="shared" si="1"/>
@@ -3194,7 +3194,7 @@
       <c r="BF6" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BG6" s="7" t="s">
         <v>109</v>
       </c>
       <c r="BH6" t="s">
@@ -3394,7 +3394,7 @@
       <c r="BF7" t="s">
         <v>102</v>
       </c>
-      <c r="BG7" s="7" t="s">
+      <c r="BG7" t="s">
         <v>114</v>
       </c>
       <c r="BH7" s="8" t="s">
@@ -3515,7 +3515,7 @@
         <v>89</v>
       </c>
       <c r="AH8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AI8" t="s">
         <v>103</v>
@@ -3583,26 +3583,23 @@
       <c r="BD8" t="s">
         <v>88</v>
       </c>
-      <c r="BE8" t="s">
-        <v>109</v>
+      <c r="BE8" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="BF8" t="s">
         <v>95</v>
       </c>
-      <c r="BG8" t="s">
-        <v>120</v>
-      </c>
       <c r="BH8" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="BJ8" t="s">
-        <v>94</v>
+      <c r="BJ8" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="BK8" t="s">
         <v>121</v>
       </c>
       <c r="BM8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="BN8" t="s">
         <v>115</v>
@@ -3711,8 +3708,8 @@
       <c r="AI9" t="s">
         <v>122</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>120</v>
+      <c r="AJ9" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="AK9" t="s">
         <v>106</v>
@@ -3774,32 +3771,29 @@
       <c r="BD9" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="BE9" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="BF9" t="s">
         <v>94</v>
       </c>
       <c r="BH9" t="s">
         <v>123</v>
       </c>
-      <c r="BJ9" s="7" t="s">
-        <v>117</v>
+      <c r="BJ9" t="s">
+        <v>92</v>
       </c>
       <c r="BK9" t="s">
         <v>115</v>
       </c>
       <c r="BM9" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BN9" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BO9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BP9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -3807,7 +3801,7 @@
         <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>95</v>
@@ -3834,7 +3828,7 @@
         <v>106</v>
       </c>
       <c r="L10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="N10" t="s">
         <v>121</v>
@@ -3885,7 +3879,7 @@
         <v>106</v>
       </c>
       <c r="AE10" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AF10" t="s">
         <v>102</v>
@@ -3896,8 +3890,8 @@
       <c r="AH10" t="s">
         <v>115</v>
       </c>
-      <c r="AJ10" s="7" t="s">
-        <v>109</v>
+      <c r="AJ10" t="s">
+        <v>111</v>
       </c>
       <c r="AK10" t="s">
         <v>124</v>
@@ -3960,8 +3954,11 @@
         <v>116</v>
       </c>
       <c r="BF10" s="7"/>
+      <c r="BH10" t="s">
+        <v>112</v>
+      </c>
       <c r="BJ10" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="BK10" t="s">
         <v>107</v>
@@ -4002,7 +3999,7 @@
         <v>119</v>
       </c>
       <c r="K11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
         <v>124</v>
@@ -4044,7 +4041,7 @@
         <v>107</v>
       </c>
       <c r="AA11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AB11" s="7" t="s">
         <v>104</v>
@@ -4056,7 +4053,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4068,7 +4065,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4107,7 +4104,7 @@
         <v>94</v>
       </c>
       <c r="AW11" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AX11" t="s">
         <v>93</v>
@@ -4130,17 +4127,14 @@
       <c r="BD11" t="s">
         <v>118</v>
       </c>
-      <c r="BJ11" t="s">
-        <v>104</v>
-      </c>
       <c r="BK11" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BM11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BN11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4160,7 +4154,7 @@
         <v>95</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>92</v>
@@ -4175,7 +4169,7 @@
         <v>112</v>
       </c>
       <c r="N12" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O12" t="s">
         <v>115</v>
@@ -4214,7 +4208,7 @@
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AC12" s="7" t="s">
         <v>117</v>
@@ -4222,20 +4216,20 @@
       <c r="AD12" t="s">
         <v>88</v>
       </c>
-      <c r="AE12" t="s">
-        <v>125</v>
+      <c r="AE12" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AG12" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AJ12" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="AK12" t="s">
         <v>95</v>
@@ -4250,13 +4244,13 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
       </c>
       <c r="AQ12" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AR12" t="s">
         <v>102</v>
@@ -4268,13 +4262,13 @@
         <v>100</v>
       </c>
       <c r="AU12" s="7" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="AV12" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>100</v>
+        <v>109</v>
+      </c>
+      <c r="AW12" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="AX12" t="s">
         <v>127</v>
@@ -4304,7 +4298,7 @@
         <v>122</v>
       </c>
       <c r="BN12" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4315,7 +4309,7 @@
         <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
         <v>102</v>
@@ -4330,22 +4324,22 @@
         <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>112</v>
       </c>
       <c r="L13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="O13" t="s">
         <v>94</v>
       </c>
       <c r="P13" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="Q13" t="s">
         <v>115</v>
@@ -4363,7 +4357,7 @@
         <v>94</v>
       </c>
       <c r="V13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="W13" t="s">
         <v>115</v>
@@ -4378,13 +4372,13 @@
         <v>112</v>
       </c>
       <c r="AC13" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AD13" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>120</v>
       </c>
       <c r="AF13" t="s">
         <v>122</v>
@@ -4395,11 +4389,8 @@
       <c r="AH13" t="s">
         <v>111</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>92</v>
-      </c>
       <c r="AK13" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AL13" t="s">
         <v>126</v>
@@ -4413,8 +4404,8 @@
       <c r="AO13" t="s">
         <v>122</v>
       </c>
-      <c r="AP13" s="7" t="s">
-        <v>109</v>
+      <c r="AP13" t="s">
+        <v>120</v>
       </c>
       <c r="AQ13" s="7" t="s">
         <v>117</v>
@@ -4434,8 +4425,8 @@
       <c r="AV13" t="s">
         <v>112</v>
       </c>
-      <c r="AW13" s="7" t="s">
-        <v>92</v>
+      <c r="AW13" t="s">
+        <v>122</v>
       </c>
       <c r="AX13" t="s">
         <v>118</v>
@@ -4453,10 +4444,10 @@
         <v>102</v>
       </c>
       <c r="BC13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BD13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BK13" t="s">
         <v>103</v>
@@ -4476,7 +4467,7 @@
         <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
         <v>122</v>
@@ -4503,7 +4494,7 @@
         <v>94</v>
       </c>
       <c r="R14" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="S14" t="s">
         <v>115</v>
@@ -4535,14 +4526,11 @@
       <c r="AD14" t="s">
         <v>112</v>
       </c>
-      <c r="AE14" t="s">
-        <v>123</v>
-      </c>
       <c r="AF14" t="s">
         <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AH14" t="s">
         <v>126</v>
@@ -4560,7 +4548,7 @@
         <v>119</v>
       </c>
       <c r="AP14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AQ14" t="s">
         <v>119</v>
@@ -4571,11 +4559,14 @@
       <c r="AT14" t="s">
         <v>115</v>
       </c>
+      <c r="AU14" t="s">
+        <v>120</v>
+      </c>
       <c r="AV14" t="s">
         <v>119</v>
       </c>
       <c r="AW14" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="AX14" s="7" t="s">
         <v>92</v>
@@ -4583,8 +4574,8 @@
       <c r="AY14" t="s">
         <v>112</v>
       </c>
-      <c r="AZ14" t="s">
-        <v>109</v>
+      <c r="AZ14" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="BA14" s="7" t="s">
         <v>104</v>
@@ -4607,13 +4598,13 @@
         <v>126</v>
       </c>
       <c r="O15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="P15" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q15" t="s">
         <v>114</v>
-      </c>
-      <c r="P15" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>120</v>
       </c>
       <c r="R15" s="7" t="s">
         <v>117</v>
@@ -4631,13 +4622,13 @@
         <v>119</v>
       </c>
       <c r="W15" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA15" t="s">
         <v>120</v>
-      </c>
-      <c r="Z15" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>123</v>
       </c>
       <c r="AC15" t="s">
         <v>126</v>
@@ -4645,14 +4636,11 @@
       <c r="AD15" t="s">
         <v>122</v>
       </c>
-      <c r="AG15" t="s">
-        <v>126</v>
-      </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AM15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AN15" t="s">
         <v>129</v>
@@ -4661,7 +4649,7 @@
         <v>127</v>
       </c>
       <c r="AP15" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="AR15" s="7" t="s">
         <v>104</v>
@@ -4673,7 +4661,7 @@
         <v>103</v>
       </c>
       <c r="AW15" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AX15" t="s">
         <v>111</v>
@@ -4681,8 +4669,8 @@
       <c r="AY15" t="s">
         <v>129</v>
       </c>
-      <c r="AZ15" s="7" t="s">
-        <v>104</v>
+      <c r="AZ15" t="s">
+        <v>112</v>
       </c>
       <c r="BA15" t="s">
         <v>103</v>
@@ -4708,10 +4696,10 @@
         <v>92</v>
       </c>
       <c r="R16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="T16" t="s">
         <v>126</v>
@@ -4740,9 +4728,6 @@
       <c r="AN16" t="s">
         <v>128</v>
       </c>
-      <c r="AP16" t="s">
-        <v>104</v>
-      </c>
       <c r="AR16" t="s">
         <v>112</v>
       </c>
@@ -4750,16 +4735,16 @@
         <v>104</v>
       </c>
       <c r="AW16" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="AX16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AY16" t="s">
         <v>122</v>
       </c>
       <c r="AZ16" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="BA16" t="s">
         <v>126</v>
@@ -4779,7 +4764,7 @@
         <v>122</v>
       </c>
       <c r="Q17" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="R17" t="s">
         <v>103</v>
@@ -4791,7 +4776,7 @@
         <v>103</v>
       </c>
       <c r="W17" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="Z17" t="s">
         <v>122</v>
@@ -4809,24 +4794,24 @@
         <v>111</v>
       </c>
       <c r="AW17" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="AX17" t="s">
         <v>122</v>
       </c>
       <c r="AZ17" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="BA17" t="s">
         <v>127</v>
       </c>
       <c r="BB17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
       <c r="P18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q18" t="s">
         <v>111</v>
@@ -4847,13 +4832,7 @@
         <v>91</v>
       </c>
       <c r="AT18" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW18" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="BB18" t="s">
         <v>127</v>
@@ -4867,10 +4846,10 @@
         <v>111</v>
       </c>
       <c r="S19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="U19" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="AR19" t="s">
         <v>128</v>
@@ -4880,11 +4859,11 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25">
-      <c r="U20" t="s">
-        <v>122</v>
+      <c r="S20" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="21:21" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15" customHeight="1" spans="19:19" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5110,7 +5089,7 @@
         <v>106</v>
       </c>
       <c r="AN3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AO3" t="s">
         <v>94</v>
@@ -5131,7 +5110,7 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
@@ -5146,7 +5125,7 @@
         <v>129</v>
       </c>
       <c r="AZ3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BA3" t="s">
         <v>126</v>
@@ -5486,7 +5465,7 @@
         <v>54</v>
       </c>
       <c r="AZ5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="BA5" t="s">
         <v>41</v>
@@ -6474,7 +6453,7 @@
         <v>26</v>
       </c>
       <c r="AX13" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AZ13" t="s">
         <v>49</v>
@@ -6934,7 +6913,7 @@
         <v>20</v>
       </c>
       <c r="AO18" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="s">
         <v>32</v>
@@ -7641,7 +7620,7 @@
         <v>106</v>
       </c>
       <c r="AN3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="AO3" t="s">
         <v>94</v>
@@ -7662,7 +7641,7 @@
         <v>104</v>
       </c>
       <c r="AU3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AV3" t="s">
         <v>103</v>
@@ -7677,7 +7656,7 @@
         <v>129</v>
       </c>
       <c r="AZ3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BA3" t="s">
         <v>126</v>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="336">
   <si>
     <t>sl</t>
   </si>
@@ -388,24 +388,24 @@
     <t>2025-01-06</t>
   </si>
   <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
     <t>2024-12-27</t>
   </si>
   <si>
@@ -655,7 +655,7 @@
     <t>Eishalle Jesenice;OrelSt;VoicanCh;LegatKo;PreiserJu</t>
   </si>
   <si>
-    <t>Eishalle Gröden;BulovecMi;LazzeriAl;AbeltinoSi;ArlicMa</t>
+    <t>Eishalle Gröden;BulovecMi;PinieOm;AbeltinoSi;ArlicMa</t>
   </si>
   <si>
     <t>Eishalle Celje;LesniakBo;UnterwegerDo;JeramFi;TelesklavFa</t>
@@ -2100,7 +2100,7 @@
         <v>16</v>
       </c>
       <c r="AU1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(AU4:AU69,"&lt;&gt;")</f>
         <v>10</v>
       </c>
       <c r="AV1">
@@ -2152,11 +2152,11 @@
         <v>4</v>
       </c>
       <c r="BH1">
-        <f t="shared" ref="BH1:BQ1" si="1">COUNTIF(BH4:BH70,"&lt;&gt;")</f>
+        <f>COUNTIF(BH4:BH69,"&lt;&gt;")</f>
         <v>6</v>
       </c>
       <c r="BI1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="BI1:BQ1" si="1">COUNTIF(BI4:BI70,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="BJ1">
@@ -3775,7 +3775,7 @@
         <v>94</v>
       </c>
       <c r="BH9" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="BJ9" t="s">
         <v>92</v>
@@ -3894,7 +3894,7 @@
         <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -3954,9 +3954,6 @@
         <v>116</v>
       </c>
       <c r="BF10" s="7"/>
-      <c r="BH10" t="s">
-        <v>112</v>
-      </c>
       <c r="BJ10" t="s">
         <v>104</v>
       </c>
@@ -3990,7 +3987,7 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>92</v>
@@ -4002,7 +3999,7 @@
         <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4029,7 +4026,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4053,7 +4050,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4065,7 +4062,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4097,7 +4094,7 @@
       <c r="AT11" t="s">
         <v>90</v>
       </c>
-      <c r="AU11" t="s">
+      <c r="AU11" s="6" t="s">
         <v>94</v>
       </c>
       <c r="AV11" t="s">
@@ -4148,7 +4145,7 @@
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
@@ -4163,7 +4160,7 @@
         <v>112</v>
       </c>
       <c r="K12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>112</v>
@@ -4261,8 +4258,8 @@
       <c r="AT12" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="AU12" s="7" t="s">
-        <v>123</v>
+      <c r="AU12" t="s">
+        <v>126</v>
       </c>
       <c r="AV12" s="7" t="s">
         <v>109</v>
@@ -4393,7 +4390,7 @@
         <v>109</v>
       </c>
       <c r="AL13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4414,13 +4411,13 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
       </c>
       <c r="AU13" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="AV13" t="s">
         <v>112</v>
@@ -4512,7 +4509,7 @@
         <v>106</v>
       </c>
       <c r="Z14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
@@ -4530,10 +4527,10 @@
         <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
@@ -4558,9 +4555,6 @@
       </c>
       <c r="AT14" t="s">
         <v>115</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>120</v>
       </c>
       <c r="AV14" t="s">
         <v>119</v>
@@ -4595,7 +4589,7 @@
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>109</v>
@@ -4607,7 +4601,7 @@
         <v>114</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="S15" t="s">
         <v>106</v>
@@ -4631,10 +4625,13 @@
         <v>120</v>
       </c>
       <c r="AC15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AD15" t="s">
         <v>122</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>117</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
@@ -4702,7 +4699,7 @@
         <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U16" s="7" t="s">
         <v>104</v>
@@ -4723,10 +4720,10 @@
         <v>122</v>
       </c>
       <c r="AM16" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN16" t="s">
         <v>126</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>128</v>
       </c>
       <c r="AR16" t="s">
         <v>112</v>
@@ -4735,7 +4732,7 @@
         <v>104</v>
       </c>
       <c r="AW16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AX16" t="s">
         <v>120</v>
@@ -4747,7 +4744,7 @@
         <v>129</v>
       </c>
       <c r="BA16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
@@ -4782,7 +4779,7 @@
         <v>122</v>
       </c>
       <c r="AK17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AM17" t="s">
         <v>122</v>
@@ -4817,7 +4814,7 @@
         <v>111</v>
       </c>
       <c r="R18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S18" t="s">
         <v>112</v>
@@ -4852,7 +4849,7 @@
         <v>122</v>
       </c>
       <c r="AR19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AT19" t="s">
         <v>122</v>
@@ -5095,10 +5092,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>124</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>125</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -5128,7 +5125,7 @@
         <v>120</v>
       </c>
       <c r="BA3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BB3" t="s">
         <v>119</v>
@@ -5137,7 +5134,7 @@
         <v>122</v>
       </c>
       <c r="BD3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
@@ -6013,7 +6010,7 @@
         <v>50</v>
       </c>
       <c r="AR9" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AS9" t="s">
         <v>72</v>
@@ -7626,10 +7623,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>124</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>125</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -7659,7 +7656,7 @@
         <v>120</v>
       </c>
       <c r="BA3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BB3" t="s">
         <v>119</v>
@@ -7668,7 +7665,7 @@
         <v>122</v>
       </c>
       <c r="BD3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="336">
   <si>
     <t>sl</t>
   </si>
@@ -376,24 +376,27 @@
     <t>2024-11-26</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2025-01-02</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2025-01-06</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
     <t>2025-01-05</t>
   </si>
   <si>
-    <t>2025-01-02</t>
-  </si>
-  <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2025-01-06</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
     <t>2025-01-04</t>
   </si>
   <si>
@@ -403,9 +406,6 @@
     <t>2024-12-04</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2024-12-27</t>
   </si>
   <si>
@@ -547,7 +547,7 @@
     <t>Eishalle Sterzing;BrockAd;MoidlDa;FecchioFe;MattheyPh</t>
   </si>
   <si>
-    <t>Eishalle Ritten;BenvegnuAn;SoraperraSi;BrondiPa;WeissAl</t>
+    <t>Eishalle Ritten;BenvegnuAn;MoschenAn;BrondiPa;WeissAl</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;LazzeriAl;PinieOm;AbeltinoSi;BrondiPa</t>
@@ -568,7 +568,7 @@
     <t>KELIT Arena Zell am See;HolzerTo;KainbergerJu;TelesklavFa;WendnerMa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;Huber rRe;SnojTa;FleischmannLu;RivisAn</t>
+    <t>Eishalle Sterzing;Huber rRe;SnojTa;ArlicMa;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;ArlicMa;TelesklavFa</t>
@@ -667,7 +667,7 @@
     <t>Eishalle Celje;BulovecMi;HlavatyAl;LegatKo;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;HolzerTo;LegaSi;DivisDo;JägerRi</t>
+    <t>Eishalle Dornbirn;HolzerTo;Huber rRe;DivisDo;JägerRi</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;EggerTh;StefenelliFe;FecchioFe;PaceJa</t>
@@ -850,13 +850,13 @@
     <t>Eishalle Gröden;LehnerMo;MoidlDa;BrondiPa;MoidlMa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;EggerTh;Huber rRe;AbeltinoSi;GrisentiLu</t>
+    <t>Eishalle Sterzing;EggerTh;GiacomozziFe;AbeltinoSi;GrisentiLu</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;RuetzMa;SpiegelSe;DivisDo;JägerRi</t>
   </si>
   <si>
-    <t>Eishalle Cortina;GiacomozziFe;PinieOm;CristeliMa;CusinFe</t>
+    <t>Eishalle Cortina;LegaSi;PinieOm;CristeliMa;CusinFe</t>
   </si>
   <si>
     <t>Eishalle Zell am See;HlavatyAl;UnterwegerDo;LegatKo;SeewaldJe</t>
@@ -3518,7 +3518,7 @@
         <v>114</v>
       </c>
       <c r="AI8" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AJ8" t="s">
         <v>77</v>
@@ -3890,6 +3890,9 @@
       <c r="AH10" t="s">
         <v>115</v>
       </c>
+      <c r="AI10" t="s">
+        <v>119</v>
+      </c>
       <c r="AJ10" t="s">
         <v>111</v>
       </c>
@@ -3993,7 +3996,7 @@
         <v>92</v>
       </c>
       <c r="J11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
@@ -4061,8 +4064,11 @@
       <c r="AH11" t="s">
         <v>100</v>
       </c>
+      <c r="AI11" t="s">
+        <v>109</v>
+      </c>
       <c r="AJ11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4077,7 +4083,7 @@
         <v>91</v>
       </c>
       <c r="AO11" s="7" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="AP11" t="s">
         <v>115</v>
@@ -4205,7 +4211,7 @@
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AC12" s="7" t="s">
         <v>117</v>
@@ -4259,7 +4265,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AV12" s="7" t="s">
         <v>109</v>
@@ -4268,7 +4274,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4390,7 +4396,7 @@
         <v>109</v>
       </c>
       <c r="AL13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4411,7 +4417,7 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
@@ -4455,10 +4461,10 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>117</v>
@@ -4473,10 +4479,10 @@
         <v>122</v>
       </c>
       <c r="K14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="N14" t="s">
         <v>111</v>
@@ -4527,10 +4533,10 @@
         <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
@@ -4542,13 +4548,13 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AP14" t="s">
         <v>122</v>
       </c>
       <c r="AQ14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
@@ -4557,7 +4563,7 @@
         <v>115</v>
       </c>
       <c r="AV14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AW14" t="s">
         <v>91</v>
@@ -4580,7 +4586,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -4589,10 +4595,10 @@
         <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="P15" t="s">
         <v>109</v>
@@ -4601,7 +4607,7 @@
         <v>114</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="S15" t="s">
         <v>106</v>
@@ -4613,7 +4619,7 @@
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="W15" t="s">
         <v>114</v>
@@ -4624,8 +4630,11 @@
       <c r="AA15" t="s">
         <v>120</v>
       </c>
+      <c r="AB15" t="s">
+        <v>92</v>
+      </c>
       <c r="AC15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AD15" t="s">
         <v>122</v>
@@ -4643,7 +4652,7 @@
         <v>129</v>
       </c>
       <c r="AO15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP15" t="s">
         <v>104</v>
@@ -4699,7 +4708,7 @@
         <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U16" s="7" t="s">
         <v>104</v>
@@ -4720,10 +4729,13 @@
         <v>122</v>
       </c>
       <c r="AM16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AN16" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>103</v>
       </c>
       <c r="AR16" t="s">
         <v>112</v>
@@ -4732,7 +4744,7 @@
         <v>104</v>
       </c>
       <c r="AW16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AX16" t="s">
         <v>120</v>
@@ -4744,15 +4756,18 @@
         <v>129</v>
       </c>
       <c r="BA16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="O17" t="s">
         <v>122</v>
@@ -4779,7 +4794,7 @@
         <v>122</v>
       </c>
       <c r="AK17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AM17" t="s">
         <v>122</v>
@@ -4800,13 +4815,13 @@
         <v>122</v>
       </c>
       <c r="BA17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BB17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
       <c r="P18" t="s">
         <v>120</v>
       </c>
@@ -4814,7 +4829,7 @@
         <v>111</v>
       </c>
       <c r="R18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S18" t="s">
         <v>112</v>
@@ -4832,7 +4847,7 @@
         <v>120</v>
       </c>
       <c r="BB18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
@@ -4849,7 +4864,7 @@
         <v>122</v>
       </c>
       <c r="AR19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT19" t="s">
         <v>122</v>
@@ -4859,8 +4874,11 @@
       <c r="S20" t="s">
         <v>94</v>
       </c>
+      <c r="U20" t="s">
+        <v>109</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="19:19" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15" customHeight="1" spans="19:21" x14ac:dyDescent="0.25"/>
     <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5065,7 +5083,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5125,16 +5143,16 @@
         <v>120</v>
       </c>
       <c r="BA3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB3" t="s">
         <v>125</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
       </c>
       <c r="BC3" t="s">
         <v>122</v>
       </c>
       <c r="BD3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
@@ -5447,7 +5465,7 @@
         <v>70</v>
       </c>
       <c r="AU5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AV5" t="s">
         <v>36</v>
@@ -5638,7 +5656,7 @@
         <v>42</v>
       </c>
       <c r="BB6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="s">
         <v>7</v>
@@ -6022,7 +6040,7 @@
         <v>68</v>
       </c>
       <c r="AV9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AW9" t="s">
         <v>29</v>
@@ -6735,7 +6753,7 @@
         <v>49</v>
       </c>
       <c r="AU16" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AV16" t="s">
         <v>68</v>
@@ -6821,7 +6839,7 @@
         <v>70</v>
       </c>
       <c r="AS17" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="AT17" t="s">
         <v>45</v>
@@ -7596,7 +7614,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7656,16 +7674,16 @@
         <v>120</v>
       </c>
       <c r="BA3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB3" t="s">
         <v>125</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>119</v>
       </c>
       <c r="BC3" t="s">
         <v>122</v>
       </c>
       <c r="BD3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="333">
   <si>
     <t>sl</t>
   </si>
@@ -376,36 +376,36 @@
     <t>2024-11-26</t>
   </si>
   <si>
+    <t>2025-01-06</t>
+  </si>
+  <si>
+    <t>2025-01-02</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2025-01-02</t>
-  </si>
-  <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2025-01-06</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
     <t>2024-12-27</t>
   </si>
   <si>
@@ -556,7 +556,7 @@
     <t>Eishalle Jesenice;LesniakBo;UnterwegerDo;ArlicMa;JavornikBl</t>
   </si>
   <si>
-    <t>Eishalle Celje;OrelSt;WidmannFl;EislCh;StrimitzerDa</t>
+    <t>Eishalle Celje;BajtMi;OrelSt;EislCh;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;OrelSt;WidmannFl;StrimitzerDa;WuchererGe</t>
@@ -682,7 +682,7 @@
     <t>Eishalle Gröden;BenvegnuAn;LazzeriAl;CristeliMa;PaceJa</t>
   </si>
   <si>
-    <t>Eishalle Celje;BajtMi;BulovecMi;JavornikBl;MarkizetiGr</t>
+    <t>Eishalle Celje;BulovecMi;WidmannFl;JavornikBl;MarkizetiGr</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
@@ -1016,15 +1016,6 @@
   </si>
   <si>
     <t>% games per team</t>
-  </si>
-  <si>
-    <t>Data untill 7.12.2024</t>
-  </si>
-  <si>
-    <t>Expected assignmnets per country based on team %</t>
-  </si>
-  <si>
-    <t>Actual assigned games per country</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1163,6 +1154,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="mediumDashDot">
+        <color theme="8" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thick"/>
       <bottom/>
       <diagonal/>
@@ -1174,6 +1174,15 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom style="mediumDashDot">
+        <color theme="8" tint="-0.249977111117893"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1410,20 +1419,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1433,134 +1433,120 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="12" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1910,6 +1896,7 @@
     <col min="65" max="65" width="12" customWidth="1"/>
     <col min="66" max="66" width="11.85546875" customWidth="1"/>
     <col min="67" max="67" width="11.28515625" customWidth="1"/>
+    <col min="68" max="68" width="10.5703125" customWidth="1"/>
     <col min="69" max="69" width="11.140625" customWidth="1"/>
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
@@ -1929,7 +1916,7 @@
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E67,"&lt;&gt;")</f>
@@ -1972,8 +1959,8 @@
         <v>12</v>
       </c>
       <c r="O1">
-        <f>COUNTIF(O4:O68,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(O4:O67,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="P1">
         <f t="shared" ref="P1:BF1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
@@ -1984,8 +1971,8 @@
         <v>16</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R66,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(R4:R65,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
@@ -1997,7 +1984,7 @@
       </c>
       <c r="U1">
         <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
@@ -2009,7 +1996,7 @@
       </c>
       <c r="X1">
         <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y1">
         <f>COUNTIF(Y4:Y68,"&lt;&gt;")</f>
@@ -2024,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="AB1">
-        <f>COUNTIF(AB4:AB68,"&lt;&gt;")</f>
+        <f>COUNTIF(AB4:AB67,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AC1">
@@ -2045,14 +2032,14 @@
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG67,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AI1">
-        <f>COUNTIF(AI4:AI69,"&lt;&gt;")</f>
+        <f>COUNTIF(AI4:AI67,"&lt;&gt;")</f>
         <v>6</v>
       </c>
       <c r="AJ1">
@@ -2076,7 +2063,7 @@
         <v>13</v>
       </c>
       <c r="AO1">
-        <f>COUNTIF(AO4:AO67,"&lt;&gt;")</f>
+        <f>COUNTIF(AO4:AO66,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="AP1">
@@ -2791,7 +2778,7 @@
       <c r="BH4" t="s">
         <v>80</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BI4" s="7" t="s">
         <v>76</v>
       </c>
       <c r="BJ4" t="s">
@@ -2856,7 +2843,7 @@
       <c r="L5" t="s">
         <v>80</v>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="8"/>
       <c r="N5" t="s">
         <v>75</v>
       </c>
@@ -2920,7 +2907,7 @@
       <c r="AH5" t="s">
         <v>93</v>
       </c>
-      <c r="AI5" s="8" t="s">
+      <c r="AI5" s="9" t="s">
         <v>95</v>
       </c>
       <c r="AJ5" t="s">
@@ -2992,24 +2979,23 @@
       <c r="BF5" t="s">
         <v>77</v>
       </c>
-      <c r="BG5" s="8" t="s">
+      <c r="BG5" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BH5" t="s">
         <v>101</v>
       </c>
-      <c r="BI5" s="7"/>
       <c r="BJ5" t="s">
         <v>88</v>
       </c>
       <c r="BK5" t="s">
         <v>99</v>
       </c>
-      <c r="BL5" s="7"/>
+      <c r="BL5" s="8"/>
       <c r="BM5" t="s">
         <v>90</v>
       </c>
-      <c r="BN5" s="8" t="s">
+      <c r="BN5" s="9" t="s">
         <v>91</v>
       </c>
       <c r="BO5" t="s">
@@ -3089,7 +3075,7 @@
       <c r="W6" t="s">
         <v>86</v>
       </c>
-      <c r="X6" s="7" t="s">
+      <c r="X6" s="8" t="s">
         <v>104</v>
       </c>
       <c r="Y6" t="s">
@@ -3188,37 +3174,37 @@
       <c r="BD6" t="s">
         <v>98</v>
       </c>
-      <c r="BE6" s="8" t="s">
+      <c r="BE6" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="BF6" s="8" t="s">
+      <c r="BF6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="BG6" s="7" t="s">
+      <c r="BG6" s="8" t="s">
         <v>109</v>
       </c>
       <c r="BH6" t="s">
         <v>110</v>
       </c>
-      <c r="BJ6" s="8" t="s">
+      <c r="BJ6" s="9" t="s">
         <v>91</v>
       </c>
       <c r="BK6" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="BM6" s="8" t="s">
+      <c r="BM6" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BN6" t="s">
         <v>94</v>
       </c>
-      <c r="BO6" s="8" t="s">
+      <c r="BO6" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BP6" t="s">
         <v>94</v>
       </c>
-      <c r="BQ6" t="s">
+      <c r="BQ6" s="7" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3241,7 +3227,7 @@
       <c r="F7" t="s">
         <v>81</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="7" t="s">
         <v>93</v>
       </c>
       <c r="H7" t="s">
@@ -3289,7 +3275,7 @@
       <c r="W7" t="s">
         <v>84</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="7" t="s">
         <v>112</v>
       </c>
       <c r="Y7" t="s">
@@ -3301,7 +3287,7 @@
       <c r="AA7" t="s">
         <v>105</v>
       </c>
-      <c r="AB7" s="8" t="s">
+      <c r="AB7" s="9" t="s">
         <v>102</v>
       </c>
       <c r="AC7" t="s">
@@ -3322,13 +3308,13 @@
       <c r="AH7" t="s">
         <v>91</v>
       </c>
-      <c r="AI7" s="7" t="s">
+      <c r="AI7" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AJ7" t="s">
         <v>106</v>
       </c>
-      <c r="AK7" s="8" t="s">
+      <c r="AK7" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AL7" t="s">
@@ -3394,10 +3380,10 @@
       <c r="BF7" t="s">
         <v>102</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BG7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="BH7" s="8" t="s">
+      <c r="BH7" s="9" t="s">
         <v>115</v>
       </c>
       <c r="BJ7" t="s">
@@ -3415,7 +3401,7 @@
       <c r="BO7" t="s">
         <v>94</v>
       </c>
-      <c r="BP7" s="7" t="s">
+      <c r="BP7" s="8" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3438,7 +3424,6 @@
       <c r="F8" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="7"/>
       <c r="H8" t="s">
         <v>93</v>
       </c>
@@ -3451,7 +3436,7 @@
       <c r="K8" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="9" t="s">
         <v>113</v>
       </c>
       <c r="N8" t="s">
@@ -3484,9 +3469,6 @@
       <c r="W8" t="s">
         <v>108</v>
       </c>
-      <c r="X8" t="s">
-        <v>119</v>
-      </c>
       <c r="Y8" t="s">
         <v>79</v>
       </c>
@@ -3583,16 +3565,16 @@
       <c r="BD8" t="s">
         <v>88</v>
       </c>
-      <c r="BE8" s="7" t="s">
+      <c r="BE8" s="10" t="s">
         <v>120</v>
       </c>
       <c r="BF8" t="s">
         <v>95</v>
       </c>
-      <c r="BH8" s="7" t="s">
+      <c r="BH8" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="BJ8" s="7" t="s">
+      <c r="BJ8" s="8" t="s">
         <v>117</v>
       </c>
       <c r="BK8" t="s">
@@ -3604,7 +3586,7 @@
       <c r="BN8" t="s">
         <v>115</v>
       </c>
-      <c r="BO8" s="7" t="s">
+      <c r="BO8" s="8" t="s">
         <v>104</v>
       </c>
       <c r="BP8" t="s">
@@ -3627,19 +3609,19 @@
       <c r="E9" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>113</v>
       </c>
       <c r="L9" t="s">
@@ -3669,7 +3651,7 @@
       <c r="U9" t="s">
         <v>90</v>
       </c>
-      <c r="V9" s="8" t="s">
+      <c r="V9" s="9" t="s">
         <v>91</v>
       </c>
       <c r="W9" t="s">
@@ -3693,7 +3675,7 @@
       <c r="AD9" t="s">
         <v>115</v>
       </c>
-      <c r="AE9" s="8" t="s">
+      <c r="AE9" s="9" t="s">
         <v>91</v>
       </c>
       <c r="AF9" t="s">
@@ -3705,8 +3687,8 @@
       <c r="AH9" t="s">
         <v>118</v>
       </c>
-      <c r="AI9" t="s">
-        <v>122</v>
+      <c r="AI9" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="AJ9" s="6" t="s">
         <v>114</v>
@@ -3714,7 +3696,7 @@
       <c r="AK9" t="s">
         <v>106</v>
       </c>
-      <c r="AL9" s="8" t="s">
+      <c r="AL9" s="9" t="s">
         <v>102</v>
       </c>
       <c r="AM9" t="s">
@@ -3726,7 +3708,7 @@
       <c r="AO9" t="s">
         <v>87</v>
       </c>
-      <c r="AP9" s="8" t="s">
+      <c r="AP9" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AQ9" t="s">
@@ -3741,7 +3723,7 @@
       <c r="AT9" t="s">
         <v>79</v>
       </c>
-      <c r="AU9" s="8" t="s">
+      <c r="AU9" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AV9" t="s">
@@ -3765,16 +3747,16 @@
       <c r="BB9" t="s">
         <v>88</v>
       </c>
-      <c r="BC9" s="8" t="s">
+      <c r="BC9" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BD9" s="8" t="s">
+      <c r="BD9" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="BF9" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="BH9" t="s">
+      <c r="BH9" s="7" t="s">
         <v>112</v>
       </c>
       <c r="BJ9" t="s">
@@ -3783,30 +3765,30 @@
       <c r="BK9" t="s">
         <v>115</v>
       </c>
-      <c r="BM9" s="7" t="s">
+      <c r="BM9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="BN9" s="7" t="s">
+      <c r="BN9" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="BO9" t="s">
+      <c r="BO9" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="BP9" t="s">
+      <c r="BP9" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B10" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>91</v>
       </c>
       <c r="E10" t="s">
@@ -3833,10 +3815,10 @@
       <c r="N10" t="s">
         <v>121</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="9" t="s">
         <v>95</v>
       </c>
       <c r="Q10" t="s">
@@ -3851,7 +3833,7 @@
       <c r="T10" t="s">
         <v>81</v>
       </c>
-      <c r="U10" s="8" t="s">
+      <c r="U10" s="9" t="s">
         <v>102</v>
       </c>
       <c r="V10" t="s">
@@ -3860,10 +3842,10 @@
       <c r="W10" t="s">
         <v>88</v>
       </c>
-      <c r="Y10" s="8" t="s">
+      <c r="Y10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="Z10" s="8" t="s">
+      <c r="Z10" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AA10" t="s">
@@ -3890,22 +3872,19 @@
       <c r="AH10" t="s">
         <v>115</v>
       </c>
-      <c r="AI10" t="s">
-        <v>119</v>
-      </c>
       <c r="AJ10" t="s">
         <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
       </c>
-      <c r="AM10" s="8" t="s">
+      <c r="AM10" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AN10" s="8" t="s">
+      <c r="AN10" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AO10" t="s">
@@ -3914,13 +3893,13 @@
       <c r="AP10" t="s">
         <v>91</v>
       </c>
-      <c r="AQ10" s="8" t="s">
+      <c r="AQ10" s="9" t="s">
         <v>95</v>
       </c>
       <c r="AR10" t="s">
         <v>77</v>
       </c>
-      <c r="AS10" s="8" t="s">
+      <c r="AS10" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AT10" t="s">
@@ -3932,13 +3911,13 @@
       <c r="AV10" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AW10" s="8" t="s">
+      <c r="AW10" s="9" t="s">
         <v>102</v>
       </c>
       <c r="AX10" t="s">
         <v>88</v>
       </c>
-      <c r="AY10" s="8" t="s">
+      <c r="AY10" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AZ10" t="s">
@@ -3956,8 +3935,7 @@
       <c r="BD10" t="s">
         <v>116</v>
       </c>
-      <c r="BF10" s="7"/>
-      <c r="BJ10" t="s">
+      <c r="BJ10" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BK10" t="s">
@@ -3983,26 +3961,26 @@
       <c r="D11" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>102</v>
       </c>
       <c r="F11" t="s">
         <v>94</v>
       </c>
       <c r="H11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" t="s">
-        <v>125</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4022,14 +4000,14 @@
       <c r="S11" t="s">
         <v>93</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="T11" s="9" t="s">
         <v>95</v>
       </c>
       <c r="U11" t="s">
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4043,7 +4021,7 @@
       <c r="AA11" t="s">
         <v>114</v>
       </c>
-      <c r="AB11" s="7" t="s">
+      <c r="AB11" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AC11" t="s">
@@ -4053,7 +4031,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4064,11 +4042,8 @@
       <c r="AH11" t="s">
         <v>100</v>
       </c>
-      <c r="AI11" t="s">
-        <v>109</v>
-      </c>
       <c r="AJ11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4082,8 +4057,8 @@
       <c r="AN11" t="s">
         <v>91</v>
       </c>
-      <c r="AO11" s="7" t="s">
-        <v>119</v>
+      <c r="AO11" t="s">
+        <v>120</v>
       </c>
       <c r="AP11" t="s">
         <v>115</v>
@@ -4091,7 +4066,7 @@
       <c r="AQ11" t="s">
         <v>106</v>
       </c>
-      <c r="AR11" s="8" t="s">
+      <c r="AR11" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AS11" t="s">
@@ -4115,10 +4090,10 @@
       <c r="AY11" t="s">
         <v>91</v>
       </c>
-      <c r="AZ11" s="8" t="s">
+      <c r="AZ11" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BA11" s="8" t="s">
+      <c r="BA11" s="9" t="s">
         <v>91</v>
       </c>
       <c r="BB11" t="s">
@@ -4130,7 +4105,7 @@
       <c r="BD11" t="s">
         <v>118</v>
       </c>
-      <c r="BK11" s="7" t="s">
+      <c r="BK11" s="8" t="s">
         <v>104</v>
       </c>
       <c r="BM11" t="s">
@@ -4144,31 +4119,31 @@
       <c r="A12" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>92</v>
       </c>
       <c r="I12" t="s">
         <v>112</v>
       </c>
       <c r="K12" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>112</v>
       </c>
       <c r="N12" t="s">
@@ -4180,13 +4155,13 @@
       <c r="P12" t="s">
         <v>106</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="9" t="s">
         <v>107</v>
       </c>
       <c r="R12" t="s">
         <v>121</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="S12" s="9" t="s">
         <v>107</v>
       </c>
       <c r="T12" t="s">
@@ -4195,49 +4170,49 @@
       <c r="U12" t="s">
         <v>115</v>
       </c>
-      <c r="V12" s="7" t="s">
+      <c r="V12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="W12" s="8" t="s">
+      <c r="W12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Y12" s="7" t="s">
         <v>95</v>
       </c>
       <c r="Z12" t="s">
         <v>115</v>
       </c>
-      <c r="AA12" s="7" t="s">
+      <c r="AA12" s="8" t="s">
         <v>91</v>
       </c>
       <c r="AB12" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC12" s="8" t="s">
         <v>117</v>
       </c>
       <c r="AD12" t="s">
         <v>88</v>
       </c>
-      <c r="AE12" s="7" t="s">
+      <c r="AE12" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="AF12" s="7" t="s">
+      <c r="AF12" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AG12" s="7" t="s">
+      <c r="AG12" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AH12" s="7" t="s">
+      <c r="AH12" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AJ12" s="7" t="s">
         <v>92</v>
       </c>
       <c r="AK12" t="s">
         <v>95</v>
       </c>
-      <c r="AL12" s="7" t="s">
+      <c r="AL12" s="8" t="s">
         <v>92</v>
       </c>
       <c r="AM12" t="s">
@@ -4247,7 +4222,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4258,23 +4233,23 @@
       <c r="AR12" t="s">
         <v>102</v>
       </c>
-      <c r="AS12" s="7" t="s">
+      <c r="AS12" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AT12" s="8" t="s">
+      <c r="AT12" s="9" t="s">
         <v>100</v>
       </c>
       <c r="AU12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AV12" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AW12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AX12" t="s">
         <v>127</v>
-      </c>
-      <c r="AV12" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AW12" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>128</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4285,27 +4260,27 @@
       <c r="BA12" t="s">
         <v>102</v>
       </c>
-      <c r="BB12" s="8" t="s">
+      <c r="BB12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BC12" s="7" t="s">
+      <c r="BC12" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="BD12" s="7" t="s">
+      <c r="BD12" s="8" t="s">
         <v>103</v>
       </c>
       <c r="BK12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BN12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BM12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN12" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>92</v>
       </c>
       <c r="B13" t="s">
@@ -4320,8 +4295,8 @@
       <c r="E13" t="s">
         <v>106</v>
       </c>
-      <c r="F13" t="s">
-        <v>122</v>
+      <c r="F13" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="H13" t="s">
         <v>111</v>
@@ -4329,13 +4304,13 @@
       <c r="I13" t="s">
         <v>120</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="8" t="s">
         <v>112</v>
       </c>
       <c r="L13" t="s">
         <v>120</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="8" t="s">
         <v>109</v>
       </c>
       <c r="O13" t="s">
@@ -4372,19 +4347,19 @@
         <v>104</v>
       </c>
       <c r="AB13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="AC13" t="s">
         <v>109</v>
       </c>
-      <c r="AD13" s="7" t="s">
+      <c r="AD13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AE13" s="7" t="s">
         <v>120</v>
       </c>
       <c r="AF13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s">
         <v>103</v>
@@ -4392,11 +4367,11 @@
       <c r="AH13" t="s">
         <v>111</v>
       </c>
-      <c r="AK13" s="7" t="s">
+      <c r="AK13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AL13" t="s">
-        <v>126</v>
+      <c r="AL13" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4405,36 +4380,36 @@
         <v>115</v>
       </c>
       <c r="AO13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AP13" t="s">
         <v>120</v>
       </c>
-      <c r="AQ13" s="7" t="s">
+      <c r="AQ13" s="8" t="s">
         <v>117</v>
       </c>
       <c r="AR13" t="s">
         <v>106</v>
       </c>
-      <c r="AS13" t="s">
-        <v>126</v>
+      <c r="AS13" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
       </c>
-      <c r="AU13" t="s">
+      <c r="AU13" s="7" t="s">
         <v>120</v>
       </c>
       <c r="AV13" t="s">
         <v>112</v>
       </c>
       <c r="AW13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AX13" t="s">
         <v>118</v>
       </c>
-      <c r="AY13" s="7" t="s">
+      <c r="AY13" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AZ13" t="s">
@@ -4446,13 +4421,13 @@
       <c r="BB13" t="s">
         <v>102</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BC13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="BD13" t="s">
+      <c r="BD13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="BK13" t="s">
+      <c r="BK13" s="7" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4460,37 +4435,37 @@
       <c r="A14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="B14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>114</v>
       </c>
-      <c r="H14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" t="s">
-        <v>122</v>
-      </c>
-      <c r="K14" t="s">
-        <v>125</v>
-      </c>
-      <c r="L14" t="s">
-        <v>125</v>
+      <c r="H14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="N14" t="s">
         <v>111</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="P14" s="7" t="s">
+      <c r="P14" s="8" t="s">
         <v>104</v>
       </c>
       <c r="Q14" t="s">
@@ -4502,7 +4477,7 @@
       <c r="S14" t="s">
         <v>115</v>
       </c>
-      <c r="T14" s="7" t="s">
+      <c r="T14" s="8" t="s">
         <v>104</v>
       </c>
       <c r="U14" t="s">
@@ -4515,13 +4490,13 @@
         <v>106</v>
       </c>
       <c r="Z14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
       </c>
-      <c r="AB14" t="s">
-        <v>118</v>
+      <c r="AB14" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="AC14" t="s">
         <v>103</v>
@@ -4529,32 +4504,32 @@
       <c r="AD14" t="s">
         <v>112</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AF14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>126</v>
+        <v>125</v>
+      </c>
+      <c r="AH14" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
-      <c r="AM14" s="7" t="s">
+      <c r="AM14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AN14" s="7" t="s">
+      <c r="AN14" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AP14" t="s">
-        <v>122</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>125</v>
+        <v>119</v>
+      </c>
+      <c r="AQ14" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
@@ -4563,21 +4538,21 @@
         <v>115</v>
       </c>
       <c r="AV14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AW14" t="s">
         <v>91</v>
       </c>
-      <c r="AX14" s="7" t="s">
+      <c r="AX14" s="8" t="s">
         <v>92</v>
       </c>
       <c r="AY14" t="s">
-        <v>112</v>
-      </c>
-      <c r="AZ14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="BA14" s="7" t="s">
+      <c r="BA14" s="8" t="s">
         <v>104</v>
       </c>
       <c r="BB14" t="s">
@@ -4585,20 +4560,23 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>125</v>
+      <c r="A15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="N15" t="s">
-        <v>126</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>119</v>
+      <c r="N15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O15" t="s">
+        <v>111</v>
       </c>
       <c r="P15" t="s">
         <v>109</v>
@@ -4606,8 +4584,8 @@
       <c r="Q15" t="s">
         <v>114</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>119</v>
+      <c r="R15" t="s">
+        <v>109</v>
       </c>
       <c r="S15" t="s">
         <v>106</v>
@@ -4618,28 +4596,25 @@
       <c r="U15" t="s">
         <v>100</v>
       </c>
-      <c r="V15" t="s">
-        <v>125</v>
+      <c r="V15" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="W15" t="s">
         <v>114</v>
       </c>
-      <c r="Z15" s="7" t="s">
+      <c r="Z15" s="8" t="s">
         <v>109</v>
       </c>
       <c r="AA15" t="s">
         <v>120</v>
       </c>
-      <c r="AB15" t="s">
-        <v>92</v>
-      </c>
       <c r="AC15" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG15" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG15" s="7" t="s">
         <v>117</v>
       </c>
       <c r="AK15" t="s">
@@ -4651,19 +4626,19 @@
       <c r="AN15" t="s">
         <v>129</v>
       </c>
-      <c r="AO15" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP15" t="s">
+      <c r="AO15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP15" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AR15" s="7" t="s">
+      <c r="AR15" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AT15" t="s">
         <v>107</v>
       </c>
-      <c r="AV15" t="s">
+      <c r="AV15" s="7" t="s">
         <v>103</v>
       </c>
       <c r="AW15" t="s">
@@ -4681,105 +4656,99 @@
       <c r="BA15" t="s">
         <v>103</v>
       </c>
-      <c r="BB15" s="7" t="s">
+      <c r="BB15" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>103</v>
       </c>
-      <c r="O16" t="s">
-        <v>111</v>
+      <c r="O16" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="P16" t="s">
         <v>111</v>
       </c>
-      <c r="Q16" s="7" t="s">
+      <c r="Q16" s="8" t="s">
         <v>92</v>
       </c>
       <c r="R16" t="s">
+        <v>103</v>
+      </c>
+      <c r="S16" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="T16" t="s">
-        <v>126</v>
-      </c>
-      <c r="U16" s="7" t="s">
+      <c r="T16" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="U16" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="W16" s="7" t="s">
+      <c r="W16" s="8" t="s">
         <v>104</v>
       </c>
       <c r="Z16" t="s">
         <v>111</v>
       </c>
-      <c r="AA16" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC16" t="s">
+      <c r="AA16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC16" s="7" t="s">
         <v>92</v>
       </c>
       <c r="AK16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AM16" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN16" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>127</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>103</v>
       </c>
       <c r="AR16" t="s">
         <v>112</v>
       </c>
-      <c r="AT16" s="7" t="s">
+      <c r="AT16" s="8" t="s">
         <v>104</v>
       </c>
       <c r="AW16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AX16" t="s">
         <v>120</v>
       </c>
-      <c r="AY16" t="s">
-        <v>122</v>
+      <c r="AY16" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="AZ16" t="s">
         <v>129</v>
       </c>
       <c r="BA16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>125</v>
-      </c>
-      <c r="O17" t="s">
-        <v>122</v>
+      <c r="D17" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="P17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q17" t="s">
         <v>109</v>
       </c>
       <c r="R17" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
@@ -4790,14 +4759,14 @@
       <c r="W17" t="s">
         <v>109</v>
       </c>
-      <c r="Z17" t="s">
-        <v>122</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>122</v>
+      <c r="Z17" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM17" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="AR17" t="s">
         <v>129</v>
@@ -4805,31 +4774,34 @@
       <c r="AT17" t="s">
         <v>111</v>
       </c>
-      <c r="AW17" t="s">
+      <c r="AW17" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="AX17" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>122</v>
-      </c>
-      <c r="BA17" t="s">
-        <v>128</v>
+      <c r="AX17" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>124</v>
+      </c>
+      <c r="AZ17" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA17" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="BB17" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="P18" t="s">
+      <c r="P18" s="7" t="s">
         <v>120</v>
       </c>
       <c r="Q18" t="s">
         <v>111</v>
       </c>
-      <c r="R18" t="s">
-        <v>126</v>
+      <c r="R18" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="S18" t="s">
         <v>112</v>
@@ -4837,7 +4809,7 @@
       <c r="U18" t="s">
         <v>112</v>
       </c>
-      <c r="W18" t="s">
+      <c r="W18" s="7" t="s">
         <v>111</v>
       </c>
       <c r="AR18" t="s">
@@ -4846,35 +4818,32 @@
       <c r="AT18" t="s">
         <v>120</v>
       </c>
-      <c r="BB18" t="s">
-        <v>128</v>
+      <c r="BB18" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
-      <c r="Q19" t="s">
-        <v>122</v>
-      </c>
-      <c r="R19" t="s">
-        <v>111</v>
+      <c r="Q19" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="S19" t="s">
         <v>120</v>
       </c>
       <c r="U19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="AR19" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AT19" s="7" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25">
-      <c r="S20" t="s">
+      <c r="S20" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="U20" t="s">
+      <c r="U20" s="7" t="s">
         <v>109</v>
       </c>
     </row>
@@ -5083,7 +5052,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5110,10 +5079,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>123</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>124</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -5143,16 +5112,16 @@
         <v>120</v>
       </c>
       <c r="BA3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3" t="s">
         <v>126</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
@@ -5304,7 +5273,7 @@
         <v>11</v>
       </c>
       <c r="AX4" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="s">
         <v>47</v>
@@ -5474,7 +5443,7 @@
         <v>72</v>
       </c>
       <c r="AX5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AY5" t="s">
         <v>54</v>
@@ -5942,7 +5911,7 @@
         <v>17</v>
       </c>
       <c r="BB8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="s">
         <v>44</v>
@@ -6055,7 +6024,7 @@
         <v>21</v>
       </c>
       <c r="BB9" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="BC9" t="s">
         <v>38</v>
@@ -7614,7 +7583,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7641,10 +7610,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AQ3" t="s">
         <v>123</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>124</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -7674,16 +7643,16 @@
         <v>120</v>
       </c>
       <c r="BA3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3" t="s">
         <v>126</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
@@ -8263,7 +8232,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -8282,47 +8251,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11">
+      <c r="B1" s="12"/>
+      <c r="C1" s="13">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>184</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14">
+      <c r="B2" s="15"/>
+      <c r="C2" s="16">
         <f>C1*4</f>
         <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="18">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>736</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="21">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>318</v>
@@ -8350,67 +8319,67 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="21">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>23</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="23">
         <v>2</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="24">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="25">
         <f>B4/B3</f>
-        <v>0.14266304347826086</v>
-      </c>
-      <c r="I5" s="24">
+        <v>0.14402173913043478</v>
+      </c>
+      <c r="I5" s="26">
         <f>C2*G5</f>
         <v>113.23076923076924</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>105</v>
-      </c>
-      <c r="K5" s="25">
+        <v>106</v>
+      </c>
+      <c r="K5" s="27">
         <f>J5-I5</f>
-        <v>-8.23076923076924</v>
-      </c>
-      <c r="L5" s="26">
+        <v>-7.230769230769241</v>
+      </c>
+      <c r="L5" s="28">
         <f>K5/4</f>
-        <v>-2.05769230769231</v>
+        <v>-1.8076923076923102</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="21">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>295</v>
-      </c>
-      <c r="E6" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="23">
         <v>1</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="24">
         <f>F6/13</f>
         <v>0.07692307692307693</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="25">
         <f>B5/B3</f>
         <v>0.03125</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="26">
         <f>C2*G6</f>
         <v>56.61538461538462</v>
       </c>
@@ -8418,84 +8387,84 @@
         <f>B5</f>
         <v>23</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="27">
         <f>J6-I6</f>
         <v>-33.61538461538462</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="28">
         <f t="shared" ref="L6" si="0">K6/4</f>
         <v>-8.403846153846155</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="30">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>313</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="31" t="s">
         <v>326</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="32">
         <v>3</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="33">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="34">
         <f>(B5+B4)/B3</f>
-        <v>0.17391304347826086</v>
-      </c>
-      <c r="I7" s="24">
+        <v>0.17527173913043478</v>
+      </c>
+      <c r="I7" s="26">
         <f>C2*G7</f>
         <v>169.84615384615387</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>128</v>
-      </c>
-      <c r="K7" s="25">
+        <v>129</v>
+      </c>
+      <c r="K7" s="27">
         <f>J7-I7</f>
-        <v>-41.84615384615387</v>
-      </c>
-      <c r="L7" s="26">
+        <v>-40.84615384615387</v>
+      </c>
+      <c r="L7" s="28">
         <f>K7/4</f>
-        <v>-10.461538461538467</v>
+        <v>-10.211538461538467</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="36">
         <v>6</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="37">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="38">
         <f>B6/B3</f>
-        <v>0.4008152173913043</v>
-      </c>
-      <c r="I8" s="24">
+        <v>0.39945652173913043</v>
+      </c>
+      <c r="I8" s="26">
         <f>C2*G8</f>
         <v>339.69230769230774</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>295</v>
-      </c>
-      <c r="K8" s="25">
+        <v>294</v>
+      </c>
+      <c r="K8" s="27">
         <f>J8-I8</f>
-        <v>-44.692307692307736</v>
-      </c>
-      <c r="L8" s="26">
+        <v>-45.692307692307736</v>
+      </c>
+      <c r="L8" s="28">
         <f>K8/4</f>
-        <v>-11.173076923076934</v>
+        <v>-11.423076923076934</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8506,21 +8475,21 @@
         <f>SUM(B4:B7)</f>
         <v>736</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="36">
         <v>4</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="37">
         <f t="shared" si="1"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="38">
         <f>B7/B3</f>
         <v>0.42527173913043476</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="26">
         <f>C2*G9</f>
         <v>226.46153846153848</v>
       </c>
@@ -8528,32 +8497,32 @@
         <f>B7</f>
         <v>313</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="39">
         <f>J9-I9</f>
         <v>86.53846153846152</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="28">
         <f>K9/4</f>
         <v>21.63461538461538</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="I11" s="39">
+      <c r="I11" s="41">
         <f>SUM(I7:I9)</f>
         <v>736.0000000000001</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="35">
         <f>SUM(J7:J9)</f>
         <v>736</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="42">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="41">
+      <c r="L11" s="43">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
@@ -8571,10 +8540,10 @@
       <c r="H16" t="s">
         <v>321</v>
       </c>
-      <c r="I16" s="42" t="s">
+      <c r="I16" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="J16" s="42" t="s">
+      <c r="J16" s="44" t="s">
         <v>323</v>
       </c>
       <c r="K16" t="s">
@@ -8585,176 +8554,114 @@
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="45" t="s">
         <v>326</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="46">
         <v>3</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="47">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="46">
+      <c r="H17" s="48">
         <f>(B5+B4)/B3</f>
-        <v>0.17391304347826086</v>
-      </c>
-      <c r="I17" s="47">
+        <v>0.17527173913043478</v>
+      </c>
+      <c r="I17" s="49">
         <f>B3*G17</f>
         <v>169.84615384615387</v>
       </c>
-      <c r="J17" s="48">
+      <c r="J17" s="50">
         <f>B5+B4</f>
-        <v>128</v>
-      </c>
-      <c r="K17" s="49">
+        <v>129</v>
+      </c>
+      <c r="K17" s="51">
         <f>J17-I17</f>
-        <v>-41.84615384615387</v>
-      </c>
-      <c r="L17" s="26">
+        <v>-40.84615384615387</v>
+      </c>
+      <c r="L17" s="28">
         <f>K17/4</f>
-        <v>-10.461538461538467</v>
+        <v>-10.211538461538467</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="52" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="51">
+      <c r="F18" s="53">
         <v>6</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="54">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="55">
         <f>B6/B3</f>
-        <v>0.4008152173913043</v>
-      </c>
-      <c r="I18" s="54">
+        <v>0.39945652173913043</v>
+      </c>
+      <c r="I18" s="56">
         <f>B3*G18</f>
         <v>339.69230769230774</v>
       </c>
-      <c r="J18" s="55">
+      <c r="J18" s="57">
         <f>B6</f>
-        <v>295</v>
-      </c>
-      <c r="K18" s="56">
+        <v>294</v>
+      </c>
+      <c r="K18" s="58">
         <f>J18-I18</f>
-        <v>-44.692307692307736</v>
-      </c>
-      <c r="L18" s="26">
+        <v>-45.692307692307736</v>
+      </c>
+      <c r="L18" s="28">
         <f>K18/4</f>
-        <v>-11.173076923076934</v>
-      </c>
-      <c r="Q18" s="57"/>
+        <v>-11.423076923076934</v>
+      </c>
+      <c r="Q18" s="59"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="F19" s="59">
+      <c r="F19" s="61">
         <v>4</v>
       </c>
-      <c r="G19" s="60">
+      <c r="G19" s="62">
         <f t="shared" si="2"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="63">
         <f>B7/B3</f>
         <v>0.42527173913043476</v>
       </c>
-      <c r="I19" s="62">
+      <c r="I19" s="64">
         <f>B3*G19</f>
         <v>226.46153846153848</v>
       </c>
-      <c r="J19" s="63">
+      <c r="J19" s="65">
         <f>B7</f>
         <v>313</v>
       </c>
-      <c r="K19" s="64">
+      <c r="K19" s="66">
         <f>J19-I19</f>
         <v>86.53846153846152</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="28">
         <f>K19/4</f>
         <v>21.63461538461538</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="P24" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="65"/>
-      <c r="S24" s="65"/>
+    <row r="24" ht="15.75" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
     </row>
-    <row r="25" ht="75.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P25" s="66"/>
-      <c r="Q25" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="R25" s="68" t="s">
-        <v>335</v>
-      </c>
-      <c r="S25" s="69" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P26" s="70" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q26" s="33">
-        <v>247</v>
-      </c>
-      <c r="R26" s="33">
-        <v>212</v>
-      </c>
-      <c r="S26" s="19">
-        <f>R26-Q26</f>
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="27" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P27" s="70" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q27" s="33">
-        <v>124</v>
-      </c>
-      <c r="R27" s="33">
-        <v>92</v>
-      </c>
-      <c r="S27" s="19">
-        <f t="shared" ref="S27:S28" si="3">R27-Q27</f>
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" spans="16:19" x14ac:dyDescent="0.25">
-      <c r="P28" s="71" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q28" s="72">
-        <v>165</v>
-      </c>
-      <c r="R28" s="72">
-        <v>232</v>
-      </c>
-      <c r="S28" s="28">
-        <f t="shared" si="3"/>
-        <v>67</v>
-      </c>
-    </row>
+    <row r="25" ht="75.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="P24:S24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="373">
   <si>
     <t>sl</t>
   </si>
@@ -382,28 +382,55 @@
     <t>2025-01-02</t>
   </si>
   <si>
+    <t>2025-01-18</t>
+  </si>
+  <si>
     <t>2024-11-19</t>
   </si>
   <si>
+    <t>2025-01-21</t>
+  </si>
+  <si>
+    <t>2025-01-11</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
     <t>2024-12-01</t>
   </si>
   <si>
+    <t>2025-01-14</t>
+  </si>
+  <si>
     <t>2024-11-24</t>
   </si>
   <si>
     <t>2025-01-05</t>
   </si>
   <si>
+    <t>2025-01-16</t>
+  </si>
+  <si>
     <t>2025-01-04</t>
   </si>
   <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
     <t>2025-01-03</t>
   </si>
   <si>
     <t>2024-12-04</t>
   </si>
   <si>
-    <t>zbrisano</t>
+    <t>2025-01-12</t>
+  </si>
+  <si>
+    <t>2025-01-22</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
   </si>
   <si>
     <t>2024-12-27</t>
@@ -577,6 +604,36 @@
     <t>Eishalle Jesenice;OrelSt;VoicanCh;PreiserJu;WuchererGe</t>
   </si>
   <si>
+    <t>Eishalle Dornbirn;BenvegnuAn;GiacomozziFe;BrondiPa;DivisDo</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;BajtMi;MeixnerSe;MarkizetiGr;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;BrockAd;WenuschHe;WeissAl;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;LehnerMo;WidmannFl;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;HolzerTo;Huber rRe;JägerRi;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;EggerTh;MoschenAn;ScalzeriAl;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;Huber rRe;RuetzMa;RinkerDa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;SnojTa;WidmannFl;JavornikBl;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;MetzingerFi;SnojTa;KnezRo;MarkizetiGr</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -688,6 +745,24 @@
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
   </si>
   <si>
+    <t>Sportpark Kitzbühel;KainbergerJu;OrelSt;SeewaldJe;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;MeixnerSe;VoicanCh;JeramFi;LegatKo</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;BrockAd;BulovecMi;EislCh;WuchererGe</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;HolzerTo;SpiegelSe;JägerRi;RivisAn</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;BenvegnuAn;PirasAn;AbeltinoSi;PaceJa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;LazzeriAl;RuetzMa;AbeltinoSi;RinkerDa</t>
+  </si>
+  <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
   </si>
   <si>
@@ -784,6 +859,21 @@
     <t>Eishalle Ritten;SoraperraSi;StefenelliFe;FecchioFe;GrisentiLu</t>
   </si>
   <si>
+    <t>Eishalle Meran;BulovecMi;SoraperraSi;ArlicMa;CristeliMa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;LegaSi;VirtaTu;CusinFe;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;HlavatyAl;MetzingerFi;KnezRo;LegatKo</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;PinieOm;StefenelliFe;BrondiPa;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BajtMi;LesniakBo;JavornikBl;WuchererGe</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -874,6 +964,21 @@
     <t>Sportpark Kitzbühel;RuetzMa;SpiegelSe;JägerRi;StrimitzerDa</t>
   </si>
   <si>
+    <t>Eishalle Dornbirn;MoidlDa;SpiegelSe;MattheyPh;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;RivisFe;SoraperraSi;AbeltinoSi;PaceJa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;KainbergerJu;VoicanCh;PreiserJu;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;GiacomozziFe;RivisFe;FecchioFe;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;RivisAn</t>
+  </si>
+  <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
   </si>
   <si>
@@ -940,6 +1045,15 @@
     <t>Eishalle Celje;HlavatyAl;PirasAn;PreiserJu;ScalzeriAl</t>
   </si>
   <si>
+    <t>Eishalle Zell am See;HlavatyAl;LebenJa;PreiserJu;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;LebenJa;LesniakBo;FecchioFe;JeramFi</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;HolzerTo;LegaSi;CusinFe;DivisDo</t>
+  </si>
+  <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
   </si>
   <si>
@@ -961,6 +1075,12 @@
     <t>Eishalle Cortina;LebenJa;MoschenAn;CristeliMa;JeramFi</t>
   </si>
   <si>
+    <t>Eishalle Cortina;LazzeriAl;OrelSt;CristeliMa;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;EggerTh;VirtaTu;FormaioniTh;ScalzeriAl</t>
+  </si>
+  <si>
     <t>vse delegirane tekme</t>
   </si>
   <si>
@@ -1012,7 +1132,7 @@
     <t>kontrola</t>
   </si>
   <si>
-    <t>till 6.1.2025</t>
+    <t>till 23.1.2025</t>
   </si>
   <si>
     <t>% games per team</t>
@@ -1134,7 +1254,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1182,6 +1302,15 @@
       <top style="thick"/>
       <bottom style="mediumDashDot">
         <color theme="8" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="mediumDashDot">
+        <color theme="4" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1423,7 +1552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1435,116 +1564,117 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1904,27 +2034,27 @@
     <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F69,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G1">
         <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
@@ -1932,23 +2062,23 @@
       </c>
       <c r="H1">
         <f>COUNTIF(H4:H68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I69,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J68,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M1">
         <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
@@ -1956,43 +2086,43 @@
       </c>
       <c r="N1">
         <f>COUNTIF(N4:N68,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O1">
         <f>COUNTIF(O4:O67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P1">
         <f t="shared" ref="P1:BF1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q68,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1">
         <f>COUNTIF(R4:R65,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U1">
         <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W1">
         <f>COUNTIF(W4:W69,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="X1">
         <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
@@ -2004,143 +2134,143 @@
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA1">
         <f>COUNTIF(AA4:AA66,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB67,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF64,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG67,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI67,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ1">
         <f>COUNTIF(AJ4:AJ64,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK1">
         <f>COUNTIF(AK4:AK65,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN65,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO66,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP1">
         <f>COUNTIF(AP4:AP67,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ1">
         <f>COUNTIF(AQ4:AQ68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR1">
         <f>COUNTIF(AR4:AR63,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS69,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT1">
         <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU1">
         <f>COUNTIF(AU4:AU69,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV65,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW1">
         <f>COUNTIF(AW4:AW65,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ65,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB69,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BE1">
         <f>COUNTIF(BE4:BE67,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG1">
         <f>COUNTIF(BG4:BG66,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BH1">
         <f>COUNTIF(BH4:BH69,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BI1">
         <f t="shared" ref="BI1:BQ1" si="1">COUNTIF(BI4:BI70,"&lt;&gt;")</f>
@@ -2148,11 +2278,11 @@
       </c>
       <c r="BJ1">
         <f>COUNTIF(BJ4:BJ68,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BL1">
         <f t="shared" si="1"/>
@@ -2160,19 +2290,19 @@
       </c>
       <c r="BM1">
         <f t="shared" ref="BM1" si="2">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BO1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BP1">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BQ1">
         <f t="shared" si="1"/>
@@ -3571,6 +3701,9 @@
       <c r="BF8" t="s">
         <v>95</v>
       </c>
+      <c r="BG8" t="s">
+        <v>121</v>
+      </c>
       <c r="BH8" s="8" t="s">
         <v>92</v>
       </c>
@@ -3578,7 +3711,7 @@
         <v>117</v>
       </c>
       <c r="BK8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BM8" t="s">
         <v>114</v>
@@ -3753,8 +3886,14 @@
       <c r="BD9" s="9" t="s">
         <v>102</v>
       </c>
+      <c r="BE9" t="s">
+        <v>123</v>
+      </c>
       <c r="BF9" s="7" t="s">
         <v>94</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>124</v>
       </c>
       <c r="BH9" s="7" t="s">
         <v>112</v>
@@ -3813,7 +3952,7 @@
         <v>114</v>
       </c>
       <c r="N10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>102</v>
@@ -3872,11 +4011,14 @@
       <c r="AH10" t="s">
         <v>115</v>
       </c>
+      <c r="AI10" t="s">
+        <v>125</v>
+      </c>
       <c r="AJ10" t="s">
         <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -3935,6 +4077,15 @@
       <c r="BD10" t="s">
         <v>116</v>
       </c>
+      <c r="BE10" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>121</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>121</v>
+      </c>
       <c r="BJ10" s="7" t="s">
         <v>104</v>
       </c>
@@ -3947,8 +4098,14 @@
       <c r="BN10" t="s">
         <v>112</v>
       </c>
+      <c r="BO10" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>123</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -3968,19 +4125,19 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>92</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4007,7 +4164,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4031,7 +4188,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4042,8 +4199,11 @@
       <c r="AH11" t="s">
         <v>100</v>
       </c>
+      <c r="AI11" t="s">
+        <v>130</v>
+      </c>
       <c r="AJ11" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4105,6 +4265,12 @@
       <c r="BD11" t="s">
         <v>118</v>
       </c>
+      <c r="BF11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>121</v>
+      </c>
       <c r="BK11" s="8" t="s">
         <v>104</v>
       </c>
@@ -4114,8 +4280,14 @@
       <c r="BN11" t="s">
         <v>120</v>
       </c>
+      <c r="BO11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>125</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -4126,7 +4298,7 @@
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
@@ -4140,8 +4312,11 @@
       <c r="I12" t="s">
         <v>112</v>
       </c>
+      <c r="J12" t="s">
+        <v>130</v>
+      </c>
       <c r="K12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>112</v>
@@ -4159,7 +4334,7 @@
         <v>107</v>
       </c>
       <c r="R12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S12" s="9" t="s">
         <v>107</v>
@@ -4206,6 +4381,9 @@
       <c r="AH12" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="AI12" t="s">
+        <v>132</v>
+      </c>
       <c r="AJ12" s="7" t="s">
         <v>92</v>
       </c>
@@ -4240,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="AV12" s="8" t="s">
         <v>109</v>
@@ -4249,7 +4427,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4268,6 +4446,9 @@
       </c>
       <c r="BD12" s="8" t="s">
         <v>103</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>125</v>
       </c>
       <c r="BK12" t="s">
         <v>119</v>
@@ -4304,6 +4485,9 @@
       <c r="I13" t="s">
         <v>120</v>
       </c>
+      <c r="J13" t="s">
+        <v>132</v>
+      </c>
       <c r="K13" s="8" t="s">
         <v>112</v>
       </c>
@@ -4367,11 +4551,14 @@
       <c r="AH13" t="s">
         <v>111</v>
       </c>
+      <c r="AJ13" t="s">
+        <v>124</v>
+      </c>
       <c r="AK13" s="8" t="s">
         <v>109</v>
       </c>
       <c r="AL13" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4380,7 +4567,7 @@
         <v>115</v>
       </c>
       <c r="AO13" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AP13" t="s">
         <v>120</v>
@@ -4392,7 +4579,7 @@
         <v>106</v>
       </c>
       <c r="AS13" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
@@ -4430,16 +4617,22 @@
       <c r="BK13" s="7" t="s">
         <v>103</v>
       </c>
+      <c r="BM13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>125</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>128</v>
+      <c r="B14" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>117</v>
@@ -4447,6 +4640,9 @@
       <c r="E14" t="s">
         <v>114</v>
       </c>
+      <c r="F14" t="s">
+        <v>121</v>
+      </c>
       <c r="H14" s="7" t="s">
         <v>119</v>
       </c>
@@ -4454,10 +4650,10 @@
         <v>119</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N14" t="s">
         <v>111</v>
@@ -4490,7 +4686,7 @@
         <v>106</v>
       </c>
       <c r="Z14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
@@ -4504,18 +4700,27 @@
       <c r="AD14" t="s">
         <v>112</v>
       </c>
+      <c r="AE14" t="s">
+        <v>125</v>
+      </c>
       <c r="AF14" s="7" t="s">
         <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AH14" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>130</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
+      <c r="AL14" t="s">
+        <v>121</v>
+      </c>
       <c r="AM14" s="8" t="s">
         <v>92</v>
       </c>
@@ -4523,22 +4728,28 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AP14" t="s">
         <v>119</v>
       </c>
       <c r="AQ14" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
       </c>
+      <c r="AS14" t="s">
+        <v>135</v>
+      </c>
       <c r="AT14" t="s">
         <v>115</v>
       </c>
+      <c r="AU14" t="s">
+        <v>123</v>
+      </c>
       <c r="AV14" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AW14" t="s">
         <v>91</v>
@@ -4547,7 +4758,7 @@
         <v>92</v>
       </c>
       <c r="AY14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AZ14" s="8" t="s">
         <v>104</v>
@@ -4556,15 +4767,30 @@
         <v>104</v>
       </c>
       <c r="BB14" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC14" t="s">
         <v>121</v>
       </c>
+      <c r="BD14" t="s">
+        <v>121</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>135</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -4572,8 +4798,23 @@
       <c r="E15" s="8" t="s">
         <v>92</v>
       </c>
+      <c r="F15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I15" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" t="s">
+        <v>124</v>
+      </c>
+      <c r="L15" t="s">
+        <v>124</v>
+      </c>
       <c r="N15" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="O15" t="s">
         <v>111</v>
@@ -4597,7 +4838,7 @@
         <v>100</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="W15" t="s">
         <v>114</v>
@@ -4608,23 +4849,38 @@
       <c r="AA15" t="s">
         <v>120</v>
       </c>
+      <c r="AB15" t="s">
+        <v>137</v>
+      </c>
       <c r="AC15" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AD15" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="AE15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>125</v>
+      </c>
       <c r="AG15" s="7" t="s">
         <v>117</v>
       </c>
+      <c r="AH15" t="s">
+        <v>125</v>
+      </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
+      <c r="AL15" t="s">
+        <v>124</v>
+      </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AO15" s="7" t="s">
         <v>103</v>
@@ -4632,12 +4888,21 @@
       <c r="AP15" s="7" t="s">
         <v>104</v>
       </c>
+      <c r="AQ15" t="s">
+        <v>135</v>
+      </c>
       <c r="AR15" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="AS15" t="s">
+        <v>121</v>
+      </c>
       <c r="AT15" t="s">
         <v>107</v>
       </c>
+      <c r="AU15" t="s">
+        <v>124</v>
+      </c>
       <c r="AV15" s="7" t="s">
         <v>103</v>
       </c>
@@ -4648,7 +4913,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -4659,14 +4924,47 @@
       <c r="BB15" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="BC15" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" t="s">
+        <v>125</v>
+      </c>
       <c r="D16" t="s">
         <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>103</v>
       </c>
+      <c r="H16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I16" t="s">
+        <v>124</v>
+      </c>
+      <c r="K16" t="s">
+        <v>132</v>
+      </c>
+      <c r="L16" t="s">
+        <v>132</v>
+      </c>
+      <c r="N16" t="s">
+        <v>137</v>
+      </c>
       <c r="O16" s="7" t="s">
         <v>119</v>
       </c>
@@ -4683,11 +4981,14 @@
         <v>109</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="U16" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="V16" t="s">
+        <v>124</v>
+      </c>
       <c r="W16" s="8" t="s">
         <v>104</v>
       </c>
@@ -4697,17 +4998,41 @@
       <c r="AA16" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="AB16" t="s">
+        <v>130</v>
+      </c>
       <c r="AC16" s="7" t="s">
         <v>92</v>
       </c>
+      <c r="AD16" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>130</v>
+      </c>
       <c r="AK16" t="s">
         <v>119</v>
       </c>
       <c r="AM16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AN16" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>123</v>
       </c>
       <c r="AR16" t="s">
         <v>112</v>
@@ -4715,8 +5040,11 @@
       <c r="AT16" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="AV16" t="s">
+        <v>123</v>
+      </c>
       <c r="AW16" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="AX16" t="s">
         <v>120</v>
@@ -4725,21 +5053,30 @@
         <v>119</v>
       </c>
       <c r="AZ16" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="BA16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>132</v>
+      </c>
       <c r="D17" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
+      </c>
+      <c r="N17" t="s">
+        <v>130</v>
+      </c>
+      <c r="O17" t="s">
+        <v>121</v>
       </c>
       <c r="P17" t="s">
         <v>119</v>
@@ -4748,32 +5085,59 @@
         <v>109</v>
       </c>
       <c r="R17" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
       </c>
+      <c r="T17" t="s">
+        <v>125</v>
+      </c>
       <c r="U17" t="s">
         <v>103</v>
       </c>
+      <c r="V17" t="s">
+        <v>130</v>
+      </c>
       <c r="W17" t="s">
         <v>109</v>
       </c>
       <c r="Z17" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="AA17" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>132</v>
+      </c>
       <c r="AK17" s="7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AM17" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="AN17" t="s">
+        <v>121</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>124</v>
+      </c>
       <c r="AR17" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
       </c>
+      <c r="AV17" t="s">
+        <v>124</v>
+      </c>
       <c r="AW17" s="7" t="s">
         <v>94</v>
       </c>
@@ -4781,19 +5145,28 @@
         <v>119</v>
       </c>
       <c r="AY17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AZ17" s="7" t="s">
         <v>119</v>
       </c>
       <c r="BA17" s="7" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="BB17" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>135</v>
+      </c>
+      <c r="O18" t="s">
+        <v>125</v>
+      </c>
       <c r="P18" s="7" t="s">
         <v>120</v>
       </c>
@@ -4806,50 +5179,175 @@
       <c r="S18" t="s">
         <v>112</v>
       </c>
+      <c r="T18" t="s">
+        <v>130</v>
+      </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
+      <c r="V18" t="s">
+        <v>132</v>
+      </c>
       <c r="W18" s="7" t="s">
         <v>111</v>
       </c>
+      <c r="Z18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>125</v>
+      </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
       <c r="AT18" t="s">
         <v>120</v>
       </c>
+      <c r="AW18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>136</v>
+      </c>
       <c r="BB18" s="7" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="P19" t="s">
+        <v>124</v>
+      </c>
       <c r="Q19" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="R19" t="s">
+        <v>124</v>
+      </c>
       <c r="S19" t="s">
         <v>120</v>
       </c>
       <c r="U19" t="s">
         <v>119</v>
       </c>
+      <c r="W19" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>130</v>
+      </c>
       <c r="AR19" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="AT19" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="AW19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>124</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>137</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="17:46" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>130</v>
+      </c>
+      <c r="R20" t="s">
+        <v>132</v>
+      </c>
       <c r="S20" s="7" t="s">
         <v>94</v>
       </c>
       <c r="U20" s="7" t="s">
         <v>109</v>
       </c>
+      <c r="W20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>121</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>127</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>130</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="19:21" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+      <c r="S21" t="s">
+        <v>137</v>
+      </c>
+      <c r="U21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="19:46" x14ac:dyDescent="0.25">
+      <c r="S22" t="s">
+        <v>130</v>
+      </c>
+      <c r="U22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="19:21" x14ac:dyDescent="0.25"/>
     <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4908,7 +5406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BD42"/>
+  <dimension ref="A3:BN42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -4954,7 +5452,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -5052,7 +5550,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5061,7 +5559,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK3" t="s">
         <v>115</v>
@@ -5079,10 +5577,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AQ3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -5106,25 +5604,55 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AZ3" t="s">
         <v>120</v>
       </c>
       <c r="BA3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="BB3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="BC3" t="s">
         <v>119</v>
       </c>
       <c r="BD3" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -5293,8 +5821,38 @@
       <c r="BD4" t="s">
         <v>47</v>
       </c>
+      <c r="BE4" t="s">
+        <v>17</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>71</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>71</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>39</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>44</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5463,8 +6021,38 @@
       <c r="BD5" t="s">
         <v>50</v>
       </c>
+      <c r="BE5" t="s">
+        <v>31</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>46</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>63</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>54</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>44</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>49</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>54</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5633,8 +6221,38 @@
       <c r="BD6" t="s">
         <v>52</v>
       </c>
+      <c r="BE6" t="s">
+        <v>22</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>62</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>65</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>53</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -5803,13 +6421,43 @@
       <c r="BD7" t="s">
         <v>43</v>
       </c>
+      <c r="BE7" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>48</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>48</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>55</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>55</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -5833,7 +6481,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -5916,8 +6564,26 @@
       <c r="BC8" t="s">
         <v>44</v>
       </c>
+      <c r="BG8" t="s">
+        <v>41</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>46</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>58</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>56</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>17</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -5931,7 +6597,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6029,8 +6695,26 @@
       <c r="BC9" t="s">
         <v>38</v>
       </c>
+      <c r="BG9" t="s">
+        <v>47</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>50</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>6</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>45</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>33</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -6142,8 +6826,26 @@
       <c r="BC10" t="s">
         <v>35</v>
       </c>
+      <c r="BG10" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>12</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>69</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>66</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -6255,8 +6957,26 @@
       <c r="BC11" t="s">
         <v>53</v>
       </c>
+      <c r="BG11" t="s">
+        <v>43</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>51</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>43</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>25</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>37</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -6282,7 +7002,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -6353,8 +7073,23 @@
       <c r="BC12" t="s">
         <v>18</v>
       </c>
+      <c r="BG12" t="s">
+        <v>6</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>38</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>68</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -6451,8 +7186,23 @@
       <c r="BC13" t="s">
         <v>29</v>
       </c>
+      <c r="BG13" t="s">
+        <v>18</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>26</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>29</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -6549,8 +7299,23 @@
       <c r="BC14" t="s">
         <v>19</v>
       </c>
+      <c r="BG14" t="s">
+        <v>7</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>35</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>15</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>22</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -6647,8 +7412,23 @@
       <c r="BC15" t="s">
         <v>20</v>
       </c>
+      <c r="BG15" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>51</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -6739,8 +7519,23 @@
       <c r="BC16" t="s">
         <v>49</v>
       </c>
+      <c r="BG16" t="s">
+        <v>70</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>34</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>41</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>31</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -6831,8 +7626,23 @@
       <c r="BC17" t="s">
         <v>45</v>
       </c>
+      <c r="BG17" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>18</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>50</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>34</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -6923,8 +7733,23 @@
       <c r="BC18" t="s">
         <v>66</v>
       </c>
+      <c r="BG18" t="s">
+        <v>65</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>32</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>52</v>
+      </c>
+      <c r="BM18" t="s">
+        <v>19</v>
+      </c>
+      <c r="BN18" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -7015,8 +7840,23 @@
       <c r="BC19" t="s">
         <v>55</v>
       </c>
+      <c r="BG19" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ19" t="s">
+        <v>37</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>62</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -7083,8 +7923,17 @@
       <c r="BC20" t="s">
         <v>68</v>
       </c>
+      <c r="BG20" t="s">
+        <v>68</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -7151,8 +8000,17 @@
       <c r="BC21" t="s">
         <v>33</v>
       </c>
+      <c r="BG21" t="s">
+        <v>9</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>11</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -7219,8 +8077,17 @@
       <c r="BC22" t="s">
         <v>52</v>
       </c>
+      <c r="BG22" t="s">
+        <v>52</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>19</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -7287,8 +8154,17 @@
       <c r="BC23" t="s">
         <v>30</v>
       </c>
+      <c r="BG23" t="s">
+        <v>42</v>
+      </c>
+      <c r="BK23" t="s">
+        <v>12</v>
+      </c>
+      <c r="BM23" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -7310,8 +8186,14 @@
       <c r="BC24" t="s">
         <v>9</v>
       </c>
+      <c r="BK24" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM24" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -7333,8 +8215,14 @@
       <c r="BC25" t="s">
         <v>24</v>
       </c>
+      <c r="BK25" t="s">
+        <v>47</v>
+      </c>
+      <c r="BM25" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -7356,8 +8244,14 @@
       <c r="BC26" t="s">
         <v>40</v>
       </c>
+      <c r="BK26" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM26" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -7379,8 +8273,14 @@
       <c r="BC27" t="s">
         <v>12</v>
       </c>
+      <c r="BK27" t="s">
+        <v>42</v>
+      </c>
+      <c r="BM27" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="46:55" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="46:65" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7402,7 +8302,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BD14"/>
+  <dimension ref="A3:BN14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -7485,7 +8385,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -7583,7 +8483,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -7592,7 +8492,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK3" t="s">
         <v>115</v>
@@ -7610,10 +8510,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AQ3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -7637,589 +8537,712 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AZ3" t="s">
         <v>120</v>
       </c>
       <c r="BA3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="BB3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="BC3" t="s">
         <v>119</v>
       </c>
       <c r="BD3" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="L4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="M4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="N4" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="O4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="P4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="Q4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="R4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="S4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="T4" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="U4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="V4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="W4" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="X4" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="Y4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Z4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AA4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="AB4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="AC4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="AD4" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="AE4" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="AF4" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AG4" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="AH4" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="AI4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="AJ4" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="AK4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="AL4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>180</v>
+      </c>
+      <c r="AP4" t="s">
         <v>168</v>
       </c>
-      <c r="AM4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>170</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>159</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AR4" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AS4" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="AT4" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AU4" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="AV4" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="AW4" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AX4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="AY4" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="AZ4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="BA4" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="BB4" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="BC4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="BD4" t="s">
-        <v>185</v>
+        <v>194</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>195</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>196</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>197</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>198</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>199</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>200</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>201</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>202</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>203</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>204</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D5" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="F5" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="G5" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="H5" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="K5" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="L5" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="N5" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="P5" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="R5" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="T5" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="U5" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="V5" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="W5" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="Y5" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="Z5" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="AB5" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="AD5" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="AE5" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="AF5" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="AI5" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="AK5" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="AL5" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="AM5" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="AN5" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="AO5" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="AR5" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="AS5" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="AT5" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="AU5" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="AV5" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="AW5" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="AX5" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="AZ5" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="BA5" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="BB5" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="BC5" t="s">
-        <v>222</v>
+        <v>241</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>242</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>243</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>244</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>245</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>247</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="F6" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="G6" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="H6" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="K6" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="L6" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="N6" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="P6" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="T6" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="V6" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="W6" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="Y6" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="Z6" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="AB6" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="AD6" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="AE6" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="AI6" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="AK6" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="AM6" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="AN6" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="AO6" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="AS6" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="AT6" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="AU6" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="AV6" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="AW6" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="AX6" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="AZ6" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="BA6" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="BB6" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="BC6" t="s">
-        <v>254</v>
+        <v>279</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>281</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>282</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>283</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>284</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="F7" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="G7" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="H7" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="K7" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="L7" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="N7" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="T7" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="V7" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="W7" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="Y7" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="Z7" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="AB7" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="AD7" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="AE7" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="AI7" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="AK7" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="AM7" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="AN7" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="AO7" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="AS7" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="AT7" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="AU7" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="AV7" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AW7" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="AX7" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="AZ7" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="BC7" t="s">
-        <v>284</v>
+        <v>314</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>315</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>316</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>317</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>318</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>319</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="D8" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="F8" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="G8" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="H8" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="K8" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="L8" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="V8" t="s">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="W8" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="Y8" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="AB8" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="AD8" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="AE8" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="AI8" t="s">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="AK8" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="AM8" t="s">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="AO8" t="s">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="AT8" t="s">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="AU8" t="s">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="AW8" t="s">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="AZ8" t="s">
-        <v>305</v>
+        <v>340</v>
       </c>
       <c r="BC8" t="s">
-        <v>306</v>
+        <v>341</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>342</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>343</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>344</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:55" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="L9" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
       <c r="AD9" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="AE9" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="AK9" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="AT9" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="BC9" t="s">
-        <v>313</v>
+        <v>351</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>352</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>353</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="46:55" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="46:65" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8251,410 +9274,410 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13">
+      <c r="A1" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>184</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="16">
+      <c r="A2" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17">
         <f>C1*4</f>
-        <v>736</v>
+        <v>860</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="B3" s="18">
+      <c r="A3" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="19">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>736</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+        <v>860</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="B4" s="21">
+      <c r="A4" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="22">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="G4" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="H4" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="I4" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="J4" t="s">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="K4" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="L4" t="s">
-        <v>325</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="22">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>23</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="F5" s="23">
+        <v>27</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="F5" s="24">
         <v>2</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="26">
         <f>B4/B3</f>
-        <v>0.14402173913043478</v>
-      </c>
-      <c r="I5" s="26">
+        <v>0.14302325581395348</v>
+      </c>
+      <c r="I5" s="27">
         <f>C2*G5</f>
-        <v>113.23076923076924</v>
+        <v>132.30769230769232</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>106</v>
-      </c>
-      <c r="K5" s="27">
+        <v>123</v>
+      </c>
+      <c r="K5" s="28">
         <f>J5-I5</f>
-        <v>-7.230769230769241</v>
-      </c>
-      <c r="L5" s="28">
+        <v>-9.30769230769232</v>
+      </c>
+      <c r="L5" s="29">
         <f>K5/4</f>
-        <v>-1.8076923076923102</v>
+        <v>-2.32692307692308</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="22">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>294</v>
-      </c>
-      <c r="E6" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="E6" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="24">
         <v>1</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="25">
         <f>F6/13</f>
         <v>0.07692307692307693</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <f>B5/B3</f>
-        <v>0.03125</v>
-      </c>
-      <c r="I6" s="26">
+        <v>0.031395348837209305</v>
+      </c>
+      <c r="I6" s="27">
         <f>C2*G6</f>
-        <v>56.61538461538462</v>
+        <v>66.15384615384616</v>
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>23</v>
-      </c>
-      <c r="K6" s="27">
+        <v>27</v>
+      </c>
+      <c r="K6" s="28">
         <f>J6-I6</f>
-        <v>-33.61538461538462</v>
-      </c>
-      <c r="L6" s="28">
+        <v>-39.15384615384616</v>
+      </c>
+      <c r="L6" s="29">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-8.403846153846155</v>
+        <v>-9.78846153846154</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>313</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="F7" s="32">
+        <v>372</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="F7" s="33">
         <v>3</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="35">
         <f>(B5+B4)/B3</f>
-        <v>0.17527173913043478</v>
-      </c>
-      <c r="I7" s="26">
+        <v>0.1744186046511628</v>
+      </c>
+      <c r="I7" s="27">
         <f>C2*G7</f>
-        <v>169.84615384615387</v>
+        <v>198.46153846153848</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>129</v>
-      </c>
-      <c r="K7" s="27">
+        <v>150</v>
+      </c>
+      <c r="K7" s="28">
         <f>J7-I7</f>
-        <v>-40.84615384615387</v>
-      </c>
-      <c r="L7" s="28">
+        <v>-48.46153846153848</v>
+      </c>
+      <c r="L7" s="29">
         <f>K7/4</f>
-        <v>-10.211538461538467</v>
+        <v>-12.11538461538462</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E8" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="F8" s="36">
+      <c r="E8" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="F8" s="37">
         <v>6</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="38">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="39">
         <f>B6/B3</f>
-        <v>0.39945652173913043</v>
-      </c>
-      <c r="I8" s="26">
+        <v>0.3930232558139535</v>
+      </c>
+      <c r="I8" s="27">
         <f>C2*G8</f>
-        <v>339.69230769230774</v>
+        <v>396.92307692307696</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>294</v>
-      </c>
-      <c r="K8" s="27">
+        <v>338</v>
+      </c>
+      <c r="K8" s="28">
         <f>J8-I8</f>
-        <v>-45.692307692307736</v>
-      </c>
-      <c r="L8" s="28">
+        <v>-58.92307692307696</v>
+      </c>
+      <c r="L8" s="29">
         <f>K8/4</f>
-        <v>-11.423076923076934</v>
+        <v>-14.73076923076924</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>736</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="F9" s="36">
+        <v>860</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>369</v>
+      </c>
+      <c r="F9" s="37">
         <v>4</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="38">
         <f t="shared" si="1"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="39">
         <f>B7/B3</f>
-        <v>0.42527173913043476</v>
-      </c>
-      <c r="I9" s="26">
+        <v>0.4325581395348837</v>
+      </c>
+      <c r="I9" s="27">
         <f>C2*G9</f>
-        <v>226.46153846153848</v>
+        <v>264.61538461538464</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>313</v>
-      </c>
-      <c r="K9" s="39">
+        <v>372</v>
+      </c>
+      <c r="K9" s="40">
         <f>J9-I9</f>
-        <v>86.53846153846152</v>
-      </c>
-      <c r="L9" s="28">
+        <v>107.38461538461536</v>
+      </c>
+      <c r="L9" s="29">
         <f>K9/4</f>
-        <v>21.63461538461538</v>
+        <v>26.84615384615384</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="40" t="s">
-        <v>330</v>
-      </c>
-      <c r="I11" s="41">
+      <c r="H11" s="41" t="s">
+        <v>370</v>
+      </c>
+      <c r="I11" s="42">
         <f>SUM(I7:I9)</f>
-        <v>736.0000000000001</v>
-      </c>
-      <c r="J11" s="35">
+        <v>860.0000000000001</v>
+      </c>
+      <c r="J11" s="36">
         <f>SUM(J7:J9)</f>
-        <v>736</v>
-      </c>
-      <c r="K11" s="42">
+        <v>860</v>
+      </c>
+      <c r="K11" s="43">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="44">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="F16" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="G16" t="s">
-        <v>332</v>
+        <v>372</v>
       </c>
       <c r="H16" t="s">
-        <v>321</v>
-      </c>
-      <c r="I16" s="44" t="s">
-        <v>322</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>323</v>
+        <v>361</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>362</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>363</v>
       </c>
       <c r="K16" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="L16" t="s">
-        <v>325</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="F17" s="46">
+      <c r="E17" s="46" t="s">
+        <v>366</v>
+      </c>
+      <c r="F17" s="47">
         <v>3</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="48">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="49">
         <f>(B5+B4)/B3</f>
-        <v>0.17527173913043478</v>
-      </c>
-      <c r="I17" s="49">
+        <v>0.1744186046511628</v>
+      </c>
+      <c r="I17" s="50">
         <f>B3*G17</f>
-        <v>169.84615384615387</v>
-      </c>
-      <c r="J17" s="50">
+        <v>198.46153846153848</v>
+      </c>
+      <c r="J17" s="51">
         <f>B5+B4</f>
-        <v>129</v>
-      </c>
-      <c r="K17" s="51">
+        <v>150</v>
+      </c>
+      <c r="K17" s="52">
         <f>J17-I17</f>
-        <v>-40.84615384615387</v>
-      </c>
-      <c r="L17" s="28">
+        <v>-48.46153846153848</v>
+      </c>
+      <c r="L17" s="29">
         <f>K17/4</f>
-        <v>-10.211538461538467</v>
+        <v>-12.11538461538462</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="53">
+      <c r="E18" s="53" t="s">
+        <v>367</v>
+      </c>
+      <c r="F18" s="54">
         <v>6</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="55">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="56">
         <f>B6/B3</f>
-        <v>0.39945652173913043</v>
-      </c>
-      <c r="I18" s="56">
+        <v>0.3930232558139535</v>
+      </c>
+      <c r="I18" s="57">
         <f>B3*G18</f>
-        <v>339.69230769230774</v>
-      </c>
-      <c r="J18" s="57">
+        <v>396.92307692307696</v>
+      </c>
+      <c r="J18" s="58">
         <f>B6</f>
-        <v>294</v>
-      </c>
-      <c r="K18" s="58">
+        <v>338</v>
+      </c>
+      <c r="K18" s="59">
         <f>J18-I18</f>
-        <v>-45.692307692307736</v>
-      </c>
-      <c r="L18" s="28">
+        <v>-58.92307692307696</v>
+      </c>
+      <c r="L18" s="29">
         <f>K18/4</f>
-        <v>-11.423076923076934</v>
-      </c>
-      <c r="Q18" s="59"/>
+        <v>-14.73076923076924</v>
+      </c>
+      <c r="Q18" s="60"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="60" t="s">
-        <v>329</v>
-      </c>
-      <c r="F19" s="61">
+      <c r="E19" s="61" t="s">
+        <v>369</v>
+      </c>
+      <c r="F19" s="62">
         <v>4</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G19" s="63">
         <f t="shared" si="2"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="64">
         <f>B7/B3</f>
-        <v>0.42527173913043476</v>
-      </c>
-      <c r="I19" s="64">
+        <v>0.4325581395348837</v>
+      </c>
+      <c r="I19" s="65">
         <f>B3*G19</f>
-        <v>226.46153846153848</v>
-      </c>
-      <c r="J19" s="65">
+        <v>264.61538461538464</v>
+      </c>
+      <c r="J19" s="66">
         <f>B7</f>
-        <v>313</v>
-      </c>
-      <c r="K19" s="66">
+        <v>372</v>
+      </c>
+      <c r="K19" s="67">
         <f>J19-I19</f>
-        <v>86.53846153846152</v>
-      </c>
-      <c r="L19" s="28">
+        <v>107.38461538461536</v>
+      </c>
+      <c r="L19" s="29">
         <f>K19/4</f>
-        <v>21.63461538461538</v>
+        <v>26.84615384615384</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
-    <row r="25" ht="75.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="376">
   <si>
     <t>sl</t>
   </si>
@@ -394,30 +394,33 @@
     <t>2025-01-11</t>
   </si>
   <si>
+    <t>2025-01-16</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2025-01-14</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2025-01-09</t>
   </si>
   <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2025-01-14</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2025-01-16</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
     <t>2025-01-03</t>
   </si>
   <si>
@@ -568,7 +571,7 @@
     <t>Eishalle Celje;LehnerMo;MeixnerSe;MattheyPh;WendnerMa</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;KainbergerJu;LehnerMo;MarkizetiGr;MattheyPh</t>
+    <t>Eishalle Jesenice;BajtMi;LehnerMo;MarkizetiGr;MattheyPh</t>
   </si>
   <si>
     <t>Eishalle Sterzing;BrockAd;MoidlDa;FecchioFe;MattheyPh</t>
@@ -586,7 +589,7 @@
     <t>Eishalle Celje;BajtMi;OrelSt;EislCh;StrimitzerDa</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;OrelSt;WidmannFl;StrimitzerDa;WuchererGe</t>
+    <t>Eishalle Dornbirn;HolzerTo;OrelSt;StrimitzerDa;WuchererGe</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;HlavatyAl;VoicanCh;EislCh;RinkerDa</t>
@@ -622,7 +625,7 @@
     <t>Eisarena Salzburg;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;EggerTh;MoschenAn;ScalzeriAl;StrimitzerDa</t>
+    <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;StrimitzerDa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;Huber rRe;RuetzMa;RinkerDa;ZacherlPa</t>
@@ -718,7 +721,7 @@
     <t>Eishalle Celje;LesniakBo;UnterwegerDo;JeramFi;TelesklavFa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;OrelSt;WidmannFl;EislCh;WuchererGe</t>
+    <t>Sportpark Kitzbühel;LazzeriAl;OrelSt;EislCh;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Celje;BulovecMi;HlavatyAl;LegatKo;TelesklavFa</t>
@@ -745,7 +748,7 @@
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;KainbergerJu;OrelSt;SeewaldJe;WuchererGe</t>
+    <t>Eishalle Meran;BulovecMi;SoraperraSi;ArlicMa;CristeliMa</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;MeixnerSe;VoicanCh;JeramFi;LegatKo</t>
@@ -760,7 +763,7 @@
     <t>Würtharena Neumarkt;BenvegnuAn;PirasAn;AbeltinoSi;PaceJa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;LazzeriAl;RuetzMa;AbeltinoSi;RinkerDa</t>
+    <t>Sportpark Kitzbühel;KainbergerJu;RuetzMa;AbeltinoSi;RinkerDa</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
@@ -847,7 +850,7 @@
     <t>Sportpark Kitzbühel;MetzingerFi;WenuschHe;KnezRo;LegatKo</t>
   </si>
   <si>
-    <t>Eishalle Meran;Huber rRe;RuetzMa;FecchioFe;ScalzeriAl</t>
+    <t>Eishalle Meran;EggerTh;RuetzMa;FecchioFe;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Cortina;EggerTh;PinieOm;AbeltinoSi;FormaioniTh</t>
@@ -859,10 +862,10 @@
     <t>Eishalle Ritten;SoraperraSi;StefenelliFe;FecchioFe;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Meran;BulovecMi;SoraperraSi;ArlicMa;CristeliMa</t>
-  </si>
-  <si>
-    <t>Eishalle Ritten;LegaSi;VirtaTu;CusinFe;FormaioniTh</t>
+    <t>Eishalle Dornbirn;MoidlDa;SpiegelSe;MattheyPh;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;EggerTh;VirtaTu;FormaioniTh;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;HlavatyAl;MetzingerFi;KnezRo;LegatKo</t>
@@ -940,7 +943,7 @@
     <t>Eishalle Gröden;LehnerMo;MoidlDa;BrondiPa;MoidlMa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;EggerTh;GiacomozziFe;AbeltinoSi;GrisentiLu</t>
+    <t>Eishalle Sterzing;EggerTh;GiacomozziFe;AbeltinoSi;PaceJa</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;RuetzMa;SpiegelSe;DivisDo;JägerRi</t>
@@ -964,7 +967,7 @@
     <t>Sportpark Kitzbühel;RuetzMa;SpiegelSe;JägerRi;StrimitzerDa</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;MoidlDa;SpiegelSe;MattheyPh;MoidlMa</t>
+    <t>Eishalle Zell am See;HlavatyAl;LebenJa;PreiserJu;TelesklavFa</t>
   </si>
   <si>
     <t>Eishalle Gröden;RivisFe;SoraperraSi;AbeltinoSi;PaceJa</t>
@@ -1045,7 +1048,7 @@
     <t>Eishalle Celje;HlavatyAl;PirasAn;PreiserJu;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Zell am See;HlavatyAl;LebenJa;PreiserJu;TelesklavFa</t>
+    <t>Sportpark Kitzbühel;LazzeriAl;OrelSt;SeewaldJe;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Meran;LebenJa;LesniakBo;FecchioFe;JeramFi</t>
@@ -1078,7 +1081,7 @@
     <t>Eishalle Cortina;LazzeriAl;OrelSt;CristeliMa;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Cortina;EggerTh;VirtaTu;FormaioniTh;ScalzeriAl</t>
+    <t>Eishalle Cortina;Huber rRe;VirtaTu;FormaioniTh;ScalzeriAl</t>
   </si>
   <si>
     <t>vse delegirane tekme</t>
@@ -1136,13 +1139,19 @@
   </si>
   <si>
     <t>% games per team</t>
+  </si>
+  <si>
+    <t>odštete delegacije traineesov</t>
+  </si>
+  <si>
+    <t>trainnees</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1179,6 +1188,14 @@
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="36"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1552,7 +1569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1677,6 +1694,10 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2038,7 +2059,7 @@
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C68,"&lt;&gt;")</f>
@@ -2097,12 +2118,12 @@
         <v>17</v>
       </c>
       <c r="Q1">
-        <f>COUNTIF(Q4:Q68,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(Q4:Q67,"&lt;&gt;")</f>
+        <v>16</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R65,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(R4:R64,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
@@ -2137,7 +2158,7 @@
         <v>15</v>
       </c>
       <c r="AA1">
-        <f>COUNTIF(AA4:AA66,"&lt;&gt;")</f>
+        <f>COUNTIF(AA4:AA65,"&lt;&gt;")</f>
         <v>15</v>
       </c>
       <c r="AB1">
@@ -2157,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="AF1">
-        <f>COUNTIF(AF4:AF64,"&lt;&gt;")</f>
+        <f>COUNTIF(AF4:AF63,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="AG1">
@@ -2166,14 +2187,14 @@
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI1">
-        <f>COUNTIF(AI4:AI67,"&lt;&gt;")</f>
+        <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ64,"&lt;&gt;")</f>
+        <f>COUNTIF(AJ4:AJ63,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AK1">
@@ -2181,15 +2202,15 @@
         <v>16</v>
       </c>
       <c r="AL1">
-        <f>COUNTIF(AL4:AL68,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AL4:AL66,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM67,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="AN1">
-        <f>COUNTIF(AN4:AN65,"&lt;&gt;")</f>
+        <f>COUNTIF(AN4:AN64,"&lt;&gt;")</f>
         <v>17</v>
       </c>
       <c r="AO1">
@@ -2205,7 +2226,7 @@
         <v>13</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR63,"&lt;&gt;")</f>
+        <f>COUNTIF(AR4:AR62,"&lt;&gt;")</f>
         <v>18</v>
       </c>
       <c r="AS1">
@@ -2233,8 +2254,8 @@
         <v>16</v>
       </c>
       <c r="AY1">
-        <f>COUNTIF(AY4:AY67,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(AY4:AY65,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ65,"&lt;&gt;")</f>
@@ -2242,7 +2263,7 @@
       </c>
       <c r="BA1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB69,"&lt;&gt;")</f>
@@ -2253,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="BD1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(BD4:BD69,"&lt;&gt;")</f>
         <v>12</v>
       </c>
       <c r="BE1">
@@ -4218,7 +4239,7 @@
         <v>91</v>
       </c>
       <c r="AO11" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AP11" t="s">
         <v>115</v>
@@ -4266,7 +4287,7 @@
         <v>118</v>
       </c>
       <c r="BF11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BJ11" t="s">
         <v>121</v>
@@ -4281,10 +4302,10 @@
         <v>120</v>
       </c>
       <c r="BO11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BP11" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4313,7 +4334,7 @@
         <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K12" t="s">
         <v>126</v>
@@ -4382,7 +4403,7 @@
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AJ12" s="7" t="s">
         <v>92</v>
@@ -4390,8 +4411,8 @@
       <c r="AK12" t="s">
         <v>95</v>
       </c>
-      <c r="AL12" s="8" t="s">
-        <v>92</v>
+      <c r="AL12" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4418,7 +4439,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AV12" s="8" t="s">
         <v>109</v>
@@ -4427,7 +4448,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4448,7 +4469,7 @@
         <v>103</v>
       </c>
       <c r="BJ12" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BK12" t="s">
         <v>119</v>
@@ -4486,7 +4507,7 @@
         <v>120</v>
       </c>
       <c r="J13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>112</v>
@@ -4552,13 +4573,13 @@
         <v>111</v>
       </c>
       <c r="AJ13" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AK13" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AL13" s="7" t="s">
-        <v>131</v>
+      <c r="AL13" t="s">
+        <v>124</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4596,8 +4617,8 @@
       <c r="AX13" t="s">
         <v>118</v>
       </c>
-      <c r="AY13" s="8" t="s">
-        <v>104</v>
+      <c r="AY13" t="s">
+        <v>129</v>
       </c>
       <c r="AZ13" t="s">
         <v>115</v>
@@ -4621,7 +4642,7 @@
         <v>121</v>
       </c>
       <c r="BN13" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4701,7 +4722,7 @@
         <v>112</v>
       </c>
       <c r="AE14" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AF14" s="7" t="s">
         <v>111</v>
@@ -4713,13 +4734,13 @@
         <v>131</v>
       </c>
       <c r="AJ14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
       <c r="AL14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="AM14" s="8" t="s">
         <v>92</v>
@@ -4728,7 +4749,7 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AP14" t="s">
         <v>119</v>
@@ -4740,7 +4761,7 @@
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
@@ -4757,8 +4778,8 @@
       <c r="AX14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AY14" t="s">
-        <v>129</v>
+      <c r="AY14" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="AZ14" s="8" t="s">
         <v>104</v>
@@ -4773,10 +4794,10 @@
         <v>121</v>
       </c>
       <c r="BD14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BK14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BM14" t="s">
         <v>124</v>
@@ -4787,7 +4808,7 @@
         <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
         <v>121</v>
@@ -4850,7 +4871,7 @@
         <v>120</v>
       </c>
       <c r="AB15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC15" t="s">
         <v>131</v>
@@ -4859,7 +4880,7 @@
         <v>119</v>
       </c>
       <c r="AE15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AF15" t="s">
         <v>125</v>
@@ -4868,19 +4889,19 @@
         <v>117</v>
       </c>
       <c r="AH15" t="s">
-        <v>125</v>
+        <v>133</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>120</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
-      <c r="AL15" t="s">
-        <v>124</v>
-      </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AO15" s="7" t="s">
         <v>103</v>
@@ -4889,7 +4910,7 @@
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AR15" s="8" t="s">
         <v>104</v>
@@ -4913,7 +4934,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -4925,10 +4946,10 @@
         <v>104</v>
       </c>
       <c r="BC15" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BD15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="BK15" t="s">
         <v>124</v>
@@ -4936,13 +4957,13 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
         <v>130</v>
       </c>
-      <c r="B16" t="s">
-        <v>132</v>
-      </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
         <v>119</v>
@@ -4951,19 +4972,19 @@
         <v>103</v>
       </c>
       <c r="H16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I16" t="s">
         <v>124</v>
       </c>
       <c r="K16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>119</v>
@@ -4971,8 +4992,8 @@
       <c r="P16" t="s">
         <v>111</v>
       </c>
-      <c r="Q16" s="8" t="s">
-        <v>92</v>
+      <c r="Q16" t="s">
+        <v>109</v>
       </c>
       <c r="R16" t="s">
         <v>103</v>
@@ -4999,22 +5020,22 @@
         <v>119</v>
       </c>
       <c r="AB16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AC16" s="7" t="s">
         <v>92</v>
       </c>
       <c r="AD16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AF16" t="s">
         <v>130</v>
       </c>
       <c r="AG16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AH16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AK16" t="s">
         <v>119</v>
@@ -5023,10 +5044,10 @@
         <v>131</v>
       </c>
       <c r="AN16" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AP16" t="s">
         <v>121</v>
@@ -5044,16 +5065,16 @@
         <v>123</v>
       </c>
       <c r="AW16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AX16" t="s">
         <v>120</v>
       </c>
-      <c r="AY16" s="7" t="s">
-        <v>119</v>
+      <c r="AY16" t="s">
+        <v>125</v>
       </c>
       <c r="AZ16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BA16" t="s">
         <v>131</v>
@@ -5064,7 +5085,10 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>129</v>
@@ -5073,7 +5097,7 @@
         <v>129</v>
       </c>
       <c r="N17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O17" t="s">
         <v>121</v>
@@ -5082,7 +5106,7 @@
         <v>119</v>
       </c>
       <c r="Q17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R17" t="s">
         <v>131</v>
@@ -5091,13 +5115,13 @@
         <v>103</v>
       </c>
       <c r="T17" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
       </c>
       <c r="V17" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="W17" t="s">
         <v>109</v>
@@ -5106,13 +5130,16 @@
         <v>119</v>
       </c>
       <c r="AA17" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF17" t="s">
         <v>124</v>
       </c>
-      <c r="AC17" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>132</v>
+      <c r="AH17" t="s">
+        <v>92</v>
       </c>
       <c r="AK17" s="7" t="s">
         <v>131</v>
@@ -5121,7 +5148,7 @@
         <v>119</v>
       </c>
       <c r="AN17" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="AO17" t="s">
         <v>127</v>
@@ -5130,7 +5157,7 @@
         <v>124</v>
       </c>
       <c r="AR17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
@@ -5144,14 +5171,11 @@
       <c r="AX17" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="AY17" t="s">
-        <v>123</v>
-      </c>
       <c r="AZ17" s="7" t="s">
         <v>119</v>
       </c>
       <c r="BA17" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BB17" t="s">
         <v>120</v>
@@ -5162,16 +5186,16 @@
         <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O18" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="P18" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="Q18" t="s">
-        <v>111</v>
+      <c r="Q18" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="R18" s="7" t="s">
         <v>111</v>
@@ -5180,25 +5204,25 @@
         <v>112</v>
       </c>
       <c r="T18" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
       <c r="V18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="W18" s="7" t="s">
         <v>111</v>
       </c>
       <c r="Z18" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AA18" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AC18" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AK18" t="s">
         <v>121</v>
@@ -5209,6 +5233,9 @@
       <c r="AN18" t="s">
         <v>125</v>
       </c>
+      <c r="AO18" t="s">
+        <v>125</v>
+      </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
@@ -5221,28 +5248,25 @@
       <c r="AX18" t="s">
         <v>127</v>
       </c>
-      <c r="AY18" t="s">
-        <v>130</v>
-      </c>
       <c r="AZ18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BA18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BB18" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
       <c r="E19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P19" t="s">
         <v>124</v>
       </c>
-      <c r="Q19" s="7" t="s">
-        <v>119</v>
+      <c r="Q19" t="s">
+        <v>125</v>
       </c>
       <c r="R19" t="s">
         <v>124</v>
@@ -5254,10 +5278,10 @@
         <v>119</v>
       </c>
       <c r="W19" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AC19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AK19" t="s">
         <v>124</v>
@@ -5269,7 +5293,7 @@
         <v>130</v>
       </c>
       <c r="AR19" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AT19" s="7" t="s">
         <v>119</v>
@@ -5278,7 +5302,7 @@
         <v>124</v>
       </c>
       <c r="AX19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AZ19" t="s">
         <v>124</v>
@@ -5287,18 +5311,15 @@
         <v>124</v>
       </c>
       <c r="BB19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
       <c r="P20" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="R20" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="S20" s="7" t="s">
         <v>94</v>
@@ -5307,44 +5328,50 @@
         <v>109</v>
       </c>
       <c r="W20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AN20" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="AR20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AT20" t="s">
         <v>127</v>
       </c>
       <c r="BA20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="BB20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+      <c r="R21" t="s">
+        <v>104</v>
+      </c>
       <c r="S21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="U21" t="s">
         <v>124</v>
       </c>
       <c r="AR21" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AT21" t="s">
-        <v>132</v>
+        <v>130</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="19:46" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
       <c r="S22" t="s">
+        <v>125</v>
+      </c>
+      <c r="U22" t="s">
         <v>130</v>
-      </c>
-      <c r="U22" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="19:21" x14ac:dyDescent="0.25"/>
@@ -5550,7 +5577,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5604,7 +5631,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AZ3" t="s">
         <v>120</v>
@@ -5619,13 +5646,13 @@
         <v>119</v>
       </c>
       <c r="BD3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BE3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BF3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BG3" t="s">
         <v>121</v>
@@ -5634,10 +5661,10 @@
         <v>123</v>
       </c>
       <c r="BI3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BJ3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BK3" t="s">
         <v>124</v>
@@ -5646,10 +5673,10 @@
         <v>127</v>
       </c>
       <c r="BM3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN3" t="s">
         <v>130</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -5786,7 +5813,7 @@
         <v>71</v>
       </c>
       <c r="AS4" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="s">
         <v>58</v>
@@ -5804,7 +5831,7 @@
         <v>5</v>
       </c>
       <c r="AY4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="AZ4" t="s">
         <v>68</v>
@@ -5840,7 +5867,7 @@
         <v>71</v>
       </c>
       <c r="BK4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BL4" t="s">
         <v>44</v>
@@ -6004,7 +6031,7 @@
         <v>47</v>
       </c>
       <c r="AY5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AZ5" t="s">
         <v>50</v>
@@ -6240,7 +6267,7 @@
         <v>65</v>
       </c>
       <c r="BK6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BL6" t="s">
         <v>53</v>
@@ -6457,7 +6484,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -6481,7 +6508,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -6538,7 +6565,7 @@
         <v>11</v>
       </c>
       <c r="AT8" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="AU8" t="s">
         <v>6</v>
@@ -6565,7 +6592,7 @@
         <v>44</v>
       </c>
       <c r="BG8" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="s">
         <v>46</v>
@@ -6580,7 +6607,7 @@
         <v>17</v>
       </c>
       <c r="BN8" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -6597,7 +6624,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6669,7 +6696,7 @@
         <v>72</v>
       </c>
       <c r="AT9" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AU9" t="s">
         <v>68</v>
@@ -6696,7 +6723,7 @@
         <v>38</v>
       </c>
       <c r="BG9" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="s">
         <v>50</v>
@@ -6827,7 +6854,7 @@
         <v>35</v>
       </c>
       <c r="BG10" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="s">
         <v>12</v>
@@ -6958,7 +6985,7 @@
         <v>53</v>
       </c>
       <c r="BG11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="BH11" t="s">
         <v>51</v>
@@ -7002,7 +7029,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -7062,7 +7089,7 @@
         <v>14</v>
       </c>
       <c r="AZ12" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="BA12" t="s">
         <v>39</v>
@@ -7074,10 +7101,10 @@
         <v>18</v>
       </c>
       <c r="BG12" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="BJ12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BK12" t="s">
         <v>68</v>
@@ -7187,7 +7214,7 @@
         <v>29</v>
       </c>
       <c r="BG13" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="BJ13" t="s">
         <v>26</v>
@@ -7300,10 +7327,10 @@
         <v>19</v>
       </c>
       <c r="BG14" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="BJ14" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="BK14" t="s">
         <v>15</v>
@@ -7413,10 +7440,10 @@
         <v>20</v>
       </c>
       <c r="BG15" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="BJ15" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BK15" t="s">
         <v>51</v>
@@ -7520,7 +7547,7 @@
         <v>49</v>
       </c>
       <c r="BG16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BJ16" t="s">
         <v>34</v>
@@ -7627,7 +7654,7 @@
         <v>45</v>
       </c>
       <c r="BG17" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="BJ17" t="s">
         <v>18</v>
@@ -7734,7 +7761,7 @@
         <v>66</v>
       </c>
       <c r="BG18" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="BJ18" t="s">
         <v>32</v>
@@ -7817,7 +7844,7 @@
         <v>61</v>
       </c>
       <c r="AS19" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="AT19" t="s">
         <v>66</v>
@@ -7841,7 +7868,7 @@
         <v>55</v>
       </c>
       <c r="BG19" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="BJ19" t="s">
         <v>37</v>
@@ -7924,7 +7951,7 @@
         <v>68</v>
       </c>
       <c r="BG20" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="BK20" t="s">
         <v>9</v>
@@ -8001,7 +8028,7 @@
         <v>33</v>
       </c>
       <c r="BG21" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="BK21" t="s">
         <v>11</v>
@@ -8078,7 +8105,7 @@
         <v>52</v>
       </c>
       <c r="BG22" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="BK22" t="s">
         <v>19</v>
@@ -8155,7 +8182,7 @@
         <v>30</v>
       </c>
       <c r="BG23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BK23" t="s">
         <v>12</v>
@@ -8190,7 +8217,7 @@
         <v>21</v>
       </c>
       <c r="BM24" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
@@ -8280,7 +8307,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="46:65" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="55:65" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8483,7 +8510,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -8537,7 +8564,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AZ3" t="s">
         <v>120</v>
@@ -8552,13 +8579,13 @@
         <v>119</v>
       </c>
       <c r="BD3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BE3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BF3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BG3" t="s">
         <v>121</v>
@@ -8567,10 +8594,10 @@
         <v>123</v>
       </c>
       <c r="BI3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BJ3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BK3" t="s">
         <v>124</v>
@@ -8579,670 +8606,670 @@
         <v>127</v>
       </c>
       <c r="BM3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN3" t="s">
         <v>130</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="V4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="W4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="X4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AB4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AC4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>180</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP4" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" t="s">
-        <v>170</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>168</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AR4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AS4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AT4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AU4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AV4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AW4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AX4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AY4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AZ4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="BA4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BB4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BC4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="BD4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="BE4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="BF4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="BG4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="BH4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="BI4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="BJ4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BK4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BL4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="BM4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BN4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="W5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Z5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AB5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AD5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AE5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AF5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AI5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AK5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AR5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AS5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AT5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AU5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AV5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AW5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AX5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AZ5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="BA5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="BB5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BC5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="BG5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="BH5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BJ5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="BK5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="BM5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="BN5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="T6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="V6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Y6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AD6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AI6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AK6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AS6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AT6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AU6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AV6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AW6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AX6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AZ6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="BA6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="BB6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="BC6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="BG6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="BJ6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="BK6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="BM6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="BN6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="W7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AB7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AD7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AE7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AI7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AK7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AS7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AT7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AU7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AV7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AW7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AX7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AZ7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BC7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="BG7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BJ7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="BK7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BM7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="BN7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="V8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="W8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Y8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AD8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AE8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AI8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AK8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AT8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AU8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AW8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AZ8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="BC8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="BG8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="BK8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="BM8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AD9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AE9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AT9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="BC9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="BK9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="BM9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="46:65" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="55:65" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9275,7 +9302,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14">
@@ -9285,7 +9312,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17">
@@ -9295,14 +9322,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B3" s="19">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>860</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -9310,35 +9337,35 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B4" s="22">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9350,7 +9377,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F5" s="24">
         <v>2</v>
@@ -9361,7 +9388,7 @@
       </c>
       <c r="H5" s="26">
         <f>B4/B3</f>
-        <v>0.14302325581395348</v>
+        <v>0.14418604651162792</v>
       </c>
       <c r="I5" s="27">
         <f>C2*G5</f>
@@ -9369,15 +9396,15 @@
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K5" s="28">
         <f>J5-I5</f>
-        <v>-9.30769230769232</v>
+        <v>-8.30769230769232</v>
       </c>
       <c r="L5" s="29">
         <f>K5/4</f>
-        <v>-2.32692307692308</v>
+        <v>-2.07692307692308</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9386,7 +9413,7 @@
       </c>
       <c r="B6" s="22">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>1</v>
@@ -9425,10 +9452,10 @@
       </c>
       <c r="B7" s="31">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F7" s="33">
         <v>3</v>
@@ -9439,7 +9466,7 @@
       </c>
       <c r="H7" s="35">
         <f>(B5+B4)/B3</f>
-        <v>0.1744186046511628</v>
+        <v>0.1755813953488372</v>
       </c>
       <c r="I7" s="27">
         <f>C2*G7</f>
@@ -9447,20 +9474,20 @@
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K7" s="28">
         <f>J7-I7</f>
-        <v>-48.46153846153848</v>
+        <v>-47.46153846153848</v>
       </c>
       <c r="L7" s="29">
         <f>K7/4</f>
-        <v>-12.11538461538462</v>
+        <v>-11.86538461538462</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E8" s="36" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F8" s="37">
         <v>6</v>
@@ -9471,7 +9498,7 @@
       </c>
       <c r="H8" s="39">
         <f>B6/B3</f>
-        <v>0.3930232558139535</v>
+        <v>0.3941860465116279</v>
       </c>
       <c r="I8" s="27">
         <f>C2*G8</f>
@@ -9479,27 +9506,27 @@
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K8" s="28">
         <f>J8-I8</f>
-        <v>-58.92307692307696</v>
+        <v>-57.92307692307696</v>
       </c>
       <c r="L8" s="29">
         <f>K8/4</f>
-        <v>-14.73076923076924</v>
+        <v>-14.48076923076924</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>860</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F9" s="37">
         <v>4</v>
@@ -9510,7 +9537,7 @@
       </c>
       <c r="H9" s="39">
         <f>B7/B3</f>
-        <v>0.4325581395348837</v>
+        <v>0.43023255813953487</v>
       </c>
       <c r="I9" s="27">
         <f>C2*G9</f>
@@ -9518,20 +9545,20 @@
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K9" s="40">
         <f>J9-I9</f>
-        <v>107.38461538461536</v>
+        <v>105.38461538461536</v>
       </c>
       <c r="L9" s="29">
         <f>K9/4</f>
-        <v>26.84615384615384</v>
+        <v>26.34615384615384</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="41" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I11" s="42">
         <f>SUM(I7:I9)</f>
@@ -9552,33 +9579,33 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I16" s="45" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="46" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F17" s="47">
         <v>3</v>
@@ -9589,7 +9616,7 @@
       </c>
       <c r="H17" s="49">
         <f>(B5+B4)/B3</f>
-        <v>0.1744186046511628</v>
+        <v>0.1755813953488372</v>
       </c>
       <c r="I17" s="50">
         <f>B3*G17</f>
@@ -9597,20 +9624,20 @@
       </c>
       <c r="J17" s="51">
         <f>B5+B4</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K17" s="52">
         <f>J17-I17</f>
-        <v>-48.46153846153848</v>
+        <v>-47.46153846153848</v>
       </c>
       <c r="L17" s="29">
         <f>K17/4</f>
-        <v>-12.11538461538462</v>
+        <v>-11.86538461538462</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="53" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F18" s="54">
         <v>6</v>
@@ -9621,7 +9648,7 @@
       </c>
       <c r="H18" s="56">
         <f>B6/B3</f>
-        <v>0.3930232558139535</v>
+        <v>0.3941860465116279</v>
       </c>
       <c r="I18" s="57">
         <f>B3*G18</f>
@@ -9629,21 +9656,21 @@
       </c>
       <c r="J18" s="58">
         <f>B6</f>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K18" s="59">
         <f>J18-I18</f>
-        <v>-58.92307692307696</v>
+        <v>-57.92307692307696</v>
       </c>
       <c r="L18" s="29">
         <f>K18/4</f>
-        <v>-14.73076923076924</v>
+        <v>-14.48076923076924</v>
       </c>
       <c r="Q18" s="60"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="61" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F19" s="62">
         <v>4</v>
@@ -9654,7 +9681,7 @@
       </c>
       <c r="H19" s="64">
         <f>B7/B3</f>
-        <v>0.4325581395348837</v>
+        <v>0.43023255813953487</v>
       </c>
       <c r="I19" s="65">
         <f>B3*G19</f>
@@ -9662,29 +9689,152 @@
       </c>
       <c r="J19" s="66">
         <f>B7</f>
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K19" s="67">
         <f>J19-I19</f>
-        <v>107.38461538461536</v>
+        <v>105.38461538461536</v>
       </c>
       <c r="L19" s="29">
         <f>K19/4</f>
-        <v>26.84615384615384</v>
+        <v>26.34615384615384</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+    <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E21" s="68" t="s">
+        <v>374</v>
+      </c>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
     </row>
-    <row r="25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>360</v>
+      </c>
+      <c r="G22" t="s">
+        <v>373</v>
+      </c>
+      <c r="H22" t="s">
+        <v>362</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="K22" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E23" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="F23" s="47">
+        <v>3</v>
+      </c>
+      <c r="G23" s="48">
+        <f t="shared" ref="G23:G25" si="3">F23/13</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="H23" s="49">
+        <f>(B4+B5-13)/(B3-102)</f>
+        <v>0.1820580474934037</v>
+      </c>
+      <c r="I23" s="50">
+        <f>(B3-102) *G23</f>
+        <v>174.92307692307693</v>
+      </c>
+      <c r="J23" s="51">
+        <f>B4+B5-13</f>
+        <v>138</v>
+      </c>
+      <c r="K23" s="52">
+        <f>J23-I23</f>
+        <v>-36.923076923076934</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E24" s="53" t="s">
+        <v>368</v>
+      </c>
+      <c r="F24" s="54">
+        <v>6</v>
+      </c>
+      <c r="G24" s="55">
+        <f t="shared" si="3"/>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H24" s="56">
+        <f>(B6-4)/(B3-102)</f>
+        <v>0.4419525065963061</v>
+      </c>
+      <c r="I24" s="57">
+        <f>(B3-102)*G24</f>
+        <v>349.84615384615387</v>
+      </c>
+      <c r="J24" s="58">
+        <f>B6-4</f>
+        <v>335</v>
+      </c>
+      <c r="K24" s="59">
+        <f>J24-I24</f>
+        <v>-14.846153846153868</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E25" s="61" t="s">
+        <v>370</v>
+      </c>
+      <c r="F25" s="62">
+        <v>4</v>
+      </c>
+      <c r="G25" s="63">
+        <f t="shared" si="3"/>
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H25" s="64">
+        <f>(B7-85)/(B3-102)</f>
+        <v>0.3759894459102902</v>
+      </c>
+      <c r="I25" s="65">
+        <f>(B3-102)*G25</f>
+        <v>233.23076923076925</v>
+      </c>
+      <c r="J25" s="66">
+        <f>B7-85</f>
+        <v>285</v>
+      </c>
+      <c r="K25" s="67">
+        <f>J25-I25</f>
+        <v>51.769230769230745</v>
+      </c>
+    </row>
+    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E26" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="69">
+        <v>102</v>
+      </c>
+      <c r="K26" s="5"/>
+    </row>
     <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -415,24 +415,21 @@
     <t>2025-01-04</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2025-01-09</t>
   </si>
   <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
     <t>2025-01-03</t>
   </si>
   <si>
-    <t>2024-12-04</t>
+    <t>2025-01-22</t>
   </si>
   <si>
     <t>2025-01-12</t>
   </si>
   <si>
-    <t>2025-01-22</t>
-  </si>
-  <si>
     <t>2025-01-08</t>
   </si>
   <si>
@@ -595,19 +592,19 @@
     <t>Sportpark Kitzbühel;HlavatyAl;VoicanCh;EislCh;RinkerDa</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;HolzerTo;KainbergerJu;TelesklavFa;WendnerMa</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;Huber rRe;SnojTa;ArlicMa;RivisAn</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;ArlicMa;TelesklavFa</t>
+    <t>KELIT Arena Zell am See;HolzerTo;VoicanCh;TelesklavFa;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;BenvegnuAn;SnojTa;ArlicMa;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;LesniakBo;OrelSt;ArlicMa;KnezRo</t>
   </si>
   <si>
     <t>Eishalle Jesenice;OrelSt;VoicanCh;PreiserJu;WuchererGe</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;BenvegnuAn;GiacomozziFe;BrondiPa;DivisDo</t>
+    <t>Eishalle Dornbirn;GiacomozziFe;Huber rRe;BrondiPa;DivisDo</t>
   </si>
   <si>
     <t>Eishalle Ritten;BajtMi;MeixnerSe;MarkizetiGr;WendnerMa</t>
@@ -739,10 +736,10 @@
     <t>KELIT Arena Zell am See;LehnerMo;MoidlDa;SeewaldJe;ZacherlPa</t>
   </si>
   <si>
-    <t>Eishalle Gröden;BenvegnuAn;LazzeriAl;CristeliMa;PaceJa</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;BulovecMi;WidmannFl;JavornikBl;MarkizetiGr</t>
+    <t>Eishalle Gröden;BenvegnuAn;LazzeriAl;FormaioniTh;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BajtMi;BulovecMi;JavornikBl;MarkizetiGr</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
@@ -853,7 +850,7 @@
     <t>Eishalle Meran;EggerTh;RuetzMa;FecchioFe;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Cortina;EggerTh;PinieOm;AbeltinoSi;FormaioniTh</t>
+    <t>Eishalle Cortina;EggerTh;GiacomozziFe;AbeltinoSi;CristeliMa</t>
   </si>
   <si>
     <t>Eishalle Jesenice;MeixnerSe;MetzingerFi;KnezRo;LegatKo</t>
@@ -874,7 +871,7 @@
     <t>Eishalle Sterzing;PinieOm;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Sissek Zibel;BajtMi;LesniakBo;JavornikBl;WuchererGe</t>
+    <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;JavornikBl;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
@@ -1045,10 +1042,10 @@
     <t>Würtharena Neumarkt;RivisFe;SpiegelSe;BrondiPa;DivisDo</t>
   </si>
   <si>
-    <t>Eishalle Celje;HlavatyAl;PirasAn;PreiserJu;ScalzeriAl</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;LazzeriAl;OrelSt;SeewaldJe;WuchererGe</t>
+    <t>Eishalle Celje;HlavatyAl;KainbergerJu;PreiserJu;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;LazzeriAl;WidmannFl;SeewaldJe;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Meran;LebenJa;LesniakBo;FecchioFe;JeramFi</t>
@@ -1121,6 +1118,9 @@
   </si>
   <si>
     <t>Slo</t>
+  </si>
+  <si>
+    <t>trainees</t>
   </si>
   <si>
     <t>It</t>
@@ -1271,7 +1271,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1517,6 +1517,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom style="medium">
@@ -1569,7 +1580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1624,6 +1635,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1631,27 +1643,27 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1678,17 +1690,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="12" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1697,7 +1709,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2058,7 +2072,7 @@
         <v>14</v>
       </c>
       <c r="B1">
-        <f>COUNTIF(B4:B68,"&lt;&gt;")</f>
+        <f>COUNTIF(B4:B67,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="C1">
@@ -2099,14 +2113,14 @@
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M1">
         <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="N1">
-        <f>COUNTIF(N4:N68,"&lt;&gt;")</f>
+        <f>COUNTIF(N4:N67,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="O1">
@@ -2139,7 +2153,7 @@
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W1">
         <f>COUNTIF(W4:W69,"&lt;&gt;")</f>
@@ -2163,15 +2177,15 @@
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="AD1">
-        <f>COUNTIF(AD4:AD69,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(AD4:AD68,"&lt;&gt;")</f>
+        <v>12</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
@@ -2182,19 +2196,19 @@
         <v>14</v>
       </c>
       <c r="AG1">
-        <f>COUNTIF(AG4:AG67,"&lt;&gt;")</f>
+        <f>COUNTIF(AG4:AG66,"&lt;&gt;")</f>
+        <v>12</v>
+      </c>
+      <c r="AH1">
+        <f>COUNTIF(AH4:AH67,"&lt;&gt;")</f>
         <v>13</v>
-      </c>
-      <c r="AH1">
-        <f>COUNTIF(AH4:AH68,"&lt;&gt;")</f>
-        <v>14</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
         <v>9</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ63,"&lt;&gt;")</f>
+        <f>COUNTIF(AJ4:AJ62,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AK1">
@@ -2202,19 +2216,19 @@
         <v>16</v>
       </c>
       <c r="AL1">
-        <f>COUNTIF(AL4:AL66,"&lt;&gt;")</f>
+        <f>COUNTIF(AL4:AL65,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="AM1">
-        <f>COUNTIF(AM4:AM67,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(AM4:AM66,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN64,"&lt;&gt;")</f>
         <v>17</v>
       </c>
       <c r="AO1">
-        <f>COUNTIF(AO4:AO66,"&lt;&gt;")</f>
+        <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="AP1">
@@ -2226,7 +2240,7 @@
         <v>13</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR62,"&lt;&gt;")</f>
+        <f>COUNTIF(AR4:AR61,"&lt;&gt;")</f>
         <v>18</v>
       </c>
       <c r="AS1">
@@ -2239,7 +2253,7 @@
       </c>
       <c r="AU1">
         <f>COUNTIF(AU4:AU69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV65,"&lt;&gt;")</f>
@@ -2254,7 +2268,7 @@
         <v>16</v>
       </c>
       <c r="AY1">
-        <f>COUNTIF(AY4:AY65,"&lt;&gt;")</f>
+        <f>COUNTIF(AY4:AY63,"&lt;&gt;")</f>
         <v>13</v>
       </c>
       <c r="AZ1">
@@ -4239,7 +4253,7 @@
         <v>91</v>
       </c>
       <c r="AO11" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="AP11" t="s">
         <v>115</v>
@@ -4287,7 +4301,7 @@
         <v>118</v>
       </c>
       <c r="BF11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BJ11" t="s">
         <v>121</v>
@@ -4302,10 +4316,10 @@
         <v>120</v>
       </c>
       <c r="BO11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BP11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4411,8 +4425,8 @@
       <c r="AK12" t="s">
         <v>95</v>
       </c>
-      <c r="AL12" s="7" t="s">
-        <v>131</v>
+      <c r="AL12" t="s">
+        <v>124</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4421,7 +4435,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4448,7 +4462,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4469,7 +4483,7 @@
         <v>103</v>
       </c>
       <c r="BJ12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BK12" t="s">
         <v>119</v>
@@ -4579,7 +4593,7 @@
         <v>109</v>
       </c>
       <c r="AL13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4587,8 +4601,8 @@
       <c r="AN13" t="s">
         <v>115</v>
       </c>
-      <c r="AO13" t="s">
-        <v>129</v>
+      <c r="AO13" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="AP13" t="s">
         <v>120</v>
@@ -4618,7 +4632,7 @@
         <v>118</v>
       </c>
       <c r="AY13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="AZ13" t="s">
         <v>115</v>
@@ -4642,7 +4656,7 @@
         <v>121</v>
       </c>
       <c r="BN13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -4722,25 +4736,25 @@
         <v>112</v>
       </c>
       <c r="AE14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AF14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="AG14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AH14" s="7" t="s">
-        <v>131</v>
+      <c r="AG14" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>132</v>
       </c>
       <c r="AJ14" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
       <c r="AL14" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AM14" s="8" t="s">
         <v>92</v>
@@ -4778,8 +4792,8 @@
       <c r="AX14" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AY14" s="7" t="s">
-        <v>119</v>
+      <c r="AY14" t="s">
+        <v>125</v>
       </c>
       <c r="AZ14" s="8" t="s">
         <v>104</v>
@@ -4797,7 +4811,7 @@
         <v>123</v>
       </c>
       <c r="BK14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BM14" t="s">
         <v>124</v>
@@ -4871,13 +4885,13 @@
         <v>120</v>
       </c>
       <c r="AB15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AC15" t="s">
         <v>131</v>
       </c>
-      <c r="AD15" s="7" t="s">
-        <v>119</v>
+      <c r="AD15" t="s">
+        <v>125</v>
       </c>
       <c r="AE15" t="s">
         <v>125</v>
@@ -4885,14 +4899,11 @@
       <c r="AF15" t="s">
         <v>125</v>
       </c>
-      <c r="AG15" s="7" t="s">
-        <v>117</v>
+      <c r="AG15" t="s">
+        <v>125</v>
       </c>
       <c r="AH15" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
@@ -4901,10 +4912,10 @@
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>139</v>
-      </c>
-      <c r="AO15" s="7" t="s">
-        <v>103</v>
+        <v>138</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>127</v>
       </c>
       <c r="AP15" s="7" t="s">
         <v>104</v>
@@ -4934,7 +4945,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -4946,7 +4957,7 @@
         <v>104</v>
       </c>
       <c r="BC15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BD15" t="s">
         <v>121</v>
@@ -4960,10 +4971,10 @@
         <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
         <v>119</v>
@@ -4984,7 +4995,7 @@
         <v>130</v>
       </c>
       <c r="N16" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>119</v>
@@ -5025,17 +5036,11 @@
       <c r="AC16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AD16" t="s">
-        <v>125</v>
-      </c>
       <c r="AF16" t="s">
         <v>130</v>
       </c>
-      <c r="AG16" t="s">
-        <v>125</v>
-      </c>
       <c r="AH16" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="AK16" t="s">
         <v>119</v>
@@ -5047,7 +5052,7 @@
         <v>134</v>
       </c>
       <c r="AO16" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="AP16" t="s">
         <v>121</v>
@@ -5061,6 +5066,9 @@
       <c r="AT16" s="8" t="s">
         <v>104</v>
       </c>
+      <c r="AU16" t="s">
+        <v>131</v>
+      </c>
       <c r="AV16" t="s">
         <v>123</v>
       </c>
@@ -5071,10 +5079,10 @@
         <v>120</v>
       </c>
       <c r="AY16" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AZ16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BA16" t="s">
         <v>131</v>
@@ -5088,7 +5096,7 @@
         <v>130</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>129</v>
@@ -5096,8 +5104,11 @@
       <c r="E17" s="7" t="s">
         <v>129</v>
       </c>
+      <c r="L17" t="s">
+        <v>119</v>
+      </c>
       <c r="N17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O17" t="s">
         <v>121</v>
@@ -5115,7 +5126,7 @@
         <v>103</v>
       </c>
       <c r="T17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
@@ -5132,32 +5143,32 @@
       <c r="AA17" t="s">
         <v>125</v>
       </c>
+      <c r="AB17" t="s">
+        <v>131</v>
+      </c>
       <c r="AC17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AF17" t="s">
         <v>124</v>
       </c>
-      <c r="AH17" t="s">
-        <v>92</v>
-      </c>
       <c r="AK17" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="AM17" s="7" t="s">
-        <v>119</v>
+      <c r="AM17" t="s">
+        <v>121</v>
       </c>
       <c r="AN17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AO17" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="AP17" t="s">
         <v>124</v>
       </c>
       <c r="AR17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
@@ -5175,7 +5186,7 @@
         <v>119</v>
       </c>
       <c r="BA17" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="BB17" t="s">
         <v>120</v>
@@ -5189,7 +5200,7 @@
         <v>136</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P18" s="7" t="s">
         <v>120</v>
@@ -5219,7 +5230,7 @@
         <v>125</v>
       </c>
       <c r="AA18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC18" t="s">
         <v>125</v>
@@ -5228,14 +5239,11 @@
         <v>121</v>
       </c>
       <c r="AM18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AN18" t="s">
         <v>125</v>
       </c>
-      <c r="AO18" t="s">
-        <v>125</v>
-      </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
@@ -5249,13 +5257,13 @@
         <v>127</v>
       </c>
       <c r="AZ18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BA18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BB18" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
@@ -5277,8 +5285,11 @@
       <c r="U19" t="s">
         <v>119</v>
       </c>
+      <c r="V19" t="s">
+        <v>131</v>
+      </c>
       <c r="W19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC19" t="s">
         <v>130</v>
@@ -5286,9 +5297,6 @@
       <c r="AK19" t="s">
         <v>124</v>
       </c>
-      <c r="AM19" t="s">
-        <v>124</v>
-      </c>
       <c r="AN19" t="s">
         <v>130</v>
       </c>
@@ -5311,7 +5319,7 @@
         <v>124</v>
       </c>
       <c r="BB19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
@@ -5351,19 +5359,19 @@
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="U21" t="s">
         <v>124</v>
       </c>
       <c r="AR21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AT21" t="s">
         <v>130</v>
       </c>
       <c r="BA21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
@@ -5577,7 +5585,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5631,7 +5639,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AZ3" t="s">
         <v>120</v>
@@ -5649,7 +5657,7 @@
         <v>134</v>
       </c>
       <c r="BE3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BF3" t="s">
         <v>136</v>
@@ -5661,10 +5669,10 @@
         <v>123</v>
       </c>
       <c r="BI3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BJ3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BK3" t="s">
         <v>124</v>
@@ -5840,7 +5848,7 @@
         <v>56</v>
       </c>
       <c r="BB4" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="s">
         <v>11</v>
@@ -5849,7 +5857,7 @@
         <v>47</v>
       </c>
       <c r="BE4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="BF4" t="s">
         <v>5</v>
@@ -6037,19 +6045,19 @@
         <v>50</v>
       </c>
       <c r="BA5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="s">
         <v>4</v>
       </c>
       <c r="BC5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="BD5" t="s">
         <v>50</v>
       </c>
       <c r="BE5" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="BF5" t="s">
         <v>46</v>
@@ -6443,7 +6451,7 @@
         <v>25</v>
       </c>
       <c r="BC7" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="s">
         <v>43</v>
@@ -6484,7 +6492,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -6508,7 +6516,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -6586,7 +6594,7 @@
         <v>17</v>
       </c>
       <c r="BB8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="s">
         <v>44</v>
@@ -6624,7 +6632,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6717,7 +6725,7 @@
         <v>21</v>
       </c>
       <c r="BB9" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="s">
         <v>38</v>
@@ -6845,7 +6853,7 @@
         <v>59</v>
       </c>
       <c r="BA10" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="s">
         <v>13</v>
@@ -6976,7 +6984,7 @@
         <v>60</v>
       </c>
       <c r="BA11" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="s">
         <v>8</v>
@@ -7029,7 +7037,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -7113,7 +7121,7 @@
         <v>36</v>
       </c>
       <c r="BN12" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -7205,7 +7213,7 @@
         <v>49</v>
       </c>
       <c r="BA13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="BB13" t="s">
         <v>14</v>
@@ -7226,7 +7234,7 @@
         <v>29</v>
       </c>
       <c r="BN13" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
@@ -7431,7 +7439,7 @@
         <v>30</v>
       </c>
       <c r="BA15" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BB15" t="s">
         <v>51</v>
@@ -8025,10 +8033,10 @@
         <v>45</v>
       </c>
       <c r="BC21" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="BG21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="BK21" t="s">
         <v>11</v>
@@ -8510,7 +8518,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -8564,7 +8572,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AZ3" t="s">
         <v>120</v>
@@ -8582,7 +8590,7 @@
         <v>134</v>
       </c>
       <c r="BE3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BF3" t="s">
         <v>136</v>
@@ -8594,10 +8602,10 @@
         <v>123</v>
       </c>
       <c r="BI3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BJ3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BK3" t="s">
         <v>124</v>
@@ -8614,659 +8622,659 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" t="s">
         <v>141</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>142</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>143</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>144</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>145</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>146</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>147</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>148</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>149</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>150</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>151</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>152</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>153</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>154</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>155</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>156</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>157</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>158</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>159</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>160</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>161</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>162</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>163</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>164</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>165</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>166</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>167</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>168</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>169</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>170</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>171</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>172</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>173</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>174</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>175</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>176</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>177</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>178</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>179</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>180</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ4" t="s">
         <v>181</v>
       </c>
-      <c r="AP4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>182</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>183</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>184</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>185</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>186</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>187</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>188</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>189</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>190</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>191</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>192</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
         <v>193</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BD4" t="s">
         <v>194</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>195</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>196</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>197</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>198</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>199</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>200</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>201</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>202</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>203</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BN4" t="s">
         <v>204</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" t="s">
         <v>206</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>207</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>208</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>209</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>210</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>211</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>212</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
         <v>213</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
         <v>214</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>215</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>216</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>217</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>218</v>
       </c>
-      <c r="W5" t="s">
+      <c r="Y5" t="s">
         <v>219</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>220</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AB5" t="s">
         <v>221</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AD5" t="s">
         <v>222</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>223</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>224</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AI5" t="s">
         <v>225</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AK5" t="s">
         <v>226</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>227</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>228</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AN5" t="s">
         <v>229</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
         <v>230</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AR5" t="s">
         <v>231</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>232</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>233</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AU5" t="s">
         <v>234</v>
       </c>
-      <c r="AU5" t="s">
+      <c r="AV5" t="s">
         <v>235</v>
       </c>
-      <c r="AV5" t="s">
+      <c r="AW5" t="s">
         <v>236</v>
       </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>237</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AZ5" t="s">
         <v>238</v>
       </c>
-      <c r="AZ5" t="s">
+      <c r="BA5" t="s">
         <v>239</v>
       </c>
-      <c r="BA5" t="s">
+      <c r="BB5" t="s">
         <v>240</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BC5" t="s">
         <v>241</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BG5" t="s">
         <v>242</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BH5" t="s">
         <v>243</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BJ5" t="s">
         <v>244</v>
       </c>
-      <c r="BJ5" t="s">
+      <c r="BK5" t="s">
         <v>245</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BM5" t="s">
         <v>246</v>
       </c>
-      <c r="BM5" t="s">
+      <c r="BN5" t="s">
         <v>247</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" t="s">
         <v>249</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>250</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>251</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>252</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>253</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>254</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>255</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
         <v>256</v>
       </c>
-      <c r="P6" t="s">
+      <c r="T6" t="s">
         <v>257</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" t="s">
         <v>258</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>259</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Y6" t="s">
         <v>260</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>261</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
         <v>262</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AD6" t="s">
         <v>263</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>264</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AI6" t="s">
         <v>265</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AK6" t="s">
         <v>266</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AM6" t="s">
         <v>267</v>
       </c>
-      <c r="AM6" t="s">
+      <c r="AN6" t="s">
         <v>268</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>269</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AS6" t="s">
         <v>270</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
         <v>271</v>
       </c>
-      <c r="AT6" t="s">
+      <c r="AU6" t="s">
         <v>272</v>
       </c>
-      <c r="AU6" t="s">
+      <c r="AV6" t="s">
         <v>273</v>
       </c>
-      <c r="AV6" t="s">
+      <c r="AW6" t="s">
         <v>274</v>
       </c>
-      <c r="AW6" t="s">
+      <c r="AX6" t="s">
         <v>275</v>
       </c>
-      <c r="AX6" t="s">
+      <c r="AZ6" t="s">
         <v>276</v>
       </c>
-      <c r="AZ6" t="s">
+      <c r="BA6" t="s">
         <v>277</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="BB6" t="s">
         <v>278</v>
       </c>
-      <c r="BB6" t="s">
+      <c r="BC6" t="s">
         <v>279</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BG6" t="s">
         <v>280</v>
       </c>
-      <c r="BG6" t="s">
+      <c r="BJ6" t="s">
         <v>281</v>
       </c>
-      <c r="BJ6" t="s">
+      <c r="BK6" t="s">
         <v>282</v>
       </c>
-      <c r="BK6" t="s">
+      <c r="BM6" t="s">
         <v>283</v>
       </c>
-      <c r="BM6" t="s">
+      <c r="BN6" t="s">
         <v>284</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" t="s">
         <v>286</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>287</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>288</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>289</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>290</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>291</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>292</v>
       </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>293</v>
       </c>
-      <c r="P7" t="s">
+      <c r="T7" t="s">
         <v>294</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>295</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>296</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>297</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>298</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AB7" t="s">
         <v>299</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>300</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>301</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AI7" t="s">
         <v>302</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AK7" t="s">
         <v>303</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AM7" t="s">
         <v>304</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AN7" t="s">
         <v>305</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>306</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AS7" t="s">
         <v>307</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AT7" t="s">
         <v>308</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AU7" t="s">
         <v>309</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>310</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>311</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>312</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AZ7" t="s">
         <v>313</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BC7" t="s">
         <v>314</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BG7" t="s">
         <v>315</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BJ7" t="s">
         <v>316</v>
       </c>
-      <c r="BJ7" t="s">
+      <c r="BK7" t="s">
         <v>317</v>
       </c>
-      <c r="BK7" t="s">
+      <c r="BM7" t="s">
         <v>318</v>
       </c>
-      <c r="BM7" t="s">
+      <c r="BN7" t="s">
         <v>319</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D8" t="s">
         <v>321</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>322</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>323</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>324</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>325</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>326</v>
       </c>
-      <c r="L8" t="s">
+      <c r="V8" t="s">
         <v>327</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>328</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y8" t="s">
         <v>329</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AB8" t="s">
         <v>330</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
         <v>331</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>332</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AI8" t="s">
         <v>333</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AK8" t="s">
         <v>334</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AM8" t="s">
         <v>335</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AO8" t="s">
         <v>336</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AT8" t="s">
         <v>337</v>
       </c>
-      <c r="AT8" t="s">
+      <c r="AU8" t="s">
         <v>338</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AW8" t="s">
         <v>339</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AZ8" t="s">
         <v>340</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BC8" t="s">
         <v>341</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BG8" t="s">
         <v>342</v>
       </c>
-      <c r="BG8" t="s">
+      <c r="BK8" t="s">
         <v>343</v>
       </c>
-      <c r="BK8" t="s">
+      <c r="BM8" t="s">
         <v>344</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
+        <v>345</v>
+      </c>
+      <c r="L9" t="s">
         <v>346</v>
       </c>
-      <c r="L9" t="s">
+      <c r="AD9" t="s">
         <v>347</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>348</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AK9" t="s">
         <v>349</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AT9" t="s">
         <v>350</v>
       </c>
-      <c r="AT9" t="s">
+      <c r="BC9" t="s">
         <v>351</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BK9" t="s">
         <v>352</v>
       </c>
-      <c r="BK9" t="s">
+      <c r="BM9" t="s">
         <v>353</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="55:65" x14ac:dyDescent="0.25"/>
@@ -9286,6 +9294,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="12.140625" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
     <col min="7" max="7" width="20.7109375" customWidth="1"/>
@@ -9302,7 +9311,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="14">
@@ -9312,7 +9321,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17">
@@ -9322,14 +9331,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B3" s="19">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>860</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -9337,35 +9346,39 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B4" s="22">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>124</v>
       </c>
+      <c r="C4">
+        <f>AHL!I1</f>
+        <v>13</v>
+      </c>
       <c r="E4" t="s">
+        <v>358</v>
+      </c>
+      <c r="F4" t="s">
         <v>359</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>360</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>361</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>362</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>363</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>364</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>365</v>
-      </c>
-      <c r="L4" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9374,10 +9387,10 @@
       </c>
       <c r="B5" s="22">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F5" s="24">
         <v>2</v>
@@ -9413,7 +9426,11 @@
       </c>
       <c r="B6" s="22">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>339</v>
+        <v>338</v>
+      </c>
+      <c r="C6">
+        <f>AHL!X1</f>
+        <v>4</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>1</v>
@@ -9427,7 +9444,7 @@
       </c>
       <c r="H6" s="26">
         <f>B5/B3</f>
-        <v>0.031395348837209305</v>
+        <v>0.03255813953488372</v>
       </c>
       <c r="I6" s="27">
         <f>C2*G6</f>
@@ -9435,15 +9452,15 @@
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" s="28">
         <f>J6-I6</f>
-        <v>-39.15384615384616</v>
+        <v>-38.15384615384616</v>
       </c>
       <c r="L6" s="29">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-9.78846153846154</v>
+        <v>-9.53846153846154</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9454,8 +9471,12 @@
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>370</v>
       </c>
+      <c r="C7">
+        <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
+        <v>86</v>
+      </c>
       <c r="E7" s="32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F7" s="33">
         <v>3</v>
@@ -9466,7 +9487,7 @@
       </c>
       <c r="H7" s="35">
         <f>(B5+B4)/B3</f>
-        <v>0.1755813953488372</v>
+        <v>0.17674418604651163</v>
       </c>
       <c r="I7" s="27">
         <f>C2*G7</f>
@@ -9474,31 +9495,38 @@
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K7" s="28">
         <f>J7-I7</f>
-        <v>-47.46153846153848</v>
+        <v>-46.46153846153848</v>
       </c>
       <c r="L7" s="29">
         <f>K7/4</f>
-        <v>-11.86538461538462</v>
+        <v>-11.61538461538462</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E8" s="36" t="s">
+    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8">
+        <f>SUM(C4:C7)</f>
+        <v>103</v>
+      </c>
+      <c r="E8" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="38">
         <v>6</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="39">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="40">
         <f>B6/B3</f>
-        <v>0.3941860465116279</v>
+        <v>0.3930232558139535</v>
       </c>
       <c r="I8" s="27">
         <f>C2*G8</f>
@@ -9506,15 +9534,15 @@
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K8" s="28">
         <f>J8-I8</f>
-        <v>-57.92307692307696</v>
+        <v>-58.92307692307696</v>
       </c>
       <c r="L8" s="29">
         <f>K8/4</f>
-        <v>-14.48076923076924</v>
+        <v>-14.73076923076924</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9525,17 +9553,17 @@
         <f>SUM(B4:B7)</f>
         <v>860</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="37" t="s">
         <v>370</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="38">
         <v>4</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="39">
         <f t="shared" si="1"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="40">
         <f>B7/B3</f>
         <v>0.43023255813953487</v>
       </c>
@@ -9547,7 +9575,7 @@
         <f>B7</f>
         <v>370</v>
       </c>
-      <c r="K9" s="40">
+      <c r="K9" s="41">
         <f>J9-I9</f>
         <v>105.38461538461536</v>
       </c>
@@ -9557,22 +9585,22 @@
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="43">
         <f>SUM(I7:I9)</f>
         <v>860.0000000000001</v>
       </c>
-      <c r="J11" s="36">
+      <c r="J11" s="37">
         <f>SUM(J7:J9)</f>
         <v>860</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="44">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="45">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
@@ -9582,116 +9610,116 @@
         <v>372</v>
       </c>
       <c r="F16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G16" t="s">
         <v>373</v>
       </c>
       <c r="H16" t="s">
+        <v>361</v>
+      </c>
+      <c r="I16" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="I16" s="45" t="s">
+      <c r="J16" s="46" t="s">
         <v>363</v>
       </c>
-      <c r="J16" s="45" t="s">
+      <c r="K16" t="s">
         <v>364</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>365</v>
-      </c>
-      <c r="L16" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="46" t="s">
-        <v>367</v>
-      </c>
-      <c r="F17" s="47">
+      <c r="E17" s="47" t="s">
+        <v>366</v>
+      </c>
+      <c r="F17" s="48">
         <v>3</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="49">
+      <c r="H17" s="50">
         <f>(B5+B4)/B3</f>
-        <v>0.1755813953488372</v>
-      </c>
-      <c r="I17" s="50">
+        <v>0.17674418604651163</v>
+      </c>
+      <c r="I17" s="51">
         <f>B3*G17</f>
         <v>198.46153846153848</v>
       </c>
-      <c r="J17" s="51">
+      <c r="J17" s="52">
         <f>B5+B4</f>
-        <v>151</v>
-      </c>
-      <c r="K17" s="52">
+        <v>152</v>
+      </c>
+      <c r="K17" s="53">
         <f>J17-I17</f>
-        <v>-47.46153846153848</v>
+        <v>-46.46153846153848</v>
       </c>
       <c r="L17" s="29">
         <f>K17/4</f>
-        <v>-11.86538461538462</v>
+        <v>-11.61538461538462</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="54" t="s">
         <v>368</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="55">
         <v>6</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="56">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="56">
+      <c r="H18" s="57">
         <f>B6/B3</f>
-        <v>0.3941860465116279</v>
-      </c>
-      <c r="I18" s="57">
+        <v>0.3930232558139535</v>
+      </c>
+      <c r="I18" s="58">
         <f>B3*G18</f>
         <v>396.92307692307696</v>
       </c>
-      <c r="J18" s="58">
+      <c r="J18" s="59">
         <f>B6</f>
-        <v>339</v>
-      </c>
-      <c r="K18" s="59">
+        <v>338</v>
+      </c>
+      <c r="K18" s="60">
         <f>J18-I18</f>
-        <v>-57.92307692307696</v>
+        <v>-58.92307692307696</v>
       </c>
       <c r="L18" s="29">
         <f>K18/4</f>
-        <v>-14.48076923076924</v>
-      </c>
-      <c r="Q18" s="60"/>
+        <v>-14.73076923076924</v>
+      </c>
+      <c r="Q18" s="61"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="61" t="s">
+      <c r="E19" s="62" t="s">
         <v>370</v>
       </c>
-      <c r="F19" s="62">
+      <c r="F19" s="63">
         <v>4</v>
       </c>
-      <c r="G19" s="63">
+      <c r="G19" s="64">
         <f t="shared" si="2"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H19" s="64">
+      <c r="H19" s="65">
         <f>B7/B3</f>
         <v>0.43023255813953487</v>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="66">
         <f>B3*G19</f>
         <v>264.61538461538464</v>
       </c>
-      <c r="J19" s="66">
+      <c r="J19" s="67">
         <f>B7</f>
         <v>370</v>
       </c>
-      <c r="K19" s="67">
+      <c r="K19" s="68">
         <f>J19-I19</f>
         <v>105.38461538461536</v>
       </c>
@@ -9701,118 +9729,118 @@
       </c>
     </row>
     <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="68" t="s">
+      <c r="E21" s="69" t="s">
         <v>374</v>
       </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G22" t="s">
         <v>373</v>
       </c>
       <c r="H22" t="s">
+        <v>361</v>
+      </c>
+      <c r="I22" s="46" t="s">
         <v>362</v>
       </c>
-      <c r="I22" s="45" t="s">
+      <c r="J22" s="46" t="s">
         <v>363</v>
       </c>
-      <c r="J22" s="45" t="s">
+      <c r="K22" t="s">
         <v>364</v>
-      </c>
-      <c r="K22" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="46" t="s">
-        <v>367</v>
-      </c>
-      <c r="F23" s="47">
+      <c r="E23" s="47" t="s">
+        <v>366</v>
+      </c>
+      <c r="F23" s="48">
         <v>3</v>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="49">
         <f t="shared" ref="G23:G25" si="3">F23/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H23" s="49">
-        <f>(B4+B5-13)/(B3-102)</f>
-        <v>0.1820580474934037</v>
-      </c>
-      <c r="I23" s="50">
-        <f>(B3-102) *G23</f>
-        <v>174.92307692307693</v>
-      </c>
-      <c r="J23" s="51">
-        <f>B4+B5-13</f>
-        <v>138</v>
-      </c>
-      <c r="K23" s="52">
+      <c r="H23" s="50">
+        <f>(B4+B5-C4)/(B3-C8)</f>
+        <v>0.18361955085865259</v>
+      </c>
+      <c r="I23" s="51">
+        <f>(B3-C8) *G23</f>
+        <v>174.6923076923077</v>
+      </c>
+      <c r="J23" s="52">
+        <f>B4+B5-C4</f>
+        <v>139</v>
+      </c>
+      <c r="K23" s="53">
         <f>J23-I23</f>
-        <v>-36.923076923076934</v>
+        <v>-35.69230769230771</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="53" t="s">
+      <c r="E24" s="54" t="s">
         <v>368</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="55">
         <v>6</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="56">
         <f t="shared" si="3"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H24" s="56">
-        <f>(B6-4)/(B3-102)</f>
-        <v>0.4419525065963061</v>
-      </c>
-      <c r="I24" s="57">
-        <f>(B3-102)*G24</f>
-        <v>349.84615384615387</v>
-      </c>
-      <c r="J24" s="58">
-        <f>B6-4</f>
-        <v>335</v>
-      </c>
-      <c r="K24" s="59">
+      <c r="H24" s="57">
+        <f>(B6-C4)/(B3-C8)</f>
+        <v>0.42932628797886396</v>
+      </c>
+      <c r="I24" s="58">
+        <f>(B3-C8)*G24</f>
+        <v>349.3846153846154</v>
+      </c>
+      <c r="J24" s="59">
+        <f>B6-C6</f>
+        <v>334</v>
+      </c>
+      <c r="K24" s="60">
         <f>J24-I24</f>
-        <v>-14.846153846153868</v>
+        <v>-15.384615384615415</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="61" t="s">
+      <c r="E25" s="62" t="s">
         <v>370</v>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="63">
         <v>4</v>
       </c>
-      <c r="G25" s="63">
+      <c r="G25" s="64">
         <f t="shared" si="3"/>
         <v>0.3076923076923077</v>
       </c>
-      <c r="H25" s="64">
-        <f>(B7-85)/(B3-102)</f>
-        <v>0.3759894459102902</v>
-      </c>
-      <c r="I25" s="65">
-        <f>(B3-102)*G25</f>
-        <v>233.23076923076925</v>
-      </c>
-      <c r="J25" s="66">
-        <f>B7-85</f>
-        <v>285</v>
-      </c>
-      <c r="K25" s="67">
+      <c r="H25" s="65">
+        <f>(B7-C7)/(B3-C8)</f>
+        <v>0.3751651254953765</v>
+      </c>
+      <c r="I25" s="66">
+        <f>(B3-C8)*G25</f>
+        <v>232.92307692307693</v>
+      </c>
+      <c r="J25" s="67">
+        <f>B7-C7</f>
+        <v>284</v>
+      </c>
+      <c r="K25" s="68">
         <f>J25-I25</f>
-        <v>51.769230769230745</v>
+        <v>51.076923076923066</v>
       </c>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.25">
@@ -9821,14 +9849,30 @@
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="70">
+        <f>C8/B9</f>
+        <v>0.11976744186046512</v>
+      </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="69">
-        <v>102</v>
+      <c r="J26" s="71">
+        <f>C8</f>
+        <v>103</v>
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>371</v>
+      </c>
+      <c r="J28">
+        <f>SUM(J23:J26)</f>
+        <v>860</v>
+      </c>
+      <c r="K28" s="72">
+        <f>SUM(K23:K25)</f>
+        <v>-5.684341886080802e-14</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E0E70-E1C1-4A3F-AAE4-6A7ED7050712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
+    <sheet name="AHL" sheetId="1" r:id="rId1"/>
+    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
+    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="394">
   <si>
     <t>sl</t>
   </si>
@@ -376,6 +390,9 @@
     <t>2024-11-26</t>
   </si>
   <si>
+    <t>2025-01-30</t>
+  </si>
+  <si>
     <t>2025-01-06</t>
   </si>
   <si>
@@ -403,6 +420,9 @@
     <t>2025-01-14</t>
   </si>
   <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
     <t>2024-11-24</t>
   </si>
   <si>
@@ -424,6 +444,12 @@
     <t>2025-01-03</t>
   </si>
   <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
+    <t>2025-01-26</t>
+  </si>
+  <si>
     <t>2025-01-22</t>
   </si>
   <si>
@@ -436,6 +462,9 @@
     <t>2024-12-27</t>
   </si>
   <si>
+    <t>2025-01-29</t>
+  </si>
+  <si>
     <t>HuberRe</t>
   </si>
   <si>
@@ -634,6 +663,21 @@
     <t>Eishalle Jesenice;MetzingerFi;SnojTa;KnezRo;MarkizetiGr</t>
   </si>
   <si>
+    <t>Würtharena Neumarkt;BajtMi;EggerTh;ArlicMa;BrondiPa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;LebenJa;WidmannFl;JavornikBl;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LazzeriAl;LehnerMo;GrisentiLu;MattheyPh</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;SoraperraSi;StefenelliFe;FecchioFe;JägerRi</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BrockAd;SnojTa;MarkizetiGr;WendnerMa</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -763,6 +807,12 @@
     <t>Sportpark Kitzbühel;KainbergerJu;RuetzMa;AbeltinoSi;RinkerDa</t>
   </si>
   <si>
+    <t>Eisarena Salzburg;HlavatyAl;VoicanCh;PreiserJu;WeissAl</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HolzerTo;SpiegelSe;DivisDo;StrimitzerDa</t>
+  </si>
+  <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
   </si>
   <si>
@@ -874,6 +924,12 @@
     <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;JavornikBl;WuchererGe</t>
   </si>
   <si>
+    <t>KELIT Arena Zell am See;KainbergerJu;OrelSt;SeewaldJe;WuchererGe</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;Huber rRe;RuetzMa;EislCh;ZacherlPa</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -979,6 +1035,12 @@
     <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;RivisAn</t>
   </si>
   <si>
+    <t>Eishalle Gröden;BulovecMi;VirtaTu;JeramFi;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;MoschenAn;PirasAn;AbeltinoSi;FormaioniTh</t>
+  </si>
+  <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
   </si>
   <si>
@@ -1054,6 +1116,12 @@
     <t>Eishalle Gröden;HolzerTo;LegaSi;CusinFe;DivisDo</t>
   </si>
   <si>
+    <t>Eishalle Cortina;BenvegnuAn;PinieOm;CristeliMa;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;GiacomozziFe;RivisFe;FleischmannLu;RivisAn</t>
+  </si>
+  <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
   </si>
   <si>
@@ -1135,9 +1203,6 @@
     <t>kontrola</t>
   </si>
   <si>
-    <t>till 23.1.2025</t>
-  </si>
-  <si>
     <t>% games per team</t>
   </si>
   <si>
@@ -1145,58 +1210,61 @@
   </si>
   <si>
     <t>trainnees</t>
+  </si>
+  <si>
+    <t>till 30.1.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF9C0006"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF006100"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="36"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="36"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1208,25 +1276,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1238,7 +1306,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1255,7 +1323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1266,69 +1334,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="20">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="mediumDashDot">
-        <color theme="8" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick"/>
-      <bottom style="mediumDashDot">
-        <color theme="8" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="mediumDashDot">
-        <color theme="4" tint="-0.249977111117893"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1580,138 +1596,132 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="12" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1991,9 +2001,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR73"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BQ73"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -2066,30 +2076,30 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1">
         <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
@@ -2101,11 +2111,11 @@
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I69,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
@@ -2121,47 +2131,47 @@
       </c>
       <c r="N1">
         <f>COUNTIF(N4:N67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O1">
         <f>COUNTIF(O4:O67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P1">
         <f t="shared" ref="P1:BF1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1">
         <f>COUNTIF(R4:R64,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U1">
         <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W1">
         <f>COUNTIF(W4:W69,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X1">
         <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y1">
         <f>COUNTIF(Y4:Y68,"&lt;&gt;")</f>
@@ -2169,7 +2179,7 @@
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA1">
         <f>COUNTIF(AA4:AA65,"&lt;&gt;")</f>
@@ -2177,19 +2187,19 @@
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD68,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF63,"&lt;&gt;")</f>
@@ -2197,11 +2207,11 @@
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG66,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
@@ -2209,31 +2219,31 @@
       </c>
       <c r="AJ1">
         <f>COUNTIF(AJ4:AJ62,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK1">
         <f>COUNTIF(AK4:AK65,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL65,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM66,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN64,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP1">
         <f>COUNTIF(AP4:AP67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ1">
         <f>COUNTIF(AQ4:AQ68,"&lt;&gt;")</f>
@@ -2241,19 +2251,19 @@
       </c>
       <c r="AR1">
         <f>COUNTIF(AR4:AR61,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT1">
         <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU1">
         <f>COUNTIF(AU4:AU69,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV65,"&lt;&gt;")</f>
@@ -2261,7 +2271,7 @@
       </c>
       <c r="AW1">
         <f>COUNTIF(AW4:AW65,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
@@ -2269,31 +2279,31 @@
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY63,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ65,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB69,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC68,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD1">
         <f>COUNTIF(BD4:BD69,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE1">
         <f>COUNTIF(BE4:BE67,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF1">
         <f t="shared" si="0"/>
@@ -2301,7 +2311,7 @@
       </c>
       <c r="BG1">
         <f>COUNTIF(BG4:BG66,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH1">
         <f>COUNTIF(BH4:BH69,"&lt;&gt;")</f>
@@ -2313,11 +2323,11 @@
       </c>
       <c r="BJ1">
         <f>COUNTIF(BJ4:BJ68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BL1">
         <f t="shared" si="1"/>
@@ -2325,11 +2335,11 @@
       </c>
       <c r="BM1">
         <f t="shared" ref="BM1" si="2">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BO1">
         <f t="shared" si="1"/>
@@ -2337,14 +2347,14 @@
       </c>
       <c r="BP1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BQ1">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2553,7 +2563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2755,14 +2765,14 @@
       <c r="BO3" t="s">
         <v>70</v>
       </c>
-      <c r="BP3" s="6" t="s">
+      <c r="BP3" t="s">
         <v>71</v>
       </c>
       <c r="BQ3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -2943,7 +2953,7 @@
       <c r="BH4" t="s">
         <v>80</v>
       </c>
-      <c r="BI4" s="7" t="s">
+      <c r="BI4" t="s">
         <v>76</v>
       </c>
       <c r="BJ4" t="s">
@@ -2971,7 +2981,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -2999,7 +3009,7 @@
       <c r="I5" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" t="s">
         <v>93</v>
       </c>
       <c r="K5" t="s">
@@ -3008,7 +3018,6 @@
       <c r="L5" t="s">
         <v>80</v>
       </c>
-      <c r="M5" s="8"/>
       <c r="N5" t="s">
         <v>75</v>
       </c>
@@ -3072,7 +3081,7 @@
       <c r="AH5" t="s">
         <v>93</v>
       </c>
-      <c r="AI5" s="9" t="s">
+      <c r="AI5" t="s">
         <v>95</v>
       </c>
       <c r="AJ5" t="s">
@@ -3144,7 +3153,7 @@
       <c r="BF5" t="s">
         <v>77</v>
       </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BG5" t="s">
         <v>100</v>
       </c>
       <c r="BH5" t="s">
@@ -3156,11 +3165,10 @@
       <c r="BK5" t="s">
         <v>99</v>
       </c>
-      <c r="BL5" s="8"/>
       <c r="BM5" t="s">
         <v>90</v>
       </c>
-      <c r="BN5" s="9" t="s">
+      <c r="BN5" t="s">
         <v>91</v>
       </c>
       <c r="BO5" t="s">
@@ -3173,7 +3181,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3240,7 +3248,7 @@
       <c r="W6" t="s">
         <v>86</v>
       </c>
-      <c r="X6" s="8" t="s">
+      <c r="X6" t="s">
         <v>104</v>
       </c>
       <c r="Y6" t="s">
@@ -3270,7 +3278,7 @@
       <c r="AG6" t="s">
         <v>84</v>
       </c>
-      <c r="AH6" s="6" t="s">
+      <c r="AH6" t="s">
         <v>105</v>
       </c>
       <c r="AI6" t="s">
@@ -3339,41 +3347,41 @@
       <c r="BD6" t="s">
         <v>98</v>
       </c>
-      <c r="BE6" s="9" t="s">
+      <c r="BE6" t="s">
         <v>95</v>
       </c>
-      <c r="BF6" s="9" t="s">
+      <c r="BF6" t="s">
         <v>91</v>
       </c>
-      <c r="BG6" s="8" t="s">
+      <c r="BG6" t="s">
         <v>109</v>
       </c>
       <c r="BH6" t="s">
         <v>110</v>
       </c>
-      <c r="BJ6" s="9" t="s">
+      <c r="BJ6" t="s">
         <v>91</v>
       </c>
-      <c r="BK6" s="6" t="s">
+      <c r="BK6" t="s">
         <v>81</v>
       </c>
-      <c r="BM6" s="9" t="s">
+      <c r="BM6" t="s">
         <v>102</v>
       </c>
       <c r="BN6" t="s">
         <v>94</v>
       </c>
-      <c r="BO6" s="9" t="s">
+      <c r="BO6" t="s">
         <v>102</v>
       </c>
       <c r="BP6" t="s">
         <v>94</v>
       </c>
-      <c r="BQ6" s="7" t="s">
+      <c r="BQ6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -3392,7 +3400,7 @@
       <c r="F7" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" t="s">
         <v>93</v>
       </c>
       <c r="H7" t="s">
@@ -3440,7 +3448,7 @@
       <c r="W7" t="s">
         <v>84</v>
       </c>
-      <c r="X7" s="7" t="s">
+      <c r="X7" t="s">
         <v>112</v>
       </c>
       <c r="Y7" t="s">
@@ -3452,7 +3460,7 @@
       <c r="AA7" t="s">
         <v>105</v>
       </c>
-      <c r="AB7" s="9" t="s">
+      <c r="AB7" t="s">
         <v>102</v>
       </c>
       <c r="AC7" t="s">
@@ -3473,13 +3481,13 @@
       <c r="AH7" t="s">
         <v>91</v>
       </c>
-      <c r="AI7" s="8" t="s">
+      <c r="AI7" t="s">
         <v>104</v>
       </c>
       <c r="AJ7" t="s">
         <v>106</v>
       </c>
-      <c r="AK7" s="9" t="s">
+      <c r="AK7" t="s">
         <v>113</v>
       </c>
       <c r="AL7" t="s">
@@ -3545,10 +3553,10 @@
       <c r="BF7" t="s">
         <v>102</v>
       </c>
-      <c r="BG7" s="7" t="s">
+      <c r="BG7" t="s">
         <v>114</v>
       </c>
-      <c r="BH7" s="9" t="s">
+      <c r="BH7" t="s">
         <v>115</v>
       </c>
       <c r="BJ7" t="s">
@@ -3566,15 +3574,15 @@
       <c r="BO7" t="s">
         <v>94</v>
       </c>
-      <c r="BP7" s="8" t="s">
+      <c r="BP7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
@@ -3601,7 +3609,7 @@
       <c r="K8" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" t="s">
         <v>113</v>
       </c>
       <c r="N8" t="s">
@@ -3634,13 +3642,16 @@
       <c r="W8" t="s">
         <v>108</v>
       </c>
+      <c r="X8" t="s">
+        <v>119</v>
+      </c>
       <c r="Y8" t="s">
         <v>79</v>
       </c>
       <c r="Z8" t="s">
         <v>77</v>
       </c>
-      <c r="AA8" s="6" t="s">
+      <c r="AA8" t="s">
         <v>79</v>
       </c>
       <c r="AB8" t="s">
@@ -3649,7 +3660,7 @@
       <c r="AC8" t="s">
         <v>79</v>
       </c>
-      <c r="AD8" s="6" t="s">
+      <c r="AD8" t="s">
         <v>105</v>
       </c>
       <c r="AE8" t="s">
@@ -3665,7 +3676,7 @@
         <v>114</v>
       </c>
       <c r="AI8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="s">
         <v>77</v>
@@ -3730,23 +3741,23 @@
       <c r="BD8" t="s">
         <v>88</v>
       </c>
-      <c r="BE8" s="10" t="s">
-        <v>120</v>
+      <c r="BE8" t="s">
+        <v>121</v>
       </c>
       <c r="BF8" t="s">
         <v>95</v>
       </c>
       <c r="BG8" t="s">
-        <v>121</v>
-      </c>
-      <c r="BH8" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="BH8" t="s">
         <v>92</v>
       </c>
-      <c r="BJ8" s="8" t="s">
+      <c r="BJ8" t="s">
         <v>117</v>
       </c>
       <c r="BK8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BM8" t="s">
         <v>114</v>
@@ -3754,14 +3765,14 @@
       <c r="BN8" t="s">
         <v>115</v>
       </c>
-      <c r="BO8" s="8" t="s">
+      <c r="BO8" t="s">
         <v>104</v>
       </c>
       <c r="BP8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -3777,25 +3788,25 @@
       <c r="E9" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" t="s">
         <v>115</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" t="s">
         <v>104</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" t="s">
         <v>113</v>
       </c>
       <c r="L9" t="s">
         <v>106</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" t="s">
         <v>101</v>
       </c>
       <c r="O9" t="s">
@@ -3819,7 +3830,7 @@
       <c r="U9" t="s">
         <v>90</v>
       </c>
-      <c r="V9" s="9" t="s">
+      <c r="V9" t="s">
         <v>91</v>
       </c>
       <c r="W9" t="s">
@@ -3843,28 +3854,28 @@
       <c r="AD9" t="s">
         <v>115</v>
       </c>
-      <c r="AE9" s="9" t="s">
+      <c r="AE9" t="s">
         <v>91</v>
       </c>
       <c r="AF9" t="s">
         <v>93</v>
       </c>
-      <c r="AG9" s="6" t="s">
+      <c r="AG9" t="s">
         <v>88</v>
       </c>
       <c r="AH9" t="s">
         <v>118</v>
       </c>
-      <c r="AI9" s="7" t="s">
+      <c r="AI9" t="s">
         <v>109</v>
       </c>
-      <c r="AJ9" s="6" t="s">
+      <c r="AJ9" t="s">
         <v>114</v>
       </c>
       <c r="AK9" t="s">
         <v>106</v>
       </c>
-      <c r="AL9" s="9" t="s">
+      <c r="AL9" t="s">
         <v>102</v>
       </c>
       <c r="AM9" t="s">
@@ -3876,7 +3887,7 @@
       <c r="AO9" t="s">
         <v>87</v>
       </c>
-      <c r="AP9" s="9" t="s">
+      <c r="AP9" t="s">
         <v>100</v>
       </c>
       <c r="AQ9" t="s">
@@ -3891,7 +3902,7 @@
       <c r="AT9" t="s">
         <v>79</v>
       </c>
-      <c r="AU9" s="9" t="s">
+      <c r="AU9" t="s">
         <v>100</v>
       </c>
       <c r="AV9" t="s">
@@ -3915,22 +3926,22 @@
       <c r="BB9" t="s">
         <v>88</v>
       </c>
-      <c r="BC9" s="9" t="s">
+      <c r="BC9" t="s">
         <v>100</v>
       </c>
-      <c r="BD9" s="9" t="s">
+      <c r="BD9" t="s">
         <v>102</v>
       </c>
       <c r="BE9" t="s">
-        <v>123</v>
-      </c>
-      <c r="BF9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF9" t="s">
         <v>94</v>
       </c>
       <c r="BG9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BH9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BH9" t="s">
         <v>112</v>
       </c>
       <c r="BJ9" t="s">
@@ -3939,30 +3950,30 @@
       <c r="BK9" t="s">
         <v>115</v>
       </c>
-      <c r="BM9" s="8" t="s">
+      <c r="BM9" t="s">
         <v>109</v>
       </c>
-      <c r="BN9" s="8" t="s">
+      <c r="BN9" t="s">
         <v>104</v>
       </c>
-      <c r="BO9" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="BP9" s="7" t="s">
-        <v>120</v>
+      <c r="BO9" t="s">
+        <v>121</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>100</v>
       </c>
       <c r="B10" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" t="s">
         <v>91</v>
       </c>
       <c r="E10" t="s">
@@ -3987,12 +3998,12 @@
         <v>114</v>
       </c>
       <c r="N10" t="s">
-        <v>122</v>
-      </c>
-      <c r="O10" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="O10" t="s">
         <v>102</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" t="s">
         <v>95</v>
       </c>
       <c r="Q10" t="s">
@@ -4007,7 +4018,7 @@
       <c r="T10" t="s">
         <v>81</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="U10" t="s">
         <v>102</v>
       </c>
       <c r="V10" t="s">
@@ -4016,10 +4027,10 @@
       <c r="W10" t="s">
         <v>88</v>
       </c>
-      <c r="Y10" s="9" t="s">
+      <c r="Y10" t="s">
         <v>87</v>
       </c>
-      <c r="Z10" s="9" t="s">
+      <c r="Z10" t="s">
         <v>113</v>
       </c>
       <c r="AA10" t="s">
@@ -4028,7 +4039,7 @@
       <c r="AB10" t="s">
         <v>94</v>
       </c>
-      <c r="AC10" s="6" t="s">
+      <c r="AC10" t="s">
         <v>88</v>
       </c>
       <c r="AD10" t="s">
@@ -4047,21 +4058,21 @@
         <v>115</v>
       </c>
       <c r="AI10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AJ10" t="s">
         <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
       </c>
-      <c r="AM10" s="9" t="s">
+      <c r="AM10" t="s">
         <v>100</v>
       </c>
-      <c r="AN10" s="9" t="s">
+      <c r="AN10" t="s">
         <v>100</v>
       </c>
       <c r="AO10" t="s">
@@ -4070,13 +4081,13 @@
       <c r="AP10" t="s">
         <v>91</v>
       </c>
-      <c r="AQ10" s="9" t="s">
+      <c r="AQ10" t="s">
         <v>95</v>
       </c>
       <c r="AR10" t="s">
         <v>77</v>
       </c>
-      <c r="AS10" s="9" t="s">
+      <c r="AS10" t="s">
         <v>100</v>
       </c>
       <c r="AT10" t="s">
@@ -4085,16 +4096,16 @@
       <c r="AU10" t="s">
         <v>91</v>
       </c>
-      <c r="AV10" s="6" t="s">
+      <c r="AV10" t="s">
         <v>101</v>
       </c>
-      <c r="AW10" s="9" t="s">
+      <c r="AW10" t="s">
         <v>102</v>
       </c>
       <c r="AX10" t="s">
         <v>88</v>
       </c>
-      <c r="AY10" s="9" t="s">
+      <c r="AY10" t="s">
         <v>100</v>
       </c>
       <c r="AZ10" t="s">
@@ -4113,15 +4124,18 @@
         <v>116</v>
       </c>
       <c r="BE10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF10" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>129</v>
       </c>
       <c r="BH10" t="s">
-        <v>121</v>
-      </c>
-      <c r="BJ10" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ10" t="s">
         <v>104</v>
       </c>
       <c r="BK10" t="s">
@@ -4134,13 +4148,13 @@
         <v>112</v>
       </c>
       <c r="BO10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BP10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -4153,26 +4167,26 @@
       <c r="D11" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" t="s">
         <v>102</v>
       </c>
       <c r="F11" t="s">
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I11" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>129</v>
+      <c r="J11" t="s">
+        <v>131</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4192,14 +4206,14 @@
       <c r="S11" t="s">
         <v>93</v>
       </c>
-      <c r="T11" s="9" t="s">
+      <c r="T11" t="s">
         <v>95</v>
       </c>
       <c r="U11" t="s">
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4213,7 +4227,7 @@
       <c r="AA11" t="s">
         <v>114</v>
       </c>
-      <c r="AB11" s="8" t="s">
+      <c r="AB11" t="s">
         <v>104</v>
       </c>
       <c r="AC11" t="s">
@@ -4223,7 +4237,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4235,10 +4249,10 @@
         <v>100</v>
       </c>
       <c r="AI11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AJ11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4253,7 +4267,7 @@
         <v>91</v>
       </c>
       <c r="AO11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="s">
         <v>115</v>
@@ -4261,7 +4275,7 @@
       <c r="AQ11" t="s">
         <v>106</v>
       </c>
-      <c r="AR11" s="9" t="s">
+      <c r="AR11" t="s">
         <v>100</v>
       </c>
       <c r="AS11" t="s">
@@ -4270,7 +4284,7 @@
       <c r="AT11" t="s">
         <v>90</v>
       </c>
-      <c r="AU11" s="6" t="s">
+      <c r="AU11" t="s">
         <v>94</v>
       </c>
       <c r="AV11" t="s">
@@ -4285,10 +4299,10 @@
       <c r="AY11" t="s">
         <v>91</v>
       </c>
-      <c r="AZ11" s="9" t="s">
+      <c r="AZ11" t="s">
         <v>100</v>
       </c>
-      <c r="BA11" s="9" t="s">
+      <c r="BA11" t="s">
         <v>91</v>
       </c>
       <c r="BB11" t="s">
@@ -4300,60 +4314,63 @@
       <c r="BD11" t="s">
         <v>118</v>
       </c>
+      <c r="BE11" t="s">
+        <v>119</v>
+      </c>
       <c r="BF11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BJ11" t="s">
+        <v>122</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>104</v>
+      </c>
+      <c r="BM11" t="s">
         <v>121</v>
       </c>
-      <c r="BK11" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>120</v>
-      </c>
       <c r="BN11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BO11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BP11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" t="s">
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="F12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" t="s">
         <v>92</v>
       </c>
       <c r="I12" t="s">
         <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K12" t="s">
-        <v>126</v>
-      </c>
-      <c r="L12" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12" t="s">
         <v>112</v>
       </c>
       <c r="N12" t="s">
@@ -4365,13 +4382,13 @@
       <c r="P12" t="s">
         <v>106</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" t="s">
         <v>107</v>
       </c>
       <c r="R12" t="s">
-        <v>122</v>
-      </c>
-      <c r="S12" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="S12" t="s">
         <v>107</v>
       </c>
       <c r="T12" t="s">
@@ -4380,53 +4397,53 @@
       <c r="U12" t="s">
         <v>115</v>
       </c>
-      <c r="V12" s="8" t="s">
+      <c r="V12" t="s">
         <v>106</v>
       </c>
-      <c r="W12" s="9" t="s">
+      <c r="W12" t="s">
         <v>100</v>
       </c>
-      <c r="Y12" s="7" t="s">
+      <c r="Y12" t="s">
         <v>95</v>
       </c>
       <c r="Z12" t="s">
         <v>115</v>
       </c>
-      <c r="AA12" s="8" t="s">
+      <c r="AA12" t="s">
         <v>91</v>
       </c>
       <c r="AB12" t="s">
         <v>112</v>
       </c>
-      <c r="AC12" s="8" t="s">
+      <c r="AC12" t="s">
         <v>117</v>
       </c>
       <c r="AD12" t="s">
         <v>88</v>
       </c>
-      <c r="AE12" s="8" t="s">
+      <c r="AE12" t="s">
         <v>111</v>
       </c>
-      <c r="AF12" s="8" t="s">
+      <c r="AF12" t="s">
         <v>109</v>
       </c>
-      <c r="AG12" s="8" t="s">
+      <c r="AG12" t="s">
         <v>109</v>
       </c>
-      <c r="AH12" s="8" t="s">
+      <c r="AH12" t="s">
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ12" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>92</v>
       </c>
       <c r="AK12" t="s">
         <v>95</v>
       </c>
       <c r="AL12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4435,7 +4452,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4446,23 +4463,23 @@
       <c r="AR12" t="s">
         <v>102</v>
       </c>
-      <c r="AS12" s="8" t="s">
+      <c r="AS12" t="s">
         <v>117</v>
       </c>
-      <c r="AT12" s="9" t="s">
+      <c r="AT12" t="s">
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV12" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV12" t="s">
         <v>109</v>
       </c>
-      <c r="AW12" s="8" t="s">
+      <c r="AW12" t="s">
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4473,30 +4490,33 @@
       <c r="BA12" t="s">
         <v>102</v>
       </c>
-      <c r="BB12" s="9" t="s">
+      <c r="BB12" t="s">
         <v>100</v>
       </c>
-      <c r="BC12" s="8" t="s">
+      <c r="BC12" t="s">
         <v>104</v>
       </c>
-      <c r="BD12" s="8" t="s">
+      <c r="BD12" t="s">
         <v>103</v>
       </c>
       <c r="BJ12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BK12" t="s">
-        <v>119</v>
-      </c>
-      <c r="BM12" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="BN12" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>120</v>
+      </c>
+      <c r="BN12" t="s">
         <v>114</v>
       </c>
+      <c r="BP12" t="s">
+        <v>137</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>92</v>
       </c>
       <c r="B13" t="s">
@@ -4511,25 +4531,25 @@
       <c r="E13" t="s">
         <v>106</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>119</v>
+      <c r="F13" t="s">
+        <v>120</v>
       </c>
       <c r="H13" t="s">
         <v>111</v>
       </c>
       <c r="I13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J13" t="s">
-        <v>130</v>
-      </c>
-      <c r="K13" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="K13" t="s">
         <v>112</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
-      </c>
-      <c r="N13" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="N13" t="s">
         <v>109</v>
       </c>
       <c r="O13" t="s">
@@ -4571,14 +4591,14 @@
       <c r="AC13" t="s">
         <v>109</v>
       </c>
-      <c r="AD13" s="8" t="s">
+      <c r="AD13" t="s">
         <v>109</v>
       </c>
-      <c r="AE13" s="7" t="s">
+      <c r="AE13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF13" t="s">
         <v>120</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>119</v>
       </c>
       <c r="AG13" t="s">
         <v>103</v>
@@ -4587,13 +4607,13 @@
         <v>111</v>
       </c>
       <c r="AJ13" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL13" t="s">
         <v>132</v>
-      </c>
-      <c r="AK13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>130</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4601,38 +4621,38 @@
       <c r="AN13" t="s">
         <v>115</v>
       </c>
-      <c r="AO13" s="7" t="s">
+      <c r="AO13" t="s">
         <v>103</v>
       </c>
       <c r="AP13" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ13" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ13" t="s">
         <v>117</v>
       </c>
       <c r="AR13" t="s">
         <v>106</v>
       </c>
-      <c r="AS13" s="7" t="s">
-        <v>131</v>
+      <c r="AS13" t="s">
+        <v>133</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
       </c>
-      <c r="AU13" s="7" t="s">
-        <v>120</v>
+      <c r="AU13" t="s">
+        <v>121</v>
       </c>
       <c r="AV13" t="s">
         <v>112</v>
       </c>
       <c r="AW13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AX13" t="s">
         <v>118</v>
       </c>
       <c r="AY13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AZ13" t="s">
         <v>115</v>
@@ -4643,60 +4663,66 @@
       <c r="BB13" t="s">
         <v>102</v>
       </c>
-      <c r="BC13" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="BD13" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="BK13" s="7" t="s">
+      <c r="BC13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>121</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>137</v>
+      </c>
+      <c r="BK13" t="s">
         <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BN13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="C14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" t="s">
         <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>129</v>
+        <v>122</v>
+      </c>
+      <c r="H14" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" t="s">
+        <v>131</v>
+      </c>
+      <c r="L14" t="s">
+        <v>131</v>
       </c>
       <c r="N14" t="s">
         <v>111</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="O14" t="s">
         <v>90</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="P14" t="s">
         <v>104</v>
       </c>
       <c r="Q14" t="s">
@@ -4708,7 +4734,7 @@
       <c r="S14" t="s">
         <v>115</v>
       </c>
-      <c r="T14" s="8" t="s">
+      <c r="T14" t="s">
         <v>104</v>
       </c>
       <c r="U14" t="s">
@@ -4721,12 +4747,12 @@
         <v>106</v>
       </c>
       <c r="Z14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
       </c>
-      <c r="AB14" s="7" t="s">
+      <c r="AB14" t="s">
         <v>92</v>
       </c>
       <c r="AC14" t="s">
@@ -4736,120 +4762,123 @@
         <v>112</v>
       </c>
       <c r="AE14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AF14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="AF14" t="s">
         <v>111</v>
       </c>
-      <c r="AG14" s="7" t="s">
+      <c r="AG14" t="s">
         <v>117</v>
       </c>
       <c r="AH14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK14" t="s">
         <v>103</v>
       </c>
       <c r="AL14" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM14" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM14" t="s">
         <v>92</v>
       </c>
-      <c r="AN14" s="8" t="s">
+      <c r="AN14" t="s">
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="AP14" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ14" s="7" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>131</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
       </c>
       <c r="AU14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AV14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AW14" t="s">
         <v>91</v>
       </c>
-      <c r="AX14" s="8" t="s">
+      <c r="AX14" t="s">
         <v>92</v>
       </c>
       <c r="AY14" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>124</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>139</v>
+      </c>
+      <c r="BM14" t="s">
         <v>125</v>
       </c>
-      <c r="AZ14" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="BA14" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="BB14" t="s">
+      <c r="BN14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" t="s">
         <v>122</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>121</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK14" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM14" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" t="s">
-        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" t="s">
         <v>92</v>
       </c>
       <c r="F15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" t="s">
         <v>124</v>
       </c>
-      <c r="H15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I15" t="s">
-        <v>123</v>
-      </c>
       <c r="K15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L15" t="s">
-        <v>124</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>131</v>
+        <v>125</v>
+      </c>
+      <c r="N15" t="s">
+        <v>133</v>
       </c>
       <c r="O15" t="s">
         <v>111</v>
@@ -4872,70 +4901,76 @@
       <c r="U15" t="s">
         <v>100</v>
       </c>
-      <c r="V15" s="7" t="s">
-        <v>129</v>
+      <c r="V15" t="s">
+        <v>131</v>
       </c>
       <c r="W15" t="s">
         <v>114</v>
       </c>
-      <c r="Z15" s="8" t="s">
+      <c r="Z15" t="s">
         <v>109</v>
       </c>
       <c r="AA15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AC15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AD15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AE15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH15" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>129</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
+      <c r="AL15" t="s">
+        <v>129</v>
+      </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AO15" t="s">
-        <v>127</v>
-      </c>
-      <c r="AP15" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP15" t="s">
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>136</v>
-      </c>
-      <c r="AR15" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AR15" t="s">
         <v>104</v>
       </c>
       <c r="AS15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AT15" t="s">
         <v>107</v>
       </c>
       <c r="AU15" t="s">
-        <v>124</v>
-      </c>
-      <c r="AV15" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV15" t="s">
         <v>103</v>
       </c>
       <c r="AW15" t="s">
@@ -4945,7 +4980,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -4953,52 +4988,58 @@
       <c r="BA15" t="s">
         <v>103</v>
       </c>
-      <c r="BB15" s="8" t="s">
+      <c r="BB15" t="s">
         <v>104</v>
       </c>
       <c r="BC15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BD15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BK15" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
         <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
         <v>103</v>
       </c>
+      <c r="F16" t="s">
+        <v>138</v>
+      </c>
       <c r="H16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N16" t="s">
-        <v>125</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>119</v>
+        <v>126</v>
+      </c>
+      <c r="O16" t="s">
+        <v>120</v>
       </c>
       <c r="P16" t="s">
         <v>111</v>
@@ -5009,389 +5050,513 @@
       <c r="R16" t="s">
         <v>103</v>
       </c>
-      <c r="S16" s="8" t="s">
+      <c r="S16" t="s">
         <v>109</v>
       </c>
-      <c r="T16" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="U16" s="8" t="s">
+      <c r="T16" t="s">
+        <v>133</v>
+      </c>
+      <c r="U16" t="s">
         <v>104</v>
       </c>
       <c r="V16" t="s">
-        <v>124</v>
-      </c>
-      <c r="W16" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="W16" t="s">
         <v>104</v>
       </c>
       <c r="Z16" t="s">
         <v>111</v>
       </c>
-      <c r="AA16" s="7" t="s">
+      <c r="AA16" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD16" t="s">
         <v>119</v>
       </c>
-      <c r="AB16" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC16" s="7" t="s">
-        <v>92</v>
+      <c r="AE16" t="s">
+        <v>119</v>
       </c>
       <c r="AF16" t="s">
-        <v>130</v>
+        <v>132</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>129</v>
       </c>
       <c r="AH16" t="s">
         <v>92</v>
       </c>
       <c r="AK16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AM16" t="s">
-        <v>131</v>
-      </c>
-      <c r="AN16" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>136</v>
       </c>
       <c r="AO16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AP16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AQ16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AR16" t="s">
         <v>112</v>
       </c>
-      <c r="AT16" s="8" t="s">
+      <c r="AS16" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT16" t="s">
         <v>104</v>
       </c>
       <c r="AU16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AV16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AW16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AX16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AY16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AZ16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="BA16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
+      <c r="BC16" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>129</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>143</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" t="s">
         <v>129</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="L17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q17" t="s">
         <v>111</v>
       </c>
       <c r="R17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
       </c>
       <c r="T17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
       </c>
       <c r="V17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W17" t="s">
         <v>109</v>
       </c>
-      <c r="Z17" s="7" t="s">
-        <v>119</v>
+      <c r="Z17" t="s">
+        <v>120</v>
       </c>
       <c r="AA17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>134</v>
+      </c>
+      <c r="AF17" t="s">
         <v>125</v>
       </c>
-      <c r="AB17" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>132</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>124</v>
-      </c>
-      <c r="AK17" s="7" t="s">
-        <v>131</v>
+      <c r="AH17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>133</v>
       </c>
       <c r="AM17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AN17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AO17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AP17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AR17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
       </c>
+      <c r="AU17" t="s">
+        <v>129</v>
+      </c>
       <c r="AV17" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AW17" t="s">
         <v>94</v>
       </c>
-      <c r="AX17" s="7" t="s">
+      <c r="AX17" t="s">
+        <v>120</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>120</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>119</v>
       </c>
-      <c r="AZ17" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA17" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="BB17" t="s">
+      <c r="B18" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>140</v>
+      </c>
+      <c r="N18" t="s">
+        <v>129</v>
+      </c>
+      <c r="O18" t="s">
+        <v>134</v>
+      </c>
+      <c r="P18" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q18" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>136</v>
-      </c>
-      <c r="O18" t="s">
-        <v>132</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="R18" s="7" t="s">
+      <c r="R18" t="s">
         <v>111</v>
       </c>
       <c r="S18" t="s">
         <v>112</v>
       </c>
       <c r="T18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
       <c r="V18" t="s">
-        <v>130</v>
-      </c>
-      <c r="W18" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="W18" t="s">
         <v>111</v>
       </c>
       <c r="Z18" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>126</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AM18" t="s">
         <v>125</v>
       </c>
-      <c r="AA18" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM18" t="s">
-        <v>124</v>
-      </c>
       <c r="AN18" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>119</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>119</v>
       </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
       <c r="AT18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>139</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="O19" t="s">
+        <v>143</v>
+      </c>
+      <c r="P19" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>126</v>
+      </c>
+      <c r="R19" t="s">
+        <v>125</v>
+      </c>
+      <c r="S19" t="s">
+        <v>121</v>
+      </c>
+      <c r="T19" t="s">
+        <v>119</v>
+      </c>
+      <c r="U19" t="s">
         <v>120</v>
       </c>
-      <c r="AW18" t="s">
-        <v>121</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>127</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA18" t="s">
-        <v>135</v>
-      </c>
-      <c r="BB18" s="7" t="s">
+      <c r="V19" t="s">
         <v>133</v>
       </c>
+      <c r="W19" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>125</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>125</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="4:54" x14ac:dyDescent="0.25">
-      <c r="E19" t="s">
-        <v>130</v>
-      </c>
-      <c r="P19" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q19" t="s">
+    <row r="20" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>119</v>
+      </c>
+      <c r="P20" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>137</v>
+      </c>
+      <c r="R20" t="s">
+        <v>122</v>
+      </c>
+      <c r="S20" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" t="s">
+        <v>109</v>
+      </c>
+      <c r="V20" t="s">
+        <v>129</v>
+      </c>
+      <c r="W20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>122</v>
+      </c>
+      <c r="AR20" t="s">
         <v>125</v>
       </c>
-      <c r="R19" t="s">
-        <v>124</v>
-      </c>
-      <c r="S19" t="s">
-        <v>120</v>
-      </c>
-      <c r="U19" t="s">
+      <c r="AT20" t="s">
+        <v>128</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>129</v>
+      </c>
+      <c r="AZ20" t="s">
         <v>119</v>
       </c>
-      <c r="V19" t="s">
-        <v>131</v>
-      </c>
-      <c r="W19" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AR19" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="AT19" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>130</v>
-      </c>
-      <c r="AZ19" t="s">
-        <v>124</v>
-      </c>
-      <c r="BA19" t="s">
-        <v>124</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>137</v>
+      <c r="BA20" t="s">
+        <v>126</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="5:54" x14ac:dyDescent="0.25">
-      <c r="P20" t="s">
-        <v>125</v>
-      </c>
-      <c r="R20" t="s">
-        <v>121</v>
-      </c>
-      <c r="S20" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="W20" t="s">
-        <v>125</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>121</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>124</v>
-      </c>
-      <c r="AT20" t="s">
-        <v>127</v>
-      </c>
-      <c r="BA20" t="s">
-        <v>125</v>
-      </c>
-      <c r="BB20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>143</v>
+      </c>
       <c r="R21" t="s">
         <v>104</v>
       </c>
       <c r="S21" t="s">
+        <v>141</v>
+      </c>
+      <c r="U21" t="s">
+        <v>125</v>
+      </c>
+      <c r="V21" t="s">
+        <v>119</v>
+      </c>
+      <c r="W21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>120</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R22" t="s">
         <v>137</v>
       </c>
-      <c r="U21" t="s">
-        <v>124</v>
-      </c>
-      <c r="AR21" t="s">
+      <c r="S22" t="s">
+        <v>126</v>
+      </c>
+      <c r="U22" t="s">
+        <v>132</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>129</v>
+      </c>
+      <c r="AT22" t="s">
         <v>119</v>
       </c>
-      <c r="AT21" t="s">
-        <v>130</v>
-      </c>
-      <c r="BA21" t="s">
-        <v>138</v>
+      <c r="BA22" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
-      <c r="S22" t="s">
-        <v>125</v>
-      </c>
-      <c r="U22" t="s">
-        <v>130</v>
+    <row r="23" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S23" t="s">
+        <v>129</v>
+      </c>
+      <c r="U23" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="19:21" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5435,14 +5600,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BN42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A3:BS42"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -5487,7 +5652,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -5585,7 +5750,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5594,7 +5759,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK3" t="s">
         <v>115</v>
@@ -5612,10 +5777,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -5639,55 +5804,70 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>132</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BP3" t="s">
         <v>138</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>131</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BC3" t="s">
+      <c r="BQ3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BS3" t="s">
         <v>119</v>
       </c>
-      <c r="BD3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>137</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>136</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>135</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>127</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -5886,8 +6066,23 @@
       <c r="BN4" t="s">
         <v>14</v>
       </c>
+      <c r="BO4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>21</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6086,8 +6281,23 @@
       <c r="BN5" t="s">
         <v>4</v>
       </c>
+      <c r="BO5" t="s">
+        <v>39</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>54</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>71</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>29</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -6286,8 +6496,23 @@
       <c r="BN6" t="s">
         <v>15</v>
       </c>
+      <c r="BO6" t="s">
+        <v>7</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>20</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>19</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -6486,13 +6711,28 @@
       <c r="BN7" t="s">
         <v>8</v>
       </c>
+      <c r="BO7" t="s">
+        <v>22</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>42</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>65</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>66</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -6516,7 +6756,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -6617,8 +6857,14 @@
       <c r="BN8" t="s">
         <v>41</v>
       </c>
+      <c r="BO8" t="s">
+        <v>68</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -6632,7 +6878,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6748,8 +6994,14 @@
       <c r="BN9" t="s">
         <v>49</v>
       </c>
+      <c r="BO9" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -6879,8 +7131,14 @@
       <c r="BN10" t="s">
         <v>32</v>
       </c>
+      <c r="BO10" t="s">
+        <v>52</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -7010,8 +7268,14 @@
       <c r="BN11" t="s">
         <v>53</v>
       </c>
+      <c r="BO11" t="s">
+        <v>62</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -7037,7 +7301,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -7123,8 +7387,14 @@
       <c r="BN12" t="s">
         <v>11</v>
       </c>
+      <c r="BO12" t="s">
+        <v>41</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -7236,8 +7506,14 @@
       <c r="BN13" t="s">
         <v>54</v>
       </c>
+      <c r="BO13" t="s">
+        <v>47</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -7349,8 +7625,14 @@
       <c r="BN14" t="s">
         <v>13</v>
       </c>
+      <c r="BO14" t="s">
+        <v>59</v>
+      </c>
+      <c r="BS14" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -7462,8 +7744,14 @@
       <c r="BN15" t="s">
         <v>43</v>
       </c>
+      <c r="BO15" t="s">
+        <v>43</v>
+      </c>
+      <c r="BS15" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -7569,8 +7857,14 @@
       <c r="BN16" t="s">
         <v>38</v>
       </c>
+      <c r="BO16" t="s">
+        <v>6</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -7676,8 +7970,14 @@
       <c r="BN17" t="s">
         <v>24</v>
       </c>
+      <c r="BO17" t="s">
+        <v>26</v>
+      </c>
+      <c r="BS17" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -7783,8 +8083,14 @@
       <c r="BN18" t="s">
         <v>35</v>
       </c>
+      <c r="BO18" t="s">
+        <v>12</v>
+      </c>
+      <c r="BS18" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -7890,8 +8196,14 @@
       <c r="BN19" t="s">
         <v>25</v>
       </c>
+      <c r="BO19" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS19" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -7967,8 +8279,14 @@
       <c r="BM20" t="s">
         <v>56</v>
       </c>
+      <c r="BO20" t="s">
+        <v>17</v>
+      </c>
+      <c r="BS20" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -8044,8 +8362,14 @@
       <c r="BM21" t="s">
         <v>38</v>
       </c>
+      <c r="BO21" t="s">
+        <v>36</v>
+      </c>
+      <c r="BS21" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -8121,8 +8445,14 @@
       <c r="BM22" t="s">
         <v>35</v>
       </c>
+      <c r="BO22" t="s">
+        <v>40</v>
+      </c>
+      <c r="BS22" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -8198,8 +8528,14 @@
       <c r="BM23" t="s">
         <v>57</v>
       </c>
+      <c r="BO23" t="s">
+        <v>25</v>
+      </c>
+      <c r="BS23" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -8228,7 +8564,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -8257,7 +8593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -8286,7 +8622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -8315,11 +8651,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="55:65" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8335,10 +8671,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BN14"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A3:BS14"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -8420,7 +8756,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -8518,7 +8854,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -8527,7 +8863,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK3" t="s">
         <v>115</v>
@@ -8545,10 +8881,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -8572,726 +8908,780 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>136</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>124</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>132</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BP3" t="s">
         <v>138</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>120</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>131</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BC3" t="s">
+      <c r="BQ3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BS3" t="s">
         <v>119</v>
       </c>
-      <c r="BD3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>137</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>136</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>121</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>123</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>135</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>127</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="N4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Q4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="R4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="T4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="U4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="V4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="W4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="X4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Y4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="Z4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AA4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AB4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AC4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AD4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AE4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AF4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AH4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>185</v>
+      </c>
+      <c r="AP4" t="s">
         <v>173</v>
       </c>
-      <c r="AI4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>168</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AR4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AS4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AT4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AU4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AV4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AW4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AX4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AY4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AZ4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="BA4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="BB4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="BC4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="BD4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="BE4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="BF4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="BG4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="BH4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="BI4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="BJ4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="BK4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="BL4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="BM4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="BN4" t="s">
-        <v>204</v>
+        <v>209</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>212</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>213</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G5" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="H5" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="K5" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L5" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="N5" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="R5" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="T5" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="U5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="V5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="W5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="Y5" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="Z5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB5" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AD5" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="AE5" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="AF5" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="AI5" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="AK5" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="AL5" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AM5" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="AN5" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="AO5" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AR5" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="AS5" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="AT5" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="AU5" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="AV5" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="AW5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AX5" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AZ5" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="BA5" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="BB5" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="BC5" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="BG5" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="BH5" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="BJ5" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="BK5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="BM5" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="BN5" t="s">
-        <v>247</v>
+        <v>257</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>258</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>259</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="G6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="H6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K6" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="L6" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="N6" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="T6" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="V6" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="W6" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="Y6" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="Z6" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AB6" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="AD6" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AE6" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AI6" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AK6" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AM6" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AN6" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AO6" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AS6" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AT6" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="AU6" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AV6" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AW6" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AX6" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="AZ6" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="BA6" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="BB6" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="BC6" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="BG6" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="BJ6" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="BK6" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="BM6" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="BN6" t="s">
-        <v>284</v>
+        <v>296</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>297</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>298</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="F7" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="G7" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="H7" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="K7" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="L7" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="N7" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="P7" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="T7" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="V7" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="W7" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="Y7" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="Z7" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="AB7" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="AD7" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="AE7" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="AI7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="AK7" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="AM7" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="AN7" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="AO7" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="AS7" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="AT7" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="AU7" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="AV7" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="AW7" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="AX7" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="AZ7" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="BC7" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="BG7" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="BJ7" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="BK7" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="BM7" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="BN7" t="s">
-        <v>319</v>
+        <v>333</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>334</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>335</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="D8" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="F8" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="G8" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="H8" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="K8" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="L8" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="V8" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="W8" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="Y8" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="AB8" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="AD8" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="AE8" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="AI8" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="AK8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="AM8" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="AO8" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="AT8" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="AU8" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="AW8" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="AZ8" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="BC8" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="BG8" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="BK8" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="BM8" t="s">
-        <v>344</v>
+        <v>360</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>361</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>362</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:65" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="L9" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="AD9" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="AE9" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="AK9" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="AT9" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="BC9" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="BK9" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="BM9" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="55:65" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -9309,568 +9699,568 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="6">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="63" t="s">
+        <v>373</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="7">
         <f>C1*4</f>
-        <v>860</v>
+        <v>912</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="B3" s="19">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="9">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>860</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+        <v>912</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>374</v>
+      </c>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="B4" s="22">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" s="11">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C4">
         <f>AHL!I1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="F4" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="G4" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="H4" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="I4" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="J4" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="K4" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="L4" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="11">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>28</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="F5" s="24">
+      <c r="E5" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="F5" s="13">
         <v>2</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="14">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="15">
         <f>B4/B3</f>
-        <v>0.14418604651162792</v>
-      </c>
-      <c r="I5" s="27">
+        <v>0.14473684210526316</v>
+      </c>
+      <c r="I5" s="16">
         <f>C2*G5</f>
-        <v>132.30769230769232</v>
+        <v>140.30769230769232</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>124</v>
-      </c>
-      <c r="K5" s="28">
+        <v>132</v>
+      </c>
+      <c r="K5" s="17">
         <f>J5-I5</f>
-        <v>-8.30769230769232</v>
-      </c>
-      <c r="L5" s="29">
+        <v>-8.3076923076923208</v>
+      </c>
+      <c r="L5" s="18">
         <f>K5/4</f>
-        <v>-2.07692307692308</v>
+        <v>-2.0769230769230802</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="11">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C6">
         <f>AHL!X1</f>
-        <v>4</v>
-      </c>
-      <c r="E6" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="14">
         <f>F6/13</f>
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="H6" s="26">
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="H6" s="15">
         <f>B5/B3</f>
-        <v>0.03255813953488372</v>
-      </c>
-      <c r="I6" s="27">
+        <v>3.0701754385964911E-2</v>
+      </c>
+      <c r="I6" s="16">
         <f>C2*G6</f>
-        <v>66.15384615384616</v>
+        <v>70.15384615384616</v>
       </c>
       <c r="J6">
         <f>B5</f>
         <v>28</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="17">
         <f>J6-I6</f>
-        <v>-38.15384615384616</v>
-      </c>
-      <c r="L6" s="29">
+        <v>-42.15384615384616</v>
+      </c>
+      <c r="L6" s="18">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-9.53846153846154</v>
+        <v>-10.53846153846154</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="20">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C7">
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
-        <v>86</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="F7" s="33">
+        <v>93</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" s="22">
         <v>3</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="23">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="24">
         <f>(B5+B4)/B3</f>
-        <v>0.17674418604651163</v>
-      </c>
-      <c r="I7" s="27">
+        <v>0.17543859649122806</v>
+      </c>
+      <c r="I7" s="16">
         <f>C2*G7</f>
-        <v>198.46153846153848</v>
+        <v>210.46153846153848</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>152</v>
-      </c>
-      <c r="K7" s="28">
+        <v>160</v>
+      </c>
+      <c r="K7" s="17">
         <f>J7-I7</f>
-        <v>-46.46153846153848</v>
-      </c>
-      <c r="L7" s="29">
+        <v>-50.461538461538481</v>
+      </c>
+      <c r="L7" s="18">
         <f>K7/4</f>
-        <v>-11.61538461538462</v>
+        <v>-12.61538461538462</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
-        <v>367</v>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>385</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>103</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="F8" s="38">
+        <v>112</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="F8" s="27">
         <v>6</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="29">
         <f>B6/B3</f>
-        <v>0.3930232558139535</v>
-      </c>
-      <c r="I8" s="27">
+        <v>0.39364035087719296</v>
+      </c>
+      <c r="I8" s="16">
         <f>C2*G8</f>
-        <v>396.92307692307696</v>
+        <v>420.92307692307696</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>338</v>
-      </c>
-      <c r="K8" s="28">
+        <v>359</v>
+      </c>
+      <c r="K8" s="17">
         <f>J8-I8</f>
-        <v>-58.92307692307696</v>
-      </c>
-      <c r="L8" s="29">
+        <v>-61.923076923076962</v>
+      </c>
+      <c r="L8" s="18">
         <f>K8/4</f>
-        <v>-14.73076923076924</v>
+        <v>-15.480769230769241</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>860</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="F9" s="38">
+        <v>912</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="F9" s="27">
         <v>4</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="28">
         <f t="shared" si="1"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H9" s="40">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H9" s="29">
         <f>B7/B3</f>
-        <v>0.43023255813953487</v>
-      </c>
-      <c r="I9" s="27">
+        <v>0.43092105263157893</v>
+      </c>
+      <c r="I9" s="16">
         <f>C2*G9</f>
-        <v>264.61538461538464</v>
+        <v>280.61538461538464</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>370</v>
-      </c>
-      <c r="K9" s="41">
+        <v>393</v>
+      </c>
+      <c r="K9" s="30">
         <f>J9-I9</f>
-        <v>105.38461538461536</v>
-      </c>
-      <c r="L9" s="29">
+        <v>112.38461538461536</v>
+      </c>
+      <c r="L9" s="18">
         <f>K9/4</f>
-        <v>26.34615384615384</v>
+        <v>28.09615384615384</v>
       </c>
     </row>
-    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="42" t="s">
-        <v>371</v>
-      </c>
-      <c r="I11" s="43">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="I11" s="32">
         <f>SUM(I7:I9)</f>
-        <v>860.0000000000001</v>
-      </c>
-      <c r="J11" s="37">
+        <v>912.00000000000011</v>
+      </c>
+      <c r="J11" s="26">
         <f>SUM(J7:J9)</f>
-        <v>860</v>
-      </c>
-      <c r="K11" s="44">
+        <v>912</v>
+      </c>
+      <c r="K11" s="33">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="45">
+      <c r="L11" s="34">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="F16" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="G16" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="H16" t="s">
-        <v>361</v>
-      </c>
-      <c r="I16" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="J16" s="46" t="s">
-        <v>363</v>
+        <v>379</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>381</v>
       </c>
       <c r="K16" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="L16" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="47" t="s">
-        <v>366</v>
-      </c>
-      <c r="F17" s="48">
+    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E17" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="F17" s="37">
         <v>3</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="38">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="39">
         <f>(B5+B4)/B3</f>
-        <v>0.17674418604651163</v>
-      </c>
-      <c r="I17" s="51">
+        <v>0.17543859649122806</v>
+      </c>
+      <c r="I17" s="40">
         <f>B3*G17</f>
-        <v>198.46153846153848</v>
-      </c>
-      <c r="J17" s="52">
+        <v>210.46153846153848</v>
+      </c>
+      <c r="J17" s="41">
         <f>B5+B4</f>
-        <v>152</v>
-      </c>
-      <c r="K17" s="53">
+        <v>160</v>
+      </c>
+      <c r="K17" s="42">
         <f>J17-I17</f>
-        <v>-46.46153846153848</v>
-      </c>
-      <c r="L17" s="29">
+        <v>-50.461538461538481</v>
+      </c>
+      <c r="L17" s="18">
         <f>K17/4</f>
-        <v>-11.61538461538462</v>
+        <v>-12.61538461538462</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="F18" s="55">
+      <c r="E18" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="F18" s="44">
         <v>6</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="45">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="46">
         <f>B6/B3</f>
-        <v>0.3930232558139535</v>
-      </c>
-      <c r="I18" s="58">
+        <v>0.39364035087719296</v>
+      </c>
+      <c r="I18" s="47">
         <f>B3*G18</f>
-        <v>396.92307692307696</v>
-      </c>
-      <c r="J18" s="59">
+        <v>420.92307692307696</v>
+      </c>
+      <c r="J18" s="48">
         <f>B6</f>
-        <v>338</v>
-      </c>
-      <c r="K18" s="60">
+        <v>359</v>
+      </c>
+      <c r="K18" s="49">
         <f>J18-I18</f>
-        <v>-58.92307692307696</v>
-      </c>
-      <c r="L18" s="29">
+        <v>-61.923076923076962</v>
+      </c>
+      <c r="L18" s="18">
         <f>K18/4</f>
-        <v>-14.73076923076924</v>
-      </c>
-      <c r="Q18" s="61"/>
+        <v>-15.480769230769241</v>
+      </c>
+      <c r="Q18" s="50"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="F19" s="63">
+    <row r="19" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="F19" s="52">
         <v>4</v>
       </c>
-      <c r="G19" s="64">
+      <c r="G19" s="53">
         <f t="shared" si="2"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H19" s="65">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H19" s="54">
         <f>B7/B3</f>
-        <v>0.43023255813953487</v>
-      </c>
-      <c r="I19" s="66">
+        <v>0.43092105263157893</v>
+      </c>
+      <c r="I19" s="55">
         <f>B3*G19</f>
-        <v>264.61538461538464</v>
-      </c>
-      <c r="J19" s="67">
+        <v>280.61538461538464</v>
+      </c>
+      <c r="J19" s="56">
         <f>B7</f>
-        <v>370</v>
-      </c>
-      <c r="K19" s="68">
+        <v>393</v>
+      </c>
+      <c r="K19" s="57">
         <f>J19-I19</f>
-        <v>105.38461538461536</v>
-      </c>
-      <c r="L19" s="29">
+        <v>112.38461538461536</v>
+      </c>
+      <c r="L19" s="18">
         <f>K19/4</f>
-        <v>26.34615384615384</v>
+        <v>28.09615384615384</v>
       </c>
     </row>
-    <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="69" t="s">
-        <v>374</v>
-      </c>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
+    <row r="21" spans="5:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E21" s="66" t="s">
+        <v>391</v>
+      </c>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="G22" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="H22" t="s">
-        <v>361</v>
-      </c>
-      <c r="I22" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="J22" s="46" t="s">
-        <v>363</v>
+        <v>379</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="J22" s="35" t="s">
+        <v>381</v>
       </c>
       <c r="K22" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
     </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="47" t="s">
-        <v>366</v>
-      </c>
-      <c r="F23" s="48">
+    <row r="23" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E23" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="F23" s="37">
         <v>3</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="38">
         <f t="shared" ref="G23:G25" si="3">F23/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H23" s="50">
+      <c r="H23" s="39">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.18361955085865259</v>
-      </c>
-      <c r="I23" s="51">
+        <v>0.1825</v>
+      </c>
+      <c r="I23" s="40">
         <f>(B3-C8) *G23</f>
-        <v>174.6923076923077</v>
-      </c>
-      <c r="J23" s="52">
+        <v>184.61538461538461</v>
+      </c>
+      <c r="J23" s="41">
         <f>B4+B5-C4</f>
-        <v>139</v>
-      </c>
-      <c r="K23" s="53">
+        <v>146</v>
+      </c>
+      <c r="K23" s="42">
         <f>J23-I23</f>
-        <v>-35.69230769230771</v>
+        <v>-38.615384615384613</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="F24" s="55">
+    <row r="24" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="F24" s="44">
         <v>6</v>
       </c>
-      <c r="G24" s="56">
+      <c r="G24" s="45">
         <f t="shared" si="3"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="46">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.42932628797886396</v>
-      </c>
-      <c r="I24" s="58">
+        <v>0.43125000000000002</v>
+      </c>
+      <c r="I24" s="47">
         <f>(B3-C8)*G24</f>
-        <v>349.3846153846154</v>
-      </c>
-      <c r="J24" s="59">
+        <v>369.23076923076923</v>
+      </c>
+      <c r="J24" s="48">
         <f>B6-C6</f>
-        <v>334</v>
-      </c>
-      <c r="K24" s="60">
+        <v>354</v>
+      </c>
+      <c r="K24" s="49">
         <f>J24-I24</f>
-        <v>-15.384615384615415</v>
+        <v>-15.230769230769226</v>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="F25" s="63">
+    <row r="25" spans="5:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="F25" s="52">
         <v>4</v>
       </c>
-      <c r="G25" s="64">
+      <c r="G25" s="53">
         <f t="shared" si="3"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H25" s="65">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H25" s="54">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.3751651254953765</v>
-      </c>
-      <c r="I25" s="66">
+        <v>0.375</v>
+      </c>
+      <c r="I25" s="55">
         <f>(B3-C8)*G25</f>
-        <v>232.92307692307693</v>
-      </c>
-      <c r="J25" s="67">
+        <v>246.15384615384616</v>
+      </c>
+      <c r="J25" s="56">
         <f>B7-C7</f>
-        <v>284</v>
-      </c>
-      <c r="K25" s="68">
+        <v>300</v>
+      </c>
+      <c r="K25" s="57">
         <f>J25-I25</f>
-        <v>51.076923076923066</v>
+        <v>53.84615384615384</v>
       </c>
     </row>
-    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="70">
+      <c r="H26" s="58">
         <f>C8/B9</f>
-        <v>0.11976744186046512</v>
+        <v>0.12280701754385964</v>
       </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="71">
+      <c r="J26" s="59">
         <f>C8</f>
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>860</v>
-      </c>
-      <c r="K28" s="72">
+        <v>912</v>
+      </c>
+      <c r="K28" s="60">
         <f>SUM(K23:K25)</f>
-        <v>-5.684341886080802e-14</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E0E70-E1C1-4A3F-AAE4-6A7ED7050712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="AHL" sheetId="1" r:id="rId1"/>
-    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
-    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
-    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
+    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="395">
   <si>
     <t>sl</t>
   </si>
@@ -399,54 +385,57 @@
     <t>2025-01-02</t>
   </si>
   <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2025-01-21</t>
+  </si>
+  <si>
+    <t>2025-02-02</t>
+  </si>
+  <si>
+    <t>2025-01-16</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2025-01-14</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
+    <t>2025-01-11</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
     <t>2025-01-18</t>
   </si>
   <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2025-01-21</t>
-  </si>
-  <si>
-    <t>2025-01-11</t>
-  </si>
-  <si>
-    <t>2025-01-16</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2025-01-14</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
-    <t>2025-01-28</t>
-  </si>
-  <si>
     <t>2025-01-26</t>
   </si>
   <si>
@@ -462,6 +451,9 @@
     <t>2024-12-27</t>
   </si>
   <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
     <t>2025-01-29</t>
   </si>
   <si>
@@ -636,48 +628,51 @@
     <t>Eishalle Dornbirn;GiacomozziFe;Huber rRe;BrondiPa;DivisDo</t>
   </si>
   <si>
-    <t>Eishalle Ritten;BajtMi;MeixnerSe;MarkizetiGr;WendnerMa</t>
+    <t>Eishalle Ritten;MeixnerSe;SnojTa;JeramFi;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;BulovecMi;SoraperraSi;ArlicMa;CristeliMa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;LehnerMo;WidmannFl;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;HolzerTo;Huber rRe;JägerRi;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;Huber rRe;RuetzMa;RinkerDa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;SnojTa;WidmannFl;JavornikBl;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;MetzingerFi;SnojTa;KnezRo;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;EggerTh;SnojTa;ArlicMa;BrondiPa</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;LebenJa;WidmannFl;JavornikBl;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LazzeriAl;LehnerMo;GrisentiLu;MattheyPh</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;SoraperraSi;StefenelliFe;FecchioFe;JägerRi</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BrockAd;SnojTa;MarkizetiGr;WendnerMa</t>
   </si>
   <si>
     <t>Eishalle Jesenice;BrockAd;WenuschHe;WeissAl;WendnerMa</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;LehnerMo;WidmannFl;SeewaldJe;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;HolzerTo;Huber rRe;JägerRi;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;LehnerMo;MoidlDa;MattheyPh;MoidlMa</t>
-  </si>
-  <si>
-    <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;StrimitzerDa</t>
-  </si>
-  <si>
-    <t>Eisarena Salzburg;Huber rRe;RuetzMa;RinkerDa;ZacherlPa</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;SnojTa;WidmannFl;JavornikBl;WuchererGe</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;MetzingerFi;SnojTa;KnezRo;MarkizetiGr</t>
-  </si>
-  <si>
-    <t>Würtharena Neumarkt;BajtMi;EggerTh;ArlicMa;BrondiPa</t>
-  </si>
-  <si>
-    <t>Eishalle Sissek Zibel;LebenJa;WidmannFl;JavornikBl;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;LazzeriAl;LehnerMo;GrisentiLu;MattheyPh</t>
-  </si>
-  <si>
-    <t>Eishalle Dornbirn;SoraperraSi;StefenelliFe;FecchioFe;JägerRi</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;BrockAd;SnojTa;MarkizetiGr;WendnerMa</t>
-  </si>
-  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -789,9 +784,6 @@
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
   </si>
   <si>
-    <t>Eishalle Meran;BulovecMi;SoraperraSi;ArlicMa;CristeliMa</t>
-  </si>
-  <si>
     <t>Eishalle Sissek Zibel;MeixnerSe;VoicanCh;JeramFi;LegatKo</t>
   </si>
   <si>
@@ -801,7 +793,7 @@
     <t>Würtharena Neumarkt;HolzerTo;SpiegelSe;JägerRi;RivisAn</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;BenvegnuAn;PirasAn;AbeltinoSi;PaceJa</t>
+    <t>Eishalle Sterzing;PinieOm;StefenelliFe;BrondiPa;GrisentiLu</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;KainbergerJu;RuetzMa;AbeltinoSi;RinkerDa</t>
@@ -810,7 +802,10 @@
     <t>Eisarena Salzburg;HlavatyAl;VoicanCh;PreiserJu;WeissAl</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;HolzerTo;SpiegelSe;DivisDo;StrimitzerDa</t>
+    <t>Würtharena Neumarkt;BenvegnuAn;GiacomozziFe;AbeltinoSi;PaceJa</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HolzerTo;SpiegelSe;SeewaldJe;StrimitzerDa</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
@@ -909,7 +904,7 @@
     <t>Eishalle Ritten;SoraperraSi;StefenelliFe;FecchioFe;GrisentiLu</t>
   </si>
   <si>
-    <t>Eishalle Dornbirn;MoidlDa;SpiegelSe;MattheyPh;MoidlMa</t>
+    <t>Eishalle Zell am See;HlavatyAl;LebenJa;PreiserJu;TelesklavFa</t>
   </si>
   <si>
     <t>Eishalle Ritten;EggerTh;VirtaTu;FormaioniTh;ScalzeriAl</t>
@@ -918,13 +913,13 @@
     <t>Eishalle Sissek Zibel;HlavatyAl;MetzingerFi;KnezRo;LegatKo</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;PinieOm;StefenelliFe;BrondiPa;GrisentiLu</t>
+    <t>Eishalle Meran;PirasAn;RivisFe;FecchioFe;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;JavornikBl;WuchererGe</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;KainbergerJu;OrelSt;SeewaldJe;WuchererGe</t>
+    <t>KELIT Arena Zell am See;KainbergerJu;OrelSt;DivisDo;WuchererGe</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;Huber rRe;RuetzMa;EislCh;ZacherlPa</t>
@@ -1020,16 +1015,16 @@
     <t>Sportpark Kitzbühel;RuetzMa;SpiegelSe;JägerRi;StrimitzerDa</t>
   </si>
   <si>
-    <t>Eishalle Zell am See;HlavatyAl;LebenJa;PreiserJu;TelesklavFa</t>
+    <t>Sportpark Kitzbühel;LazzeriAl;WidmannFl;SeewaldJe;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Gröden;RivisFe;SoraperraSi;AbeltinoSi;PaceJa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;KainbergerJu;VoicanCh;PreiserJu;WeissAl</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;GiacomozziFe;RivisFe;FecchioFe;RivisAn</t>
+    <t>Eishalle Meran;LebenJa;LesniakBo;FecchioFe;JeramFi</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;HolzerTo;LegaSi;CusinFe;DivisDo</t>
   </si>
   <si>
     <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;RivisAn</t>
@@ -1107,13 +1102,10 @@
     <t>Eishalle Celje;HlavatyAl;KainbergerJu;PreiserJu;ScalzeriAl</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;LazzeriAl;WidmannFl;SeewaldJe;WuchererGe</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;LebenJa;LesniakBo;FecchioFe;JeramFi</t>
-  </si>
-  <si>
-    <t>Eishalle Gröden;HolzerTo;LegaSi;CusinFe;DivisDo</t>
+    <t>Eishalle Cortina;LazzeriAl;OrelSt;PaceJa;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;Huber rRe;VirtaTu;FormaioniTh;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Cortina;BenvegnuAn;PinieOm;CristeliMa;RivisAn</t>
@@ -1143,10 +1135,7 @@
     <t>Eishalle Cortina;LebenJa;MoschenAn;CristeliMa;JeramFi</t>
   </si>
   <si>
-    <t>Eishalle Cortina;LazzeriAl;OrelSt;CristeliMa;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Cortina;Huber rRe;VirtaTu;FormaioniTh;ScalzeriAl</t>
+    <t>Sportpark Kitzbühel;KainbergerJu;VoicanCh;PreiserJu;SeewaldJe</t>
   </si>
   <si>
     <t>vse delegirane tekme</t>
@@ -1203,6 +1192,9 @@
     <t>kontrola</t>
   </si>
   <si>
+    <t>till 30.1.2025</t>
+  </si>
+  <si>
     <t>% games per team</t>
   </si>
   <si>
@@ -1210,61 +1202,58 @@
   </si>
   <si>
     <t>trainnees</t>
-  </si>
-  <si>
-    <t>till 30.1.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF9C0006"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF006100"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="36"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="36"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1276,25 +1265,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1306,7 +1295,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1323,7 +1312,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1334,7 +1323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1603,10 +1592,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1701,27 +1705,12 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2001,9 +1990,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BQ73"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BR73"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -2076,14 +2065,14 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1">
-        <f>COUNTIF(B4:B67,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(B4:B65,"&lt;&gt;")</f>
+        <v>13</v>
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C68,"&lt;&gt;")</f>
@@ -2098,7 +2087,7 @@
         <v>17</v>
       </c>
       <c r="F1">
-        <f>COUNTIF(F4:F69,"&lt;&gt;")</f>
+        <f>COUNTIF(F4:F67,"&lt;&gt;")</f>
         <v>13</v>
       </c>
       <c r="G1">
@@ -2114,7 +2103,7 @@
         <v>14</v>
       </c>
       <c r="J1">
-        <f>COUNTIF(J4:J68,"&lt;&gt;")</f>
+        <f>COUNTIF(J4:J66,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="K1">
@@ -2130,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="N1">
-        <f>COUNTIF(N4:N67,"&lt;&gt;")</f>
+        <f>COUNTIF(N4:N66,"&lt;&gt;")</f>
         <v>15</v>
       </c>
       <c r="O1">
@@ -2138,7 +2127,7 @@
         <v>16</v>
       </c>
       <c r="P1">
-        <f t="shared" ref="P1:BF1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
+        <f t="shared" ref="P1:BA1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
         <v>18</v>
       </c>
       <c r="Q1">
@@ -2187,15 +2176,15 @@
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC1">
-        <f>COUNTIF(AC4:AC69,"&lt;&gt;")</f>
+        <f>COUNTIF(AC4:AC68,"&lt;&gt;")</f>
         <v>17</v>
       </c>
       <c r="AD1">
-        <f>COUNTIF(AD4:AD68,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(AD4:AD67,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
@@ -2210,8 +2199,8 @@
         <v>13</v>
       </c>
       <c r="AH1">
-        <f>COUNTIF(AH4:AH67,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(AH4:AH66,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
@@ -2230,7 +2219,7 @@
         <v>12</v>
       </c>
       <c r="AM1">
-        <f>COUNTIF(AM4:AM66,"&lt;&gt;")</f>
+        <f>COUNTIF(AM4:AM64,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="AN1">
@@ -2239,11 +2228,11 @@
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP1">
-        <f>COUNTIF(AP4:AP67,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(AP4:AP66,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="AQ1">
         <f>COUNTIF(AQ4:AQ68,"&lt;&gt;")</f>
@@ -2254,7 +2243,7 @@
         <v>19</v>
       </c>
       <c r="AS1">
-        <f>COUNTIF(AS4:AS69,"&lt;&gt;")</f>
+        <f>COUNTIF(AS4:AS68,"&lt;&gt;")</f>
         <v>13</v>
       </c>
       <c r="AT1">
@@ -2278,43 +2267,43 @@
         <v>16</v>
       </c>
       <c r="AY1">
-        <f>COUNTIF(AY4:AY63,"&lt;&gt;")</f>
+        <f>COUNTIF(AY4:AY61,"&lt;&gt;")</f>
         <v>14</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ65,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB1">
-        <f>COUNTIF(BB4:BB69,"&lt;&gt;")</f>
+        <f>COUNTIF(BB4:BB68,"&lt;&gt;")</f>
         <v>18</v>
       </c>
       <c r="BC1">
-        <f>COUNTIF(BC4:BC68,"&lt;&gt;")</f>
+        <f>COUNTIF(BC4:BC67,"&lt;&gt;")</f>
         <v>13</v>
       </c>
       <c r="BD1">
-        <f>COUNTIF(BD4:BD69,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(BD4:BD68,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="BE1">
         <f>COUNTIF(BE4:BE67,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="BF1">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>COUNTIF(BF4:BF69,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="BG1">
-        <f>COUNTIF(BG4:BG66,"&lt;&gt;")</f>
-        <v>7</v>
+        <f>COUNTIF(BG4:BG64,"&lt;&gt;")</f>
+        <v>6</v>
       </c>
       <c r="BH1">
-        <f>COUNTIF(BH4:BH69,"&lt;&gt;")</f>
+        <f>COUNTIF(BH4:BH68,"&lt;&gt;")</f>
         <v>7</v>
       </c>
       <c r="BI1">
@@ -2322,12 +2311,12 @@
         <v>1</v>
       </c>
       <c r="BJ1">
-        <f>COUNTIF(BJ4:BJ68,"&lt;&gt;")</f>
-        <v>10</v>
+        <f>COUNTIF(BJ4:BJ67,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BL1">
         <f t="shared" si="1"/>
@@ -2342,8 +2331,8 @@
         <v>11</v>
       </c>
       <c r="BO1">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>COUNTIF(BO4:BO69,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="BP1">
         <f t="shared" si="1"/>
@@ -2354,7 +2343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2563,7 +2552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2772,7 +2761,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -2981,7 +2970,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3181,7 +3170,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3381,7 +3370,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -3578,7 +3567,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3772,7 +3761,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -3963,7 +3952,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -4127,13 +4116,10 @@
         <v>128</v>
       </c>
       <c r="BF10" t="s">
-        <v>122</v>
-      </c>
-      <c r="BG10" t="s">
         <v>129</v>
       </c>
       <c r="BH10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="BJ10" t="s">
         <v>104</v>
@@ -4148,13 +4134,13 @@
         <v>112</v>
       </c>
       <c r="BO10" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="BP10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -4317,11 +4303,8 @@
       <c r="BE11" t="s">
         <v>119</v>
       </c>
-      <c r="BF11" t="s">
-        <v>134</v>
-      </c>
       <c r="BJ11" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="BK11" t="s">
         <v>104</v>
@@ -4332,14 +4315,11 @@
       <c r="BN11" t="s">
         <v>121</v>
       </c>
-      <c r="BO11" t="s">
-        <v>134</v>
-      </c>
       <c r="BP11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -4434,7 +4414,7 @@
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AJ12" t="s">
         <v>92</v>
@@ -4443,7 +4423,7 @@
         <v>95</v>
       </c>
       <c r="AL12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4500,7 +4480,7 @@
         <v>103</v>
       </c>
       <c r="BJ12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BK12" t="s">
         <v>120</v>
@@ -4515,7 +4495,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -4607,7 +4587,7 @@
         <v>111</v>
       </c>
       <c r="AJ13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AK13" t="s">
         <v>109</v>
@@ -4669,20 +4649,17 @@
       <c r="BD13" t="s">
         <v>121</v>
       </c>
-      <c r="BJ13" t="s">
-        <v>137</v>
-      </c>
       <c r="BK13" t="s">
         <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="BN13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -4699,7 +4676,7 @@
         <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="H14" t="s">
         <v>120</v>
@@ -4708,7 +4685,7 @@
         <v>120</v>
       </c>
       <c r="J14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K14" t="s">
         <v>131</v>
@@ -4762,7 +4739,7 @@
         <v>112</v>
       </c>
       <c r="AE14" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AF14" t="s">
         <v>111</v>
@@ -4771,7 +4748,7 @@
         <v>117</v>
       </c>
       <c r="AH14" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -4789,7 +4766,7 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AP14" t="s">
         <v>120</v>
@@ -4801,7 +4778,7 @@
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
@@ -4831,30 +4808,30 @@
         <v>123</v>
       </c>
       <c r="BC14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="BD14" t="s">
         <v>124</v>
       </c>
       <c r="BK14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BM14" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="BN14" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -4863,19 +4840,19 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="I15" t="s">
         <v>124</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="L15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="N15" t="s">
         <v>133</v>
@@ -4914,13 +4891,13 @@
         <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC15" t="s">
         <v>133</v>
       </c>
       <c r="AD15" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AE15" t="s">
         <v>126</v>
@@ -4932,22 +4909,22 @@
         <v>126</v>
       </c>
       <c r="AH15" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="AJ15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AL15" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AO15" t="s">
         <v>128</v>
@@ -4956,19 +4933,19 @@
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AR15" t="s">
         <v>104</v>
       </c>
       <c r="AS15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AT15" t="s">
         <v>107</v>
       </c>
       <c r="AU15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AV15" t="s">
         <v>103</v>
@@ -4980,7 +4957,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -4992,27 +4969,27 @@
         <v>104</v>
       </c>
       <c r="BC15" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK15" t="s">
         <v>134</v>
       </c>
-      <c r="BD15" t="s">
+      <c r="BM15" t="s">
         <v>122</v>
       </c>
-      <c r="BK15" t="s">
-        <v>125</v>
-      </c>
-      <c r="BM15" t="s">
-        <v>129</v>
-      </c>
     </row>
-    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
         <v>120</v>
@@ -5021,13 +4998,13 @@
         <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H16" t="s">
         <v>132</v>
       </c>
       <c r="I16" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K16" t="s">
         <v>132</v>
@@ -5036,7 +5013,7 @@
         <v>132</v>
       </c>
       <c r="N16" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="O16" t="s">
         <v>120</v>
@@ -5060,7 +5037,7 @@
         <v>104</v>
       </c>
       <c r="V16" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="W16" t="s">
         <v>104</v>
@@ -5072,13 +5049,13 @@
         <v>120</v>
       </c>
       <c r="AB16" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="AC16" t="s">
         <v>92</v>
       </c>
       <c r="AD16" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="AE16" t="s">
         <v>119</v>
@@ -5087,10 +5064,10 @@
         <v>132</v>
       </c>
       <c r="AG16" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AH16" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="AK16" t="s">
         <v>120</v>
@@ -5105,7 +5082,7 @@
         <v>126</v>
       </c>
       <c r="AP16" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AQ16" t="s">
         <v>124</v>
@@ -5114,7 +5091,7 @@
         <v>112</v>
       </c>
       <c r="AS16" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AT16" t="s">
         <v>104</v>
@@ -5135,7 +5112,7 @@
         <v>132</v>
       </c>
       <c r="AZ16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BA16" t="s">
         <v>133</v>
@@ -5144,24 +5121,21 @@
         <v>103</v>
       </c>
       <c r="BC16" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BD16" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="BK16" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>132</v>
       </c>
-      <c r="B17" t="s">
-        <v>131</v>
-      </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
@@ -5170,16 +5144,16 @@
         <v>131</v>
       </c>
       <c r="I17" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s">
         <v>120</v>
       </c>
       <c r="N17" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="O17" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="P17" t="s">
         <v>120</v>
@@ -5194,7 +5168,7 @@
         <v>103</v>
       </c>
       <c r="T17" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
@@ -5215,40 +5189,43 @@
         <v>133</v>
       </c>
       <c r="AC17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF17" t="s">
         <v>134</v>
       </c>
-      <c r="AF17" t="s">
-        <v>125</v>
-      </c>
       <c r="AH17" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="AK17" t="s">
         <v>133</v>
       </c>
       <c r="AM17" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AN17" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AO17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AP17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AR17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
       </c>
       <c r="AU17" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AV17" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AW17" t="s">
         <v>94</v>
@@ -5257,7 +5234,7 @@
         <v>120</v>
       </c>
       <c r="AY17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AZ17" t="s">
         <v>120</v>
@@ -5268,25 +5245,31 @@
       <c r="BB17" t="s">
         <v>121</v>
       </c>
+      <c r="BD17" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="18" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" t="s">
+        <v>141</v>
+      </c>
+      <c r="N18" t="s">
+        <v>137</v>
+      </c>
+      <c r="O18" t="s">
         <v>129</v>
-      </c>
-      <c r="D18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" t="s">
-        <v>140</v>
-      </c>
-      <c r="N18" t="s">
-        <v>129</v>
-      </c>
-      <c r="O18" t="s">
-        <v>134</v>
       </c>
       <c r="P18" t="s">
         <v>121</v>
@@ -5316,19 +5299,22 @@
         <v>126</v>
       </c>
       <c r="AA18" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AB18" t="s">
         <v>119</v>
       </c>
       <c r="AC18" t="s">
-        <v>126</v>
+        <v>132</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>134</v>
       </c>
       <c r="AK18" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AM18" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AN18" t="s">
         <v>126</v>
@@ -5336,9 +5322,6 @@
       <c r="AO18" t="s">
         <v>119</v>
       </c>
-      <c r="AP18" t="s">
-        <v>119</v>
-      </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
@@ -5346,39 +5329,42 @@
         <v>121</v>
       </c>
       <c r="AW18" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AX18" t="s">
         <v>128</v>
       </c>
       <c r="AZ18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BA18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BB18" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>141</v>
+      </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
         <v>132</v>
       </c>
       <c r="O19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="Q19" t="s">
         <v>126</v>
       </c>
       <c r="R19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="S19" t="s">
         <v>121</v>
@@ -5393,23 +5379,29 @@
         <v>133</v>
       </c>
       <c r="W19" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Z19" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>137</v>
       </c>
       <c r="AC19" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="AM19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AN19" t="s">
         <v>132</v>
       </c>
+      <c r="AO19" t="s">
+        <v>138</v>
+      </c>
       <c r="AR19" t="s">
         <v>136</v>
       </c>
@@ -5417,22 +5409,25 @@
         <v>120</v>
       </c>
       <c r="AW19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AX19" t="s">
         <v>132</v>
       </c>
       <c r="AZ19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="BA19" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="BB19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
       <c r="E20" t="s">
         <v>119</v>
       </c>
@@ -5443,7 +5438,7 @@
         <v>137</v>
       </c>
       <c r="R20" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="S20" t="s">
         <v>94</v>
@@ -5452,28 +5447,28 @@
         <v>109</v>
       </c>
       <c r="V20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="W20" t="s">
         <v>126</v>
       </c>
       <c r="AC20" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="AK20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AN20" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="AR20" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AT20" t="s">
         <v>128</v>
       </c>
       <c r="AW20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AZ20" t="s">
         <v>119</v>
@@ -5485,27 +5480,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="P21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R21" t="s">
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U21" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="V21" t="s">
         <v>119</v>
       </c>
       <c r="W21" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AN21" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AR21" t="s">
         <v>120</v>
@@ -5513,14 +5508,17 @@
       <c r="AT21" t="s">
         <v>132</v>
       </c>
+      <c r="AZ21" t="s">
+        <v>138</v>
+      </c>
       <c r="BA21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BB21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
       <c r="R22" t="s">
         <v>137</v>
       </c>
@@ -5531,7 +5529,7 @@
         <v>132</v>
       </c>
       <c r="AR22" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="AT22" t="s">
         <v>119</v>
@@ -5540,23 +5538,26 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
       <c r="S23" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="U23" t="s">
         <v>119</v>
       </c>
+      <c r="BA23" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="24" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" spans="19:53" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5600,14 +5601,14 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A3:BS42"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:BT42"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -5652,7 +5653,7 @@
     <col min="85" max="85" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -5804,7 +5805,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
@@ -5822,25 +5823,25 @@
         <v>136</v>
       </c>
       <c r="BE3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF3" t="s">
         <v>141</v>
       </c>
-      <c r="BF3" t="s">
-        <v>140</v>
-      </c>
       <c r="BG3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="BH3" t="s">
         <v>124</v>
       </c>
       <c r="BI3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BJ3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BK3" t="s">
         <v>134</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>125</v>
       </c>
       <c r="BL3" t="s">
         <v>128</v>
@@ -5852,22 +5853,25 @@
         <v>132</v>
       </c>
       <c r="BO3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="BP3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BQ3" t="s">
         <v>137</v>
       </c>
       <c r="BR3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
       </c>
+      <c r="BT3" t="s">
+        <v>125</v>
+      </c>
     </row>
-    <row r="4" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -6040,10 +6044,10 @@
         <v>31</v>
       </c>
       <c r="BF4" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="BG4" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="s">
         <v>71</v>
@@ -6067,7 +6071,7 @@
         <v>14</v>
       </c>
       <c r="BO4" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="BP4" t="s">
         <v>9</v>
@@ -6081,8 +6085,11 @@
       <c r="BS4" t="s">
         <v>58</v>
       </c>
+      <c r="BT4" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="5" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6255,10 +6262,10 @@
         <v>44</v>
       </c>
       <c r="BF5" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="BH5" t="s">
         <v>54</v>
@@ -6282,7 +6289,7 @@
         <v>4</v>
       </c>
       <c r="BO5" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="s">
         <v>54</v>
@@ -6296,8 +6303,11 @@
       <c r="BS5" t="s">
         <v>4</v>
       </c>
+      <c r="BT5" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="6" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -6470,10 +6480,10 @@
         <v>22</v>
       </c>
       <c r="BF6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="s">
         <v>59</v>
@@ -6511,8 +6521,11 @@
       <c r="BS6" t="s">
         <v>8</v>
       </c>
+      <c r="BT6" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="7" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -6688,7 +6701,7 @@
         <v>48</v>
       </c>
       <c r="BG7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BH7" t="s">
         <v>60</v>
@@ -6726,13 +6739,16 @@
       <c r="BS7" t="s">
         <v>48</v>
       </c>
+      <c r="BT7" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="8" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -6756,7 +6772,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -6840,7 +6856,7 @@
         <v>44</v>
       </c>
       <c r="BG8" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="BH8" t="s">
         <v>46</v>
@@ -6852,7 +6868,7 @@
         <v>56</v>
       </c>
       <c r="BM8" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BN8" t="s">
         <v>41</v>
@@ -6860,11 +6876,14 @@
       <c r="BO8" t="s">
         <v>68</v>
       </c>
+      <c r="BQ8" t="s">
+        <v>17</v>
+      </c>
       <c r="BS8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -6878,7 +6897,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -6977,7 +6996,7 @@
         <v>38</v>
       </c>
       <c r="BG9" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="BH9" t="s">
         <v>50</v>
@@ -6989,7 +7008,7 @@
         <v>45</v>
       </c>
       <c r="BM9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="BN9" t="s">
         <v>49</v>
@@ -6997,11 +7016,14 @@
       <c r="BO9" t="s">
         <v>50</v>
       </c>
+      <c r="BQ9" t="s">
+        <v>31</v>
+      </c>
       <c r="BS9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -7114,7 +7136,7 @@
         <v>35</v>
       </c>
       <c r="BG10" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="BH10" t="s">
         <v>12</v>
@@ -7126,7 +7148,7 @@
         <v>66</v>
       </c>
       <c r="BM10" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BN10" t="s">
         <v>32</v>
@@ -7134,11 +7156,14 @@
       <c r="BO10" t="s">
         <v>52</v>
       </c>
+      <c r="BQ10" t="s">
+        <v>32</v>
+      </c>
       <c r="BS10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -7251,7 +7276,7 @@
         <v>53</v>
       </c>
       <c r="BG11" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BH11" t="s">
         <v>51</v>
@@ -7263,7 +7288,7 @@
         <v>25</v>
       </c>
       <c r="BM11" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="BN11" t="s">
         <v>53</v>
@@ -7271,11 +7296,14 @@
       <c r="BO11" t="s">
         <v>62</v>
       </c>
+      <c r="BQ11" t="s">
+        <v>37</v>
+      </c>
       <c r="BS11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -7301,7 +7329,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -7373,7 +7401,7 @@
         <v>18</v>
       </c>
       <c r="BG12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BJ12" t="s">
         <v>39</v>
@@ -7382,7 +7410,7 @@
         <v>68</v>
       </c>
       <c r="BM12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="BN12" t="s">
         <v>11</v>
@@ -7394,7 +7422,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -7492,7 +7520,7 @@
         <v>29</v>
       </c>
       <c r="BG13" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="BJ13" t="s">
         <v>26</v>
@@ -7501,7 +7529,7 @@
         <v>14</v>
       </c>
       <c r="BM13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BN13" t="s">
         <v>54</v>
@@ -7513,7 +7541,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -7611,7 +7639,7 @@
         <v>19</v>
       </c>
       <c r="BG14" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="BJ14" t="s">
         <v>23</v>
@@ -7620,19 +7648,19 @@
         <v>15</v>
       </c>
       <c r="BM14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BN14" t="s">
         <v>13</v>
       </c>
       <c r="BO14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="BS14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -7730,7 +7758,7 @@
         <v>20</v>
       </c>
       <c r="BG15" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="BJ15" t="s">
         <v>30</v>
@@ -7739,7 +7767,7 @@
         <v>51</v>
       </c>
       <c r="BM15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BN15" t="s">
         <v>43</v>
@@ -7751,7 +7779,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -7843,16 +7871,16 @@
         <v>49</v>
       </c>
       <c r="BG16" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="BJ16" t="s">
         <v>34</v>
       </c>
       <c r="BK16" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="BM16" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="BN16" t="s">
         <v>38</v>
@@ -7864,7 +7892,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -7956,16 +7984,16 @@
         <v>45</v>
       </c>
       <c r="BG17" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="BJ17" t="s">
         <v>18</v>
       </c>
       <c r="BK17" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BM17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BN17" t="s">
         <v>24</v>
@@ -7977,7 +8005,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -8069,16 +8097,16 @@
         <v>66</v>
       </c>
       <c r="BG18" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="BJ18" t="s">
         <v>32</v>
       </c>
       <c r="BK18" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="BM18" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="BN18" t="s">
         <v>35</v>
@@ -8090,7 +8118,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -8182,16 +8210,16 @@
         <v>55</v>
       </c>
       <c r="BG19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BJ19" t="s">
         <v>37</v>
       </c>
       <c r="BK19" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="BM19" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="BN19" t="s">
         <v>25</v>
@@ -8203,7 +8231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -8270,14 +8298,11 @@
       <c r="BC20" t="s">
         <v>68</v>
       </c>
-      <c r="BG20" t="s">
+      <c r="BK20" t="s">
         <v>21</v>
       </c>
-      <c r="BK20" t="s">
-        <v>9</v>
-      </c>
       <c r="BM20" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="BO20" t="s">
         <v>17</v>
@@ -8286,7 +8311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -8353,14 +8378,11 @@
       <c r="BC21" t="s">
         <v>41</v>
       </c>
-      <c r="BG21" t="s">
-        <v>54</v>
-      </c>
       <c r="BK21" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="BM21" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BO21" t="s">
         <v>36</v>
@@ -8369,7 +8391,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -8436,14 +8458,11 @@
       <c r="BC22" t="s">
         <v>52</v>
       </c>
-      <c r="BG22" t="s">
-        <v>59</v>
-      </c>
       <c r="BK22" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="BM22" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="BO22" t="s">
         <v>40</v>
@@ -8452,7 +8471,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -8519,14 +8538,11 @@
       <c r="BC23" t="s">
         <v>30</v>
       </c>
-      <c r="BG23" t="s">
-        <v>43</v>
-      </c>
       <c r="BK23" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BM23" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="BO23" t="s">
         <v>25</v>
@@ -8535,7 +8551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:71" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -8558,13 +8574,10 @@
         <v>9</v>
       </c>
       <c r="BK24" t="s">
-        <v>21</v>
-      </c>
-      <c r="BM24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:63" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -8587,13 +8600,10 @@
         <v>24</v>
       </c>
       <c r="BK25" t="s">
-        <v>47</v>
-      </c>
-      <c r="BM25" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:63" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -8616,13 +8626,10 @@
         <v>40</v>
       </c>
       <c r="BK26" t="s">
-        <v>40</v>
-      </c>
-      <c r="BM26" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:63" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -8645,17 +8652,14 @@
         <v>12</v>
       </c>
       <c r="BK27" t="s">
-        <v>42</v>
-      </c>
-      <c r="BM27" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8671,10 +8675,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A3:BS14"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:BT14"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -8741,6 +8745,7 @@
     <col min="65" max="65" width="73.85546875" customWidth="1"/>
     <col min="66" max="66" width="67.140625" customWidth="1"/>
     <col min="67" max="67" width="57.85546875" customWidth="1"/>
+    <col min="68" max="68" width="34.85546875" customWidth="1"/>
     <col min="69" max="69" width="19.28515625" customWidth="1"/>
     <col min="70" max="70" width="55.7109375" customWidth="1"/>
     <col min="78" max="78" width="9.28515625" customWidth="1"/>
@@ -8756,7 +8761,7 @@
     <col min="103" max="103" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -8908,7 +8913,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
@@ -8926,25 +8931,25 @@
         <v>136</v>
       </c>
       <c r="BE3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BF3" t="s">
         <v>141</v>
       </c>
-      <c r="BF3" t="s">
-        <v>140</v>
-      </c>
       <c r="BG3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="BH3" t="s">
         <v>124</v>
       </c>
       <c r="BI3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BJ3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BK3" t="s">
         <v>134</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>125</v>
       </c>
       <c r="BL3" t="s">
         <v>128</v>
@@ -8956,732 +8961,735 @@
         <v>132</v>
       </c>
       <c r="BO3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="BP3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BQ3" t="s">
         <v>137</v>
       </c>
       <c r="BR3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
       </c>
+      <c r="BT3" t="s">
+        <v>125</v>
+      </c>
     </row>
-    <row r="4" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="S4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="T4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="U4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="V4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="W4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="X4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Y4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AA4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AB4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AC4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AD4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AE4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>180</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>185</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>187</v>
+      </c>
+      <c r="AP4" t="s">
         <v>175</v>
       </c>
-      <c r="AF4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>182</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>183</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>185</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>173</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AR4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AS4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AT4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AU4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AV4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AW4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AX4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AY4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AZ4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="BA4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="BB4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="BC4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="BD4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BE4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BF4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BG4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BH4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="BI4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="BJ4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="BK4" t="s">
+        <v>208</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>209</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>212</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>213</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>214</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>216</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H5" t="s">
+        <v>222</v>
+      </c>
+      <c r="K5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L5" t="s">
+        <v>224</v>
+      </c>
+      <c r="N5" t="s">
+        <v>225</v>
+      </c>
+      <c r="P5" t="s">
+        <v>226</v>
+      </c>
+      <c r="R5" t="s">
+        <v>227</v>
+      </c>
+      <c r="T5" t="s">
+        <v>228</v>
+      </c>
+      <c r="U5" t="s">
+        <v>229</v>
+      </c>
+      <c r="V5" t="s">
+        <v>230</v>
+      </c>
+      <c r="W5" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>233</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>234</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>237</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>238</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>239</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>242</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>243</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>245</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>246</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>247</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>249</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>250</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>252</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>253</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>254</v>
+      </c>
+      <c r="BG5" t="s">
         <v>206</v>
       </c>
-      <c r="BL4" t="s">
-        <v>207</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>208</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>209</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>212</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>213</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>214</v>
+      <c r="BH5" t="s">
+        <v>255</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>256</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>257</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>258</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>259</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>260</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>261</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G5" t="s">
-        <v>218</v>
-      </c>
-      <c r="H5" t="s">
-        <v>219</v>
-      </c>
-      <c r="K5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L5" t="s">
-        <v>221</v>
-      </c>
-      <c r="N5" t="s">
-        <v>222</v>
-      </c>
-      <c r="P5" t="s">
-        <v>223</v>
-      </c>
-      <c r="R5" t="s">
-        <v>224</v>
-      </c>
-      <c r="T5" t="s">
-        <v>225</v>
-      </c>
-      <c r="U5" t="s">
-        <v>226</v>
-      </c>
-      <c r="V5" t="s">
-        <v>227</v>
-      </c>
-      <c r="W5" t="s">
-        <v>228</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>232</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>233</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>234</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>235</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>236</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>237</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>238</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>239</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>240</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>242</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>243</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>244</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>245</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>246</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>247</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>248</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>249</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>250</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>251</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>252</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>253</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>254</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>255</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>256</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>257</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>258</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>259</v>
+    <row r="6" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H6" t="s">
+        <v>267</v>
+      </c>
+      <c r="K6" t="s">
+        <v>268</v>
+      </c>
+      <c r="L6" t="s">
+        <v>269</v>
+      </c>
+      <c r="N6" t="s">
+        <v>270</v>
+      </c>
+      <c r="P6" t="s">
+        <v>271</v>
+      </c>
+      <c r="T6" t="s">
+        <v>272</v>
+      </c>
+      <c r="V6" t="s">
+        <v>273</v>
+      </c>
+      <c r="W6" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>278</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>280</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>281</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>282</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>283</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>285</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>286</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>290</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>291</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>292</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>293</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>294</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>295</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>296</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>297</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>298</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>299</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>300</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>301</v>
       </c>
     </row>
-    <row r="6" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>260</v>
-      </c>
-      <c r="D6" t="s">
-        <v>261</v>
-      </c>
-      <c r="F6" t="s">
-        <v>262</v>
-      </c>
-      <c r="G6" t="s">
-        <v>263</v>
-      </c>
-      <c r="H6" t="s">
-        <v>264</v>
-      </c>
-      <c r="K6" t="s">
-        <v>265</v>
-      </c>
-      <c r="L6" t="s">
-        <v>266</v>
-      </c>
-      <c r="N6" t="s">
-        <v>267</v>
-      </c>
-      <c r="P6" t="s">
-        <v>268</v>
-      </c>
-      <c r="T6" t="s">
-        <v>269</v>
-      </c>
-      <c r="V6" t="s">
-        <v>270</v>
-      </c>
-      <c r="W6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>272</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>273</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>274</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>275</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>276</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>277</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>278</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>279</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>280</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>281</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>282</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>283</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>284</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>285</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>286</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>287</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>288</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>289</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>290</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>291</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>292</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>293</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>294</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>295</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>296</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>297</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>298</v>
+    <row r="7" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" t="s">
+        <v>304</v>
+      </c>
+      <c r="G7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H7" t="s">
+        <v>306</v>
+      </c>
+      <c r="K7" t="s">
+        <v>307</v>
+      </c>
+      <c r="L7" t="s">
+        <v>308</v>
+      </c>
+      <c r="N7" t="s">
+        <v>309</v>
+      </c>
+      <c r="P7" t="s">
+        <v>310</v>
+      </c>
+      <c r="T7" t="s">
+        <v>311</v>
+      </c>
+      <c r="V7" t="s">
+        <v>312</v>
+      </c>
+      <c r="W7" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>314</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>315</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>316</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>317</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>318</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>319</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>321</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>322</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>323</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>324</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>325</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>326</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>327</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>328</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>329</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>330</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>331</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>332</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>333</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>334</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>335</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>336</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>337</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>338</v>
       </c>
     </row>
-    <row r="7" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D7" t="s">
-        <v>300</v>
-      </c>
-      <c r="F7" t="s">
-        <v>301</v>
-      </c>
-      <c r="G7" t="s">
-        <v>302</v>
-      </c>
-      <c r="H7" t="s">
-        <v>303</v>
-      </c>
-      <c r="K7" t="s">
-        <v>304</v>
-      </c>
-      <c r="L7" t="s">
-        <v>305</v>
-      </c>
-      <c r="N7" t="s">
-        <v>306</v>
-      </c>
-      <c r="P7" t="s">
-        <v>307</v>
-      </c>
-      <c r="T7" t="s">
-        <v>308</v>
-      </c>
-      <c r="V7" t="s">
-        <v>309</v>
-      </c>
-      <c r="W7" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>312</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>313</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>314</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>315</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>316</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>318</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>319</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>320</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>321</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>322</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>323</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>324</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>325</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>326</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>327</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>328</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>329</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>330</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>331</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>332</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>333</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>334</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>335</v>
+    <row r="8" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G8" t="s">
+        <v>342</v>
+      </c>
+      <c r="H8" t="s">
+        <v>343</v>
+      </c>
+      <c r="K8" t="s">
+        <v>344</v>
+      </c>
+      <c r="L8" t="s">
+        <v>345</v>
+      </c>
+      <c r="V8" t="s">
+        <v>346</v>
+      </c>
+      <c r="W8" t="s">
+        <v>347</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>348</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>349</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>350</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>351</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>352</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>353</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>354</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>355</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>356</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>357</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>358</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>359</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>360</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>361</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>362</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>363</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>364</v>
       </c>
     </row>
-    <row r="8" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>336</v>
-      </c>
-      <c r="D8" t="s">
-        <v>337</v>
-      </c>
-      <c r="F8" t="s">
-        <v>338</v>
-      </c>
-      <c r="G8" t="s">
-        <v>339</v>
-      </c>
-      <c r="H8" t="s">
-        <v>340</v>
-      </c>
-      <c r="K8" t="s">
-        <v>341</v>
-      </c>
-      <c r="L8" t="s">
-        <v>342</v>
-      </c>
-      <c r="V8" t="s">
-        <v>343</v>
-      </c>
-      <c r="W8" t="s">
-        <v>344</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>345</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>346</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>347</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>348</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>349</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>350</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>351</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>352</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>353</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>354</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>355</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>356</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>357</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>358</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>359</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>360</v>
-      </c>
-      <c r="BO8" t="s">
-        <v>361</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>362</v>
+    <row r="9" ht="15" customHeight="1" spans="7:71" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>365</v>
+      </c>
+      <c r="L9" t="s">
+        <v>366</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>368</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>369</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>370</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>371</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>372</v>
       </c>
     </row>
-    <row r="9" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>363</v>
-      </c>
-      <c r="L9" t="s">
-        <v>364</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>365</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>366</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>367</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>368</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>369</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>370</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="10" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:71" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -9699,46 +9707,46 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="6">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
-        <v>373</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="7">
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11">
         <f>C1*4</f>
         <v>912</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="B3" s="9">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="B3" s="13">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>912</v>
-      </c>
-      <c r="E3" s="65" t="s">
-        <v>374</v>
-      </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
+        <v>915</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="B4" s="11">
+    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4" s="16">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
         <v>132</v>
       </c>
@@ -9747,53 +9755,53 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="16">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>28</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="E5" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" s="18">
         <v>2</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="19">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="20">
         <f>B4/B3</f>
-        <v>0.14473684210526316</v>
-      </c>
-      <c r="I5" s="16">
+        <v>0.14426229508196722</v>
+      </c>
+      <c r="I5" s="21">
         <f>C2*G5</f>
         <v>140.30769230769232</v>
       </c>
@@ -9801,42 +9809,42 @@
         <f>B4</f>
         <v>132</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="22">
         <f>J5-I5</f>
-        <v>-8.3076923076923208</v>
-      </c>
-      <c r="L5" s="18">
+        <v>-8.30769230769232</v>
+      </c>
+      <c r="L5" s="23">
         <f>K5/4</f>
-        <v>-2.0769230769230802</v>
+        <v>-2.07692307692308</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="16">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C6">
         <f>AHL!X1</f>
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="18">
         <v>1</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="19">
         <f>F6/13</f>
-        <v>7.6923076923076927E-2</v>
-      </c>
-      <c r="H6" s="15">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H6" s="20">
         <f>B5/B3</f>
-        <v>3.0701754385964911E-2</v>
-      </c>
-      <c r="I6" s="16">
+        <v>0.030601092896174863</v>
+      </c>
+      <c r="I6" s="21">
         <f>C2*G6</f>
         <v>70.15384615384616</v>
       </c>
@@ -9844,20 +9852,20 @@
         <f>B5</f>
         <v>28</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="22">
         <f>J6-I6</f>
         <v>-42.15384615384616</v>
       </c>
-      <c r="L6" s="18">
+      <c r="L6" s="23">
         <f t="shared" ref="L6" si="0">K6/4</f>
         <v>-10.53846153846154</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="25">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
         <v>393</v>
       </c>
@@ -9865,21 +9873,21 @@
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
         <v>93</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E7" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="F7" s="27">
         <v>3</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="28">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="29">
         <f>(B5+B4)/B3</f>
-        <v>0.17543859649122806</v>
-      </c>
-      <c r="I7" s="16">
+        <v>0.17486338797814208</v>
+      </c>
+      <c r="I7" s="21">
         <f>C2*G7</f>
         <v>210.46153846153848</v>
       </c>
@@ -9887,77 +9895,77 @@
         <f>B4+B5</f>
         <v>160</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="22">
         <f>J7-I7</f>
-        <v>-50.461538461538481</v>
-      </c>
-      <c r="L7" s="18">
+        <v>-50.46153846153848</v>
+      </c>
+      <c r="L7" s="23">
         <f>K7/4</f>
         <v>-12.61538461538462</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>385</v>
+    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
+        <v>386</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
         <v>112</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="F8" s="27">
+      <c r="E8" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="32">
         <v>6</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="33">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="34">
         <f>B6/B3</f>
-        <v>0.39364035087719296</v>
-      </c>
-      <c r="I8" s="16">
+        <v>0.39562841530054643</v>
+      </c>
+      <c r="I8" s="21">
         <f>C2*G8</f>
         <v>420.92307692307696</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>359</v>
-      </c>
-      <c r="K8" s="17">
+        <v>362</v>
+      </c>
+      <c r="K8" s="22">
         <f>J8-I8</f>
-        <v>-61.923076923076962</v>
-      </c>
-      <c r="L8" s="18">
+        <v>-58.92307692307696</v>
+      </c>
+      <c r="L8" s="23">
         <f>K8/4</f>
-        <v>-15.480769230769241</v>
+        <v>-14.73076923076924</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>912</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="F9" s="27">
+        <v>915</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="F9" s="32">
         <v>4</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="33">
         <f t="shared" si="1"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H9" s="29">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H9" s="34">
         <f>B7/B3</f>
-        <v>0.43092105263157893</v>
-      </c>
-      <c r="I9" s="16">
+        <v>0.42950819672131146</v>
+      </c>
+      <c r="I9" s="21">
         <f>C2*G9</f>
         <v>280.61538461538464</v>
       </c>
@@ -9965,302 +9973,302 @@
         <f>B7</f>
         <v>393</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="35">
         <f>J9-I9</f>
         <v>112.38461538461536</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="23">
         <f>K9/4</f>
         <v>28.09615384615384</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="31" t="s">
-        <v>389</v>
-      </c>
-      <c r="I11" s="32">
+    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="I11" s="37">
         <f>SUM(I7:I9)</f>
-        <v>912.00000000000011</v>
-      </c>
-      <c r="J11" s="26">
+        <v>912.0000000000001</v>
+      </c>
+      <c r="J11" s="31">
         <f>SUM(J7:J9)</f>
-        <v>912</v>
-      </c>
-      <c r="K11" s="33">
+        <v>915</v>
+      </c>
+      <c r="K11" s="38">
         <f>SUM(K7:K9)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="34">
+        <v>2.9999999999999147</v>
+      </c>
+      <c r="L11" s="39">
         <f>SUM(L7:L9)</f>
-        <v>0</v>
+        <v>0.7499999999999787</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G16" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H16" t="s">
-        <v>379</v>
-      </c>
-      <c r="I16" s="35" t="s">
         <v>380</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="I16" s="40" t="s">
         <v>381</v>
       </c>
+      <c r="J16" s="40" t="s">
+        <v>382</v>
+      </c>
       <c r="K16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
-    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E17" s="36" t="s">
-        <v>384</v>
-      </c>
-      <c r="F17" s="37">
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="F17" s="42">
         <v>3</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="43">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="44">
         <f>(B5+B4)/B3</f>
-        <v>0.17543859649122806</v>
-      </c>
-      <c r="I17" s="40">
+        <v>0.17486338797814208</v>
+      </c>
+      <c r="I17" s="45">
         <f>B3*G17</f>
-        <v>210.46153846153848</v>
-      </c>
-      <c r="J17" s="41">
+        <v>211.15384615384616</v>
+      </c>
+      <c r="J17" s="46">
         <f>B5+B4</f>
         <v>160</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="47">
         <f>J17-I17</f>
-        <v>-50.461538461538481</v>
-      </c>
-      <c r="L17" s="18">
+        <v>-51.15384615384616</v>
+      </c>
+      <c r="L17" s="23">
         <f>K17/4</f>
-        <v>-12.61538461538462</v>
+        <v>-12.78846153846154</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="F18" s="44">
+      <c r="E18" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="F18" s="49">
         <v>6</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="50">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="46">
+      <c r="H18" s="51">
         <f>B6/B3</f>
-        <v>0.39364035087719296</v>
-      </c>
-      <c r="I18" s="47">
+        <v>0.39562841530054643</v>
+      </c>
+      <c r="I18" s="52">
         <f>B3*G18</f>
-        <v>420.92307692307696</v>
-      </c>
-      <c r="J18" s="48">
+        <v>422.3076923076923</v>
+      </c>
+      <c r="J18" s="53">
         <f>B6</f>
-        <v>359</v>
-      </c>
-      <c r="K18" s="49">
+        <v>362</v>
+      </c>
+      <c r="K18" s="54">
         <f>J18-I18</f>
-        <v>-61.923076923076962</v>
-      </c>
-      <c r="L18" s="18">
+        <v>-60.30769230769232</v>
+      </c>
+      <c r="L18" s="23">
         <f>K18/4</f>
-        <v>-15.480769230769241</v>
-      </c>
-      <c r="Q18" s="50"/>
+        <v>-15.07692307692308</v>
+      </c>
+      <c r="Q18" s="55"/>
     </row>
-    <row r="19" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="51" t="s">
-        <v>388</v>
-      </c>
-      <c r="F19" s="52">
+    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="56" t="s">
+        <v>389</v>
+      </c>
+      <c r="F19" s="57">
         <v>4</v>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="58">
         <f t="shared" si="2"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H19" s="54">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H19" s="59">
         <f>B7/B3</f>
-        <v>0.43092105263157893</v>
-      </c>
-      <c r="I19" s="55">
+        <v>0.42950819672131146</v>
+      </c>
+      <c r="I19" s="60">
         <f>B3*G19</f>
-        <v>280.61538461538464</v>
-      </c>
-      <c r="J19" s="56">
+        <v>281.53846153846155</v>
+      </c>
+      <c r="J19" s="61">
         <f>B7</f>
         <v>393</v>
       </c>
-      <c r="K19" s="57">
+      <c r="K19" s="62">
         <f>J19-I19</f>
-        <v>112.38461538461536</v>
-      </c>
-      <c r="L19" s="18">
+        <v>111.46153846153845</v>
+      </c>
+      <c r="L19" s="23">
         <f>K19/4</f>
-        <v>28.09615384615384</v>
+        <v>27.865384615384613</v>
       </c>
     </row>
-    <row r="21" spans="5:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E21" s="66" t="s">
-        <v>391</v>
-      </c>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
+    <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E21" s="63" t="s">
+        <v>393</v>
+      </c>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
     </row>
-    <row r="22" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G22" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H22" t="s">
-        <v>379</v>
-      </c>
-      <c r="I22" s="35" t="s">
         <v>380</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="I22" s="40" t="s">
         <v>381</v>
       </c>
+      <c r="J22" s="40" t="s">
+        <v>382</v>
+      </c>
       <c r="K22" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="23" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E23" s="36" t="s">
-        <v>384</v>
-      </c>
-      <c r="F23" s="37">
+    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E23" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="F23" s="42">
         <v>3</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="43">
         <f t="shared" ref="G23:G25" si="3">F23/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="44">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.1825</v>
-      </c>
-      <c r="I23" s="40">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="I23" s="45">
         <f>(B3-C8) *G23</f>
-        <v>184.61538461538461</v>
-      </c>
-      <c r="J23" s="41">
+        <v>185.30769230769232</v>
+      </c>
+      <c r="J23" s="46">
         <f>B4+B5-C4</f>
         <v>146</v>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="47">
         <f>J23-I23</f>
-        <v>-38.615384615384613</v>
+        <v>-39.30769230769232</v>
       </c>
     </row>
-    <row r="24" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="43" t="s">
-        <v>386</v>
-      </c>
-      <c r="F24" s="44">
+    <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E24" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="F24" s="49">
         <v>6</v>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="50">
         <f t="shared" si="3"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H24" s="46">
+      <c r="H24" s="51">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="I24" s="47">
+        <v>0.43337484433374845</v>
+      </c>
+      <c r="I24" s="52">
         <f>(B3-C8)*G24</f>
-        <v>369.23076923076923</v>
-      </c>
-      <c r="J24" s="48">
+        <v>370.61538461538464</v>
+      </c>
+      <c r="J24" s="53">
         <f>B6-C6</f>
-        <v>354</v>
-      </c>
-      <c r="K24" s="49">
+        <v>357</v>
+      </c>
+      <c r="K24" s="54">
         <f>J24-I24</f>
-        <v>-15.230769230769226</v>
+        <v>-13.615384615384642</v>
       </c>
     </row>
-    <row r="25" spans="5:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E25" s="51" t="s">
-        <v>388</v>
-      </c>
-      <c r="F25" s="52">
+    <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E25" s="56" t="s">
+        <v>389</v>
+      </c>
+      <c r="F25" s="57">
         <v>4</v>
       </c>
-      <c r="G25" s="53">
+      <c r="G25" s="58">
         <f t="shared" si="3"/>
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="H25" s="54">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H25" s="59">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.375</v>
-      </c>
-      <c r="I25" s="55">
+        <v>0.37359900373599003</v>
+      </c>
+      <c r="I25" s="60">
         <f>(B3-C8)*G25</f>
-        <v>246.15384615384616</v>
-      </c>
-      <c r="J25" s="56">
+        <v>247.0769230769231</v>
+      </c>
+      <c r="J25" s="61">
         <f>B7-C7</f>
         <v>300</v>
       </c>
-      <c r="K25" s="57">
+      <c r="K25" s="62">
         <f>J25-I25</f>
-        <v>53.84615384615384</v>
+        <v>52.923076923076906</v>
       </c>
     </row>
-    <row r="26" spans="5:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="58">
+      <c r="H26" s="64">
         <f>C8/B9</f>
-        <v>0.12280701754385964</v>
+        <v>0.12240437158469945</v>
       </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="59">
+      <c r="J26" s="65">
         <f>C8</f>
         <v>112</v>
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="28" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>912</v>
-      </c>
-      <c r="K28" s="60">
+        <v>915</v>
+      </c>
+      <c r="K28" s="66">
         <f>SUM(K23:K25)</f>
-        <v>0</v>
+        <v>-5.684341886080802e-14</v>
       </c>
     </row>
   </sheetData>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2733" uniqueCount="441">
   <si>
     <t>sl</t>
   </si>
@@ -385,78 +385,102 @@
     <t>2025-01-02</t>
   </si>
   <si>
+    <t>2025-02-04</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>2025-01-21</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>2025-01-16</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2025-01-14</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>2025-02-02</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>2025-01-05</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>2025-01-04</t>
+  </si>
+  <si>
+    <t>2025-02-20</t>
+  </si>
+  <si>
+    <t>2025-01-11</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>2025-01-03</t>
+  </si>
+  <si>
+    <t>zbrisano</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
+    <t>2025-02-18</t>
+  </si>
+  <si>
+    <t>2025-01-18</t>
+  </si>
+  <si>
+    <t>2025-02-11</t>
+  </si>
+  <si>
+    <t>2025-01-22</t>
+  </si>
+  <si>
+    <t>2025-01-12</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
     <t>2025-01-25</t>
   </si>
   <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2025-01-21</t>
-  </si>
-  <si>
-    <t>2025-02-02</t>
-  </si>
-  <si>
-    <t>2025-01-16</t>
-  </si>
-  <si>
-    <t>2024-12-01</t>
-  </si>
-  <si>
-    <t>2025-01-14</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>2024-11-24</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2025-01-11</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
-    <t>2025-01-28</t>
-  </si>
-  <si>
-    <t>2025-01-18</t>
+    <t>2024-12-27</t>
   </si>
   <si>
     <t>2025-01-26</t>
   </si>
   <si>
-    <t>2025-01-22</t>
-  </si>
-  <si>
-    <t>2025-01-12</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2024-12-27</t>
-  </si>
-  <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2025-01-29</t>
   </si>
   <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
     <t>HuberRe</t>
   </si>
   <si>
@@ -631,7 +655,7 @@
     <t>Eishalle Ritten;MeixnerSe;SnojTa;JeramFi;WendnerMa</t>
   </si>
   <si>
-    <t>Eishalle Meran;BulovecMi;SoraperraSi;ArlicMa;CristeliMa</t>
+    <t>Eishalle Meran;BulovecMi;GiacomozziFe;ArlicMa;CristeliMa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;LehnerMo;WidmannFl;SeewaldJe;ZacherlPa</t>
@@ -658,10 +682,10 @@
     <t>Würtharena Neumarkt;EggerTh;SnojTa;ArlicMa;BrondiPa</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;LebenJa;WidmannFl;JavornikBl;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Jesenice;LazzeriAl;LehnerMo;GrisentiLu;MattheyPh</t>
+    <t>Würtharena Neumarkt;LebenJa;WidmannFl;FecchioFe;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LehnerMo;MeixnerSe;MattheyPh;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;SoraperraSi;StefenelliFe;FecchioFe;JägerRi</t>
@@ -670,7 +694,31 @@
     <t>Eishalle Celje;BrockAd;SnojTa;MarkizetiGr;WendnerMa</t>
   </si>
   <si>
-    <t>Eishalle Jesenice;BrockAd;WenuschHe;WeissAl;WendnerMa</t>
+    <t>Eishalle Gröden;EggerTh;LazzeriAl;GrisentiLu;IlmerNo</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HlavatyAl;VoicanCh;PreiserJu;WeissAl</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;BajtMi;LegaSi;CusinFe;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;Huber rRe;RuetzMa;DivisDo;JägerRi</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BajtMi;MetzingerFi;KnezRo;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;BrockAd;KainbergerJu;EislCh;WendnerMa</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;MoschenAn;PinieOm;AbeltinoSi;FecchioFe</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BrockAd;MeixnerSe;KnezRo;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BajtMi;BulovecMi;ArlicMa;JeramFi</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
@@ -784,6 +832,9 @@
     <t>Würtharena Neumarkt;Huber rRe;LegaSi;CusinFe;RinkerDa</t>
   </si>
   <si>
+    <t>Eishalle Dornbirn;HolzerTo;Huber rRe;EislCh;StrimitzerDa</t>
+  </si>
+  <si>
     <t>Eishalle Sissek Zibel;MeixnerSe;VoicanCh;JeramFi;LegatKo</t>
   </si>
   <si>
@@ -799,13 +850,40 @@
     <t>Sportpark Kitzbühel;KainbergerJu;RuetzMa;AbeltinoSi;RinkerDa</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;HlavatyAl;VoicanCh;PreiserJu;WeissAl</t>
+    <t>KELIT Arena Zell am See;KainbergerJu;OrelSt;DivisDo;WuchererGe</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;BulovecMi;VirtaTu;JeramFi;PaceJa</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;BenvegnuAn;GiacomozziFe;AbeltinoSi;PaceJa</t>
   </si>
   <si>
-    <t>Eisarena Salzburg;HolzerTo;SpiegelSe;SeewaldJe;StrimitzerDa</t>
+    <t>Eisarena Salzburg;HolzerTo;SpiegelSe;RinkerDa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;BrockAd;WenuschHe;LegatKo;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;GiacomozziFe;PinieOm;GrisentiLu;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;Huber rRe;LesniakBo;ArlicMa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;MeixnerSe;WidmannFl;TelesklavFa;WendnerMa</t>
+  </si>
+  <si>
+    <t>ZBRISANO</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;HlavatyAl;LebenJa;PreiserJu;WeissAl</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;HolzerTo;VoicanCh;DivisDo;LegatKo</t>
+  </si>
+  <si>
+    <t>Eisarena Salzburg;HlavatyAl;WenuschHe;PreiserJu;WeissAl</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
@@ -919,12 +997,33 @@
     <t>Eishalle Sissek Zibel;LesniakBo;WidmannFl;JavornikBl;WuchererGe</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;KainbergerJu;OrelSt;DivisDo;WuchererGe</t>
+    <t>Eisarena Toblach;BenvegnuAn;PinieOm;CristeliMa;RivisAn</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;Huber rRe;RuetzMa;EislCh;ZacherlPa</t>
   </si>
   <si>
+    <t>Eishalle Cortina;LazzeriAl;PirasAn;BrondiPa;CristeliMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;BulovecMi;OrelSt;JeramFi;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;HolzerTo;SpiegelSe;DivisDo;JägerRi</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;EggerTh;LazzeriAl;CristeliMa;GrisentiLu</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BulovecMi;SnojTa;ArlicMa;JeramFi</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;Huber rRe;RuetzMa;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;MoidlDa;SpiegelSe;JägerRi;RinkerDa</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -946,9 +1045,6 @@
     <t>Eishalle Gröden;LebenJa;LesniakBo;ArlicMa;MarkizetiGr</t>
   </si>
   <si>
-    <t>Eishalle Celje;BulovecMi;SnojTa;ArlicMa;JeramFi</t>
-  </si>
-  <si>
     <t>Eishalle Sterzing;LazzeriAl;PinieOm;IlmerNo;ScalzeriAl</t>
   </si>
   <si>
@@ -1024,18 +1120,33 @@
     <t>Eishalle Meran;LebenJa;LesniakBo;FecchioFe;JeramFi</t>
   </si>
   <si>
-    <t>Eishalle Gröden;HolzerTo;LegaSi;CusinFe;DivisDo</t>
+    <t>Eishalle Gröden;LegaSi;SpiegelSe;CusinFe;DivisDo</t>
   </si>
   <si>
     <t>Eishalle Sterzing;LegaSi;MoschenAn;CusinFe;RivisAn</t>
   </si>
   <si>
-    <t>Eishalle Gröden;BulovecMi;VirtaTu;JeramFi;PaceJa</t>
-  </si>
-  <si>
     <t>Eishalle Sterzing;MoschenAn;PirasAn;AbeltinoSi;FormaioniTh</t>
   </si>
   <si>
+    <t>Sportpark Kitzbühel;LehnerMo;MetzingerFi;MoidlMa;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;BenvegnuAn;SoraperraSi;FecchioFe;IlmerNo</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;PirasAn;VirtaTu;PaceJa;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;BenvegnuAn;StefenelliFe;FleischmannLu;IlmerNo</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;EggerTh;LazzeriAl;AbeltinoSi;CristeliMa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;KainbergerJu;LehnerMo;EislCh;MoidlMa</t>
+  </si>
+  <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
   </si>
   <si>
@@ -1108,10 +1219,22 @@
     <t>Eishalle Cortina;Huber rRe;VirtaTu;FormaioniTh;ScalzeriAl</t>
   </si>
   <si>
-    <t>Eishalle Cortina;BenvegnuAn;PinieOm;CristeliMa;RivisAn</t>
-  </si>
-  <si>
-    <t>Eishalle Meran;GiacomozziFe;RivisFe;FleischmannLu;RivisAn</t>
+    <t>Eishalle Meran;RivisFe;StefenelliFe;FleischmannLu;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;LegaSi;StefenelliFe;CusinFe;FormaioniTh</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;GiacomozziFe;PinieOm;BrondiPa;RivisAn</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;LegaSi;SoraperraSi;FormaioniTh;PaceJa</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;PirasAn;SnojTa;BrondiPa;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;VirtaTu;WidmannFl;BrondiPa;TelesklavFa</t>
   </si>
   <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
@@ -1136,6 +1259,21 @@
   </si>
   <si>
     <t>Sportpark Kitzbühel;KainbergerJu;VoicanCh;PreiserJu;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;Huber rRe;MoschenAn;RinkerDa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;MeixnerSe;RuetzMa;MoidlMa;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;LesniakBo;OrelSt;JavornikBl;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;GiacomozziFe;SoraperraSi;IlmerNo;RivisAn</t>
+  </si>
+  <si>
+    <t>Würtharena Neumarkt;BenvegnuAn;StefenelliFe;PaceJa;ScalzeriAl</t>
   </si>
   <si>
     <t>vse delegirane tekme</t>
@@ -2068,27 +2206,27 @@
     <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
+        <v>19</v>
+      </c>
+      <c r="B1">
+        <f>COUNTIF(B4:B64,"&lt;&gt;")</f>
+        <v>16</v>
+      </c>
+      <c r="C1">
+        <f>COUNTIF(C4:C67,"&lt;&gt;")</f>
         <v>17</v>
-      </c>
-      <c r="B1">
-        <f>COUNTIF(B4:B65,"&lt;&gt;")</f>
-        <v>13</v>
-      </c>
-      <c r="C1">
-        <f>COUNTIF(C4:C68,"&lt;&gt;")</f>
-        <v>14</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1">
-        <f>COUNTIF(E4:E67,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(E4:E66,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1">
         <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
@@ -2096,95 +2234,95 @@
       </c>
       <c r="H1">
         <f>COUNTIF(H4:H68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I1">
-        <f>COUNTIF(I4:I69,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(I4:I68,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="J1">
-        <f>COUNTIF(J4:J66,"&lt;&gt;")</f>
+        <f>COUNTIF(J4:J64,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M1">
         <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="N1">
-        <f>COUNTIF(N4:N66,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(N4:N65,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="O1">
-        <f>COUNTIF(O4:O67,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(O4:O66,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="P1">
-        <f t="shared" ref="P1:BA1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
-        <v>18</v>
+        <f t="shared" ref="P1:Z1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="Q1">
-        <f>COUNTIF(Q4:Q67,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(Q4:Q66,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="R1">
-        <f>COUNTIF(R4:R64,"&lt;&gt;")</f>
-        <v>19</v>
+        <f>COUNTIF(R4:R63,"&lt;&gt;")</f>
+        <v>22</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U1">
         <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
+        <v>22</v>
+      </c>
+      <c r="V1">
+        <f>COUNTIF(V4:V66,"&lt;&gt;")</f>
         <v>20</v>
       </c>
-      <c r="V1">
-        <f>COUNTIF(V4:V67,"&lt;&gt;")</f>
-        <v>18</v>
-      </c>
       <c r="W1">
-        <f>COUNTIF(W4:W69,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(W4:W68,"&lt;&gt;")</f>
+        <v>20</v>
       </c>
       <c r="X1">
         <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y1">
         <f>COUNTIF(Y4:Y68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA1">
         <f>COUNTIF(AA4:AA65,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AB1">
-        <f>COUNTIF(AB4:AB67,"&lt;&gt;")</f>
-        <v>16</v>
+        <f>COUNTIF(AB4:AB65,"&lt;&gt;")</f>
+        <v>18</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC68,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AD1">
-        <f>COUNTIF(AD4:AD67,"&lt;&gt;")</f>
-        <v>14</v>
+        <f>COUNTIF(AD4:AD66,"&lt;&gt;")</f>
+        <v>16</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
@@ -2192,119 +2330,119 @@
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF63,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG1">
-        <f>COUNTIF(AG4:AG66,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(AG4:AG65,"&lt;&gt;")</f>
+        <v>16</v>
       </c>
       <c r="AH1">
-        <f>COUNTIF(AH4:AH66,"&lt;&gt;")</f>
-        <v>15</v>
+        <f>COUNTIF(AH4:AH65,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ1">
-        <f>COUNTIF(AJ4:AJ62,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(AJ4:AJ61,"&lt;&gt;")</f>
+        <v>15</v>
       </c>
       <c r="AK1">
-        <f>COUNTIF(AK4:AK65,"&lt;&gt;")</f>
-        <v>17</v>
+        <f>COUNTIF(AK4:AK63,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL65,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM64,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AN1">
-        <f>COUNTIF(AN4:AN64,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(AN4:AN63,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AP1">
         <f>COUNTIF(AP4:AP66,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ1">
-        <f>COUNTIF(AQ4:AQ68,"&lt;&gt;")</f>
-        <v>13</v>
+        <f>COUNTIF(AQ4:AQ67,"&lt;&gt;")</f>
+        <v>16</v>
       </c>
       <c r="AR1">
-        <f>COUNTIF(AR4:AR61,"&lt;&gt;")</f>
-        <v>19</v>
+        <f>COUNTIF(AR4:AR60,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT1">
         <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
+        <v>22</v>
+      </c>
+      <c r="AU1">
+        <f>COUNTIF(AU4:AU67,"&lt;&gt;")</f>
+        <v>15</v>
+      </c>
+      <c r="AV1">
+        <f>COUNTIF(AV4:AV64,"&lt;&gt;")</f>
+        <v>16</v>
+      </c>
+      <c r="AW1">
+        <f>COUNTIF(AW4:AW64,"&lt;&gt;")</f>
         <v>19</v>
       </c>
-      <c r="AU1">
-        <f>COUNTIF(AU4:AU69,"&lt;&gt;")</f>
-        <v>14</v>
-      </c>
-      <c r="AV1">
-        <f>COUNTIF(AV4:AV65,"&lt;&gt;")</f>
-        <v>14</v>
-      </c>
-      <c r="AW1">
-        <f>COUNTIF(AW4:AW65,"&lt;&gt;")</f>
-        <v>17</v>
-      </c>
       <c r="AX1">
-        <f>COUNTIF(AX4:AX67,"&lt;&gt;")</f>
+        <f>COUNTIF(AX4:AX65,"&lt;&gt;")</f>
+        <v>19</v>
+      </c>
+      <c r="AY1">
+        <f>COUNTIF(AY4:AY60,"&lt;&gt;")</f>
         <v>16</v>
       </c>
-      <c r="AY1">
-        <f>COUNTIF(AY4:AY61,"&lt;&gt;")</f>
-        <v>14</v>
-      </c>
       <c r="AZ1">
-        <f>COUNTIF(AZ4:AZ65,"&lt;&gt;")</f>
-        <v>18</v>
+        <f>COUNTIF(AZ4:AZ64,"&lt;&gt;")</f>
+        <v>19</v>
       </c>
       <c r="BA1">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>COUNTIF(BA4:BA69,"&lt;&gt;")</f>
+        <v>21</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB68,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD1">
         <f>COUNTIF(BD4:BD68,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BE1">
         <f>COUNTIF(BE4:BE67,"&lt;&gt;")</f>
+        <v>10</v>
+      </c>
+      <c r="BF1">
+        <f>COUNTIF(BF4:BF68,"&lt;&gt;")</f>
+        <v>10</v>
+      </c>
+      <c r="BG1">
+        <f>COUNTIF(BG4:BG61,"&lt;&gt;")</f>
         <v>8</v>
-      </c>
-      <c r="BF1">
-        <f>COUNTIF(BF4:BF69,"&lt;&gt;")</f>
-        <v>7</v>
-      </c>
-      <c r="BG1">
-        <f>COUNTIF(BG4:BG64,"&lt;&gt;")</f>
-        <v>6</v>
       </c>
       <c r="BH1">
         <f>COUNTIF(BH4:BH68,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BI1">
         <f t="shared" ref="BI1:BQ1" si="1">COUNTIF(BI4:BI70,"&lt;&gt;")</f>
@@ -2316,27 +2454,27 @@
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BL1">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BM1">
-        <f t="shared" ref="BM1" si="2">COUNTIF(BM4:BM69,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(BM4:BM67,"&lt;&gt;")</f>
+        <v>14</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BO1">
         <f>COUNTIF(BO4:BO69,"&lt;&gt;")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BP1">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f>COUNTIF(BP4:BP69,"&lt;&gt;")</f>
+        <v>12</v>
       </c>
       <c r="BQ1">
         <f t="shared" si="1"/>
@@ -3825,6 +3963,9 @@
       <c r="W9" t="s">
         <v>77</v>
       </c>
+      <c r="X9" t="s">
+        <v>124</v>
+      </c>
       <c r="Y9" t="s">
         <v>90</v>
       </c>
@@ -3922,13 +4063,13 @@
         <v>102</v>
       </c>
       <c r="BE9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BF9" t="s">
         <v>94</v>
       </c>
       <c r="BG9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BH9" t="s">
         <v>112</v>
@@ -4047,13 +4188,13 @@
         <v>115</v>
       </c>
       <c r="AI10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AJ10" t="s">
         <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -4113,13 +4254,16 @@
         <v>116</v>
       </c>
       <c r="BE10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BF10" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>124</v>
       </c>
       <c r="BH10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="BJ10" t="s">
         <v>104</v>
@@ -4134,10 +4278,10 @@
         <v>112</v>
       </c>
       <c r="BO10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BP10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4160,19 +4304,19 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I11" t="s">
         <v>92</v>
       </c>
       <c r="J11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4199,7 +4343,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4223,7 +4367,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4235,10 +4379,10 @@
         <v>100</v>
       </c>
       <c r="AI11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AJ11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4303,8 +4447,17 @@
       <c r="BE11" t="s">
         <v>119</v>
       </c>
+      <c r="BF11" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>136</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>136</v>
+      </c>
       <c r="BJ11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BK11" t="s">
         <v>104</v>
@@ -4315,8 +4468,11 @@
       <c r="BN11" t="s">
         <v>121</v>
       </c>
+      <c r="BO11" t="s">
+        <v>136</v>
+      </c>
       <c r="BP11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4330,7 +4486,7 @@
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
@@ -4345,10 +4501,10 @@
         <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L12" t="s">
         <v>112</v>
@@ -4414,7 +4570,7 @@
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AJ12" t="s">
         <v>92</v>
@@ -4423,7 +4579,7 @@
         <v>95</v>
       </c>
       <c r="AL12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4432,7 +4588,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4450,7 +4606,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AV12" t="s">
         <v>109</v>
@@ -4459,7 +4615,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4479,8 +4635,14 @@
       <c r="BD12" t="s">
         <v>103</v>
       </c>
+      <c r="BE12" t="s">
+        <v>140</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>141</v>
+      </c>
       <c r="BJ12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="BK12" t="s">
         <v>120</v>
@@ -4492,7 +4654,7 @@
         <v>114</v>
       </c>
       <c r="BP12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4521,7 +4683,7 @@
         <v>121</v>
       </c>
       <c r="J13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K13" t="s">
         <v>112</v>
@@ -4559,6 +4721,9 @@
       <c r="W13" t="s">
         <v>115</v>
       </c>
+      <c r="Y13" t="s">
+        <v>131</v>
+      </c>
       <c r="Z13" t="s">
         <v>106</v>
       </c>
@@ -4586,14 +4751,17 @@
       <c r="AH13" t="s">
         <v>111</v>
       </c>
+      <c r="AI13" t="s">
+        <v>126</v>
+      </c>
       <c r="AJ13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AK13" t="s">
         <v>109</v>
       </c>
       <c r="AL13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4614,7 +4782,7 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
@@ -4632,7 +4800,7 @@
         <v>118</v>
       </c>
       <c r="AY13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AZ13" t="s">
         <v>115</v>
@@ -4649,17 +4817,26 @@
       <c r="BD13" t="s">
         <v>121</v>
       </c>
+      <c r="BE13" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>136</v>
+      </c>
       <c r="BK13" t="s">
         <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BN13" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -4667,7 +4844,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
         <v>117</v>
@@ -4676,7 +4853,7 @@
         <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H14" t="s">
         <v>120</v>
@@ -4685,13 +4862,13 @@
         <v>120</v>
       </c>
       <c r="J14" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="K14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N14" t="s">
         <v>111</v>
@@ -4723,8 +4900,11 @@
       <c r="W14" t="s">
         <v>106</v>
       </c>
+      <c r="Y14" t="s">
+        <v>145</v>
+      </c>
       <c r="Z14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
@@ -4739,7 +4919,7 @@
         <v>112</v>
       </c>
       <c r="AE14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="s">
         <v>111</v>
@@ -4748,7 +4928,10 @@
         <v>117</v>
       </c>
       <c r="AH14" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>145</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -4766,28 +4949,28 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AP14" t="s">
         <v>120</v>
       </c>
       <c r="AQ14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
       </c>
       <c r="AU14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AV14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AW14" t="s">
         <v>91</v>
@@ -4796,7 +4979,7 @@
         <v>92</v>
       </c>
       <c r="AY14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AZ14" t="s">
         <v>104</v>
@@ -4808,30 +4991,33 @@
         <v>123</v>
       </c>
       <c r="BC14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BD14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BK14" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="BM14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BN14" t="s">
         <v>119</v>
       </c>
+      <c r="BP14" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -4840,22 +5026,22 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O15" t="s">
         <v>111</v>
@@ -4879,11 +5065,14 @@
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W15" t="s">
         <v>114</v>
       </c>
+      <c r="Y15" t="s">
+        <v>124</v>
+      </c>
       <c r="Z15" t="s">
         <v>109</v>
       </c>
@@ -4891,49 +5080,52 @@
         <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AC15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AD15" t="s">
         <v>119</v>
       </c>
       <c r="AE15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AF15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AH15" t="s">
         <v>92</v>
       </c>
+      <c r="AI15" t="s">
+        <v>124</v>
+      </c>
       <c r="AJ15" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AL15" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AO15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AP15" t="s">
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AR15" t="s">
         <v>104</v>
@@ -4945,7 +5137,7 @@
         <v>107</v>
       </c>
       <c r="AU15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AV15" t="s">
         <v>103</v>
@@ -4957,7 +5149,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -4972,24 +5164,30 @@
         <v>119</v>
       </c>
       <c r="BD15" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BK15" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BM15" t="s">
         <v>122</v>
       </c>
+      <c r="BN15" t="s">
+        <v>144</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
         <v>120</v>
@@ -4998,22 +5196,22 @@
         <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I16" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" t="s">
         <v>134</v>
       </c>
-      <c r="K16" t="s">
-        <v>132</v>
-      </c>
       <c r="L16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O16" t="s">
         <v>120</v>
@@ -5031,17 +5229,20 @@
         <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="U16" t="s">
         <v>104</v>
       </c>
       <c r="V16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="W16" t="s">
         <v>104</v>
       </c>
+      <c r="Y16" t="s">
+        <v>143</v>
+      </c>
       <c r="Z16" t="s">
         <v>111</v>
       </c>
@@ -5049,111 +5250,135 @@
         <v>120</v>
       </c>
       <c r="AB16" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="AC16" t="s">
         <v>92</v>
       </c>
       <c r="AD16" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="AE16" t="s">
         <v>119</v>
       </c>
       <c r="AF16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AG16" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="AH16" t="s">
-        <v>122</v>
+        <v>142</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>131</v>
       </c>
       <c r="AK16" t="s">
         <v>120</v>
       </c>
+      <c r="AL16" t="s">
+        <v>141</v>
+      </c>
       <c r="AM16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AO16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AQ16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AR16" t="s">
         <v>112</v>
       </c>
       <c r="AS16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AT16" t="s">
         <v>104</v>
       </c>
       <c r="AU16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AV16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AW16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AX16" t="s">
         <v>121</v>
       </c>
       <c r="AY16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AZ16" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="BA16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
       <c r="BC16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="BD16" t="s">
+        <v>137</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>152</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>124</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>134</v>
       </c>
-      <c r="BK16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>132</v>
+      <c r="B17" t="s">
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="F17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" t="s">
+        <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>122</v>
+        <v>147</v>
+      </c>
+      <c r="K17" t="s">
+        <v>126</v>
       </c>
       <c r="L17" t="s">
         <v>120</v>
       </c>
       <c r="N17" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="O17" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="P17" t="s">
         <v>120</v>
@@ -5162,19 +5387,19 @@
         <v>111</v>
       </c>
       <c r="R17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
       </c>
       <c r="T17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
       </c>
       <c r="V17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W17" t="s">
         <v>109</v>
@@ -5183,40 +5408,55 @@
         <v>120</v>
       </c>
       <c r="AA17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB17" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="AC17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AD17" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AF17" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>122</v>
       </c>
       <c r="AH17" t="s">
         <v>137</v>
       </c>
+      <c r="AJ17" t="s">
+        <v>141</v>
+      </c>
       <c r="AK17" t="s">
-        <v>133</v>
+        <v>135</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>136</v>
       </c>
       <c r="AM17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AN17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AO17" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AP17" t="s">
         <v>119</v>
       </c>
+      <c r="AQ17" t="s">
+        <v>142</v>
+      </c>
       <c r="AR17" t="s">
-        <v>143</v>
+        <v>150</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>145</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
@@ -5225,7 +5465,7 @@
         <v>122</v>
       </c>
       <c r="AV17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AW17" t="s">
         <v>94</v>
@@ -5234,42 +5474,66 @@
         <v>120</v>
       </c>
       <c r="AY17" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="AZ17" t="s">
         <v>120</v>
       </c>
       <c r="BA17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BB17" t="s">
         <v>121</v>
       </c>
+      <c r="BC17" t="s">
+        <v>141</v>
+      </c>
       <c r="BD17" t="s">
         <v>119</v>
       </c>
       <c r="BK17" t="s">
-        <v>138</v>
+        <v>153</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>136</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
+      <c r="B18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>144</v>
+        <v>134</v>
+      </c>
+      <c r="H18" t="s">
+        <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>141</v>
+        <v>151</v>
+      </c>
+      <c r="K18" t="s">
+        <v>145</v>
+      </c>
+      <c r="L18" t="s">
+        <v>145</v>
       </c>
       <c r="N18" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="O18" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="P18" t="s">
         <v>121</v>
@@ -5284,87 +5548,141 @@
         <v>112</v>
       </c>
       <c r="T18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
       <c r="V18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="W18" t="s">
         <v>111</v>
       </c>
       <c r="Z18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>144</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>141</v>
+      </c>
+      <c r="AF18" t="s">
         <v>126</v>
       </c>
-      <c r="AA18" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>132</v>
+      <c r="AG18" t="s">
+        <v>141</v>
       </c>
       <c r="AH18" t="s">
-        <v>134</v>
+        <v>151</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>143</v>
       </c>
       <c r="AK18" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AM18" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AN18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO18" t="s">
         <v>119</v>
       </c>
+      <c r="AP18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>145</v>
+      </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
+      <c r="AS18" t="s">
+        <v>143</v>
+      </c>
       <c r="AT18" t="s">
         <v>121</v>
       </c>
+      <c r="AU18" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>131</v>
+      </c>
       <c r="AW18" t="s">
+        <v>144</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>129</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>145</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>146</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>146</v>
+      </c>
+      <c r="BB18" t="s">
         <v>138</v>
       </c>
-      <c r="AX18" t="s">
-        <v>128</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>140</v>
-      </c>
-      <c r="BA18" t="s">
-        <v>140</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>135</v>
+      <c r="BC18" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>141</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>145</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>147</v>
+      </c>
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" t="s">
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>119</v>
+      </c>
+      <c r="I19" t="s">
+        <v>126</v>
+      </c>
+      <c r="L19" t="s">
+        <v>143</v>
+      </c>
+      <c r="N19" t="s">
+        <v>145</v>
       </c>
       <c r="O19" t="s">
         <v>145</v>
       </c>
       <c r="P19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="S19" t="s">
         <v>121</v>
@@ -5376,184 +5694,446 @@
         <v>120</v>
       </c>
       <c r="V19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="W19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z19" t="s">
-        <v>145</v>
+        <v>152</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>122</v>
       </c>
       <c r="AB19" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="AC19" t="s">
         <v>119</v>
       </c>
+      <c r="AD19" t="s">
+        <v>143</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>126</v>
+      </c>
       <c r="AK19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO19" t="s">
         <v>144</v>
       </c>
-      <c r="AM19" t="s">
+      <c r="AP19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR19" t="s">
         <v>139</v>
       </c>
-      <c r="AN19" t="s">
-        <v>132</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>138</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>136</v>
+      <c r="AS19" t="s">
+        <v>141</v>
       </c>
       <c r="AT19" t="s">
         <v>120</v>
       </c>
+      <c r="AV19" t="s">
+        <v>143</v>
+      </c>
       <c r="AW19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AX19" t="s">
         <v>134</v>
       </c>
-      <c r="AX19" t="s">
-        <v>132</v>
+      <c r="AY19" t="s">
+        <v>136</v>
       </c>
       <c r="AZ19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BA19" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BB19" t="s">
-        <v>142</v>
+        <v>148</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>143</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N20" t="s">
+        <v>124</v>
+      </c>
+      <c r="O20" t="s">
+        <v>124</v>
+      </c>
+      <c r="P20" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q20" t="s">
         <v>122</v>
       </c>
-      <c r="E20" t="s">
-        <v>119</v>
-      </c>
-      <c r="P20" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>137</v>
-      </c>
       <c r="R20" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="S20" t="s">
         <v>94</v>
       </c>
+      <c r="T20" t="s">
+        <v>145</v>
+      </c>
       <c r="U20" t="s">
         <v>109</v>
       </c>
       <c r="V20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="W20" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>141</v>
       </c>
       <c r="AC20" t="s">
-        <v>137</v>
+        <v>142</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>141</v>
       </c>
       <c r="AK20" t="s">
         <v>122</v>
       </c>
+      <c r="AM20" t="s">
+        <v>126</v>
+      </c>
       <c r="AN20" t="s">
-        <v>138</v>
+        <v>144</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>126</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>136</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>141</v>
       </c>
       <c r="AR20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AT20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AW20" t="s">
         <v>122</v>
       </c>
+      <c r="AX20" t="s">
+        <v>119</v>
+      </c>
       <c r="AZ20" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="BA20" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="BB20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s">
+        <v>143</v>
+      </c>
+      <c r="I21" t="s">
+        <v>136</v>
+      </c>
+      <c r="N21" t="s">
+        <v>136</v>
+      </c>
+      <c r="O21" t="s">
+        <v>143</v>
+      </c>
       <c r="P21" t="s">
-        <v>145</v>
+        <v>152</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>131</v>
       </c>
       <c r="R21" t="s">
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>142</v>
+        <v>148</v>
+      </c>
+      <c r="T21" t="s">
+        <v>124</v>
       </c>
       <c r="U21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="V21" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="W21" t="s">
-        <v>122</v>
+        <v>151</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>145</v>
       </c>
       <c r="AN21" t="s">
-        <v>122</v>
+        <v>149</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>153</v>
       </c>
       <c r="AR21" t="s">
         <v>120</v>
       </c>
       <c r="AT21" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>145</v>
       </c>
       <c r="AZ21" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="BA21" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>143</v>
       </c>
-      <c r="BB21" t="s">
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>141</v>
+      </c>
+      <c r="R22" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
-      <c r="R22" t="s">
-        <v>137</v>
-      </c>
       <c r="S22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U22" t="s">
-        <v>132</v>
+        <v>134</v>
+      </c>
+      <c r="V22" t="s">
+        <v>141</v>
+      </c>
+      <c r="W22" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>142</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>145</v>
       </c>
       <c r="AR22" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="AT22" t="s">
         <v>119</v>
       </c>
+      <c r="AW22" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>136</v>
+      </c>
+      <c r="AZ22" t="s">
+        <v>145</v>
+      </c>
       <c r="BA22" t="s">
-        <v>119</v>
+        <v>144</v>
+      </c>
+      <c r="BB22" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="P23" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" t="s">
+        <v>131</v>
+      </c>
       <c r="S23" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="U23" t="s">
         <v>119</v>
       </c>
+      <c r="V23" t="s">
+        <v>143</v>
+      </c>
+      <c r="W23" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>126</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>153</v>
+      </c>
       <c r="BA23" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="BB23" t="s">
+        <v>145</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="19:53" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+      <c r="P24" t="s">
+        <v>124</v>
+      </c>
+      <c r="R24" t="s">
+        <v>141</v>
+      </c>
+      <c r="S24" t="s">
+        <v>122</v>
+      </c>
+      <c r="U24" t="s">
+        <v>145</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>143</v>
+      </c>
+      <c r="BB24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+      <c r="R25" t="s">
+        <v>143</v>
+      </c>
+      <c r="S25" t="s">
+        <v>141</v>
+      </c>
+      <c r="U25" t="s">
+        <v>124</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="18:46" x14ac:dyDescent="0.25">
+      <c r="S26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="19:19" x14ac:dyDescent="0.25">
+      <c r="S27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="19:19" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5607,7 +6187,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BT42"/>
+  <dimension ref="A3:CB42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -5649,11 +6229,13 @@
     <col min="65" max="65" width="14.85546875" customWidth="1"/>
     <col min="66" max="66" width="15" customWidth="1"/>
     <col min="70" max="70" width="17.140625" customWidth="1"/>
-    <col min="83" max="83" width="13.7109375" customWidth="1"/>
-    <col min="85" max="85" width="17.28515625" customWidth="1"/>
+    <col min="72" max="72" width="24.140625" customWidth="1"/>
+    <col min="73" max="73" width="18.42578125" customWidth="1"/>
+    <col min="81" max="81" width="13.7109375" customWidth="1"/>
+    <col min="83" max="83" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -5751,7 +6333,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -5778,10 +6360,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -5805,73 +6387,97 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
       </c>
       <c r="BA3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB3" t="s">
         <v>133</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>131</v>
       </c>
       <c r="BC3" t="s">
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BE3" t="s">
+        <v>148</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>147</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>151</v>
+      </c>
+      <c r="BQ3" t="s">
         <v>142</v>
       </c>
-      <c r="BF3" t="s">
-        <v>141</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>137</v>
-      </c>
       <c r="BR3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
       </c>
       <c r="BT3" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>145</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -6077,7 +6683,7 @@
         <v>9</v>
       </c>
       <c r="BQ4" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="BR4" t="s">
         <v>18</v>
@@ -6086,10 +6692,34 @@
         <v>58</v>
       </c>
       <c r="BT4" t="s">
+        <v>39</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY4" t="s">
         <v>58</v>
       </c>
+      <c r="BZ4" t="s">
+        <v>24</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>58</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6265,7 +6895,7 @@
         <v>4</v>
       </c>
       <c r="BG5" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="BH5" t="s">
         <v>54</v>
@@ -6295,7 +6925,7 @@
         <v>54</v>
       </c>
       <c r="BQ5" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="BR5" t="s">
         <v>29</v>
@@ -6304,10 +6934,34 @@
         <v>4</v>
       </c>
       <c r="BT5" t="s">
-        <v>63</v>
+        <v>21</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>50</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>38</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>49</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>41</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>36</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -6510,10 +7164,10 @@
         <v>7</v>
       </c>
       <c r="BP6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BQ6" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="BR6" t="s">
         <v>19</v>
@@ -6522,10 +7176,34 @@
         <v>8</v>
       </c>
       <c r="BT6" t="s">
-        <v>62</v>
+        <v>20</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>52</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>35</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>57</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>15</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>15</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -6731,7 +7409,7 @@
         <v>42</v>
       </c>
       <c r="BQ7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="BR7" t="s">
         <v>66</v>
@@ -6740,15 +7418,39 @@
         <v>48</v>
       </c>
       <c r="BT7" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>37</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>66</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY7" t="s">
         <v>48</v>
       </c>
+      <c r="BZ7" t="s">
+        <v>19</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>48</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -6772,7 +7474,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -6874,7 +7576,10 @@
         <v>41</v>
       </c>
       <c r="BO8" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>6</v>
       </c>
       <c r="BQ8" t="s">
         <v>17</v>
@@ -6882,8 +7587,32 @@
       <c r="BS8" t="s">
         <v>56</v>
       </c>
+      <c r="BT8" t="s">
+        <v>58</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>31</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>46</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>39</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>68</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>56</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -6897,7 +7626,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -7014,7 +7743,10 @@
         <v>49</v>
       </c>
       <c r="BO9" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>26</v>
       </c>
       <c r="BQ9" t="s">
         <v>31</v>
@@ -7022,8 +7754,32 @@
       <c r="BS9" t="s">
         <v>45</v>
       </c>
+      <c r="BT9" t="s">
+        <v>63</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>11</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>54</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>50</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -7136,7 +7892,7 @@
         <v>35</v>
       </c>
       <c r="BG10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BH10" t="s">
         <v>12</v>
@@ -7154,16 +7910,43 @@
         <v>32</v>
       </c>
       <c r="BO10" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>12</v>
       </c>
       <c r="BQ10" t="s">
         <v>32</v>
       </c>
       <c r="BS10" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>51</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>20</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>7</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>42</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>40</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>52</v>
+      </c>
+      <c r="CA10" t="s">
+        <v>57</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -7294,16 +8077,43 @@
         <v>53</v>
       </c>
       <c r="BO11" t="s">
-        <v>62</v>
+        <v>43</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>37</v>
       </c>
       <c r="BQ11" t="s">
         <v>37</v>
       </c>
       <c r="BS11" t="s">
+        <v>59</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>48</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>30</v>
+      </c>
+      <c r="BV11" t="s">
         <v>55</v>
       </c>
+      <c r="BX11" t="s">
+        <v>48</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>62</v>
+      </c>
+      <c r="CA11" t="s">
+        <v>51</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -7329,7 +8139,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -7415,14 +8225,35 @@
       <c r="BN12" t="s">
         <v>11</v>
       </c>
-      <c r="BO12" t="s">
-        <v>41</v>
+      <c r="BP12" t="s">
+        <v>17</v>
       </c>
       <c r="BS12" t="s">
         <v>44</v>
       </c>
+      <c r="BU12" t="s">
+        <v>21</v>
+      </c>
+      <c r="BV12" t="s">
+        <v>6</v>
+      </c>
+      <c r="BX12" t="s">
+        <v>56</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>33</v>
+      </c>
+      <c r="BZ12" t="s">
+        <v>6</v>
+      </c>
+      <c r="CA12" t="s">
+        <v>44</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -7534,14 +8365,35 @@
       <c r="BN13" t="s">
         <v>54</v>
       </c>
-      <c r="BO13" t="s">
-        <v>47</v>
+      <c r="BP13" t="s">
+        <v>36</v>
       </c>
       <c r="BS13" t="s">
         <v>49</v>
       </c>
+      <c r="BU13" t="s">
+        <v>33</v>
+      </c>
+      <c r="BV13" t="s">
+        <v>47</v>
+      </c>
+      <c r="BX13" t="s">
+        <v>45</v>
+      </c>
+      <c r="BY13" t="s">
+        <v>26</v>
+      </c>
+      <c r="BZ13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CA13" t="s">
+        <v>49</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -7653,14 +8505,35 @@
       <c r="BN14" t="s">
         <v>13</v>
       </c>
-      <c r="BO14" t="s">
-        <v>57</v>
+      <c r="BP14" t="s">
+        <v>40</v>
       </c>
       <c r="BS14" t="s">
         <v>69</v>
       </c>
+      <c r="BU14" t="s">
+        <v>22</v>
+      </c>
+      <c r="BV14" t="s">
+        <v>12</v>
+      </c>
+      <c r="BX14" t="s">
+        <v>57</v>
+      </c>
+      <c r="BY14" t="s">
+        <v>37</v>
+      </c>
+      <c r="BZ14" t="s">
+        <v>7</v>
+      </c>
+      <c r="CA14" t="s">
+        <v>59</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -7772,14 +8645,35 @@
       <c r="BN15" t="s">
         <v>43</v>
       </c>
-      <c r="BO15" t="s">
-        <v>43</v>
+      <c r="BP15" t="s">
+        <v>25</v>
       </c>
       <c r="BS15" t="s">
         <v>60</v>
       </c>
+      <c r="BU15" t="s">
+        <v>40</v>
+      </c>
+      <c r="BV15" t="s">
+        <v>42</v>
+      </c>
+      <c r="BX15" t="s">
+        <v>66</v>
+      </c>
+      <c r="BY15" t="s">
+        <v>30</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>12</v>
+      </c>
+      <c r="CA15" t="s">
+        <v>60</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -7880,19 +8774,34 @@
         <v>9</v>
       </c>
       <c r="BM16" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="BN16" t="s">
         <v>38</v>
       </c>
-      <c r="BO16" t="s">
-        <v>6</v>
-      </c>
       <c r="BS16" t="s">
         <v>24</v>
       </c>
+      <c r="BV16" t="s">
+        <v>71</v>
+      </c>
+      <c r="BX16" t="s">
+        <v>17</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>31</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>17</v>
+      </c>
+      <c r="CA16" t="s">
+        <v>39</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -7993,19 +8902,34 @@
         <v>11</v>
       </c>
       <c r="BM17" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="BN17" t="s">
         <v>24</v>
       </c>
-      <c r="BO17" t="s">
-        <v>26</v>
-      </c>
       <c r="BS17" t="s">
         <v>33</v>
       </c>
+      <c r="BV17" t="s">
+        <v>14</v>
+      </c>
+      <c r="BX17" t="s">
+        <v>18</v>
+      </c>
+      <c r="BY17" t="s">
+        <v>36</v>
+      </c>
+      <c r="BZ17" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA17" t="s">
+        <v>21</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -8111,14 +9035,29 @@
       <c r="BN18" t="s">
         <v>35</v>
       </c>
-      <c r="BO18" t="s">
-        <v>12</v>
-      </c>
       <c r="BS18" t="s">
         <v>32</v>
       </c>
+      <c r="BV18" t="s">
+        <v>61</v>
+      </c>
+      <c r="BX18" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY18" t="s">
+        <v>22</v>
+      </c>
+      <c r="BZ18" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA18" t="s">
+        <v>32</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -8224,14 +9163,29 @@
       <c r="BN19" t="s">
         <v>25</v>
       </c>
-      <c r="BO19" t="s">
-        <v>37</v>
-      </c>
       <c r="BS19" t="s">
         <v>23</v>
       </c>
+      <c r="BV19" t="s">
+        <v>62</v>
+      </c>
+      <c r="BX19" t="s">
+        <v>28</v>
+      </c>
+      <c r="BY19" t="s">
+        <v>25</v>
+      </c>
+      <c r="BZ19" t="s">
+        <v>28</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>40</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -8304,14 +9258,26 @@
       <c r="BM20" t="s">
         <v>44</v>
       </c>
-      <c r="BO20" t="s">
-        <v>17</v>
-      </c>
       <c r="BS20" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="BX20" t="s">
+        <v>38</v>
+      </c>
+      <c r="BY20" t="s">
+        <v>46</v>
+      </c>
+      <c r="BZ20" t="s">
+        <v>38</v>
+      </c>
+      <c r="CA20" t="s">
+        <v>33</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -8384,14 +9350,26 @@
       <c r="BM21" t="s">
         <v>26</v>
       </c>
-      <c r="BO21" t="s">
-        <v>36</v>
-      </c>
       <c r="BS21" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="BX21" t="s">
+        <v>29</v>
+      </c>
+      <c r="BY21" t="s">
+        <v>49</v>
+      </c>
+      <c r="BZ21" t="s">
+        <v>18</v>
+      </c>
+      <c r="CA21" t="s">
+        <v>4</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -8464,14 +9442,26 @@
       <c r="BM22" t="s">
         <v>23</v>
       </c>
-      <c r="BO22" t="s">
-        <v>40</v>
-      </c>
       <c r="BS22" t="s">
         <v>27</v>
       </c>
+      <c r="BX22" t="s">
+        <v>35</v>
+      </c>
+      <c r="BY22" t="s">
+        <v>61</v>
+      </c>
+      <c r="BZ22" t="s">
+        <v>23</v>
+      </c>
+      <c r="CA22" t="s">
+        <v>22</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -8544,14 +9534,26 @@
       <c r="BM23" t="s">
         <v>30</v>
       </c>
-      <c r="BO23" t="s">
-        <v>25</v>
-      </c>
       <c r="BS23" t="s">
         <v>25</v>
       </c>
+      <c r="BX23" t="s">
+        <v>23</v>
+      </c>
+      <c r="BY23" t="s">
+        <v>59</v>
+      </c>
+      <c r="BZ23" t="s">
+        <v>37</v>
+      </c>
+      <c r="CA23" t="s">
+        <v>8</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:71" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -8576,8 +9578,20 @@
       <c r="BK24" t="s">
         <v>41</v>
       </c>
+      <c r="BX24" t="s">
+        <v>44</v>
+      </c>
+      <c r="BZ24" t="s">
+        <v>11</v>
+      </c>
+      <c r="CA24" t="s">
+        <v>31</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:63" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -8602,8 +9616,20 @@
       <c r="BK25" t="s">
         <v>50</v>
       </c>
+      <c r="BX25" t="s">
+        <v>24</v>
+      </c>
+      <c r="BZ25" t="s">
+        <v>47</v>
+      </c>
+      <c r="CA25" t="s">
+        <v>18</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:63" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -8628,8 +9654,20 @@
       <c r="BK26" t="s">
         <v>52</v>
       </c>
+      <c r="BX26" t="s">
+        <v>53</v>
+      </c>
+      <c r="BZ26" t="s">
+        <v>13</v>
+      </c>
+      <c r="CA26" t="s">
+        <v>28</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:63" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -8654,8 +9692,20 @@
       <c r="BK27" t="s">
         <v>59</v>
       </c>
+      <c r="BX27" t="s">
+        <v>55</v>
+      </c>
+      <c r="BZ27" t="s">
+        <v>42</v>
+      </c>
+      <c r="CA27" t="s">
+        <v>25</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="78:80" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8677,7 +9727,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:BT14"/>
+  <dimension ref="A3:CB14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -8745,23 +9795,27 @@
     <col min="65" max="65" width="73.85546875" customWidth="1"/>
     <col min="66" max="66" width="67.140625" customWidth="1"/>
     <col min="67" max="67" width="57.85546875" customWidth="1"/>
-    <col min="68" max="68" width="34.85546875" customWidth="1"/>
-    <col min="69" max="69" width="19.28515625" customWidth="1"/>
-    <col min="70" max="70" width="55.7109375" customWidth="1"/>
-    <col min="78" max="78" width="9.28515625" customWidth="1"/>
-    <col min="79" max="79" width="66.140625" customWidth="1"/>
-    <col min="80" max="80" width="56.28515625" customWidth="1"/>
-    <col min="81" max="81" width="41.28515625" customWidth="1"/>
-    <col min="82" max="82" width="75.7109375" customWidth="1"/>
-    <col min="83" max="83" width="65.7109375" customWidth="1"/>
-    <col min="84" max="84" width="52.28515625" customWidth="1"/>
-    <col min="85" max="85" width="49.7109375" customWidth="1"/>
-    <col min="91" max="91" width="44.42578125" customWidth="1"/>
-    <col min="92" max="92" width="54.28515625" customWidth="1"/>
-    <col min="103" max="103" width="66.85546875" customWidth="1"/>
+    <col min="68" max="68" width="77.140625" customWidth="1"/>
+    <col min="69" max="69" width="55.5703125" customWidth="1"/>
+    <col min="70" max="70" width="69.5703125" customWidth="1"/>
+    <col min="71" max="71" width="85.85546875" customWidth="1"/>
+    <col min="72" max="72" width="61" customWidth="1"/>
+    <col min="73" max="73" width="55.7109375" customWidth="1"/>
+    <col min="74" max="74" width="70.7109375" customWidth="1"/>
+    <col min="76" max="76" width="9.28515625" customWidth="1"/>
+    <col min="77" max="77" width="66.140625" customWidth="1"/>
+    <col min="78" max="78" width="56.28515625" customWidth="1"/>
+    <col min="79" max="79" width="41.28515625" customWidth="1"/>
+    <col min="80" max="80" width="75.7109375" customWidth="1"/>
+    <col min="81" max="81" width="65.7109375" customWidth="1"/>
+    <col min="82" max="82" width="52.28515625" customWidth="1"/>
+    <col min="83" max="83" width="49.7109375" customWidth="1"/>
+    <col min="89" max="89" width="44.42578125" customWidth="1"/>
+    <col min="90" max="90" width="54.28515625" customWidth="1"/>
+    <col min="101" max="101" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -8859,7 +9913,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -8886,10 +9940,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -8913,769 +9967,907 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
       </c>
       <c r="BA3" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB3" t="s">
         <v>133</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>131</v>
       </c>
       <c r="BC3" t="s">
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BE3" t="s">
+        <v>148</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>147</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>151</v>
+      </c>
+      <c r="BQ3" t="s">
         <v>142</v>
       </c>
-      <c r="BF3" t="s">
-        <v>141</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>124</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>137</v>
-      </c>
       <c r="BR3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
       </c>
       <c r="BT3" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>122</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>145</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>143</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="I4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="K4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="L4" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="O4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="Q4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="R4" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="S4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="T4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="U4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="V4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="W4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="X4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="Y4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="Z4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="AA4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AB4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AC4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AD4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="AE4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AF4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AG4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AH4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AI4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AJ4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK4" t="s">
+        <v>191</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>194</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AP4" t="s">
         <v>183</v>
       </c>
-      <c r="AL4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>185</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>186</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>187</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>175</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="AR4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AS4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AT4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="AU4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="AV4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AW4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AX4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AY4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="AZ4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="BA4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="BB4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="BC4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="BD4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="BE4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="BF4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="BG4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="BH4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="BI4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="BJ4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="BK4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="BL4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="BM4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="BN4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="BO4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="BP4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="BQ4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="BR4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="BS4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="BT4" t="s">
-        <v>217</v>
+        <v>225</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>226</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>227</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>228</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>229</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>230</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>231</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>232</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>233</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="F5" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="G5" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="H5" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="K5" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="L5" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="N5" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="P5" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="R5" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="T5" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="U5" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="V5" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="W5" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="Y5" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="Z5" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="AB5" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="AD5" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="AE5" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="AF5" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AI5" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="AK5" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="AL5" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="AM5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AN5" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="AO5" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="AR5" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="AS5" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="AT5" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="AU5" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="AV5" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="AW5" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="AX5" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="AZ5" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="BA5" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="BB5" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="BC5" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="BG5" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="BH5" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="BJ5" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="BK5" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="BM5" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="BN5" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="BO5" t="s">
-        <v>260</v>
+        <v>277</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>278</v>
       </c>
       <c r="BQ5" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="BS5" t="s">
-        <v>262</v>
+        <v>280</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>281</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>282</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>283</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>284</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>285</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>286</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>287</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>288</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="D6" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="G6" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="H6" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="K6" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="L6" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="N6" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="P6" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="T6" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="V6" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="W6" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="Y6" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="Z6" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="AB6" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="AD6" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="AE6" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="AI6" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="AK6" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="AM6" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="AN6" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="AO6" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="AS6" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="AT6" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AU6" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="AV6" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="AW6" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="AX6" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="AZ6" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="BA6" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="BB6" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="BC6" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="BG6" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="BJ6" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="BK6" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="BM6" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="BN6" t="s">
-        <v>299</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>300</v>
+        <v>325</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>326</v>
       </c>
       <c r="BS6" t="s">
-        <v>301</v>
+        <v>327</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>328</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>329</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>330</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>331</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>332</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>333</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>334</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="D7" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="F7" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="G7" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="H7" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="K7" t="s">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="L7" t="s">
-        <v>308</v>
+        <v>341</v>
       </c>
       <c r="N7" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="P7" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="T7" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="V7" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="W7" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="Y7" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="Z7" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="AB7" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="AD7" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="AE7" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="AI7" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="AK7" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="AM7" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="AN7" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="AO7" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="AS7" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="AT7" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="AU7" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="AV7" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="AW7" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="AX7" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="AZ7" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="BC7" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="BG7" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="BJ7" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="BK7" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="BM7" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="BN7" t="s">
-        <v>336</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="BS7" t="s">
-        <v>338</v>
+        <v>369</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>370</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>371</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>372</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>373</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>374</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>375</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="D8" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="F8" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="G8" t="s">
-        <v>342</v>
+        <v>379</v>
       </c>
       <c r="H8" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="K8" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="L8" t="s">
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="V8" t="s">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="W8" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="Y8" t="s">
-        <v>348</v>
+        <v>385</v>
       </c>
       <c r="AB8" t="s">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="AD8" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="AE8" t="s">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="AI8" t="s">
-        <v>352</v>
+        <v>389</v>
       </c>
       <c r="AK8" t="s">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="AM8" t="s">
-        <v>354</v>
+        <v>391</v>
       </c>
       <c r="AO8" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="AT8" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="AU8" t="s">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="AW8" t="s">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="AZ8" t="s">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="BC8" t="s">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="BK8" t="s">
-        <v>361</v>
+        <v>398</v>
       </c>
       <c r="BM8" t="s">
-        <v>362</v>
-      </c>
-      <c r="BO8" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="BS8" t="s">
-        <v>364</v>
+        <v>400</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>401</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>402</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>403</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>404</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:71" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="L9" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="AD9" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="AE9" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="AK9" t="s">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="AT9" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="BC9" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="BK9" t="s">
-        <v>372</v>
+        <v>413</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>414</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>415</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>416</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>417</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>418</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="77:80" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9709,34 +10901,34 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>228</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="11">
         <f>C1*4</f>
-        <v>912</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="B3" s="13">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>915</v>
+        <v>1060</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>375</v>
+        <v>421</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -9744,39 +10936,39 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="B4" s="16">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C4">
         <f>AHL!I1</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>377</v>
+        <v>423</v>
       </c>
       <c r="F4" t="s">
-        <v>378</v>
+        <v>424</v>
       </c>
       <c r="G4" t="s">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="H4" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="I4" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="J4" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="K4" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="L4" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9785,10 +10977,10 @@
       </c>
       <c r="B5" s="16">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="F5" s="18">
         <v>2</v>
@@ -9799,23 +10991,23 @@
       </c>
       <c r="H5" s="20">
         <f>B4/B3</f>
-        <v>0.14426229508196722</v>
+        <v>0.14245283018867924</v>
       </c>
       <c r="I5" s="21">
         <f>C2*G5</f>
-        <v>140.30769230769232</v>
+        <v>163.0769230769231</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="K5" s="22">
         <f>J5-I5</f>
-        <v>-8.30769230769232</v>
+        <v>-12.076923076923094</v>
       </c>
       <c r="L5" s="23">
         <f>K5/4</f>
-        <v>-2.07692307692308</v>
+        <v>-3.0192307692307736</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9824,11 +11016,11 @@
       </c>
       <c r="B6" s="16">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="C6">
         <f>AHL!X1</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>1</v>
@@ -9842,23 +11034,23 @@
       </c>
       <c r="H6" s="20">
         <f>B5/B3</f>
-        <v>0.030601092896174863</v>
+        <v>0.03018867924528302</v>
       </c>
       <c r="I6" s="21">
         <f>C2*G6</f>
-        <v>70.15384615384616</v>
+        <v>81.53846153846155</v>
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K6" s="22">
         <f>J6-I6</f>
-        <v>-42.15384615384616</v>
+        <v>-49.53846153846155</v>
       </c>
       <c r="L6" s="23">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-10.53846153846154</v>
+        <v>-12.384615384615387</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9867,14 +11059,14 @@
       </c>
       <c r="B7" s="25">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>393</v>
+        <v>455</v>
       </c>
       <c r="C7">
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="F7" s="27">
         <v>3</v>
@@ -9885,35 +11077,35 @@
       </c>
       <c r="H7" s="29">
         <f>(B5+B4)/B3</f>
-        <v>0.17486338797814208</v>
+        <v>0.17264150943396225</v>
       </c>
       <c r="I7" s="21">
         <f>C2*G7</f>
-        <v>210.46153846153848</v>
+        <v>244.61538461538464</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="K7" s="22">
         <f>J7-I7</f>
-        <v>-50.46153846153848</v>
+        <v>-61.61538461538464</v>
       </c>
       <c r="L7" s="23">
         <f>K7/4</f>
-        <v>-12.61538461538462</v>
+        <v>-15.40384615384616</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="F8" s="32">
         <v>6</v>
@@ -9924,35 +11116,35 @@
       </c>
       <c r="H8" s="34">
         <f>B6/B3</f>
-        <v>0.39562841530054643</v>
+        <v>0.39811320754716983</v>
       </c>
       <c r="I8" s="21">
         <f>C2*G8</f>
-        <v>420.92307692307696</v>
+        <v>489.2307692307693</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="K8" s="22">
         <f>J8-I8</f>
-        <v>-58.92307692307696</v>
+        <v>-67.23076923076928</v>
       </c>
       <c r="L8" s="23">
         <f>K8/4</f>
-        <v>-14.73076923076924</v>
+        <v>-16.80769230769232</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>915</v>
+        <v>1060</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="F9" s="32">
         <v>4</v>
@@ -9963,75 +11155,75 @@
       </c>
       <c r="H9" s="34">
         <f>B7/B3</f>
-        <v>0.42950819672131146</v>
+        <v>0.42924528301886794</v>
       </c>
       <c r="I9" s="21">
         <f>C2*G9</f>
-        <v>280.61538461538464</v>
+        <v>326.1538461538462</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>393</v>
+        <v>455</v>
       </c>
       <c r="K9" s="35">
         <f>J9-I9</f>
-        <v>112.38461538461536</v>
+        <v>128.8461538461538</v>
       </c>
       <c r="L9" s="23">
         <f>K9/4</f>
-        <v>28.09615384615384</v>
+        <v>32.21153846153845</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="36" t="s">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="I11" s="37">
         <f>SUM(I7:I9)</f>
-        <v>912.0000000000001</v>
+        <v>1060</v>
       </c>
       <c r="J11" s="31">
         <f>SUM(J7:J9)</f>
-        <v>915</v>
+        <v>1060</v>
       </c>
       <c r="K11" s="38">
         <f>SUM(K7:K9)</f>
-        <v>2.9999999999999147</v>
+        <v>0</v>
       </c>
       <c r="L11" s="39">
         <f>SUM(L7:L9)</f>
-        <v>0.7499999999999787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>391</v>
+        <v>437</v>
       </c>
       <c r="F16" t="s">
-        <v>378</v>
+        <v>424</v>
       </c>
       <c r="G16" t="s">
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="H16" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="J16" s="40" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="K16" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="L16" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="41" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="F17" s="42">
         <v>3</v>
@@ -10042,28 +11234,28 @@
       </c>
       <c r="H17" s="44">
         <f>(B5+B4)/B3</f>
-        <v>0.17486338797814208</v>
+        <v>0.17264150943396225</v>
       </c>
       <c r="I17" s="45">
         <f>B3*G17</f>
-        <v>211.15384615384616</v>
+        <v>244.61538461538464</v>
       </c>
       <c r="J17" s="46">
         <f>B5+B4</f>
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="K17" s="47">
         <f>J17-I17</f>
-        <v>-51.15384615384616</v>
+        <v>-61.61538461538464</v>
       </c>
       <c r="L17" s="23">
         <f>K17/4</f>
-        <v>-12.78846153846154</v>
+        <v>-15.40384615384616</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="48" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="F18" s="49">
         <v>6</v>
@@ -10074,29 +11266,29 @@
       </c>
       <c r="H18" s="51">
         <f>B6/B3</f>
-        <v>0.39562841530054643</v>
+        <v>0.39811320754716983</v>
       </c>
       <c r="I18" s="52">
         <f>B3*G18</f>
-        <v>422.3076923076923</v>
+        <v>489.2307692307693</v>
       </c>
       <c r="J18" s="53">
         <f>B6</f>
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="K18" s="54">
         <f>J18-I18</f>
-        <v>-60.30769230769232</v>
+        <v>-67.23076923076928</v>
       </c>
       <c r="L18" s="23">
         <f>K18/4</f>
-        <v>-15.07692307692308</v>
+        <v>-16.80769230769232</v>
       </c>
       <c r="Q18" s="55"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="56" t="s">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="F19" s="57">
         <v>4</v>
@@ -10107,28 +11299,28 @@
       </c>
       <c r="H19" s="59">
         <f>B7/B3</f>
-        <v>0.42950819672131146</v>
+        <v>0.42924528301886794</v>
       </c>
       <c r="I19" s="60">
         <f>B3*G19</f>
-        <v>281.53846153846155</v>
+        <v>326.1538461538462</v>
       </c>
       <c r="J19" s="61">
         <f>B7</f>
-        <v>393</v>
+        <v>455</v>
       </c>
       <c r="K19" s="62">
         <f>J19-I19</f>
-        <v>111.46153846153845</v>
+        <v>128.8461538461538</v>
       </c>
       <c r="L19" s="23">
         <f>K19/4</f>
-        <v>27.865384615384613</v>
+        <v>32.21153846153845</v>
       </c>
     </row>
     <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E21" s="63" t="s">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="F21" s="63"/>
       <c r="G21" s="63"/>
@@ -10139,27 +11331,27 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>378</v>
+        <v>424</v>
       </c>
       <c r="G22" t="s">
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="H22" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="I22" s="40" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="J22" s="40" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="K22" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E23" s="41" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="F23" s="42">
         <v>3</v>
@@ -10170,24 +11362,24 @@
       </c>
       <c r="H23" s="44">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.18181818181818182</v>
+        <v>0.17780172413793102</v>
       </c>
       <c r="I23" s="45">
         <f>(B3-C8) *G23</f>
-        <v>185.30769230769232</v>
+        <v>214.15384615384616</v>
       </c>
       <c r="J23" s="46">
         <f>B4+B5-C4</f>
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="K23" s="47">
         <f>J23-I23</f>
-        <v>-39.30769230769232</v>
+        <v>-49.15384615384616</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E24" s="48" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="F24" s="49">
         <v>6</v>
@@ -10198,24 +11390,24 @@
       </c>
       <c r="H24" s="51">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.43337484433374845</v>
+        <v>0.4353448275862069</v>
       </c>
       <c r="I24" s="52">
         <f>(B3-C8)*G24</f>
-        <v>370.61538461538464</v>
+        <v>428.3076923076923</v>
       </c>
       <c r="J24" s="53">
         <f>B6-C6</f>
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="K24" s="54">
         <f>J24-I24</f>
-        <v>-13.615384615384642</v>
+        <v>-12.30769230769232</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E25" s="56" t="s">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="F25" s="57">
         <v>4</v>
@@ -10226,49 +11418,49 @@
       </c>
       <c r="H25" s="59">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.37359900373599003</v>
+        <v>0.3739224137931034</v>
       </c>
       <c r="I25" s="60">
         <f>(B3-C8)*G25</f>
-        <v>247.0769230769231</v>
+        <v>285.53846153846155</v>
       </c>
       <c r="J25" s="61">
         <f>B7-C7</f>
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="K25" s="62">
         <f>J25-I25</f>
-        <v>52.923076923076906</v>
+        <v>61.46153846153845</v>
       </c>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="64">
         <f>C8/B9</f>
-        <v>0.12240437158469945</v>
+        <v>0.12452830188679245</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="65">
         <f>C8</f>
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="K26" s="5"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>915</v>
+        <v>1060</v>
       </c>
       <c r="K28" s="66">
         <f>SUM(K23:K25)</f>
-        <v>-5.684341886080802e-14</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2733" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="450">
   <si>
     <t>sl</t>
   </si>
@@ -439,18 +439,18 @@
     <t>2025-01-03</t>
   </si>
   <si>
+    <t>2025-02-18</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
     <t>zbrisano</t>
   </si>
   <si>
-    <t>2025-02-13</t>
-  </si>
-  <si>
-    <t>2025-01-28</t>
-  </si>
-  <si>
-    <t>2025-02-18</t>
-  </si>
-  <si>
     <t>2025-01-18</t>
   </si>
   <si>
@@ -463,6 +463,9 @@
     <t>2025-01-12</t>
   </si>
   <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
     <t>2025-01-08</t>
   </si>
   <si>
@@ -475,6 +478,9 @@
     <t>2025-01-26</t>
   </si>
   <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
     <t>2025-01-29</t>
   </si>
   <si>
@@ -721,6 +727,12 @@
     <t>Eishalle Celje;BajtMi;BulovecMi;ArlicMa;JeramFi</t>
   </si>
   <si>
+    <t>Eishalle Jesenice;BrockAd;RuetzMa;RinkerDa;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;LazzeriAl;LegaSi;CusinFe;GrisentiLu</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -886,6 +898,9 @@
     <t>Eisarena Salzburg;HlavatyAl;WenuschHe;PreiserJu;WeissAl</t>
   </si>
   <si>
+    <t>Eishalle Celje;LebenJa;MetzingerFi;JavornikBl;KnezRo</t>
+  </si>
+  <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
   </si>
   <si>
@@ -1024,6 +1039,9 @@
     <t>Sportpark Kitzbühel;MoidlDa;SpiegelSe;JägerRi;RinkerDa</t>
   </si>
   <si>
+    <t>Eisarena Salzburg;HolzerTo;SpiegelSe;DivisDo;JägerRi</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -1144,7 +1162,10 @@
     <t>Eishalle Gröden;EggerTh;LazzeriAl;AbeltinoSi;CristeliMa</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;KainbergerJu;LehnerMo;EislCh;MoidlMa</t>
+    <t>Eishalle Sterzing;KainbergerJu;PinieOm;CristeliMa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;Huber rRe;OrelSt;StrimitzerDa;WuchererGe</t>
   </si>
   <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
@@ -1231,12 +1252,15 @@
     <t>Eishalle Gröden;LegaSi;SoraperraSi;FormaioniTh;PaceJa</t>
   </si>
   <si>
-    <t>Eishalle Cortina;PirasAn;SnojTa;BrondiPa;MarkizetiGr</t>
+    <t>Eishalle Cortina;PirasAn;SnojTa;BrondiPa;JeramFi</t>
   </si>
   <si>
     <t>Eishalle Ritten;VirtaTu;WidmannFl;BrondiPa;TelesklavFa</t>
   </si>
   <si>
+    <t>Sportpark Kitzbühel;KainbergerJu;SnojTa;JeramFi;SeewaldJe</t>
+  </si>
+  <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
   </si>
   <si>
@@ -1264,7 +1288,7 @@
     <t>Eishalle Gröden;Huber rRe;MoschenAn;RinkerDa;StrimitzerDa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;MeixnerSe;RuetzMa;MoidlMa;SeewaldJe</t>
+    <t>Sportpark Kitzbühel;MeixnerSe;RuetzMa;MoidlMa;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Cortina;LesniakBo;OrelSt;JavornikBl;TelesklavFa</t>
@@ -1274,6 +1298,9 @@
   </si>
   <si>
     <t>Würtharena Neumarkt;BenvegnuAn;StefenelliFe;PaceJa;ScalzeriAl</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;MoschenAn;RivisFe;FecchioFe;FormaioniTh</t>
   </si>
   <si>
     <t>vse delegirane tekme</t>
@@ -2206,7 +2233,7 @@
     <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B64,"&lt;&gt;")</f>
@@ -2226,7 +2253,7 @@
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G1">
         <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
@@ -2238,19 +2265,19 @@
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I68,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J64,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M1">
         <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
@@ -2266,15 +2293,15 @@
       </c>
       <c r="P1">
         <f t="shared" ref="P1:Z1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q66,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R1">
         <f>COUNTIF(R4:R63,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
@@ -2282,11 +2309,11 @@
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1">
         <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V66,"&lt;&gt;")</f>
@@ -2326,11 +2353,11 @@
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF63,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG65,"&lt;&gt;")</f>
@@ -2342,7 +2369,7 @@
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ1">
         <f>COUNTIF(AJ4:AJ61,"&lt;&gt;")</f>
@@ -2354,7 +2381,7 @@
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL65,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM64,"&lt;&gt;")</f>
@@ -2362,31 +2389,31 @@
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN63,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP1">
         <f>COUNTIF(AP4:AP66,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ1">
         <f>COUNTIF(AQ4:AQ67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR1">
         <f>COUNTIF(AR4:AR60,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS68,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT1">
         <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU1">
         <f>COUNTIF(AU4:AU67,"&lt;&gt;")</f>
@@ -2402,7 +2429,7 @@
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX65,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY60,"&lt;&gt;")</f>
@@ -2410,27 +2437,27 @@
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ64,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA1">
         <f>COUNTIF(BA4:BA69,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB68,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD1">
-        <f>COUNTIF(BD4:BD68,"&lt;&gt;")</f>
+        <f>COUNTIF(BD4:BD67,"&lt;&gt;")</f>
         <v>16</v>
       </c>
       <c r="BE1">
-        <f>COUNTIF(BE4:BE67,"&lt;&gt;")</f>
-        <v>10</v>
+        <f>COUNTIF(BE4:BE66,"&lt;&gt;")</f>
+        <v>9</v>
       </c>
       <c r="BF1">
         <f>COUNTIF(BF4:BF68,"&lt;&gt;")</f>
@@ -2454,7 +2481,7 @@
       </c>
       <c r="BK1">
         <f>COUNTIF(BK4:BK65,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BL1">
         <f t="shared" si="1"/>
@@ -2466,15 +2493,15 @@
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BO1">
         <f>COUNTIF(BO4:BO69,"&lt;&gt;")</f>
         <v>8</v>
       </c>
       <c r="BP1">
-        <f>COUNTIF(BP4:BP69,"&lt;&gt;")</f>
-        <v>12</v>
+        <f>COUNTIF(BP4:BP68,"&lt;&gt;")</f>
+        <v>11</v>
       </c>
       <c r="BQ1">
         <f t="shared" si="1"/>
@@ -4817,11 +4844,8 @@
       <c r="BD13" t="s">
         <v>121</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BF13" t="s">
         <v>143</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>136</v>
       </c>
       <c r="BK13" t="s">
         <v>103</v>
@@ -5006,7 +5030,7 @@
         <v>119</v>
       </c>
       <c r="BP14" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -5034,6 +5058,9 @@
       <c r="I15" t="s">
         <v>125</v>
       </c>
+      <c r="J15" t="s">
+        <v>148</v>
+      </c>
       <c r="K15" t="s">
         <v>137</v>
       </c>
@@ -5080,7 +5107,7 @@
         <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC15" t="s">
         <v>135</v>
@@ -5104,19 +5131,19 @@
         <v>124</v>
       </c>
       <c r="AJ15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AL15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AO15" t="s">
         <v>129</v>
@@ -5175,11 +5202,8 @@
       <c r="BN15" t="s">
         <v>144</v>
       </c>
-      <c r="BP15" t="s">
-        <v>136</v>
-      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -5196,7 +5220,7 @@
         <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H16" t="s">
         <v>134</v>
@@ -5241,7 +5265,7 @@
         <v>104</v>
       </c>
       <c r="Y16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="Z16" t="s">
         <v>111</v>
@@ -5265,11 +5289,14 @@
         <v>134</v>
       </c>
       <c r="AG16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH16" t="s">
         <v>142</v>
       </c>
+      <c r="AI16" t="s">
+        <v>153</v>
+      </c>
       <c r="AJ16" t="s">
         <v>131</v>
       </c>
@@ -5319,7 +5346,7 @@
         <v>134</v>
       </c>
       <c r="AZ16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BA16" t="s">
         <v>135</v>
@@ -5334,7 +5361,7 @@
         <v>137</v>
       </c>
       <c r="BK16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BM16" t="s">
         <v>124</v>
@@ -5351,7 +5378,7 @@
         <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
         <v>133</v>
@@ -5419,6 +5446,9 @@
       <c r="AD17" t="s">
         <v>122</v>
       </c>
+      <c r="AE17" t="s">
+        <v>148</v>
+      </c>
       <c r="AF17" t="s">
         <v>137</v>
       </c>
@@ -5444,7 +5474,7 @@
         <v>130</v>
       </c>
       <c r="AO17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AP17" t="s">
         <v>119</v>
@@ -5453,7 +5483,7 @@
         <v>142</v>
       </c>
       <c r="AR17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AS17" t="s">
         <v>145</v>
@@ -5474,7 +5504,7 @@
         <v>120</v>
       </c>
       <c r="AY17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AZ17" t="s">
         <v>120</v>
@@ -5492,16 +5522,13 @@
         <v>119</v>
       </c>
       <c r="BK17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BM17" t="s">
         <v>136</v>
       </c>
-      <c r="BN17" t="s">
-        <v>136</v>
-      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -5517,11 +5544,14 @@
       <c r="E18" t="s">
         <v>134</v>
       </c>
+      <c r="F18" t="s">
+        <v>148</v>
+      </c>
       <c r="H18" t="s">
         <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
         <v>145</v>
@@ -5530,10 +5560,10 @@
         <v>145</v>
       </c>
       <c r="N18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P18" t="s">
         <v>121</v>
@@ -5581,14 +5611,17 @@
         <v>141</v>
       </c>
       <c r="AH18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AJ18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s">
         <v>144</v>
       </c>
+      <c r="AL18" t="s">
+        <v>148</v>
+      </c>
       <c r="AM18" t="s">
         <v>137</v>
       </c>
@@ -5608,13 +5641,13 @@
         <v>91</v>
       </c>
       <c r="AS18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AT18" t="s">
         <v>121</v>
       </c>
       <c r="AU18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AV18" t="s">
         <v>131</v>
@@ -5638,10 +5671,10 @@
         <v>138</v>
       </c>
       <c r="BC18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="BD18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK18" t="s">
         <v>145</v>
@@ -5658,7 +5691,7 @@
         <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
         <v>119</v>
@@ -5666,8 +5699,11 @@
       <c r="I19" t="s">
         <v>126</v>
       </c>
+      <c r="K19" t="s">
+        <v>148</v>
+      </c>
       <c r="L19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N19" t="s">
         <v>145</v>
@@ -5700,7 +5736,7 @@
         <v>130</v>
       </c>
       <c r="Z19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AA19" t="s">
         <v>122</v>
@@ -5712,7 +5748,7 @@
         <v>119</v>
       </c>
       <c r="AD19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="s">
         <v>145</v>
@@ -5724,10 +5760,10 @@
         <v>126</v>
       </c>
       <c r="AK19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN19" t="s">
         <v>134</v>
@@ -5739,7 +5775,7 @@
         <v>145</v>
       </c>
       <c r="AQ19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AR19" t="s">
         <v>139</v>
@@ -5751,7 +5787,7 @@
         <v>120</v>
       </c>
       <c r="AV19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AW19" t="s">
         <v>137</v>
@@ -5769,10 +5805,13 @@
         <v>137</v>
       </c>
       <c r="BB19" t="s">
+        <v>149</v>
+      </c>
+      <c r="BC19" t="s">
         <v>148</v>
       </c>
       <c r="BD19" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="BK19" t="s">
         <v>136</v>
@@ -5780,7 +5819,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
         <v>136</v>
@@ -5794,6 +5833,9 @@
       <c r="I20" t="s">
         <v>124</v>
       </c>
+      <c r="L20" t="s">
+        <v>148</v>
+      </c>
       <c r="N20" t="s">
         <v>124</v>
       </c>
@@ -5836,6 +5878,12 @@
       <c r="AC20" t="s">
         <v>142</v>
       </c>
+      <c r="AF20" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>136</v>
+      </c>
       <c r="AH20" t="s">
         <v>141</v>
       </c>
@@ -5860,6 +5908,9 @@
       <c r="AR20" t="s">
         <v>137</v>
       </c>
+      <c r="AS20" t="s">
+        <v>148</v>
+      </c>
       <c r="AT20" t="s">
         <v>129</v>
       </c>
@@ -5873,13 +5924,16 @@
         <v>144</v>
       </c>
       <c r="BA20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BB20" t="s">
         <v>127</v>
       </c>
+      <c r="BK20" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
@@ -5896,10 +5950,10 @@
         <v>136</v>
       </c>
       <c r="O21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q21" t="s">
         <v>131</v>
@@ -5908,7 +5962,7 @@
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="T21" t="s">
         <v>124</v>
@@ -5917,10 +5971,10 @@
         <v>137</v>
       </c>
       <c r="V21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="W21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z21" t="s">
         <v>145</v>
@@ -5929,7 +5983,7 @@
         <v>136</v>
       </c>
       <c r="AB21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AC21" t="s">
         <v>124</v>
@@ -5944,10 +5998,13 @@
         <v>145</v>
       </c>
       <c r="AN21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AO21" t="s">
-        <v>153</v>
+        <v>155</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>148</v>
       </c>
       <c r="AR21" t="s">
         <v>120</v>
@@ -5968,18 +6025,21 @@
         <v>119</v>
       </c>
       <c r="BB21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
       </c>
+      <c r="I22" t="s">
+        <v>148</v>
+      </c>
       <c r="P22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q22" t="s">
         <v>141</v>
@@ -5990,6 +6050,9 @@
       <c r="S22" t="s">
         <v>127</v>
       </c>
+      <c r="T22" t="s">
+        <v>148</v>
+      </c>
       <c r="U22" t="s">
         <v>134</v>
       </c>
@@ -6003,13 +6066,13 @@
         <v>124</v>
       </c>
       <c r="AC22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AH22" t="s">
         <v>136</v>
       </c>
       <c r="AK22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AM22" t="s">
         <v>124</v>
@@ -6021,7 +6084,7 @@
         <v>145</v>
       </c>
       <c r="AR22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT22" t="s">
         <v>119</v>
@@ -6039,24 +6102,33 @@
         <v>144</v>
       </c>
       <c r="BB22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" t="s">
+        <v>140</v>
+      </c>
       <c r="P23" t="s">
         <v>145</v>
       </c>
+      <c r="Q23" t="s">
+        <v>153</v>
+      </c>
       <c r="R23" t="s">
         <v>131</v>
       </c>
       <c r="S23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U23" t="s">
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="W23" t="s">
         <v>136</v>
@@ -6064,17 +6136,29 @@
       <c r="Z23" t="s">
         <v>136</v>
       </c>
+      <c r="AK23" t="s">
+        <v>136</v>
+      </c>
       <c r="AM23" t="s">
         <v>136</v>
       </c>
+      <c r="AN23" t="s">
+        <v>148</v>
+      </c>
       <c r="AO23" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AR23" t="s">
         <v>126</v>
       </c>
       <c r="AT23" t="s">
-        <v>153</v>
+        <v>155</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>148</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>148</v>
       </c>
       <c r="BA23" t="s">
         <v>145</v>
@@ -6083,7 +6167,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="P24" t="s">
         <v>124</v>
       </c>
@@ -6096,22 +6180,31 @@
       <c r="U24" t="s">
         <v>145</v>
       </c>
+      <c r="AO24" t="s">
+        <v>148</v>
+      </c>
       <c r="AR24" t="s">
         <v>124</v>
       </c>
       <c r="AT24" t="s">
         <v>141</v>
       </c>
+      <c r="AZ24" t="s">
+        <v>136</v>
+      </c>
       <c r="BA24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="BB24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>148</v>
+      </c>
       <c r="R25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S25" t="s">
         <v>141</v>
@@ -6119,16 +6212,37 @@
       <c r="U25" t="s">
         <v>124</v>
       </c>
+      <c r="AR25" t="s">
+        <v>148</v>
+      </c>
       <c r="AT25" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="AZ25" t="s">
+        <v>141</v>
+      </c>
+      <c r="BA25" t="s">
+        <v>148</v>
+      </c>
+      <c r="BB25" t="s">
+        <v>148</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="18:46" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+      <c r="R26" t="s">
+        <v>153</v>
+      </c>
       <c r="S26" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="U26" t="s">
+        <v>148</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>148</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="19:19" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="18:46" x14ac:dyDescent="0.25">
       <c r="S27" t="s">
         <v>136</v>
       </c>
@@ -6187,7 +6301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CB42"/>
+  <dimension ref="A3:CD42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -6235,7 +6349,7 @@
     <col min="83" max="83" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -6387,7 +6501,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
@@ -6405,7 +6519,7 @@
         <v>139</v>
       </c>
       <c r="BE3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BF3" t="s">
         <v>147</v>
@@ -6435,16 +6549,16 @@
         <v>134</v>
       </c>
       <c r="BO3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BP3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BQ3" t="s">
         <v>142</v>
       </c>
       <c r="BR3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
@@ -6459,7 +6573,7 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BX3" t="s">
         <v>145</v>
@@ -6471,13 +6585,19 @@
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="CB3" t="s">
         <v>136</v>
       </c>
+      <c r="CC3" t="s">
+        <v>148</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -6718,8 +6838,14 @@
       <c r="CB4" t="s">
         <v>5</v>
       </c>
+      <c r="CC4" t="s">
+        <v>58</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6960,8 +7086,14 @@
       <c r="CB5" t="s">
         <v>6</v>
       </c>
+      <c r="CC5" t="s">
+        <v>49</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -7202,8 +7334,14 @@
       <c r="CB6" t="s">
         <v>7</v>
       </c>
+      <c r="CC6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -7444,13 +7582,19 @@
       <c r="CB7" t="s">
         <v>12</v>
       </c>
+      <c r="CC7" t="s">
+        <v>48</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -7474,7 +7618,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -7611,8 +7755,11 @@
       <c r="CB8" t="s">
         <v>68</v>
       </c>
+      <c r="CC8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -7626,7 +7773,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -7778,8 +7925,11 @@
       <c r="CB9" t="s">
         <v>63</v>
       </c>
+      <c r="CC9" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -7945,8 +8095,11 @@
       <c r="CB10" t="s">
         <v>52</v>
       </c>
+      <c r="CC10" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -8112,8 +8265,11 @@
       <c r="CB11" t="s">
         <v>62</v>
       </c>
+      <c r="CC11" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -8139,7 +8295,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -8252,8 +8408,11 @@
       <c r="CB12" t="s">
         <v>70</v>
       </c>
+      <c r="CC12" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -8392,8 +8551,11 @@
       <c r="CB13" t="s">
         <v>45</v>
       </c>
+      <c r="CC13" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -8532,8 +8694,11 @@
       <c r="CB14" t="s">
         <v>66</v>
       </c>
+      <c r="CC14" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -8672,8 +8837,11 @@
       <c r="CB15" t="s">
         <v>53</v>
       </c>
+      <c r="CC15" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -8800,8 +8968,11 @@
       <c r="CB16" t="s">
         <v>41</v>
       </c>
+      <c r="CC16" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -8926,10 +9097,13 @@
         <v>21</v>
       </c>
       <c r="CB17" t="s">
-        <v>71</v>
+        <v>36</v>
+      </c>
+      <c r="CC17" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -9054,10 +9228,13 @@
         <v>32</v>
       </c>
       <c r="CB18" t="s">
-        <v>69</v>
+        <v>40</v>
+      </c>
+      <c r="CC18" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -9182,10 +9359,13 @@
         <v>40</v>
       </c>
       <c r="CB19" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="CC19" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -9276,8 +9456,11 @@
       <c r="CB20" t="s">
         <v>26</v>
       </c>
+      <c r="CC20" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -9368,8 +9551,11 @@
       <c r="CB21" t="s">
         <v>54</v>
       </c>
+      <c r="CC21" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -9460,8 +9646,11 @@
       <c r="CB22" t="s">
         <v>22</v>
       </c>
+      <c r="CC22" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -9541,19 +9730,22 @@
         <v>23</v>
       </c>
       <c r="BY23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="BZ23" t="s">
         <v>37</v>
       </c>
       <c r="CA23" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="s">
         <v>42</v>
       </c>
+      <c r="CC23" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -9590,8 +9782,11 @@
       <c r="CB24" t="s">
         <v>17</v>
       </c>
+      <c r="CC24" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -9628,8 +9823,11 @@
       <c r="CB25" t="s">
         <v>29</v>
       </c>
+      <c r="CC25" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -9666,8 +9864,11 @@
       <c r="CB26" t="s">
         <v>37</v>
       </c>
+      <c r="CC26" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -9704,8 +9905,11 @@
       <c r="CB27" t="s">
         <v>30</v>
       </c>
+      <c r="CC27" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="78:80" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" spans="79:81" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9727,7 +9931,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CB14"/>
+  <dimension ref="A3:CD14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -9815,7 +10019,7 @@
     <col min="101" max="101" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -9967,7 +10171,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
@@ -9985,7 +10189,7 @@
         <v>139</v>
       </c>
       <c r="BE3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BF3" t="s">
         <v>147</v>
@@ -10015,16 +10219,16 @@
         <v>134</v>
       </c>
       <c r="BO3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BP3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BQ3" t="s">
         <v>142</v>
       </c>
       <c r="BR3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
@@ -10039,7 +10243,7 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BX3" t="s">
         <v>145</v>
@@ -10051,823 +10255,850 @@
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="CB3" t="s">
         <v>136</v>
       </c>
+      <c r="CC3" t="s">
+        <v>148</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="S4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="T4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="U4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="V4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="W4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="X4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Z4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AA4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AB4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AC4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AD4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AE4" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>189</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>191</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>194</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AP4" t="s">
         <v>185</v>
       </c>
-      <c r="AF4" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>187</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>188</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>189</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>190</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>192</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>194</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>195</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>183</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AR4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AS4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AT4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AU4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AV4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AW4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AX4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AY4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AZ4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="BA4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="BB4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="BC4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BD4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BE4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BF4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BG4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BH4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BI4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BJ4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BK4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BL4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="BM4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="BN4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BO4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BP4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BQ4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BR4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BS4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BT4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BU4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BV4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BW4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BX4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="BY4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BZ4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="CA4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="CB4" t="s">
-        <v>233</v>
+        <v>235</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>236</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="L5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="P5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="R5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="T5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="U5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="V5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="W5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Y5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Z5" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AB5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AD5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AE5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AF5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AI5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AK5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AL5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AM5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AN5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AO5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AR5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AS5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AT5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AU5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AV5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AW5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AX5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AZ5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="BA5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="BB5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="BC5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="BG5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="BH5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="BJ5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="BK5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="BM5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="BN5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="BO5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="BP5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="BQ5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="BS5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="BT5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="BU5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="BV5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="BX5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="BY5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="BZ5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="CA5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="CB5" t="s">
-        <v>288</v>
+        <v>292</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>293</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F6" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G6" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H6" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K6" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="L6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N6" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="P6" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="T6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="V6" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="W6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Y6" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Z6" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AB6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AD6" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AE6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AI6" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AK6" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AM6" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AN6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AO6" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AS6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AT6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AU6" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AV6" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AW6" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AX6" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AZ6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="BA6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="BB6" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="BC6" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="BG6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="BJ6" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="BK6" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="BM6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="BN6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="BP6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="BS6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="BU6" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="BV6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="BX6" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="BY6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="BZ6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="CA6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="CB6" t="s">
-        <v>334</v>
+        <v>339</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>340</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D7" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F7" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H7" t="s">
+        <v>345</v>
+      </c>
+      <c r="K7" t="s">
+        <v>346</v>
+      </c>
+      <c r="L7" t="s">
+        <v>347</v>
+      </c>
+      <c r="N7" t="s">
         <v>337</v>
       </c>
-      <c r="G7" t="s">
-        <v>338</v>
-      </c>
-      <c r="H7" t="s">
-        <v>339</v>
-      </c>
-      <c r="K7" t="s">
-        <v>340</v>
-      </c>
-      <c r="L7" t="s">
-        <v>341</v>
-      </c>
-      <c r="N7" t="s">
-        <v>332</v>
-      </c>
       <c r="P7" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="T7" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="V7" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="W7" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="Y7" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="Z7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AB7" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AD7" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AE7" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AI7" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AK7" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AM7" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AN7" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AO7" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AS7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AT7" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="AU7" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AV7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AW7" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AX7" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AZ7" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="BC7" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="BG7" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="BJ7" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="BK7" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="BM7" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="BN7" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="BS7" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="BV7" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="BX7" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="BY7" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="BZ7" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="CA7" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="CB7" t="s">
-        <v>375</v>
+        <v>381</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>382</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:80" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D8" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F8" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="G8" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="H8" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="K8" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="L8" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="V8" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="W8" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Y8" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AB8" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="AD8" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="AE8" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="AI8" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AK8" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AM8" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AO8" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AT8" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="AU8" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AW8" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="AZ8" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="BC8" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="BK8" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="BM8" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="BS8" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="BX8" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="BY8" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="BZ8" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="CA8" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="CB8" t="s">
-        <v>405</v>
+        <v>412</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>413</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:80" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="L9" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AD9" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AE9" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AK9" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AT9" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="BC9" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="BK9" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="BX9" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="BY9" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="BZ9" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="CA9" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="CB9" t="s">
-        <v>418</v>
+        <v>426</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>427</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="77:80" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" spans="79:81" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10901,34 +11132,34 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="11">
         <f>C1*4</f>
-        <v>1060</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B3" s="13">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -10936,39 +11167,39 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B4" s="16">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C4">
         <f>AHL!I1</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F4" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G4" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="H4" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="I4" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="J4" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="K4" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="L4" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -10977,10 +11208,10 @@
       </c>
       <c r="B5" s="16">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="F5" s="18">
         <v>2</v>
@@ -10991,23 +11222,23 @@
       </c>
       <c r="H5" s="20">
         <f>B4/B3</f>
-        <v>0.14245283018867924</v>
+        <v>0.14246323529411764</v>
       </c>
       <c r="I5" s="21">
         <f>C2*G5</f>
-        <v>163.0769230769231</v>
+        <v>168</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K5" s="22">
         <f>J5-I5</f>
-        <v>-12.076923076923094</v>
+        <v>-13</v>
       </c>
       <c r="L5" s="23">
         <f>K5/4</f>
-        <v>-3.0192307692307736</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11016,7 +11247,7 @@
       </c>
       <c r="B6" s="16">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C6">
         <f>AHL!X1</f>
@@ -11034,23 +11265,23 @@
       </c>
       <c r="H6" s="20">
         <f>B5/B3</f>
-        <v>0.03018867924528302</v>
+        <v>0.03125</v>
       </c>
       <c r="I6" s="21">
         <f>C2*G6</f>
-        <v>81.53846153846155</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" s="22">
         <f>J6-I6</f>
-        <v>-49.53846153846155</v>
+        <v>-50</v>
       </c>
       <c r="L6" s="23">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-12.384615384615387</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11059,14 +11290,14 @@
       </c>
       <c r="B7" s="25">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="C7">
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F7" s="27">
         <v>3</v>
@@ -11077,35 +11308,35 @@
       </c>
       <c r="H7" s="29">
         <f>(B5+B4)/B3</f>
-        <v>0.17264150943396225</v>
+        <v>0.17371323529411764</v>
       </c>
       <c r="I7" s="21">
         <f>C2*G7</f>
-        <v>244.61538461538464</v>
+        <v>252</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K7" s="22">
         <f>J7-I7</f>
-        <v>-61.61538461538464</v>
+        <v>-63</v>
       </c>
       <c r="L7" s="23">
         <f>K7/4</f>
-        <v>-15.40384615384616</v>
+        <v>-15.75</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F8" s="32">
         <v>6</v>
@@ -11116,35 +11347,35 @@
       </c>
       <c r="H8" s="34">
         <f>B6/B3</f>
-        <v>0.39811320754716983</v>
+        <v>0.3952205882352941</v>
       </c>
       <c r="I8" s="21">
         <f>C2*G8</f>
-        <v>489.2307692307693</v>
+        <v>504</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="K8" s="22">
         <f>J8-I8</f>
-        <v>-67.23076923076928</v>
+        <v>-74</v>
       </c>
       <c r="L8" s="23">
         <f>K8/4</f>
-        <v>-16.80769230769232</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="F9" s="32">
         <v>4</v>
@@ -11155,75 +11386,75 @@
       </c>
       <c r="H9" s="34">
         <f>B7/B3</f>
-        <v>0.42924528301886794</v>
+        <v>0.43106617647058826</v>
       </c>
       <c r="I9" s="21">
         <f>C2*G9</f>
-        <v>326.1538461538462</v>
+        <v>336</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="K9" s="35">
         <f>J9-I9</f>
-        <v>128.8461538461538</v>
+        <v>133</v>
       </c>
       <c r="L9" s="23">
         <f>K9/4</f>
-        <v>32.21153846153845</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="36" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="I11" s="37">
         <f>SUM(I7:I9)</f>
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="J11" s="31">
         <f>SUM(J7:J9)</f>
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="K11" s="38">
         <f>SUM(K7:K9)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L11" s="39">
         <f>SUM(L7:L9)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>446</v>
+      </c>
+      <c r="F16" t="s">
+        <v>433</v>
+      </c>
+      <c r="G16" t="s">
+        <v>447</v>
+      </c>
+      <c r="H16" t="s">
+        <v>435</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>436</v>
+      </c>
+      <c r="J16" s="40" t="s">
         <v>437</v>
       </c>
-      <c r="F16" t="s">
-        <v>424</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="K16" t="s">
         <v>438</v>
       </c>
-      <c r="H16" t="s">
-        <v>426</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="J16" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="K16" t="s">
-        <v>429</v>
-      </c>
       <c r="L16" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="41" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F17" s="42">
         <v>3</v>
@@ -11234,28 +11465,28 @@
       </c>
       <c r="H17" s="44">
         <f>(B5+B4)/B3</f>
-        <v>0.17264150943396225</v>
+        <v>0.17371323529411764</v>
       </c>
       <c r="I17" s="45">
         <f>B3*G17</f>
-        <v>244.61538461538464</v>
+        <v>251.0769230769231</v>
       </c>
       <c r="J17" s="46">
         <f>B5+B4</f>
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K17" s="47">
         <f>J17-I17</f>
-        <v>-61.61538461538464</v>
+        <v>-62.076923076923094</v>
       </c>
       <c r="L17" s="23">
         <f>K17/4</f>
-        <v>-15.40384615384616</v>
+        <v>-15.519230769230774</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="48" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F18" s="49">
         <v>6</v>
@@ -11266,29 +11497,29 @@
       </c>
       <c r="H18" s="51">
         <f>B6/B3</f>
-        <v>0.39811320754716983</v>
+        <v>0.3952205882352941</v>
       </c>
       <c r="I18" s="52">
         <f>B3*G18</f>
-        <v>489.2307692307693</v>
+        <v>502.1538461538462</v>
       </c>
       <c r="J18" s="53">
         <f>B6</f>
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="K18" s="54">
         <f>J18-I18</f>
-        <v>-67.23076923076928</v>
+        <v>-72.15384615384619</v>
       </c>
       <c r="L18" s="23">
         <f>K18/4</f>
-        <v>-16.80769230769232</v>
+        <v>-18.038461538461547</v>
       </c>
       <c r="Q18" s="55"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="56" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="F19" s="57">
         <v>4</v>
@@ -11299,28 +11530,28 @@
       </c>
       <c r="H19" s="59">
         <f>B7/B3</f>
-        <v>0.42924528301886794</v>
+        <v>0.43106617647058826</v>
       </c>
       <c r="I19" s="60">
         <f>B3*G19</f>
-        <v>326.1538461538462</v>
+        <v>334.7692307692308</v>
       </c>
       <c r="J19" s="61">
         <f>B7</f>
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="K19" s="62">
         <f>J19-I19</f>
-        <v>128.8461538461538</v>
+        <v>134.23076923076923</v>
       </c>
       <c r="L19" s="23">
         <f>K19/4</f>
-        <v>32.21153846153845</v>
+        <v>33.55769230769231</v>
       </c>
     </row>
     <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E21" s="63" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="F21" s="63"/>
       <c r="G21" s="63"/>
@@ -11331,27 +11562,27 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G22" t="s">
+        <v>447</v>
+      </c>
+      <c r="H22" t="s">
+        <v>435</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>436</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>437</v>
+      </c>
+      <c r="K22" t="s">
         <v>438</v>
-      </c>
-      <c r="H22" t="s">
-        <v>426</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="K22" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E23" s="41" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F23" s="42">
         <v>3</v>
@@ -11362,24 +11593,24 @@
       </c>
       <c r="H23" s="44">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.17780172413793102</v>
+        <v>0.17819706498951782</v>
       </c>
       <c r="I23" s="45">
         <f>(B3-C8) *G23</f>
-        <v>214.15384615384616</v>
+        <v>220.15384615384616</v>
       </c>
       <c r="J23" s="46">
         <f>B4+B5-C4</f>
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K23" s="47">
         <f>J23-I23</f>
-        <v>-49.15384615384616</v>
+        <v>-50.15384615384616</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E24" s="48" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F24" s="49">
         <v>6</v>
@@ -11390,24 +11621,24 @@
       </c>
       <c r="H24" s="51">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.4353448275862069</v>
+        <v>0.4308176100628931</v>
       </c>
       <c r="I24" s="52">
         <f>(B3-C8)*G24</f>
-        <v>428.3076923076923</v>
+        <v>440.3076923076923</v>
       </c>
       <c r="J24" s="53">
         <f>B6-C6</f>
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="K24" s="54">
         <f>J24-I24</f>
-        <v>-12.30769230769232</v>
+        <v>-16.30769230769232</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E25" s="56" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="F25" s="57">
         <v>4</v>
@@ -11418,45 +11649,45 @@
       </c>
       <c r="H25" s="59">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.3739224137931034</v>
+        <v>0.37735849056603776</v>
       </c>
       <c r="I25" s="60">
         <f>(B3-C8)*G25</f>
-        <v>285.53846153846155</v>
+        <v>293.53846153846155</v>
       </c>
       <c r="J25" s="61">
         <f>B7-C7</f>
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="K25" s="62">
         <f>J25-I25</f>
-        <v>61.46153846153845</v>
+        <v>66.46153846153845</v>
       </c>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="64">
         <f>C8/B9</f>
-        <v>0.12452830188679245</v>
+        <v>0.12316176470588236</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="65">
         <f>C8</f>
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K26" s="5"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>1060</v>
+        <v>1088</v>
       </c>
       <c r="K28" s="66">
         <f>SUM(K23:K25)</f>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2801" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="463">
   <si>
     <t>sl</t>
   </si>
@@ -400,6 +400,9 @@
     <t>2025-02-01</t>
   </si>
   <si>
+    <t>2025-03-01</t>
+  </si>
+  <si>
     <t>2025-01-16</t>
   </si>
   <si>
@@ -445,12 +448,12 @@
     <t>2025-02-13</t>
   </si>
   <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
     <t>2025-01-28</t>
   </si>
   <si>
-    <t>zbrisano</t>
-  </si>
-  <si>
     <t>2025-01-18</t>
   </si>
   <si>
@@ -487,6 +490,9 @@
     <t>2025-02-05</t>
   </si>
   <si>
+    <t>2025-02-25</t>
+  </si>
+  <si>
     <t>HuberRe</t>
   </si>
   <si>
@@ -733,6 +739,15 @@
     <t>Eishalle Dornbirn;LazzeriAl;LegaSi;CusinFe;GrisentiLu</t>
   </si>
   <si>
+    <t>Eishalle Zell am See;BenvegnuAn;HlavatyAl;AbeltinoSi;LegatKo</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LesniakBo;SoraperraSi;ArlicMa;BrondiPa</t>
+  </si>
+  <si>
+    <t>Eishalle Sissek Zibel;VirtaTu;VoicanCh;FleischmannLu;WeissAl</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -886,19 +901,28 @@
     <t>KELIT Arena Zell am See;MeixnerSe;WidmannFl;TelesklavFa;WendnerMa</t>
   </si>
   <si>
-    <t>ZBRISANO</t>
+    <t>Eishalle Ritten;EggerTh;LazzeriAl;CristeliMa;GrisentiLu</t>
   </si>
   <si>
     <t>Eishalle Jesenice;HlavatyAl;LebenJa;PreiserJu;WeissAl</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;HolzerTo;VoicanCh;DivisDo;LegatKo</t>
+    <t>KELIT Arena Zell am See;HolzerTo;KainbergerJu;DivisDo;RinkerDa</t>
   </si>
   <si>
     <t>Eisarena Salzburg;HlavatyAl;WenuschHe;PreiserJu;WeissAl</t>
   </si>
   <si>
-    <t>Eishalle Celje;LebenJa;MetzingerFi;JavornikBl;KnezRo</t>
+    <t>Eishalle Celje;LebenJa;LesniakBo;JavornikBl;KnezRo</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;GiacomozziFe;RuetzMa;CristeliMa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;MoschenAn;WidmannFl;JägerRi;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BulovecMi;LazzeriAl;CristeliMa;JeramFi</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
@@ -1027,7 +1051,7 @@
     <t>Eishalle Dornbirn;HolzerTo;SpiegelSe;DivisDo;JägerRi</t>
   </si>
   <si>
-    <t>Eishalle Ritten;EggerTh;LazzeriAl;CristeliMa;GrisentiLu</t>
+    <t>Würtharena Neumarkt;PirasAn;VirtaTu;PaceJa;ScalzeriAl</t>
   </si>
   <si>
     <t>Eishalle Celje;BulovecMi;SnojTa;ArlicMa;JeramFi</t>
@@ -1042,6 +1066,12 @@
     <t>Eisarena Salzburg;HolzerTo;SpiegelSe;DivisDo;JägerRi</t>
   </si>
   <si>
+    <t>Eishalle Dornbirn;HolzerTo;KainbergerJu;SeewaldJe;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;PinieOm;PirasAn;RivisAn;ScalzeriAl</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -1153,13 +1183,13 @@
     <t>Eishalle Ritten;BenvegnuAn;SoraperraSi;FecchioFe;IlmerNo</t>
   </si>
   <si>
-    <t>Würtharena Neumarkt;PirasAn;VirtaTu;PaceJa;ScalzeriAl</t>
+    <t>Eishalle Sterzing;GiacomozziFe;PinieOm;BrondiPa;RivisAn</t>
   </si>
   <si>
     <t>Eishalle Sterzing;BenvegnuAn;StefenelliFe;FleischmannLu;IlmerNo</t>
   </si>
   <si>
-    <t>Eishalle Gröden;EggerTh;LazzeriAl;AbeltinoSi;CristeliMa</t>
+    <t>Eishalle Gröden;LazzeriAl;PinieOm;AbeltinoSi;CristeliMa</t>
   </si>
   <si>
     <t>Eishalle Sterzing;KainbergerJu;PinieOm;CristeliMa;StrimitzerDa</t>
@@ -1168,6 +1198,12 @@
     <t>Eishalle Dornbirn;Huber rRe;OrelSt;StrimitzerDa;WuchererGe</t>
   </si>
   <si>
+    <t>Eishalle Sterzing;HlavatyAl;VirtaTu;RinkerDa;WeissAl</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;BajtMi;LebenJa;DivisDo;StrimitzerDa</t>
+  </si>
+  <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
   </si>
   <si>
@@ -1246,7 +1282,7 @@
     <t>Eishalle Meran;LegaSi;StefenelliFe;CusinFe;FormaioniTh</t>
   </si>
   <si>
-    <t>Eishalle Sterzing;GiacomozziFe;PinieOm;BrondiPa;RivisAn</t>
+    <t>Sportpark Kitzbühel;MeixnerSe;RuetzMa;MoidlMa;StrimitzerDa</t>
   </si>
   <si>
     <t>Eishalle Gröden;LegaSi;SoraperraSi;FormaioniTh;PaceJa</t>
@@ -1255,10 +1291,16 @@
     <t>Eishalle Cortina;PirasAn;SnojTa;BrondiPa;JeramFi</t>
   </si>
   <si>
-    <t>Eishalle Ritten;VirtaTu;WidmannFl;BrondiPa;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Sportpark Kitzbühel;KainbergerJu;SnojTa;JeramFi;SeewaldJe</t>
+    <t>Eishalle Ritten;VirtaTu;WidmannFl;BrondiPa;WuchererGe</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;BulovecMi;KainbergerJu;JeramFi;SeewaldJe</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;BulovecMi;LazzeriAl;CristeliMa;JeramFi</t>
+  </si>
+  <si>
+    <t>Eishalle Gröden;HolzerTo;LehnerMo;MoidlMa;SeewaldJe</t>
   </si>
   <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
@@ -1288,13 +1330,10 @@
     <t>Eishalle Gröden;Huber rRe;MoschenAn;RinkerDa;StrimitzerDa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;MeixnerSe;RuetzMa;MoidlMa;StrimitzerDa</t>
-  </si>
-  <si>
     <t>Eishalle Cortina;LesniakBo;OrelSt;JavornikBl;TelesklavFa</t>
   </si>
   <si>
-    <t>Eishalle Meran;GiacomozziFe;SoraperraSi;IlmerNo;RivisAn</t>
+    <t>Eishalle Meran;GiacomozziFe;SoraperraSi;GrisentiLu;RivisAn</t>
   </si>
   <si>
     <t>Würtharena Neumarkt;BenvegnuAn;StefenelliFe;PaceJa;ScalzeriAl</t>
@@ -1880,7 +1919,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2212,7 +2259,7 @@
     <col min="52" max="52" width="11.140625" customWidth="1"/>
     <col min="53" max="53" width="11" customWidth="1"/>
     <col min="54" max="54" width="13.28515625" customWidth="1"/>
-    <col min="55" max="55" width="18.140625" customWidth="1"/>
+    <col min="55" max="55" width="12.5703125" customWidth="1"/>
     <col min="56" max="56" width="10.7109375" customWidth="1"/>
     <col min="57" max="57" width="10.140625" customWidth="1"/>
     <col min="58" max="58" width="11.7109375" customWidth="1"/>
@@ -2233,7 +2280,7 @@
     <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B64,"&lt;&gt;")</f>
@@ -2241,7 +2288,7 @@
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C67,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
@@ -2249,7 +2296,7 @@
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E66,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F67,"&lt;&gt;")</f>
@@ -2261,11 +2308,11 @@
       </c>
       <c r="H1">
         <f>COUNTIF(H4:H68,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I68,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J64,"&lt;&gt;")</f>
@@ -2273,7 +2320,7 @@
       </c>
       <c r="K1">
         <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L1">
         <f>COUNTIF(L4:L69,"&lt;&gt;")</f>
@@ -2285,7 +2332,7 @@
       </c>
       <c r="N1">
         <f>COUNTIF(N4:N65,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O1">
         <f>COUNTIF(O4:O66,"&lt;&gt;")</f>
@@ -2297,7 +2344,7 @@
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q66,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R1">
         <f>COUNTIF(R4:R63,"&lt;&gt;")</f>
@@ -2329,7 +2376,7 @@
       </c>
       <c r="Y1">
         <f>COUNTIF(Y4:Y68,"&lt;&gt;")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
@@ -2341,11 +2388,11 @@
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB65,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC1">
         <f>COUNTIF(AC4:AC68,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD66,"&lt;&gt;")</f>
@@ -2361,7 +2408,7 @@
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG65,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH65,"&lt;&gt;")</f>
@@ -2373,23 +2420,23 @@
       </c>
       <c r="AJ1">
         <f>COUNTIF(AJ4:AJ61,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK1">
         <f>COUNTIF(AK4:AK63,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL65,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM64,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN63,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
@@ -2413,11 +2460,11 @@
       </c>
       <c r="AT1">
         <f>COUNTIF(AT4:AT67,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU1">
         <f>COUNTIF(AU4:AU67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV64,"&lt;&gt;")</f>
@@ -2429,7 +2476,7 @@
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX65,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY60,"&lt;&gt;")</f>
@@ -2437,7 +2484,7 @@
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ64,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA1">
         <f>COUNTIF(BA4:BA69,"&lt;&gt;")</f>
@@ -2461,7 +2508,7 @@
       </c>
       <c r="BF1">
         <f>COUNTIF(BF4:BF68,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG1">
         <f>COUNTIF(BG4:BG61,"&lt;&gt;")</f>
@@ -2489,7 +2536,7 @@
       </c>
       <c r="BM1">
         <f>COUNTIF(BM4:BM67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
@@ -2501,7 +2548,7 @@
       </c>
       <c r="BP1">
         <f>COUNTIF(BP4:BP68,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BQ1">
         <f t="shared" si="1"/>
@@ -4184,6 +4231,9 @@
       <c r="W10" t="s">
         <v>88</v>
       </c>
+      <c r="X10" t="s">
+        <v>127</v>
+      </c>
       <c r="Y10" t="s">
         <v>87</v>
       </c>
@@ -4215,13 +4265,13 @@
         <v>115</v>
       </c>
       <c r="AI10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AJ10" t="s">
         <v>111</v>
       </c>
       <c r="AK10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL10" t="s">
         <v>95</v>
@@ -4281,16 +4331,16 @@
         <v>116</v>
       </c>
       <c r="BE10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BF10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BG10" t="s">
         <v>124</v>
       </c>
       <c r="BH10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BJ10" t="s">
         <v>104</v>
@@ -4305,7 +4355,7 @@
         <v>112</v>
       </c>
       <c r="BO10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BP10" t="s">
         <v>125</v>
@@ -4331,19 +4381,19 @@
         <v>94</v>
       </c>
       <c r="H11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I11" t="s">
         <v>92</v>
       </c>
       <c r="J11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K11" t="s">
         <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N11" t="s">
         <v>118</v>
@@ -4370,7 +4420,7 @@
         <v>95</v>
       </c>
       <c r="V11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="W11" t="s">
         <v>93</v>
@@ -4394,7 +4444,7 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AF11" t="s">
         <v>94</v>
@@ -4406,10 +4456,10 @@
         <v>100</v>
       </c>
       <c r="AI11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AJ11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4478,13 +4528,13 @@
         <v>126</v>
       </c>
       <c r="BG11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BH11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BJ11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BK11" t="s">
         <v>104</v>
@@ -4496,10 +4546,10 @@
         <v>121</v>
       </c>
       <c r="BO11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BP11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4513,7 +4563,7 @@
         <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
         <v>95</v>
@@ -4528,10 +4578,10 @@
         <v>112</v>
       </c>
       <c r="J12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L12" t="s">
         <v>112</v>
@@ -4597,7 +4647,7 @@
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AJ12" t="s">
         <v>92</v>
@@ -4606,7 +4656,7 @@
         <v>95</v>
       </c>
       <c r="AL12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4615,7 +4665,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4633,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AV12" t="s">
         <v>109</v>
@@ -4642,7 +4692,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4663,13 +4713,16 @@
         <v>103</v>
       </c>
       <c r="BE12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BF12" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>143</v>
       </c>
       <c r="BJ12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BK12" t="s">
         <v>120</v>
@@ -4681,7 +4734,7 @@
         <v>114</v>
       </c>
       <c r="BP12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
@@ -4710,7 +4763,7 @@
         <v>121</v>
       </c>
       <c r="J13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K13" t="s">
         <v>112</v>
@@ -4749,7 +4802,7 @@
         <v>115</v>
       </c>
       <c r="Y13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Z13" t="s">
         <v>106</v>
@@ -4782,13 +4835,13 @@
         <v>126</v>
       </c>
       <c r="AJ13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AK13" t="s">
         <v>109</v>
       </c>
       <c r="AL13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4809,7 +4862,7 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
@@ -4844,17 +4897,23 @@
       <c r="BD13" t="s">
         <v>121</v>
       </c>
+      <c r="BE13" t="s">
+        <v>143</v>
+      </c>
       <c r="BF13" t="s">
-        <v>143</v>
+        <v>127</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>127</v>
       </c>
       <c r="BK13" t="s">
         <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BN13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BP13" t="s">
         <v>126</v>
@@ -4868,7 +4927,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
         <v>117</v>
@@ -4877,7 +4936,7 @@
         <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H14" t="s">
         <v>120</v>
@@ -4889,10 +4948,10 @@
         <v>124</v>
       </c>
       <c r="K14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N14" t="s">
         <v>111</v>
@@ -4925,10 +4984,10 @@
         <v>106</v>
       </c>
       <c r="Y14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA14" t="s">
         <v>111</v>
@@ -4943,7 +5002,7 @@
         <v>112</v>
       </c>
       <c r="AE14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AF14" t="s">
         <v>111</v>
@@ -4952,10 +5011,10 @@
         <v>117</v>
       </c>
       <c r="AH14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AI14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -4973,19 +5032,19 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AP14" t="s">
         <v>120</v>
       </c>
       <c r="AQ14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AR14" t="s">
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
@@ -4994,7 +5053,7 @@
         <v>125</v>
       </c>
       <c r="AV14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AW14" t="s">
         <v>91</v>
@@ -5003,7 +5062,7 @@
         <v>92</v>
       </c>
       <c r="AY14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AZ14" t="s">
         <v>104</v>
@@ -5015,33 +5074,33 @@
         <v>123</v>
       </c>
       <c r="BC14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BD14" t="s">
         <v>125</v>
       </c>
       <c r="BK14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BM14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BN14" t="s">
         <v>119</v>
       </c>
       <c r="BP14" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -5050,25 +5109,25 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I15" t="s">
         <v>125</v>
       </c>
       <c r="J15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O15" t="s">
         <v>111</v>
@@ -5092,7 +5151,7 @@
         <v>100</v>
       </c>
       <c r="V15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="W15" t="s">
         <v>114</v>
@@ -5107,22 +5166,22 @@
         <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AC15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD15" t="s">
         <v>119</v>
       </c>
       <c r="AE15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AF15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH15" t="s">
         <v>92</v>
@@ -5131,28 +5190,28 @@
         <v>124</v>
       </c>
       <c r="AJ15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AL15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AO15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AP15" t="s">
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AR15" t="s">
         <v>104</v>
@@ -5164,7 +5223,7 @@
         <v>107</v>
       </c>
       <c r="AU15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AV15" t="s">
         <v>103</v>
@@ -5176,7 +5235,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -5191,27 +5250,27 @@
         <v>119</v>
       </c>
       <c r="BD15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BK15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BM15" t="s">
         <v>122</v>
       </c>
       <c r="BN15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D16" t="s">
         <v>120</v>
@@ -5220,22 +5279,22 @@
         <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I16" t="s">
+        <v>138</v>
+      </c>
+      <c r="K16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" t="s">
+        <v>135</v>
+      </c>
+      <c r="N16" t="s">
         <v>134</v>
-      </c>
-      <c r="I16" t="s">
-        <v>137</v>
-      </c>
-      <c r="K16" t="s">
-        <v>134</v>
-      </c>
-      <c r="L16" t="s">
-        <v>134</v>
-      </c>
-      <c r="N16" t="s">
-        <v>133</v>
       </c>
       <c r="O16" t="s">
         <v>120</v>
@@ -5253,20 +5312,17 @@
         <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U16" t="s">
         <v>104</v>
       </c>
       <c r="V16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W16" t="s">
         <v>104</v>
       </c>
-      <c r="Y16" t="s">
-        <v>140</v>
-      </c>
       <c r="Z16" t="s">
         <v>111</v>
       </c>
@@ -5274,49 +5330,49 @@
         <v>120</v>
       </c>
       <c r="AB16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC16" t="s">
         <v>92</v>
       </c>
       <c r="AD16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE16" t="s">
         <v>119</v>
       </c>
       <c r="AF16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AH16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AJ16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK16" t="s">
         <v>120</v>
       </c>
       <c r="AL16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AM16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AO16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AQ16" t="s">
         <v>125</v>
@@ -5325,66 +5381,66 @@
         <v>112</v>
       </c>
       <c r="AS16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AT16" t="s">
         <v>104</v>
       </c>
       <c r="AU16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AV16" t="s">
         <v>125</v>
       </c>
       <c r="AW16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AX16" t="s">
         <v>121</v>
       </c>
       <c r="AY16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AZ16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BA16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
       </c>
       <c r="BC16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BD16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BK16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BM16" t="s">
         <v>124</v>
       </c>
       <c r="BN16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
         <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17" t="s">
         <v>124</v>
@@ -5393,7 +5449,7 @@
         <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K17" t="s">
         <v>126</v>
@@ -5402,10 +5458,10 @@
         <v>120</v>
       </c>
       <c r="N17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P17" t="s">
         <v>120</v>
@@ -5414,19 +5470,19 @@
         <v>111</v>
       </c>
       <c r="R17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
       </c>
       <c r="T17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U17" t="s">
         <v>103</v>
       </c>
       <c r="V17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="W17" t="s">
         <v>109</v>
@@ -5435,58 +5491,58 @@
         <v>120</v>
       </c>
       <c r="AA17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AC17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AD17" t="s">
         <v>122</v>
       </c>
       <c r="AE17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AF17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s">
         <v>122</v>
       </c>
       <c r="AH17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL17" t="s">
         <v>137</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>141</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>135</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>136</v>
-      </c>
       <c r="AM17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AN17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AO17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AP17" t="s">
         <v>119</v>
       </c>
       <c r="AQ17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AR17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AS17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
@@ -5495,7 +5551,7 @@
         <v>122</v>
       </c>
       <c r="AV17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AW17" t="s">
         <v>94</v>
@@ -5504,28 +5560,28 @@
         <v>120</v>
       </c>
       <c r="AY17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ17" t="s">
         <v>120</v>
       </c>
       <c r="BA17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BB17" t="s">
         <v>121</v>
       </c>
       <c r="BC17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BD17" t="s">
         <v>119</v>
       </c>
       <c r="BK17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BM17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
@@ -5533,37 +5589,37 @@
         <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
         <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H18" t="s">
         <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P18" t="s">
         <v>121</v>
@@ -5578,147 +5634,150 @@
         <v>112</v>
       </c>
       <c r="T18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
       <c r="V18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="W18" t="s">
         <v>111</v>
       </c>
       <c r="Z18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AC18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AD18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF18" t="s">
         <v>126</v>
       </c>
       <c r="AG18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH18" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AK18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AN18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO18" t="s">
         <v>119</v>
       </c>
       <c r="AP18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
       <c r="AS18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AT18" t="s">
         <v>121</v>
       </c>
       <c r="AU18" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="AV18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AW18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AX18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AY18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ18" t="s">
+        <v>147</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>147</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>139</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>141</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>141</v>
+      </c>
+      <c r="BK18" t="s">
         <v>146</v>
       </c>
-      <c r="BA18" t="s">
-        <v>146</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>138</v>
-      </c>
-      <c r="BC18" t="s">
-        <v>140</v>
-      </c>
-      <c r="BD18" t="s">
-        <v>140</v>
-      </c>
-      <c r="BK18" t="s">
-        <v>145</v>
+      <c r="BM18" t="s">
+        <v>157</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
         <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
         <v>119</v>
       </c>
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" t="s">
+        <v>149</v>
+      </c>
       <c r="I19" t="s">
         <v>126</v>
       </c>
-      <c r="K19" t="s">
-        <v>148</v>
-      </c>
       <c r="L19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S19" t="s">
         <v>121</v>
@@ -5730,13 +5789,13 @@
         <v>120</v>
       </c>
       <c r="V19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="W19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA19" t="s">
         <v>122</v>
@@ -5748,10 +5807,10 @@
         <v>119</v>
       </c>
       <c r="AD19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AF19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s">
         <v>124</v>
@@ -5760,81 +5819,93 @@
         <v>126</v>
       </c>
       <c r="AK19" t="s">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>141</v>
       </c>
       <c r="AM19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AN19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AO19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AP19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AQ19" t="s">
+        <v>141</v>
+      </c>
+      <c r="AR19" t="s">
         <v>140</v>
       </c>
-      <c r="AR19" t="s">
-        <v>139</v>
-      </c>
       <c r="AS19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AT19" t="s">
         <v>120</v>
       </c>
       <c r="AV19" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AW19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>135</v>
+      </c>
+      <c r="AY19" t="s">
         <v>137</v>
       </c>
-      <c r="AX19" t="s">
-        <v>134</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>136</v>
-      </c>
       <c r="AZ19" t="s">
+        <v>138</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>138</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>150</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>149</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK19" t="s">
         <v>137</v>
       </c>
-      <c r="BA19" t="s">
+      <c r="BM19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" t="s">
         <v>137</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>149</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>148</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>148</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" t="s">
-        <v>136</v>
       </c>
       <c r="D20" t="s">
         <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="H20" t="s">
+        <v>143</v>
       </c>
       <c r="I20" t="s">
         <v>124</v>
       </c>
       <c r="L20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N20" t="s">
         <v>124</v>
@@ -5843,19 +5914,19 @@
         <v>124</v>
       </c>
       <c r="P20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q20" t="s">
         <v>122</v>
       </c>
       <c r="R20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S20" t="s">
         <v>94</v>
       </c>
       <c r="T20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U20" t="s">
         <v>109</v>
@@ -5864,55 +5935,61 @@
         <v>119</v>
       </c>
       <c r="W20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z20" t="s">
         <v>119</v>
       </c>
       <c r="AA20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AB20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC20" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH20" t="s">
         <v>142</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>153</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>141</v>
       </c>
       <c r="AK20" t="s">
         <v>122</v>
       </c>
+      <c r="AL20" t="s">
+        <v>143</v>
+      </c>
       <c r="AM20" t="s">
         <v>126</v>
       </c>
       <c r="AN20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AO20" t="s">
         <v>126</v>
       </c>
       <c r="AP20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AQ20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AR20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AS20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AW20" t="s">
         <v>122</v>
@@ -5920,103 +5997,112 @@
       <c r="AX20" t="s">
         <v>119</v>
       </c>
+      <c r="AY20" t="s">
+        <v>143</v>
+      </c>
       <c r="AZ20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BA20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BB20" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>143</v>
       </c>
       <c r="BK20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
       <c r="D21" t="s">
         <v>124</v>
       </c>
-      <c r="E21" t="s">
-        <v>143</v>
-      </c>
       <c r="I21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R21" t="s">
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T21" t="s">
         <v>124</v>
       </c>
       <c r="U21" t="s">
+        <v>138</v>
+      </c>
+      <c r="V21" t="s">
+        <v>153</v>
+      </c>
+      <c r="W21" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA21" t="s">
         <v>137</v>
       </c>
-      <c r="V21" t="s">
-        <v>152</v>
-      </c>
-      <c r="W21" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>136</v>
-      </c>
       <c r="AB21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC21" t="s">
         <v>124</v>
       </c>
+      <c r="AG21" t="s">
+        <v>141</v>
+      </c>
       <c r="AH21" t="s">
         <v>124</v>
       </c>
       <c r="AK21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AM21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AN21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AO21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AP21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AR21" t="s">
         <v>120</v>
       </c>
       <c r="AT21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AW21" t="s">
         <v>124</v>
       </c>
       <c r="AX21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ21" t="s">
         <v>126</v>
@@ -6025,230 +6111,327 @@
         <v>119</v>
       </c>
       <c r="BB21" t="s">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>127</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>143</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="C22" t="s">
+        <v>143</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I22" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="N22" t="s">
+        <v>157</v>
+      </c>
+      <c r="O22" t="s">
+        <v>143</v>
       </c>
       <c r="P22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R22" t="s">
         <v>122</v>
       </c>
       <c r="S22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="V22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Z22" t="s">
         <v>124</v>
       </c>
+      <c r="AA22" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>157</v>
+      </c>
       <c r="AC22" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>127</v>
       </c>
       <c r="AH22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AM22" t="s">
         <v>124</v>
       </c>
       <c r="AN22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AO22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AR22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AT22" t="s">
         <v>119</v>
       </c>
       <c r="AW22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AX22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AZ22" t="s">
+        <v>146</v>
+      </c>
+      <c r="BA22" t="s">
         <v>145</v>
       </c>
-      <c r="BA22" t="s">
-        <v>144</v>
-      </c>
       <c r="BB22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>148</v>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" t="s">
+        <v>143</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U23" t="s">
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="W23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Z23" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>157</v>
       </c>
       <c r="AK23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AM23" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AN23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AO23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AR23" t="s">
         <v>126</v>
       </c>
       <c r="AT23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AX23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AZ23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BA23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BB23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+      <c r="I24" t="s">
+        <v>143</v>
+      </c>
       <c r="P24" t="s">
         <v>124</v>
       </c>
+      <c r="Q24" t="s">
+        <v>141</v>
+      </c>
       <c r="R24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="S24" t="s">
         <v>122</v>
       </c>
       <c r="U24" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="V24" t="s">
+        <v>127</v>
+      </c>
+      <c r="W24" t="s">
+        <v>143</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>157</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>137</v>
       </c>
       <c r="AO24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AR24" t="s">
         <v>124</v>
       </c>
       <c r="AT24" t="s">
+        <v>142</v>
+      </c>
+      <c r="AX24" t="s">
         <v>141</v>
       </c>
       <c r="AZ24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BA24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BB24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>127</v>
+      </c>
       <c r="P25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U25" t="s">
         <v>124</v>
       </c>
+      <c r="W25" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>143</v>
+      </c>
       <c r="AR25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT25" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>143</v>
       </c>
       <c r="AZ25" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA25" t="s">
+        <v>149</v>
+      </c>
+      <c r="BB25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
+      <c r="R26" t="s">
+        <v>154</v>
+      </c>
+      <c r="S26" t="s">
         <v>141</v>
       </c>
-      <c r="BA25" t="s">
-        <v>148</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>148</v>
+      <c r="U26" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>127</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ26" t="s">
+        <v>157</v>
+      </c>
+      <c r="BA26" t="s">
+        <v>143</v>
+      </c>
+      <c r="BB26" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="16:54" x14ac:dyDescent="0.25">
-      <c r="R26" t="s">
-        <v>153</v>
-      </c>
-      <c r="S26" t="s">
-        <v>140</v>
-      </c>
-      <c r="U26" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT26" t="s">
-        <v>148</v>
+    <row r="27" ht="15" customHeight="1" spans="18:54" x14ac:dyDescent="0.25">
+      <c r="R27" t="s">
+        <v>143</v>
+      </c>
+      <c r="S27" t="s">
+        <v>137</v>
+      </c>
+      <c r="U27" t="s">
+        <v>143</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>157</v>
+      </c>
+      <c r="AZ27" t="s">
+        <v>127</v>
+      </c>
+      <c r="BA27" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="18:46" x14ac:dyDescent="0.25">
-      <c r="S27" t="s">
-        <v>136</v>
+    <row r="28" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+      <c r="R28" t="s">
+        <v>127</v>
+      </c>
+      <c r="S28" t="s">
+        <v>143</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="19:19" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15" customHeight="1" spans="18:19" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6294,6 +6477,11 @@
     <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="A4:XFD27">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>A4 &gt; "2025-02-10"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
@@ -6301,7 +6489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CD42"/>
+  <dimension ref="A3:CG42"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -6313,6 +6501,7 @@
     <col min="8" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" customWidth="1"/>
     <col min="13" max="13" width="19.5703125" customWidth="1"/>
     <col min="14" max="14" width="20.42578125" customWidth="1"/>
     <col min="16" max="16" width="20.28515625" customWidth="1"/>
@@ -6349,7 +6538,7 @@
     <col min="83" max="83" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -6447,7 +6636,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -6474,10 +6663,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AQ3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -6501,70 +6690,70 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
       </c>
       <c r="BA3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BC3" t="s">
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BE3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BF3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BG3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
       </c>
       <c r="BI3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BJ3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BL3" t="s">
         <v>130</v>
       </c>
-      <c r="BK3" t="s">
-        <v>137</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>129</v>
-      </c>
       <c r="BM3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BO3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BP3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BQ3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BR3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
       </c>
       <c r="BT3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BU3" t="s">
         <v>122</v>
@@ -6573,31 +6762,40 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BX3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BY3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="CB3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CC3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CD3" t="s">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>157</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>143</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -6844,8 +7042,17 @@
       <c r="CD4" t="s">
         <v>21</v>
       </c>
+      <c r="CE4" t="s">
+        <v>17</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7092,8 +7299,17 @@
       <c r="CD5" t="s">
         <v>38</v>
       </c>
+      <c r="CE5" t="s">
+        <v>68</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>18</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -7340,8 +7556,17 @@
       <c r="CD6" t="s">
         <v>35</v>
       </c>
+      <c r="CE6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -7588,13 +7813,22 @@
       <c r="CD7" t="s">
         <v>20</v>
       </c>
+      <c r="CE7" t="s">
+        <v>51</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>22</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -7618,7 +7852,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -7758,8 +7992,17 @@
       <c r="CC8" t="s">
         <v>9</v>
       </c>
+      <c r="CE8" t="s">
+        <v>31</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>24</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -7773,7 +8016,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -7920,16 +8163,25 @@
         <v>9</v>
       </c>
       <c r="CA9" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="CB9" t="s">
         <v>63</v>
       </c>
       <c r="CC9" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>49</v>
+      </c>
+      <c r="CF9" t="s">
+        <v>54</v>
+      </c>
+      <c r="CG9" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -8098,8 +8350,17 @@
       <c r="CC10" t="s">
         <v>13</v>
       </c>
+      <c r="CE10" t="s">
+        <v>40</v>
+      </c>
+      <c r="CF10" t="s">
+        <v>66</v>
+      </c>
+      <c r="CG10" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -8260,7 +8521,7 @@
         <v>62</v>
       </c>
       <c r="CA11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="CB11" t="s">
         <v>62</v>
@@ -8268,8 +8529,17 @@
       <c r="CC11" t="s">
         <v>15</v>
       </c>
+      <c r="CE11" t="s">
+        <v>55</v>
+      </c>
+      <c r="CF11" t="s">
+        <v>42</v>
+      </c>
+      <c r="CG11" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -8295,7 +8565,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -8411,8 +8681,14 @@
       <c r="CC12" t="s">
         <v>56</v>
       </c>
+      <c r="CF12" t="s">
+        <v>56</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -8554,8 +8830,14 @@
       <c r="CC13" t="s">
         <v>45</v>
       </c>
+      <c r="CF13" t="s">
+        <v>41</v>
+      </c>
+      <c r="CG13" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -8697,8 +8979,14 @@
       <c r="CC14" t="s">
         <v>57</v>
       </c>
+      <c r="CF14" t="s">
+        <v>59</v>
+      </c>
+      <c r="CG14" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -8840,8 +9128,14 @@
       <c r="CC15" t="s">
         <v>66</v>
       </c>
+      <c r="CF15" t="s">
+        <v>60</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -8963,7 +9257,7 @@
         <v>17</v>
       </c>
       <c r="CA16" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="CB16" t="s">
         <v>41</v>
@@ -8971,8 +9265,14 @@
       <c r="CC16" t="s">
         <v>44</v>
       </c>
+      <c r="CF16" t="s">
+        <v>68</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -9094,7 +9394,7 @@
         <v>29</v>
       </c>
       <c r="CA17" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="CB17" t="s">
         <v>36</v>
@@ -9102,8 +9402,14 @@
       <c r="CC17" t="s">
         <v>47</v>
       </c>
+      <c r="CF17" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG17" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -9233,8 +9539,14 @@
       <c r="CC18" t="s">
         <v>55</v>
       </c>
+      <c r="CF18" t="s">
+        <v>53</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -9364,8 +9676,14 @@
       <c r="CC19" t="s">
         <v>43</v>
       </c>
+      <c r="CF19" t="s">
+        <v>62</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -9457,10 +9775,16 @@
         <v>26</v>
       </c>
       <c r="CC20" t="s">
-        <v>41</v>
+        <v>6</v>
+      </c>
+      <c r="CF20" t="s">
+        <v>6</v>
+      </c>
+      <c r="CG20" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -9552,10 +9876,16 @@
         <v>54</v>
       </c>
       <c r="CC21" t="s">
-        <v>4</v>
+        <v>41</v>
+      </c>
+      <c r="CF21" t="s">
+        <v>21</v>
+      </c>
+      <c r="CG21" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -9649,8 +9979,14 @@
       <c r="CC22" t="s">
         <v>12</v>
       </c>
+      <c r="CF22" t="s">
+        <v>40</v>
+      </c>
+      <c r="CG22" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -9739,13 +10075,19 @@
         <v>12</v>
       </c>
       <c r="CB23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CC23" t="s">
         <v>59</v>
       </c>
+      <c r="CF23" t="s">
+        <v>12</v>
+      </c>
+      <c r="CG23" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="7:85" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -9859,7 +10201,7 @@
         <v>13</v>
       </c>
       <c r="CA26" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="CB26" t="s">
         <v>37</v>
@@ -9909,7 +10251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="79:81" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9931,7 +10273,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CD14"/>
+  <dimension ref="A3:CG14"/>
   <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
@@ -10019,7 +10361,7 @@
     <col min="101" max="101" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -10117,7 +10459,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -10144,10 +10486,10 @@
         <v>94</v>
       </c>
       <c r="AP3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AQ3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AR3" t="s">
         <v>117</v>
@@ -10171,70 +10513,70 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
       </c>
       <c r="BA3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BB3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BC3" t="s">
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BE3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BF3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BG3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
       </c>
       <c r="BI3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BJ3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BL3" t="s">
         <v>130</v>
       </c>
-      <c r="BK3" t="s">
-        <v>137</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>129</v>
-      </c>
       <c r="BM3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BN3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BO3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BP3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BQ3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BR3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
       </c>
       <c r="BT3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BU3" t="s">
         <v>122</v>
@@ -10243,862 +10585,904 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BX3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BY3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="CB3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CC3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CD3" t="s">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>157</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>143</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="R4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="S4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="T4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="U4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="V4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="W4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="X4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Y4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Z4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AA4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AB4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AC4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AD4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AE4" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>194</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>196</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>198</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AP4" t="s">
         <v>187</v>
       </c>
-      <c r="AF4" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>189</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>191</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>192</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>194</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>195</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>197</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>185</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AR4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AS4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AT4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AU4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AV4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AW4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AX4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AY4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AZ4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="BA4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BB4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="BC4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BD4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="BE4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BF4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BG4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BH4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BI4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BJ4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="BK4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="BL4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="BM4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="BN4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BO4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BP4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BQ4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BR4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BS4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BT4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="BU4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BV4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="BW4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="BX4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="BY4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BZ4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="CA4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="CB4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="CC4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="CD4" t="s">
-        <v>237</v>
+        <v>239</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>240</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>241</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>242</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:82" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F5" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G5" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K5" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="L5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="N5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="P5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="R5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="T5" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="U5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="V5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="W5" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Y5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Z5" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AB5" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AD5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AE5" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AF5" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AI5" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AK5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AL5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AM5" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AN5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AO5" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AR5" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AS5" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AT5" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AU5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AV5" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AW5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AX5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AZ5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="BA5" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="BB5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="BC5" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="BG5" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="BH5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="BJ5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="BK5" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="BM5" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="BN5" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="BO5" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="BP5" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="BQ5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="BS5" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="BT5" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="BU5" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="BV5" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="BX5" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="BY5" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="BZ5" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="CA5" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="CB5" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="CC5" t="s">
-        <v>293</v>
+        <v>298</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>299</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>300</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>301</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D6" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="F6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="G6" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H6" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="K6" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="L6" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="N6" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="P6" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="T6" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="V6" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="W6" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="Y6" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="Z6" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="AB6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AD6" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AE6" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AI6" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AK6" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="AM6" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="AN6" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AO6" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="AS6" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AT6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AU6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AV6" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AW6" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AX6" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="AZ6" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="BA6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="BB6" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="BC6" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="BG6" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="BJ6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="BK6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="BM6" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="BN6" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="BP6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="BS6" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="BU6" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="BV6" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="BX6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="BY6" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="BZ6" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="CA6" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="CB6" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="CC6" t="s">
-        <v>340</v>
+        <v>348</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>349</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>350</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="F7" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="G7" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="H7" t="s">
+        <v>355</v>
+      </c>
+      <c r="K7" t="s">
+        <v>356</v>
+      </c>
+      <c r="L7" t="s">
+        <v>357</v>
+      </c>
+      <c r="N7" t="s">
         <v>345</v>
       </c>
-      <c r="K7" t="s">
-        <v>346</v>
-      </c>
-      <c r="L7" t="s">
-        <v>347</v>
-      </c>
-      <c r="N7" t="s">
-        <v>337</v>
-      </c>
       <c r="P7" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="T7" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="V7" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="W7" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="Y7" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="Z7" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="AB7" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="AD7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="AE7" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AI7" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AK7" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AM7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="AN7" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AO7" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="AS7" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="AT7" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="AU7" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="AV7" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AW7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AX7" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AZ7" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="BC7" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="BG7" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="BJ7" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="BK7" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="BM7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="BN7" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="BS7" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="BV7" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="BX7" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="BY7" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="BZ7" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="CA7" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="CB7" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="CC7" t="s">
-        <v>382</v>
+        <v>392</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>393</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>394</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:81" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="D8" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="F8" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="G8" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="H8" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="K8" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="L8" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="V8" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="W8" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="Y8" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="AB8" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="AD8" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="AE8" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="AI8" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AK8" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="AM8" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="AO8" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="AT8" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="AU8" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="AW8" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="AZ8" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="BC8" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="BK8" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="BM8" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="BS8" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="BX8" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="BY8" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="BZ8" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="CA8" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="CB8" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="CC8" t="s">
-        <v>413</v>
+        <v>425</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>426</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>427</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="7:85" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="L9" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="AD9" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="AE9" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="AK9" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="AT9" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="BC9" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="BK9" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="BX9" t="s">
-        <v>422</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="BZ9" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="CA9" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="CB9" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="CC9" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="79:81" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11132,34 +11516,34 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="11">
         <f>C1*4</f>
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B3" s="13">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -11167,39 +11551,39 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="B4" s="16">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4">
         <f>AHL!I1</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="F4" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="G4" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="H4" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="I4" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J4" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="K4" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="L4" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11208,10 +11592,10 @@
       </c>
       <c r="B5" s="16">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="F5" s="18">
         <v>2</v>
@@ -11222,23 +11606,23 @@
       </c>
       <c r="H5" s="20">
         <f>B4/B3</f>
-        <v>0.14246323529411764</v>
+        <v>0.14233576642335766</v>
       </c>
       <c r="I5" s="21">
         <f>C2*G5</f>
-        <v>168</v>
+        <v>168.6153846153846</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K5" s="22">
         <f>J5-I5</f>
-        <v>-13</v>
+        <v>-12.615384615384613</v>
       </c>
       <c r="L5" s="23">
         <f>K5/4</f>
-        <v>-3.25</v>
+        <v>-3.1538461538461533</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11247,7 +11631,7 @@
       </c>
       <c r="B6" s="16">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C6">
         <f>AHL!X1</f>
@@ -11265,23 +11649,23 @@
       </c>
       <c r="H6" s="20">
         <f>B5/B3</f>
-        <v>0.03125</v>
+        <v>0.030109489051094892</v>
       </c>
       <c r="I6" s="21">
         <f>C2*G6</f>
-        <v>84</v>
+        <v>84.3076923076923</v>
       </c>
       <c r="J6">
         <f>B5</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" s="22">
         <f>J6-I6</f>
-        <v>-50</v>
+        <v>-51.30769230769231</v>
       </c>
       <c r="L6" s="23">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-12.5</v>
+        <v>-12.826923076923077</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11290,14 +11674,14 @@
       </c>
       <c r="B7" s="25">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C7">
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
         <v>109</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F7" s="27">
         <v>3</v>
@@ -11308,11 +11692,11 @@
       </c>
       <c r="H7" s="29">
         <f>(B5+B4)/B3</f>
-        <v>0.17371323529411764</v>
+        <v>0.17244525547445255</v>
       </c>
       <c r="I7" s="21">
         <f>C2*G7</f>
-        <v>252</v>
+        <v>252.92307692307693</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
@@ -11320,23 +11704,23 @@
       </c>
       <c r="K7" s="22">
         <f>J7-I7</f>
-        <v>-63</v>
+        <v>-63.923076923076934</v>
       </c>
       <c r="L7" s="23">
         <f>K7/4</f>
-        <v>-15.75</v>
+        <v>-15.980769230769234</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F8" s="32">
         <v>6</v>
@@ -11347,35 +11731,35 @@
       </c>
       <c r="H8" s="34">
         <f>B6/B3</f>
-        <v>0.3952205882352941</v>
+        <v>0.3978102189781022</v>
       </c>
       <c r="I8" s="21">
         <f>C2*G8</f>
-        <v>504</v>
+        <v>505.84615384615387</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K8" s="22">
         <f>J8-I8</f>
-        <v>-74</v>
+        <v>-69.84615384615387</v>
       </c>
       <c r="L8" s="23">
         <f>K8/4</f>
-        <v>-18.5</v>
+        <v>-17.461538461538467</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="F9" s="32">
         <v>4</v>
@@ -11386,75 +11770,75 @@
       </c>
       <c r="H9" s="34">
         <f>B7/B3</f>
-        <v>0.43106617647058826</v>
+        <v>0.42974452554744524</v>
       </c>
       <c r="I9" s="21">
         <f>C2*G9</f>
-        <v>336</v>
+        <v>337.2307692307692</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K9" s="35">
         <f>J9-I9</f>
-        <v>133</v>
+        <v>133.76923076923077</v>
       </c>
       <c r="L9" s="23">
         <f>K9/4</f>
-        <v>33.25</v>
+        <v>33.44230769230769</v>
       </c>
     </row>
     <row r="11" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H11" s="36" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="I11" s="37">
         <f>SUM(I7:I9)</f>
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="J11" s="31">
         <f>SUM(J7:J9)</f>
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="K11" s="38">
         <f>SUM(K7:K9)</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="39">
         <f>SUM(L7:L9)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>459</v>
+      </c>
+      <c r="F16" t="s">
         <v>446</v>
       </c>
-      <c r="F16" t="s">
-        <v>433</v>
-      </c>
       <c r="G16" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="H16" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J16" s="40" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="K16" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="L16" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="41" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F17" s="42">
         <v>3</v>
@@ -11465,11 +11849,11 @@
       </c>
       <c r="H17" s="44">
         <f>(B5+B4)/B3</f>
-        <v>0.17371323529411764</v>
+        <v>0.17244525547445255</v>
       </c>
       <c r="I17" s="45">
         <f>B3*G17</f>
-        <v>251.0769230769231</v>
+        <v>252.92307692307693</v>
       </c>
       <c r="J17" s="46">
         <f>B5+B4</f>
@@ -11477,16 +11861,16 @@
       </c>
       <c r="K17" s="47">
         <f>J17-I17</f>
-        <v>-62.076923076923094</v>
+        <v>-63.923076923076934</v>
       </c>
       <c r="L17" s="23">
         <f>K17/4</f>
-        <v>-15.519230769230774</v>
+        <v>-15.980769230769234</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="48" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F18" s="49">
         <v>6</v>
@@ -11497,29 +11881,29 @@
       </c>
       <c r="H18" s="51">
         <f>B6/B3</f>
-        <v>0.3952205882352941</v>
+        <v>0.3978102189781022</v>
       </c>
       <c r="I18" s="52">
         <f>B3*G18</f>
-        <v>502.1538461538462</v>
+        <v>505.84615384615387</v>
       </c>
       <c r="J18" s="53">
         <f>B6</f>
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="K18" s="54">
         <f>J18-I18</f>
-        <v>-72.15384615384619</v>
+        <v>-69.84615384615387</v>
       </c>
       <c r="L18" s="23">
         <f>K18/4</f>
-        <v>-18.038461538461547</v>
+        <v>-17.461538461538467</v>
       </c>
       <c r="Q18" s="55"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="56" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="F19" s="57">
         <v>4</v>
@@ -11530,28 +11914,28 @@
       </c>
       <c r="H19" s="59">
         <f>B7/B3</f>
-        <v>0.43106617647058826</v>
+        <v>0.42974452554744524</v>
       </c>
       <c r="I19" s="60">
         <f>B3*G19</f>
-        <v>334.7692307692308</v>
+        <v>337.2307692307692</v>
       </c>
       <c r="J19" s="61">
         <f>B7</f>
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K19" s="62">
         <f>J19-I19</f>
-        <v>134.23076923076923</v>
+        <v>133.76923076923077</v>
       </c>
       <c r="L19" s="23">
         <f>K19/4</f>
-        <v>33.55769230769231</v>
+        <v>33.44230769230769</v>
       </c>
     </row>
     <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E21" s="63" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="F21" s="63"/>
       <c r="G21" s="63"/>
@@ -11562,27 +11946,27 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="G22" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="H22" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="I22" s="40" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J22" s="40" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="K22" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E23" s="41" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F23" s="42">
         <v>3</v>
@@ -11593,24 +11977,24 @@
       </c>
       <c r="H23" s="44">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.17819706498951782</v>
+        <v>0.17585848074921956</v>
       </c>
       <c r="I23" s="45">
         <f>(B3-C8) *G23</f>
-        <v>220.15384615384616</v>
+        <v>221.76923076923077</v>
       </c>
       <c r="J23" s="46">
         <f>B4+B5-C4</f>
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K23" s="47">
         <f>J23-I23</f>
-        <v>-50.15384615384616</v>
+        <v>-52.769230769230774</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E24" s="48" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="F24" s="49">
         <v>6</v>
@@ -11621,24 +12005,24 @@
       </c>
       <c r="H24" s="51">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.4308176100628931</v>
+        <v>0.4328824141519251</v>
       </c>
       <c r="I24" s="52">
         <f>(B3-C8)*G24</f>
-        <v>440.3076923076923</v>
+        <v>443.53846153846155</v>
       </c>
       <c r="J24" s="53">
         <f>B6-C6</f>
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="K24" s="54">
         <f>J24-I24</f>
-        <v>-16.30769230769232</v>
+        <v>-13.538461538461547</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E25" s="56" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="F25" s="57">
         <v>4</v>
@@ -11649,45 +12033,45 @@
       </c>
       <c r="H25" s="59">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.37735849056603776</v>
+        <v>0.37669094693028093</v>
       </c>
       <c r="I25" s="60">
         <f>(B3-C8)*G25</f>
-        <v>293.53846153846155</v>
+        <v>295.69230769230774</v>
       </c>
       <c r="J25" s="61">
         <f>B7-C7</f>
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K25" s="62">
         <f>J25-I25</f>
-        <v>66.46153846153845</v>
+        <v>66.30769230769226</v>
       </c>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="64">
         <f>C8/B9</f>
-        <v>0.12316176470588236</v>
+        <v>0.12317518248175183</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="65">
         <f>C8</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K26" s="5"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="K28" s="66">
         <f>SUM(K23:K25)</f>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5152A42A-A9F8-4371-8C1F-7C6A0DF1BA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
+    <sheet name="AHL" sheetId="1" r:id="rId1"/>
+    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
+    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2911" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="468">
   <si>
     <t>sl</t>
   </si>
@@ -424,6 +438,9 @@
     <t>2025-01-05</t>
   </si>
   <si>
+    <t>2025-03-04</t>
+  </si>
+  <si>
     <t>2025-01-23</t>
   </si>
   <si>
@@ -745,7 +762,10 @@
     <t>Eishalle Jesenice;LesniakBo;SoraperraSi;ArlicMa;BrondiPa</t>
   </si>
   <si>
-    <t>Eishalle Sissek Zibel;VirtaTu;VoicanCh;FleischmannLu;WeissAl</t>
+    <t>Eishalle Sissek Zibel;KainbergerJu;VoicanCh;MoidlMa;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;OrelSt;SnojTa;MarkizetiGr;WuchererGe</t>
   </si>
   <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
@@ -919,10 +939,13 @@
     <t>Eishalle Cortina;GiacomozziFe;RuetzMa;CristeliMa;StrimitzerDa</t>
   </si>
   <si>
-    <t>Sportpark Kitzbühel;MoschenAn;WidmannFl;JägerRi;TelesklavFa</t>
-  </si>
-  <si>
-    <t>Eishalle Celje;BulovecMi;LazzeriAl;CristeliMa;JeramFi</t>
+    <t>Sportpark Kitzbühel;MoschenAn;WidmannFl;FecchioFe;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Celje;BulovecMi;LazzeriAl;JeramFi;MarkizetiGr</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;RivisFe;StefenelliFe;FormaioniTh;PaceJa</t>
   </si>
   <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
@@ -1072,6 +1095,9 @@
     <t>Eishalle Ritten;PinieOm;PirasAn;RivisAn;ScalzeriAl</t>
   </si>
   <si>
+    <t>Eishalle Dornbirn;BrockAd;LazzeriAl;FleischmannLu;ZacherlPa</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -1201,7 +1227,10 @@
     <t>Eishalle Sterzing;HlavatyAl;VirtaTu;RinkerDa;WeissAl</t>
   </si>
   <si>
-    <t>KELIT Arena Zell am See;BajtMi;LebenJa;DivisDo;StrimitzerDa</t>
+    <t>KELIT Arena Zell am See;BajtMi;LebenJa;SeewaldJe;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;HlavatyAl;VoicanCh;MoidlMa;WeissAl</t>
   </si>
   <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
@@ -1300,7 +1329,7 @@
     <t>Eishalle Meran;BulovecMi;LazzeriAl;CristeliMa;JeramFi</t>
   </si>
   <si>
-    <t>Eishalle Gröden;HolzerTo;LehnerMo;MoidlMa;SeewaldJe</t>
+    <t>Eishalle Gröden;HolzerTo;VirtaTu;DivisDo;FleischmannLu</t>
   </si>
   <si>
     <t>Eishalle Celje;LebenJa;OrelSt;MarkizetiGr;PuffWo</t>
@@ -1411,53 +1440,53 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF9C0006"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
-      <color rgb="FF006100"/>
-      <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="36"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="36"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1469,25 +1498,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1499,7 +1528,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1516,7 +1545,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1527,7 +1556,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1796,25 +1825,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1909,21 +1923,43 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.5999633777886288"/>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2202,9 +2238,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR73"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BQ73"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -2277,30 +2313,30 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1">
         <f>COUNTIF(B4:B64,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1">
         <f>COUNTIF(C4:C67,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1">
         <f>COUNTIF(D4:D67,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1">
         <f>COUNTIF(E4:E66,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1">
         <f>COUNTIF(F4:F67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1">
         <f>COUNTIF(G4:G68,"&lt;&gt;")</f>
@@ -2308,11 +2344,11 @@
       </c>
       <c r="H1">
         <f>COUNTIF(H4:H68,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I1">
         <f>COUNTIF(I4:I68,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J1">
         <f>COUNTIF(J4:J64,"&lt;&gt;")</f>
@@ -2336,11 +2372,11 @@
       </c>
       <c r="O1">
         <f>COUNTIF(O4:O66,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P1">
         <f t="shared" ref="P1:Z1" si="0">COUNTIF(P4:P70,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q1">
         <f>COUNTIF(Q4:Q66,"&lt;&gt;")</f>
@@ -2348,31 +2384,31 @@
       </c>
       <c r="R1">
         <f>COUNTIF(R4:R63,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="S1">
         <f>COUNTIF(S4:S69,"&lt;&gt;")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T1">
         <f>COUNTIF(T4:T68,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1">
         <f>COUNTIF(U4:U69,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V1">
         <f>COUNTIF(V4:V66,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1">
         <f>COUNTIF(W4:W68,"&lt;&gt;")</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X1">
         <f>COUNTIF(X4:X68,"&lt;&gt;")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y1">
         <f>COUNTIF(Y4:Y68,"&lt;&gt;")</f>
@@ -2380,11 +2416,11 @@
       </c>
       <c r="Z1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA1">
         <f>COUNTIF(AA4:AA65,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB1">
         <f>COUNTIF(AB4:AB65,"&lt;&gt;")</f>
@@ -2396,11 +2432,11 @@
       </c>
       <c r="AD1">
         <f>COUNTIF(AD4:AD66,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE1">
         <f>COUNTIF(AE4:AE67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF1">
         <f>COUNTIF(AF4:AF63,"&lt;&gt;")</f>
@@ -2408,11 +2444,11 @@
       </c>
       <c r="AG1">
         <f>COUNTIF(AG4:AG65,"&lt;&gt;")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH1">
         <f>COUNTIF(AH4:AH65,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI1">
         <f>COUNTIF(AI4:AI66,"&lt;&gt;")</f>
@@ -2424,19 +2460,19 @@
       </c>
       <c r="AK1">
         <f>COUNTIF(AK4:AK63,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL1">
         <f>COUNTIF(AL4:AL65,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM1">
         <f>COUNTIF(AM4:AM64,"&lt;&gt;")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN1">
         <f>COUNTIF(AN4:AN63,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO1">
         <f>COUNTIF(AO4:AO64,"&lt;&gt;")</f>
@@ -2452,7 +2488,7 @@
       </c>
       <c r="AR1">
         <f>COUNTIF(AR4:AR60,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS1">
         <f>COUNTIF(AS4:AS68,"&lt;&gt;")</f>
@@ -2464,7 +2500,7 @@
       </c>
       <c r="AU1">
         <f>COUNTIF(AU4:AU67,"&lt;&gt;")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV1">
         <f>COUNTIF(AV4:AV64,"&lt;&gt;")</f>
@@ -2476,43 +2512,43 @@
       </c>
       <c r="AX1">
         <f>COUNTIF(AX4:AX65,"&lt;&gt;")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY1">
         <f>COUNTIF(AY4:AY60,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ1">
         <f>COUNTIF(AZ4:AZ64,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA1">
         <f>COUNTIF(BA4:BA69,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB1">
         <f>COUNTIF(BB4:BB68,"&lt;&gt;")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC1">
         <f>COUNTIF(BC4:BC67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD1">
         <f>COUNTIF(BD4:BD67,"&lt;&gt;")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BE1">
         <f>COUNTIF(BE4:BE66,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF1">
         <f>COUNTIF(BF4:BF68,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BG1">
         <f>COUNTIF(BG4:BG61,"&lt;&gt;")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH1">
         <f>COUNTIF(BH4:BH68,"&lt;&gt;")</f>
@@ -2536,7 +2572,7 @@
       </c>
       <c r="BM1">
         <f>COUNTIF(BM4:BM67,"&lt;&gt;")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN1">
         <f>COUNTIF(BN4:BN68,"&lt;&gt;")</f>
@@ -2555,7 +2591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2764,7 +2800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2973,7 +3009,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3182,7 +3218,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3382,7 +3418,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3582,7 +3618,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -3779,7 +3815,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -3973,7 +4009,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -4167,7 +4203,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -4361,7 +4397,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -4425,6 +4461,9 @@
       <c r="W11" t="s">
         <v>93</v>
       </c>
+      <c r="X11" t="s">
+        <v>135</v>
+      </c>
       <c r="Y11" t="s">
         <v>100</v>
       </c>
@@ -4456,10 +4495,10 @@
         <v>100</v>
       </c>
       <c r="AI11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AJ11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s">
         <v>88</v>
@@ -4528,10 +4567,10 @@
         <v>126</v>
       </c>
       <c r="BG11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BH11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BJ11" t="s">
         <v>131</v>
@@ -4546,13 +4585,13 @@
         <v>121</v>
       </c>
       <c r="BO11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BP11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -4647,7 +4686,7 @@
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AJ12" t="s">
         <v>92</v>
@@ -4656,7 +4695,7 @@
         <v>95</v>
       </c>
       <c r="AL12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4665,7 +4704,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4683,7 +4722,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AV12" t="s">
         <v>109</v>
@@ -4692,7 +4731,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4713,16 +4752,16 @@
         <v>103</v>
       </c>
       <c r="BE12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BF12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BG12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BJ12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BK12" t="s">
         <v>120</v>
@@ -4734,10 +4773,10 @@
         <v>114</v>
       </c>
       <c r="BP12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -4763,7 +4802,7 @@
         <v>121</v>
       </c>
       <c r="J13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K13" t="s">
         <v>112</v>
@@ -4841,7 +4880,7 @@
         <v>109</v>
       </c>
       <c r="AL13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AM13" t="s">
         <v>106</v>
@@ -4862,7 +4901,7 @@
         <v>106</v>
       </c>
       <c r="AS13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
@@ -4898,7 +4937,7 @@
         <v>121</v>
       </c>
       <c r="BE13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BF13" t="s">
         <v>127</v>
@@ -4910,7 +4949,7 @@
         <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BN13" t="s">
         <v>131</v>
@@ -4919,7 +4958,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -4936,7 +4975,7 @@
         <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H14" t="s">
         <v>120</v>
@@ -4984,7 +5023,7 @@
         <v>106</v>
       </c>
       <c r="Y14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Z14" t="s">
         <v>129</v>
@@ -5014,7 +5053,7 @@
         <v>131</v>
       </c>
       <c r="AI14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -5032,7 +5071,7 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AP14" t="s">
         <v>120</v>
@@ -5044,7 +5083,7 @@
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
@@ -5079,20 +5118,26 @@
       <c r="BD14" t="s">
         <v>125</v>
       </c>
+      <c r="BE14" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>135</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>135</v>
+      </c>
       <c r="BK14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BM14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BN14" t="s">
         <v>119</v>
       </c>
-      <c r="BP14" t="s">
-        <v>127</v>
-      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>134</v>
       </c>
@@ -5100,7 +5145,7 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -5109,25 +5154,25 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I15" t="s">
         <v>125</v>
       </c>
       <c r="J15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O15" t="s">
         <v>111</v>
@@ -5166,10 +5211,10 @@
         <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AD15" t="s">
         <v>119</v>
@@ -5190,19 +5235,19 @@
         <v>124</v>
       </c>
       <c r="AJ15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AL15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AO15" t="s">
         <v>130</v>
@@ -5211,7 +5256,7 @@
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AR15" t="s">
         <v>104</v>
@@ -5223,7 +5268,7 @@
         <v>107</v>
       </c>
       <c r="AU15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AV15" t="s">
         <v>103</v>
@@ -5235,7 +5280,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -5250,19 +5295,19 @@
         <v>119</v>
       </c>
       <c r="BD15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BK15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BM15" t="s">
         <v>122</v>
       </c>
       <c r="BN15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -5279,19 +5324,19 @@
         <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N16" t="s">
         <v>134</v>
@@ -5312,13 +5357,13 @@
         <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U16" t="s">
         <v>104</v>
       </c>
       <c r="V16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="W16" t="s">
         <v>104</v>
@@ -5330,7 +5375,7 @@
         <v>120</v>
       </c>
       <c r="AB16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s">
         <v>92</v>
@@ -5342,16 +5387,16 @@
         <v>119</v>
       </c>
       <c r="AF16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AH16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AI16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AJ16" t="s">
         <v>132</v>
@@ -5360,19 +5405,19 @@
         <v>120</v>
       </c>
       <c r="AL16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AM16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AN16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AO16" t="s">
         <v>128</v>
       </c>
       <c r="AP16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AQ16" t="s">
         <v>125</v>
@@ -5387,25 +5432,25 @@
         <v>104</v>
       </c>
       <c r="AU16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AV16" t="s">
         <v>125</v>
       </c>
       <c r="AW16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AX16" t="s">
         <v>121</v>
       </c>
       <c r="AY16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AZ16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BA16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BB16" t="s">
         <v>103</v>
@@ -5414,27 +5459,27 @@
         <v>132</v>
       </c>
       <c r="BD16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BK16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BM16" t="s">
         <v>124</v>
       </c>
       <c r="BN16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
         <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -5449,7 +5494,7 @@
         <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K17" t="s">
         <v>126</v>
@@ -5458,7 +5503,7 @@
         <v>120</v>
       </c>
       <c r="N17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O17" t="s">
         <v>131</v>
@@ -5470,7 +5515,7 @@
         <v>111</v>
       </c>
       <c r="R17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S17" t="s">
         <v>103</v>
@@ -5494,7 +5539,7 @@
         <v>128</v>
       </c>
       <c r="AB17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AC17" t="s">
         <v>131</v>
@@ -5503,46 +5548,46 @@
         <v>122</v>
       </c>
       <c r="AE17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AF17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s">
         <v>122</v>
       </c>
       <c r="AH17" t="s">
+        <v>139</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>143</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL17" t="s">
         <v>138</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>137</v>
-      </c>
       <c r="AM17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AN17" t="s">
         <v>131</v>
       </c>
       <c r="AO17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AP17" t="s">
         <v>119</v>
       </c>
       <c r="AQ17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AR17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AS17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
@@ -5551,7 +5596,7 @@
         <v>122</v>
       </c>
       <c r="AV17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AW17" t="s">
         <v>94</v>
@@ -5560,66 +5605,66 @@
         <v>120</v>
       </c>
       <c r="AY17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AZ17" t="s">
         <v>120</v>
       </c>
       <c r="BA17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BB17" t="s">
         <v>121</v>
       </c>
       <c r="BC17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BD17" t="s">
         <v>119</v>
       </c>
       <c r="BK17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BM17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
         <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H18" t="s">
         <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P18" t="s">
         <v>121</v>
@@ -5640,7 +5685,7 @@
         <v>112</v>
       </c>
       <c r="V18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="W18" t="s">
         <v>111</v>
@@ -5652,31 +5697,34 @@
         <v>131</v>
       </c>
       <c r="AB18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC18" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE18" t="s">
         <v>135</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>142</v>
       </c>
       <c r="AF18" t="s">
         <v>126</v>
       </c>
       <c r="AG18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AH18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AK18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AL18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AM18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AN18" t="s">
         <v>128</v>
@@ -5688,13 +5736,13 @@
         <v>128</v>
       </c>
       <c r="AQ18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
       <c r="AS18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AT18" t="s">
         <v>121</v>
@@ -5706,48 +5754,48 @@
         <v>132</v>
       </c>
       <c r="AW18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AX18" t="s">
         <v>130</v>
       </c>
       <c r="AY18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AZ18" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>148</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>140</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>142</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>142</v>
+      </c>
+      <c r="BK18" t="s">
         <v>147</v>
       </c>
-      <c r="BA18" t="s">
-        <v>147</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>139</v>
-      </c>
-      <c r="BC18" t="s">
-        <v>141</v>
-      </c>
-      <c r="BD18" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK18" t="s">
-        <v>146</v>
-      </c>
       <c r="BM18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
         <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E19" t="s">
         <v>119</v>
@@ -5756,28 +5804,28 @@
         <v>127</v>
       </c>
       <c r="H19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I19" t="s">
         <v>126</v>
       </c>
       <c r="L19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q19" t="s">
         <v>128</v>
       </c>
       <c r="R19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S19" t="s">
         <v>121</v>
@@ -5789,13 +5837,13 @@
         <v>120</v>
       </c>
       <c r="V19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="W19" t="s">
         <v>131</v>
       </c>
       <c r="Z19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA19" t="s">
         <v>122</v>
@@ -5807,10 +5855,10 @@
         <v>119</v>
       </c>
       <c r="AD19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s">
         <v>124</v>
@@ -5819,93 +5867,96 @@
         <v>126</v>
       </c>
       <c r="AK19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL19" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>147</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>142</v>
+      </c>
+      <c r="AR19" t="s">
         <v>141</v>
       </c>
-      <c r="AM19" t="s">
-        <v>153</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>141</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>140</v>
-      </c>
       <c r="AS19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AT19" t="s">
         <v>120</v>
       </c>
+      <c r="AU19" t="s">
+        <v>135</v>
+      </c>
       <c r="AV19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AW19" t="s">
+        <v>139</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>136</v>
+      </c>
+      <c r="AY19" t="s">
         <v>138</v>
       </c>
-      <c r="AX19" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>137</v>
-      </c>
       <c r="AZ19" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>139</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>151</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>150</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>150</v>
+      </c>
+      <c r="BK19" t="s">
         <v>138</v>
       </c>
-      <c r="BA19" t="s">
-        <v>138</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>150</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>149</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>149</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>137</v>
-      </c>
       <c r="BM19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
         <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I20" t="s">
         <v>124</v>
       </c>
       <c r="L20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" t="s">
         <v>124</v>
@@ -5920,13 +5971,13 @@
         <v>122</v>
       </c>
       <c r="R20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S20" t="s">
         <v>94</v>
       </c>
       <c r="T20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U20" t="s">
         <v>109</v>
@@ -5941,52 +5992,52 @@
         <v>119</v>
       </c>
       <c r="AA20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AC20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD20" t="s">
         <v>127</v>
       </c>
       <c r="AF20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK20" t="s">
         <v>122</v>
       </c>
       <c r="AL20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AM20" t="s">
         <v>126</v>
       </c>
       <c r="AN20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AO20" t="s">
         <v>126</v>
       </c>
       <c r="AP20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AQ20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AR20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AS20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AT20" t="s">
         <v>130</v>
@@ -5998,45 +6049,54 @@
         <v>119</v>
       </c>
       <c r="AY20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AZ20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BA20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BB20" t="s">
         <v>128</v>
       </c>
+      <c r="BC20" t="s">
+        <v>135</v>
+      </c>
       <c r="BD20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BK20" t="s">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
         <v>124</v>
       </c>
+      <c r="E21" t="s">
+        <v>135</v>
+      </c>
       <c r="I21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q21" t="s">
         <v>132</v>
@@ -6045,64 +6105,67 @@
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T21" t="s">
         <v>124</v>
       </c>
       <c r="U21" t="s">
+        <v>139</v>
+      </c>
+      <c r="V21" t="s">
+        <v>154</v>
+      </c>
+      <c r="W21" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA21" t="s">
         <v>138</v>
       </c>
-      <c r="V21" t="s">
-        <v>153</v>
-      </c>
-      <c r="W21" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>137</v>
-      </c>
       <c r="AB21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AC21" t="s">
         <v>124</v>
       </c>
       <c r="AG21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AH21" t="s">
         <v>124</v>
       </c>
       <c r="AK21" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>127</v>
       </c>
       <c r="AM21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AN21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AO21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AP21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AR21" t="s">
         <v>120</v>
       </c>
       <c r="AT21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AW21" t="s">
         <v>124</v>
       </c>
       <c r="AX21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AZ21" t="s">
         <v>126</v>
@@ -6111,39 +6174,39 @@
         <v>119</v>
       </c>
       <c r="BB21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BD21" t="s">
         <v>127</v>
       </c>
-      <c r="BK21" t="s">
+    </row>
+    <row r="22" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" t="s">
+        <v>150</v>
+      </c>
+      <c r="N22" t="s">
+        <v>158</v>
+      </c>
+      <c r="O22" t="s">
+        <v>144</v>
+      </c>
+      <c r="P22" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q22" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="I22" t="s">
-        <v>149</v>
-      </c>
-      <c r="N22" t="s">
-        <v>157</v>
-      </c>
-      <c r="O22" t="s">
-        <v>143</v>
-      </c>
-      <c r="P22" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>142</v>
       </c>
       <c r="R22" t="s">
         <v>122</v>
@@ -6152,16 +6215,16 @@
         <v>128</v>
       </c>
       <c r="T22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="V22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="W22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z22" t="s">
         <v>124</v>
@@ -6170,184 +6233,196 @@
         <v>127</v>
       </c>
       <c r="AB22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AC22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG22" t="s">
         <v>127</v>
       </c>
       <c r="AH22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AM22" t="s">
         <v>124</v>
       </c>
       <c r="AN22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AO22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AR22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AT22" t="s">
         <v>119</v>
       </c>
       <c r="AW22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AX22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AZ22" t="s">
+        <v>147</v>
+      </c>
+      <c r="BA22" t="s">
         <v>146</v>
       </c>
-      <c r="BA22" t="s">
-        <v>145</v>
-      </c>
       <c r="BB22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>135</v>
+      </c>
       <c r="C23" t="s">
         <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R23" t="s">
         <v>132</v>
       </c>
       <c r="S23" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="T23" t="s">
+        <v>135</v>
       </c>
       <c r="U23" t="s">
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Z23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC23" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>135</v>
       </c>
       <c r="AK23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AM23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AN23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AO23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AR23" t="s">
         <v>126</v>
       </c>
       <c r="AT23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AX23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AZ23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BA23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BB23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="3:54" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P24" t="s">
         <v>124</v>
       </c>
       <c r="Q24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S24" t="s">
         <v>122</v>
       </c>
       <c r="U24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V24" t="s">
         <v>127</v>
       </c>
       <c r="W24" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>135</v>
       </c>
       <c r="AK24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AO24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AR24" t="s">
         <v>124</v>
       </c>
       <c r="AT24" t="s">
+        <v>143</v>
+      </c>
+      <c r="AX24" t="s">
         <v>142</v>
       </c>
-      <c r="AX24" t="s">
-        <v>141</v>
-      </c>
       <c r="AZ24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BA24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BB24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I25" t="s">
         <v>127</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="S25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U25" t="s">
         <v>124</v>
@@ -6356,65 +6431,71 @@
         <v>127</v>
       </c>
       <c r="AK25" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>135</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>150</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>142</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>144</v>
+      </c>
+      <c r="AZ25" t="s">
         <v>143</v>
       </c>
-      <c r="AR25" t="s">
-        <v>149</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>141</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>143</v>
-      </c>
-      <c r="AZ25" t="s">
+      <c r="BA25" t="s">
+        <v>150</v>
+      </c>
+      <c r="BB25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>144</v>
+      </c>
+      <c r="R26" t="s">
+        <v>155</v>
+      </c>
+      <c r="S26" t="s">
         <v>142</v>
       </c>
-      <c r="BA25" t="s">
-        <v>149</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
-      <c r="R26" t="s">
-        <v>154</v>
-      </c>
-      <c r="S26" t="s">
-        <v>141</v>
-      </c>
       <c r="U26" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>127</v>
+        <v>150</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>135</v>
       </c>
       <c r="AT26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AZ26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BA26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BB26" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="18:54" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="U27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AT27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AZ27" t="s">
         <v>127</v>
@@ -6423,18 +6504,22 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="R28" t="s">
         <v>127</v>
       </c>
       <c r="S28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="18:19" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6477,20 +6562,20 @@
     <row r="72" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A4:XFD27">
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>A4 &gt; "2025-02-10"</formula>
+  <conditionalFormatting sqref="A4:XFD32">
+    <cfRule type="expression" dxfId="1" priority="6">
+      <formula>A4 &gt; "2025-03-05"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CG42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A3:CH42"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -6538,7 +6623,7 @@
     <col min="83" max="83" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -6636,7 +6721,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -6690,13 +6775,13 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
       </c>
       <c r="BA3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BB3" t="s">
         <v>134</v>
@@ -6705,28 +6790,28 @@
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BE3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BF3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BG3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
       </c>
       <c r="BI3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BJ3" t="s">
         <v>131</v>
       </c>
       <c r="BK3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BL3" t="s">
         <v>130</v>
@@ -6735,19 +6820,19 @@
         <v>128</v>
       </c>
       <c r="BN3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BO3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BP3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BQ3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BR3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
@@ -6762,40 +6847,43 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BX3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BY3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="CC3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="CD3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="CE3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CF3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="CG3" t="s">
         <v>127</v>
       </c>
+      <c r="CH3" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -7049,10 +7137,13 @@
         <v>11</v>
       </c>
       <c r="CG4" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7308,8 +7399,11 @@
       <c r="CG5" t="s">
         <v>50</v>
       </c>
+      <c r="CH5" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -7563,10 +7657,13 @@
         <v>7</v>
       </c>
       <c r="CG6" t="s">
-        <v>27</v>
+        <v>61</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -7822,13 +7919,16 @@
       <c r="CG7" t="s">
         <v>62</v>
       </c>
+      <c r="CH7" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -7852,7 +7952,7 @@
         <v>16</v>
       </c>
       <c r="R8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T8" t="s">
         <v>4</v>
@@ -8001,8 +8101,11 @@
       <c r="CG8" t="s">
         <v>6</v>
       </c>
+      <c r="CH8" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -8016,7 +8119,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K9" t="s">
         <v>50</v>
@@ -8180,8 +8283,11 @@
       <c r="CG9" t="s">
         <v>21</v>
       </c>
+      <c r="CH9" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -8354,13 +8460,16 @@
         <v>40</v>
       </c>
       <c r="CF10" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="CG10" t="s">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="CH10" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -8536,10 +8645,13 @@
         <v>42</v>
       </c>
       <c r="CG11" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -8565,7 +8677,7 @@
         <v>34</v>
       </c>
       <c r="P12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T12" t="s">
         <v>14</v>
@@ -8687,8 +8799,11 @@
       <c r="CG12" t="s">
         <v>36</v>
       </c>
+      <c r="CH12" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -8836,8 +8951,11 @@
       <c r="CG13" t="s">
         <v>33</v>
       </c>
+      <c r="CH13" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -8985,8 +9103,11 @@
       <c r="CG14" t="s">
         <v>25</v>
       </c>
+      <c r="CH14" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -9134,8 +9255,11 @@
       <c r="CG15" t="s">
         <v>30</v>
       </c>
+      <c r="CH15" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -9271,8 +9395,11 @@
       <c r="CG16" t="s">
         <v>5</v>
       </c>
+      <c r="CH16" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -9408,8 +9535,11 @@
       <c r="CG17" t="s">
         <v>9</v>
       </c>
+      <c r="CH17" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -9543,10 +9673,13 @@
         <v>53</v>
       </c>
       <c r="CG18" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -9682,8 +9815,11 @@
       <c r="CG19" t="s">
         <v>55</v>
       </c>
+      <c r="CH19" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -9784,7 +9920,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -9882,10 +10018,10 @@
         <v>21</v>
       </c>
       <c r="CG21" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -9983,10 +10119,10 @@
         <v>40</v>
       </c>
       <c r="CG22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -10084,10 +10220,10 @@
         <v>12</v>
       </c>
       <c r="CG23" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="7:85" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -10128,7 +10264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" t="s">
         <v>47</v>
       </c>
@@ -10169,7 +10305,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G26" t="s">
         <v>8</v>
       </c>
@@ -10210,7 +10346,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="7:81" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G27" t="s">
         <v>64</v>
       </c>
@@ -10251,11 +10387,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10271,10 +10407,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:CG14"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A3:CH14"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.140625" customWidth="1"/>
     <col min="2" max="2" width="58.28515625" customWidth="1"/>
@@ -10361,7 +10497,7 @@
     <col min="101" max="101" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -10459,7 +10595,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -10513,13 +10649,13 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
       </c>
       <c r="BA3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BB3" t="s">
         <v>134</v>
@@ -10528,28 +10664,28 @@
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BE3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BF3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BG3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
       </c>
       <c r="BI3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BJ3" t="s">
         <v>131</v>
       </c>
       <c r="BK3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BL3" t="s">
         <v>130</v>
@@ -10558,19 +10694,19 @@
         <v>128</v>
       </c>
       <c r="BN3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BO3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BP3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BQ3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BR3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
@@ -10585,918 +10721,933 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BX3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BY3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="CC3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="CD3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="CE3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="CF3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="CG3" t="s">
         <v>127</v>
       </c>
+      <c r="CH3" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="R4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="U4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="W4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="X4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AB4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AC4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AD4" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>190</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>191</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>194</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP4" t="s">
         <v>188</v>
       </c>
-      <c r="AE4" t="s">
-        <v>189</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>190</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>194</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>198</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>199</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>187</v>
-      </c>
       <c r="AQ4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AR4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AS4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AT4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AU4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AV4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AW4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AX4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AY4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AZ4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BA4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BB4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="BC4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="BD4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="BE4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="BF4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="BG4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="BH4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="BI4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="BJ4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="BK4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="BL4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="BM4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="BN4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="BO4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="BP4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="BQ4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BR4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="BS4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="BT4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="BU4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="BV4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BW4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="BX4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="BY4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="BZ4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="CA4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="CB4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="CC4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="CD4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="CE4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="CF4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="CG4" t="s">
-        <v>242</v>
+        <v>243</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>244</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="R5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="T5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="U5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="V5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="W5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Y5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AB5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AD5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AE5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AF5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AI5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AK5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AO5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AR5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AS5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AT5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AU5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AV5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AW5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AX5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AZ5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BA5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BB5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BC5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="BG5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="BH5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="BJ5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="BK5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="BM5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="BN5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="BO5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="BP5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="BQ5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="BS5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="BT5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="BU5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="BV5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="BX5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="BY5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="BZ5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="CA5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="CB5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="CC5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="CE5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="CF5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="CG5" t="s">
-        <v>301</v>
+        <v>303</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>304</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="P6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="T6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="V6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="W6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Y6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Z6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AB6" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AD6" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AE6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AI6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AK6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AM6" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AN6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AS6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AT6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AU6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AV6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AW6" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AX6" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AZ6" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="BA6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="BB6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="BC6" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="BG6" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="BJ6" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="BK6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="BM6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="BN6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="BP6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="BS6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="BU6" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="BV6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="BX6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="BY6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="BZ6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="CA6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="CB6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="CC6" t="s">
+        <v>351</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>352</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>353</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>359</v>
+      </c>
+      <c r="K7" t="s">
+        <v>360</v>
+      </c>
+      <c r="L7" t="s">
+        <v>361</v>
+      </c>
+      <c r="N7" t="s">
         <v>348</v>
       </c>
-      <c r="CF6" t="s">
-        <v>349</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>350</v>
+      <c r="P7" t="s">
+        <v>362</v>
+      </c>
+      <c r="T7" t="s">
+        <v>363</v>
+      </c>
+      <c r="V7" t="s">
+        <v>364</v>
+      </c>
+      <c r="W7" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>366</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>368</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>370</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>371</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>374</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>375</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>376</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>377</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>378</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>379</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>380</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>381</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>382</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>383</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>384</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>385</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>386</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>387</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>388</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>389</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>390</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>391</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>392</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>393</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>394</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>395</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>396</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>397</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>398</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>399</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F7" t="s">
-        <v>353</v>
-      </c>
-      <c r="G7" t="s">
-        <v>354</v>
-      </c>
-      <c r="H7" t="s">
-        <v>355</v>
-      </c>
-      <c r="K7" t="s">
-        <v>356</v>
-      </c>
-      <c r="L7" t="s">
-        <v>357</v>
-      </c>
-      <c r="N7" t="s">
-        <v>345</v>
-      </c>
-      <c r="P7" t="s">
-        <v>358</v>
-      </c>
-      <c r="T7" t="s">
-        <v>359</v>
-      </c>
-      <c r="V7" t="s">
-        <v>360</v>
-      </c>
-      <c r="W7" t="s">
-        <v>361</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>362</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>363</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>364</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>365</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>366</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>367</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>368</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>369</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>370</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>371</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>372</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>373</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>374</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>375</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>376</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>377</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>378</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>379</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>380</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>381</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>382</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>383</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>384</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>385</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>386</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>387</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>388</v>
-      </c>
-      <c r="BZ7" t="s">
-        <v>389</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>390</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>391</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>392</v>
-      </c>
-      <c r="CF7" t="s">
-        <v>393</v>
-      </c>
-      <c r="CG7" t="s">
-        <v>394</v>
+    <row r="8" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" t="s">
+        <v>402</v>
+      </c>
+      <c r="G8" t="s">
+        <v>403</v>
+      </c>
+      <c r="H8" t="s">
+        <v>404</v>
+      </c>
+      <c r="K8" t="s">
+        <v>405</v>
+      </c>
+      <c r="L8" t="s">
+        <v>406</v>
+      </c>
+      <c r="V8" t="s">
+        <v>407</v>
+      </c>
+      <c r="W8" t="s">
+        <v>408</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>409</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>410</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>411</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>412</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>413</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>414</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>415</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>416</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>417</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>418</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>419</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>420</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>421</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>422</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>423</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>424</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>425</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>426</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>427</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>428</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>429</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>430</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>431</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>432</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:85" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>395</v>
-      </c>
-      <c r="D8" t="s">
-        <v>396</v>
-      </c>
-      <c r="F8" t="s">
-        <v>397</v>
-      </c>
-      <c r="G8" t="s">
-        <v>398</v>
-      </c>
-      <c r="H8" t="s">
-        <v>399</v>
-      </c>
-      <c r="K8" t="s">
-        <v>400</v>
-      </c>
-      <c r="L8" t="s">
-        <v>401</v>
-      </c>
-      <c r="V8" t="s">
-        <v>402</v>
-      </c>
-      <c r="W8" t="s">
-        <v>403</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>404</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>405</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>406</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>407</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>408</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>409</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>410</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>411</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>412</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>413</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>414</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>415</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>416</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>417</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>418</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>419</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>420</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>421</v>
-      </c>
-      <c r="BZ8" t="s">
-        <v>422</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>423</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>424</v>
-      </c>
-      <c r="CC8" t="s">
-        <v>425</v>
-      </c>
-      <c r="CF8" t="s">
-        <v>426</v>
-      </c>
-      <c r="CG8" t="s">
-        <v>427</v>
+    <row r="9" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>433</v>
+      </c>
+      <c r="L9" t="s">
+        <v>434</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>435</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>436</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>437</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>438</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>439</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>440</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>441</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>442</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>443</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>444</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>445</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="7:85" x14ac:dyDescent="0.25">
-      <c r="G9" t="s">
-        <v>428</v>
-      </c>
-      <c r="L9" t="s">
-        <v>429</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>430</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>431</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>432</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>433</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>434</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>435</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>436</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>437</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>438</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>439</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
@@ -11514,568 +11665,568 @@
     <col min="19" max="19" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
+        <v>446</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="6">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>274</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="63" t="s">
+        <v>447</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="7">
         <f>C1*4</f>
-        <v>1096</v>
+        <v>1152</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="B3" s="13">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B3" s="9">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
-        <v>1096</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+        <v>1152</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="B4" s="16">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" s="11">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <f>AHL!I1</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="G4" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="H4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="I4" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L4" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="11">
         <f>SUMIF(AHL!2:2,"hr",AHL!1:1)</f>
         <v>33</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="F5" s="18">
+      <c r="E5" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="F5" s="13">
         <v>2</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="14">
         <f>F5/13</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="15">
         <f>B4/B3</f>
-        <v>0.14233576642335766</v>
-      </c>
-      <c r="I5" s="21">
+        <v>0.14496527777777779</v>
+      </c>
+      <c r="I5" s="16">
         <f>C2*G5</f>
-        <v>168.6153846153846</v>
+        <v>177.23076923076923</v>
       </c>
       <c r="J5">
         <f>B4</f>
-        <v>156</v>
-      </c>
-      <c r="K5" s="22">
+        <v>167</v>
+      </c>
+      <c r="K5" s="17">
         <f>J5-I5</f>
-        <v>-12.615384615384613</v>
-      </c>
-      <c r="L5" s="23">
+        <v>-10.230769230769226</v>
+      </c>
+      <c r="L5" s="18">
         <f>K5/4</f>
-        <v>-3.1538461538461533</v>
+        <v>-2.5576923076923066</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="11">
         <f>SUMIF(AHL!2:2,"it",AHL!1:1)</f>
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C6">
         <f>AHL!X1</f>
-        <v>6</v>
-      </c>
-      <c r="E6" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="14">
         <f>F6/13</f>
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="H6" s="20">
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="H6" s="15">
         <f>B5/B3</f>
-        <v>0.030109489051094892</v>
-      </c>
-      <c r="I6" s="21">
+        <v>2.8645833333333332E-2</v>
+      </c>
+      <c r="I6" s="16">
         <f>C2*G6</f>
-        <v>84.3076923076923</v>
+        <v>88.615384615384613</v>
       </c>
       <c r="J6">
         <f>B5</f>
         <v>33</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="17">
         <f>J6-I6</f>
-        <v>-51.30769230769231</v>
-      </c>
-      <c r="L6" s="23">
+        <v>-55.615384615384613</v>
+      </c>
+      <c r="L6" s="18">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-12.826923076923077</v>
+        <v>-13.903846153846153</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="20">
         <f>SUMIF(AHL!2:2,"au",AHL!1:1)</f>
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="C7">
         <f>SUM(AHL!AL1,AHL!AU1,AHL!BA1,AHL!BD1,AHL!BE1,AHL!BF1,AHL!BG1,AHL!BM1)</f>
-        <v>109</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>453</v>
-      </c>
-      <c r="F7" s="27">
+        <v>126</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" s="22">
         <v>3</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="23">
         <f t="shared" ref="G7:G9" si="1">F7/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="24">
         <f>(B5+B4)/B3</f>
-        <v>0.17244525547445255</v>
-      </c>
-      <c r="I7" s="21">
+        <v>0.1736111111111111</v>
+      </c>
+      <c r="I7" s="16">
         <f>C2*G7</f>
-        <v>252.92307692307693</v>
+        <v>265.84615384615387</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
-        <v>189</v>
-      </c>
-      <c r="K7" s="22">
+        <v>200</v>
+      </c>
+      <c r="K7" s="17">
         <f>J7-I7</f>
-        <v>-63.923076923076934</v>
-      </c>
-      <c r="L7" s="23">
+        <v>-65.846153846153868</v>
+      </c>
+      <c r="L7" s="18">
         <f>K7/4</f>
-        <v>-15.980769230769234</v>
+        <v>-16.461538461538467</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
-        <v>454</v>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>459</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
-        <v>135</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="F8" s="32">
+        <v>156</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>460</v>
+      </c>
+      <c r="F8" s="27">
         <v>6</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="29">
         <f>B6/B3</f>
-        <v>0.3978102189781022</v>
-      </c>
-      <c r="I8" s="21">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I8" s="16">
         <f>C2*G8</f>
-        <v>505.84615384615387</v>
+        <v>531.69230769230774</v>
       </c>
       <c r="J8">
         <f>B6</f>
-        <v>436</v>
-      </c>
-      <c r="K8" s="22">
+        <v>456</v>
+      </c>
+      <c r="K8" s="17">
         <f>J8-I8</f>
-        <v>-69.84615384615387</v>
-      </c>
-      <c r="L8" s="23">
+        <v>-75.692307692307736</v>
+      </c>
+      <c r="L8" s="18">
         <f>K8/4</f>
-        <v>-17.461538461538467</v>
+        <v>-18.923076923076934</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
-        <v>1096</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="F9" s="32">
+        <v>1152</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>462</v>
+      </c>
+      <c r="F9" s="27">
         <v>4</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="28">
         <f t="shared" si="1"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H9" s="34">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H9" s="29">
         <f>B7/B3</f>
-        <v>0.42974452554744524</v>
-      </c>
-      <c r="I9" s="21">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="I9" s="16">
         <f>C2*G9</f>
-        <v>337.2307692307692</v>
+        <v>354.46153846153845</v>
       </c>
       <c r="J9">
         <f>B7</f>
-        <v>471</v>
-      </c>
-      <c r="K9" s="35">
+        <v>496</v>
+      </c>
+      <c r="K9" s="30">
         <f>J9-I9</f>
-        <v>133.76923076923077</v>
-      </c>
-      <c r="L9" s="23">
+        <v>141.53846153846155</v>
+      </c>
+      <c r="L9" s="18">
         <f>K9/4</f>
-        <v>33.44230769230769</v>
+        <v>35.384615384615387</v>
       </c>
     </row>
-    <row r="11" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="36" t="s">
-        <v>458</v>
-      </c>
-      <c r="I11" s="37">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="I11" s="32">
         <f>SUM(I7:I9)</f>
-        <v>1096</v>
-      </c>
-      <c r="J11" s="31">
+        <v>1152</v>
+      </c>
+      <c r="J11" s="26">
         <f>SUM(J7:J9)</f>
-        <v>1096</v>
-      </c>
-      <c r="K11" s="38">
+        <v>1152</v>
+      </c>
+      <c r="K11" s="33">
         <f>SUM(K7:K9)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="39">
+      <c r="L11" s="34">
         <f>SUM(L7:L9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F16" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="G16" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="H16" t="s">
-        <v>448</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>449</v>
-      </c>
-      <c r="J16" s="40" t="s">
-        <v>450</v>
+        <v>453</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>454</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>455</v>
       </c>
       <c r="K16" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L16" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="F17" s="42">
+    <row r="17" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E17" s="36" t="s">
+        <v>458</v>
+      </c>
+      <c r="F17" s="37">
         <v>3</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="38">
         <f t="shared" ref="G17:G19" si="2">F17/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="39">
         <f>(B5+B4)/B3</f>
-        <v>0.17244525547445255</v>
-      </c>
-      <c r="I17" s="45">
+        <v>0.1736111111111111</v>
+      </c>
+      <c r="I17" s="40">
         <f>B3*G17</f>
-        <v>252.92307692307693</v>
-      </c>
-      <c r="J17" s="46">
+        <v>265.84615384615387</v>
+      </c>
+      <c r="J17" s="41">
         <f>B5+B4</f>
-        <v>189</v>
-      </c>
-      <c r="K17" s="47">
+        <v>200</v>
+      </c>
+      <c r="K17" s="42">
         <f>J17-I17</f>
-        <v>-63.923076923076934</v>
-      </c>
-      <c r="L17" s="23">
+        <v>-65.846153846153868</v>
+      </c>
+      <c r="L17" s="18">
         <f>K17/4</f>
-        <v>-15.980769230769234</v>
+        <v>-16.461538461538467</v>
       </c>
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
-      <c r="E18" s="48" t="s">
-        <v>455</v>
-      </c>
-      <c r="F18" s="49">
+      <c r="E18" s="43" t="s">
+        <v>460</v>
+      </c>
+      <c r="F18" s="44">
         <v>6</v>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="45">
         <f t="shared" si="2"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H18" s="51">
+      <c r="H18" s="46">
         <f>B6/B3</f>
-        <v>0.3978102189781022</v>
-      </c>
-      <c r="I18" s="52">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I18" s="47">
         <f>B3*G18</f>
-        <v>505.84615384615387</v>
-      </c>
-      <c r="J18" s="53">
+        <v>531.69230769230774</v>
+      </c>
+      <c r="J18" s="48">
         <f>B6</f>
-        <v>436</v>
-      </c>
-      <c r="K18" s="54">
+        <v>456</v>
+      </c>
+      <c r="K18" s="49">
         <f>J18-I18</f>
-        <v>-69.84615384615387</v>
-      </c>
-      <c r="L18" s="23">
+        <v>-75.692307692307736</v>
+      </c>
+      <c r="L18" s="18">
         <f>K18/4</f>
-        <v>-17.461538461538467</v>
-      </c>
-      <c r="Q18" s="55"/>
+        <v>-18.923076923076934</v>
+      </c>
+      <c r="Q18" s="50"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="56" t="s">
-        <v>457</v>
-      </c>
-      <c r="F19" s="57">
+    <row r="19" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="51" t="s">
+        <v>462</v>
+      </c>
+      <c r="F19" s="52">
         <v>4</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="53">
         <f t="shared" si="2"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H19" s="59">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H19" s="54">
         <f>B7/B3</f>
-        <v>0.42974452554744524</v>
-      </c>
-      <c r="I19" s="60">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="I19" s="55">
         <f>B3*G19</f>
-        <v>337.2307692307692</v>
-      </c>
-      <c r="J19" s="61">
+        <v>354.46153846153845</v>
+      </c>
+      <c r="J19" s="56">
         <f>B7</f>
-        <v>471</v>
-      </c>
-      <c r="K19" s="62">
+        <v>496</v>
+      </c>
+      <c r="K19" s="57">
         <f>J19-I19</f>
-        <v>133.76923076923077</v>
-      </c>
-      <c r="L19" s="23">
+        <v>141.53846153846155</v>
+      </c>
+      <c r="L19" s="18">
         <f>K19/4</f>
-        <v>33.44230769230769</v>
+        <v>35.384615384615387</v>
       </c>
     </row>
-    <row r="21" ht="46.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="63" t="s">
-        <v>461</v>
-      </c>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="63"/>
+    <row r="21" spans="5:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E21" s="66" t="s">
+        <v>466</v>
+      </c>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="66"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="6:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="G22" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="H22" t="s">
-        <v>448</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>449</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>450</v>
+        <v>453</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>454</v>
+      </c>
+      <c r="J22" s="35" t="s">
+        <v>455</v>
       </c>
       <c r="K22" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="F23" s="42">
+    <row r="23" spans="5:17" x14ac:dyDescent="0.25">
+      <c r="E23" s="36" t="s">
+        <v>458</v>
+      </c>
+      <c r="F23" s="37">
         <v>3</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="38">
         <f t="shared" ref="G23:G25" si="3">F23/13</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="39">
         <f>(B4+B5-C4)/(B3-C8)</f>
-        <v>0.17585848074921956</v>
-      </c>
-      <c r="I23" s="45">
+        <v>0.17871485943775101</v>
+      </c>
+      <c r="I23" s="40">
         <f>(B3-C8) *G23</f>
-        <v>221.76923076923077</v>
-      </c>
-      <c r="J23" s="46">
+        <v>229.84615384615387</v>
+      </c>
+      <c r="J23" s="41">
         <f>B4+B5-C4</f>
-        <v>169</v>
-      </c>
-      <c r="K23" s="47">
+        <v>178</v>
+      </c>
+      <c r="K23" s="42">
         <f>J23-I23</f>
-        <v>-52.769230769230774</v>
+        <v>-51.846153846153868</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="48" t="s">
-        <v>455</v>
-      </c>
-      <c r="F24" s="49">
+    <row r="24" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="43" t="s">
+        <v>460</v>
+      </c>
+      <c r="F24" s="44">
         <v>6</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="45">
         <f t="shared" si="3"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="46">
         <f>(B6-C4)/(B3-C8)</f>
-        <v>0.4328824141519251</v>
-      </c>
-      <c r="I24" s="52">
+        <v>0.43574297188755018</v>
+      </c>
+      <c r="I24" s="47">
         <f>(B3-C8)*G24</f>
-        <v>443.53846153846155</v>
-      </c>
-      <c r="J24" s="53">
+        <v>459.69230769230774</v>
+      </c>
+      <c r="J24" s="48">
         <f>B6-C6</f>
-        <v>430</v>
-      </c>
-      <c r="K24" s="54">
+        <v>448</v>
+      </c>
+      <c r="K24" s="49">
         <f>J24-I24</f>
-        <v>-13.538461538461547</v>
+        <v>-11.692307692307736</v>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E25" s="56" t="s">
-        <v>457</v>
-      </c>
-      <c r="F25" s="57">
+    <row r="25" spans="5:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="51" t="s">
+        <v>462</v>
+      </c>
+      <c r="F25" s="52">
         <v>4</v>
       </c>
-      <c r="G25" s="58">
+      <c r="G25" s="53">
         <f t="shared" si="3"/>
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="H25" s="59">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H25" s="54">
         <f>(B7-C7)/(B3-C8)</f>
-        <v>0.37669094693028093</v>
-      </c>
-      <c r="I25" s="60">
+        <v>0.37148594377510041</v>
+      </c>
+      <c r="I25" s="55">
         <f>(B3-C8)*G25</f>
-        <v>295.69230769230774</v>
-      </c>
-      <c r="J25" s="61">
+        <v>306.46153846153845</v>
+      </c>
+      <c r="J25" s="56">
         <f>B7-C7</f>
-        <v>362</v>
-      </c>
-      <c r="K25" s="62">
+        <v>370</v>
+      </c>
+      <c r="K25" s="57">
         <f>J25-I25</f>
-        <v>66.30769230769226</v>
+        <v>63.538461538461547</v>
       </c>
     </row>
-    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="64">
+      <c r="H26" s="58">
         <f>C8/B9</f>
-        <v>0.12317518248175183</v>
+        <v>0.13541666666666666</v>
       </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="65">
+      <c r="J26" s="59">
         <f>C8</f>
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="K26" s="5"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
-        <v>1096</v>
-      </c>
-      <c r="K28" s="66">
+        <v>1152</v>
+      </c>
+      <c r="K28" s="60">
         <f>SUM(K23:K25)</f>
-        <v>0</v>
+        <v>-5.6843418860808015E-14</v>
       </c>
     </row>
   </sheetData>

--- a/data/AHLdelegacije.xlsx
+++ b/data/AHLdelegacije.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5152A42A-A9F8-4371-8C1F-7C6A0DF1BA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
   </bookViews>
   <sheets>
-    <sheet name="AHL" sheetId="1" r:id="rId1"/>
-    <sheet name="AHL_DAT" sheetId="3" r:id="rId2"/>
-    <sheet name="AHL_DAT_STRING" sheetId="4" r:id="rId3"/>
-    <sheet name="Stevilo tekem po drzavah" sheetId="5" r:id="rId4"/>
+    <sheet sheetId="1" name="AHL" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="AHL_DAT" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="AHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Stevilo tekem po drzavah" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="489">
   <si>
     <t>sl</t>
   </si>
@@ -450,6 +436,9 @@
     <t>2025-02-20</t>
   </si>
   <si>
+    <t>2025-03-11</t>
+  </si>
+  <si>
     <t>2025-01-11</t>
   </si>
   <si>
@@ -471,9 +460,15 @@
     <t>2025-01-28</t>
   </si>
   <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
     <t>2025-01-18</t>
   </si>
   <si>
+    <t>2025-03-15</t>
+  </si>
+  <si>
     <t>2025-02-11</t>
   </si>
   <si>
@@ -495,6 +490,9 @@
     <t>2024-12-27</t>
   </si>
   <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
     <t>2025-01-26</t>
   </si>
   <si>
@@ -504,6 +502,9 @@
     <t>2025-01-29</t>
   </si>
   <si>
+    <t>2025-03-16</t>
+  </si>
+  <si>
     <t>2025-02-05</t>
   </si>
   <si>
@@ -768,6 +769,21 @@
     <t>Eishalle Jesenice;OrelSt;SnojTa;MarkizetiGr;WuchererGe</t>
   </si>
   <si>
+    <t>Eishalle Jesenice;BulovecMi;KainbergerJu;JeramFi;TelesklavFa</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;BrockAd;Huber rRe;RinkerDa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Jesenice;LazzeriAl;VoicanCh;FleischmannLu;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;HolzerTo;VirtaTu;BrondiPa;FleischmannLu</t>
+  </si>
+  <si>
+    <t>Eishalle Dornbirn;KainbergerJu;OrelSt;WuchererGe;ZacherlPa</t>
+  </si>
+  <si>
     <t>Sportpark Kitzbühel;LazzeriAl;SpiegelSe;BrondiPa;FormaioniTh</t>
   </si>
   <si>
@@ -948,6 +964,18 @@
     <t>Eishalle Cortina;RivisFe;StefenelliFe;FormaioniTh;PaceJa</t>
   </si>
   <si>
+    <t>Eishalle Ritten;GiacomozziFe;HolzerTo;BrondiPa;StrimitzerDa</t>
+  </si>
+  <si>
+    <t>Eishalle Sterzing;KainbergerJu;PinieOm;BrondiPa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;BulovecMi;GiacomozziFe;CristeliMa;JeramFi</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;PinieOm;SnojTa;CristeliMa;MarkizetiGr</t>
+  </si>
+  <si>
     <t>KELIT Arena Zell am See;OrelSt;WidmannFl;WendnerMa;WuchererGe</t>
   </si>
   <si>
@@ -1098,6 +1126,18 @@
     <t>Eishalle Dornbirn;BrockAd;LazzeriAl;FleischmannLu;ZacherlPa</t>
   </si>
   <si>
+    <t>KELIT Arena Zell am See;BrockAd;Huber rRe;MoidlMa;WendnerMa</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;OrelSt;SnojTa;MarkizetiGr;WuchererGe</t>
+  </si>
+  <si>
+    <t>KELIT Arena Zell am See;HlavatyAl;HolzerTo;MoidlMa;ZacherlPa</t>
+  </si>
+  <si>
+    <t>Eishalle Cortina;LazzeriAl;RivisFe;RinkerDa;StrimitzerDa</t>
+  </si>
+  <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
   </si>
   <si>
@@ -1231,6 +1271,15 @@
   </si>
   <si>
     <t>Eishalle Sterzing;HlavatyAl;VoicanCh;MoidlMa;WeissAl</t>
+  </si>
+  <si>
+    <t>Sportpark Kitzbühel;HlavatyAl;VoicanCh;PaceJa;WeissAl</t>
+  </si>
+  <si>
+    <t>Eishalle Meran;LazzeriAl;RivisFe;CristeliMa;FleischmannLu</t>
+  </si>
+  <si>
+    <t>Eishalle Ritten;PinieOm;VirtaTu;BrondiPa;RinkerDa</t>
   </si>
   <si>
     <t>Eishalle Meran;MoschenAn;SnojTa;MarkizetiGr;RivisAn</t>
@@ -1440,53 +1489,53 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF9C0006"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <charset val="238"/>
+      <color rgb="FF006100"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="36"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="36"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1498,25 +1547,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1528,7 +1577,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1545,7 +1594,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1556,7 +1605,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1825,10 +1874,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1923,43 +1987,21 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
+          <bgColor theme="4" tint="0.5999633777886288"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2238,9 +2280,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BQ73"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BR73"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -2313,7 +2355,7 @@
     <col min="73" max="73" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>COUNTIF(A4:A69,"&lt;&gt;")</f>
         <v>20</v>
@@ -2591,7 +2633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:69" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.45" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2800,7 +2842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3009,7 +3051,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -3218,7 +3260,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3418,7 +3460,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3618,7 +3660,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -3815,7 +3857,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -4009,7 +4051,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -4203,7 +4245,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -4397,7 +4439,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -4591,7 +4633,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -4655,6 +4697,9 @@
       <c r="W12" t="s">
         <v>100</v>
       </c>
+      <c r="X12" t="s">
+        <v>139</v>
+      </c>
       <c r="Y12" t="s">
         <v>95</v>
       </c>
@@ -4686,7 +4731,7 @@
         <v>104</v>
       </c>
       <c r="AI12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AJ12" t="s">
         <v>92</v>
@@ -4695,7 +4740,7 @@
         <v>95</v>
       </c>
       <c r="AL12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AM12" t="s">
         <v>102</v>
@@ -4704,7 +4749,7 @@
         <v>102</v>
       </c>
       <c r="AO12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AP12" t="s">
         <v>107</v>
@@ -4722,7 +4767,7 @@
         <v>100</v>
       </c>
       <c r="AU12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AV12" t="s">
         <v>109</v>
@@ -4731,7 +4776,7 @@
         <v>92</v>
       </c>
       <c r="AX12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AY12" t="s">
         <v>102</v>
@@ -4752,16 +4797,16 @@
         <v>103</v>
       </c>
       <c r="BE12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BG12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BJ12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BK12" t="s">
         <v>120</v>
@@ -4773,10 +4818,10 @@
         <v>114</v>
       </c>
       <c r="BP12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -4840,6 +4885,9 @@
       <c r="W13" t="s">
         <v>115</v>
       </c>
+      <c r="X13" t="s">
+        <v>147</v>
+      </c>
       <c r="Y13" t="s">
         <v>132</v>
       </c>
@@ -4937,7 +4985,7 @@
         <v>121</v>
       </c>
       <c r="BE13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BF13" t="s">
         <v>127</v>
@@ -4949,7 +4997,7 @@
         <v>103</v>
       </c>
       <c r="BM13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BN13" t="s">
         <v>131</v>
@@ -4958,7 +5006,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -4975,7 +5023,7 @@
         <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H14" t="s">
         <v>120</v>
@@ -5022,8 +5070,11 @@
       <c r="W14" t="s">
         <v>106</v>
       </c>
+      <c r="X14" t="s">
+        <v>149</v>
+      </c>
       <c r="Y14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z14" t="s">
         <v>129</v>
@@ -5053,7 +5104,7 @@
         <v>131</v>
       </c>
       <c r="AI14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="s">
         <v>121</v>
@@ -5071,7 +5122,7 @@
         <v>104</v>
       </c>
       <c r="AO14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AP14" t="s">
         <v>120</v>
@@ -5083,7 +5134,7 @@
         <v>94</v>
       </c>
       <c r="AS14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AT14" t="s">
         <v>115</v>
@@ -5128,16 +5179,16 @@
         <v>135</v>
       </c>
       <c r="BK14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="BM14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BN14" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>134</v>
       </c>
@@ -5145,7 +5196,7 @@
         <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -5154,22 +5205,22 @@
         <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I15" t="s">
         <v>125</v>
       </c>
       <c r="J15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N15" t="s">
         <v>137</v>
@@ -5211,7 +5262,7 @@
         <v>121</v>
       </c>
       <c r="AB15" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AC15" t="s">
         <v>137</v>
@@ -5235,19 +5286,19 @@
         <v>124</v>
       </c>
       <c r="AJ15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AK15" t="s">
         <v>112</v>
       </c>
       <c r="AL15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AM15" t="s">
         <v>109</v>
       </c>
       <c r="AN15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AO15" t="s">
         <v>130</v>
@@ -5256,7 +5307,7 @@
         <v>104</v>
       </c>
       <c r="AQ15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AR15" t="s">
         <v>104</v>
@@ -5268,7 +5319,7 @@
         <v>107</v>
       </c>
       <c r="AU15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AV15" t="s">
         <v>103</v>
@@ -5280,7 +5331,7 @@
         <v>111</v>
       </c>
       <c r="AY15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AZ15" t="s">
         <v>112</v>
@@ -5295,19 +5346,28 @@
         <v>119</v>
       </c>
       <c r="BD15" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>139</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>157</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>157</v>
       </c>
       <c r="BK15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BM15" t="s">
         <v>122</v>
       </c>
       <c r="BN15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -5324,13 +5384,13 @@
         <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H16" t="s">
         <v>136</v>
       </c>
       <c r="I16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K16" t="s">
         <v>136</v>
@@ -5363,7 +5423,7 @@
         <v>104</v>
       </c>
       <c r="V16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="W16" t="s">
         <v>104</v>
@@ -5390,13 +5450,13 @@
         <v>136</v>
       </c>
       <c r="AG16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AH16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AI16" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AJ16" t="s">
         <v>132</v>
@@ -5405,19 +5465,19 @@
         <v>120</v>
       </c>
       <c r="AL16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AM16" t="s">
         <v>137</v>
       </c>
       <c r="AN16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AO16" t="s">
         <v>128</v>
       </c>
       <c r="AP16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AQ16" t="s">
         <v>125</v>
@@ -5438,7 +5498,7 @@
         <v>125</v>
       </c>
       <c r="AW16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AX16" t="s">
         <v>121</v>
@@ -5447,7 +5507,7 @@
         <v>136</v>
       </c>
       <c r="AZ16" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="BA16" t="s">
         <v>137</v>
@@ -5459,19 +5519,28 @@
         <v>132</v>
       </c>
       <c r="BD16" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>147</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>147</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>147</v>
       </c>
       <c r="BK16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="BM16" t="s">
         <v>124</v>
       </c>
       <c r="BN16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>136</v>
       </c>
@@ -5479,7 +5548,7 @@
         <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -5494,7 +5563,7 @@
         <v>126</v>
       </c>
       <c r="I17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K17" t="s">
         <v>126</v>
@@ -5503,7 +5572,7 @@
         <v>120</v>
       </c>
       <c r="N17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O17" t="s">
         <v>131</v>
@@ -5539,7 +5608,7 @@
         <v>128</v>
       </c>
       <c r="AB17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC17" t="s">
         <v>131</v>
@@ -5548,19 +5617,19 @@
         <v>122</v>
       </c>
       <c r="AE17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AF17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s">
         <v>122</v>
       </c>
       <c r="AH17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AJ17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK17" t="s">
         <v>137</v>
@@ -5569,25 +5638,25 @@
         <v>138</v>
       </c>
       <c r="AM17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AN17" t="s">
         <v>131</v>
       </c>
       <c r="AO17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AP17" t="s">
         <v>119</v>
       </c>
       <c r="AQ17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AR17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AS17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AT17" t="s">
         <v>111</v>
@@ -5596,7 +5665,7 @@
         <v>122</v>
       </c>
       <c r="AV17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AW17" t="s">
         <v>94</v>
@@ -5605,66 +5674,69 @@
         <v>120</v>
       </c>
       <c r="AY17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AZ17" t="s">
         <v>120</v>
       </c>
       <c r="BA17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BB17" t="s">
         <v>121</v>
       </c>
       <c r="BC17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BD17" t="s">
         <v>119</v>
       </c>
+      <c r="BE17" t="s">
+        <v>161</v>
+      </c>
       <c r="BK17" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="BM17" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s">
         <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
         <v>136</v>
       </c>
       <c r="F18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H18" t="s">
         <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O18" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="P18" t="s">
         <v>121</v>
@@ -5697,13 +5769,13 @@
         <v>131</v>
       </c>
       <c r="AB18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AC18" t="s">
         <v>136</v>
       </c>
       <c r="AD18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AE18" t="s">
         <v>135</v>
@@ -5712,19 +5784,19 @@
         <v>126</v>
       </c>
       <c r="AG18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AH18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AK18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AL18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AM18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="s">
         <v>128</v>
@@ -5736,13 +5808,13 @@
         <v>128</v>
       </c>
       <c r="AQ18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AR18" t="s">
         <v>91</v>
       </c>
       <c r="AS18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AT18" t="s">
         <v>121</v>
@@ -5754,39 +5826,39 @@
         <v>132</v>
       </c>
       <c r="AW18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AX18" t="s">
         <v>130</v>
       </c>
       <c r="AY18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AZ18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="BA18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="BB18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BC18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BD18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BK18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="BM18" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
         <v>138</v>
@@ -5795,7 +5867,7 @@
         <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
         <v>119</v>
@@ -5804,28 +5876,28 @@
         <v>127</v>
       </c>
       <c r="H19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s">
         <v>126</v>
       </c>
       <c r="L19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q19" t="s">
         <v>128</v>
       </c>
       <c r="R19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S19" t="s">
         <v>121</v>
@@ -5843,7 +5915,7 @@
         <v>131</v>
       </c>
       <c r="Z19" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AA19" t="s">
         <v>122</v>
@@ -5855,10 +5927,13 @@
         <v>119</v>
       </c>
       <c r="AD19" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>139</v>
       </c>
       <c r="AF19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AG19" t="s">
         <v>124</v>
@@ -5867,31 +5942,31 @@
         <v>126</v>
       </c>
       <c r="AK19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AL19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AM19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN19" t="s">
         <v>136</v>
       </c>
       <c r="AO19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AP19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AQ19" t="s">
+        <v>143</v>
+      </c>
+      <c r="AR19" t="s">
         <v>142</v>
       </c>
-      <c r="AR19" t="s">
-        <v>141</v>
-      </c>
       <c r="AS19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AT19" t="s">
         <v>120</v>
@@ -5900,10 +5975,10 @@
         <v>135</v>
       </c>
       <c r="AV19" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AW19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AX19" t="s">
         <v>136</v>
@@ -5912,30 +5987,30 @@
         <v>138</v>
       </c>
       <c r="AZ19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BA19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BB19" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="BC19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="BD19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="BK19" t="s">
         <v>138</v>
       </c>
       <c r="BM19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
         <v>127</v>
@@ -5947,16 +6022,16 @@
         <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I20" t="s">
         <v>124</v>
       </c>
       <c r="L20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N20" t="s">
         <v>124</v>
@@ -5971,13 +6046,13 @@
         <v>122</v>
       </c>
       <c r="R20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S20" t="s">
         <v>94</v>
       </c>
       <c r="T20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="U20" t="s">
         <v>109</v>
@@ -5992,37 +6067,40 @@
         <v>119</v>
       </c>
       <c r="AA20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AB20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AC20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AD20" t="s">
         <v>127</v>
       </c>
+      <c r="AE20" t="s">
+        <v>149</v>
+      </c>
       <c r="AF20" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AG20" t="s">
         <v>138</v>
       </c>
       <c r="AH20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s">
         <v>122</v>
       </c>
       <c r="AL20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AM20" t="s">
         <v>126</v>
       </c>
       <c r="AN20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AO20" t="s">
         <v>126</v>
@@ -6031,17 +6109,20 @@
         <v>138</v>
       </c>
       <c r="AQ20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AR20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AS20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AT20" t="s">
         <v>130</v>
       </c>
+      <c r="AU20" t="s">
+        <v>157</v>
+      </c>
       <c r="AW20" t="s">
         <v>122</v>
       </c>
@@ -6049,13 +6130,13 @@
         <v>119</v>
       </c>
       <c r="AY20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AZ20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BA20" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="BB20" t="s">
         <v>128</v>
@@ -6064,21 +6145,21 @@
         <v>135</v>
       </c>
       <c r="BD20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BK20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="BM20" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
         <v>124</v>
@@ -6093,10 +6174,10 @@
         <v>138</v>
       </c>
       <c r="O21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q21" t="s">
         <v>132</v>
@@ -6105,67 +6186,73 @@
         <v>104</v>
       </c>
       <c r="S21" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T21" t="s">
         <v>124</v>
       </c>
       <c r="U21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="V21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="W21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Z21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AA21" t="s">
         <v>138</v>
       </c>
       <c r="AB21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AC21" t="s">
         <v>124</v>
       </c>
       <c r="AG21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AH21" t="s">
         <v>124</v>
       </c>
       <c r="AK21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AL21" t="s">
         <v>127</v>
       </c>
       <c r="AM21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AN21" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AO21" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AP21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AR21" t="s">
         <v>120</v>
       </c>
+      <c r="AS21" t="s">
+        <v>157</v>
+      </c>
       <c r="AT21" t="s">
         <v>136</v>
       </c>
+      <c r="AU21" t="s">
+        <v>147</v>
+      </c>
       <c r="AW21" t="s">
         <v>124</v>
       </c>
       <c r="AX21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AZ21" t="s">
         <v>126</v>
@@ -6174,18 +6261,24 @@
         <v>119</v>
       </c>
       <c r="BB21" t="s">
-        <v>152</v>
+        <v>155</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>157</v>
       </c>
       <c r="BD21" t="s">
         <v>127</v>
       </c>
+      <c r="BM21" t="s">
+        <v>157</v>
+      </c>
     </row>
-    <row r="22" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
         <v>138</v>
@@ -6194,19 +6287,19 @@
         <v>127</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N22" t="s">
+        <v>163</v>
+      </c>
+      <c r="O22" t="s">
+        <v>145</v>
+      </c>
+      <c r="P22" t="s">
         <v>158</v>
       </c>
-      <c r="O22" t="s">
+      <c r="Q22" t="s">
         <v>144</v>
-      </c>
-      <c r="P22" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>143</v>
       </c>
       <c r="R22" t="s">
         <v>122</v>
@@ -6215,16 +6308,16 @@
         <v>128</v>
       </c>
       <c r="T22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="U22" t="s">
         <v>136</v>
       </c>
       <c r="V22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="W22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Z22" t="s">
         <v>124</v>
@@ -6233,10 +6326,10 @@
         <v>127</v>
       </c>
       <c r="AB22" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AC22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s">
         <v>127</v>
@@ -6245,19 +6338,22 @@
         <v>138</v>
       </c>
       <c r="AK22" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>157</v>
       </c>
       <c r="AM22" t="s">
         <v>124</v>
       </c>
       <c r="AN22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AO22" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AR22" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AT22" t="s">
         <v>119</v>
@@ -6269,16 +6365,22 @@
         <v>138</v>
       </c>
       <c r="AZ22" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA22" t="s">
+        <v>148</v>
+      </c>
+      <c r="BB22" t="s">
+        <v>162</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BM22" t="s">
         <v>147</v>
       </c>
-      <c r="BA22" t="s">
-        <v>146</v>
-      </c>
-      <c r="BB22" t="s">
-        <v>157</v>
-      </c>
     </row>
-    <row r="23" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -6286,22 +6388,25 @@
         <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="E23" t="s">
+        <v>139</v>
       </c>
       <c r="I23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P23" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q23" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R23" t="s">
         <v>132</v>
       </c>
       <c r="S23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="T23" t="s">
         <v>135</v>
@@ -6310,7 +6415,7 @@
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="W23" t="s">
         <v>138</v>
@@ -6318,8 +6423,14 @@
       <c r="Z23" t="s">
         <v>138</v>
       </c>
+      <c r="AB23" t="s">
+        <v>157</v>
+      </c>
       <c r="AC23" t="s">
-        <v>158</v>
+        <v>163</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>139</v>
       </c>
       <c r="AH23" t="s">
         <v>135</v>
@@ -6327,102 +6438,135 @@
       <c r="AK23" t="s">
         <v>138</v>
       </c>
+      <c r="AL23" t="s">
+        <v>139</v>
+      </c>
       <c r="AM23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AN23" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AO23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AR23" t="s">
         <v>126</v>
       </c>
       <c r="AT23" t="s">
+        <v>162</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>153</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>153</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>150</v>
+      </c>
+      <c r="BB23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="s">
         <v>157</v>
       </c>
-      <c r="AX23" t="s">
-        <v>150</v>
-      </c>
-      <c r="AZ23" t="s">
-        <v>150</v>
-      </c>
-      <c r="BA23" t="s">
-        <v>147</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>149</v>
+      </c>
       <c r="I24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P24" t="s">
         <v>124</v>
       </c>
       <c r="Q24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S24" t="s">
         <v>122</v>
       </c>
       <c r="U24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="V24" t="s">
         <v>127</v>
       </c>
       <c r="W24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z24" t="s">
         <v>135</v>
       </c>
+      <c r="AB24" t="s">
+        <v>147</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>147</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>157</v>
+      </c>
       <c r="AK24" t="s">
-        <v>158</v>
+        <v>163</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>161</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>157</v>
       </c>
       <c r="AN24" t="s">
         <v>138</v>
       </c>
       <c r="AO24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AR24" t="s">
         <v>124</v>
       </c>
       <c r="AT24" t="s">
+        <v>144</v>
+      </c>
+      <c r="AX24" t="s">
         <v>143</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>142</v>
       </c>
       <c r="AZ24" t="s">
         <v>138</v>
       </c>
       <c r="BA24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BB24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" t="s">
+        <v>147</v>
+      </c>
       <c r="I25" t="s">
         <v>127</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="R25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="U25" t="s">
         <v>124</v>
@@ -6430,72 +6574,114 @@
       <c r="W25" t="s">
         <v>127</v>
       </c>
+      <c r="AG25" t="s">
+        <v>149</v>
+      </c>
       <c r="AK25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AN25" t="s">
         <v>135</v>
       </c>
+      <c r="AO25" t="s">
+        <v>157</v>
+      </c>
       <c r="AR25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AT25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AX25" t="s">
+        <v>145</v>
+      </c>
+      <c r="AZ25" t="s">
         <v>144</v>
       </c>
-      <c r="AZ25" t="s">
+      <c r="BA25" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>157</v>
+      </c>
+      <c r="P26" t="s">
+        <v>145</v>
+      </c>
+      <c r="R26" t="s">
+        <v>159</v>
+      </c>
+      <c r="S26" t="s">
         <v>143</v>
       </c>
-      <c r="BA25" t="s">
-        <v>150</v>
-      </c>
-      <c r="BB25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" spans="1:65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" t="s">
-        <v>144</v>
-      </c>
-      <c r="R26" t="s">
-        <v>155</v>
-      </c>
-      <c r="S26" t="s">
-        <v>142</v>
-      </c>
       <c r="U26" t="s">
-        <v>150</v>
+        <v>153</v>
+      </c>
+      <c r="W26" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>139</v>
       </c>
       <c r="AR26" t="s">
         <v>135</v>
       </c>
       <c r="AT26" t="s">
-        <v>150</v>
+        <v>153</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>139</v>
       </c>
       <c r="AZ26" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="BA26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BB26" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="9:54" x14ac:dyDescent="0.25">
+      <c r="I27" t="s">
+        <v>147</v>
+      </c>
       <c r="R27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S27" t="s">
         <v>138</v>
       </c>
       <c r="U27" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="W27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>147</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>161</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>139</v>
       </c>
       <c r="AT27" t="s">
-        <v>158</v>
+        <v>163</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>147</v>
       </c>
       <c r="AZ27" t="s">
         <v>127</v>
@@ -6504,23 +6690,74 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="9:53" x14ac:dyDescent="0.25">
       <c r="R28" t="s">
         <v>127</v>
       </c>
       <c r="S28" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>161</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ28" t="s">
+        <v>157</v>
+      </c>
+      <c r="BA28" t="s">
+        <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
       <c r="R29" t="s">
         <v>135</v>
       </c>
+      <c r="S29" t="s">
+        <v>157</v>
+      </c>
+      <c r="AZ29" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA29" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="30" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+      <c r="R30" t="s">
+        <v>139</v>
+      </c>
+      <c r="S30" t="s">
+        <v>139</v>
+      </c>
+      <c r="AZ30" t="s">
+        <v>149</v>
+      </c>
+      <c r="BA30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="18:53" x14ac:dyDescent="0.25">
+      <c r="R31" t="s">
+        <v>147</v>
+      </c>
+      <c r="S31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" spans="18:19" x14ac:dyDescent="0.25">
+      <c r="R32" t="s">
+        <v>149</v>
+      </c>
+      <c r="S32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="18:19" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6563,19 +6800,19 @@
     <row r="73" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="A4:XFD32">
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>A4 &gt; "2025-03-05"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A3:CH42"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:CM42"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -6623,7 +6860,7 @@
     <col min="83" max="83" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -6721,7 +6958,7 @@
         <v>107</v>
       </c>
       <c r="AG3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH3" t="s">
         <v>116</v>
@@ -6775,7 +7012,7 @@
         <v>112</v>
       </c>
       <c r="AY3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AZ3" t="s">
         <v>121</v>
@@ -6790,28 +7027,28 @@
         <v>120</v>
       </c>
       <c r="BD3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BE3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="BF3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="BG3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
       </c>
       <c r="BI3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="BJ3" t="s">
         <v>131</v>
       </c>
       <c r="BK3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BL3" t="s">
         <v>130</v>
@@ -6823,16 +7060,16 @@
         <v>136</v>
       </c>
       <c r="BO3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="BP3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="BQ3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BR3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="BS3" t="s">
         <v>119</v>
@@ -6847,34 +7084,34 @@
         <v>126</v>
       </c>
       <c r="BW3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="BX3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="BY3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BZ3" t="s">
         <v>124</v>
       </c>
       <c r="CA3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="CB3" t="s">
         <v>138</v>
       </c>
       <c r="CC3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="CD3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="CE3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="CF3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="CG3" t="s">
         <v>127</v>
@@ -6882,8 +7119,23 @@
       <c r="CH3" t="s">
         <v>135</v>
       </c>
+      <c r="CI3" t="s">
+        <v>157</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>139</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>147</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>161</v>
+      </c>
     </row>
-    <row r="4" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -7142,8 +7394,23 @@
       <c r="CH4" t="s">
         <v>47</v>
       </c>
+      <c r="CI4" t="s">
+        <v>6</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>58</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>21</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>56</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="5" spans="1:86" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7402,8 +7669,23 @@
       